--- a/data/gas_prices.xlsx
+++ b/data/gas_prices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I641"/>
+  <dimension ref="A1:I701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25392,10 +25392,8 @@
       </c>
     </row>
     <row r="622">
-      <c r="A622" t="inlineStr">
-        <is>
-          <t>65515</t>
-        </is>
+      <c r="A622" t="n">
+        <v>65515</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
@@ -25435,10 +25433,8 @@
       </c>
     </row>
     <row r="623">
-      <c r="A623" t="inlineStr">
-        <is>
-          <t>77205</t>
-        </is>
+      <c r="A623" t="n">
+        <v>77205</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
@@ -25478,10 +25474,8 @@
       </c>
     </row>
     <row r="624">
-      <c r="A624" t="inlineStr">
-        <is>
-          <t>77223</t>
-        </is>
+      <c r="A624" t="n">
+        <v>77223</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
@@ -25509,10 +25503,8 @@
       <c r="I624" t="inlineStr"/>
     </row>
     <row r="625">
-      <c r="A625" t="inlineStr">
-        <is>
-          <t>65514</t>
-        </is>
+      <c r="A625" t="n">
+        <v>65514</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
@@ -25552,10 +25544,8 @@
       </c>
     </row>
     <row r="626">
-      <c r="A626" t="inlineStr">
-        <is>
-          <t>77232</t>
-        </is>
+      <c r="A626" t="n">
+        <v>77232</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
@@ -25595,10 +25585,8 @@
       </c>
     </row>
     <row r="627">
-      <c r="A627" t="inlineStr">
-        <is>
-          <t>77202</t>
-        </is>
+      <c r="A627" t="n">
+        <v>77202</v>
       </c>
       <c r="B627" t="inlineStr">
         <is>
@@ -25638,10 +25626,8 @@
       </c>
     </row>
     <row r="628">
-      <c r="A628" t="inlineStr">
-        <is>
-          <t>86650</t>
-        </is>
+      <c r="A628" t="n">
+        <v>86650</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
@@ -25681,10 +25667,8 @@
       </c>
     </row>
     <row r="629">
-      <c r="A629" t="inlineStr">
-        <is>
-          <t>77218</t>
-        </is>
+      <c r="A629" t="n">
+        <v>77218</v>
       </c>
       <c r="B629" t="inlineStr">
         <is>
@@ -25724,10 +25708,8 @@
       </c>
     </row>
     <row r="630">
-      <c r="A630" t="inlineStr">
-        <is>
-          <t>77243</t>
-        </is>
+      <c r="A630" t="n">
+        <v>77243</v>
       </c>
       <c r="B630" t="inlineStr">
         <is>
@@ -25767,10 +25749,8 @@
       </c>
     </row>
     <row r="631">
-      <c r="A631" t="inlineStr">
-        <is>
-          <t>77235</t>
-        </is>
+      <c r="A631" t="n">
+        <v>77235</v>
       </c>
       <c r="B631" t="inlineStr">
         <is>
@@ -25810,10 +25790,8 @@
       </c>
     </row>
     <row r="632">
-      <c r="A632" t="inlineStr">
-        <is>
-          <t>77228</t>
-        </is>
+      <c r="A632" t="n">
+        <v>77228</v>
       </c>
       <c r="B632" t="inlineStr">
         <is>
@@ -25853,10 +25831,8 @@
       </c>
     </row>
     <row r="633">
-      <c r="A633" t="inlineStr">
-        <is>
-          <t>69163</t>
-        </is>
+      <c r="A633" t="n">
+        <v>69163</v>
       </c>
       <c r="B633" t="inlineStr">
         <is>
@@ -25896,10 +25872,8 @@
       </c>
     </row>
     <row r="634">
-      <c r="A634" t="inlineStr">
-        <is>
-          <t>109205</t>
-        </is>
+      <c r="A634" t="n">
+        <v>109205</v>
       </c>
       <c r="B634" t="inlineStr">
         <is>
@@ -25939,10 +25913,8 @@
       </c>
     </row>
     <row r="635">
-      <c r="A635" t="inlineStr">
-        <is>
-          <t>65512</t>
-        </is>
+      <c r="A635" t="n">
+        <v>65512</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
@@ -25982,10 +25954,8 @@
       </c>
     </row>
     <row r="636">
-      <c r="A636" t="inlineStr">
-        <is>
-          <t>83384</t>
-        </is>
+      <c r="A636" t="n">
+        <v>83384</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
@@ -26025,10 +25995,8 @@
       </c>
     </row>
     <row r="637">
-      <c r="A637" t="inlineStr">
-        <is>
-          <t>77015</t>
-        </is>
+      <c r="A637" t="n">
+        <v>77015</v>
       </c>
       <c r="B637" t="inlineStr">
         <is>
@@ -26068,10 +26036,8 @@
       </c>
     </row>
     <row r="638">
-      <c r="A638" t="inlineStr">
-        <is>
-          <t>107728</t>
-        </is>
+      <c r="A638" t="n">
+        <v>107728</v>
       </c>
       <c r="B638" t="inlineStr">
         <is>
@@ -26111,10 +26077,8 @@
       </c>
     </row>
     <row r="639">
-      <c r="A639" t="inlineStr">
-        <is>
-          <t>65572</t>
-        </is>
+      <c r="A639" t="n">
+        <v>65572</v>
       </c>
       <c r="B639" t="inlineStr">
         <is>
@@ -26154,10 +26118,8 @@
       </c>
     </row>
     <row r="640">
-      <c r="A640" t="inlineStr">
-        <is>
-          <t>65511</t>
-        </is>
+      <c r="A640" t="n">
+        <v>65511</v>
       </c>
       <c r="B640" t="inlineStr">
         <is>
@@ -26197,10 +26159,8 @@
       </c>
     </row>
     <row r="641">
-      <c r="A641" t="inlineStr">
-        <is>
-          <t>65556</t>
-        </is>
+      <c r="A641" t="n">
+        <v>65556</v>
       </c>
       <c r="B641" t="inlineStr">
         <is>
@@ -26237,6 +26197,2374 @@
       </c>
       <c r="I641" t="n">
         <v>184.9</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="n">
+        <v>65542</v>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>3250 MacDonald St</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2573819, 'Longitude': -123.1680407}</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:38:53</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:45:00.108Z</t>
+        </is>
+      </c>
+      <c r="G642" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>2025-08-18T20:00:38.663Z</t>
+        </is>
+      </c>
+      <c r="I642" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="n">
+        <v>65533</v>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>4615 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2449719, 'Longitude': -123.1540385}</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:38:53</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:41:12.206Z</t>
+        </is>
+      </c>
+      <c r="G643" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>2025-08-18T20:01:38.582Z</t>
+        </is>
+      </c>
+      <c r="I643" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="n">
+        <v>83068</v>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>3205 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.256927568207, 'Longitude': -123.153288960457}</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:38:53</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr"/>
+      <c r="G644" t="inlineStr"/>
+      <c r="H644" t="inlineStr"/>
+      <c r="I644" t="inlineStr"/>
+    </row>
+    <row r="645">
+      <c r="A645" t="n">
+        <v>65562</v>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>2808 W Broadway</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263883932125, 'Longitude': -123.168604373932}</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:38:53</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:17:36.374Z</t>
+        </is>
+      </c>
+      <c r="G645" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:17:36.405Z</t>
+        </is>
+      </c>
+      <c r="I645" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="n">
+        <v>113305</v>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>3596 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234385296079, 'Longitude': -123.184762001038}</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:38:53</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:29:29.571Z</t>
+        </is>
+      </c>
+      <c r="G646" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H646" t="inlineStr"/>
+      <c r="I646" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:38:53</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:35:04.188Z</t>
+        </is>
+      </c>
+      <c r="G647" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>2025-08-19T17:50:59.425Z</t>
+        </is>
+      </c>
+      <c r="I647" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="n">
+        <v>65554</v>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>1795 W Broadway</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264037962303, 'Longitude': -123.145408630371}</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:38:53</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:33:38.071Z</t>
+        </is>
+      </c>
+      <c r="G648" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:44:20.091Z</t>
+        </is>
+      </c>
+      <c r="I648" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="n">
+        <v>65571</v>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>4314 W 10th Ave</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263533861752, 'Longitude': -123.203430175781}</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:38:53</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>2025-08-19T21:12:07.564Z</t>
+        </is>
+      </c>
+      <c r="G649" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>2025-08-19T16:29:09.259Z</t>
+        </is>
+      </c>
+      <c r="I649" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:38:53</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:51:14.843Z</t>
+        </is>
+      </c>
+      <c r="G650" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H650" t="inlineStr"/>
+      <c r="I650" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="n">
+        <v>32376</v>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>1503 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234634576953, 'Longitude': -123.139971792698}</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:38:53</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:47:31.224Z</t>
+        </is>
+      </c>
+      <c r="G651" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:30:08.915Z</t>
+        </is>
+      </c>
+      <c r="I651" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="n">
+        <v>65549</v>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>5702 Granville St</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234036184118, 'Longitude': -123.139244914055}</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:38:53</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:29:49.623Z</t>
+        </is>
+      </c>
+      <c r="G652" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:13:29.302Z</t>
+        </is>
+      </c>
+      <c r="I652" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:38:53</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:51:31.870Z</t>
+        </is>
+      </c>
+      <c r="G653" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:57:09.641Z</t>
+        </is>
+      </c>
+      <c r="I653" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:38:53</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:51:19.264Z</t>
+        </is>
+      </c>
+      <c r="G654" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:53:03.891Z</t>
+        </is>
+      </c>
+      <c r="I654" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="n">
+        <v>72747</v>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>1010 W King Edward Ave</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249188, 'Longitude': -123.127767}</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:38:53</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:43:58.820Z</t>
+        </is>
+      </c>
+      <c r="G655" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:43:58.867Z</t>
+        </is>
+      </c>
+      <c r="I655" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="n">
+        <v>32375</v>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>4110 Oak St</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.24894071957, 'Longitude': -123.127040863037}</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:38:53</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:16:00.265Z</t>
+        </is>
+      </c>
+      <c r="G656" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:13:19.073Z</t>
+        </is>
+      </c>
+      <c r="I656" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="n">
+        <v>65564</v>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>5680 Oak St</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234217162181, 'Longitude': -123.127684593201}</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:38:53</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:14:02.226Z</t>
+        </is>
+      </c>
+      <c r="G657" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:12:49.425Z</t>
+        </is>
+      </c>
+      <c r="I657" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="n">
+        <v>32372</v>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>6525 Oak St</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226226639452, 'Longitude': -123.128687739372}</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:38:53</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:15:00.452Z</t>
+        </is>
+      </c>
+      <c r="G658" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:29:56.703Z</t>
+        </is>
+      </c>
+      <c r="I658" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:38:53</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:44:10.433Z</t>
+        </is>
+      </c>
+      <c r="G659" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:44:10.464Z</t>
+        </is>
+      </c>
+      <c r="I659" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="n">
+        <v>65566</v>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>8072 Granville St</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.212495055855, 'Longitude': -123.14013004303}</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:38:53</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:28:24.653Z</t>
+        </is>
+      </c>
+      <c r="G660" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:30:08.359Z</t>
+        </is>
+      </c>
+      <c r="I660" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="n">
+        <v>65572</v>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:38:53</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:07:36.107Z</t>
+        </is>
+      </c>
+      <c r="G661" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:31:11.263Z</t>
+        </is>
+      </c>
+      <c r="I661" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="n">
+        <v>65558</v>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>1390 E 33rd Ave</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.240045470021, 'Longitude': -123.076765537262}</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:40:16</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:29:52.466Z</t>
+        </is>
+      </c>
+      <c r="G662" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:21:41.203Z</t>
+        </is>
+      </c>
+      <c r="I662" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="n">
+        <v>83394</v>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>4064 Fraser St</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.248864, 'Longitude': -123.09002}</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:40:16</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:12:27.452Z</t>
+        </is>
+      </c>
+      <c r="G663" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:01:42.428Z</t>
+        </is>
+      </c>
+      <c r="I663" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="n">
+        <v>65573</v>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>1396 E 41st Ave</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.232593005895, 'Longitude': -123.07728856802}</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:40:16</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:48:05.113Z</t>
+        </is>
+      </c>
+      <c r="G664" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>2025-08-19T12:24:57.478Z</t>
+        </is>
+      </c>
+      <c r="I664" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="n">
+        <v>80714</v>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Husky</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>4933 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2397388, 'Longitude': -123.065748}</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:40:16</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:42:20.723Z</t>
+        </is>
+      </c>
+      <c r="G665" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:53:12.369Z</t>
+        </is>
+      </c>
+      <c r="I665" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="n">
+        <v>65552</v>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>2001 Kingsway</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.245312771918, 'Longitude': -123.064910173416}</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:40:16</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:22:00.873Z</t>
+        </is>
+      </c>
+      <c r="G666" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:22:00.919Z</t>
+        </is>
+      </c>
+      <c r="I666" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="n">
+        <v>65538</v>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>5252 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2372145, 'Longitude': -123.0650857}</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:40:16</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:42:46.627Z</t>
+        </is>
+      </c>
+      <c r="G667" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:06:44.322Z</t>
+        </is>
+      </c>
+      <c r="I667" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="n">
+        <v>90814</v>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>2277 Kingsway</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.242132845692, 'Longitude': -123.058204650879}</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:40:16</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:52:59.976Z</t>
+        </is>
+      </c>
+      <c r="G668" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:53:00.012Z</t>
+        </is>
+      </c>
+      <c r="I668" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="n">
+        <v>39768</v>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>5736 Main St</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2325708, 'Longitude': -123.1010069}</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:40:16</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:55:11.332Z</t>
+        </is>
+      </c>
+      <c r="G669" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:38:37.384Z</t>
+        </is>
+      </c>
+      <c r="I669" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="n">
+        <v>9710</v>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>1295 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259878978744, 'Longitude': -123.078074455261}</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:40:16</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:21:28.785Z</t>
+        </is>
+      </c>
+      <c r="G670" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:21:28.848Z</t>
+        </is>
+      </c>
+      <c r="I670" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="n">
+        <v>99146</v>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>1317 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259758544957, 'Longitude': -123.077272474766}</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:40:16</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:21:18.799Z</t>
+        </is>
+      </c>
+      <c r="G671" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:07:50.993Z</t>
+        </is>
+      </c>
+      <c r="I671" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="n">
+        <v>65560</v>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>1289 E Broadway</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.262693682723, 'Longitude': -123.078117370605}</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:40:16</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:21:17.777Z</t>
+        </is>
+      </c>
+      <c r="G672" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:07:33.651Z</t>
+        </is>
+      </c>
+      <c r="I672" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="n">
+        <v>65557</v>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>2120 Grandview Hwy S</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2591601, 'Longitude': -123.0617495}</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:40:16</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:24:44.518Z</t>
+        </is>
+      </c>
+      <c r="G673" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:24:48.707Z</t>
+        </is>
+      </c>
+      <c r="I673" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="n">
+        <v>71502</v>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>2748 Main St</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2604441, 'Longitude': -123.1005869}</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:40:16</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:26:29.676Z</t>
+        </is>
+      </c>
+      <c r="G674" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>2025-08-19T21:21:33.123Z</t>
+        </is>
+      </c>
+      <c r="I674" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="n">
+        <v>65559</v>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>6502 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.224996944057, 'Longitude': -123.065521717072}</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:40:16</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:49:37.095Z</t>
+        </is>
+      </c>
+      <c r="G675" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:59:10.689Z</t>
+        </is>
+      </c>
+      <c r="I675" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="n">
+        <v>89943</v>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>6808 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2220242, 'Longitude': -123.0654247}</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:40:16</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:23:29.099Z</t>
+        </is>
+      </c>
+      <c r="G676" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:59:15.108Z</t>
+        </is>
+      </c>
+      <c r="I676" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:40:16</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:43:19.274Z</t>
+        </is>
+      </c>
+      <c r="G677" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>2025-08-19T15:14:14.480Z</t>
+        </is>
+      </c>
+      <c r="I677" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="n">
+        <v>65537</v>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>2918 Kingsway</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.23608, 'Longitude': -123.0454858}</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:40:16</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:26:21.446Z</t>
+        </is>
+      </c>
+      <c r="G678" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:26:21.493Z</t>
+        </is>
+      </c>
+      <c r="I678" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:40:16</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:12:58.540Z</t>
+        </is>
+      </c>
+      <c r="G679" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>2025-08-19T15:14:04.724Z</t>
+        </is>
+      </c>
+      <c r="I679" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="n">
+        <v>65535</v>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>2605 E 49th Ave</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2251291, 'Longitude': -123.0545048}</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:40:16</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:00:06.584Z</t>
+        </is>
+      </c>
+      <c r="G680" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="H680" t="inlineStr"/>
+      <c r="I680" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="n">
+        <v>65539</v>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>2902 Grandview Hwy</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2579053, 'Longitude': -123.0438464}</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:40:16</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:38:57.148Z</t>
+        </is>
+      </c>
+      <c r="G681" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:32:43.274Z</t>
+        </is>
+      </c>
+      <c r="I681" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>77015</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169873456637, 'Longitude': -123.091178619746}</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:41:32</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:31:08.938Z</t>
+        </is>
+      </c>
+      <c r="G682" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:31:09.788Z</t>
+        </is>
+      </c>
+      <c r="I682" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>65511</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:41:32</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:26:17.849Z</t>
+        </is>
+      </c>
+      <c r="G683" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:02:10.241Z</t>
+        </is>
+      </c>
+      <c r="I683" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>86650</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169856952787, 'Longitude': -123.123961687088}</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:41:32</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:43:58.858Z</t>
+        </is>
+      </c>
+      <c r="G684" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:55:51.764Z</t>
+        </is>
+      </c>
+      <c r="I684" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>77218</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.173339635958, 'Longitude': -123.124954104424}</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:41:32</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:05:36.665Z</t>
+        </is>
+      </c>
+      <c r="G685" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:05:36.774Z</t>
+        </is>
+      </c>
+      <c r="I685" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>77228</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1843249, 'Longitude': -123.1236078}</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:41:32</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:56:31.374Z</t>
+        </is>
+      </c>
+      <c r="G686" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:56:31.406Z</t>
+        </is>
+      </c>
+      <c r="I686" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>83384</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192001, 'Longitude': -123.124004}</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:41:32</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:26:37.349Z</t>
+        </is>
+      </c>
+      <c r="G687" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:33:12.509Z</t>
+        </is>
+      </c>
+      <c r="I687" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>77202</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.162989071149, 'Longitude': -123.134229183197}</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:41:32</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:33:01.855Z</t>
+        </is>
+      </c>
+      <c r="G688" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:56:29.411Z</t>
+        </is>
+      </c>
+      <c r="I688" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>77243</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.179182137142, 'Longitude': -123.137152791023}</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:41:32</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:36:53.942Z</t>
+        </is>
+      </c>
+      <c r="G689" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:24:58.074Z</t>
+        </is>
+      </c>
+      <c r="I689" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>83387</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>710 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21081995506, 'Longitude': -123.090755939484}</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:41:32</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:29:19.613Z</t>
+        </is>
+      </c>
+      <c r="G690" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:30:19.967Z</t>
+        </is>
+      </c>
+      <c r="I690" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>65551</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>688 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210798928329, 'Longitude': -123.09152841568}</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:41:32</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:32:13.071Z</t>
+        </is>
+      </c>
+      <c r="G691" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>2025-08-19T14:59:32.762Z</t>
+        </is>
+      </c>
+      <c r="I691" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>77235</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:41:32</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr"/>
+      <c r="G692" t="inlineStr"/>
+      <c r="H692" t="inlineStr"/>
+      <c r="I692" t="inlineStr"/>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>82925</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>350 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:41:32</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr"/>
+      <c r="G693" t="inlineStr"/>
+      <c r="H693" t="inlineStr"/>
+      <c r="I693" t="inlineStr"/>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>109205</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:41:32</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr"/>
+      <c r="G694" t="inlineStr"/>
+      <c r="H694" t="inlineStr"/>
+      <c r="I694" t="inlineStr"/>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>65540</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>196 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:41:32</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr"/>
+      <c r="G695" t="inlineStr"/>
+      <c r="H695" t="inlineStr"/>
+      <c r="I695" t="inlineStr"/>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>65512</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:41:32</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr"/>
+      <c r="G696" t="inlineStr"/>
+      <c r="H696" t="inlineStr"/>
+      <c r="I696" t="inlineStr"/>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>77205</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:41:32</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr"/>
+      <c r="G697" t="inlineStr"/>
+      <c r="H697" t="inlineStr"/>
+      <c r="I697" t="inlineStr"/>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>65536</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:41:32</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr"/>
+      <c r="G698" t="inlineStr"/>
+      <c r="H698" t="inlineStr"/>
+      <c r="I698" t="inlineStr"/>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>86880</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:41:32</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr"/>
+      <c r="G699" t="inlineStr"/>
+      <c r="H699" t="inlineStr"/>
+      <c r="I699" t="inlineStr"/>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>65556</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:41:32</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr"/>
+      <c r="G700" t="inlineStr"/>
+      <c r="H700" t="inlineStr"/>
+      <c r="I700" t="inlineStr"/>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>86937</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>8655 Boundary Rd</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20476, 'Longitude': -123.02398}</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>2025-08-19 22:41:32</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:08:31.375Z</t>
+        </is>
+      </c>
+      <c r="G701" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>2025-08-19T16:02:16.797Z</t>
+        </is>
+      </c>
+      <c r="I701" t="n">
+        <v>197.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/gas_prices.xlsx
+++ b/data/gas_prices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I701"/>
+  <dimension ref="A1:I721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27816,10 +27816,8 @@
       </c>
     </row>
     <row r="682">
-      <c r="A682" t="inlineStr">
-        <is>
-          <t>77015</t>
-        </is>
+      <c r="A682" t="n">
+        <v>77015</v>
       </c>
       <c r="B682" t="inlineStr">
         <is>
@@ -27859,10 +27857,8 @@
       </c>
     </row>
     <row r="683">
-      <c r="A683" t="inlineStr">
-        <is>
-          <t>65511</t>
-        </is>
+      <c r="A683" t="n">
+        <v>65511</v>
       </c>
       <c r="B683" t="inlineStr">
         <is>
@@ -27902,10 +27898,8 @@
       </c>
     </row>
     <row r="684">
-      <c r="A684" t="inlineStr">
-        <is>
-          <t>86650</t>
-        </is>
+      <c r="A684" t="n">
+        <v>86650</v>
       </c>
       <c r="B684" t="inlineStr">
         <is>
@@ -27945,10 +27939,8 @@
       </c>
     </row>
     <row r="685">
-      <c r="A685" t="inlineStr">
-        <is>
-          <t>77218</t>
-        </is>
+      <c r="A685" t="n">
+        <v>77218</v>
       </c>
       <c r="B685" t="inlineStr">
         <is>
@@ -27988,10 +27980,8 @@
       </c>
     </row>
     <row r="686">
-      <c r="A686" t="inlineStr">
-        <is>
-          <t>77228</t>
-        </is>
+      <c r="A686" t="n">
+        <v>77228</v>
       </c>
       <c r="B686" t="inlineStr">
         <is>
@@ -28031,10 +28021,8 @@
       </c>
     </row>
     <row r="687">
-      <c r="A687" t="inlineStr">
-        <is>
-          <t>83384</t>
-        </is>
+      <c r="A687" t="n">
+        <v>83384</v>
       </c>
       <c r="B687" t="inlineStr">
         <is>
@@ -28074,10 +28062,8 @@
       </c>
     </row>
     <row r="688">
-      <c r="A688" t="inlineStr">
-        <is>
-          <t>77202</t>
-        </is>
+      <c r="A688" t="n">
+        <v>77202</v>
       </c>
       <c r="B688" t="inlineStr">
         <is>
@@ -28117,10 +28103,8 @@
       </c>
     </row>
     <row r="689">
-      <c r="A689" t="inlineStr">
-        <is>
-          <t>77243</t>
-        </is>
+      <c r="A689" t="n">
+        <v>77243</v>
       </c>
       <c r="B689" t="inlineStr">
         <is>
@@ -28160,10 +28144,8 @@
       </c>
     </row>
     <row r="690">
-      <c r="A690" t="inlineStr">
-        <is>
-          <t>83387</t>
-        </is>
+      <c r="A690" t="n">
+        <v>83387</v>
       </c>
       <c r="B690" t="inlineStr">
         <is>
@@ -28203,10 +28185,8 @@
       </c>
     </row>
     <row r="691">
-      <c r="A691" t="inlineStr">
-        <is>
-          <t>65551</t>
-        </is>
+      <c r="A691" t="n">
+        <v>65551</v>
       </c>
       <c r="B691" t="inlineStr">
         <is>
@@ -28246,10 +28226,8 @@
       </c>
     </row>
     <row r="692">
-      <c r="A692" t="inlineStr">
-        <is>
-          <t>77235</t>
-        </is>
+      <c r="A692" t="n">
+        <v>77235</v>
       </c>
       <c r="B692" t="inlineStr">
         <is>
@@ -28277,10 +28255,8 @@
       <c r="I692" t="inlineStr"/>
     </row>
     <row r="693">
-      <c r="A693" t="inlineStr">
-        <is>
-          <t>82925</t>
-        </is>
+      <c r="A693" t="n">
+        <v>82925</v>
       </c>
       <c r="B693" t="inlineStr">
         <is>
@@ -28308,10 +28284,8 @@
       <c r="I693" t="inlineStr"/>
     </row>
     <row r="694">
-      <c r="A694" t="inlineStr">
-        <is>
-          <t>109205</t>
-        </is>
+      <c r="A694" t="n">
+        <v>109205</v>
       </c>
       <c r="B694" t="inlineStr">
         <is>
@@ -28339,10 +28313,8 @@
       <c r="I694" t="inlineStr"/>
     </row>
     <row r="695">
-      <c r="A695" t="inlineStr">
-        <is>
-          <t>65540</t>
-        </is>
+      <c r="A695" t="n">
+        <v>65540</v>
       </c>
       <c r="B695" t="inlineStr">
         <is>
@@ -28370,10 +28342,8 @@
       <c r="I695" t="inlineStr"/>
     </row>
     <row r="696">
-      <c r="A696" t="inlineStr">
-        <is>
-          <t>65512</t>
-        </is>
+      <c r="A696" t="n">
+        <v>65512</v>
       </c>
       <c r="B696" t="inlineStr">
         <is>
@@ -28401,10 +28371,8 @@
       <c r="I696" t="inlineStr"/>
     </row>
     <row r="697">
-      <c r="A697" t="inlineStr">
-        <is>
-          <t>77205</t>
-        </is>
+      <c r="A697" t="n">
+        <v>77205</v>
       </c>
       <c r="B697" t="inlineStr">
         <is>
@@ -28432,10 +28400,8 @@
       <c r="I697" t="inlineStr"/>
     </row>
     <row r="698">
-      <c r="A698" t="inlineStr">
-        <is>
-          <t>65536</t>
-        </is>
+      <c r="A698" t="n">
+        <v>65536</v>
       </c>
       <c r="B698" t="inlineStr">
         <is>
@@ -28463,10 +28429,8 @@
       <c r="I698" t="inlineStr"/>
     </row>
     <row r="699">
-      <c r="A699" t="inlineStr">
-        <is>
-          <t>86880</t>
-        </is>
+      <c r="A699" t="n">
+        <v>86880</v>
       </c>
       <c r="B699" t="inlineStr">
         <is>
@@ -28494,10 +28458,8 @@
       <c r="I699" t="inlineStr"/>
     </row>
     <row r="700">
-      <c r="A700" t="inlineStr">
-        <is>
-          <t>65556</t>
-        </is>
+      <c r="A700" t="n">
+        <v>65556</v>
       </c>
       <c r="B700" t="inlineStr">
         <is>
@@ -28525,10 +28487,8 @@
       <c r="I700" t="inlineStr"/>
     </row>
     <row r="701">
-      <c r="A701" t="inlineStr">
-        <is>
-          <t>86937</t>
-        </is>
+      <c r="A701" t="n">
+        <v>86937</v>
       </c>
       <c r="B701" t="inlineStr">
         <is>
@@ -28566,6 +28526,786 @@
       <c r="I701" t="n">
         <v>197.9</v>
       </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>65542</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>3250 MacDonald St</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2573819, 'Longitude': -123.1680407}</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:16:13</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:45:00.108Z</t>
+        </is>
+      </c>
+      <c r="G702" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>2025-08-18T20:00:38.663Z</t>
+        </is>
+      </c>
+      <c r="I702" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>65533</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>4615 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2449719, 'Longitude': -123.1540385}</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:16:13</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:41:12.206Z</t>
+        </is>
+      </c>
+      <c r="G703" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>2025-08-18T20:01:38.582Z</t>
+        </is>
+      </c>
+      <c r="I703" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>83068</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>3205 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.256927568207, 'Longitude': -123.153288960457}</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:16:13</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr"/>
+      <c r="G704" t="inlineStr"/>
+      <c r="H704" t="inlineStr"/>
+      <c r="I704" t="inlineStr"/>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>65562</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>2808 W Broadway</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263883932125, 'Longitude': -123.168604373932}</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:16:13</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:17:36.374Z</t>
+        </is>
+      </c>
+      <c r="G705" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:17:36.405Z</t>
+        </is>
+      </c>
+      <c r="I705" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>113305</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>3596 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234385296079, 'Longitude': -123.184762001038}</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:16:13</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:29:29.571Z</t>
+        </is>
+      </c>
+      <c r="G706" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H706" t="inlineStr"/>
+      <c r="I706" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>65570</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:16:13</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:35:04.188Z</t>
+        </is>
+      </c>
+      <c r="G707" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>2025-08-19T17:50:59.425Z</t>
+        </is>
+      </c>
+      <c r="I707" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>65554</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>1795 W Broadway</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264037962303, 'Longitude': -123.145408630371}</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:16:13</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:33:38.071Z</t>
+        </is>
+      </c>
+      <c r="G708" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:44:20.091Z</t>
+        </is>
+      </c>
+      <c r="I708" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>65571</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>4314 W 10th Ave</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263533861752, 'Longitude': -123.203430175781}</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:16:13</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>2025-08-19T21:12:07.564Z</t>
+        </is>
+      </c>
+      <c r="G709" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>2025-08-19T16:29:09.259Z</t>
+        </is>
+      </c>
+      <c r="I709" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>65565</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:16:13</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:51:14.843Z</t>
+        </is>
+      </c>
+      <c r="G710" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H710" t="inlineStr"/>
+      <c r="I710" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>32376</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>1503 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234634576953, 'Longitude': -123.139971792698}</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:16:13</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:53:01.817Z</t>
+        </is>
+      </c>
+      <c r="G711" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:30:08.915Z</t>
+        </is>
+      </c>
+      <c r="I711" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>65549</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>5702 Granville St</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234036184118, 'Longitude': -123.139244914055}</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:16:13</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:53:09.681Z</t>
+        </is>
+      </c>
+      <c r="G712" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:13:29.302Z</t>
+        </is>
+      </c>
+      <c r="I712" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>65543</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:16:13</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:51:31.870Z</t>
+        </is>
+      </c>
+      <c r="G713" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:57:09.641Z</t>
+        </is>
+      </c>
+      <c r="I713" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>65563</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:16:13</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:51:19.264Z</t>
+        </is>
+      </c>
+      <c r="G714" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:53:03.891Z</t>
+        </is>
+      </c>
+      <c r="I714" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>72747</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>1010 W King Edward Ave</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249188, 'Longitude': -123.127767}</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:16:13</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:43:58.820Z</t>
+        </is>
+      </c>
+      <c r="G715" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:43:58.867Z</t>
+        </is>
+      </c>
+      <c r="I715" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>32375</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>4110 Oak St</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.24894071957, 'Longitude': -123.127040863037}</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:16:13</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>2025-08-20T06:39:46.052Z</t>
+        </is>
+      </c>
+      <c r="G716" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:13:19.073Z</t>
+        </is>
+      </c>
+      <c r="I716" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>65564</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>5680 Oak St</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:16:13</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr"/>
+      <c r="G717" t="inlineStr"/>
+      <c r="H717" t="inlineStr"/>
+      <c r="I717" t="inlineStr"/>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>32372</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>6525 Oak St</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:16:13</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr"/>
+      <c r="G718" t="inlineStr"/>
+      <c r="H718" t="inlineStr"/>
+      <c r="I718" t="inlineStr"/>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>9707</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:16:13</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr"/>
+      <c r="G719" t="inlineStr"/>
+      <c r="H719" t="inlineStr"/>
+      <c r="I719" t="inlineStr"/>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>65566</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>8072 Granville St</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:16:13</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr"/>
+      <c r="G720" t="inlineStr"/>
+      <c r="H720" t="inlineStr"/>
+      <c r="I720" t="inlineStr"/>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>65572</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:16:13</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr"/>
+      <c r="G721" t="inlineStr"/>
+      <c r="H721" t="inlineStr"/>
+      <c r="I721" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/gas_prices.xlsx
+++ b/data/gas_prices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I721"/>
+  <dimension ref="A1:I761"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28528,10 +28528,8 @@
       </c>
     </row>
     <row r="702">
-      <c r="A702" t="inlineStr">
-        <is>
-          <t>65542</t>
-        </is>
+      <c r="A702" t="n">
+        <v>65542</v>
       </c>
       <c r="B702" t="inlineStr">
         <is>
@@ -28571,10 +28569,8 @@
       </c>
     </row>
     <row r="703">
-      <c r="A703" t="inlineStr">
-        <is>
-          <t>65533</t>
-        </is>
+      <c r="A703" t="n">
+        <v>65533</v>
       </c>
       <c r="B703" t="inlineStr">
         <is>
@@ -28614,10 +28610,8 @@
       </c>
     </row>
     <row r="704">
-      <c r="A704" t="inlineStr">
-        <is>
-          <t>83068</t>
-        </is>
+      <c r="A704" t="n">
+        <v>83068</v>
       </c>
       <c r="B704" t="inlineStr">
         <is>
@@ -28645,10 +28639,8 @@
       <c r="I704" t="inlineStr"/>
     </row>
     <row r="705">
-      <c r="A705" t="inlineStr">
-        <is>
-          <t>65562</t>
-        </is>
+      <c r="A705" t="n">
+        <v>65562</v>
       </c>
       <c r="B705" t="inlineStr">
         <is>
@@ -28688,10 +28680,8 @@
       </c>
     </row>
     <row r="706">
-      <c r="A706" t="inlineStr">
-        <is>
-          <t>113305</t>
-        </is>
+      <c r="A706" t="n">
+        <v>113305</v>
       </c>
       <c r="B706" t="inlineStr">
         <is>
@@ -28727,10 +28717,8 @@
       </c>
     </row>
     <row r="707">
-      <c r="A707" t="inlineStr">
-        <is>
-          <t>65570</t>
-        </is>
+      <c r="A707" t="n">
+        <v>65570</v>
       </c>
       <c r="B707" t="inlineStr">
         <is>
@@ -28770,10 +28758,8 @@
       </c>
     </row>
     <row r="708">
-      <c r="A708" t="inlineStr">
-        <is>
-          <t>65554</t>
-        </is>
+      <c r="A708" t="n">
+        <v>65554</v>
       </c>
       <c r="B708" t="inlineStr">
         <is>
@@ -28813,10 +28799,8 @@
       </c>
     </row>
     <row r="709">
-      <c r="A709" t="inlineStr">
-        <is>
-          <t>65571</t>
-        </is>
+      <c r="A709" t="n">
+        <v>65571</v>
       </c>
       <c r="B709" t="inlineStr">
         <is>
@@ -28856,10 +28840,8 @@
       </c>
     </row>
     <row r="710">
-      <c r="A710" t="inlineStr">
-        <is>
-          <t>65565</t>
-        </is>
+      <c r="A710" t="n">
+        <v>65565</v>
       </c>
       <c r="B710" t="inlineStr">
         <is>
@@ -28895,10 +28877,8 @@
       </c>
     </row>
     <row r="711">
-      <c r="A711" t="inlineStr">
-        <is>
-          <t>32376</t>
-        </is>
+      <c r="A711" t="n">
+        <v>32376</v>
       </c>
       <c r="B711" t="inlineStr">
         <is>
@@ -28938,10 +28918,8 @@
       </c>
     </row>
     <row r="712">
-      <c r="A712" t="inlineStr">
-        <is>
-          <t>65549</t>
-        </is>
+      <c r="A712" t="n">
+        <v>65549</v>
       </c>
       <c r="B712" t="inlineStr">
         <is>
@@ -28981,10 +28959,8 @@
       </c>
     </row>
     <row r="713">
-      <c r="A713" t="inlineStr">
-        <is>
-          <t>65543</t>
-        </is>
+      <c r="A713" t="n">
+        <v>65543</v>
       </c>
       <c r="B713" t="inlineStr">
         <is>
@@ -29024,10 +29000,8 @@
       </c>
     </row>
     <row r="714">
-      <c r="A714" t="inlineStr">
-        <is>
-          <t>65563</t>
-        </is>
+      <c r="A714" t="n">
+        <v>65563</v>
       </c>
       <c r="B714" t="inlineStr">
         <is>
@@ -29067,10 +29041,8 @@
       </c>
     </row>
     <row r="715">
-      <c r="A715" t="inlineStr">
-        <is>
-          <t>72747</t>
-        </is>
+      <c r="A715" t="n">
+        <v>72747</v>
       </c>
       <c r="B715" t="inlineStr">
         <is>
@@ -29110,10 +29082,8 @@
       </c>
     </row>
     <row r="716">
-      <c r="A716" t="inlineStr">
-        <is>
-          <t>32375</t>
-        </is>
+      <c r="A716" t="n">
+        <v>32375</v>
       </c>
       <c r="B716" t="inlineStr">
         <is>
@@ -29153,10 +29123,8 @@
       </c>
     </row>
     <row r="717">
-      <c r="A717" t="inlineStr">
-        <is>
-          <t>65564</t>
-        </is>
+      <c r="A717" t="n">
+        <v>65564</v>
       </c>
       <c r="B717" t="inlineStr">
         <is>
@@ -29184,10 +29152,8 @@
       <c r="I717" t="inlineStr"/>
     </row>
     <row r="718">
-      <c r="A718" t="inlineStr">
-        <is>
-          <t>32372</t>
-        </is>
+      <c r="A718" t="n">
+        <v>32372</v>
       </c>
       <c r="B718" t="inlineStr">
         <is>
@@ -29215,10 +29181,8 @@
       <c r="I718" t="inlineStr"/>
     </row>
     <row r="719">
-      <c r="A719" t="inlineStr">
-        <is>
-          <t>9707</t>
-        </is>
+      <c r="A719" t="n">
+        <v>9707</v>
       </c>
       <c r="B719" t="inlineStr">
         <is>
@@ -29246,10 +29210,8 @@
       <c r="I719" t="inlineStr"/>
     </row>
     <row r="720">
-      <c r="A720" t="inlineStr">
-        <is>
-          <t>65566</t>
-        </is>
+      <c r="A720" t="n">
+        <v>65566</v>
       </c>
       <c r="B720" t="inlineStr">
         <is>
@@ -29277,10 +29239,8 @@
       <c r="I720" t="inlineStr"/>
     </row>
     <row r="721">
-      <c r="A721" t="inlineStr">
-        <is>
-          <t>65572</t>
-        </is>
+      <c r="A721" t="n">
+        <v>65572</v>
       </c>
       <c r="B721" t="inlineStr">
         <is>
@@ -29307,6 +29267,1462 @@
       <c r="H721" t="inlineStr"/>
       <c r="I721" t="inlineStr"/>
     </row>
+    <row r="722">
+      <c r="A722" t="n">
+        <v>65542</v>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>3250 MacDonald St</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2573819, 'Longitude': -123.1680407}</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:33:28</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:45:00.108Z</t>
+        </is>
+      </c>
+      <c r="G722" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>2025-08-18T20:00:38.663Z</t>
+        </is>
+      </c>
+      <c r="I722" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="n">
+        <v>65533</v>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>4615 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2449719, 'Longitude': -123.1540385}</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:33:28</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:41:12.206Z</t>
+        </is>
+      </c>
+      <c r="G723" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>2025-08-18T20:01:38.582Z</t>
+        </is>
+      </c>
+      <c r="I723" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="n">
+        <v>83068</v>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>3205 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.256927568207, 'Longitude': -123.153288960457}</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:33:28</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr"/>
+      <c r="G724" t="inlineStr"/>
+      <c r="H724" t="inlineStr"/>
+      <c r="I724" t="inlineStr"/>
+    </row>
+    <row r="725">
+      <c r="A725" t="n">
+        <v>65562</v>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>2808 W Broadway</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263883932125, 'Longitude': -123.168604373932}</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:33:28</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:17:36.374Z</t>
+        </is>
+      </c>
+      <c r="G725" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:17:36.405Z</t>
+        </is>
+      </c>
+      <c r="I725" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="n">
+        <v>113305</v>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>3596 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234385296079, 'Longitude': -123.184762001038}</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:33:28</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:29:29.571Z</t>
+        </is>
+      </c>
+      <c r="G726" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H726" t="inlineStr"/>
+      <c r="I726" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:33:28</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:35:04.188Z</t>
+        </is>
+      </c>
+      <c r="G727" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>2025-08-19T17:50:59.425Z</t>
+        </is>
+      </c>
+      <c r="I727" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="n">
+        <v>65554</v>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>1795 W Broadway</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264037962303, 'Longitude': -123.145408630371}</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:33:28</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:33:38.071Z</t>
+        </is>
+      </c>
+      <c r="G728" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:44:20.091Z</t>
+        </is>
+      </c>
+      <c r="I728" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="n">
+        <v>65571</v>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>4314 W 10th Ave</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263533861752, 'Longitude': -123.203430175781}</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:33:28</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>2025-08-19T21:12:07.564Z</t>
+        </is>
+      </c>
+      <c r="G729" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>2025-08-19T16:29:09.259Z</t>
+        </is>
+      </c>
+      <c r="I729" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:33:28</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:51:14.843Z</t>
+        </is>
+      </c>
+      <c r="G730" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H730" t="inlineStr"/>
+      <c r="I730" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="n">
+        <v>32376</v>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>1503 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234634576953, 'Longitude': -123.139971792698}</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:33:28</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:53:01.817Z</t>
+        </is>
+      </c>
+      <c r="G731" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:30:08.915Z</t>
+        </is>
+      </c>
+      <c r="I731" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="n">
+        <v>65549</v>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>5702 Granville St</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234036184118, 'Longitude': -123.139244914055}</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:33:28</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:53:09.681Z</t>
+        </is>
+      </c>
+      <c r="G732" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:13:29.302Z</t>
+        </is>
+      </c>
+      <c r="I732" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:33:28</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:51:31.870Z</t>
+        </is>
+      </c>
+      <c r="G733" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:57:09.641Z</t>
+        </is>
+      </c>
+      <c r="I733" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:33:28</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:51:19.264Z</t>
+        </is>
+      </c>
+      <c r="G734" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:53:03.891Z</t>
+        </is>
+      </c>
+      <c r="I734" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="n">
+        <v>72747</v>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>1010 W King Edward Ave</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249188, 'Longitude': -123.127767}</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:33:28</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:43:58.820Z</t>
+        </is>
+      </c>
+      <c r="G735" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:43:58.867Z</t>
+        </is>
+      </c>
+      <c r="I735" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="n">
+        <v>32375</v>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>4110 Oak St</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.24894071957, 'Longitude': -123.127040863037}</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:33:28</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>2025-08-20T06:39:46.052Z</t>
+        </is>
+      </c>
+      <c r="G736" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:13:19.073Z</t>
+        </is>
+      </c>
+      <c r="I736" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="n">
+        <v>65564</v>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>5680 Oak St</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234217162181, 'Longitude': -123.127684593201}</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:33:28</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:14:02.226Z</t>
+        </is>
+      </c>
+      <c r="G737" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:12:49.425Z</t>
+        </is>
+      </c>
+      <c r="I737" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="n">
+        <v>32372</v>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>6525 Oak St</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226226639452, 'Longitude': -123.128687739372}</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:33:28</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:15:00.452Z</t>
+        </is>
+      </c>
+      <c r="G738" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:29:56.703Z</t>
+        </is>
+      </c>
+      <c r="I738" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:33:28</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:44:10.433Z</t>
+        </is>
+      </c>
+      <c r="G739" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:44:10.464Z</t>
+        </is>
+      </c>
+      <c r="I739" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="n">
+        <v>65566</v>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>8072 Granville St</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.212495055855, 'Longitude': -123.14013004303}</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:33:28</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:28:24.653Z</t>
+        </is>
+      </c>
+      <c r="G740" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:30:08.359Z</t>
+        </is>
+      </c>
+      <c r="I740" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="n">
+        <v>65572</v>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:33:28</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>2025-08-20T06:38:38.123Z</t>
+        </is>
+      </c>
+      <c r="G741" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:31:11.263Z</t>
+        </is>
+      </c>
+      <c r="I741" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>65558</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>1390 E 33rd Ave</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.240045470021, 'Longitude': -123.076765537262}</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:34:45</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>2025-08-20T06:50:15.993Z</t>
+        </is>
+      </c>
+      <c r="G742" t="n">
+        <v>168</v>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:59:17.385Z</t>
+        </is>
+      </c>
+      <c r="I742" t="n">
+        <v>178.9</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>83394</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>4064 Fraser St</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.248864, 'Longitude': -123.09002}</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:34:45</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:12:27.452Z</t>
+        </is>
+      </c>
+      <c r="G743" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:01:42.428Z</t>
+        </is>
+      </c>
+      <c r="I743" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>65573</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>1396 E 41st Ave</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.232593005895, 'Longitude': -123.07728856802}</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:34:45</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>2025-08-20T07:11:03.641Z</t>
+        </is>
+      </c>
+      <c r="G744" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>2025-08-20T07:11:03.688Z</t>
+        </is>
+      </c>
+      <c r="I744" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>80714</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Husky</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>4933 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:34:45</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr"/>
+      <c r="G745" t="inlineStr"/>
+      <c r="H745" t="inlineStr"/>
+      <c r="I745" t="inlineStr"/>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>65552</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>2001 Kingsway</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:34:45</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr"/>
+      <c r="G746" t="inlineStr"/>
+      <c r="H746" t="inlineStr"/>
+      <c r="I746" t="inlineStr"/>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>65538</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>5252 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:34:45</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr"/>
+      <c r="G747" t="inlineStr"/>
+      <c r="H747" t="inlineStr"/>
+      <c r="I747" t="inlineStr"/>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>90814</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>2277 Kingsway</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:34:45</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr"/>
+      <c r="G748" t="inlineStr"/>
+      <c r="H748" t="inlineStr"/>
+      <c r="I748" t="inlineStr"/>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>39768</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>5736 Main St</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:34:45</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr"/>
+      <c r="G749" t="inlineStr"/>
+      <c r="H749" t="inlineStr"/>
+      <c r="I749" t="inlineStr"/>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>9710</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>1295 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:34:45</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr"/>
+      <c r="G750" t="inlineStr"/>
+      <c r="H750" t="inlineStr"/>
+      <c r="I750" t="inlineStr"/>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>99146</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>1317 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:34:45</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr"/>
+      <c r="G751" t="inlineStr"/>
+      <c r="H751" t="inlineStr"/>
+      <c r="I751" t="inlineStr"/>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>65560</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>1289 E Broadway</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:34:45</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr"/>
+      <c r="G752" t="inlineStr"/>
+      <c r="H752" t="inlineStr"/>
+      <c r="I752" t="inlineStr"/>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>65557</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>2120 Grandview Hwy S</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:34:45</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr"/>
+      <c r="G753" t="inlineStr"/>
+      <c r="H753" t="inlineStr"/>
+      <c r="I753" t="inlineStr"/>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>71502</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>2748 Main St</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:34:45</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr"/>
+      <c r="G754" t="inlineStr"/>
+      <c r="H754" t="inlineStr"/>
+      <c r="I754" t="inlineStr"/>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>65559</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>6502 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:34:45</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr"/>
+      <c r="G755" t="inlineStr"/>
+      <c r="H755" t="inlineStr"/>
+      <c r="I755" t="inlineStr"/>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>89943</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>6808 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:34:45</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr"/>
+      <c r="G756" t="inlineStr"/>
+      <c r="H756" t="inlineStr"/>
+      <c r="I756" t="inlineStr"/>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>86880</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:34:45</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr"/>
+      <c r="G757" t="inlineStr"/>
+      <c r="H757" t="inlineStr"/>
+      <c r="I757" t="inlineStr"/>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>65537</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>2918 Kingsway</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:34:45</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr"/>
+      <c r="G758" t="inlineStr"/>
+      <c r="H758" t="inlineStr"/>
+      <c r="I758" t="inlineStr"/>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>65536</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:34:45</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr"/>
+      <c r="G759" t="inlineStr"/>
+      <c r="H759" t="inlineStr"/>
+      <c r="I759" t="inlineStr"/>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>65535</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>2605 E 49th Ave</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:34:45</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr"/>
+      <c r="G760" t="inlineStr"/>
+      <c r="H760" t="inlineStr"/>
+      <c r="I760" t="inlineStr"/>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>65539</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>2902 Grandview Hwy</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>2025-08-20 02:34:45</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr"/>
+      <c r="G761" t="inlineStr"/>
+      <c r="H761" t="inlineStr"/>
+      <c r="I761" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gas_prices.xlsx
+++ b/data/gas_prices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I761"/>
+  <dimension ref="A1:I821"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30068,10 +30068,8 @@
       </c>
     </row>
     <row r="742">
-      <c r="A742" t="inlineStr">
-        <is>
-          <t>65558</t>
-        </is>
+      <c r="A742" t="n">
+        <v>65558</v>
       </c>
       <c r="B742" t="inlineStr">
         <is>
@@ -30111,10 +30109,8 @@
       </c>
     </row>
     <row r="743">
-      <c r="A743" t="inlineStr">
-        <is>
-          <t>83394</t>
-        </is>
+      <c r="A743" t="n">
+        <v>83394</v>
       </c>
       <c r="B743" t="inlineStr">
         <is>
@@ -30154,10 +30150,8 @@
       </c>
     </row>
     <row r="744">
-      <c r="A744" t="inlineStr">
-        <is>
-          <t>65573</t>
-        </is>
+      <c r="A744" t="n">
+        <v>65573</v>
       </c>
       <c r="B744" t="inlineStr">
         <is>
@@ -30197,10 +30191,8 @@
       </c>
     </row>
     <row r="745">
-      <c r="A745" t="inlineStr">
-        <is>
-          <t>80714</t>
-        </is>
+      <c r="A745" t="n">
+        <v>80714</v>
       </c>
       <c r="B745" t="inlineStr">
         <is>
@@ -30228,10 +30220,8 @@
       <c r="I745" t="inlineStr"/>
     </row>
     <row r="746">
-      <c r="A746" t="inlineStr">
-        <is>
-          <t>65552</t>
-        </is>
+      <c r="A746" t="n">
+        <v>65552</v>
       </c>
       <c r="B746" t="inlineStr">
         <is>
@@ -30259,10 +30249,8 @@
       <c r="I746" t="inlineStr"/>
     </row>
     <row r="747">
-      <c r="A747" t="inlineStr">
-        <is>
-          <t>65538</t>
-        </is>
+      <c r="A747" t="n">
+        <v>65538</v>
       </c>
       <c r="B747" t="inlineStr">
         <is>
@@ -30290,10 +30278,8 @@
       <c r="I747" t="inlineStr"/>
     </row>
     <row r="748">
-      <c r="A748" t="inlineStr">
-        <is>
-          <t>90814</t>
-        </is>
+      <c r="A748" t="n">
+        <v>90814</v>
       </c>
       <c r="B748" t="inlineStr">
         <is>
@@ -30321,10 +30307,8 @@
       <c r="I748" t="inlineStr"/>
     </row>
     <row r="749">
-      <c r="A749" t="inlineStr">
-        <is>
-          <t>39768</t>
-        </is>
+      <c r="A749" t="n">
+        <v>39768</v>
       </c>
       <c r="B749" t="inlineStr">
         <is>
@@ -30352,10 +30336,8 @@
       <c r="I749" t="inlineStr"/>
     </row>
     <row r="750">
-      <c r="A750" t="inlineStr">
-        <is>
-          <t>9710</t>
-        </is>
+      <c r="A750" t="n">
+        <v>9710</v>
       </c>
       <c r="B750" t="inlineStr">
         <is>
@@ -30383,10 +30365,8 @@
       <c r="I750" t="inlineStr"/>
     </row>
     <row r="751">
-      <c r="A751" t="inlineStr">
-        <is>
-          <t>99146</t>
-        </is>
+      <c r="A751" t="n">
+        <v>99146</v>
       </c>
       <c r="B751" t="inlineStr">
         <is>
@@ -30414,10 +30394,8 @@
       <c r="I751" t="inlineStr"/>
     </row>
     <row r="752">
-      <c r="A752" t="inlineStr">
-        <is>
-          <t>65560</t>
-        </is>
+      <c r="A752" t="n">
+        <v>65560</v>
       </c>
       <c r="B752" t="inlineStr">
         <is>
@@ -30445,10 +30423,8 @@
       <c r="I752" t="inlineStr"/>
     </row>
     <row r="753">
-      <c r="A753" t="inlineStr">
-        <is>
-          <t>65557</t>
-        </is>
+      <c r="A753" t="n">
+        <v>65557</v>
       </c>
       <c r="B753" t="inlineStr">
         <is>
@@ -30476,10 +30452,8 @@
       <c r="I753" t="inlineStr"/>
     </row>
     <row r="754">
-      <c r="A754" t="inlineStr">
-        <is>
-          <t>71502</t>
-        </is>
+      <c r="A754" t="n">
+        <v>71502</v>
       </c>
       <c r="B754" t="inlineStr">
         <is>
@@ -30507,10 +30481,8 @@
       <c r="I754" t="inlineStr"/>
     </row>
     <row r="755">
-      <c r="A755" t="inlineStr">
-        <is>
-          <t>65559</t>
-        </is>
+      <c r="A755" t="n">
+        <v>65559</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
@@ -30538,10 +30510,8 @@
       <c r="I755" t="inlineStr"/>
     </row>
     <row r="756">
-      <c r="A756" t="inlineStr">
-        <is>
-          <t>89943</t>
-        </is>
+      <c r="A756" t="n">
+        <v>89943</v>
       </c>
       <c r="B756" t="inlineStr">
         <is>
@@ -30569,10 +30539,8 @@
       <c r="I756" t="inlineStr"/>
     </row>
     <row r="757">
-      <c r="A757" t="inlineStr">
-        <is>
-          <t>86880</t>
-        </is>
+      <c r="A757" t="n">
+        <v>86880</v>
       </c>
       <c r="B757" t="inlineStr">
         <is>
@@ -30600,10 +30568,8 @@
       <c r="I757" t="inlineStr"/>
     </row>
     <row r="758">
-      <c r="A758" t="inlineStr">
-        <is>
-          <t>65537</t>
-        </is>
+      <c r="A758" t="n">
+        <v>65537</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
@@ -30631,10 +30597,8 @@
       <c r="I758" t="inlineStr"/>
     </row>
     <row r="759">
-      <c r="A759" t="inlineStr">
-        <is>
-          <t>65536</t>
-        </is>
+      <c r="A759" t="n">
+        <v>65536</v>
       </c>
       <c r="B759" t="inlineStr">
         <is>
@@ -30662,10 +30626,8 @@
       <c r="I759" t="inlineStr"/>
     </row>
     <row r="760">
-      <c r="A760" t="inlineStr">
-        <is>
-          <t>65535</t>
-        </is>
+      <c r="A760" t="n">
+        <v>65535</v>
       </c>
       <c r="B760" t="inlineStr">
         <is>
@@ -30693,10 +30655,8 @@
       <c r="I760" t="inlineStr"/>
     </row>
     <row r="761">
-      <c r="A761" t="inlineStr">
-        <is>
-          <t>65539</t>
-        </is>
+      <c r="A761" t="n">
+        <v>65539</v>
       </c>
       <c r="B761" t="inlineStr">
         <is>
@@ -30723,6 +30683,2398 @@
       <c r="H761" t="inlineStr"/>
       <c r="I761" t="inlineStr"/>
     </row>
+    <row r="762">
+      <c r="A762" t="n">
+        <v>65542</v>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>3250 MacDonald St</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2573819, 'Longitude': -123.1680407}</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:17:52</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:32:23.017Z</t>
+        </is>
+      </c>
+      <c r="G762" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>2025-08-18T20:00:38.663Z</t>
+        </is>
+      </c>
+      <c r="I762" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="n">
+        <v>65533</v>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>4615 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2449719, 'Longitude': -123.1540385}</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:17:52</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:41:12.206Z</t>
+        </is>
+      </c>
+      <c r="G763" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>2025-08-18T20:01:38.582Z</t>
+        </is>
+      </c>
+      <c r="I763" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="n">
+        <v>83068</v>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>3205 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.256927568207, 'Longitude': -123.153288960457}</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:17:52</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr"/>
+      <c r="G764" t="inlineStr"/>
+      <c r="H764" t="inlineStr"/>
+      <c r="I764" t="inlineStr"/>
+    </row>
+    <row r="765">
+      <c r="A765" t="n">
+        <v>65562</v>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>2808 W Broadway</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263883932125, 'Longitude': -123.168604373932}</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:17:52</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:32:49.864Z</t>
+        </is>
+      </c>
+      <c r="G765" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:17:36.405Z</t>
+        </is>
+      </c>
+      <c r="I765" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="n">
+        <v>113305</v>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>3596 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234385296079, 'Longitude': -123.184762001038}</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:17:52</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:30:12.587Z</t>
+        </is>
+      </c>
+      <c r="G766" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H766" t="inlineStr"/>
+      <c r="I766" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:17:52</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:36:50.738Z</t>
+        </is>
+      </c>
+      <c r="G767" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>2025-08-19T17:50:59.425Z</t>
+        </is>
+      </c>
+      <c r="I767" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="n">
+        <v>65554</v>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>1795 W Broadway</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264037962303, 'Longitude': -123.145408630371}</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:17:52</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:35:36.365Z</t>
+        </is>
+      </c>
+      <c r="G768" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:44:20.091Z</t>
+        </is>
+      </c>
+      <c r="I768" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="n">
+        <v>65571</v>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>4314 W 10th Ave</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263533861752, 'Longitude': -123.203430175781}</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:17:52</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:41:06.081Z</t>
+        </is>
+      </c>
+      <c r="G769" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>2025-08-19T16:29:09.259Z</t>
+        </is>
+      </c>
+      <c r="I769" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:17:52</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:51:14.843Z</t>
+        </is>
+      </c>
+      <c r="G770" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H770" t="inlineStr"/>
+      <c r="I770" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="n">
+        <v>32376</v>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>1503 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234634576953, 'Longitude': -123.139971792698}</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:17:52</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:26:29.841Z</t>
+        </is>
+      </c>
+      <c r="G771" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:30:08.915Z</t>
+        </is>
+      </c>
+      <c r="I771" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="n">
+        <v>65549</v>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>5702 Granville St</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234036184118, 'Longitude': -123.139244914055}</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:17:52</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:26:58.155Z</t>
+        </is>
+      </c>
+      <c r="G772" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:13:29.302Z</t>
+        </is>
+      </c>
+      <c r="I772" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:17:52</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:50:12.866Z</t>
+        </is>
+      </c>
+      <c r="G773" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:57:09.641Z</t>
+        </is>
+      </c>
+      <c r="I773" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:17:52</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:49:36.007Z</t>
+        </is>
+      </c>
+      <c r="G774" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:53:03.891Z</t>
+        </is>
+      </c>
+      <c r="I774" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="n">
+        <v>72747</v>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>1010 W King Edward Ave</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249188, 'Longitude': -123.127767}</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:17:52</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:58:51.602Z</t>
+        </is>
+      </c>
+      <c r="G775" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:43:58.867Z</t>
+        </is>
+      </c>
+      <c r="I775" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="n">
+        <v>32375</v>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>4110 Oak St</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.24894071957, 'Longitude': -123.127040863037}</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:17:52</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:58:58.196Z</t>
+        </is>
+      </c>
+      <c r="G776" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:13:19.073Z</t>
+        </is>
+      </c>
+      <c r="I776" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="n">
+        <v>65564</v>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>5680 Oak St</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234217162181, 'Longitude': -123.127684593201}</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:17:52</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:14:02.226Z</t>
+        </is>
+      </c>
+      <c r="G777" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:12:49.425Z</t>
+        </is>
+      </c>
+      <c r="I777" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="n">
+        <v>32372</v>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>6525 Oak St</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226226639452, 'Longitude': -123.128687739372}</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:17:52</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:56:55.122Z</t>
+        </is>
+      </c>
+      <c r="G778" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:29:56.703Z</t>
+        </is>
+      </c>
+      <c r="I778" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:17:52</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:29:46.633Z</t>
+        </is>
+      </c>
+      <c r="G779" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:29:46.649Z</t>
+        </is>
+      </c>
+      <c r="I779" t="n">
+        <v>199.9</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="n">
+        <v>65566</v>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>8072 Granville St</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.212495055855, 'Longitude': -123.14013004303}</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:17:52</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:28:24.653Z</t>
+        </is>
+      </c>
+      <c r="G780" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:30:08.359Z</t>
+        </is>
+      </c>
+      <c r="I780" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="n">
+        <v>65572</v>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:17:52</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:08:18.885Z</t>
+        </is>
+      </c>
+      <c r="G781" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:31:11.263Z</t>
+        </is>
+      </c>
+      <c r="I781" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="n">
+        <v>65558</v>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>1390 E 33rd Ave</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.240045470021, 'Longitude': -123.076765537262}</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:19:08</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:17:43.492Z</t>
+        </is>
+      </c>
+      <c r="G782" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:59:17.385Z</t>
+        </is>
+      </c>
+      <c r="I782" t="n">
+        <v>178.9</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="n">
+        <v>83394</v>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>4064 Fraser St</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.248864, 'Longitude': -123.09002}</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:19:08</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:04:18.249Z</t>
+        </is>
+      </c>
+      <c r="G783" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:01:42.428Z</t>
+        </is>
+      </c>
+      <c r="I783" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="n">
+        <v>65573</v>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>1396 E 41st Ave</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.232593005895, 'Longitude': -123.07728856802}</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:19:08</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:49:00.775Z</t>
+        </is>
+      </c>
+      <c r="G784" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:46:12.728Z</t>
+        </is>
+      </c>
+      <c r="I784" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="n">
+        <v>80714</v>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Husky</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>4933 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2397388, 'Longitude': -123.065748}</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:19:08</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:34:21.514Z</t>
+        </is>
+      </c>
+      <c r="G785" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:34:21.539Z</t>
+        </is>
+      </c>
+      <c r="I785" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="n">
+        <v>65552</v>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>2001 Kingsway</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.245312771918, 'Longitude': -123.064910173416}</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:19:08</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:07:11.809Z</t>
+        </is>
+      </c>
+      <c r="G786" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:22:00.919Z</t>
+        </is>
+      </c>
+      <c r="I786" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="n">
+        <v>65538</v>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>5252 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2372145, 'Longitude': -123.0650857}</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:19:08</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:27:08.446Z</t>
+        </is>
+      </c>
+      <c r="G787" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:06:44.322Z</t>
+        </is>
+      </c>
+      <c r="I787" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="n">
+        <v>90814</v>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>2277 Kingsway</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.242132845692, 'Longitude': -123.058204650879}</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:19:08</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:08:17.246Z</t>
+        </is>
+      </c>
+      <c r="G788" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:53:00.012Z</t>
+        </is>
+      </c>
+      <c r="I788" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="n">
+        <v>39768</v>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>5736 Main St</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2325708, 'Longitude': -123.1010069}</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:19:08</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:20:50.878Z</t>
+        </is>
+      </c>
+      <c r="G789" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:38:37.384Z</t>
+        </is>
+      </c>
+      <c r="I789" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="n">
+        <v>9710</v>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>1295 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259878978744, 'Longitude': -123.078074455261}</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:19:08</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:09:03.168Z</t>
+        </is>
+      </c>
+      <c r="G790" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:21:28.848Z</t>
+        </is>
+      </c>
+      <c r="I790" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="n">
+        <v>99146</v>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>1317 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259758544957, 'Longitude': -123.077272474766}</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:19:08</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:08:52.105Z</t>
+        </is>
+      </c>
+      <c r="G791" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:07:50.993Z</t>
+        </is>
+      </c>
+      <c r="I791" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="n">
+        <v>65560</v>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>1289 E Broadway</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.262693682723, 'Longitude': -123.078117370605}</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:19:08</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:09:12.455Z</t>
+        </is>
+      </c>
+      <c r="G792" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>2025-08-20T08:21:41.203Z</t>
+        </is>
+      </c>
+      <c r="I792" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="n">
+        <v>65557</v>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>2120 Grandview Hwy S</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2591601, 'Longitude': -123.0617495}</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:19:08</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:24:44.518Z</t>
+        </is>
+      </c>
+      <c r="G793" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:24:48.707Z</t>
+        </is>
+      </c>
+      <c r="I793" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="n">
+        <v>71502</v>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>2748 Main St</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2604441, 'Longitude': -123.1005869}</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:19:08</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:04:27.093Z</t>
+        </is>
+      </c>
+      <c r="G794" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:30:55.406Z</t>
+        </is>
+      </c>
+      <c r="I794" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="n">
+        <v>65559</v>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>6502 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.224996944057, 'Longitude': -123.065521717072}</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:19:08</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:05:12.272Z</t>
+        </is>
+      </c>
+      <c r="G795" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:59:10.689Z</t>
+        </is>
+      </c>
+      <c r="I795" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="n">
+        <v>89943</v>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>6808 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2220242, 'Longitude': -123.0654247}</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:19:08</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:47:33.419Z</t>
+        </is>
+      </c>
+      <c r="G796" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:59:15.108Z</t>
+        </is>
+      </c>
+      <c r="I796" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:19:08</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:14:16.959Z</t>
+        </is>
+      </c>
+      <c r="G797" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>2025-08-19T15:14:14.480Z</t>
+        </is>
+      </c>
+      <c r="I797" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="n">
+        <v>65537</v>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>2918 Kingsway</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.23608, 'Longitude': -123.0454858}</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:19:08</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:39:55.040Z</t>
+        </is>
+      </c>
+      <c r="G798" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:26:21.493Z</t>
+        </is>
+      </c>
+      <c r="I798" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:19:08</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:14:09.621Z</t>
+        </is>
+      </c>
+      <c r="G799" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:52:58.575Z</t>
+        </is>
+      </c>
+      <c r="I799" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="n">
+        <v>65535</v>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>2605 E 49th Ave</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2251291, 'Longitude': -123.0545048}</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:19:08</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:00:06.584Z</t>
+        </is>
+      </c>
+      <c r="G800" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="H800" t="inlineStr"/>
+      <c r="I800" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="n">
+        <v>65539</v>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>2902 Grandview Hwy</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2579053, 'Longitude': -123.0438464}</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:19:08</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:38:57.148Z</t>
+        </is>
+      </c>
+      <c r="G801" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:32:43.274Z</t>
+        </is>
+      </c>
+      <c r="I801" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>77015</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169873456637, 'Longitude': -123.091178619746}</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:20:23</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:56:32.661Z</t>
+        </is>
+      </c>
+      <c r="G802" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:56:32.708Z</t>
+        </is>
+      </c>
+      <c r="I802" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>65511</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:20:23</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:26:04.817Z</t>
+        </is>
+      </c>
+      <c r="G803" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:52:38.422Z</t>
+        </is>
+      </c>
+      <c r="I803" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>86650</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169856952787, 'Longitude': -123.123961687088}</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:20:23</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:45:40.385Z</t>
+        </is>
+      </c>
+      <c r="G804" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:55:51.764Z</t>
+        </is>
+      </c>
+      <c r="I804" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>77218</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.173339635958, 'Longitude': -123.124954104424}</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:20:23</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:24:16.351Z</t>
+        </is>
+      </c>
+      <c r="G805" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:05:36.774Z</t>
+        </is>
+      </c>
+      <c r="I805" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>77228</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1843249, 'Longitude': -123.1236078}</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:20:23</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:59:15.055Z</t>
+        </is>
+      </c>
+      <c r="G806" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:56:31.406Z</t>
+        </is>
+      </c>
+      <c r="I806" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>83384</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192001, 'Longitude': -123.124004}</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:20:23</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:59:22.624Z</t>
+        </is>
+      </c>
+      <c r="G807" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:12:49.675Z</t>
+        </is>
+      </c>
+      <c r="I807" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>77202</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.162989071149, 'Longitude': -123.134229183197}</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:20:23</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:48:42.957Z</t>
+        </is>
+      </c>
+      <c r="G808" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:27:53.585Z</t>
+        </is>
+      </c>
+      <c r="I808" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>77243</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.179182137142, 'Longitude': -123.137152791023}</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:20:23</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:25:26.273Z</t>
+        </is>
+      </c>
+      <c r="G809" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:24:58.074Z</t>
+        </is>
+      </c>
+      <c r="I809" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>83387</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>710 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21081995506, 'Longitude': -123.090755939484}</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:20:23</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:12:44.238Z</t>
+        </is>
+      </c>
+      <c r="G810" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>2025-08-20T11:07:44.929Z</t>
+        </is>
+      </c>
+      <c r="I810" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>65551</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>688 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210798928329, 'Longitude': -123.09152841568}</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:20:23</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:12:33.985Z</t>
+        </is>
+      </c>
+      <c r="G811" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>2025-08-20T11:07:33.051Z</t>
+        </is>
+      </c>
+      <c r="I811" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>77235</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.18409178594, 'Longitude': -123.136823830688}</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:20:23</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:24:37.722Z</t>
+        </is>
+      </c>
+      <c r="G812" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:07:48.316Z</t>
+        </is>
+      </c>
+      <c r="I812" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>82925</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>350 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210245, 'Longitude': -123.099328}</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:20:23</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:12:15.138Z</t>
+        </is>
+      </c>
+      <c r="G813" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:34:57.215Z</t>
+        </is>
+      </c>
+      <c r="I813" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>109205</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:20:23</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr"/>
+      <c r="G814" t="inlineStr"/>
+      <c r="H814" t="inlineStr"/>
+      <c r="I814" t="inlineStr"/>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>65540</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>196 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2106867, 'Longitude': -123.1027436}</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:20:23</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:10:58.755Z</t>
+        </is>
+      </c>
+      <c r="G815" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:29:30.493Z</t>
+        </is>
+      </c>
+      <c r="I815" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>65512</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:20:23</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr"/>
+      <c r="G816" t="inlineStr"/>
+      <c r="H816" t="inlineStr"/>
+      <c r="I816" t="inlineStr"/>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>77205</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:20:23</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr"/>
+      <c r="G817" t="inlineStr"/>
+      <c r="H817" t="inlineStr"/>
+      <c r="I817" t="inlineStr"/>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>65536</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:20:23</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr"/>
+      <c r="G818" t="inlineStr"/>
+      <c r="H818" t="inlineStr"/>
+      <c r="I818" t="inlineStr"/>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>86880</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:20:23</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr"/>
+      <c r="G819" t="inlineStr"/>
+      <c r="H819" t="inlineStr"/>
+      <c r="I819" t="inlineStr"/>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>65556</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:20:23</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr"/>
+      <c r="G820" t="inlineStr"/>
+      <c r="H820" t="inlineStr"/>
+      <c r="I820" t="inlineStr"/>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>86937</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>8655 Boundary Rd</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:20:23</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr"/>
+      <c r="G821" t="inlineStr"/>
+      <c r="H821" t="inlineStr"/>
+      <c r="I821" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gas_prices.xlsx
+++ b/data/gas_prices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I821"/>
+  <dimension ref="A1:I901"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32300,10 +32300,8 @@
       </c>
     </row>
     <row r="802">
-      <c r="A802" t="inlineStr">
-        <is>
-          <t>77015</t>
-        </is>
+      <c r="A802" t="n">
+        <v>77015</v>
       </c>
       <c r="B802" t="inlineStr">
         <is>
@@ -32343,10 +32341,8 @@
       </c>
     </row>
     <row r="803">
-      <c r="A803" t="inlineStr">
-        <is>
-          <t>65511</t>
-        </is>
+      <c r="A803" t="n">
+        <v>65511</v>
       </c>
       <c r="B803" t="inlineStr">
         <is>
@@ -32386,10 +32382,8 @@
       </c>
     </row>
     <row r="804">
-      <c r="A804" t="inlineStr">
-        <is>
-          <t>86650</t>
-        </is>
+      <c r="A804" t="n">
+        <v>86650</v>
       </c>
       <c r="B804" t="inlineStr">
         <is>
@@ -32429,10 +32423,8 @@
       </c>
     </row>
     <row r="805">
-      <c r="A805" t="inlineStr">
-        <is>
-          <t>77218</t>
-        </is>
+      <c r="A805" t="n">
+        <v>77218</v>
       </c>
       <c r="B805" t="inlineStr">
         <is>
@@ -32472,10 +32464,8 @@
       </c>
     </row>
     <row r="806">
-      <c r="A806" t="inlineStr">
-        <is>
-          <t>77228</t>
-        </is>
+      <c r="A806" t="n">
+        <v>77228</v>
       </c>
       <c r="B806" t="inlineStr">
         <is>
@@ -32515,10 +32505,8 @@
       </c>
     </row>
     <row r="807">
-      <c r="A807" t="inlineStr">
-        <is>
-          <t>83384</t>
-        </is>
+      <c r="A807" t="n">
+        <v>83384</v>
       </c>
       <c r="B807" t="inlineStr">
         <is>
@@ -32558,10 +32546,8 @@
       </c>
     </row>
     <row r="808">
-      <c r="A808" t="inlineStr">
-        <is>
-          <t>77202</t>
-        </is>
+      <c r="A808" t="n">
+        <v>77202</v>
       </c>
       <c r="B808" t="inlineStr">
         <is>
@@ -32601,10 +32587,8 @@
       </c>
     </row>
     <row r="809">
-      <c r="A809" t="inlineStr">
-        <is>
-          <t>77243</t>
-        </is>
+      <c r="A809" t="n">
+        <v>77243</v>
       </c>
       <c r="B809" t="inlineStr">
         <is>
@@ -32644,10 +32628,8 @@
       </c>
     </row>
     <row r="810">
-      <c r="A810" t="inlineStr">
-        <is>
-          <t>83387</t>
-        </is>
+      <c r="A810" t="n">
+        <v>83387</v>
       </c>
       <c r="B810" t="inlineStr">
         <is>
@@ -32687,10 +32669,8 @@
       </c>
     </row>
     <row r="811">
-      <c r="A811" t="inlineStr">
-        <is>
-          <t>65551</t>
-        </is>
+      <c r="A811" t="n">
+        <v>65551</v>
       </c>
       <c r="B811" t="inlineStr">
         <is>
@@ -32730,10 +32710,8 @@
       </c>
     </row>
     <row r="812">
-      <c r="A812" t="inlineStr">
-        <is>
-          <t>77235</t>
-        </is>
+      <c r="A812" t="n">
+        <v>77235</v>
       </c>
       <c r="B812" t="inlineStr">
         <is>
@@ -32773,10 +32751,8 @@
       </c>
     </row>
     <row r="813">
-      <c r="A813" t="inlineStr">
-        <is>
-          <t>82925</t>
-        </is>
+      <c r="A813" t="n">
+        <v>82925</v>
       </c>
       <c r="B813" t="inlineStr">
         <is>
@@ -32816,10 +32792,8 @@
       </c>
     </row>
     <row r="814">
-      <c r="A814" t="inlineStr">
-        <is>
-          <t>109205</t>
-        </is>
+      <c r="A814" t="n">
+        <v>109205</v>
       </c>
       <c r="B814" t="inlineStr">
         <is>
@@ -32847,10 +32821,8 @@
       <c r="I814" t="inlineStr"/>
     </row>
     <row r="815">
-      <c r="A815" t="inlineStr">
-        <is>
-          <t>65540</t>
-        </is>
+      <c r="A815" t="n">
+        <v>65540</v>
       </c>
       <c r="B815" t="inlineStr">
         <is>
@@ -32890,10 +32862,8 @@
       </c>
     </row>
     <row r="816">
-      <c r="A816" t="inlineStr">
-        <is>
-          <t>65512</t>
-        </is>
+      <c r="A816" t="n">
+        <v>65512</v>
       </c>
       <c r="B816" t="inlineStr">
         <is>
@@ -32921,10 +32891,8 @@
       <c r="I816" t="inlineStr"/>
     </row>
     <row r="817">
-      <c r="A817" t="inlineStr">
-        <is>
-          <t>77205</t>
-        </is>
+      <c r="A817" t="n">
+        <v>77205</v>
       </c>
       <c r="B817" t="inlineStr">
         <is>
@@ -32952,10 +32920,8 @@
       <c r="I817" t="inlineStr"/>
     </row>
     <row r="818">
-      <c r="A818" t="inlineStr">
-        <is>
-          <t>65536</t>
-        </is>
+      <c r="A818" t="n">
+        <v>65536</v>
       </c>
       <c r="B818" t="inlineStr">
         <is>
@@ -32983,10 +32949,8 @@
       <c r="I818" t="inlineStr"/>
     </row>
     <row r="819">
-      <c r="A819" t="inlineStr">
-        <is>
-          <t>86880</t>
-        </is>
+      <c r="A819" t="n">
+        <v>86880</v>
       </c>
       <c r="B819" t="inlineStr">
         <is>
@@ -33014,10 +32978,8 @@
       <c r="I819" t="inlineStr"/>
     </row>
     <row r="820">
-      <c r="A820" t="inlineStr">
-        <is>
-          <t>65556</t>
-        </is>
+      <c r="A820" t="n">
+        <v>65556</v>
       </c>
       <c r="B820" t="inlineStr">
         <is>
@@ -33045,10 +33007,8 @@
       <c r="I820" t="inlineStr"/>
     </row>
     <row r="821">
-      <c r="A821" t="inlineStr">
-        <is>
-          <t>86937</t>
-        </is>
+      <c r="A821" t="n">
+        <v>86937</v>
       </c>
       <c r="B821" t="inlineStr">
         <is>
@@ -33075,6 +33035,3290 @@
       <c r="H821" t="inlineStr"/>
       <c r="I821" t="inlineStr"/>
     </row>
+    <row r="822">
+      <c r="A822" t="n">
+        <v>65542</v>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>3250 MacDonald St</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2573819, 'Longitude': -123.1680407}</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:36:25</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:32:23.017Z</t>
+        </is>
+      </c>
+      <c r="G822" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>2025-08-18T20:00:38.663Z</t>
+        </is>
+      </c>
+      <c r="I822" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="n">
+        <v>65533</v>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>4615 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2449719, 'Longitude': -123.1540385}</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:36:25</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:41:12.206Z</t>
+        </is>
+      </c>
+      <c r="G823" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>2025-08-18T20:01:38.582Z</t>
+        </is>
+      </c>
+      <c r="I823" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="n">
+        <v>83068</v>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>3205 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.256927568207, 'Longitude': -123.153288960457}</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:36:25</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr"/>
+      <c r="G824" t="inlineStr"/>
+      <c r="H824" t="inlineStr"/>
+      <c r="I824" t="inlineStr"/>
+    </row>
+    <row r="825">
+      <c r="A825" t="n">
+        <v>65562</v>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>2808 W Broadway</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263883932125, 'Longitude': -123.168604373932}</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:36:25</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:32:49.864Z</t>
+        </is>
+      </c>
+      <c r="G825" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:17:36.405Z</t>
+        </is>
+      </c>
+      <c r="I825" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="n">
+        <v>113305</v>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>3596 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234385296079, 'Longitude': -123.184762001038}</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:36:25</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:30:12.587Z</t>
+        </is>
+      </c>
+      <c r="G826" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H826" t="inlineStr"/>
+      <c r="I826" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:36:25</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:36:50.738Z</t>
+        </is>
+      </c>
+      <c r="G827" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>2025-08-19T17:50:59.425Z</t>
+        </is>
+      </c>
+      <c r="I827" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="n">
+        <v>65554</v>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>1795 W Broadway</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264037962303, 'Longitude': -123.145408630371}</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:36:25</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:35:36.365Z</t>
+        </is>
+      </c>
+      <c r="G828" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:44:20.091Z</t>
+        </is>
+      </c>
+      <c r="I828" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="n">
+        <v>65571</v>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>4314 W 10th Ave</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263533861752, 'Longitude': -123.203430175781}</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:36:25</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:41:06.081Z</t>
+        </is>
+      </c>
+      <c r="G829" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>2025-08-19T16:29:09.259Z</t>
+        </is>
+      </c>
+      <c r="I829" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:36:25</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:51:14.843Z</t>
+        </is>
+      </c>
+      <c r="G830" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H830" t="inlineStr"/>
+      <c r="I830" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="n">
+        <v>32376</v>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>1503 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234634576953, 'Longitude': -123.139971792698}</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:36:25</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:26:29.841Z</t>
+        </is>
+      </c>
+      <c r="G831" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:30:08.915Z</t>
+        </is>
+      </c>
+      <c r="I831" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="n">
+        <v>65549</v>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>5702 Granville St</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234036184118, 'Longitude': -123.139244914055}</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:36:25</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:26:58.155Z</t>
+        </is>
+      </c>
+      <c r="G832" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:13:29.302Z</t>
+        </is>
+      </c>
+      <c r="I832" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:36:25</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:50:12.866Z</t>
+        </is>
+      </c>
+      <c r="G833" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:57:09.641Z</t>
+        </is>
+      </c>
+      <c r="I833" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:36:25</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:49:36.007Z</t>
+        </is>
+      </c>
+      <c r="G834" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:53:03.891Z</t>
+        </is>
+      </c>
+      <c r="I834" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="n">
+        <v>72747</v>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>1010 W King Edward Ave</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249188, 'Longitude': -123.127767}</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:36:25</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:58:51.602Z</t>
+        </is>
+      </c>
+      <c r="G835" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:43:58.867Z</t>
+        </is>
+      </c>
+      <c r="I835" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="n">
+        <v>32375</v>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>4110 Oak St</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.24894071957, 'Longitude': -123.127040863037}</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:36:25</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:58:58.196Z</t>
+        </is>
+      </c>
+      <c r="G836" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:13:19.073Z</t>
+        </is>
+      </c>
+      <c r="I836" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="n">
+        <v>65564</v>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>5680 Oak St</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234217162181, 'Longitude': -123.127684593201}</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:36:25</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:14:02.226Z</t>
+        </is>
+      </c>
+      <c r="G837" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:12:49.425Z</t>
+        </is>
+      </c>
+      <c r="I837" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="n">
+        <v>32372</v>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>6525 Oak St</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226226639452, 'Longitude': -123.128687739372}</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:36:25</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:56:55.122Z</t>
+        </is>
+      </c>
+      <c r="G838" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:29:56.703Z</t>
+        </is>
+      </c>
+      <c r="I838" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:36:25</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:29:46.633Z</t>
+        </is>
+      </c>
+      <c r="G839" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:29:46.649Z</t>
+        </is>
+      </c>
+      <c r="I839" t="n">
+        <v>199.9</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="n">
+        <v>65566</v>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>8072 Granville St</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.212495055855, 'Longitude': -123.14013004303}</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:36:25</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:28:24.653Z</t>
+        </is>
+      </c>
+      <c r="G840" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:30:08.359Z</t>
+        </is>
+      </c>
+      <c r="I840" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="n">
+        <v>65572</v>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:36:25</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:08:18.885Z</t>
+        </is>
+      </c>
+      <c r="G841" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:31:11.263Z</t>
+        </is>
+      </c>
+      <c r="I841" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="n">
+        <v>65558</v>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>1390 E 33rd Ave</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.240045470021, 'Longitude': -123.076765537262}</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:37:47</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:27:09.380Z</t>
+        </is>
+      </c>
+      <c r="G842" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:27:09.411Z</t>
+        </is>
+      </c>
+      <c r="I842" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="n">
+        <v>83394</v>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>4064 Fraser St</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.248864, 'Longitude': -123.09002}</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:37:47</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:04:18.249Z</t>
+        </is>
+      </c>
+      <c r="G843" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:01:42.428Z</t>
+        </is>
+      </c>
+      <c r="I843" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="n">
+        <v>65573</v>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>1396 E 41st Ave</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.232593005895, 'Longitude': -123.07728856802}</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:37:47</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:49:00.775Z</t>
+        </is>
+      </c>
+      <c r="G844" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:46:12.728Z</t>
+        </is>
+      </c>
+      <c r="I844" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="n">
+        <v>80714</v>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Husky</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>4933 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2397388, 'Longitude': -123.065748}</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:37:47</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:26:55.951Z</t>
+        </is>
+      </c>
+      <c r="G845" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:34:21.539Z</t>
+        </is>
+      </c>
+      <c r="I845" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="n">
+        <v>65552</v>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>2001 Kingsway</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.245312771918, 'Longitude': -123.064910173416}</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:37:47</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:07:11.809Z</t>
+        </is>
+      </c>
+      <c r="G846" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:22:00.919Z</t>
+        </is>
+      </c>
+      <c r="I846" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="n">
+        <v>65538</v>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>5252 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2372145, 'Longitude': -123.0650857}</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:37:47</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:27:07.443Z</t>
+        </is>
+      </c>
+      <c r="G847" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:06:44.322Z</t>
+        </is>
+      </c>
+      <c r="I847" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="n">
+        <v>90814</v>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>2277 Kingsway</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.242132845692, 'Longitude': -123.058204650879}</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:37:47</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:08:17.246Z</t>
+        </is>
+      </c>
+      <c r="G848" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:53:00.012Z</t>
+        </is>
+      </c>
+      <c r="I848" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="n">
+        <v>39768</v>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>5736 Main St</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2325708, 'Longitude': -123.1010069}</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:37:47</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:20:50.878Z</t>
+        </is>
+      </c>
+      <c r="G849" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:38:37.384Z</t>
+        </is>
+      </c>
+      <c r="I849" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="n">
+        <v>9710</v>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>1295 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259878978744, 'Longitude': -123.078074455261}</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:37:47</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:23:13.071Z</t>
+        </is>
+      </c>
+      <c r="G850" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:21:28.848Z</t>
+        </is>
+      </c>
+      <c r="I850" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="n">
+        <v>99146</v>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>1317 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259758544957, 'Longitude': -123.077272474766}</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:37:47</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:08:52.105Z</t>
+        </is>
+      </c>
+      <c r="G851" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:07:50.993Z</t>
+        </is>
+      </c>
+      <c r="I851" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="n">
+        <v>65560</v>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>1289 E Broadway</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.262693682723, 'Longitude': -123.078117370605}</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:37:47</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:09:12.455Z</t>
+        </is>
+      </c>
+      <c r="G852" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>2025-08-20T08:21:41.203Z</t>
+        </is>
+      </c>
+      <c r="I852" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="n">
+        <v>65557</v>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>2120 Grandview Hwy S</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2591601, 'Longitude': -123.0617495}</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:37:47</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:24:44.518Z</t>
+        </is>
+      </c>
+      <c r="G853" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:24:48.707Z</t>
+        </is>
+      </c>
+      <c r="I853" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="n">
+        <v>71502</v>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>2748 Main St</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2604441, 'Longitude': -123.1005869}</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:37:47</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:04:27.093Z</t>
+        </is>
+      </c>
+      <c r="G854" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:30:55.406Z</t>
+        </is>
+      </c>
+      <c r="I854" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="n">
+        <v>65559</v>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>6502 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.224996944057, 'Longitude': -123.065521717072}</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:37:47</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:05:12.272Z</t>
+        </is>
+      </c>
+      <c r="G855" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:59:10.689Z</t>
+        </is>
+      </c>
+      <c r="I855" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="n">
+        <v>89943</v>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>6808 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2220242, 'Longitude': -123.0654247}</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:37:47</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:47:33.419Z</t>
+        </is>
+      </c>
+      <c r="G856" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:59:15.108Z</t>
+        </is>
+      </c>
+      <c r="I856" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:37:47</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:14:16.959Z</t>
+        </is>
+      </c>
+      <c r="G857" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>2025-08-19T15:14:14.480Z</t>
+        </is>
+      </c>
+      <c r="I857" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="n">
+        <v>65537</v>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>2918 Kingsway</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.23608, 'Longitude': -123.0454858}</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:37:47</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:39:55.040Z</t>
+        </is>
+      </c>
+      <c r="G858" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:26:21.493Z</t>
+        </is>
+      </c>
+      <c r="I858" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:37:47</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:14:09.621Z</t>
+        </is>
+      </c>
+      <c r="G859" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:52:58.575Z</t>
+        </is>
+      </c>
+      <c r="I859" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="n">
+        <v>65535</v>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>2605 E 49th Ave</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2251291, 'Longitude': -123.0545048}</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:37:47</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:00:06.584Z</t>
+        </is>
+      </c>
+      <c r="G860" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="H860" t="inlineStr"/>
+      <c r="I860" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="n">
+        <v>65539</v>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>2902 Grandview Hwy</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2579053, 'Longitude': -123.0438464}</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:37:47</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:38:57.148Z</t>
+        </is>
+      </c>
+      <c r="G861" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:32:43.274Z</t>
+        </is>
+      </c>
+      <c r="I861" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="n">
+        <v>77015</v>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169873456637, 'Longitude': -123.091178619746}</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:39:07</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:31:36.293Z</t>
+        </is>
+      </c>
+      <c r="G862" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:31:33.166Z</t>
+        </is>
+      </c>
+      <c r="I862" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="n">
+        <v>65511</v>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:39:07</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:26:04.817Z</t>
+        </is>
+      </c>
+      <c r="G863" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:52:38.422Z</t>
+        </is>
+      </c>
+      <c r="I863" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="n">
+        <v>86650</v>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169856952787, 'Longitude': -123.123961687088}</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:39:07</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:45:40.385Z</t>
+        </is>
+      </c>
+      <c r="G864" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:55:51.764Z</t>
+        </is>
+      </c>
+      <c r="I864" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="n">
+        <v>77218</v>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.173339635958, 'Longitude': -123.124954104424}</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:39:07</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:24:16.351Z</t>
+        </is>
+      </c>
+      <c r="G865" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:05:36.774Z</t>
+        </is>
+      </c>
+      <c r="I865" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="n">
+        <v>77228</v>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1843249, 'Longitude': -123.1236078}</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:39:07</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:59:15.055Z</t>
+        </is>
+      </c>
+      <c r="G866" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:56:31.406Z</t>
+        </is>
+      </c>
+      <c r="I866" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="n">
+        <v>83384</v>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192001, 'Longitude': -123.124004}</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:39:07</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:37:20.938Z</t>
+        </is>
+      </c>
+      <c r="G867" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:12:49.675Z</t>
+        </is>
+      </c>
+      <c r="I867" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="n">
+        <v>77202</v>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.162989071149, 'Longitude': -123.134229183197}</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:39:07</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:48:42.957Z</t>
+        </is>
+      </c>
+      <c r="G868" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:27:53.585Z</t>
+        </is>
+      </c>
+      <c r="I868" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="n">
+        <v>77243</v>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.179182137142, 'Longitude': -123.137152791023}</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:39:07</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:33:01.833Z</t>
+        </is>
+      </c>
+      <c r="G869" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:24:58.074Z</t>
+        </is>
+      </c>
+      <c r="I869" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="n">
+        <v>83387</v>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>710 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21081995506, 'Longitude': -123.090755939484}</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:39:07</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:12:44.238Z</t>
+        </is>
+      </c>
+      <c r="G870" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>2025-08-20T11:07:44.929Z</t>
+        </is>
+      </c>
+      <c r="I870" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="n">
+        <v>65551</v>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>688 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210798928329, 'Longitude': -123.09152841568}</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:39:07</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:12:33.985Z</t>
+        </is>
+      </c>
+      <c r="G871" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>2025-08-20T11:07:33.051Z</t>
+        </is>
+      </c>
+      <c r="I871" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="n">
+        <v>77235</v>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.18409178594, 'Longitude': -123.136823830688}</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:39:07</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:24:37.722Z</t>
+        </is>
+      </c>
+      <c r="G872" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:07:48.316Z</t>
+        </is>
+      </c>
+      <c r="I872" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="n">
+        <v>82925</v>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>350 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210245, 'Longitude': -123.099328}</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:39:07</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:12:15.138Z</t>
+        </is>
+      </c>
+      <c r="G873" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:34:57.215Z</t>
+        </is>
+      </c>
+      <c r="I873" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="n">
+        <v>109205</v>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.133556536531, 'Longitude': -123.092424273491}</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:39:07</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:48:43.942Z</t>
+        </is>
+      </c>
+      <c r="G874" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:18:17.381Z</t>
+        </is>
+      </c>
+      <c r="I874" t="n">
+        <v>178.9</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="n">
+        <v>65540</v>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>196 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2106867, 'Longitude': -123.1027436}</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:39:07</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:10:58.755Z</t>
+        </is>
+      </c>
+      <c r="G875" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:29:30.493Z</t>
+        </is>
+      </c>
+      <c r="I875" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="n">
+        <v>65512</v>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1328393, 'Longitude': -123.0926312}</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:39:07</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:48:49.608Z</t>
+        </is>
+      </c>
+      <c r="G876" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:20:26.891Z</t>
+        </is>
+      </c>
+      <c r="I876" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="n">
+        <v>77205</v>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1558882, 'Longitude': -123.1369625}</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:39:07</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:24:42.524Z</t>
+        </is>
+      </c>
+      <c r="G877" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:11:19.742Z</t>
+        </is>
+      </c>
+      <c r="I877" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:39:07</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:14:09.621Z</t>
+        </is>
+      </c>
+      <c r="G878" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:52:58.575Z</t>
+        </is>
+      </c>
+      <c r="I878" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:39:07</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:14:16.959Z</t>
+        </is>
+      </c>
+      <c r="G879" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>2025-08-19T15:14:14.480Z</t>
+        </is>
+      </c>
+      <c r="I879" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="n">
+        <v>65556</v>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20806537721, 'Longitude': -123.123285770416}</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:39:07</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:08:50.162Z</t>
+        </is>
+      </c>
+      <c r="G880" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>2025-08-20T07:11:27.660Z</t>
+        </is>
+      </c>
+      <c r="I880" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="n">
+        <v>86937</v>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>8655 Boundary Rd</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20476, 'Longitude': -123.02398}</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:39:07</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:35:10.116Z</t>
+        </is>
+      </c>
+      <c r="G881" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>2025-08-20T09:58:09.662Z</t>
+        </is>
+      </c>
+      <c r="I881" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>65515</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>4011 Francis Rd</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.14867500071, 'Longitude': -123.180856704712}</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:40:28</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:07:51.485Z</t>
+        </is>
+      </c>
+      <c r="G882" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:12:10.433Z</t>
+        </is>
+      </c>
+      <c r="I882" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>77205</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1558882, 'Longitude': -123.1369625}</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:40:28</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:24:42.524Z</t>
+        </is>
+      </c>
+      <c r="G883" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:11:19.742Z</t>
+        </is>
+      </c>
+      <c r="I883" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>77223</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>7991 No 1 Rd</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.155888686563, 'Longitude': -123.181414604187}</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:40:28</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr"/>
+      <c r="G884" t="inlineStr"/>
+      <c r="H884" t="inlineStr"/>
+      <c r="I884" t="inlineStr"/>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>65514</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>7980 Williams Rd</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.140582914547, 'Longitude': -123.137168884277}</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:40:28</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:24:32.982Z</t>
+        </is>
+      </c>
+      <c r="G885" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:22:52.988Z</t>
+        </is>
+      </c>
+      <c r="I885" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>77232</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900 Westminster Hwy </t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1698419, 'Longitude': -123.159282}</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:40:28</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:30:25.628Z</t>
+        </is>
+      </c>
+      <c r="G886" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:30:25.660Z</t>
+        </is>
+      </c>
+      <c r="I886" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>77202</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.162989071149, 'Longitude': -123.134229183197}</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:40:28</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:48:42.957Z</t>
+        </is>
+      </c>
+      <c r="G887" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:27:53.585Z</t>
+        </is>
+      </c>
+      <c r="I887" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>86650</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169856952787, 'Longitude': -123.123961687088}</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:40:28</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:45:40.385Z</t>
+        </is>
+      </c>
+      <c r="G888" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:55:51.764Z</t>
+        </is>
+      </c>
+      <c r="I888" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>77218</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.173339635958, 'Longitude': -123.124954104424}</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:40:28</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:24:16.351Z</t>
+        </is>
+      </c>
+      <c r="G889" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:05:36.774Z</t>
+        </is>
+      </c>
+      <c r="I889" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>77243</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.179182137142, 'Longitude': -123.137152791023}</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:40:28</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:33:01.833Z</t>
+        </is>
+      </c>
+      <c r="G890" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>2025-08-20T05:24:58.074Z</t>
+        </is>
+      </c>
+      <c r="I890" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>77235</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.18409178594, 'Longitude': -123.136823830688}</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:40:28</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:24:37.722Z</t>
+        </is>
+      </c>
+      <c r="G891" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:07:48.316Z</t>
+        </is>
+      </c>
+      <c r="I891" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>77228</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1843249, 'Longitude': -123.1236078}</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:40:28</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:59:15.055Z</t>
+        </is>
+      </c>
+      <c r="G892" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:56:31.406Z</t>
+        </is>
+      </c>
+      <c r="I892" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>69163</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>5111 Grant McConachie Way</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192919, 'Longitude': -123.166797}</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:40:28</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:57:45.848Z</t>
+        </is>
+      </c>
+      <c r="G893" t="n">
+        <v>168.9</v>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>2025-08-20T10:13:47.773Z</t>
+        </is>
+      </c>
+      <c r="I893" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>109205</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.133556536531, 'Longitude': -123.092424273491}</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:40:28</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:48:43.942Z</t>
+        </is>
+      </c>
+      <c r="G894" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:18:17.381Z</t>
+        </is>
+      </c>
+      <c r="I894" t="n">
+        <v>178.9</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>65512</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1328393, 'Longitude': -123.0926312}</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:40:28</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:48:49.608Z</t>
+        </is>
+      </c>
+      <c r="G895" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:20:26.891Z</t>
+        </is>
+      </c>
+      <c r="I895" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>83384</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192001, 'Longitude': -123.124004}</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:40:28</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:37:20.938Z</t>
+        </is>
+      </c>
+      <c r="G896" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:12:49.675Z</t>
+        </is>
+      </c>
+      <c r="I896" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>77015</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169873456637, 'Longitude': -123.091178619746}</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:40:28</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:31:36.293Z</t>
+        </is>
+      </c>
+      <c r="G897" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:31:33.166Z</t>
+        </is>
+      </c>
+      <c r="I897" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>107728</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>8884 Granville St</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2054215, 'Longitude': -123.1401677}</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:40:28</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:07:58.981Z</t>
+        </is>
+      </c>
+      <c r="G898" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>2025-08-19T21:28:32.275Z</t>
+        </is>
+      </c>
+      <c r="I898" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>65572</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:40:28</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:08:18.885Z</t>
+        </is>
+      </c>
+      <c r="G899" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:31:11.263Z</t>
+        </is>
+      </c>
+      <c r="I899" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>65511</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:40:28</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:26:04.817Z</t>
+        </is>
+      </c>
+      <c r="G900" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>2025-08-20T13:52:38.422Z</t>
+        </is>
+      </c>
+      <c r="I900" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>65556</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20806537721, 'Longitude': -123.123285770416}</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>2025-08-20 08:40:28</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:08:50.162Z</t>
+        </is>
+      </c>
+      <c r="G901" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>2025-08-20T07:11:27.660Z</t>
+        </is>
+      </c>
+      <c r="I901" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gas_prices.xlsx
+++ b/data/gas_prices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I901"/>
+  <dimension ref="A1:I981"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35472,10 +35472,8 @@
       </c>
     </row>
     <row r="882">
-      <c r="A882" t="inlineStr">
-        <is>
-          <t>65515</t>
-        </is>
+      <c r="A882" t="n">
+        <v>65515</v>
       </c>
       <c r="B882" t="inlineStr">
         <is>
@@ -35515,10 +35513,8 @@
       </c>
     </row>
     <row r="883">
-      <c r="A883" t="inlineStr">
-        <is>
-          <t>77205</t>
-        </is>
+      <c r="A883" t="n">
+        <v>77205</v>
       </c>
       <c r="B883" t="inlineStr">
         <is>
@@ -35558,10 +35554,8 @@
       </c>
     </row>
     <row r="884">
-      <c r="A884" t="inlineStr">
-        <is>
-          <t>77223</t>
-        </is>
+      <c r="A884" t="n">
+        <v>77223</v>
       </c>
       <c r="B884" t="inlineStr">
         <is>
@@ -35589,10 +35583,8 @@
       <c r="I884" t="inlineStr"/>
     </row>
     <row r="885">
-      <c r="A885" t="inlineStr">
-        <is>
-          <t>65514</t>
-        </is>
+      <c r="A885" t="n">
+        <v>65514</v>
       </c>
       <c r="B885" t="inlineStr">
         <is>
@@ -35632,10 +35624,8 @@
       </c>
     </row>
     <row r="886">
-      <c r="A886" t="inlineStr">
-        <is>
-          <t>77232</t>
-        </is>
+      <c r="A886" t="n">
+        <v>77232</v>
       </c>
       <c r="B886" t="inlineStr">
         <is>
@@ -35675,10 +35665,8 @@
       </c>
     </row>
     <row r="887">
-      <c r="A887" t="inlineStr">
-        <is>
-          <t>77202</t>
-        </is>
+      <c r="A887" t="n">
+        <v>77202</v>
       </c>
       <c r="B887" t="inlineStr">
         <is>
@@ -35718,10 +35706,8 @@
       </c>
     </row>
     <row r="888">
-      <c r="A888" t="inlineStr">
-        <is>
-          <t>86650</t>
-        </is>
+      <c r="A888" t="n">
+        <v>86650</v>
       </c>
       <c r="B888" t="inlineStr">
         <is>
@@ -35761,10 +35747,8 @@
       </c>
     </row>
     <row r="889">
-      <c r="A889" t="inlineStr">
-        <is>
-          <t>77218</t>
-        </is>
+      <c r="A889" t="n">
+        <v>77218</v>
       </c>
       <c r="B889" t="inlineStr">
         <is>
@@ -35804,10 +35788,8 @@
       </c>
     </row>
     <row r="890">
-      <c r="A890" t="inlineStr">
-        <is>
-          <t>77243</t>
-        </is>
+      <c r="A890" t="n">
+        <v>77243</v>
       </c>
       <c r="B890" t="inlineStr">
         <is>
@@ -35847,10 +35829,8 @@
       </c>
     </row>
     <row r="891">
-      <c r="A891" t="inlineStr">
-        <is>
-          <t>77235</t>
-        </is>
+      <c r="A891" t="n">
+        <v>77235</v>
       </c>
       <c r="B891" t="inlineStr">
         <is>
@@ -35890,10 +35870,8 @@
       </c>
     </row>
     <row r="892">
-      <c r="A892" t="inlineStr">
-        <is>
-          <t>77228</t>
-        </is>
+      <c r="A892" t="n">
+        <v>77228</v>
       </c>
       <c r="B892" t="inlineStr">
         <is>
@@ -35933,10 +35911,8 @@
       </c>
     </row>
     <row r="893">
-      <c r="A893" t="inlineStr">
-        <is>
-          <t>69163</t>
-        </is>
+      <c r="A893" t="n">
+        <v>69163</v>
       </c>
       <c r="B893" t="inlineStr">
         <is>
@@ -35976,10 +35952,8 @@
       </c>
     </row>
     <row r="894">
-      <c r="A894" t="inlineStr">
-        <is>
-          <t>109205</t>
-        </is>
+      <c r="A894" t="n">
+        <v>109205</v>
       </c>
       <c r="B894" t="inlineStr">
         <is>
@@ -36019,10 +35993,8 @@
       </c>
     </row>
     <row r="895">
-      <c r="A895" t="inlineStr">
-        <is>
-          <t>65512</t>
-        </is>
+      <c r="A895" t="n">
+        <v>65512</v>
       </c>
       <c r="B895" t="inlineStr">
         <is>
@@ -36062,10 +36034,8 @@
       </c>
     </row>
     <row r="896">
-      <c r="A896" t="inlineStr">
-        <is>
-          <t>83384</t>
-        </is>
+      <c r="A896" t="n">
+        <v>83384</v>
       </c>
       <c r="B896" t="inlineStr">
         <is>
@@ -36105,10 +36075,8 @@
       </c>
     </row>
     <row r="897">
-      <c r="A897" t="inlineStr">
-        <is>
-          <t>77015</t>
-        </is>
+      <c r="A897" t="n">
+        <v>77015</v>
       </c>
       <c r="B897" t="inlineStr">
         <is>
@@ -36148,10 +36116,8 @@
       </c>
     </row>
     <row r="898">
-      <c r="A898" t="inlineStr">
-        <is>
-          <t>107728</t>
-        </is>
+      <c r="A898" t="n">
+        <v>107728</v>
       </c>
       <c r="B898" t="inlineStr">
         <is>
@@ -36191,10 +36157,8 @@
       </c>
     </row>
     <row r="899">
-      <c r="A899" t="inlineStr">
-        <is>
-          <t>65572</t>
-        </is>
+      <c r="A899" t="n">
+        <v>65572</v>
       </c>
       <c r="B899" t="inlineStr">
         <is>
@@ -36234,10 +36198,8 @@
       </c>
     </row>
     <row r="900">
-      <c r="A900" t="inlineStr">
-        <is>
-          <t>65511</t>
-        </is>
+      <c r="A900" t="n">
+        <v>65511</v>
       </c>
       <c r="B900" t="inlineStr">
         <is>
@@ -36277,10 +36239,8 @@
       </c>
     </row>
     <row r="901">
-      <c r="A901" t="inlineStr">
-        <is>
-          <t>65556</t>
-        </is>
+      <c r="A901" t="n">
+        <v>65556</v>
       </c>
       <c r="B901" t="inlineStr">
         <is>
@@ -36316,6 +36276,3286 @@
         </is>
       </c>
       <c r="I901" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="n">
+        <v>65542</v>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>3250 MacDonald St</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2573819, 'Longitude': -123.1680407}</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:22:00</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:32:17.174Z</t>
+        </is>
+      </c>
+      <c r="G902" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H902" t="inlineStr"/>
+      <c r="I902" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="n">
+        <v>65533</v>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>4615 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2449719, 'Longitude': -123.1540385}</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:22:00</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:56:29.329Z</t>
+        </is>
+      </c>
+      <c r="G903" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>2025-08-18T20:01:38.582Z</t>
+        </is>
+      </c>
+      <c r="I903" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="n">
+        <v>83068</v>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>3205 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.256927568207, 'Longitude': -123.153288960457}</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:22:00</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr"/>
+      <c r="G904" t="inlineStr"/>
+      <c r="H904" t="inlineStr"/>
+      <c r="I904" t="inlineStr"/>
+    </row>
+    <row r="905">
+      <c r="A905" t="n">
+        <v>65562</v>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>2808 W Broadway</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263883932125, 'Longitude': -123.168604373932}</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:22:00</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:30:54.416Z</t>
+        </is>
+      </c>
+      <c r="G905" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:17:36.405Z</t>
+        </is>
+      </c>
+      <c r="I905" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="n">
+        <v>113305</v>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>3596 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234385296079, 'Longitude': -123.184762001038}</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:22:00</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:30:12.587Z</t>
+        </is>
+      </c>
+      <c r="G906" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H906" t="inlineStr"/>
+      <c r="I906" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:22:00</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:36:50.738Z</t>
+        </is>
+      </c>
+      <c r="G907" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>2025-08-19T17:50:59.425Z</t>
+        </is>
+      </c>
+      <c r="I907" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="n">
+        <v>65554</v>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>1795 W Broadway</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264037962303, 'Longitude': -123.145408630371}</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:22:00</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:56:12.728Z</t>
+        </is>
+      </c>
+      <c r="G908" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:56:12.775Z</t>
+        </is>
+      </c>
+      <c r="I908" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="n">
+        <v>65571</v>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>4314 W 10th Ave</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263533861752, 'Longitude': -123.203430175781}</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:22:00</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:03:27.417Z</t>
+        </is>
+      </c>
+      <c r="G909" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>2025-08-19T16:29:09.259Z</t>
+        </is>
+      </c>
+      <c r="I909" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:22:00</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:52:47.547Z</t>
+        </is>
+      </c>
+      <c r="G910" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H910" t="inlineStr"/>
+      <c r="I910" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="n">
+        <v>32376</v>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>1503 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234634576953, 'Longitude': -123.139971792698}</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:22:00</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:41:31.203Z</t>
+        </is>
+      </c>
+      <c r="G911" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:30:08.915Z</t>
+        </is>
+      </c>
+      <c r="I911" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="n">
+        <v>65549</v>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>5702 Granville St</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234036184118, 'Longitude': -123.139244914055}</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:22:00</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:41:38.898Z</t>
+        </is>
+      </c>
+      <c r="G912" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:38:32.763Z</t>
+        </is>
+      </c>
+      <c r="I912" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:22:00</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:56:40.190Z</t>
+        </is>
+      </c>
+      <c r="G913" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:48:06.744Z</t>
+        </is>
+      </c>
+      <c r="I913" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:22:00</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:48:29.910Z</t>
+        </is>
+      </c>
+      <c r="G914" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:53:03.891Z</t>
+        </is>
+      </c>
+      <c r="I914" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="n">
+        <v>72747</v>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>1010 W King Edward Ave</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249188, 'Longitude': -123.127767}</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:22:00</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:51:42.830Z</t>
+        </is>
+      </c>
+      <c r="G915" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:43:58.867Z</t>
+        </is>
+      </c>
+      <c r="I915" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="n">
+        <v>32375</v>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>4110 Oak St</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.24894071957, 'Longitude': -123.127040863037}</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:22:00</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:51:34.593Z</t>
+        </is>
+      </c>
+      <c r="G916" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:13:19.073Z</t>
+        </is>
+      </c>
+      <c r="I916" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="n">
+        <v>65564</v>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>5680 Oak St</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234217162181, 'Longitude': -123.127684593201}</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:22:00</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:48:51.365Z</t>
+        </is>
+      </c>
+      <c r="G917" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:08:24.294Z</t>
+        </is>
+      </c>
+      <c r="I917" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="n">
+        <v>32372</v>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>6525 Oak St</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226226639452, 'Longitude': -123.128687739372}</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:22:00</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:12:05.514Z</t>
+        </is>
+      </c>
+      <c r="G918" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:33:23.261Z</t>
+        </is>
+      </c>
+      <c r="I918" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:22:00</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:55:59.572Z</t>
+        </is>
+      </c>
+      <c r="G919" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:55:59.603Z</t>
+        </is>
+      </c>
+      <c r="I919" t="n">
+        <v>199.9</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="n">
+        <v>65566</v>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>8072 Granville St</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.212495055855, 'Longitude': -123.14013004303}</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:22:00</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:37:02.379Z</t>
+        </is>
+      </c>
+      <c r="G920" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:30:08.359Z</t>
+        </is>
+      </c>
+      <c r="I920" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="n">
+        <v>65572</v>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:22:00</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:59:49.910Z</t>
+        </is>
+      </c>
+      <c r="G921" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:31:11.263Z</t>
+        </is>
+      </c>
+      <c r="I921" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="n">
+        <v>65558</v>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>1390 E 33rd Ave</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.240045470021, 'Longitude': -123.076765537262}</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:23:21</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:55:13.357Z</t>
+        </is>
+      </c>
+      <c r="G922" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:25:25.460Z</t>
+        </is>
+      </c>
+      <c r="I922" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="n">
+        <v>83394</v>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>4064 Fraser St</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.248864, 'Longitude': -123.09002}</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:23:21</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:15:27.819Z</t>
+        </is>
+      </c>
+      <c r="G923" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:15:27.854Z</t>
+        </is>
+      </c>
+      <c r="I923" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="n">
+        <v>65573</v>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>1396 E 41st Ave</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.232593005895, 'Longitude': -123.07728856802}</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:23:21</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:55:19.254Z</t>
+        </is>
+      </c>
+      <c r="G924" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:26:51.474Z</t>
+        </is>
+      </c>
+      <c r="I924" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="n">
+        <v>80714</v>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Husky</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>4933 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2397388, 'Longitude': -123.065748}</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:23:21</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>2025-08-20T17:36:39.483Z</t>
+        </is>
+      </c>
+      <c r="G925" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>2025-08-20T17:36:39.499Z</t>
+        </is>
+      </c>
+      <c r="I925" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="n">
+        <v>65552</v>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>2001 Kingsway</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.245312771918, 'Longitude': -123.064910173416}</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:23:21</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:43:49.403Z</t>
+        </is>
+      </c>
+      <c r="G926" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:03:38.233Z</t>
+        </is>
+      </c>
+      <c r="I926" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="n">
+        <v>65538</v>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>5252 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2372145, 'Longitude': -123.0650857}</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:23:21</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:27:07.443Z</t>
+        </is>
+      </c>
+      <c r="G927" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:06:44.322Z</t>
+        </is>
+      </c>
+      <c r="I927" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="n">
+        <v>90814</v>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>2277 Kingsway</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.242132845692, 'Longitude': -123.058204650879}</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:23:21</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:17:47.018Z</t>
+        </is>
+      </c>
+      <c r="G928" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:04:49.610Z</t>
+        </is>
+      </c>
+      <c r="I928" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="n">
+        <v>39768</v>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>5736 Main St</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2325708, 'Longitude': -123.1010069}</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:23:21</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:40:52.418Z</t>
+        </is>
+      </c>
+      <c r="G929" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:37:55.027Z</t>
+        </is>
+      </c>
+      <c r="I929" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="n">
+        <v>9710</v>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>1295 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259878978744, 'Longitude': -123.078074455261}</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:23:21</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:22:34.485Z</t>
+        </is>
+      </c>
+      <c r="G930" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:23:50.433Z</t>
+        </is>
+      </c>
+      <c r="I930" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="n">
+        <v>99146</v>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>1317 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259758544957, 'Longitude': -123.077272474766}</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:23:21</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:52:54.938Z</t>
+        </is>
+      </c>
+      <c r="G931" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:48:31.812Z</t>
+        </is>
+      </c>
+      <c r="I931" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="n">
+        <v>65560</v>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>1289 E Broadway</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.262693682723, 'Longitude': -123.078117370605}</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:23:21</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:38:00.698Z</t>
+        </is>
+      </c>
+      <c r="G932" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:18:54.353Z</t>
+        </is>
+      </c>
+      <c r="I932" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="n">
+        <v>65557</v>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>2120 Grandview Hwy S</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2591601, 'Longitude': -123.0617495}</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:23:21</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:12:29.736Z</t>
+        </is>
+      </c>
+      <c r="G933" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>2025-08-20T17:36:22.195Z</t>
+        </is>
+      </c>
+      <c r="I933" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="n">
+        <v>71502</v>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>2748 Main St</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2604441, 'Longitude': -123.1005869}</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:23:21</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:12:52.741Z</t>
+        </is>
+      </c>
+      <c r="G934" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:48:22.375Z</t>
+        </is>
+      </c>
+      <c r="I934" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="n">
+        <v>65559</v>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>6502 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.224996944057, 'Longitude': -123.065521717072}</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:23:21</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:37:03.284Z</t>
+        </is>
+      </c>
+      <c r="G935" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:59:10.689Z</t>
+        </is>
+      </c>
+      <c r="I935" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="n">
+        <v>89943</v>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>6808 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2220242, 'Longitude': -123.0654247}</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:23:21</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:36:52.827Z</t>
+        </is>
+      </c>
+      <c r="G936" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:59:15.108Z</t>
+        </is>
+      </c>
+      <c r="I936" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:23:21</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:04:01.398Z</t>
+        </is>
+      </c>
+      <c r="G937" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:28:38.427Z</t>
+        </is>
+      </c>
+      <c r="I937" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="n">
+        <v>65537</v>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>2918 Kingsway</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.23608, 'Longitude': -123.0454858}</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:23:21</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:07:14.786Z</t>
+        </is>
+      </c>
+      <c r="G938" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:24:44.587Z</t>
+        </is>
+      </c>
+      <c r="I938" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:23:21</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:04:03.802Z</t>
+        </is>
+      </c>
+      <c r="G939" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:30:10.518Z</t>
+        </is>
+      </c>
+      <c r="I939" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="n">
+        <v>65535</v>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>2605 E 49th Ave</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2251291, 'Longitude': -123.0545048}</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:23:21</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:17:16.617Z</t>
+        </is>
+      </c>
+      <c r="G940" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="H940" t="inlineStr"/>
+      <c r="I940" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="n">
+        <v>65539</v>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>2902 Grandview Hwy</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2579053, 'Longitude': -123.0438464}</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:23:21</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:14:36.931Z</t>
+        </is>
+      </c>
+      <c r="G941" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:29:57.825Z</t>
+        </is>
+      </c>
+      <c r="I941" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="n">
+        <v>77015</v>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169873456637, 'Longitude': -123.091178619746}</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:24:40</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:17:49.565Z</t>
+        </is>
+      </c>
+      <c r="G942" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:17:49.596Z</t>
+        </is>
+      </c>
+      <c r="I942" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="n">
+        <v>65511</v>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:24:40</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:54:19.301Z</t>
+        </is>
+      </c>
+      <c r="G943" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:54:19.348Z</t>
+        </is>
+      </c>
+      <c r="I943" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="n">
+        <v>86650</v>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169856952787, 'Longitude': -123.123961687088}</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:24:40</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:02:30.258Z</t>
+        </is>
+      </c>
+      <c r="G944" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:36:33.523Z</t>
+        </is>
+      </c>
+      <c r="I944" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="n">
+        <v>77218</v>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.173339635958, 'Longitude': -123.124954104424}</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:24:40</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:33:42.862Z</t>
+        </is>
+      </c>
+      <c r="G945" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:33:42.893Z</t>
+        </is>
+      </c>
+      <c r="I945" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="n">
+        <v>77228</v>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1843249, 'Longitude': -123.1236078}</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:24:40</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:15:29.444Z</t>
+        </is>
+      </c>
+      <c r="G946" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:49:44.964Z</t>
+        </is>
+      </c>
+      <c r="I946" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="n">
+        <v>83384</v>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192001, 'Longitude': -123.124004}</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:24:40</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:48:33.112Z</t>
+        </is>
+      </c>
+      <c r="G947" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:12:41.249Z</t>
+        </is>
+      </c>
+      <c r="I947" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="n">
+        <v>77202</v>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.162989071149, 'Longitude': -123.134229183197}</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:24:40</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:18:46.580Z</t>
+        </is>
+      </c>
+      <c r="G948" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:33:39.861Z</t>
+        </is>
+      </c>
+      <c r="I948" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="n">
+        <v>77243</v>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.179182137142, 'Longitude': -123.137152791023}</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:24:40</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:03:06.427Z</t>
+        </is>
+      </c>
+      <c r="G949" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:47:26.975Z</t>
+        </is>
+      </c>
+      <c r="I949" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="n">
+        <v>83387</v>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>710 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21081995506, 'Longitude': -123.090755939484}</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:24:40</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:12:16.228Z</t>
+        </is>
+      </c>
+      <c r="G950" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:56:27.190Z</t>
+        </is>
+      </c>
+      <c r="I950" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="n">
+        <v>65551</v>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>688 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210798928329, 'Longitude': -123.09152841568}</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:24:40</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:12:47.334Z</t>
+        </is>
+      </c>
+      <c r="G951" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:56:51.419Z</t>
+        </is>
+      </c>
+      <c r="I951" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="n">
+        <v>77235</v>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.18409178594, 'Longitude': -123.136823830688}</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:24:40</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:58:39.983Z</t>
+        </is>
+      </c>
+      <c r="G952" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:46:41.801Z</t>
+        </is>
+      </c>
+      <c r="I952" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="n">
+        <v>82925</v>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>350 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210245, 'Longitude': -123.099328}</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:24:40</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:17:17.611Z</t>
+        </is>
+      </c>
+      <c r="G953" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:17:17.685Z</t>
+        </is>
+      </c>
+      <c r="I953" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="n">
+        <v>109205</v>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.133556536531, 'Longitude': -123.092424273491}</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:24:40</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:13:47.159Z</t>
+        </is>
+      </c>
+      <c r="G954" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:25:08.457Z</t>
+        </is>
+      </c>
+      <c r="I954" t="n">
+        <v>178.9</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="n">
+        <v>65540</v>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>196 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2106867, 'Longitude': -123.1027436}</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:24:40</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:16:59.117Z</t>
+        </is>
+      </c>
+      <c r="G955" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:16:59.195Z</t>
+        </is>
+      </c>
+      <c r="I955" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="n">
+        <v>65512</v>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1328393, 'Longitude': -123.0926312}</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:24:40</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:13:57.719Z</t>
+        </is>
+      </c>
+      <c r="G956" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:25:00.452Z</t>
+        </is>
+      </c>
+      <c r="I956" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="n">
+        <v>77205</v>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1558882, 'Longitude': -123.1369625}</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:24:40</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:24:46.885Z</t>
+        </is>
+      </c>
+      <c r="G957" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:11:19.742Z</t>
+        </is>
+      </c>
+      <c r="I957" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:24:40</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:04:03.802Z</t>
+        </is>
+      </c>
+      <c r="G958" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:30:10.518Z</t>
+        </is>
+      </c>
+      <c r="I958" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:24:40</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:04:01.398Z</t>
+        </is>
+      </c>
+      <c r="G959" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:28:38.427Z</t>
+        </is>
+      </c>
+      <c r="I959" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="n">
+        <v>65556</v>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20806537721, 'Longitude': -123.123285770416}</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:24:40</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:11:11.549Z</t>
+        </is>
+      </c>
+      <c r="G960" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>2025-08-20T07:11:27.660Z</t>
+        </is>
+      </c>
+      <c r="I960" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="n">
+        <v>86937</v>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>8655 Boundary Rd</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20476, 'Longitude': -123.02398}</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:24:40</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:38:00.169Z</t>
+        </is>
+      </c>
+      <c r="G961" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:38:00.200Z</t>
+        </is>
+      </c>
+      <c r="I961" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>65515</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>4011 Francis Rd</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.14867500071, 'Longitude': -123.180856704712}</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:26:03</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:23:12.406Z</t>
+        </is>
+      </c>
+      <c r="G962" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:11:08.658Z</t>
+        </is>
+      </c>
+      <c r="I962" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>77205</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1558882, 'Longitude': -123.1369625}</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:26:03</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:24:46.885Z</t>
+        </is>
+      </c>
+      <c r="G963" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:11:19.742Z</t>
+        </is>
+      </c>
+      <c r="I963" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>77223</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>7991 No 1 Rd</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.155888686563, 'Longitude': -123.181414604187}</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:26:03</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr"/>
+      <c r="G964" t="inlineStr"/>
+      <c r="H964" t="inlineStr"/>
+      <c r="I964" t="inlineStr"/>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>65514</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>7980 Williams Rd</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.140582914547, 'Longitude': -123.137168884277}</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:26:03</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:37:11.831Z</t>
+        </is>
+      </c>
+      <c r="G965" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:22:52.988Z</t>
+        </is>
+      </c>
+      <c r="I965" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>77232</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900 Westminster Hwy </t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1698419, 'Longitude': -123.159282}</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:26:03</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:12:23.435Z</t>
+        </is>
+      </c>
+      <c r="G966" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:30:25.660Z</t>
+        </is>
+      </c>
+      <c r="I966" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>77202</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.162989071149, 'Longitude': -123.134229183197}</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:26:03</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:18:46.580Z</t>
+        </is>
+      </c>
+      <c r="G967" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:33:39.861Z</t>
+        </is>
+      </c>
+      <c r="I967" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>86650</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169856952787, 'Longitude': -123.123961687088}</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:26:03</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:02:30.258Z</t>
+        </is>
+      </c>
+      <c r="G968" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:36:33.523Z</t>
+        </is>
+      </c>
+      <c r="I968" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>77218</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.173339635958, 'Longitude': -123.124954104424}</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:26:03</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:33:42.862Z</t>
+        </is>
+      </c>
+      <c r="G969" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:33:42.893Z</t>
+        </is>
+      </c>
+      <c r="I969" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>77243</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.179182137142, 'Longitude': -123.137152791023}</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:26:03</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:03:06.427Z</t>
+        </is>
+      </c>
+      <c r="G970" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:47:26.975Z</t>
+        </is>
+      </c>
+      <c r="I970" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>77235</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.18409178594, 'Longitude': -123.136823830688}</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:26:03</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:58:39.983Z</t>
+        </is>
+      </c>
+      <c r="G971" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:46:41.801Z</t>
+        </is>
+      </c>
+      <c r="I971" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>77228</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1843249, 'Longitude': -123.1236078}</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:26:03</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:15:29.444Z</t>
+        </is>
+      </c>
+      <c r="G972" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:49:44.964Z</t>
+        </is>
+      </c>
+      <c r="I972" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>69163</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>5111 Grant McConachie Way</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192919, 'Longitude': -123.166797}</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:26:03</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>2025-08-20T17:39:37.739Z</t>
+        </is>
+      </c>
+      <c r="G973" t="n">
+        <v>168.9</v>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>2025-08-20T10:13:47.773Z</t>
+        </is>
+      </c>
+      <c r="I973" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>109205</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.133556536531, 'Longitude': -123.092424273491}</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:26:03</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:13:47.159Z</t>
+        </is>
+      </c>
+      <c r="G974" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:25:08.457Z</t>
+        </is>
+      </c>
+      <c r="I974" t="n">
+        <v>178.9</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>65512</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1328393, 'Longitude': -123.0926312}</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:26:03</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:13:57.719Z</t>
+        </is>
+      </c>
+      <c r="G975" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:25:00.452Z</t>
+        </is>
+      </c>
+      <c r="I975" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>83384</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192001, 'Longitude': -123.124004}</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:26:03</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:48:33.112Z</t>
+        </is>
+      </c>
+      <c r="G976" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:12:41.249Z</t>
+        </is>
+      </c>
+      <c r="I976" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>77015</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169873456637, 'Longitude': -123.091178619746}</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:26:03</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:17:49.565Z</t>
+        </is>
+      </c>
+      <c r="G977" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:17:49.596Z</t>
+        </is>
+      </c>
+      <c r="I977" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>107728</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>8884 Granville St</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2054215, 'Longitude': -123.1401677}</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:26:03</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:58:08.856Z</t>
+        </is>
+      </c>
+      <c r="G978" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>2025-08-19T21:28:32.275Z</t>
+        </is>
+      </c>
+      <c r="I978" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>65572</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:26:03</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:59:49.910Z</t>
+        </is>
+      </c>
+      <c r="G979" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:31:11.263Z</t>
+        </is>
+      </c>
+      <c r="I979" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>65511</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:26:03</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:54:19.301Z</t>
+        </is>
+      </c>
+      <c r="G980" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:54:19.348Z</t>
+        </is>
+      </c>
+      <c r="I980" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>65556</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20806537721, 'Longitude': -123.123285770416}</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:26:03</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:11:11.549Z</t>
+        </is>
+      </c>
+      <c r="G981" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t>2025-08-20T07:11:27.660Z</t>
+        </is>
+      </c>
+      <c r="I981" t="n">
         <v>179.9</v>
       </c>
     </row>

--- a/data/gas_prices.xlsx
+++ b/data/gas_prices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I981"/>
+  <dimension ref="A1:I1061"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38712,10 +38712,8 @@
       </c>
     </row>
     <row r="962">
-      <c r="A962" t="inlineStr">
-        <is>
-          <t>65515</t>
-        </is>
+      <c r="A962" t="n">
+        <v>65515</v>
       </c>
       <c r="B962" t="inlineStr">
         <is>
@@ -38755,10 +38753,8 @@
       </c>
     </row>
     <row r="963">
-      <c r="A963" t="inlineStr">
-        <is>
-          <t>77205</t>
-        </is>
+      <c r="A963" t="n">
+        <v>77205</v>
       </c>
       <c r="B963" t="inlineStr">
         <is>
@@ -38798,10 +38794,8 @@
       </c>
     </row>
     <row r="964">
-      <c r="A964" t="inlineStr">
-        <is>
-          <t>77223</t>
-        </is>
+      <c r="A964" t="n">
+        <v>77223</v>
       </c>
       <c r="B964" t="inlineStr">
         <is>
@@ -38829,10 +38823,8 @@
       <c r="I964" t="inlineStr"/>
     </row>
     <row r="965">
-      <c r="A965" t="inlineStr">
-        <is>
-          <t>65514</t>
-        </is>
+      <c r="A965" t="n">
+        <v>65514</v>
       </c>
       <c r="B965" t="inlineStr">
         <is>
@@ -38872,10 +38864,8 @@
       </c>
     </row>
     <row r="966">
-      <c r="A966" t="inlineStr">
-        <is>
-          <t>77232</t>
-        </is>
+      <c r="A966" t="n">
+        <v>77232</v>
       </c>
       <c r="B966" t="inlineStr">
         <is>
@@ -38915,10 +38905,8 @@
       </c>
     </row>
     <row r="967">
-      <c r="A967" t="inlineStr">
-        <is>
-          <t>77202</t>
-        </is>
+      <c r="A967" t="n">
+        <v>77202</v>
       </c>
       <c r="B967" t="inlineStr">
         <is>
@@ -38958,10 +38946,8 @@
       </c>
     </row>
     <row r="968">
-      <c r="A968" t="inlineStr">
-        <is>
-          <t>86650</t>
-        </is>
+      <c r="A968" t="n">
+        <v>86650</v>
       </c>
       <c r="B968" t="inlineStr">
         <is>
@@ -39001,10 +38987,8 @@
       </c>
     </row>
     <row r="969">
-      <c r="A969" t="inlineStr">
-        <is>
-          <t>77218</t>
-        </is>
+      <c r="A969" t="n">
+        <v>77218</v>
       </c>
       <c r="B969" t="inlineStr">
         <is>
@@ -39044,10 +39028,8 @@
       </c>
     </row>
     <row r="970">
-      <c r="A970" t="inlineStr">
-        <is>
-          <t>77243</t>
-        </is>
+      <c r="A970" t="n">
+        <v>77243</v>
       </c>
       <c r="B970" t="inlineStr">
         <is>
@@ -39087,10 +39069,8 @@
       </c>
     </row>
     <row r="971">
-      <c r="A971" t="inlineStr">
-        <is>
-          <t>77235</t>
-        </is>
+      <c r="A971" t="n">
+        <v>77235</v>
       </c>
       <c r="B971" t="inlineStr">
         <is>
@@ -39130,10 +39110,8 @@
       </c>
     </row>
     <row r="972">
-      <c r="A972" t="inlineStr">
-        <is>
-          <t>77228</t>
-        </is>
+      <c r="A972" t="n">
+        <v>77228</v>
       </c>
       <c r="B972" t="inlineStr">
         <is>
@@ -39173,10 +39151,8 @@
       </c>
     </row>
     <row r="973">
-      <c r="A973" t="inlineStr">
-        <is>
-          <t>69163</t>
-        </is>
+      <c r="A973" t="n">
+        <v>69163</v>
       </c>
       <c r="B973" t="inlineStr">
         <is>
@@ -39216,10 +39192,8 @@
       </c>
     </row>
     <row r="974">
-      <c r="A974" t="inlineStr">
-        <is>
-          <t>109205</t>
-        </is>
+      <c r="A974" t="n">
+        <v>109205</v>
       </c>
       <c r="B974" t="inlineStr">
         <is>
@@ -39259,10 +39233,8 @@
       </c>
     </row>
     <row r="975">
-      <c r="A975" t="inlineStr">
-        <is>
-          <t>65512</t>
-        </is>
+      <c r="A975" t="n">
+        <v>65512</v>
       </c>
       <c r="B975" t="inlineStr">
         <is>
@@ -39302,10 +39274,8 @@
       </c>
     </row>
     <row r="976">
-      <c r="A976" t="inlineStr">
-        <is>
-          <t>83384</t>
-        </is>
+      <c r="A976" t="n">
+        <v>83384</v>
       </c>
       <c r="B976" t="inlineStr">
         <is>
@@ -39345,10 +39315,8 @@
       </c>
     </row>
     <row r="977">
-      <c r="A977" t="inlineStr">
-        <is>
-          <t>77015</t>
-        </is>
+      <c r="A977" t="n">
+        <v>77015</v>
       </c>
       <c r="B977" t="inlineStr">
         <is>
@@ -39388,10 +39356,8 @@
       </c>
     </row>
     <row r="978">
-      <c r="A978" t="inlineStr">
-        <is>
-          <t>107728</t>
-        </is>
+      <c r="A978" t="n">
+        <v>107728</v>
       </c>
       <c r="B978" t="inlineStr">
         <is>
@@ -39431,10 +39397,8 @@
       </c>
     </row>
     <row r="979">
-      <c r="A979" t="inlineStr">
-        <is>
-          <t>65572</t>
-        </is>
+      <c r="A979" t="n">
+        <v>65572</v>
       </c>
       <c r="B979" t="inlineStr">
         <is>
@@ -39474,10 +39438,8 @@
       </c>
     </row>
     <row r="980">
-      <c r="A980" t="inlineStr">
-        <is>
-          <t>65511</t>
-        </is>
+      <c r="A980" t="n">
+        <v>65511</v>
       </c>
       <c r="B980" t="inlineStr">
         <is>
@@ -39517,10 +39479,8 @@
       </c>
     </row>
     <row r="981">
-      <c r="A981" t="inlineStr">
-        <is>
-          <t>65556</t>
-        </is>
+      <c r="A981" t="n">
+        <v>65556</v>
       </c>
       <c r="B981" t="inlineStr">
         <is>
@@ -39558,6 +39518,2958 @@
       <c r="I981" t="n">
         <v>179.9</v>
       </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="n">
+        <v>65542</v>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>3250 MacDonald St</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2573819, 'Longitude': -123.1680407}</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:42:01</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:32:17.174Z</t>
+        </is>
+      </c>
+      <c r="G982" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H982" t="inlineStr"/>
+      <c r="I982" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="n">
+        <v>65533</v>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>4615 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2449719, 'Longitude': -123.1540385}</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:42:01</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:29:22.296Z</t>
+        </is>
+      </c>
+      <c r="G983" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H983" t="inlineStr"/>
+      <c r="I983" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="n">
+        <v>83068</v>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>3205 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.256927568207, 'Longitude': -123.153288960457}</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:42:01</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr"/>
+      <c r="G984" t="inlineStr"/>
+      <c r="H984" t="inlineStr"/>
+      <c r="I984" t="inlineStr"/>
+    </row>
+    <row r="985">
+      <c r="A985" t="n">
+        <v>65562</v>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>2808 W Broadway</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263883932125, 'Longitude': -123.168604373932}</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:42:01</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:30:54.416Z</t>
+        </is>
+      </c>
+      <c r="G985" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:17:36.405Z</t>
+        </is>
+      </c>
+      <c r="I985" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="n">
+        <v>113305</v>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>3596 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234385296079, 'Longitude': -123.184762001038}</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:42:01</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>2025-08-20T14:30:12.587Z</t>
+        </is>
+      </c>
+      <c r="G986" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H986" t="inlineStr"/>
+      <c r="I986" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:42:01</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>2025-08-20T12:36:50.738Z</t>
+        </is>
+      </c>
+      <c r="G987" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>2025-08-19T17:50:59.425Z</t>
+        </is>
+      </c>
+      <c r="I987" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="n">
+        <v>65554</v>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>1795 W Broadway</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264037962303, 'Longitude': -123.145408630371}</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:42:01</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:56:12.728Z</t>
+        </is>
+      </c>
+      <c r="G988" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:56:12.775Z</t>
+        </is>
+      </c>
+      <c r="I988" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="n">
+        <v>65571</v>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>4314 W 10th Ave</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263533861752, 'Longitude': -123.203430175781}</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:42:01</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:03:27.417Z</t>
+        </is>
+      </c>
+      <c r="G989" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>2025-08-19T16:29:09.259Z</t>
+        </is>
+      </c>
+      <c r="I989" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:42:01</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:52:47.547Z</t>
+        </is>
+      </c>
+      <c r="G990" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H990" t="inlineStr"/>
+      <c r="I990" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="n">
+        <v>32376</v>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>1503 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234634576953, 'Longitude': -123.139971792698}</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:42:01</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:41:31.203Z</t>
+        </is>
+      </c>
+      <c r="G991" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:30:08.915Z</t>
+        </is>
+      </c>
+      <c r="I991" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="n">
+        <v>65549</v>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>5702 Granville St</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234036184118, 'Longitude': -123.139244914055}</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:42:01</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:41:38.898Z</t>
+        </is>
+      </c>
+      <c r="G992" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:38:32.763Z</t>
+        </is>
+      </c>
+      <c r="I992" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:42:01</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:56:40.190Z</t>
+        </is>
+      </c>
+      <c r="G993" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:48:06.744Z</t>
+        </is>
+      </c>
+      <c r="I993" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:42:01</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:48:29.910Z</t>
+        </is>
+      </c>
+      <c r="G994" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:53:03.891Z</t>
+        </is>
+      </c>
+      <c r="I994" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="n">
+        <v>72747</v>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>1010 W King Edward Ave</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249188, 'Longitude': -123.127767}</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:42:01</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:51:42.830Z</t>
+        </is>
+      </c>
+      <c r="G995" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:43:58.867Z</t>
+        </is>
+      </c>
+      <c r="I995" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="n">
+        <v>32375</v>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>4110 Oak St</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.24894071957, 'Longitude': -123.127040863037}</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:42:01</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:51:34.593Z</t>
+        </is>
+      </c>
+      <c r="G996" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:13:19.073Z</t>
+        </is>
+      </c>
+      <c r="I996" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="n">
+        <v>65564</v>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>5680 Oak St</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234217162181, 'Longitude': -123.127684593201}</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:42:01</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:48:51.365Z</t>
+        </is>
+      </c>
+      <c r="G997" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:08:24.294Z</t>
+        </is>
+      </c>
+      <c r="I997" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="n">
+        <v>32372</v>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>6525 Oak St</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226226639452, 'Longitude': -123.128687739372}</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:42:01</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:12:05.514Z</t>
+        </is>
+      </c>
+      <c r="G998" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H998" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:33:23.261Z</t>
+        </is>
+      </c>
+      <c r="I998" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:42:01</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:55:59.572Z</t>
+        </is>
+      </c>
+      <c r="G999" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H999" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:55:59.603Z</t>
+        </is>
+      </c>
+      <c r="I999" t="n">
+        <v>199.9</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="n">
+        <v>65566</v>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>8072 Granville St</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.212495055855, 'Longitude': -123.14013004303}</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:42:01</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:37:02.379Z</t>
+        </is>
+      </c>
+      <c r="G1000" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:30:08.359Z</t>
+        </is>
+      </c>
+      <c r="I1000" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="n">
+        <v>65572</v>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:42:01</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:59:49.910Z</t>
+        </is>
+      </c>
+      <c r="G1001" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1001" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:31:11.263Z</t>
+        </is>
+      </c>
+      <c r="I1001" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="n">
+        <v>65558</v>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>1390 E 33rd Ave</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.240045470021, 'Longitude': -123.076765537262}</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:43:23</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:55:13.357Z</t>
+        </is>
+      </c>
+      <c r="G1002" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1002" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:25:25.460Z</t>
+        </is>
+      </c>
+      <c r="I1002" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="n">
+        <v>83394</v>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>4064 Fraser St</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.248864, 'Longitude': -123.09002}</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:43:23</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:15:27.819Z</t>
+        </is>
+      </c>
+      <c r="G1003" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1003" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:15:27.854Z</t>
+        </is>
+      </c>
+      <c r="I1003" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="n">
+        <v>65573</v>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>1396 E 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.232593005895, 'Longitude': -123.07728856802}</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:43:23</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:55:19.254Z</t>
+        </is>
+      </c>
+      <c r="G1004" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1004" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:26:51.474Z</t>
+        </is>
+      </c>
+      <c r="I1004" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="n">
+        <v>80714</v>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>Husky</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>4933 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2397388, 'Longitude': -123.065748}</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:43:23</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>2025-08-20T17:36:39.483Z</t>
+        </is>
+      </c>
+      <c r="G1005" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1005" t="inlineStr">
+        <is>
+          <t>2025-08-20T17:36:39.499Z</t>
+        </is>
+      </c>
+      <c r="I1005" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="n">
+        <v>65552</v>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>2001 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.245312771918, 'Longitude': -123.064910173416}</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:43:23</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:43:49.403Z</t>
+        </is>
+      </c>
+      <c r="G1006" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1006" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:03:38.233Z</t>
+        </is>
+      </c>
+      <c r="I1006" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="n">
+        <v>65538</v>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>5252 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2372145, 'Longitude': -123.0650857}</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:43:23</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:27:07.443Z</t>
+        </is>
+      </c>
+      <c r="G1007" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>2025-08-20T01:06:44.322Z</t>
+        </is>
+      </c>
+      <c r="I1007" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="n">
+        <v>90814</v>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>2277 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.242132845692, 'Longitude': -123.058204650879}</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:43:23</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:17:47.018Z</t>
+        </is>
+      </c>
+      <c r="G1008" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1008" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:04:49.610Z</t>
+        </is>
+      </c>
+      <c r="I1008" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="n">
+        <v>39768</v>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>5736 Main St</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2325708, 'Longitude': -123.1010069}</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:43:23</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:40:52.418Z</t>
+        </is>
+      </c>
+      <c r="G1009" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:37:55.027Z</t>
+        </is>
+      </c>
+      <c r="I1009" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="n">
+        <v>9710</v>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>1295 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259878978744, 'Longitude': -123.078074455261}</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:43:23</t>
+        </is>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:22:34.485Z</t>
+        </is>
+      </c>
+      <c r="G1010" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H1010" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:23:50.433Z</t>
+        </is>
+      </c>
+      <c r="I1010" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="n">
+        <v>99146</v>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>1317 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259758544957, 'Longitude': -123.077272474766}</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:43:23</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:23:00.352Z</t>
+        </is>
+      </c>
+      <c r="G1011" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:48:31.812Z</t>
+        </is>
+      </c>
+      <c r="I1011" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="n">
+        <v>65560</v>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>1289 E Broadway</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.262693682723, 'Longitude': -123.078117370605}</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:43:23</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:22:50.240Z</t>
+        </is>
+      </c>
+      <c r="G1012" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:18:54.353Z</t>
+        </is>
+      </c>
+      <c r="I1012" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="n">
+        <v>65557</v>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>2120 Grandview Hwy S</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2591601, 'Longitude': -123.0617495}</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:43:23</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:12:29.736Z</t>
+        </is>
+      </c>
+      <c r="G1013" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>2025-08-20T17:36:22.195Z</t>
+        </is>
+      </c>
+      <c r="I1013" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="n">
+        <v>71502</v>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>2748 Main St</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2604441, 'Longitude': -123.1005869}</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:43:23</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:12:52.741Z</t>
+        </is>
+      </c>
+      <c r="G1014" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1014" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:48:22.375Z</t>
+        </is>
+      </c>
+      <c r="I1014" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="n">
+        <v>65559</v>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>6502 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.224996944057, 'Longitude': -123.065521717072}</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:43:23</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:37:03.284Z</t>
+        </is>
+      </c>
+      <c r="G1015" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:59:10.689Z</t>
+        </is>
+      </c>
+      <c r="I1015" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="n">
+        <v>89943</v>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>6808 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2220242, 'Longitude': -123.0654247}</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:43:23</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:36:52.827Z</t>
+        </is>
+      </c>
+      <c r="G1016" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:59:15.108Z</t>
+        </is>
+      </c>
+      <c r="I1016" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:43:23</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:04:01.398Z</t>
+        </is>
+      </c>
+      <c r="G1017" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1017" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:28:38.427Z</t>
+        </is>
+      </c>
+      <c r="I1017" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="n">
+        <v>65537</v>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>2918 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.23608, 'Longitude': -123.0454858}</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:43:23</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:07:14.786Z</t>
+        </is>
+      </c>
+      <c r="G1018" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1018" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:24:44.587Z</t>
+        </is>
+      </c>
+      <c r="I1018" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:43:23</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:04:03.802Z</t>
+        </is>
+      </c>
+      <c r="G1019" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1019" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:30:10.518Z</t>
+        </is>
+      </c>
+      <c r="I1019" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="n">
+        <v>65535</v>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>2605 E 49th Ave</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2251291, 'Longitude': -123.0545048}</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:43:23</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:17:16.617Z</t>
+        </is>
+      </c>
+      <c r="G1020" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="H1020" t="inlineStr"/>
+      <c r="I1020" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="n">
+        <v>65539</v>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>2902 Grandview Hwy</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2579053, 'Longitude': -123.0438464}</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:43:23</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:14:36.931Z</t>
+        </is>
+      </c>
+      <c r="G1021" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1021" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:29:57.825Z</t>
+        </is>
+      </c>
+      <c r="I1021" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="n">
+        <v>77015</v>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169873456637, 'Longitude': -123.091178619746}</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:44:33</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:31:25.486Z</t>
+        </is>
+      </c>
+      <c r="G1022" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1022" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:31:22.600Z</t>
+        </is>
+      </c>
+      <c r="I1022" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="n">
+        <v>65511</v>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:44:33</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:54:19.301Z</t>
+        </is>
+      </c>
+      <c r="G1023" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1023" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:54:19.348Z</t>
+        </is>
+      </c>
+      <c r="I1023" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="n">
+        <v>86650</v>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169856952787, 'Longitude': -123.123961687088}</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:44:33</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:02:30.258Z</t>
+        </is>
+      </c>
+      <c r="G1024" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="H1024" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:36:33.523Z</t>
+        </is>
+      </c>
+      <c r="I1024" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="n">
+        <v>77218</v>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.173339635958, 'Longitude': -123.124954104424}</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:44:33</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:33:42.862Z</t>
+        </is>
+      </c>
+      <c r="G1025" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1025" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:33:42.893Z</t>
+        </is>
+      </c>
+      <c r="I1025" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="n">
+        <v>77228</v>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:44:33</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr"/>
+      <c r="G1026" t="inlineStr"/>
+      <c r="H1026" t="inlineStr"/>
+      <c r="I1026" t="inlineStr"/>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="n">
+        <v>83384</v>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:44:33</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr"/>
+      <c r="G1027" t="inlineStr"/>
+      <c r="H1027" t="inlineStr"/>
+      <c r="I1027" t="inlineStr"/>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="n">
+        <v>77202</v>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:44:33</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr"/>
+      <c r="G1028" t="inlineStr"/>
+      <c r="H1028" t="inlineStr"/>
+      <c r="I1028" t="inlineStr"/>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="n">
+        <v>77243</v>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:44:33</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr"/>
+      <c r="G1029" t="inlineStr"/>
+      <c r="H1029" t="inlineStr"/>
+      <c r="I1029" t="inlineStr"/>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="n">
+        <v>83387</v>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>710 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:44:33</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr"/>
+      <c r="G1030" t="inlineStr"/>
+      <c r="H1030" t="inlineStr"/>
+      <c r="I1030" t="inlineStr"/>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="n">
+        <v>65551</v>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>688 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210798928329, 'Longitude': -123.09152841568}</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:44:33</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:12:47.334Z</t>
+        </is>
+      </c>
+      <c r="G1031" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:56:51.419Z</t>
+        </is>
+      </c>
+      <c r="I1031" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="n">
+        <v>77235</v>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:44:33</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr"/>
+      <c r="G1032" t="inlineStr"/>
+      <c r="H1032" t="inlineStr"/>
+      <c r="I1032" t="inlineStr"/>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="n">
+        <v>82925</v>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>350 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210245, 'Longitude': -123.099328}</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:44:33</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:17:17.611Z</t>
+        </is>
+      </c>
+      <c r="G1033" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:17:17.685Z</t>
+        </is>
+      </c>
+      <c r="I1033" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="n">
+        <v>109205</v>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:44:33</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr"/>
+      <c r="G1034" t="inlineStr"/>
+      <c r="H1034" t="inlineStr"/>
+      <c r="I1034" t="inlineStr"/>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="n">
+        <v>65540</v>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>196 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:44:33</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr"/>
+      <c r="G1035" t="inlineStr"/>
+      <c r="H1035" t="inlineStr"/>
+      <c r="I1035" t="inlineStr"/>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="n">
+        <v>65512</v>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:44:33</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr"/>
+      <c r="G1036" t="inlineStr"/>
+      <c r="H1036" t="inlineStr"/>
+      <c r="I1036" t="inlineStr"/>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="n">
+        <v>77205</v>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1558882, 'Longitude': -123.1369625}</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:44:33</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:33:53.480Z</t>
+        </is>
+      </c>
+      <c r="G1037" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>2025-08-20T03:11:19.742Z</t>
+        </is>
+      </c>
+      <c r="I1037" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:44:33</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr"/>
+      <c r="G1038" t="inlineStr"/>
+      <c r="H1038" t="inlineStr"/>
+      <c r="I1038" t="inlineStr"/>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:44:33</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr"/>
+      <c r="G1039" t="inlineStr"/>
+      <c r="H1039" t="inlineStr"/>
+      <c r="I1039" t="inlineStr"/>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="n">
+        <v>65556</v>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20806537721, 'Longitude': -123.123285770416}</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:44:33</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:11:11.549Z</t>
+        </is>
+      </c>
+      <c r="G1040" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>2025-08-20T07:11:27.660Z</t>
+        </is>
+      </c>
+      <c r="I1040" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="n">
+        <v>86937</v>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>8655 Boundary Rd</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:44:33</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr"/>
+      <c r="G1041" t="inlineStr"/>
+      <c r="H1041" t="inlineStr"/>
+      <c r="I1041" t="inlineStr"/>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>65515</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>4011 Francis Rd</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.14867500071, 'Longitude': -123.180856704712}</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:45:50</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:23:12.406Z</t>
+        </is>
+      </c>
+      <c r="G1042" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:11:08.658Z</t>
+        </is>
+      </c>
+      <c r="I1042" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>77205</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:45:50</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr"/>
+      <c r="G1043" t="inlineStr"/>
+      <c r="H1043" t="inlineStr"/>
+      <c r="I1043" t="inlineStr"/>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>77223</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>7991 No 1 Rd</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:45:50</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr"/>
+      <c r="G1044" t="inlineStr"/>
+      <c r="H1044" t="inlineStr"/>
+      <c r="I1044" t="inlineStr"/>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>65514</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>7980 Williams Rd</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:45:50</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr"/>
+      <c r="G1045" t="inlineStr"/>
+      <c r="H1045" t="inlineStr"/>
+      <c r="I1045" t="inlineStr"/>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>77232</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900 Westminster Hwy </t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:45:50</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr"/>
+      <c r="G1046" t="inlineStr"/>
+      <c r="H1046" t="inlineStr"/>
+      <c r="I1046" t="inlineStr"/>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>77202</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.162989071149, 'Longitude': -123.134229183197}</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:45:50</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:34:01.297Z</t>
+        </is>
+      </c>
+      <c r="G1047" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:33:39.861Z</t>
+        </is>
+      </c>
+      <c r="I1047" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>86650</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:45:50</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr"/>
+      <c r="G1048" t="inlineStr"/>
+      <c r="H1048" t="inlineStr"/>
+      <c r="I1048" t="inlineStr"/>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>77218</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:45:50</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr"/>
+      <c r="G1049" t="inlineStr"/>
+      <c r="H1049" t="inlineStr"/>
+      <c r="I1049" t="inlineStr"/>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>77243</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:45:50</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr"/>
+      <c r="G1050" t="inlineStr"/>
+      <c r="H1050" t="inlineStr"/>
+      <c r="I1050" t="inlineStr"/>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>77235</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:45:50</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr"/>
+      <c r="G1051" t="inlineStr"/>
+      <c r="H1051" t="inlineStr"/>
+      <c r="I1051" t="inlineStr"/>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>77228</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:45:50</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr"/>
+      <c r="G1052" t="inlineStr"/>
+      <c r="H1052" t="inlineStr"/>
+      <c r="I1052" t="inlineStr"/>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>69163</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>5111 Grant McConachie Way</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:45:50</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr"/>
+      <c r="G1053" t="inlineStr"/>
+      <c r="H1053" t="inlineStr"/>
+      <c r="I1053" t="inlineStr"/>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>109205</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.133556536531, 'Longitude': -123.092424273491}</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:45:50</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:13:47.159Z</t>
+        </is>
+      </c>
+      <c r="G1054" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1054" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:25:08.457Z</t>
+        </is>
+      </c>
+      <c r="I1054" t="n">
+        <v>178.9</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>65512</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:45:50</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr"/>
+      <c r="G1055" t="inlineStr"/>
+      <c r="H1055" t="inlineStr"/>
+      <c r="I1055" t="inlineStr"/>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>83384</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:45:50</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr"/>
+      <c r="G1056" t="inlineStr"/>
+      <c r="H1056" t="inlineStr"/>
+      <c r="I1056" t="inlineStr"/>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>77015</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:45:50</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr"/>
+      <c r="G1057" t="inlineStr"/>
+      <c r="H1057" t="inlineStr"/>
+      <c r="I1057" t="inlineStr"/>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>107728</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>8884 Granville St</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:45:50</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr"/>
+      <c r="G1058" t="inlineStr"/>
+      <c r="H1058" t="inlineStr"/>
+      <c r="I1058" t="inlineStr"/>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>65572</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:45:50</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr"/>
+      <c r="G1059" t="inlineStr"/>
+      <c r="H1059" t="inlineStr"/>
+      <c r="I1059" t="inlineStr"/>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>65511</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:45:50</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:54:19.301Z</t>
+        </is>
+      </c>
+      <c r="G1060" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1060" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:54:19.348Z</t>
+        </is>
+      </c>
+      <c r="I1060" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>65556</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>2025-08-20 14:45:50</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr"/>
+      <c r="G1061" t="inlineStr"/>
+      <c r="H1061" t="inlineStr"/>
+      <c r="I1061" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/gas_prices.xlsx
+++ b/data/gas_prices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1061"/>
+  <dimension ref="A1:I1141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41804,10 +41804,8 @@
       <c r="I1041" t="inlineStr"/>
     </row>
     <row r="1042">
-      <c r="A1042" t="inlineStr">
-        <is>
-          <t>65515</t>
-        </is>
+      <c r="A1042" t="n">
+        <v>65515</v>
       </c>
       <c r="B1042" t="inlineStr">
         <is>
@@ -41847,10 +41845,8 @@
       </c>
     </row>
     <row r="1043">
-      <c r="A1043" t="inlineStr">
-        <is>
-          <t>77205</t>
-        </is>
+      <c r="A1043" t="n">
+        <v>77205</v>
       </c>
       <c r="B1043" t="inlineStr">
         <is>
@@ -41878,10 +41874,8 @@
       <c r="I1043" t="inlineStr"/>
     </row>
     <row r="1044">
-      <c r="A1044" t="inlineStr">
-        <is>
-          <t>77223</t>
-        </is>
+      <c r="A1044" t="n">
+        <v>77223</v>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
@@ -41909,10 +41903,8 @@
       <c r="I1044" t="inlineStr"/>
     </row>
     <row r="1045">
-      <c r="A1045" t="inlineStr">
-        <is>
-          <t>65514</t>
-        </is>
+      <c r="A1045" t="n">
+        <v>65514</v>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
@@ -41940,10 +41932,8 @@
       <c r="I1045" t="inlineStr"/>
     </row>
     <row r="1046">
-      <c r="A1046" t="inlineStr">
-        <is>
-          <t>77232</t>
-        </is>
+      <c r="A1046" t="n">
+        <v>77232</v>
       </c>
       <c r="B1046" t="inlineStr">
         <is>
@@ -41971,10 +41961,8 @@
       <c r="I1046" t="inlineStr"/>
     </row>
     <row r="1047">
-      <c r="A1047" t="inlineStr">
-        <is>
-          <t>77202</t>
-        </is>
+      <c r="A1047" t="n">
+        <v>77202</v>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
@@ -42014,10 +42002,8 @@
       </c>
     </row>
     <row r="1048">
-      <c r="A1048" t="inlineStr">
-        <is>
-          <t>86650</t>
-        </is>
+      <c r="A1048" t="n">
+        <v>86650</v>
       </c>
       <c r="B1048" t="inlineStr">
         <is>
@@ -42045,10 +42031,8 @@
       <c r="I1048" t="inlineStr"/>
     </row>
     <row r="1049">
-      <c r="A1049" t="inlineStr">
-        <is>
-          <t>77218</t>
-        </is>
+      <c r="A1049" t="n">
+        <v>77218</v>
       </c>
       <c r="B1049" t="inlineStr">
         <is>
@@ -42076,10 +42060,8 @@
       <c r="I1049" t="inlineStr"/>
     </row>
     <row r="1050">
-      <c r="A1050" t="inlineStr">
-        <is>
-          <t>77243</t>
-        </is>
+      <c r="A1050" t="n">
+        <v>77243</v>
       </c>
       <c r="B1050" t="inlineStr">
         <is>
@@ -42107,10 +42089,8 @@
       <c r="I1050" t="inlineStr"/>
     </row>
     <row r="1051">
-      <c r="A1051" t="inlineStr">
-        <is>
-          <t>77235</t>
-        </is>
+      <c r="A1051" t="n">
+        <v>77235</v>
       </c>
       <c r="B1051" t="inlineStr">
         <is>
@@ -42138,10 +42118,8 @@
       <c r="I1051" t="inlineStr"/>
     </row>
     <row r="1052">
-      <c r="A1052" t="inlineStr">
-        <is>
-          <t>77228</t>
-        </is>
+      <c r="A1052" t="n">
+        <v>77228</v>
       </c>
       <c r="B1052" t="inlineStr">
         <is>
@@ -42169,10 +42147,8 @@
       <c r="I1052" t="inlineStr"/>
     </row>
     <row r="1053">
-      <c r="A1053" t="inlineStr">
-        <is>
-          <t>69163</t>
-        </is>
+      <c r="A1053" t="n">
+        <v>69163</v>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
@@ -42200,10 +42176,8 @@
       <c r="I1053" t="inlineStr"/>
     </row>
     <row r="1054">
-      <c r="A1054" t="inlineStr">
-        <is>
-          <t>109205</t>
-        </is>
+      <c r="A1054" t="n">
+        <v>109205</v>
       </c>
       <c r="B1054" t="inlineStr">
         <is>
@@ -42243,10 +42217,8 @@
       </c>
     </row>
     <row r="1055">
-      <c r="A1055" t="inlineStr">
-        <is>
-          <t>65512</t>
-        </is>
+      <c r="A1055" t="n">
+        <v>65512</v>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
@@ -42274,10 +42246,8 @@
       <c r="I1055" t="inlineStr"/>
     </row>
     <row r="1056">
-      <c r="A1056" t="inlineStr">
-        <is>
-          <t>83384</t>
-        </is>
+      <c r="A1056" t="n">
+        <v>83384</v>
       </c>
       <c r="B1056" t="inlineStr">
         <is>
@@ -42305,10 +42275,8 @@
       <c r="I1056" t="inlineStr"/>
     </row>
     <row r="1057">
-      <c r="A1057" t="inlineStr">
-        <is>
-          <t>77015</t>
-        </is>
+      <c r="A1057" t="n">
+        <v>77015</v>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
@@ -42336,10 +42304,8 @@
       <c r="I1057" t="inlineStr"/>
     </row>
     <row r="1058">
-      <c r="A1058" t="inlineStr">
-        <is>
-          <t>107728</t>
-        </is>
+      <c r="A1058" t="n">
+        <v>107728</v>
       </c>
       <c r="B1058" t="inlineStr">
         <is>
@@ -42367,10 +42333,8 @@
       <c r="I1058" t="inlineStr"/>
     </row>
     <row r="1059">
-      <c r="A1059" t="inlineStr">
-        <is>
-          <t>65572</t>
-        </is>
+      <c r="A1059" t="n">
+        <v>65572</v>
       </c>
       <c r="B1059" t="inlineStr">
         <is>
@@ -42398,10 +42362,8 @@
       <c r="I1059" t="inlineStr"/>
     </row>
     <row r="1060">
-      <c r="A1060" t="inlineStr">
-        <is>
-          <t>65511</t>
-        </is>
+      <c r="A1060" t="n">
+        <v>65511</v>
       </c>
       <c r="B1060" t="inlineStr">
         <is>
@@ -42441,10 +42403,8 @@
       </c>
     </row>
     <row r="1061">
-      <c r="A1061" t="inlineStr">
-        <is>
-          <t>65556</t>
-        </is>
+      <c r="A1061" t="n">
+        <v>65556</v>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
@@ -42471,6 +42431,3282 @@
       <c r="H1061" t="inlineStr"/>
       <c r="I1061" t="inlineStr"/>
     </row>
+    <row r="1062">
+      <c r="A1062" t="n">
+        <v>65542</v>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>3250 MacDonald St</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2573819, 'Longitude': -123.1680407}</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:27:37</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:07:00.516Z</t>
+        </is>
+      </c>
+      <c r="G1062" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1062" t="inlineStr"/>
+      <c r="I1062" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="n">
+        <v>65533</v>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>4615 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2449719, 'Longitude': -123.1540385}</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:27:37</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:29:22.296Z</t>
+        </is>
+      </c>
+      <c r="G1063" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1063" t="inlineStr"/>
+      <c r="I1063" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="n">
+        <v>83068</v>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>3205 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.256927568207, 'Longitude': -123.153288960457}</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:27:37</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr"/>
+      <c r="G1064" t="inlineStr"/>
+      <c r="H1064" t="inlineStr"/>
+      <c r="I1064" t="inlineStr"/>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="n">
+        <v>65562</v>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>2808 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263883932125, 'Longitude': -123.168604373932}</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:27:37</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:17:05.427Z</t>
+        </is>
+      </c>
+      <c r="G1065" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1065" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:17:36.405Z</t>
+        </is>
+      </c>
+      <c r="I1065" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="n">
+        <v>113305</v>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>3596 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234385296079, 'Longitude': -123.184762001038}</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:27:37</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:09:27.609Z</t>
+        </is>
+      </c>
+      <c r="G1066" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1066" t="inlineStr"/>
+      <c r="I1066" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:27:37</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:23:23.785Z</t>
+        </is>
+      </c>
+      <c r="G1067" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1067" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:16:34.188Z</t>
+        </is>
+      </c>
+      <c r="I1067" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="n">
+        <v>65554</v>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>1795 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264037962303, 'Longitude': -123.145408630371}</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:27:37</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:17:45.124Z</t>
+        </is>
+      </c>
+      <c r="G1068" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:31:16.269Z</t>
+        </is>
+      </c>
+      <c r="I1068" t="n">
+        <v>199.3</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="n">
+        <v>65571</v>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>4314 W 10th Ave</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263533861752, 'Longitude': -123.203430175781}</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:27:37</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:35:47.299Z</t>
+        </is>
+      </c>
+      <c r="G1069" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>2025-08-19T16:29:09.259Z</t>
+        </is>
+      </c>
+      <c r="I1069" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:27:37</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:52:47.547Z</t>
+        </is>
+      </c>
+      <c r="G1070" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1070" t="inlineStr"/>
+      <c r="I1070" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="n">
+        <v>32376</v>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>1503 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234634576953, 'Longitude': -123.139971792698}</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:27:37</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:07:57.832Z</t>
+        </is>
+      </c>
+      <c r="G1071" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:30:08.915Z</t>
+        </is>
+      </c>
+      <c r="I1071" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="n">
+        <v>65549</v>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>5702 Granville St</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234036184118, 'Longitude': -123.139244914055}</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:27:37</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:13:44.526Z</t>
+        </is>
+      </c>
+      <c r="G1072" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:38:32.763Z</t>
+        </is>
+      </c>
+      <c r="I1072" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:27:37</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:06:41.472Z</t>
+        </is>
+      </c>
+      <c r="G1073" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:22.999Z</t>
+        </is>
+      </c>
+      <c r="I1073" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:27:37</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:06:28.814Z</t>
+        </is>
+      </c>
+      <c r="G1074" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1074" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:11.555Z</t>
+        </is>
+      </c>
+      <c r="I1074" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="n">
+        <v>72747</v>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>1010 W King Edward Ave</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249188, 'Longitude': -123.127767}</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:27:37</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:14:28.766Z</t>
+        </is>
+      </c>
+      <c r="G1075" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:43:58.867Z</t>
+        </is>
+      </c>
+      <c r="I1075" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="n">
+        <v>32375</v>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>4110 Oak St</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.24894071957, 'Longitude': -123.127040863037}</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:27:37</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:14:23.259Z</t>
+        </is>
+      </c>
+      <c r="G1076" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1076" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:13:19.073Z</t>
+        </is>
+      </c>
+      <c r="I1076" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="n">
+        <v>65564</v>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>5680 Oak St</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234217162181, 'Longitude': -123.127684593201}</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:27:37</t>
+        </is>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:06:51.878Z</t>
+        </is>
+      </c>
+      <c r="G1077" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1077" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:08:24.294Z</t>
+        </is>
+      </c>
+      <c r="I1077" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="n">
+        <v>32372</v>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>6525 Oak St</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226226639452, 'Longitude': -123.128687739372}</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:27:37</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:09:51.222Z</t>
+        </is>
+      </c>
+      <c r="G1078" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1078" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:33:23.261Z</t>
+        </is>
+      </c>
+      <c r="I1078" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:27:37</t>
+        </is>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:14:33.794Z</t>
+        </is>
+      </c>
+      <c r="G1079" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1079" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:44:27.069Z</t>
+        </is>
+      </c>
+      <c r="I1079" t="n">
+        <v>199.9</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="n">
+        <v>65566</v>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>8072 Granville St</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.212495055855, 'Longitude': -123.14013004303}</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:27:37</t>
+        </is>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:39:19.179Z</t>
+        </is>
+      </c>
+      <c r="G1080" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1080" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:30:08.359Z</t>
+        </is>
+      </c>
+      <c r="I1080" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="n">
+        <v>65572</v>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:27:37</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:42:32.062Z</t>
+        </is>
+      </c>
+      <c r="G1081" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:31:11.263Z</t>
+        </is>
+      </c>
+      <c r="I1081" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="n">
+        <v>65558</v>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>1390 E 33rd Ave</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.240045470021, 'Longitude': -123.076765537262}</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:28:59</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:50:52.759Z</t>
+        </is>
+      </c>
+      <c r="G1082" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H1082" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:24:49.291Z</t>
+        </is>
+      </c>
+      <c r="I1082" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="n">
+        <v>83394</v>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>4064 Fraser St</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.248864, 'Longitude': -123.09002}</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:28:59</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:34:57.523Z</t>
+        </is>
+      </c>
+      <c r="G1083" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:15:27.854Z</t>
+        </is>
+      </c>
+      <c r="I1083" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="n">
+        <v>65573</v>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>1396 E 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.232593005895, 'Longitude': -123.07728856802}</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:28:59</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:38:34.693Z</t>
+        </is>
+      </c>
+      <c r="G1084" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:26:51.474Z</t>
+        </is>
+      </c>
+      <c r="I1084" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="n">
+        <v>80714</v>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>Husky</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>4933 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2397388, 'Longitude': -123.065748}</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:28:59</t>
+        </is>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:32:58.239Z</t>
+        </is>
+      </c>
+      <c r="G1085" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:32:58.255Z</t>
+        </is>
+      </c>
+      <c r="I1085" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="n">
+        <v>65552</v>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>2001 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.245312771918, 'Longitude': -123.064910173416}</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:28:59</t>
+        </is>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:54:53.724Z</t>
+        </is>
+      </c>
+      <c r="G1086" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H1086" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:25:23.251Z</t>
+        </is>
+      </c>
+      <c r="I1086" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="n">
+        <v>65538</v>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>5252 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2372145, 'Longitude': -123.0650857}</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:28:59</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:33:00.367Z</t>
+        </is>
+      </c>
+      <c r="G1087" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:33:00.388Z</t>
+        </is>
+      </c>
+      <c r="I1087" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="n">
+        <v>90814</v>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>2277 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.242132845692, 'Longitude': -123.058204650879}</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:28:59</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:04:13.580Z</t>
+        </is>
+      </c>
+      <c r="G1088" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="H1088" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:17:33.155Z</t>
+        </is>
+      </c>
+      <c r="I1088" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="n">
+        <v>39768</v>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>5736 Main St</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2325708, 'Longitude': -123.1010069}</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:28:59</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:20:28.754Z</t>
+        </is>
+      </c>
+      <c r="G1089" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:37:55.027Z</t>
+        </is>
+      </c>
+      <c r="I1089" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="n">
+        <v>9710</v>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>1295 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259878978744, 'Longitude': -123.078074455261}</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:28:59</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:04:44.313Z</t>
+        </is>
+      </c>
+      <c r="G1090" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H1090" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:33:02.098Z</t>
+        </is>
+      </c>
+      <c r="I1090" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="n">
+        <v>99146</v>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>1317 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259758544957, 'Longitude': -123.077272474766}</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:28:59</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:28:02.163Z</t>
+        </is>
+      </c>
+      <c r="G1091" t="n">
+        <v>145.9</v>
+      </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:41:52.253Z</t>
+        </is>
+      </c>
+      <c r="I1091" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="n">
+        <v>65560</v>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>1289 E Broadway</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.262693682723, 'Longitude': -123.078117370605}</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:28:59</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:26:19.226Z</t>
+        </is>
+      </c>
+      <c r="G1092" t="n">
+        <v>145.9</v>
+      </c>
+      <c r="H1092" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:05:17.339Z</t>
+        </is>
+      </c>
+      <c r="I1092" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="n">
+        <v>65557</v>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>2120 Grandview Hwy S</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2591601, 'Longitude': -123.0617495}</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:28:59</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:23:34.671Z</t>
+        </is>
+      </c>
+      <c r="G1093" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H1093" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:23:34.713Z</t>
+        </is>
+      </c>
+      <c r="I1093" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="n">
+        <v>71502</v>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>2748 Main St</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2604441, 'Longitude': -123.1005869}</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:28:59</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:19:08.049Z</t>
+        </is>
+      </c>
+      <c r="G1094" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:18:31.731Z</t>
+        </is>
+      </c>
+      <c r="I1094" t="n">
+        <v>175.9</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="n">
+        <v>65559</v>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>6502 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.224996944057, 'Longitude': -123.065521717072}</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:28:59</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:13:08.596Z</t>
+        </is>
+      </c>
+      <c r="G1095" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:06:56.250Z</t>
+        </is>
+      </c>
+      <c r="I1095" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="n">
+        <v>89943</v>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>6808 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2220242, 'Longitude': -123.0654247}</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:28:59</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:12:54.504Z</t>
+        </is>
+      </c>
+      <c r="G1096" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:59:15.108Z</t>
+        </is>
+      </c>
+      <c r="I1096" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:28:59</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:23:53.804Z</t>
+        </is>
+      </c>
+      <c r="G1097" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1097" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:36:47.048Z</t>
+        </is>
+      </c>
+      <c r="I1097" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="n">
+        <v>65537</v>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>2918 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.23608, 'Longitude': -123.0454858}</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:28:59</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:23:18.569Z</t>
+        </is>
+      </c>
+      <c r="G1098" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1098" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:24:44.587Z</t>
+        </is>
+      </c>
+      <c r="I1098" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:28:59</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:32:45.310Z</t>
+        </is>
+      </c>
+      <c r="G1099" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1099" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:36:59.816Z</t>
+        </is>
+      </c>
+      <c r="I1099" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="n">
+        <v>65535</v>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>2605 E 49th Ave</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2251291, 'Longitude': -123.0545048}</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:28:59</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:14:32.764Z</t>
+        </is>
+      </c>
+      <c r="G1100" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1100" t="inlineStr"/>
+      <c r="I1100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="n">
+        <v>75425</v>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>1785 Main St</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.26940640121, 'Longitude': -123.101197779179}</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:28:59</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:07:59.429Z</t>
+        </is>
+      </c>
+      <c r="G1101" t="n">
+        <v>148.9</v>
+      </c>
+      <c r="H1101" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:26:33.749Z</t>
+        </is>
+      </c>
+      <c r="I1101" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="n">
+        <v>77015</v>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169873456637, 'Longitude': -123.091178619746}</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:30:20</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:04:45.153Z</t>
+        </is>
+      </c>
+      <c r="G1102" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H1102" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:04:45.184Z</t>
+        </is>
+      </c>
+      <c r="I1102" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="n">
+        <v>65511</v>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:30:20</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:40:01.312Z</t>
+        </is>
+      </c>
+      <c r="G1103" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1103" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:54:19.348Z</t>
+        </is>
+      </c>
+      <c r="I1103" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="n">
+        <v>86650</v>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169856952787, 'Longitude': -123.123961687088}</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:30:20</t>
+        </is>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:24:37.304Z</t>
+        </is>
+      </c>
+      <c r="G1104" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="H1104" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:05:27.032Z</t>
+        </is>
+      </c>
+      <c r="I1104" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="n">
+        <v>77218</v>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.173339635958, 'Longitude': -123.124954104424}</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:30:20</t>
+        </is>
+      </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:35:53.275Z</t>
+        </is>
+      </c>
+      <c r="G1105" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1105" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:04:48.775Z</t>
+        </is>
+      </c>
+      <c r="I1105" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="n">
+        <v>77228</v>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1843249, 'Longitude': -123.1236078}</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:30:20</t>
+        </is>
+      </c>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:58:09.591Z</t>
+        </is>
+      </c>
+      <c r="G1106" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1106" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:29:09.481Z</t>
+        </is>
+      </c>
+      <c r="I1106" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="n">
+        <v>83384</v>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192001, 'Longitude': -123.124004}</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:30:20</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:12:26.094Z</t>
+        </is>
+      </c>
+      <c r="G1107" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="H1107" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:12:26.110Z</t>
+        </is>
+      </c>
+      <c r="I1107" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="n">
+        <v>77202</v>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.162989071149, 'Longitude': -123.134229183197}</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:30:20</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:07:41.480Z</t>
+        </is>
+      </c>
+      <c r="G1108" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="H1108" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:02:00.124Z</t>
+        </is>
+      </c>
+      <c r="I1108" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="n">
+        <v>77243</v>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.179182137142, 'Longitude': -123.137152791023}</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:30:20</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:58:00.361Z</t>
+        </is>
+      </c>
+      <c r="G1109" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H1109" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:47:26.975Z</t>
+        </is>
+      </c>
+      <c r="I1109" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="n">
+        <v>83387</v>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>710 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21081995506, 'Longitude': -123.090755939484}</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:30:20</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:33:34.285Z</t>
+        </is>
+      </c>
+      <c r="G1110" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1110" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:17:36.454Z</t>
+        </is>
+      </c>
+      <c r="I1110" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="n">
+        <v>65551</v>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>688 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210798928329, 'Longitude': -123.09152841568}</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:30:20</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:16:37.833Z</t>
+        </is>
+      </c>
+      <c r="G1111" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H1111" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:06:09.964Z</t>
+        </is>
+      </c>
+      <c r="I1111" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="n">
+        <v>77235</v>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.18409178594, 'Longitude': -123.136823830688}</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:30:20</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:57:28.430Z</t>
+        </is>
+      </c>
+      <c r="G1112" t="n">
+        <v>151.9</v>
+      </c>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:57:43.427Z</t>
+        </is>
+      </c>
+      <c r="I1112" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="n">
+        <v>82925</v>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>350 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210245, 'Longitude': -123.099328}</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:30:20</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:01:49.193Z</t>
+        </is>
+      </c>
+      <c r="G1113" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1113" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:35:52.098Z</t>
+        </is>
+      </c>
+      <c r="I1113" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="n">
+        <v>109205</v>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.133556536531, 'Longitude': -123.092424273491}</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:30:20</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:04:51.071Z</t>
+        </is>
+      </c>
+      <c r="G1114" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:04:51.118Z</t>
+        </is>
+      </c>
+      <c r="I1114" t="n">
+        <v>178.9</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="n">
+        <v>65540</v>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>196 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2106867, 'Longitude': -123.1027436}</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:30:20</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:23:21.688Z</t>
+        </is>
+      </c>
+      <c r="G1115" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:26:15.975Z</t>
+        </is>
+      </c>
+      <c r="I1115" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="n">
+        <v>65512</v>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1328393, 'Longitude': -123.0926312}</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:30:20</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:04:56.735Z</t>
+        </is>
+      </c>
+      <c r="G1116" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1116" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:04:56.798Z</t>
+        </is>
+      </c>
+      <c r="I1116" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="n">
+        <v>77205</v>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1558882, 'Longitude': -123.1369625}</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:30:20</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:09:47.540Z</t>
+        </is>
+      </c>
+      <c r="G1117" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1117" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:09:47.598Z</t>
+        </is>
+      </c>
+      <c r="I1117" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:30:20</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:32:45.310Z</t>
+        </is>
+      </c>
+      <c r="G1118" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1118" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:36:59.816Z</t>
+        </is>
+      </c>
+      <c r="I1118" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:30:20</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:23:53.804Z</t>
+        </is>
+      </c>
+      <c r="G1119" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1119" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:36:47.048Z</t>
+        </is>
+      </c>
+      <c r="I1119" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="n">
+        <v>65556</v>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20806537721, 'Longitude': -123.123285770416}</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:30:20</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:24:01.246Z</t>
+        </is>
+      </c>
+      <c r="G1120" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1120" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:39:32.617Z</t>
+        </is>
+      </c>
+      <c r="I1120" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="n">
+        <v>86937</v>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>8655 Boundary Rd</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20476, 'Longitude': -123.02398}</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:30:20</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:05:30.247Z</t>
+        </is>
+      </c>
+      <c r="G1121" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1121" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:14:20.553Z</t>
+        </is>
+      </c>
+      <c r="I1121" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>65515</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>4011 Francis Rd</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.14867500071, 'Longitude': -123.180856704712}</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:31:45</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:49:14.189Z</t>
+        </is>
+      </c>
+      <c r="G1122" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H1122" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:49:17.229Z</t>
+        </is>
+      </c>
+      <c r="I1122" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>77205</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1558882, 'Longitude': -123.1369625}</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:31:45</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:09:47.540Z</t>
+        </is>
+      </c>
+      <c r="G1123" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1123" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:09:47.598Z</t>
+        </is>
+      </c>
+      <c r="I1123" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>77223</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>7991 No 1 Rd</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.155888686563, 'Longitude': -123.181414604187}</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:31:45</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr"/>
+      <c r="G1124" t="inlineStr"/>
+      <c r="H1124" t="inlineStr"/>
+      <c r="I1124" t="inlineStr"/>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>65514</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>7980 Williams Rd</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.140582914547, 'Longitude': -123.137168884277}</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:31:45</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:09:58.131Z</t>
+        </is>
+      </c>
+      <c r="G1125" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="H1125" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:09:58.219Z</t>
+        </is>
+      </c>
+      <c r="I1125" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>77232</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900 Westminster Hwy </t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1698419, 'Longitude': -123.159282}</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:31:45</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:52:26.862Z</t>
+        </is>
+      </c>
+      <c r="G1126" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1126" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:52:26.878Z</t>
+        </is>
+      </c>
+      <c r="I1126" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>77202</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.162989071149, 'Longitude': -123.134229183197}</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:31:45</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:07:41.480Z</t>
+        </is>
+      </c>
+      <c r="G1127" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="H1127" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:02:00.124Z</t>
+        </is>
+      </c>
+      <c r="I1127" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>86650</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169856952787, 'Longitude': -123.123961687088}</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:31:45</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:24:37.304Z</t>
+        </is>
+      </c>
+      <c r="G1128" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="H1128" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:05:27.032Z</t>
+        </is>
+      </c>
+      <c r="I1128" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>77218</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.173339635958, 'Longitude': -123.124954104424}</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:31:45</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:35:53.275Z</t>
+        </is>
+      </c>
+      <c r="G1129" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1129" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:04:48.775Z</t>
+        </is>
+      </c>
+      <c r="I1129" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>77243</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.179182137142, 'Longitude': -123.137152791023}</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:31:45</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:58:00.361Z</t>
+        </is>
+      </c>
+      <c r="G1130" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H1130" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:47:26.975Z</t>
+        </is>
+      </c>
+      <c r="I1130" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>77235</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.18409178594, 'Longitude': -123.136823830688}</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:31:45</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:57:28.430Z</t>
+        </is>
+      </c>
+      <c r="G1131" t="n">
+        <v>151.9</v>
+      </c>
+      <c r="H1131" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:57:43.427Z</t>
+        </is>
+      </c>
+      <c r="I1131" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>77228</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1843249, 'Longitude': -123.1236078}</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:31:45</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:58:09.591Z</t>
+        </is>
+      </c>
+      <c r="G1132" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1132" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:29:09.481Z</t>
+        </is>
+      </c>
+      <c r="I1132" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>69163</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>5111 Grant McConachie Way</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192919, 'Longitude': -123.166797}</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:31:45</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:11:39.268Z</t>
+        </is>
+      </c>
+      <c r="G1133" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1133" t="inlineStr">
+        <is>
+          <t>2025-08-20T10:13:47.773Z</t>
+        </is>
+      </c>
+      <c r="I1133" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>109205</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.133556536531, 'Longitude': -123.092424273491}</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:31:45</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:04:51.071Z</t>
+        </is>
+      </c>
+      <c r="G1134" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H1134" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:04:51.118Z</t>
+        </is>
+      </c>
+      <c r="I1134" t="n">
+        <v>178.9</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>65512</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1328393, 'Longitude': -123.0926312}</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:31:45</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:04:56.735Z</t>
+        </is>
+      </c>
+      <c r="G1135" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1135" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:04:56.798Z</t>
+        </is>
+      </c>
+      <c r="I1135" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>83384</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192001, 'Longitude': -123.124004}</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:31:45</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:12:26.094Z</t>
+        </is>
+      </c>
+      <c r="G1136" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="H1136" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:12:26.110Z</t>
+        </is>
+      </c>
+      <c r="I1136" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>77015</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169873456637, 'Longitude': -123.091178619746}</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:31:45</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:31:01.890Z</t>
+        </is>
+      </c>
+      <c r="G1137" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H1137" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:31:02.184Z</t>
+        </is>
+      </c>
+      <c r="I1137" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>107728</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>8884 Granville St</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2054215, 'Longitude': -123.1401677}</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:31:45</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:42:06.591Z</t>
+        </is>
+      </c>
+      <c r="G1138" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1138" t="inlineStr">
+        <is>
+          <t>2025-08-19T21:28:32.275Z</t>
+        </is>
+      </c>
+      <c r="I1138" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>65572</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:31:45</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:42:32.062Z</t>
+        </is>
+      </c>
+      <c r="G1139" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1139" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:31:11.263Z</t>
+        </is>
+      </c>
+      <c r="I1139" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>65511</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:31:45</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:40:01.312Z</t>
+        </is>
+      </c>
+      <c r="G1140" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1140" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:54:19.348Z</t>
+        </is>
+      </c>
+      <c r="I1140" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>65556</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20806537721, 'Longitude': -123.123285770416}</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:31:45</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:24:01.246Z</t>
+        </is>
+      </c>
+      <c r="G1141" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1141" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:39:32.617Z</t>
+        </is>
+      </c>
+      <c r="I1141" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gas_prices.xlsx
+++ b/data/gas_prices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1141"/>
+  <dimension ref="A1:I1221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44860,10 +44860,8 @@
       </c>
     </row>
     <row r="1122">
-      <c r="A1122" t="inlineStr">
-        <is>
-          <t>65515</t>
-        </is>
+      <c r="A1122" t="n">
+        <v>65515</v>
       </c>
       <c r="B1122" t="inlineStr">
         <is>
@@ -44903,10 +44901,8 @@
       </c>
     </row>
     <row r="1123">
-      <c r="A1123" t="inlineStr">
-        <is>
-          <t>77205</t>
-        </is>
+      <c r="A1123" t="n">
+        <v>77205</v>
       </c>
       <c r="B1123" t="inlineStr">
         <is>
@@ -44946,10 +44942,8 @@
       </c>
     </row>
     <row r="1124">
-      <c r="A1124" t="inlineStr">
-        <is>
-          <t>77223</t>
-        </is>
+      <c r="A1124" t="n">
+        <v>77223</v>
       </c>
       <c r="B1124" t="inlineStr">
         <is>
@@ -44977,10 +44971,8 @@
       <c r="I1124" t="inlineStr"/>
     </row>
     <row r="1125">
-      <c r="A1125" t="inlineStr">
-        <is>
-          <t>65514</t>
-        </is>
+      <c r="A1125" t="n">
+        <v>65514</v>
       </c>
       <c r="B1125" t="inlineStr">
         <is>
@@ -45020,10 +45012,8 @@
       </c>
     </row>
     <row r="1126">
-      <c r="A1126" t="inlineStr">
-        <is>
-          <t>77232</t>
-        </is>
+      <c r="A1126" t="n">
+        <v>77232</v>
       </c>
       <c r="B1126" t="inlineStr">
         <is>
@@ -45063,10 +45053,8 @@
       </c>
     </row>
     <row r="1127">
-      <c r="A1127" t="inlineStr">
-        <is>
-          <t>77202</t>
-        </is>
+      <c r="A1127" t="n">
+        <v>77202</v>
       </c>
       <c r="B1127" t="inlineStr">
         <is>
@@ -45106,10 +45094,8 @@
       </c>
     </row>
     <row r="1128">
-      <c r="A1128" t="inlineStr">
-        <is>
-          <t>86650</t>
-        </is>
+      <c r="A1128" t="n">
+        <v>86650</v>
       </c>
       <c r="B1128" t="inlineStr">
         <is>
@@ -45149,10 +45135,8 @@
       </c>
     </row>
     <row r="1129">
-      <c r="A1129" t="inlineStr">
-        <is>
-          <t>77218</t>
-        </is>
+      <c r="A1129" t="n">
+        <v>77218</v>
       </c>
       <c r="B1129" t="inlineStr">
         <is>
@@ -45192,10 +45176,8 @@
       </c>
     </row>
     <row r="1130">
-      <c r="A1130" t="inlineStr">
-        <is>
-          <t>77243</t>
-        </is>
+      <c r="A1130" t="n">
+        <v>77243</v>
       </c>
       <c r="B1130" t="inlineStr">
         <is>
@@ -45235,10 +45217,8 @@
       </c>
     </row>
     <row r="1131">
-      <c r="A1131" t="inlineStr">
-        <is>
-          <t>77235</t>
-        </is>
+      <c r="A1131" t="n">
+        <v>77235</v>
       </c>
       <c r="B1131" t="inlineStr">
         <is>
@@ -45278,10 +45258,8 @@
       </c>
     </row>
     <row r="1132">
-      <c r="A1132" t="inlineStr">
-        <is>
-          <t>77228</t>
-        </is>
+      <c r="A1132" t="n">
+        <v>77228</v>
       </c>
       <c r="B1132" t="inlineStr">
         <is>
@@ -45321,10 +45299,8 @@
       </c>
     </row>
     <row r="1133">
-      <c r="A1133" t="inlineStr">
-        <is>
-          <t>69163</t>
-        </is>
+      <c r="A1133" t="n">
+        <v>69163</v>
       </c>
       <c r="B1133" t="inlineStr">
         <is>
@@ -45364,10 +45340,8 @@
       </c>
     </row>
     <row r="1134">
-      <c r="A1134" t="inlineStr">
-        <is>
-          <t>109205</t>
-        </is>
+      <c r="A1134" t="n">
+        <v>109205</v>
       </c>
       <c r="B1134" t="inlineStr">
         <is>
@@ -45407,10 +45381,8 @@
       </c>
     </row>
     <row r="1135">
-      <c r="A1135" t="inlineStr">
-        <is>
-          <t>65512</t>
-        </is>
+      <c r="A1135" t="n">
+        <v>65512</v>
       </c>
       <c r="B1135" t="inlineStr">
         <is>
@@ -45450,10 +45422,8 @@
       </c>
     </row>
     <row r="1136">
-      <c r="A1136" t="inlineStr">
-        <is>
-          <t>83384</t>
-        </is>
+      <c r="A1136" t="n">
+        <v>83384</v>
       </c>
       <c r="B1136" t="inlineStr">
         <is>
@@ -45493,10 +45463,8 @@
       </c>
     </row>
     <row r="1137">
-      <c r="A1137" t="inlineStr">
-        <is>
-          <t>77015</t>
-        </is>
+      <c r="A1137" t="n">
+        <v>77015</v>
       </c>
       <c r="B1137" t="inlineStr">
         <is>
@@ -45536,10 +45504,8 @@
       </c>
     </row>
     <row r="1138">
-      <c r="A1138" t="inlineStr">
-        <is>
-          <t>107728</t>
-        </is>
+      <c r="A1138" t="n">
+        <v>107728</v>
       </c>
       <c r="B1138" t="inlineStr">
         <is>
@@ -45579,10 +45545,8 @@
       </c>
     </row>
     <row r="1139">
-      <c r="A1139" t="inlineStr">
-        <is>
-          <t>65572</t>
-        </is>
+      <c r="A1139" t="n">
+        <v>65572</v>
       </c>
       <c r="B1139" t="inlineStr">
         <is>
@@ -45622,10 +45586,8 @@
       </c>
     </row>
     <row r="1140">
-      <c r="A1140" t="inlineStr">
-        <is>
-          <t>65511</t>
-        </is>
+      <c r="A1140" t="n">
+        <v>65511</v>
       </c>
       <c r="B1140" t="inlineStr">
         <is>
@@ -45665,10 +45627,8 @@
       </c>
     </row>
     <row r="1141">
-      <c r="A1141" t="inlineStr">
-        <is>
-          <t>65556</t>
-        </is>
+      <c r="A1141" t="n">
+        <v>65556</v>
       </c>
       <c r="B1141" t="inlineStr">
         <is>
@@ -45705,6 +45665,3282 @@
       </c>
       <c r="I1141" t="n">
         <v>182.9</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="n">
+        <v>65542</v>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>3250 MacDonald St</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2573819, 'Longitude': -123.1680407}</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:47:20</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:07:00.516Z</t>
+        </is>
+      </c>
+      <c r="G1142" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1142" t="inlineStr"/>
+      <c r="I1142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="n">
+        <v>65533</v>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>4615 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2449719, 'Longitude': -123.1540385}</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:47:20</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:29:22.296Z</t>
+        </is>
+      </c>
+      <c r="G1143" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1143" t="inlineStr"/>
+      <c r="I1143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="n">
+        <v>83068</v>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>3205 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.256927568207, 'Longitude': -123.153288960457}</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:47:20</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr"/>
+      <c r="G1144" t="inlineStr"/>
+      <c r="H1144" t="inlineStr"/>
+      <c r="I1144" t="inlineStr"/>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="n">
+        <v>65562</v>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>2808 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263883932125, 'Longitude': -123.168604373932}</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:47:20</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:17:05.427Z</t>
+        </is>
+      </c>
+      <c r="G1145" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1145" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:17:36.405Z</t>
+        </is>
+      </c>
+      <c r="I1145" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="n">
+        <v>113305</v>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>3596 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234385296079, 'Longitude': -123.184762001038}</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:47:20</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:09:27.609Z</t>
+        </is>
+      </c>
+      <c r="G1146" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1146" t="inlineStr"/>
+      <c r="I1146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:47:20</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:23:23.785Z</t>
+        </is>
+      </c>
+      <c r="G1147" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1147" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:16:34.188Z</t>
+        </is>
+      </c>
+      <c r="I1147" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="n">
+        <v>65554</v>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>1795 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264037962303, 'Longitude': -123.145408630371}</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:47:20</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:37:14.595Z</t>
+        </is>
+      </c>
+      <c r="G1148" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1148" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:31:16.269Z</t>
+        </is>
+      </c>
+      <c r="I1148" t="n">
+        <v>199.3</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="n">
+        <v>65571</v>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>4314 W 10th Ave</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263533861752, 'Longitude': -123.203430175781}</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:47:20</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:35:47.299Z</t>
+        </is>
+      </c>
+      <c r="G1149" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1149" t="inlineStr">
+        <is>
+          <t>2025-08-19T16:29:09.259Z</t>
+        </is>
+      </c>
+      <c r="I1149" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:47:20</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:52:47.547Z</t>
+        </is>
+      </c>
+      <c r="G1150" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1150" t="inlineStr"/>
+      <c r="I1150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="n">
+        <v>32376</v>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>1503 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234634576953, 'Longitude': -123.139971792698}</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:47:20</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:34:22.591Z</t>
+        </is>
+      </c>
+      <c r="G1151" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1151" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:30:08.915Z</t>
+        </is>
+      </c>
+      <c r="I1151" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="n">
+        <v>65549</v>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>5702 Granville St</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234036184118, 'Longitude': -123.139244914055}</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:47:20</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:34:33.317Z</t>
+        </is>
+      </c>
+      <c r="G1152" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1152" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:38:32.763Z</t>
+        </is>
+      </c>
+      <c r="I1152" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:47:20</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:37:55.561Z</t>
+        </is>
+      </c>
+      <c r="G1153" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1153" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:22.999Z</t>
+        </is>
+      </c>
+      <c r="I1153" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:47:20</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:38:34.695Z</t>
+        </is>
+      </c>
+      <c r="G1154" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1154" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:11.555Z</t>
+        </is>
+      </c>
+      <c r="I1154" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="n">
+        <v>72747</v>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>1010 W King Edward Ave</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249188, 'Longitude': -123.127767}</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:47:20</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:14:28.766Z</t>
+        </is>
+      </c>
+      <c r="G1155" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1155" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:43:58.867Z</t>
+        </is>
+      </c>
+      <c r="I1155" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="n">
+        <v>32375</v>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>4110 Oak St</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.24894071957, 'Longitude': -123.127040863037}</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:47:20</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:14:23.259Z</t>
+        </is>
+      </c>
+      <c r="G1156" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1156" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:13:19.073Z</t>
+        </is>
+      </c>
+      <c r="I1156" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="n">
+        <v>65564</v>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>5680 Oak St</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234217162181, 'Longitude': -123.127684593201}</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:47:20</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:06:51.878Z</t>
+        </is>
+      </c>
+      <c r="G1157" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1157" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:08:24.294Z</t>
+        </is>
+      </c>
+      <c r="I1157" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="n">
+        <v>32372</v>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>6525 Oak St</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226226639452, 'Longitude': -123.128687739372}</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:47:20</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:09:51.222Z</t>
+        </is>
+      </c>
+      <c r="G1158" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1158" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:33:23.261Z</t>
+        </is>
+      </c>
+      <c r="I1158" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:47:20</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:14:33.794Z</t>
+        </is>
+      </c>
+      <c r="G1159" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1159" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:44:27.069Z</t>
+        </is>
+      </c>
+      <c r="I1159" t="n">
+        <v>199.9</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="n">
+        <v>65566</v>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>8072 Granville St</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.212495055855, 'Longitude': -123.14013004303}</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:47:20</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:39:19.179Z</t>
+        </is>
+      </c>
+      <c r="G1160" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1160" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:30:08.359Z</t>
+        </is>
+      </c>
+      <c r="I1160" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="n">
+        <v>65572</v>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:47:20</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:42:32.062Z</t>
+        </is>
+      </c>
+      <c r="G1161" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1161" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:31:11.263Z</t>
+        </is>
+      </c>
+      <c r="I1161" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="n">
+        <v>65558</v>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>1390 E 33rd Ave</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.240045470021, 'Longitude': -123.076765537262}</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:48:43</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:50:52.759Z</t>
+        </is>
+      </c>
+      <c r="G1162" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H1162" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:24:49.291Z</t>
+        </is>
+      </c>
+      <c r="I1162" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="n">
+        <v>83394</v>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>4064 Fraser St</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.248864, 'Longitude': -123.09002}</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:48:43</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:34:57.523Z</t>
+        </is>
+      </c>
+      <c r="G1163" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1163" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:15:27.854Z</t>
+        </is>
+      </c>
+      <c r="I1163" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="n">
+        <v>65573</v>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>1396 E 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.232593005895, 'Longitude': -123.07728856802}</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:48:43</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:45:42.490Z</t>
+        </is>
+      </c>
+      <c r="G1164" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H1164" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:28:44.531Z</t>
+        </is>
+      </c>
+      <c r="I1164" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="n">
+        <v>80714</v>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>Husky</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>4933 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2397388, 'Longitude': -123.065748}</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:48:43</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:32:58.239Z</t>
+        </is>
+      </c>
+      <c r="G1165" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1165" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:32:58.255Z</t>
+        </is>
+      </c>
+      <c r="I1165" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="n">
+        <v>65552</v>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>2001 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.245312771918, 'Longitude': -123.064910173416}</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:48:43</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:54:53.724Z</t>
+        </is>
+      </c>
+      <c r="G1166" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H1166" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:25:23.251Z</t>
+        </is>
+      </c>
+      <c r="I1166" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="n">
+        <v>65538</v>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>5252 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2372145, 'Longitude': -123.0650857}</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:48:43</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:33:00.367Z</t>
+        </is>
+      </c>
+      <c r="G1167" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1167" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:33:00.388Z</t>
+        </is>
+      </c>
+      <c r="I1167" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="n">
+        <v>90814</v>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>2277 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.242132845692, 'Longitude': -123.058204650879}</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:48:43</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:04:13.580Z</t>
+        </is>
+      </c>
+      <c r="G1168" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="H1168" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:17:33.155Z</t>
+        </is>
+      </c>
+      <c r="I1168" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="n">
+        <v>39768</v>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>5736 Main St</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2325708, 'Longitude': -123.1010069}</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:48:43</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:20:28.754Z</t>
+        </is>
+      </c>
+      <c r="G1169" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1169" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:37:55.027Z</t>
+        </is>
+      </c>
+      <c r="I1169" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="n">
+        <v>99146</v>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>1317 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259758544957, 'Longitude': -123.077272474766}</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:48:43</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:28:02.163Z</t>
+        </is>
+      </c>
+      <c r="G1170" t="n">
+        <v>145.9</v>
+      </c>
+      <c r="H1170" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:41:52.253Z</t>
+        </is>
+      </c>
+      <c r="I1170" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="n">
+        <v>9710</v>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>1295 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259878978744, 'Longitude': -123.078074455261}</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:48:43</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:47:45.002Z</t>
+        </is>
+      </c>
+      <c r="G1171" t="n">
+        <v>147.9</v>
+      </c>
+      <c r="H1171" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:33:02.098Z</t>
+        </is>
+      </c>
+      <c r="I1171" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="n">
+        <v>65560</v>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>1289 E Broadway</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.262693682723, 'Longitude': -123.078117370605}</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:48:43</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:41:07.274Z</t>
+        </is>
+      </c>
+      <c r="G1172" t="n">
+        <v>145.9</v>
+      </c>
+      <c r="H1172" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:05:17.339Z</t>
+        </is>
+      </c>
+      <c r="I1172" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="n">
+        <v>65557</v>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>2120 Grandview Hwy S</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2591601, 'Longitude': -123.0617495}</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:48:43</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:23:34.671Z</t>
+        </is>
+      </c>
+      <c r="G1173" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H1173" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:23:34.713Z</t>
+        </is>
+      </c>
+      <c r="I1173" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="n">
+        <v>65559</v>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>6502 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.224996944057, 'Longitude': -123.065521717072}</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:48:43</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:13:08.596Z</t>
+        </is>
+      </c>
+      <c r="G1174" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1174" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:06:56.250Z</t>
+        </is>
+      </c>
+      <c r="I1174" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="n">
+        <v>71502</v>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>2748 Main St</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2604441, 'Longitude': -123.1005869}</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:48:43</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:32:49.133Z</t>
+        </is>
+      </c>
+      <c r="G1175" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H1175" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:32:49.163Z</t>
+        </is>
+      </c>
+      <c r="I1175" t="n">
+        <v>175.9</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="n">
+        <v>89943</v>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>6808 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2220242, 'Longitude': -123.0654247}</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:48:43</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:12:54.504Z</t>
+        </is>
+      </c>
+      <c r="G1176" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1176" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:59:15.108Z</t>
+        </is>
+      </c>
+      <c r="I1176" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:48:43</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:23:53.804Z</t>
+        </is>
+      </c>
+      <c r="G1177" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1177" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:36:47.048Z</t>
+        </is>
+      </c>
+      <c r="I1177" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="n">
+        <v>65537</v>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>2918 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.23608, 'Longitude': -123.0454858}</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:48:43</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:23:18.569Z</t>
+        </is>
+      </c>
+      <c r="G1178" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1178" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:24:44.587Z</t>
+        </is>
+      </c>
+      <c r="I1178" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:48:43</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:32:45.310Z</t>
+        </is>
+      </c>
+      <c r="G1179" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1179" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:36:59.816Z</t>
+        </is>
+      </c>
+      <c r="I1179" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="n">
+        <v>65535</v>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>2605 E 49th Ave</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2251291, 'Longitude': -123.0545048}</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:48:43</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:14:32.764Z</t>
+        </is>
+      </c>
+      <c r="G1180" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1180" t="inlineStr"/>
+      <c r="I1180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="n">
+        <v>75425</v>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>1785 Main St</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.26940640121, 'Longitude': -123.101197779179}</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:48:43</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:36:50.011Z</t>
+        </is>
+      </c>
+      <c r="G1181" t="n">
+        <v>148.9</v>
+      </c>
+      <c r="H1181" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:26:33.749Z</t>
+        </is>
+      </c>
+      <c r="I1181" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="n">
+        <v>77015</v>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169873456637, 'Longitude': -123.091178619746}</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:50:05</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:48:09.493Z</t>
+        </is>
+      </c>
+      <c r="G1182" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H1182" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:31:02.184Z</t>
+        </is>
+      </c>
+      <c r="I1182" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="n">
+        <v>65511</v>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:50:05</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:40:01.312Z</t>
+        </is>
+      </c>
+      <c r="G1183" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1183" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:54:19.348Z</t>
+        </is>
+      </c>
+      <c r="I1183" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="n">
+        <v>86650</v>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169856952787, 'Longitude': -123.123961687088}</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:50:05</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:24:37.304Z</t>
+        </is>
+      </c>
+      <c r="G1184" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="H1184" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:05:27.032Z</t>
+        </is>
+      </c>
+      <c r="I1184" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="n">
+        <v>77218</v>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.173339635958, 'Longitude': -123.124954104424}</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:50:05</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:35:53.275Z</t>
+        </is>
+      </c>
+      <c r="G1185" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1185" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:04:48.775Z</t>
+        </is>
+      </c>
+      <c r="I1185" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="n">
+        <v>77228</v>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1843249, 'Longitude': -123.1236078}</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:50:05</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:58:09.591Z</t>
+        </is>
+      </c>
+      <c r="G1186" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1186" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:29:09.481Z</t>
+        </is>
+      </c>
+      <c r="I1186" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="n">
+        <v>83384</v>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192001, 'Longitude': -123.124004}</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:50:05</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:12:26.094Z</t>
+        </is>
+      </c>
+      <c r="G1187" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="H1187" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:12:26.110Z</t>
+        </is>
+      </c>
+      <c r="I1187" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="n">
+        <v>77202</v>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.162989071149, 'Longitude': -123.134229183197}</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:50:05</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:07:41.480Z</t>
+        </is>
+      </c>
+      <c r="G1188" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="H1188" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:02:00.124Z</t>
+        </is>
+      </c>
+      <c r="I1188" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="n">
+        <v>77243</v>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.179182137142, 'Longitude': -123.137152791023}</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:50:05</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:58:00.361Z</t>
+        </is>
+      </c>
+      <c r="G1189" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H1189" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:47:26.975Z</t>
+        </is>
+      </c>
+      <c r="I1189" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="n">
+        <v>83387</v>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>710 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21081995506, 'Longitude': -123.090755939484}</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:50:05</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:33:34.285Z</t>
+        </is>
+      </c>
+      <c r="G1190" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1190" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:17:36.454Z</t>
+        </is>
+      </c>
+      <c r="I1190" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="n">
+        <v>65551</v>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>688 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210798928329, 'Longitude': -123.09152841568}</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:50:05</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:34:14.829Z</t>
+        </is>
+      </c>
+      <c r="G1191" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H1191" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:06:09.964Z</t>
+        </is>
+      </c>
+      <c r="I1191" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="n">
+        <v>77235</v>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.18409178594, 'Longitude': -123.136823830688}</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:50:05</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:57:28.430Z</t>
+        </is>
+      </c>
+      <c r="G1192" t="n">
+        <v>151.9</v>
+      </c>
+      <c r="H1192" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:57:43.427Z</t>
+        </is>
+      </c>
+      <c r="I1192" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="n">
+        <v>82925</v>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>350 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210245, 'Longitude': -123.099328}</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:50:05</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:01:49.193Z</t>
+        </is>
+      </c>
+      <c r="G1193" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1193" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:35:52.098Z</t>
+        </is>
+      </c>
+      <c r="I1193" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="n">
+        <v>109205</v>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.133556536531, 'Longitude': -123.092424273491}</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:50:05</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:04:51.071Z</t>
+        </is>
+      </c>
+      <c r="G1194" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H1194" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:04:51.118Z</t>
+        </is>
+      </c>
+      <c r="I1194" t="n">
+        <v>178.9</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="n">
+        <v>65540</v>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>196 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2106867, 'Longitude': -123.1027436}</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:50:05</t>
+        </is>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:23:21.688Z</t>
+        </is>
+      </c>
+      <c r="G1195" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1195" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:26:15.975Z</t>
+        </is>
+      </c>
+      <c r="I1195" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="n">
+        <v>65512</v>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1328393, 'Longitude': -123.0926312}</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:50:05</t>
+        </is>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:04:56.735Z</t>
+        </is>
+      </c>
+      <c r="G1196" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1196" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:04:56.798Z</t>
+        </is>
+      </c>
+      <c r="I1196" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="n">
+        <v>77205</v>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1558882, 'Longitude': -123.1369625}</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:50:05</t>
+        </is>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:09:47.540Z</t>
+        </is>
+      </c>
+      <c r="G1197" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1197" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:09:47.598Z</t>
+        </is>
+      </c>
+      <c r="I1197" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:50:05</t>
+        </is>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:32:45.310Z</t>
+        </is>
+      </c>
+      <c r="G1198" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1198" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:36:59.816Z</t>
+        </is>
+      </c>
+      <c r="I1198" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:50:05</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:23:53.804Z</t>
+        </is>
+      </c>
+      <c r="G1199" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1199" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:36:47.048Z</t>
+        </is>
+      </c>
+      <c r="I1199" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="n">
+        <v>65556</v>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20806537721, 'Longitude': -123.123285770416}</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:50:05</t>
+        </is>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:36:34.048Z</t>
+        </is>
+      </c>
+      <c r="G1200" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1200" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:36:34.079Z</t>
+        </is>
+      </c>
+      <c r="I1200" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="n">
+        <v>86937</v>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>8655 Boundary Rd</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20476, 'Longitude': -123.02398}</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:50:05</t>
+        </is>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:05:30.247Z</t>
+        </is>
+      </c>
+      <c r="G1201" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1201" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:14:20.553Z</t>
+        </is>
+      </c>
+      <c r="I1201" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>65515</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>4011 Francis Rd</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.14867500071, 'Longitude': -123.180856704712}</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:51:21</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:43:10.927Z</t>
+        </is>
+      </c>
+      <c r="G1202" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="H1202" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:49:17.229Z</t>
+        </is>
+      </c>
+      <c r="I1202" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>77205</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1558882, 'Longitude': -123.1369625}</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:51:21</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:09:47.540Z</t>
+        </is>
+      </c>
+      <c r="G1203" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1203" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:09:47.598Z</t>
+        </is>
+      </c>
+      <c r="I1203" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>77223</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>7991 No 1 Rd</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.155888686563, 'Longitude': -123.181414604187}</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:51:21</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr"/>
+      <c r="G1204" t="inlineStr"/>
+      <c r="H1204" t="inlineStr"/>
+      <c r="I1204" t="inlineStr"/>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>65514</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>7980 Williams Rd</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.140582914547, 'Longitude': -123.137168884277}</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:51:21</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:32:46.218Z</t>
+        </is>
+      </c>
+      <c r="G1205" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="H1205" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:32:46.234Z</t>
+        </is>
+      </c>
+      <c r="I1205" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>77232</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900 Westminster Hwy </t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1698419, 'Longitude': -123.159282}</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:51:21</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:46:47.733Z</t>
+        </is>
+      </c>
+      <c r="G1206" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1206" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:52:26.878Z</t>
+        </is>
+      </c>
+      <c r="I1206" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>77202</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.162989071149, 'Longitude': -123.134229183197}</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:51:21</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:49:16.933Z</t>
+        </is>
+      </c>
+      <c r="G1207" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H1207" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:02:00.124Z</t>
+        </is>
+      </c>
+      <c r="I1207" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>86650</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169856952787, 'Longitude': -123.123961687088}</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:51:21</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:24:37.304Z</t>
+        </is>
+      </c>
+      <c r="G1208" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="H1208" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:05:27.032Z</t>
+        </is>
+      </c>
+      <c r="I1208" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>77218</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.173339635958, 'Longitude': -123.124954104424}</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:51:21</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:35:53.275Z</t>
+        </is>
+      </c>
+      <c r="G1209" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1209" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:04:48.775Z</t>
+        </is>
+      </c>
+      <c r="I1209" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>77243</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.179182137142, 'Longitude': -123.137152791023}</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:51:21</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:58:00.361Z</t>
+        </is>
+      </c>
+      <c r="G1210" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H1210" t="inlineStr">
+        <is>
+          <t>2025-08-20T19:47:26.975Z</t>
+        </is>
+      </c>
+      <c r="I1210" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>77235</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.18409178594, 'Longitude': -123.136823830688}</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:51:21</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:57:28.430Z</t>
+        </is>
+      </c>
+      <c r="G1211" t="n">
+        <v>151.9</v>
+      </c>
+      <c r="H1211" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:57:43.427Z</t>
+        </is>
+      </c>
+      <c r="I1211" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>77228</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1843249, 'Longitude': -123.1236078}</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:51:21</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:58:09.591Z</t>
+        </is>
+      </c>
+      <c r="G1212" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1212" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:29:09.481Z</t>
+        </is>
+      </c>
+      <c r="I1212" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>69163</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>5111 Grant McConachie Way</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192919, 'Longitude': -123.166797}</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:51:21</t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:11:39.268Z</t>
+        </is>
+      </c>
+      <c r="G1213" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1213" t="inlineStr">
+        <is>
+          <t>2025-08-20T10:13:47.773Z</t>
+        </is>
+      </c>
+      <c r="I1213" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>109205</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.133556536531, 'Longitude': -123.092424273491}</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:51:21</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:04:51.071Z</t>
+        </is>
+      </c>
+      <c r="G1214" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H1214" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:04:51.118Z</t>
+        </is>
+      </c>
+      <c r="I1214" t="n">
+        <v>178.9</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>65512</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1328393, 'Longitude': -123.0926312}</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:51:21</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:04:56.735Z</t>
+        </is>
+      </c>
+      <c r="G1215" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1215" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:04:56.798Z</t>
+        </is>
+      </c>
+      <c r="I1215" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>83384</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192001, 'Longitude': -123.124004}</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:51:21</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:12:26.094Z</t>
+        </is>
+      </c>
+      <c r="G1216" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="H1216" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:12:26.110Z</t>
+        </is>
+      </c>
+      <c r="I1216" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>77015</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169873456637, 'Longitude': -123.091178619746}</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:51:21</t>
+        </is>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:48:09.493Z</t>
+        </is>
+      </c>
+      <c r="G1217" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H1217" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:31:02.184Z</t>
+        </is>
+      </c>
+      <c r="I1217" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>107728</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>8884 Granville St</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2054215, 'Longitude': -123.1401677}</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:51:21</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:42:06.591Z</t>
+        </is>
+      </c>
+      <c r="G1218" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1218" t="inlineStr">
+        <is>
+          <t>2025-08-19T21:28:32.275Z</t>
+        </is>
+      </c>
+      <c r="I1218" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>65572</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:51:21</t>
+        </is>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:42:32.062Z</t>
+        </is>
+      </c>
+      <c r="G1219" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1219" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:31:11.263Z</t>
+        </is>
+      </c>
+      <c r="I1219" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>65511</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:51:21</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:40:01.312Z</t>
+        </is>
+      </c>
+      <c r="G1220" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1220" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:54:19.348Z</t>
+        </is>
+      </c>
+      <c r="I1220" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>65556</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20806537721, 'Longitude': -123.123285770416}</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>2025-08-20 20:51:21</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:36:34.048Z</t>
+        </is>
+      </c>
+      <c r="G1221" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1221" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:36:34.079Z</t>
+        </is>
+      </c>
+      <c r="I1221" t="n">
+        <v>179.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/gas_prices.xlsx
+++ b/data/gas_prices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1221"/>
+  <dimension ref="A1:I1241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48096,10 +48096,8 @@
       </c>
     </row>
     <row r="1202">
-      <c r="A1202" t="inlineStr">
-        <is>
-          <t>65515</t>
-        </is>
+      <c r="A1202" t="n">
+        <v>65515</v>
       </c>
       <c r="B1202" t="inlineStr">
         <is>
@@ -48139,10 +48137,8 @@
       </c>
     </row>
     <row r="1203">
-      <c r="A1203" t="inlineStr">
-        <is>
-          <t>77205</t>
-        </is>
+      <c r="A1203" t="n">
+        <v>77205</v>
       </c>
       <c r="B1203" t="inlineStr">
         <is>
@@ -48182,10 +48178,8 @@
       </c>
     </row>
     <row r="1204">
-      <c r="A1204" t="inlineStr">
-        <is>
-          <t>77223</t>
-        </is>
+      <c r="A1204" t="n">
+        <v>77223</v>
       </c>
       <c r="B1204" t="inlineStr">
         <is>
@@ -48213,10 +48207,8 @@
       <c r="I1204" t="inlineStr"/>
     </row>
     <row r="1205">
-      <c r="A1205" t="inlineStr">
-        <is>
-          <t>65514</t>
-        </is>
+      <c r="A1205" t="n">
+        <v>65514</v>
       </c>
       <c r="B1205" t="inlineStr">
         <is>
@@ -48256,10 +48248,8 @@
       </c>
     </row>
     <row r="1206">
-      <c r="A1206" t="inlineStr">
-        <is>
-          <t>77232</t>
-        </is>
+      <c r="A1206" t="n">
+        <v>77232</v>
       </c>
       <c r="B1206" t="inlineStr">
         <is>
@@ -48299,10 +48289,8 @@
       </c>
     </row>
     <row r="1207">
-      <c r="A1207" t="inlineStr">
-        <is>
-          <t>77202</t>
-        </is>
+      <c r="A1207" t="n">
+        <v>77202</v>
       </c>
       <c r="B1207" t="inlineStr">
         <is>
@@ -48342,10 +48330,8 @@
       </c>
     </row>
     <row r="1208">
-      <c r="A1208" t="inlineStr">
-        <is>
-          <t>86650</t>
-        </is>
+      <c r="A1208" t="n">
+        <v>86650</v>
       </c>
       <c r="B1208" t="inlineStr">
         <is>
@@ -48385,10 +48371,8 @@
       </c>
     </row>
     <row r="1209">
-      <c r="A1209" t="inlineStr">
-        <is>
-          <t>77218</t>
-        </is>
+      <c r="A1209" t="n">
+        <v>77218</v>
       </c>
       <c r="B1209" t="inlineStr">
         <is>
@@ -48428,10 +48412,8 @@
       </c>
     </row>
     <row r="1210">
-      <c r="A1210" t="inlineStr">
-        <is>
-          <t>77243</t>
-        </is>
+      <c r="A1210" t="n">
+        <v>77243</v>
       </c>
       <c r="B1210" t="inlineStr">
         <is>
@@ -48471,10 +48453,8 @@
       </c>
     </row>
     <row r="1211">
-      <c r="A1211" t="inlineStr">
-        <is>
-          <t>77235</t>
-        </is>
+      <c r="A1211" t="n">
+        <v>77235</v>
       </c>
       <c r="B1211" t="inlineStr">
         <is>
@@ -48514,10 +48494,8 @@
       </c>
     </row>
     <row r="1212">
-      <c r="A1212" t="inlineStr">
-        <is>
-          <t>77228</t>
-        </is>
+      <c r="A1212" t="n">
+        <v>77228</v>
       </c>
       <c r="B1212" t="inlineStr">
         <is>
@@ -48557,10 +48535,8 @@
       </c>
     </row>
     <row r="1213">
-      <c r="A1213" t="inlineStr">
-        <is>
-          <t>69163</t>
-        </is>
+      <c r="A1213" t="n">
+        <v>69163</v>
       </c>
       <c r="B1213" t="inlineStr">
         <is>
@@ -48600,10 +48576,8 @@
       </c>
     </row>
     <row r="1214">
-      <c r="A1214" t="inlineStr">
-        <is>
-          <t>109205</t>
-        </is>
+      <c r="A1214" t="n">
+        <v>109205</v>
       </c>
       <c r="B1214" t="inlineStr">
         <is>
@@ -48643,10 +48617,8 @@
       </c>
     </row>
     <row r="1215">
-      <c r="A1215" t="inlineStr">
-        <is>
-          <t>65512</t>
-        </is>
+      <c r="A1215" t="n">
+        <v>65512</v>
       </c>
       <c r="B1215" t="inlineStr">
         <is>
@@ -48686,10 +48658,8 @@
       </c>
     </row>
     <row r="1216">
-      <c r="A1216" t="inlineStr">
-        <is>
-          <t>83384</t>
-        </is>
+      <c r="A1216" t="n">
+        <v>83384</v>
       </c>
       <c r="B1216" t="inlineStr">
         <is>
@@ -48729,10 +48699,8 @@
       </c>
     </row>
     <row r="1217">
-      <c r="A1217" t="inlineStr">
-        <is>
-          <t>77015</t>
-        </is>
+      <c r="A1217" t="n">
+        <v>77015</v>
       </c>
       <c r="B1217" t="inlineStr">
         <is>
@@ -48772,10 +48740,8 @@
       </c>
     </row>
     <row r="1218">
-      <c r="A1218" t="inlineStr">
-        <is>
-          <t>107728</t>
-        </is>
+      <c r="A1218" t="n">
+        <v>107728</v>
       </c>
       <c r="B1218" t="inlineStr">
         <is>
@@ -48815,10 +48781,8 @@
       </c>
     </row>
     <row r="1219">
-      <c r="A1219" t="inlineStr">
-        <is>
-          <t>65572</t>
-        </is>
+      <c r="A1219" t="n">
+        <v>65572</v>
       </c>
       <c r="B1219" t="inlineStr">
         <is>
@@ -48858,10 +48822,8 @@
       </c>
     </row>
     <row r="1220">
-      <c r="A1220" t="inlineStr">
-        <is>
-          <t>65511</t>
-        </is>
+      <c r="A1220" t="n">
+        <v>65511</v>
       </c>
       <c r="B1220" t="inlineStr">
         <is>
@@ -48901,10 +48863,8 @@
       </c>
     </row>
     <row r="1221">
-      <c r="A1221" t="inlineStr">
-        <is>
-          <t>65556</t>
-        </is>
+      <c r="A1221" t="n">
+        <v>65556</v>
       </c>
       <c r="B1221" t="inlineStr">
         <is>
@@ -48942,6 +48902,830 @@
       <c r="I1221" t="n">
         <v>179.9</v>
       </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>65542</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>3250 MacDonald St</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2573819, 'Longitude': -123.1680407}</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:02:59</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:37:56.487Z</t>
+        </is>
+      </c>
+      <c r="G1222" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1222" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:37:56.532Z</t>
+        </is>
+      </c>
+      <c r="I1222" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>65533</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>4615 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2449719, 'Longitude': -123.1540385}</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:02:59</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:14:33.406Z</t>
+        </is>
+      </c>
+      <c r="G1223" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1223" t="inlineStr"/>
+      <c r="I1223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>83068</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>3205 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.256927568207, 'Longitude': -123.153288960457}</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:02:59</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr"/>
+      <c r="G1224" t="inlineStr"/>
+      <c r="H1224" t="inlineStr"/>
+      <c r="I1224" t="inlineStr"/>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>65562</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>2808 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263883932125, 'Longitude': -123.168604373932}</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:02:59</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:59:34.178Z</t>
+        </is>
+      </c>
+      <c r="G1225" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1225" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:17:36.405Z</t>
+        </is>
+      </c>
+      <c r="I1225" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>113305</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>3596 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234385296079, 'Longitude': -123.184762001038}</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:02:59</t>
+        </is>
+      </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:19:41.317Z</t>
+        </is>
+      </c>
+      <c r="G1226" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1226" t="inlineStr"/>
+      <c r="I1226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>65570</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:02:59</t>
+        </is>
+      </c>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:59:52.538Z</t>
+        </is>
+      </c>
+      <c r="G1227" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1227" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:16:34.188Z</t>
+        </is>
+      </c>
+      <c r="I1227" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>65554</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>1795 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264037962303, 'Longitude': -123.145408630371}</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:02:59</t>
+        </is>
+      </c>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:37:14.595Z</t>
+        </is>
+      </c>
+      <c r="G1228" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1228" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:31:16.269Z</t>
+        </is>
+      </c>
+      <c r="I1228" t="n">
+        <v>199.3</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>65571</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>4314 W 10th Ave</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263533861752, 'Longitude': -123.203430175781}</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:02:59</t>
+        </is>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:35:47.299Z</t>
+        </is>
+      </c>
+      <c r="G1229" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1229" t="inlineStr">
+        <is>
+          <t>2025-08-19T16:29:09.259Z</t>
+        </is>
+      </c>
+      <c r="I1229" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>65565</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:02:59</t>
+        </is>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:39:55.743Z</t>
+        </is>
+      </c>
+      <c r="G1230" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1230" t="inlineStr"/>
+      <c r="I1230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>32376</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>1503 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234634576953, 'Longitude': -123.139971792698}</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:02:59</t>
+        </is>
+      </c>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:34:22.591Z</t>
+        </is>
+      </c>
+      <c r="G1231" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1231" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:30:08.915Z</t>
+        </is>
+      </c>
+      <c r="I1231" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>65549</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>5702 Granville St</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234036184118, 'Longitude': -123.139244914055}</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:02:59</t>
+        </is>
+      </c>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:34:33.317Z</t>
+        </is>
+      </c>
+      <c r="G1232" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1232" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:38:32.763Z</t>
+        </is>
+      </c>
+      <c r="I1232" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>65543</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:02:59</t>
+        </is>
+      </c>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:39:05.578Z</t>
+        </is>
+      </c>
+      <c r="G1233" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1233" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:22.999Z</t>
+        </is>
+      </c>
+      <c r="I1233" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>65563</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:02:59</t>
+        </is>
+      </c>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:39:08.177Z</t>
+        </is>
+      </c>
+      <c r="G1234" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1234" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:11.555Z</t>
+        </is>
+      </c>
+      <c r="I1234" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>72747</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>1010 W King Edward Ave</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249188, 'Longitude': -123.127767}</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:02:59</t>
+        </is>
+      </c>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:32:35.299Z</t>
+        </is>
+      </c>
+      <c r="G1235" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1235" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:43:58.867Z</t>
+        </is>
+      </c>
+      <c r="I1235" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>32375</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>4110 Oak St</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.24894071957, 'Longitude': -123.127040863037}</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:02:59</t>
+        </is>
+      </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:32:29.262Z</t>
+        </is>
+      </c>
+      <c r="G1236" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1236" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:13:19.073Z</t>
+        </is>
+      </c>
+      <c r="I1236" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>65564</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>5680 Oak St</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234217162181, 'Longitude': -123.127684593201}</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:02:59</t>
+        </is>
+      </c>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:36:11.798Z</t>
+        </is>
+      </c>
+      <c r="G1237" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1237" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:08:24.294Z</t>
+        </is>
+      </c>
+      <c r="I1237" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>32372</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>6525 Oak St</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226226639452, 'Longitude': -123.128687739372}</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:02:59</t>
+        </is>
+      </c>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:35:35.977Z</t>
+        </is>
+      </c>
+      <c r="G1238" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1238" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:33:23.261Z</t>
+        </is>
+      </c>
+      <c r="I1238" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>9707</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:02:59</t>
+        </is>
+      </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:53:46.947Z</t>
+        </is>
+      </c>
+      <c r="G1239" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1239" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:44:27.069Z</t>
+        </is>
+      </c>
+      <c r="I1239" t="n">
+        <v>199.9</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>65566</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>8072 Granville St</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.212495055855, 'Longitude': -123.14013004303}</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:02:59</t>
+        </is>
+      </c>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:39:19.179Z</t>
+        </is>
+      </c>
+      <c r="G1240" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1240" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:30:08.359Z</t>
+        </is>
+      </c>
+      <c r="I1240" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>65572</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:02:59</t>
+        </is>
+      </c>
+      <c r="F1241" t="inlineStr"/>
+      <c r="G1241" t="inlineStr"/>
+      <c r="H1241" t="inlineStr"/>
+      <c r="I1241" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/gas_prices.xlsx
+++ b/data/gas_prices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1241"/>
+  <dimension ref="A1:I1401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48904,10 +48904,8 @@
       </c>
     </row>
     <row r="1222">
-      <c r="A1222" t="inlineStr">
-        <is>
-          <t>65542</t>
-        </is>
+      <c r="A1222" t="n">
+        <v>65542</v>
       </c>
       <c r="B1222" t="inlineStr">
         <is>
@@ -48947,10 +48945,8 @@
       </c>
     </row>
     <row r="1223">
-      <c r="A1223" t="inlineStr">
-        <is>
-          <t>65533</t>
-        </is>
+      <c r="A1223" t="n">
+        <v>65533</v>
       </c>
       <c r="B1223" t="inlineStr">
         <is>
@@ -48986,10 +48982,8 @@
       </c>
     </row>
     <row r="1224">
-      <c r="A1224" t="inlineStr">
-        <is>
-          <t>83068</t>
-        </is>
+      <c r="A1224" t="n">
+        <v>83068</v>
       </c>
       <c r="B1224" t="inlineStr">
         <is>
@@ -49017,10 +49011,8 @@
       <c r="I1224" t="inlineStr"/>
     </row>
     <row r="1225">
-      <c r="A1225" t="inlineStr">
-        <is>
-          <t>65562</t>
-        </is>
+      <c r="A1225" t="n">
+        <v>65562</v>
       </c>
       <c r="B1225" t="inlineStr">
         <is>
@@ -49060,10 +49052,8 @@
       </c>
     </row>
     <row r="1226">
-      <c r="A1226" t="inlineStr">
-        <is>
-          <t>113305</t>
-        </is>
+      <c r="A1226" t="n">
+        <v>113305</v>
       </c>
       <c r="B1226" t="inlineStr">
         <is>
@@ -49099,10 +49089,8 @@
       </c>
     </row>
     <row r="1227">
-      <c r="A1227" t="inlineStr">
-        <is>
-          <t>65570</t>
-        </is>
+      <c r="A1227" t="n">
+        <v>65570</v>
       </c>
       <c r="B1227" t="inlineStr">
         <is>
@@ -49142,10 +49130,8 @@
       </c>
     </row>
     <row r="1228">
-      <c r="A1228" t="inlineStr">
-        <is>
-          <t>65554</t>
-        </is>
+      <c r="A1228" t="n">
+        <v>65554</v>
       </c>
       <c r="B1228" t="inlineStr">
         <is>
@@ -49185,10 +49171,8 @@
       </c>
     </row>
     <row r="1229">
-      <c r="A1229" t="inlineStr">
-        <is>
-          <t>65571</t>
-        </is>
+      <c r="A1229" t="n">
+        <v>65571</v>
       </c>
       <c r="B1229" t="inlineStr">
         <is>
@@ -49228,10 +49212,8 @@
       </c>
     </row>
     <row r="1230">
-      <c r="A1230" t="inlineStr">
-        <is>
-          <t>65565</t>
-        </is>
+      <c r="A1230" t="n">
+        <v>65565</v>
       </c>
       <c r="B1230" t="inlineStr">
         <is>
@@ -49267,10 +49249,8 @@
       </c>
     </row>
     <row r="1231">
-      <c r="A1231" t="inlineStr">
-        <is>
-          <t>32376</t>
-        </is>
+      <c r="A1231" t="n">
+        <v>32376</v>
       </c>
       <c r="B1231" t="inlineStr">
         <is>
@@ -49310,10 +49290,8 @@
       </c>
     </row>
     <row r="1232">
-      <c r="A1232" t="inlineStr">
-        <is>
-          <t>65549</t>
-        </is>
+      <c r="A1232" t="n">
+        <v>65549</v>
       </c>
       <c r="B1232" t="inlineStr">
         <is>
@@ -49353,10 +49331,8 @@
       </c>
     </row>
     <row r="1233">
-      <c r="A1233" t="inlineStr">
-        <is>
-          <t>65543</t>
-        </is>
+      <c r="A1233" t="n">
+        <v>65543</v>
       </c>
       <c r="B1233" t="inlineStr">
         <is>
@@ -49396,10 +49372,8 @@
       </c>
     </row>
     <row r="1234">
-      <c r="A1234" t="inlineStr">
-        <is>
-          <t>65563</t>
-        </is>
+      <c r="A1234" t="n">
+        <v>65563</v>
       </c>
       <c r="B1234" t="inlineStr">
         <is>
@@ -49439,10 +49413,8 @@
       </c>
     </row>
     <row r="1235">
-      <c r="A1235" t="inlineStr">
-        <is>
-          <t>72747</t>
-        </is>
+      <c r="A1235" t="n">
+        <v>72747</v>
       </c>
       <c r="B1235" t="inlineStr">
         <is>
@@ -49482,10 +49454,8 @@
       </c>
     </row>
     <row r="1236">
-      <c r="A1236" t="inlineStr">
-        <is>
-          <t>32375</t>
-        </is>
+      <c r="A1236" t="n">
+        <v>32375</v>
       </c>
       <c r="B1236" t="inlineStr">
         <is>
@@ -49525,10 +49495,8 @@
       </c>
     </row>
     <row r="1237">
-      <c r="A1237" t="inlineStr">
-        <is>
-          <t>65564</t>
-        </is>
+      <c r="A1237" t="n">
+        <v>65564</v>
       </c>
       <c r="B1237" t="inlineStr">
         <is>
@@ -49568,10 +49536,8 @@
       </c>
     </row>
     <row r="1238">
-      <c r="A1238" t="inlineStr">
-        <is>
-          <t>32372</t>
-        </is>
+      <c r="A1238" t="n">
+        <v>32372</v>
       </c>
       <c r="B1238" t="inlineStr">
         <is>
@@ -49611,10 +49577,8 @@
       </c>
     </row>
     <row r="1239">
-      <c r="A1239" t="inlineStr">
-        <is>
-          <t>9707</t>
-        </is>
+      <c r="A1239" t="n">
+        <v>9707</v>
       </c>
       <c r="B1239" t="inlineStr">
         <is>
@@ -49654,10 +49618,8 @@
       </c>
     </row>
     <row r="1240">
-      <c r="A1240" t="inlineStr">
-        <is>
-          <t>65566</t>
-        </is>
+      <c r="A1240" t="n">
+        <v>65566</v>
       </c>
       <c r="B1240" t="inlineStr">
         <is>
@@ -49697,10 +49659,8 @@
       </c>
     </row>
     <row r="1241">
-      <c r="A1241" t="inlineStr">
-        <is>
-          <t>65572</t>
-        </is>
+      <c r="A1241" t="n">
+        <v>65572</v>
       </c>
       <c r="B1241" t="inlineStr">
         <is>
@@ -49727,6 +49687,6502 @@
       <c r="H1241" t="inlineStr"/>
       <c r="I1241" t="inlineStr"/>
     </row>
+    <row r="1242">
+      <c r="A1242" t="n">
+        <v>65542</v>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>3250 MacDonald St</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2573819, 'Longitude': -123.1680407}</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:15:29</t>
+        </is>
+      </c>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:37:56.487Z</t>
+        </is>
+      </c>
+      <c r="G1242" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1242" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:37:56.532Z</t>
+        </is>
+      </c>
+      <c r="I1242" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="n">
+        <v>65533</v>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>4615 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2449719, 'Longitude': -123.1540385}</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:15:29</t>
+        </is>
+      </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:14:33.406Z</t>
+        </is>
+      </c>
+      <c r="G1243" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1243" t="inlineStr"/>
+      <c r="I1243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="n">
+        <v>83068</v>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>3205 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.256927568207, 'Longitude': -123.153288960457}</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:15:29</t>
+        </is>
+      </c>
+      <c r="F1244" t="inlineStr"/>
+      <c r="G1244" t="inlineStr"/>
+      <c r="H1244" t="inlineStr"/>
+      <c r="I1244" t="inlineStr"/>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="n">
+        <v>65562</v>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>2808 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263883932125, 'Longitude': -123.168604373932}</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:15:29</t>
+        </is>
+      </c>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:59:34.178Z</t>
+        </is>
+      </c>
+      <c r="G1245" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1245" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:17:36.405Z</t>
+        </is>
+      </c>
+      <c r="I1245" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="n">
+        <v>113305</v>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>3596 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234385296079, 'Longitude': -123.184762001038}</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:15:29</t>
+        </is>
+      </c>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:19:41.317Z</t>
+        </is>
+      </c>
+      <c r="G1246" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1246" t="inlineStr"/>
+      <c r="I1246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:15:29</t>
+        </is>
+      </c>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:59:52.538Z</t>
+        </is>
+      </c>
+      <c r="G1247" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1247" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:16:34.188Z</t>
+        </is>
+      </c>
+      <c r="I1247" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="n">
+        <v>65554</v>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>1795 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264037962303, 'Longitude': -123.145408630371}</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:15:29</t>
+        </is>
+      </c>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:37:14.595Z</t>
+        </is>
+      </c>
+      <c r="G1248" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1248" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:31:16.269Z</t>
+        </is>
+      </c>
+      <c r="I1248" t="n">
+        <v>199.3</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="n">
+        <v>65571</v>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>4314 W 10th Ave</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263533861752, 'Longitude': -123.203430175781}</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:15:29</t>
+        </is>
+      </c>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:35:47.299Z</t>
+        </is>
+      </c>
+      <c r="G1249" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1249" t="inlineStr">
+        <is>
+          <t>2025-08-19T16:29:09.259Z</t>
+        </is>
+      </c>
+      <c r="I1249" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:15:29</t>
+        </is>
+      </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:39:55.743Z</t>
+        </is>
+      </c>
+      <c r="G1250" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1250" t="inlineStr"/>
+      <c r="I1250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="n">
+        <v>32376</v>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>1503 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234634576953, 'Longitude': -123.139971792698}</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:15:29</t>
+        </is>
+      </c>
+      <c r="F1251" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:34:22.591Z</t>
+        </is>
+      </c>
+      <c r="G1251" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1251" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:30:08.915Z</t>
+        </is>
+      </c>
+      <c r="I1251" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="n">
+        <v>65549</v>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>5702 Granville St</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234036184118, 'Longitude': -123.139244914055}</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:15:29</t>
+        </is>
+      </c>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:34:33.317Z</t>
+        </is>
+      </c>
+      <c r="G1252" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1252" t="inlineStr">
+        <is>
+          <t>2025-08-20T15:38:32.763Z</t>
+        </is>
+      </c>
+      <c r="I1252" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:15:29</t>
+        </is>
+      </c>
+      <c r="F1253" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:39:05.578Z</t>
+        </is>
+      </c>
+      <c r="G1253" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1253" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:22.999Z</t>
+        </is>
+      </c>
+      <c r="I1253" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:15:29</t>
+        </is>
+      </c>
+      <c r="F1254" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:39:08.177Z</t>
+        </is>
+      </c>
+      <c r="G1254" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1254" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:11.555Z</t>
+        </is>
+      </c>
+      <c r="I1254" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="n">
+        <v>72747</v>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>1010 W King Edward Ave</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249188, 'Longitude': -123.127767}</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:15:29</t>
+        </is>
+      </c>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:32:35.299Z</t>
+        </is>
+      </c>
+      <c r="G1255" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1255" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:43:58.867Z</t>
+        </is>
+      </c>
+      <c r="I1255" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="n">
+        <v>32375</v>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>4110 Oak St</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.24894071957, 'Longitude': -123.127040863037}</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:15:29</t>
+        </is>
+      </c>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:32:29.262Z</t>
+        </is>
+      </c>
+      <c r="G1256" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1256" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:13:19.073Z</t>
+        </is>
+      </c>
+      <c r="I1256" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="n">
+        <v>65564</v>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>5680 Oak St</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234217162181, 'Longitude': -123.127684593201}</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:15:29</t>
+        </is>
+      </c>
+      <c r="F1257" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:36:11.798Z</t>
+        </is>
+      </c>
+      <c r="G1257" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1257" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:08:24.294Z</t>
+        </is>
+      </c>
+      <c r="I1257" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="n">
+        <v>32372</v>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>6525 Oak St</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226226639452, 'Longitude': -123.128687739372}</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:15:29</t>
+        </is>
+      </c>
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:35:35.977Z</t>
+        </is>
+      </c>
+      <c r="G1258" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1258" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:33:23.261Z</t>
+        </is>
+      </c>
+      <c r="I1258" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:15:29</t>
+        </is>
+      </c>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:53:46.947Z</t>
+        </is>
+      </c>
+      <c r="G1259" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1259" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:44:27.069Z</t>
+        </is>
+      </c>
+      <c r="I1259" t="n">
+        <v>199.9</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="n">
+        <v>65566</v>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>8072 Granville St</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.212495055855, 'Longitude': -123.14013004303}</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:15:29</t>
+        </is>
+      </c>
+      <c r="F1260" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:39:19.179Z</t>
+        </is>
+      </c>
+      <c r="G1260" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1260" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:30:08.359Z</t>
+        </is>
+      </c>
+      <c r="I1260" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="n">
+        <v>65572</v>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:15:29</t>
+        </is>
+      </c>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:18:36.192Z</t>
+        </is>
+      </c>
+      <c r="G1261" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1261" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:31:11.263Z</t>
+        </is>
+      </c>
+      <c r="I1261" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="n">
+        <v>65558</v>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>1390 E 33rd Ave</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.240045470021, 'Longitude': -123.076765537262}</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:18:02</t>
+        </is>
+      </c>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:19:17.439Z</t>
+        </is>
+      </c>
+      <c r="G1262" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H1262" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:19:17.486Z</t>
+        </is>
+      </c>
+      <c r="I1262" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="n">
+        <v>83394</v>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>4064 Fraser St</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.248864, 'Longitude': -123.09002}</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:18:02</t>
+        </is>
+      </c>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:34:57.523Z</t>
+        </is>
+      </c>
+      <c r="G1263" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1263" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:15:27.854Z</t>
+        </is>
+      </c>
+      <c r="I1263" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="n">
+        <v>65573</v>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>1396 E 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.232593005895, 'Longitude': -123.07728856802}</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:18:02</t>
+        </is>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:22:50.113Z</t>
+        </is>
+      </c>
+      <c r="G1264" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H1264" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:28:44.531Z</t>
+        </is>
+      </c>
+      <c r="I1264" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="n">
+        <v>80714</v>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>Husky</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>4933 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2397388, 'Longitude': -123.065748}</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:18:02</t>
+        </is>
+      </c>
+      <c r="F1265" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:17:49.698Z</t>
+        </is>
+      </c>
+      <c r="G1265" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1265" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:17:49.745Z</t>
+        </is>
+      </c>
+      <c r="I1265" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="n">
+        <v>65552</v>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>2001 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.245312771918, 'Longitude': -123.064910173416}</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:18:02</t>
+        </is>
+      </c>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:54:53.724Z</t>
+        </is>
+      </c>
+      <c r="G1266" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H1266" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:25:23.251Z</t>
+        </is>
+      </c>
+      <c r="I1266" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="n">
+        <v>65538</v>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>5252 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2372145, 'Longitude': -123.0650857}</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:18:02</t>
+        </is>
+      </c>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:17:15.702Z</t>
+        </is>
+      </c>
+      <c r="G1267" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1267" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:17:15.749Z</t>
+        </is>
+      </c>
+      <c r="I1267" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="n">
+        <v>90814</v>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>2277 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.242132845692, 'Longitude': -123.058204650879}</t>
+        </is>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:18:02</t>
+        </is>
+      </c>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:02:05.337Z</t>
+        </is>
+      </c>
+      <c r="G1268" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1268" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:17:33.155Z</t>
+        </is>
+      </c>
+      <c r="I1268" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="n">
+        <v>39768</v>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>5736 Main St</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2325708, 'Longitude': -123.1010069}</t>
+        </is>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:18:02</t>
+        </is>
+      </c>
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:25:29.167Z</t>
+        </is>
+      </c>
+      <c r="G1269" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1269" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:25:29.209Z</t>
+        </is>
+      </c>
+      <c r="I1269" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="n">
+        <v>9710</v>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>1295 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259878978744, 'Longitude': -123.078074455261}</t>
+        </is>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:18:02</t>
+        </is>
+      </c>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:16:42.438Z</t>
+        </is>
+      </c>
+      <c r="G1270" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1270" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:16:42.500Z</t>
+        </is>
+      </c>
+      <c r="I1270" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="n">
+        <v>99146</v>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>1317 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259758544957, 'Longitude': -123.077272474766}</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:18:02</t>
+        </is>
+      </c>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:09:00.206Z</t>
+        </is>
+      </c>
+      <c r="G1271" t="n">
+        <v>145.9</v>
+      </c>
+      <c r="H1271" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:46:02.493Z</t>
+        </is>
+      </c>
+      <c r="I1271" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="n">
+        <v>65560</v>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>1289 E Broadway</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.262693682723, 'Longitude': -123.078117370605}</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:18:02</t>
+        </is>
+      </c>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:23:32.683Z</t>
+        </is>
+      </c>
+      <c r="G1272" t="n">
+        <v>145.9</v>
+      </c>
+      <c r="H1272" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:34:57.313Z</t>
+        </is>
+      </c>
+      <c r="I1272" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="n">
+        <v>65557</v>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>2120 Grandview Hwy S</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2591601, 'Longitude': -123.0617495}</t>
+        </is>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:18:02</t>
+        </is>
+      </c>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:50:11.954Z</t>
+        </is>
+      </c>
+      <c r="G1273" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H1273" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:50:12.000Z</t>
+        </is>
+      </c>
+      <c r="I1273" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="n">
+        <v>65559</v>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>6502 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.224996944057, 'Longitude': -123.065521717072}</t>
+        </is>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:18:02</t>
+        </is>
+      </c>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:45:10.949Z</t>
+        </is>
+      </c>
+      <c r="G1274" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1274" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:06:56.250Z</t>
+        </is>
+      </c>
+      <c r="I1274" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="n">
+        <v>71502</v>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>2748 Main St</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2604441, 'Longitude': -123.1005869}</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:18:02</t>
+        </is>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:33:17.912Z</t>
+        </is>
+      </c>
+      <c r="G1275" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H1275" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:00:35.937Z</t>
+        </is>
+      </c>
+      <c r="I1275" t="n">
+        <v>175.9</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="n">
+        <v>89943</v>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>6808 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2220242, 'Longitude': -123.0654247}</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:18:02</t>
+        </is>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:12:54.504Z</t>
+        </is>
+      </c>
+      <c r="G1276" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1276" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:59:15.108Z</t>
+        </is>
+      </c>
+      <c r="I1276" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:18:02</t>
+        </is>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:56.964Z</t>
+        </is>
+      </c>
+      <c r="G1277" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1277" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:57.027Z</t>
+        </is>
+      </c>
+      <c r="I1277" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="n">
+        <v>65537</v>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>2918 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.23608, 'Longitude': -123.0454858}</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:18:02</t>
+        </is>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:23:18.569Z</t>
+        </is>
+      </c>
+      <c r="G1278" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1278" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:24:44.587Z</t>
+        </is>
+      </c>
+      <c r="I1278" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:18:02</t>
+        </is>
+      </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:37.582Z</t>
+        </is>
+      </c>
+      <c r="G1279" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1279" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:37.661Z</t>
+        </is>
+      </c>
+      <c r="I1279" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="n">
+        <v>65535</v>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>2605 E 49th Ave</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2251291, 'Longitude': -123.0545048}</t>
+        </is>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:18:02</t>
+        </is>
+      </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:14:32.764Z</t>
+        </is>
+      </c>
+      <c r="G1280" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1280" t="inlineStr"/>
+      <c r="I1280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="n">
+        <v>75425</v>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>1785 Main St</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.26940640121, 'Longitude': -123.101197779179}</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:18:02</t>
+        </is>
+      </c>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:56:20.135Z</t>
+        </is>
+      </c>
+      <c r="G1281" t="n">
+        <v>147.9</v>
+      </c>
+      <c r="H1281" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:55:16.815Z</t>
+        </is>
+      </c>
+      <c r="I1281" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="n">
+        <v>77015</v>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169873456637, 'Longitude': -123.091178619746}</t>
+        </is>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:20:23</t>
+        </is>
+      </c>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:31:06.078Z</t>
+        </is>
+      </c>
+      <c r="G1282" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H1282" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:31:03.107Z</t>
+        </is>
+      </c>
+      <c r="I1282" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="n">
+        <v>65511</v>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:20:23</t>
+        </is>
+      </c>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:33:47.013Z</t>
+        </is>
+      </c>
+      <c r="G1283" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1283" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:54:19.348Z</t>
+        </is>
+      </c>
+      <c r="I1283" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="n">
+        <v>86650</v>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169856952787, 'Longitude': -123.123961687088}</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:20:23</t>
+        </is>
+      </c>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:16:08.792Z</t>
+        </is>
+      </c>
+      <c r="G1284" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H1284" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:05:27.032Z</t>
+        </is>
+      </c>
+      <c r="I1284" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="n">
+        <v>77218</v>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.173339635958, 'Longitude': -123.124954104424}</t>
+        </is>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:20:23</t>
+        </is>
+      </c>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:04:39.182Z</t>
+        </is>
+      </c>
+      <c r="G1285" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H1285" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:04:48.775Z</t>
+        </is>
+      </c>
+      <c r="I1285" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="n">
+        <v>77228</v>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1843249, 'Longitude': -123.1236078}</t>
+        </is>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:20:23</t>
+        </is>
+      </c>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:36:44.162Z</t>
+        </is>
+      </c>
+      <c r="G1286" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1286" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:29:09.481Z</t>
+        </is>
+      </c>
+      <c r="I1286" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="n">
+        <v>83384</v>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192001, 'Longitude': -123.124004}</t>
+        </is>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:20:23</t>
+        </is>
+      </c>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:58:54.806Z</t>
+        </is>
+      </c>
+      <c r="G1287" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H1287" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:12:26.110Z</t>
+        </is>
+      </c>
+      <c r="I1287" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="n">
+        <v>77202</v>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.162989071149, 'Longitude': -123.134229183197}</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:20:23</t>
+        </is>
+      </c>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:28:12.749Z</t>
+        </is>
+      </c>
+      <c r="G1288" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H1288" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:47:01.715Z</t>
+        </is>
+      </c>
+      <c r="I1288" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="n">
+        <v>77243</v>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.179182137142, 'Longitude': -123.137152791023}</t>
+        </is>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:20:23</t>
+        </is>
+      </c>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:55:29.336Z</t>
+        </is>
+      </c>
+      <c r="G1289" t="n">
+        <v>146.9</v>
+      </c>
+      <c r="H1289" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:55:29.368Z</t>
+        </is>
+      </c>
+      <c r="I1289" t="n">
+        <v>171.9</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="n">
+        <v>83387</v>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>710 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21081995506, 'Longitude': -123.090755939484}</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:20:23</t>
+        </is>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:36.070Z</t>
+        </is>
+      </c>
+      <c r="G1290" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1290" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:36.117Z</t>
+        </is>
+      </c>
+      <c r="I1290" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="n">
+        <v>65551</v>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>688 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210798928329, 'Longitude': -123.09152841568}</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:20:23</t>
+        </is>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:41.118Z</t>
+        </is>
+      </c>
+      <c r="G1291" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1291" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:41.149Z</t>
+        </is>
+      </c>
+      <c r="I1291" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="n">
+        <v>77235</v>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.18409178594, 'Longitude': -123.136823830688}</t>
+        </is>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:20:23</t>
+        </is>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:30:53.814Z</t>
+        </is>
+      </c>
+      <c r="G1292" t="n">
+        <v>151.9</v>
+      </c>
+      <c r="H1292" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:57:43.427Z</t>
+        </is>
+      </c>
+      <c r="I1292" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="n">
+        <v>82925</v>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>350 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210245, 'Longitude': -123.099328}</t>
+        </is>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:20:23</t>
+        </is>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:30.559Z</t>
+        </is>
+      </c>
+      <c r="G1293" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1293" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:30.605Z</t>
+        </is>
+      </c>
+      <c r="I1293" t="n">
+        <v>171.9</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="n">
+        <v>109205</v>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.133556536531, 'Longitude': -123.092424273491}</t>
+        </is>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:20:23</t>
+        </is>
+      </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:43:32.889Z</t>
+        </is>
+      </c>
+      <c r="G1294" t="n">
+        <v>150.9</v>
+      </c>
+      <c r="H1294" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:39:09.550Z</t>
+        </is>
+      </c>
+      <c r="I1294" t="n">
+        <v>175.9</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="n">
+        <v>65540</v>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>196 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2106867, 'Longitude': -123.1027436}</t>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:20:23</t>
+        </is>
+      </c>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:17:29.583Z</t>
+        </is>
+      </c>
+      <c r="G1295" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1295" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:17:29.630Z</t>
+        </is>
+      </c>
+      <c r="I1295" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="n">
+        <v>65512</v>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1328393, 'Longitude': -123.0926312}</t>
+        </is>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:20:23</t>
+        </is>
+      </c>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:53:20.325Z</t>
+        </is>
+      </c>
+      <c r="G1296" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H1296" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:39:12.965Z</t>
+        </is>
+      </c>
+      <c r="I1296" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="n">
+        <v>77205</v>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1558882, 'Longitude': -123.1369625}</t>
+        </is>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:20:23</t>
+        </is>
+      </c>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:35:57.949Z</t>
+        </is>
+      </c>
+      <c r="G1297" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1297" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:09:47.598Z</t>
+        </is>
+      </c>
+      <c r="I1297" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:20:23</t>
+        </is>
+      </c>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:37.582Z</t>
+        </is>
+      </c>
+      <c r="G1298" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1298" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:37.661Z</t>
+        </is>
+      </c>
+      <c r="I1298" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:20:23</t>
+        </is>
+      </c>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:56.964Z</t>
+        </is>
+      </c>
+      <c r="G1299" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1299" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:57.027Z</t>
+        </is>
+      </c>
+      <c r="I1299" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="n">
+        <v>65556</v>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20806537721, 'Longitude': -123.123285770416}</t>
+        </is>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:20:23</t>
+        </is>
+      </c>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:46.593Z</t>
+        </is>
+      </c>
+      <c r="G1300" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1300" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:46.640Z</t>
+        </is>
+      </c>
+      <c r="I1300" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="n">
+        <v>86937</v>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>8655 Boundary Rd</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20476, 'Longitude': -123.02398}</t>
+        </is>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:20:23</t>
+        </is>
+      </c>
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:06:44.117Z</t>
+        </is>
+      </c>
+      <c r="G1301" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1301" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:06:44.227Z</t>
+        </is>
+      </c>
+      <c r="I1301" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="n">
+        <v>65515</v>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>4011 Francis Rd</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.14867500071, 'Longitude': -123.180856704712}</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:22:43</t>
+        </is>
+      </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:06:22.229Z</t>
+        </is>
+      </c>
+      <c r="G1302" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="H1302" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:49:17.229Z</t>
+        </is>
+      </c>
+      <c r="I1302" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="n">
+        <v>77205</v>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1558882, 'Longitude': -123.1369625}</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:22:43</t>
+        </is>
+      </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:35:57.949Z</t>
+        </is>
+      </c>
+      <c r="G1303" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1303" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:09:47.598Z</t>
+        </is>
+      </c>
+      <c r="I1303" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="n">
+        <v>77223</v>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>7991 No 1 Rd</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.155888686563, 'Longitude': -123.181414604187}</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:22:43</t>
+        </is>
+      </c>
+      <c r="F1304" t="inlineStr"/>
+      <c r="G1304" t="inlineStr"/>
+      <c r="H1304" t="inlineStr"/>
+      <c r="I1304" t="inlineStr"/>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="n">
+        <v>65514</v>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>7980 Williams Rd</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.140582914547, 'Longitude': -123.137168884277}</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:22:43</t>
+        </is>
+      </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:40:55.460Z</t>
+        </is>
+      </c>
+      <c r="G1305" t="n">
+        <v>150.9</v>
+      </c>
+      <c r="H1305" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:04:20.233Z</t>
+        </is>
+      </c>
+      <c r="I1305" t="n">
+        <v>175.9</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="n">
+        <v>77232</v>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900 Westminster Hwy </t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1698419, 'Longitude': -123.159282}</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:22:43</t>
+        </is>
+      </c>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:35:40.338Z</t>
+        </is>
+      </c>
+      <c r="G1306" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1306" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:52:26.878Z</t>
+        </is>
+      </c>
+      <c r="I1306" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="n">
+        <v>77202</v>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.162989071149, 'Longitude': -123.134229183197}</t>
+        </is>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:22:43</t>
+        </is>
+      </c>
+      <c r="F1307" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:28:12.749Z</t>
+        </is>
+      </c>
+      <c r="G1307" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H1307" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:47:01.715Z</t>
+        </is>
+      </c>
+      <c r="I1307" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="n">
+        <v>86650</v>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169856952787, 'Longitude': -123.123961687088}</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:22:43</t>
+        </is>
+      </c>
+      <c r="F1308" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:16:08.792Z</t>
+        </is>
+      </c>
+      <c r="G1308" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H1308" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:05:27.032Z</t>
+        </is>
+      </c>
+      <c r="I1308" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="n">
+        <v>77218</v>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.173339635958, 'Longitude': -123.124954104424}</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:22:43</t>
+        </is>
+      </c>
+      <c r="F1309" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:04:39.182Z</t>
+        </is>
+      </c>
+      <c r="G1309" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H1309" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:04:48.775Z</t>
+        </is>
+      </c>
+      <c r="I1309" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="n">
+        <v>77243</v>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.179182137142, 'Longitude': -123.137152791023}</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:22:43</t>
+        </is>
+      </c>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:55:29.336Z</t>
+        </is>
+      </c>
+      <c r="G1310" t="n">
+        <v>146.9</v>
+      </c>
+      <c r="H1310" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:55:29.368Z</t>
+        </is>
+      </c>
+      <c r="I1310" t="n">
+        <v>171.9</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="n">
+        <v>77235</v>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.18409178594, 'Longitude': -123.136823830688}</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:22:43</t>
+        </is>
+      </c>
+      <c r="F1311" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:30:53.814Z</t>
+        </is>
+      </c>
+      <c r="G1311" t="n">
+        <v>151.9</v>
+      </c>
+      <c r="H1311" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:57:43.427Z</t>
+        </is>
+      </c>
+      <c r="I1311" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="n">
+        <v>77228</v>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1843249, 'Longitude': -123.1236078}</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:22:43</t>
+        </is>
+      </c>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:36:44.162Z</t>
+        </is>
+      </c>
+      <c r="G1312" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1312" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:29:09.481Z</t>
+        </is>
+      </c>
+      <c r="I1312" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="n">
+        <v>69163</v>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>5111 Grant McConachie Way</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192919, 'Longitude': -123.166797}</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:22:43</t>
+        </is>
+      </c>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:52:59.459Z</t>
+        </is>
+      </c>
+      <c r="G1313" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="H1313" t="inlineStr">
+        <is>
+          <t>2025-08-20T10:13:47.773Z</t>
+        </is>
+      </c>
+      <c r="I1313" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="n">
+        <v>109205</v>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.133556536531, 'Longitude': -123.092424273491}</t>
+        </is>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:22:43</t>
+        </is>
+      </c>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:43:32.889Z</t>
+        </is>
+      </c>
+      <c r="G1314" t="n">
+        <v>150.9</v>
+      </c>
+      <c r="H1314" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:39:09.550Z</t>
+        </is>
+      </c>
+      <c r="I1314" t="n">
+        <v>175.9</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="n">
+        <v>65512</v>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1328393, 'Longitude': -123.0926312}</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:22:43</t>
+        </is>
+      </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:53:20.325Z</t>
+        </is>
+      </c>
+      <c r="G1315" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H1315" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:39:12.965Z</t>
+        </is>
+      </c>
+      <c r="I1315" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="n">
+        <v>83384</v>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192001, 'Longitude': -123.124004}</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:22:43</t>
+        </is>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:58:54.806Z</t>
+        </is>
+      </c>
+      <c r="G1316" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H1316" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:12:26.110Z</t>
+        </is>
+      </c>
+      <c r="I1316" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="n">
+        <v>77015</v>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169873456637, 'Longitude': -123.091178619746}</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:22:43</t>
+        </is>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:31:06.078Z</t>
+        </is>
+      </c>
+      <c r="G1317" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H1317" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:31:03.107Z</t>
+        </is>
+      </c>
+      <c r="I1317" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="n">
+        <v>107728</v>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>8884 Granville St</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2054215, 'Longitude': -123.1401677}</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:22:43</t>
+        </is>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:13.367Z</t>
+        </is>
+      </c>
+      <c r="G1318" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1318" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:13.470Z</t>
+        </is>
+      </c>
+      <c r="I1318" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="n">
+        <v>65572</v>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:22:43</t>
+        </is>
+      </c>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:18:36.192Z</t>
+        </is>
+      </c>
+      <c r="G1319" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1319" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:31:11.263Z</t>
+        </is>
+      </c>
+      <c r="I1319" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="n">
+        <v>65511</v>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:22:43</t>
+        </is>
+      </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:33:47.013Z</t>
+        </is>
+      </c>
+      <c r="G1320" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1320" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:54:19.348Z</t>
+        </is>
+      </c>
+      <c r="I1320" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="n">
+        <v>65556</v>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20806537721, 'Longitude': -123.123285770416}</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:22:43</t>
+        </is>
+      </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:46.593Z</t>
+        </is>
+      </c>
+      <c r="G1321" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1321" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:46.640Z</t>
+        </is>
+      </c>
+      <c r="I1321" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="n">
+        <v>32378</v>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>1613 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3288556, 'Longitude': -123.1592779}</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:25:17</t>
+        </is>
+      </c>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:23:48.032Z</t>
+        </is>
+      </c>
+      <c r="G1322" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1322" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:23:48.047Z</t>
+        </is>
+      </c>
+      <c r="I1322" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="n">
+        <v>98624</v>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>1503 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.328484, 'Longitude': -123.15694}</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:25:17</t>
+        </is>
+      </c>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:15:01.270Z</t>
+        </is>
+      </c>
+      <c r="G1323" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1323" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:24:13.558Z</t>
+        </is>
+      </c>
+      <c r="I1323" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="n">
+        <v>98626</v>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>1490 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.328176303121, 'Longitude': -123.1565746665}</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:25:17</t>
+        </is>
+      </c>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:14:31.488Z</t>
+        </is>
+      </c>
+      <c r="G1324" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1324" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:57:16.589Z</t>
+        </is>
+      </c>
+      <c r="I1324" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="n">
+        <v>65575</v>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>1305 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.327918987512, 'Longitude': -123.151953220367}</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:25:17</t>
+        </is>
+      </c>
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:13:52.915Z</t>
+        </is>
+      </c>
+      <c r="G1325" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1325" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:58:23.220Z</t>
+        </is>
+      </c>
+      <c r="I1325" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="n">
+        <v>65505</v>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>1731 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.325583506404, 'Longitude': -123.121590614319}</t>
+        </is>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:25:17</t>
+        </is>
+      </c>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:56:52.357Z</t>
+        </is>
+      </c>
+      <c r="G1326" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1326" t="inlineStr"/>
+      <c r="I1326" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="n">
+        <v>65503</v>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>1980 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.324534601594, 'Longitude': -123.121654987335}</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:25:17</t>
+        </is>
+      </c>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:56:55.183Z</t>
+        </is>
+      </c>
+      <c r="G1327" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1327" t="inlineStr"/>
+      <c r="I1327" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="n">
+        <v>75407</v>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>2698 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3343054, 'Longitude': -123.1157865}</t>
+        </is>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:25:17</t>
+        </is>
+      </c>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>2025-08-20T17:57:49.298Z</t>
+        </is>
+      </c>
+      <c r="G1328" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1328" t="inlineStr"/>
+      <c r="I1328" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="n">
+        <v>75406</v>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>1198 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.323975176559, 'Longitude': -123.107525110245}</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:25:17</t>
+        </is>
+      </c>
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:12:38.776Z</t>
+        </is>
+      </c>
+      <c r="G1329" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1329" t="inlineStr"/>
+      <c r="I1329" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="n">
+        <v>75409</v>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>3150 Edgemont Blvd</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.338128, 'Longitude': -123.1021338}</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:25:17</t>
+        </is>
+      </c>
+      <c r="F1330" t="inlineStr"/>
+      <c r="G1330" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1330" t="inlineStr"/>
+      <c r="I1330" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="n">
+        <v>98622</v>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>3690 Westmount Rd</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3459143, 'Longitude': -123.2177286}</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:25:17</t>
+        </is>
+      </c>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:08:16.327Z</t>
+        </is>
+      </c>
+      <c r="G1331" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1331" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:08:16.374Z</t>
+        </is>
+      </c>
+      <c r="I1331" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="n">
+        <v>18803</v>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>2501 Westview Dr</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.332617583893, 'Longitude': -123.088846206665}</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:25:17</t>
+        </is>
+      </c>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:02:33.190Z</t>
+        </is>
+      </c>
+      <c r="G1332" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1332" t="inlineStr"/>
+      <c r="I1332" t="inlineStr"/>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="n">
+        <v>18804</v>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>660 3rd St  W</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319671, 'Longitude': -123.0902808}</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:25:17</t>
+        </is>
+      </c>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:08:23.486Z</t>
+        </is>
+      </c>
+      <c r="G1333" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1333" t="inlineStr">
+        <is>
+          <t>2025-08-19T17:13:18.796Z</t>
+        </is>
+      </c>
+      <c r="I1333" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="n">
+        <v>32349</v>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>106 W Queens St</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.336724992343, 'Longitude': -123.072506189346}</t>
+        </is>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:25:17</t>
+        </is>
+      </c>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:36:38.345Z</t>
+        </is>
+      </c>
+      <c r="G1334" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1334" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:31:29.513Z</t>
+        </is>
+      </c>
+      <c r="I1334" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="n">
+        <v>18509</v>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>2305 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3306729, 'Longitude': -123.0728536}</t>
+        </is>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:25:17</t>
+        </is>
+      </c>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:46:45.103Z</t>
+        </is>
+      </c>
+      <c r="G1335" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1335" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:46:45.134Z</t>
+        </is>
+      </c>
+      <c r="I1335" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="n">
+        <v>22117</v>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>1245 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319695364751, 'Longitude': -123.07279586792}</t>
+        </is>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:25:17</t>
+        </is>
+      </c>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:11:12.019Z</t>
+        </is>
+      </c>
+      <c r="G1336" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1336" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:29:40.955Z</t>
+        </is>
+      </c>
+      <c r="I1336" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:25:17</t>
+        </is>
+      </c>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:53:46.947Z</t>
+        </is>
+      </c>
+      <c r="G1337" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1337" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:44:27.069Z</t>
+        </is>
+      </c>
+      <c r="I1337" t="n">
+        <v>199.9</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:25:17</t>
+        </is>
+      </c>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:39:08.177Z</t>
+        </is>
+      </c>
+      <c r="G1338" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1338" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:11.555Z</t>
+        </is>
+      </c>
+      <c r="I1338" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:25:17</t>
+        </is>
+      </c>
+      <c r="F1339" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:39:05.578Z</t>
+        </is>
+      </c>
+      <c r="G1339" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1339" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:22.999Z</t>
+        </is>
+      </c>
+      <c r="I1339" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:25:17</t>
+        </is>
+      </c>
+      <c r="F1340" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:39:55.743Z</t>
+        </is>
+      </c>
+      <c r="G1340" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1340" t="inlineStr"/>
+      <c r="I1340" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:25:17</t>
+        </is>
+      </c>
+      <c r="F1341" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:59:52.538Z</t>
+        </is>
+      </c>
+      <c r="G1341" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1341" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:16:34.188Z</t>
+        </is>
+      </c>
+      <c r="I1341" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="n">
+        <v>18509</v>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>2305 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3306729, 'Longitude': -123.0728536}</t>
+        </is>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:27:32</t>
+        </is>
+      </c>
+      <c r="F1342" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:46:45.103Z</t>
+        </is>
+      </c>
+      <c r="G1342" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1342" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:46:45.134Z</t>
+        </is>
+      </c>
+      <c r="I1342" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="n">
+        <v>22117</v>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>1245 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319695364751, 'Longitude': -123.07279586792}</t>
+        </is>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:27:32</t>
+        </is>
+      </c>
+      <c r="F1343" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:11:12.019Z</t>
+        </is>
+      </c>
+      <c r="G1343" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1343" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:29:40.955Z</t>
+        </is>
+      </c>
+      <c r="I1343" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="n">
+        <v>32349</v>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>106 W Queens St</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.336724992343, 'Longitude': -123.072506189346}</t>
+        </is>
+      </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:27:32</t>
+        </is>
+      </c>
+      <c r="F1344" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:36:38.345Z</t>
+        </is>
+      </c>
+      <c r="G1344" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1344" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:31:29.513Z</t>
+        </is>
+      </c>
+      <c r="I1344" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="n">
+        <v>18803</v>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>2501 Westview Dr</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.332617583893, 'Longitude': -123.088846206665}</t>
+        </is>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:27:32</t>
+        </is>
+      </c>
+      <c r="F1345" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:02:33.190Z</t>
+        </is>
+      </c>
+      <c r="G1345" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1345" t="inlineStr"/>
+      <c r="I1345" t="inlineStr"/>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="n">
+        <v>18804</v>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>660 3rd St  W</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319671, 'Longitude': -123.0902808}</t>
+        </is>
+      </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:27:32</t>
+        </is>
+      </c>
+      <c r="F1346" t="inlineStr">
+        <is>
+          <t>2025-08-21T09:25:09.433Z</t>
+        </is>
+      </c>
+      <c r="G1346" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1346" t="inlineStr">
+        <is>
+          <t>2025-08-19T17:13:18.796Z</t>
+        </is>
+      </c>
+      <c r="I1346" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="n">
+        <v>75409</v>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>3150 Edgemont Blvd</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.338128, 'Longitude': -123.1021338}</t>
+        </is>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:27:32</t>
+        </is>
+      </c>
+      <c r="F1347" t="inlineStr"/>
+      <c r="G1347" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1347" t="inlineStr"/>
+      <c r="I1347" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="n">
+        <v>75406</v>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>1198 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.323975176559, 'Longitude': -123.107525110245}</t>
+        </is>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:27:32</t>
+        </is>
+      </c>
+      <c r="F1348" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:12:38.776Z</t>
+        </is>
+      </c>
+      <c r="G1348" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1348" t="inlineStr"/>
+      <c r="I1348" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="n">
+        <v>18512</v>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>2747 Mountain Hwy</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.333694, 'Longitude': -123.038315}</t>
+        </is>
+      </c>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:27:32</t>
+        </is>
+      </c>
+      <c r="F1349" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:51.574Z</t>
+        </is>
+      </c>
+      <c r="G1349" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1349" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:51.669Z</t>
+        </is>
+      </c>
+      <c r="I1349" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="n">
+        <v>9706</v>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>2979 Mountain Hwy</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3356515, 'Longitude': -123.038272}</t>
+        </is>
+      </c>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:27:32</t>
+        </is>
+      </c>
+      <c r="F1350" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:27.273Z</t>
+        </is>
+      </c>
+      <c r="G1350" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1350" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:24.292Z</t>
+        </is>
+      </c>
+      <c r="I1350" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="n">
+        <v>32289</v>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>1270 Lynn Valley Rd</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.337231840266, 'Longitude': -123.038763999939}</t>
+        </is>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:27:32</t>
+        </is>
+      </c>
+      <c r="F1351" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:20:04.635Z</t>
+        </is>
+      </c>
+      <c r="G1351" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1351" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:20:21.066Z</t>
+        </is>
+      </c>
+      <c r="I1351" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="n">
+        <v>75407</v>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>2698 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3343054, 'Longitude': -123.1157865}</t>
+        </is>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:27:32</t>
+        </is>
+      </c>
+      <c r="F1352" t="inlineStr">
+        <is>
+          <t>2025-08-20T17:57:49.298Z</t>
+        </is>
+      </c>
+      <c r="G1352" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1352" t="inlineStr"/>
+      <c r="I1352" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="n">
+        <v>65505</v>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>1731 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.325583506404, 'Longitude': -123.121590614319}</t>
+        </is>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:27:32</t>
+        </is>
+      </c>
+      <c r="F1353" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:56:52.357Z</t>
+        </is>
+      </c>
+      <c r="G1353" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1353" t="inlineStr"/>
+      <c r="I1353" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="n">
+        <v>65503</v>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>1980 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.324534601594, 'Longitude': -123.121654987335}</t>
+        </is>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:27:32</t>
+        </is>
+      </c>
+      <c r="F1354" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:56:55.183Z</t>
+        </is>
+      </c>
+      <c r="G1354" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1354" t="inlineStr"/>
+      <c r="I1354" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="n">
+        <v>18510</v>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>1490 Main St</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3057944, 'Longitude': -123.0328688}</t>
+        </is>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:27:32</t>
+        </is>
+      </c>
+      <c r="F1355" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:46:56.130Z</t>
+        </is>
+      </c>
+      <c r="G1355" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1355" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:46:56.146Z</t>
+        </is>
+      </c>
+      <c r="I1355" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="n">
+        <v>69296</v>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185 Mountain Hwy </t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.305048881232, 'Longitude': -123.0324447155}</t>
+        </is>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:27:32</t>
+        </is>
+      </c>
+      <c r="F1356" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:47:21.070Z</t>
+        </is>
+      </c>
+      <c r="G1356" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1356" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:47:21.149Z</t>
+        </is>
+      </c>
+      <c r="I1356" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="n">
+        <v>65506</v>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>333 Seymour Blvd</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.311498347051, 'Longitude': -123.022198677063}</t>
+        </is>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:27:32</t>
+        </is>
+      </c>
+      <c r="F1357" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:55:45.837Z</t>
+        </is>
+      </c>
+      <c r="G1357" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1357" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:55:45.868Z</t>
+        </is>
+      </c>
+      <c r="I1357" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="n">
+        <v>98513</v>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>1955 Powell St</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.28504, 'Longitude': -123.0643977}</t>
+        </is>
+      </c>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:27:32</t>
+        </is>
+      </c>
+      <c r="F1358" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:02:42.373Z</t>
+        </is>
+      </c>
+      <c r="G1358" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1358" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:59:12.373Z</t>
+        </is>
+      </c>
+      <c r="I1358" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="n">
+        <v>75410</v>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>2177 Dollarton Hwy</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.305160809746, 'Longitude': -123.014302253723}</t>
+        </is>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:27:32</t>
+        </is>
+      </c>
+      <c r="F1359" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:09:28.635Z</t>
+        </is>
+      </c>
+      <c r="G1359" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1359" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:09:28.667Z</t>
+        </is>
+      </c>
+      <c r="I1359" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="n">
+        <v>65546</v>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>1212 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2809987, 'Longitude': -123.0786929}</t>
+        </is>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:27:32</t>
+        </is>
+      </c>
+      <c r="F1360" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:16:07.492Z</t>
+        </is>
+      </c>
+      <c r="G1360" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1360" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:35:00.625Z</t>
+        </is>
+      </c>
+      <c r="I1360" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="n">
+        <v>98515</v>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>1896 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.281018940561, 'Longitude': -123.065712153912}</t>
+        </is>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:27:32</t>
+        </is>
+      </c>
+      <c r="F1361" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:16:25.413Z</t>
+        </is>
+      </c>
+      <c r="G1361" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1361" t="inlineStr">
+        <is>
+          <t>2025-08-20T07:10:51.610Z</t>
+        </is>
+      </c>
+      <c r="I1361" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="n">
+        <v>65464</v>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>6751 Lougheed Hwy</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2598029, 'Longitude': -122.9640097}</t>
+        </is>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:30:02</t>
+        </is>
+      </c>
+      <c r="F1362" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:49:56.063Z</t>
+        </is>
+      </c>
+      <c r="G1362" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1362" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:49:02.294Z</t>
+        </is>
+      </c>
+      <c r="I1362" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="n">
+        <v>100210</v>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>7089 Lougheed Hwy</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259055582449, 'Longitude': -122.956455763229}</t>
+        </is>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:30:02</t>
+        </is>
+      </c>
+      <c r="F1363" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:50:13.512Z</t>
+        </is>
+      </c>
+      <c r="G1363" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1363" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:49:43.230Z</t>
+        </is>
+      </c>
+      <c r="I1363" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="n">
+        <v>98628</v>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>6568 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.280205, 'Longitude': -122.96824}</t>
+        </is>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:30:02</t>
+        </is>
+      </c>
+      <c r="F1364" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:09:51.399Z</t>
+        </is>
+      </c>
+      <c r="G1364" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1364" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:03:59.509Z</t>
+        </is>
+      </c>
+      <c r="I1364" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="n">
+        <v>65465</v>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>7009 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.280651, 'Longitude': -122.9578017}</t>
+        </is>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:30:02</t>
+        </is>
+      </c>
+      <c r="F1365" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:44:36.309Z</t>
+        </is>
+      </c>
+      <c r="G1365" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1365" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:44:36.357Z</t>
+        </is>
+      </c>
+      <c r="I1365" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="n">
+        <v>117793</v>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>6511 Hastings St</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.280589202387, 'Longitude': -122.969627380371}</t>
+        </is>
+      </c>
+      <c r="E1366" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:30:02</t>
+        </is>
+      </c>
+      <c r="F1366" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:04:08.264Z</t>
+        </is>
+      </c>
+      <c r="G1366" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1366" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:04:08.295Z</t>
+        </is>
+      </c>
+      <c r="I1366" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="n">
+        <v>65476</v>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>Husky</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>5720 Hastings St</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.280138464632, 'Longitude': -122.980592250824}</t>
+        </is>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:30:02</t>
+        </is>
+      </c>
+      <c r="F1367" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:09:18.873Z</t>
+        </is>
+      </c>
+      <c r="G1367" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1367" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:05:16.925Z</t>
+        </is>
+      </c>
+      <c r="I1367" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="n">
+        <v>212356</v>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>CENTEX</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>3855 Douglas Rd</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249718360686, 'Longitude': -122.981165650914}</t>
+        </is>
+      </c>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:30:02</t>
+        </is>
+      </c>
+      <c r="F1368" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:29:32.947Z</t>
+        </is>
+      </c>
+      <c r="G1368" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1368" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:30:32.371Z</t>
+        </is>
+      </c>
+      <c r="I1368" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="n">
+        <v>919</v>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>4512 Lougheed Hwy</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.266012306544, 'Longitude': -123.002243041992}</t>
+        </is>
+      </c>
+      <c r="E1369" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:30:02</t>
+        </is>
+      </c>
+      <c r="F1369" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:01:44.476Z</t>
+        </is>
+      </c>
+      <c r="G1369" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1369" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:59:41.327Z</t>
+        </is>
+      </c>
+      <c r="I1369" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="n">
+        <v>164809</v>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>1969 Willingdon Ave</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.266593392816, 'Longitude': -123.003401756287}</t>
+        </is>
+      </c>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:30:02</t>
+        </is>
+      </c>
+      <c r="F1370" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:31:01.089Z</t>
+        </is>
+      </c>
+      <c r="G1370" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1370" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:31:01.167Z</t>
+        </is>
+      </c>
+      <c r="I1370" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="n">
+        <v>65471</v>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>5059 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.239569143746, 'Longitude': -122.96440243721}</t>
+        </is>
+      </c>
+      <c r="E1371" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:30:02</t>
+        </is>
+      </c>
+      <c r="F1371" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:19:34.223Z</t>
+        </is>
+      </c>
+      <c r="G1371" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1371" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:32:11.629Z</t>
+        </is>
+      </c>
+      <c r="I1371" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="n">
+        <v>1669</v>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>975 Willingdon Ave</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2758486, 'Longitude': -123.0035135}</t>
+        </is>
+      </c>
+      <c r="E1372" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:30:02</t>
+        </is>
+      </c>
+      <c r="F1372" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:28:51.214Z</t>
+        </is>
+      </c>
+      <c r="G1372" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1372" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:28:51.246Z</t>
+        </is>
+      </c>
+      <c r="I1372" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="n">
+        <v>65479</v>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>4505 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.255159438214, 'Longitude': -123.003401756287}</t>
+        </is>
+      </c>
+      <c r="E1373" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:30:02</t>
+        </is>
+      </c>
+      <c r="F1373" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:10:51.331Z</t>
+        </is>
+      </c>
+      <c r="G1373" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1373" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:10:51.378Z</t>
+        </is>
+      </c>
+      <c r="I1373" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="n">
+        <v>69963</v>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>4487 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.255044, 'Longitude': -123.0046907}</t>
+        </is>
+      </c>
+      <c r="E1374" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:30:02</t>
+        </is>
+      </c>
+      <c r="F1374" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:32:44.949Z</t>
+        </is>
+      </c>
+      <c r="G1374" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1374" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:10:38.822Z</t>
+        </is>
+      </c>
+      <c r="I1374" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="n">
+        <v>65466</v>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>4507 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2812235, 'Longitude': -123.0025696}</t>
+        </is>
+      </c>
+      <c r="E1375" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:30:02</t>
+        </is>
+      </c>
+      <c r="F1375" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:28:44.929Z</t>
+        </is>
+      </c>
+      <c r="G1375" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1375" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:28:44.960Z</t>
+        </is>
+      </c>
+      <c r="I1375" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="n">
+        <v>65475</v>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>3826 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2544887, 'Longitude': -123.0193605}</t>
+        </is>
+      </c>
+      <c r="E1376" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:30:02</t>
+        </is>
+      </c>
+      <c r="F1376" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:58:50.738Z</t>
+        </is>
+      </c>
+      <c r="G1376" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1376" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:58:50.785Z</t>
+        </is>
+      </c>
+      <c r="I1376" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="n">
+        <v>39293</v>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>3030 Boundary Rd</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2567447, 'Longitude': -123.0230847}</t>
+        </is>
+      </c>
+      <c r="E1377" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:30:02</t>
+        </is>
+      </c>
+      <c r="F1377" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:33:06.790Z</t>
+        </is>
+      </c>
+      <c r="G1377" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H1377" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:57:46.557Z</t>
+        </is>
+      </c>
+      <c r="I1377" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="n">
+        <v>119589</v>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>Smart Gas</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>6869 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226505740129, 'Longitude': -122.944511175156}</t>
+        </is>
+      </c>
+      <c r="E1378" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:30:02</t>
+        </is>
+      </c>
+      <c r="F1378" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:03.684Z</t>
+        </is>
+      </c>
+      <c r="G1378" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1378" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:03.731Z</t>
+        </is>
+      </c>
+      <c r="I1378" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="n">
+        <v>124671</v>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>3505 Grandview Hwy</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2585701, 'Longitude': -123.0281066}</t>
+        </is>
+      </c>
+      <c r="E1379" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:30:02</t>
+        </is>
+      </c>
+      <c r="F1379" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:51:07.379Z</t>
+        </is>
+      </c>
+      <c r="G1379" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1379" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:53:59.992Z</t>
+        </is>
+      </c>
+      <c r="I1379" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="n">
+        <v>65474</v>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>7274 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2244118, 'Longitude': -122.9410264}</t>
+        </is>
+      </c>
+      <c r="E1380" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:30:02</t>
+        </is>
+      </c>
+      <c r="F1380" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:41:39.387Z</t>
+        </is>
+      </c>
+      <c r="G1380" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1380" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:59.321Z</t>
+        </is>
+      </c>
+      <c r="I1380" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="n">
+        <v>5768</v>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>5009 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2264629, 'Longitude': -122.992576}</t>
+        </is>
+      </c>
+      <c r="E1381" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:30:02</t>
+        </is>
+      </c>
+      <c r="F1381" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:29:04.349Z</t>
+        </is>
+      </c>
+      <c r="G1381" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1381" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:12:00.421Z</t>
+        </is>
+      </c>
+      <c r="I1381" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>65480</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>6591 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21925095319, 'Longitude': -122.968211174011}</t>
+        </is>
+      </c>
+      <c r="E1382" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:32:34</t>
+        </is>
+      </c>
+      <c r="F1382" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:37:33.570Z</t>
+        </is>
+      </c>
+      <c r="G1382" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H1382" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:25:44.411Z</t>
+        </is>
+      </c>
+      <c r="I1382" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>65467</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>6138 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2201556, 'Longitude': -122.9743751}</t>
+        </is>
+      </c>
+      <c r="E1383" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:32:34</t>
+        </is>
+      </c>
+      <c r="F1383" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:37:31.647Z</t>
+        </is>
+      </c>
+      <c r="G1383" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1383" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:56:58.102Z</t>
+        </is>
+      </c>
+      <c r="I1383" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>119589</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>Smart Gas</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>6869 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226505740129, 'Longitude': -122.944511175156}</t>
+        </is>
+      </c>
+      <c r="E1384" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:32:34</t>
+        </is>
+      </c>
+      <c r="F1384" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:03.684Z</t>
+        </is>
+      </c>
+      <c r="G1384" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1384" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:03.731Z</t>
+        </is>
+      </c>
+      <c r="I1384" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>65474</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>7274 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2244118, 'Longitude': -122.9410264}</t>
+        </is>
+      </c>
+      <c r="E1385" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:32:34</t>
+        </is>
+      </c>
+      <c r="F1385" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:41:39.387Z</t>
+        </is>
+      </c>
+      <c r="G1385" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1385" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:59.321Z</t>
+        </is>
+      </c>
+      <c r="I1385" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>87633</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>5608 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.222913, 'Longitude': -122.982433}</t>
+        </is>
+      </c>
+      <c r="E1386" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:32:34</t>
+        </is>
+      </c>
+      <c r="F1386" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:35:44.530Z</t>
+        </is>
+      </c>
+      <c r="G1386" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H1386" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:48:12.771Z</t>
+        </is>
+      </c>
+      <c r="I1386" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>65481</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>7377 6th St</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.225214157435, 'Longitude': -122.935831546783}</t>
+        </is>
+      </c>
+      <c r="E1387" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:32:34</t>
+        </is>
+      </c>
+      <c r="F1387" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:31:04.755Z</t>
+        </is>
+      </c>
+      <c r="G1387" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H1387" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:31:06.319Z</t>
+        </is>
+      </c>
+      <c r="I1387" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>65477</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>7890 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.217246706543, 'Longitude': -122.931432723999}</t>
+        </is>
+      </c>
+      <c r="E1388" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:32:34</t>
+        </is>
+      </c>
+      <c r="F1388" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:38:11.932Z</t>
+        </is>
+      </c>
+      <c r="G1388" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1388" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:38:12.010Z</t>
+        </is>
+      </c>
+      <c r="I1388" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>65468</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>7587 Royal Oak Ave</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2151443, 'Longitude': -122.9890903}</t>
+        </is>
+      </c>
+      <c r="E1389" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:32:34</t>
+        </is>
+      </c>
+      <c r="F1389" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:38:45.754Z</t>
+        </is>
+      </c>
+      <c r="G1389" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1389" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:05:59.185Z</t>
+        </is>
+      </c>
+      <c r="I1389" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>65471</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>5059 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.239569143746, 'Longitude': -122.96440243721}</t>
+        </is>
+      </c>
+      <c r="E1390" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:32:34</t>
+        </is>
+      </c>
+      <c r="F1390" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:19:34.223Z</t>
+        </is>
+      </c>
+      <c r="G1390" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1390" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:32:11.629Z</t>
+        </is>
+      </c>
+      <c r="I1390" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>5768</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>5009 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2264629, 'Longitude': -122.992576}</t>
+        </is>
+      </c>
+      <c r="E1391" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:32:34</t>
+        </is>
+      </c>
+      <c r="F1391" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:29:04.349Z</t>
+        </is>
+      </c>
+      <c r="G1391" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1391" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:12:00.421Z</t>
+        </is>
+      </c>
+      <c r="I1391" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>111740</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>780 6th St</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21557, 'Longitude': -122.92387}</t>
+        </is>
+      </c>
+      <c r="E1392" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:32:34</t>
+        </is>
+      </c>
+      <c r="F1392" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:37:54.809Z</t>
+        </is>
+      </c>
+      <c r="G1392" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1392" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:37:54.856Z</t>
+        </is>
+      </c>
+      <c r="I1392" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>65469</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>4692 Imperial St</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2217244, 'Longitude': -122.9980797}</t>
+        </is>
+      </c>
+      <c r="E1393" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:32:34</t>
+        </is>
+      </c>
+      <c r="F1393" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:16:38.363Z</t>
+        </is>
+      </c>
+      <c r="G1393" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1393" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:58:12.777Z</t>
+        </is>
+      </c>
+      <c r="I1393" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>65499</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>736 Sixth Ave</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21129, 'Longitude': -122.92333}</t>
+        </is>
+      </c>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:32:34</t>
+        </is>
+      </c>
+      <c r="F1394" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:30.175Z</t>
+        </is>
+      </c>
+      <c r="G1394" t="n">
+        <v>164.6</v>
+      </c>
+      <c r="H1394" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:30.222Z</t>
+        </is>
+      </c>
+      <c r="I1394" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>65497</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>428 Sixth St</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2109656, 'Longitude': -122.9179526}</t>
+        </is>
+      </c>
+      <c r="E1395" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:32:34</t>
+        </is>
+      </c>
+      <c r="F1395" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:25:12.088Z</t>
+        </is>
+      </c>
+      <c r="G1395" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1395" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:25:12.166Z</t>
+        </is>
+      </c>
+      <c r="I1395" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>32350</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>132 12th St</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.201144, 'Longitude': -122.922922}</t>
+        </is>
+      </c>
+      <c r="E1396" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:32:34</t>
+        </is>
+      </c>
+      <c r="F1396" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:38:14.677Z</t>
+        </is>
+      </c>
+      <c r="G1396" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1396" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:38:14.709Z</t>
+        </is>
+      </c>
+      <c r="I1396" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>65502</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>5 W 8th Ave</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.222332, 'Longitude': -122.91267}</t>
+        </is>
+      </c>
+      <c r="E1397" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:32:34</t>
+        </is>
+      </c>
+      <c r="F1397" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:20:57.796Z</t>
+        </is>
+      </c>
+      <c r="G1397" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1397" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:44:49.538Z</t>
+        </is>
+      </c>
+      <c r="I1397" t="n">
+        <v>199.9</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>65498</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>3 E 8th Ave</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2228942, 'Longitude': -122.9117512}</t>
+        </is>
+      </c>
+      <c r="E1398" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:32:34</t>
+        </is>
+      </c>
+      <c r="F1398" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:20:59.978Z</t>
+        </is>
+      </c>
+      <c r="G1398" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1398" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:16:11.660Z</t>
+        </is>
+      </c>
+      <c r="I1398" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>65470</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>4444 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.23030428362, 'Longitude': -123.006110787392}</t>
+        </is>
+      </c>
+      <c r="E1399" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:32:34</t>
+        </is>
+      </c>
+      <c r="F1399" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:31:41.284Z</t>
+        </is>
+      </c>
+      <c r="G1399" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1399" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:30:13.104Z</t>
+        </is>
+      </c>
+      <c r="I1399" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>212356</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>CENTEX</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>3855 Douglas Rd</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249718360686, 'Longitude': -122.981165650914}</t>
+        </is>
+      </c>
+      <c r="E1400" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:32:34</t>
+        </is>
+      </c>
+      <c r="F1400" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:29:32.947Z</t>
+        </is>
+      </c>
+      <c r="G1400" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1400" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:30:32.371Z</t>
+        </is>
+      </c>
+      <c r="I1400" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>87636</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>CENTEX</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>1101 Ewen Ave</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.185333, 'Longitude': -122.949622}</t>
+        </is>
+      </c>
+      <c r="E1401" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:32:34</t>
+        </is>
+      </c>
+      <c r="F1401" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:41:02.053Z</t>
+        </is>
+      </c>
+      <c r="G1401" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1401" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:41:02.116Z</t>
+        </is>
+      </c>
+      <c r="I1401" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gas_prices.xlsx
+++ b/data/gas_prices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1401"/>
+  <dimension ref="A1:I1421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55324,10 +55324,8 @@
       </c>
     </row>
     <row r="1382">
-      <c r="A1382" t="inlineStr">
-        <is>
-          <t>65480</t>
-        </is>
+      <c r="A1382" t="n">
+        <v>65480</v>
       </c>
       <c r="B1382" t="inlineStr">
         <is>
@@ -55367,10 +55365,8 @@
       </c>
     </row>
     <row r="1383">
-      <c r="A1383" t="inlineStr">
-        <is>
-          <t>65467</t>
-        </is>
+      <c r="A1383" t="n">
+        <v>65467</v>
       </c>
       <c r="B1383" t="inlineStr">
         <is>
@@ -55410,10 +55406,8 @@
       </c>
     </row>
     <row r="1384">
-      <c r="A1384" t="inlineStr">
-        <is>
-          <t>119589</t>
-        </is>
+      <c r="A1384" t="n">
+        <v>119589</v>
       </c>
       <c r="B1384" t="inlineStr">
         <is>
@@ -55453,10 +55447,8 @@
       </c>
     </row>
     <row r="1385">
-      <c r="A1385" t="inlineStr">
-        <is>
-          <t>65474</t>
-        </is>
+      <c r="A1385" t="n">
+        <v>65474</v>
       </c>
       <c r="B1385" t="inlineStr">
         <is>
@@ -55496,10 +55488,8 @@
       </c>
     </row>
     <row r="1386">
-      <c r="A1386" t="inlineStr">
-        <is>
-          <t>87633</t>
-        </is>
+      <c r="A1386" t="n">
+        <v>87633</v>
       </c>
       <c r="B1386" t="inlineStr">
         <is>
@@ -55539,10 +55529,8 @@
       </c>
     </row>
     <row r="1387">
-      <c r="A1387" t="inlineStr">
-        <is>
-          <t>65481</t>
-        </is>
+      <c r="A1387" t="n">
+        <v>65481</v>
       </c>
       <c r="B1387" t="inlineStr">
         <is>
@@ -55582,10 +55570,8 @@
       </c>
     </row>
     <row r="1388">
-      <c r="A1388" t="inlineStr">
-        <is>
-          <t>65477</t>
-        </is>
+      <c r="A1388" t="n">
+        <v>65477</v>
       </c>
       <c r="B1388" t="inlineStr">
         <is>
@@ -55625,10 +55611,8 @@
       </c>
     </row>
     <row r="1389">
-      <c r="A1389" t="inlineStr">
-        <is>
-          <t>65468</t>
-        </is>
+      <c r="A1389" t="n">
+        <v>65468</v>
       </c>
       <c r="B1389" t="inlineStr">
         <is>
@@ -55668,10 +55652,8 @@
       </c>
     </row>
     <row r="1390">
-      <c r="A1390" t="inlineStr">
-        <is>
-          <t>65471</t>
-        </is>
+      <c r="A1390" t="n">
+        <v>65471</v>
       </c>
       <c r="B1390" t="inlineStr">
         <is>
@@ -55711,10 +55693,8 @@
       </c>
     </row>
     <row r="1391">
-      <c r="A1391" t="inlineStr">
-        <is>
-          <t>5768</t>
-        </is>
+      <c r="A1391" t="n">
+        <v>5768</v>
       </c>
       <c r="B1391" t="inlineStr">
         <is>
@@ -55754,10 +55734,8 @@
       </c>
     </row>
     <row r="1392">
-      <c r="A1392" t="inlineStr">
-        <is>
-          <t>111740</t>
-        </is>
+      <c r="A1392" t="n">
+        <v>111740</v>
       </c>
       <c r="B1392" t="inlineStr">
         <is>
@@ -55797,10 +55775,8 @@
       </c>
     </row>
     <row r="1393">
-      <c r="A1393" t="inlineStr">
-        <is>
-          <t>65469</t>
-        </is>
+      <c r="A1393" t="n">
+        <v>65469</v>
       </c>
       <c r="B1393" t="inlineStr">
         <is>
@@ -55840,10 +55816,8 @@
       </c>
     </row>
     <row r="1394">
-      <c r="A1394" t="inlineStr">
-        <is>
-          <t>65499</t>
-        </is>
+      <c r="A1394" t="n">
+        <v>65499</v>
       </c>
       <c r="B1394" t="inlineStr">
         <is>
@@ -55883,10 +55857,8 @@
       </c>
     </row>
     <row r="1395">
-      <c r="A1395" t="inlineStr">
-        <is>
-          <t>65497</t>
-        </is>
+      <c r="A1395" t="n">
+        <v>65497</v>
       </c>
       <c r="B1395" t="inlineStr">
         <is>
@@ -55926,10 +55898,8 @@
       </c>
     </row>
     <row r="1396">
-      <c r="A1396" t="inlineStr">
-        <is>
-          <t>32350</t>
-        </is>
+      <c r="A1396" t="n">
+        <v>32350</v>
       </c>
       <c r="B1396" t="inlineStr">
         <is>
@@ -55969,10 +55939,8 @@
       </c>
     </row>
     <row r="1397">
-      <c r="A1397" t="inlineStr">
-        <is>
-          <t>65502</t>
-        </is>
+      <c r="A1397" t="n">
+        <v>65502</v>
       </c>
       <c r="B1397" t="inlineStr">
         <is>
@@ -56012,10 +55980,8 @@
       </c>
     </row>
     <row r="1398">
-      <c r="A1398" t="inlineStr">
-        <is>
-          <t>65498</t>
-        </is>
+      <c r="A1398" t="n">
+        <v>65498</v>
       </c>
       <c r="B1398" t="inlineStr">
         <is>
@@ -56055,10 +56021,8 @@
       </c>
     </row>
     <row r="1399">
-      <c r="A1399" t="inlineStr">
-        <is>
-          <t>65470</t>
-        </is>
+      <c r="A1399" t="n">
+        <v>65470</v>
       </c>
       <c r="B1399" t="inlineStr">
         <is>
@@ -56098,10 +56062,8 @@
       </c>
     </row>
     <row r="1400">
-      <c r="A1400" t="inlineStr">
-        <is>
-          <t>212356</t>
-        </is>
+      <c r="A1400" t="n">
+        <v>212356</v>
       </c>
       <c r="B1400" t="inlineStr">
         <is>
@@ -56141,10 +56103,8 @@
       </c>
     </row>
     <row r="1401">
-      <c r="A1401" t="inlineStr">
-        <is>
-          <t>87636</t>
-        </is>
+      <c r="A1401" t="n">
+        <v>87636</v>
       </c>
       <c r="B1401" t="inlineStr">
         <is>
@@ -56181,6 +56141,862 @@
       </c>
       <c r="I1401" t="n">
         <v>183.9</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>65558</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>1390 E 33rd Ave</t>
+        </is>
+      </c>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.240045470021, 'Longitude': -123.076765537262}</t>
+        </is>
+      </c>
+      <c r="E1402" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:37:04</t>
+        </is>
+      </c>
+      <c r="F1402" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:19:17.439Z</t>
+        </is>
+      </c>
+      <c r="G1402" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H1402" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:19:17.486Z</t>
+        </is>
+      </c>
+      <c r="I1402" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>83394</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>4064 Fraser St</t>
+        </is>
+      </c>
+      <c r="D1403" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.248864, 'Longitude': -123.09002}</t>
+        </is>
+      </c>
+      <c r="E1403" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:37:04</t>
+        </is>
+      </c>
+      <c r="F1403" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:34:57.523Z</t>
+        </is>
+      </c>
+      <c r="G1403" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1403" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:15:27.854Z</t>
+        </is>
+      </c>
+      <c r="I1403" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>65573</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>1396 E 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.232593005895, 'Longitude': -123.07728856802}</t>
+        </is>
+      </c>
+      <c r="E1404" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:37:04</t>
+        </is>
+      </c>
+      <c r="F1404" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:22:50.113Z</t>
+        </is>
+      </c>
+      <c r="G1404" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H1404" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:28:44.531Z</t>
+        </is>
+      </c>
+      <c r="I1404" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>80714</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>Husky</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>4933 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2397388, 'Longitude': -123.065748}</t>
+        </is>
+      </c>
+      <c r="E1405" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:37:04</t>
+        </is>
+      </c>
+      <c r="F1405" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:17:49.698Z</t>
+        </is>
+      </c>
+      <c r="G1405" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1405" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:17:49.745Z</t>
+        </is>
+      </c>
+      <c r="I1405" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>65552</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>2001 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.245312771918, 'Longitude': -123.064910173416}</t>
+        </is>
+      </c>
+      <c r="E1406" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:37:04</t>
+        </is>
+      </c>
+      <c r="F1406" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:54:53.724Z</t>
+        </is>
+      </c>
+      <c r="G1406" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H1406" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:25:23.251Z</t>
+        </is>
+      </c>
+      <c r="I1406" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>65538</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>5252 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2372145, 'Longitude': -123.0650857}</t>
+        </is>
+      </c>
+      <c r="E1407" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:37:04</t>
+        </is>
+      </c>
+      <c r="F1407" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:17:15.702Z</t>
+        </is>
+      </c>
+      <c r="G1407" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1407" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:17:15.749Z</t>
+        </is>
+      </c>
+      <c r="I1407" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>90814</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>2277 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.242132845692, 'Longitude': -123.058204650879}</t>
+        </is>
+      </c>
+      <c r="E1408" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:37:04</t>
+        </is>
+      </c>
+      <c r="F1408" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:02:05.337Z</t>
+        </is>
+      </c>
+      <c r="G1408" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1408" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:17:33.155Z</t>
+        </is>
+      </c>
+      <c r="I1408" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>39768</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>5736 Main St</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2325708, 'Longitude': -123.1010069}</t>
+        </is>
+      </c>
+      <c r="E1409" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:37:04</t>
+        </is>
+      </c>
+      <c r="F1409" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:25:29.167Z</t>
+        </is>
+      </c>
+      <c r="G1409" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1409" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:25:29.209Z</t>
+        </is>
+      </c>
+      <c r="I1409" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>9710</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>1295 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259878978744, 'Longitude': -123.078074455261}</t>
+        </is>
+      </c>
+      <c r="E1410" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:37:04</t>
+        </is>
+      </c>
+      <c r="F1410" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:16:42.438Z</t>
+        </is>
+      </c>
+      <c r="G1410" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1410" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:16:42.500Z</t>
+        </is>
+      </c>
+      <c r="I1410" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>99146</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>1317 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259758544957, 'Longitude': -123.077272474766}</t>
+        </is>
+      </c>
+      <c r="E1411" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:37:04</t>
+        </is>
+      </c>
+      <c r="F1411" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:09:00.206Z</t>
+        </is>
+      </c>
+      <c r="G1411" t="n">
+        <v>145.9</v>
+      </c>
+      <c r="H1411" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:46:02.493Z</t>
+        </is>
+      </c>
+      <c r="I1411" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>65560</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>1289 E Broadway</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.262693682723, 'Longitude': -123.078117370605}</t>
+        </is>
+      </c>
+      <c r="E1412" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:37:04</t>
+        </is>
+      </c>
+      <c r="F1412" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:23:32.683Z</t>
+        </is>
+      </c>
+      <c r="G1412" t="n">
+        <v>145.9</v>
+      </c>
+      <c r="H1412" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:34:57.313Z</t>
+        </is>
+      </c>
+      <c r="I1412" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>65557</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>2120 Grandview Hwy S</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2591601, 'Longitude': -123.0617495}</t>
+        </is>
+      </c>
+      <c r="E1413" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:37:04</t>
+        </is>
+      </c>
+      <c r="F1413" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:50:11.954Z</t>
+        </is>
+      </c>
+      <c r="G1413" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H1413" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:50:12.000Z</t>
+        </is>
+      </c>
+      <c r="I1413" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>65559</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>6502 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.224996944057, 'Longitude': -123.065521717072}</t>
+        </is>
+      </c>
+      <c r="E1414" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:37:04</t>
+        </is>
+      </c>
+      <c r="F1414" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:45:10.949Z</t>
+        </is>
+      </c>
+      <c r="G1414" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1414" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:06:56.250Z</t>
+        </is>
+      </c>
+      <c r="I1414" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>71502</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>2748 Main St</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2604441, 'Longitude': -123.1005869}</t>
+        </is>
+      </c>
+      <c r="E1415" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:37:04</t>
+        </is>
+      </c>
+      <c r="F1415" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:33:17.912Z</t>
+        </is>
+      </c>
+      <c r="G1415" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H1415" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:00:35.937Z</t>
+        </is>
+      </c>
+      <c r="I1415" t="n">
+        <v>175.9</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>89943</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>6808 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2220242, 'Longitude': -123.0654247}</t>
+        </is>
+      </c>
+      <c r="E1416" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:37:04</t>
+        </is>
+      </c>
+      <c r="F1416" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:12:54.504Z</t>
+        </is>
+      </c>
+      <c r="G1416" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1416" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:59:15.108Z</t>
+        </is>
+      </c>
+      <c r="I1416" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>86880</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E1417" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:37:04</t>
+        </is>
+      </c>
+      <c r="F1417" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:56.964Z</t>
+        </is>
+      </c>
+      <c r="G1417" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1417" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:57.027Z</t>
+        </is>
+      </c>
+      <c r="I1417" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>65537</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>2918 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.23608, 'Longitude': -123.0454858}</t>
+        </is>
+      </c>
+      <c r="E1418" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:37:04</t>
+        </is>
+      </c>
+      <c r="F1418" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:23:18.569Z</t>
+        </is>
+      </c>
+      <c r="G1418" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1418" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:24:44.587Z</t>
+        </is>
+      </c>
+      <c r="I1418" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>65536</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E1419" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:37:04</t>
+        </is>
+      </c>
+      <c r="F1419" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:37.582Z</t>
+        </is>
+      </c>
+      <c r="G1419" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1419" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:37.661Z</t>
+        </is>
+      </c>
+      <c r="I1419" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>65535</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>2605 E 49th Ave</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2251291, 'Longitude': -123.0545048}</t>
+        </is>
+      </c>
+      <c r="E1420" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:37:04</t>
+        </is>
+      </c>
+      <c r="F1420" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:14:32.764Z</t>
+        </is>
+      </c>
+      <c r="G1420" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1420" t="inlineStr"/>
+      <c r="I1420" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>75425</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>1785 Main St</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.26940640121, 'Longitude': -123.101197779179}</t>
+        </is>
+      </c>
+      <c r="E1421" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:37:04</t>
+        </is>
+      </c>
+      <c r="F1421" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:56:20.135Z</t>
+        </is>
+      </c>
+      <c r="G1421" t="n">
+        <v>147.9</v>
+      </c>
+      <c r="H1421" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:55:16.815Z</t>
+        </is>
+      </c>
+      <c r="I1421" t="n">
+        <v>177.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/gas_prices.xlsx
+++ b/data/gas_prices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1421"/>
+  <dimension ref="A1:I1541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56144,10 +56144,8 @@
       </c>
     </row>
     <row r="1402">
-      <c r="A1402" t="inlineStr">
-        <is>
-          <t>65558</t>
-        </is>
+      <c r="A1402" t="n">
+        <v>65558</v>
       </c>
       <c r="B1402" t="inlineStr">
         <is>
@@ -56187,10 +56185,8 @@
       </c>
     </row>
     <row r="1403">
-      <c r="A1403" t="inlineStr">
-        <is>
-          <t>83394</t>
-        </is>
+      <c r="A1403" t="n">
+        <v>83394</v>
       </c>
       <c r="B1403" t="inlineStr">
         <is>
@@ -56230,10 +56226,8 @@
       </c>
     </row>
     <row r="1404">
-      <c r="A1404" t="inlineStr">
-        <is>
-          <t>65573</t>
-        </is>
+      <c r="A1404" t="n">
+        <v>65573</v>
       </c>
       <c r="B1404" t="inlineStr">
         <is>
@@ -56273,10 +56267,8 @@
       </c>
     </row>
     <row r="1405">
-      <c r="A1405" t="inlineStr">
-        <is>
-          <t>80714</t>
-        </is>
+      <c r="A1405" t="n">
+        <v>80714</v>
       </c>
       <c r="B1405" t="inlineStr">
         <is>
@@ -56316,10 +56308,8 @@
       </c>
     </row>
     <row r="1406">
-      <c r="A1406" t="inlineStr">
-        <is>
-          <t>65552</t>
-        </is>
+      <c r="A1406" t="n">
+        <v>65552</v>
       </c>
       <c r="B1406" t="inlineStr">
         <is>
@@ -56359,10 +56349,8 @@
       </c>
     </row>
     <row r="1407">
-      <c r="A1407" t="inlineStr">
-        <is>
-          <t>65538</t>
-        </is>
+      <c r="A1407" t="n">
+        <v>65538</v>
       </c>
       <c r="B1407" t="inlineStr">
         <is>
@@ -56402,10 +56390,8 @@
       </c>
     </row>
     <row r="1408">
-      <c r="A1408" t="inlineStr">
-        <is>
-          <t>90814</t>
-        </is>
+      <c r="A1408" t="n">
+        <v>90814</v>
       </c>
       <c r="B1408" t="inlineStr">
         <is>
@@ -56445,10 +56431,8 @@
       </c>
     </row>
     <row r="1409">
-      <c r="A1409" t="inlineStr">
-        <is>
-          <t>39768</t>
-        </is>
+      <c r="A1409" t="n">
+        <v>39768</v>
       </c>
       <c r="B1409" t="inlineStr">
         <is>
@@ -56488,10 +56472,8 @@
       </c>
     </row>
     <row r="1410">
-      <c r="A1410" t="inlineStr">
-        <is>
-          <t>9710</t>
-        </is>
+      <c r="A1410" t="n">
+        <v>9710</v>
       </c>
       <c r="B1410" t="inlineStr">
         <is>
@@ -56531,10 +56513,8 @@
       </c>
     </row>
     <row r="1411">
-      <c r="A1411" t="inlineStr">
-        <is>
-          <t>99146</t>
-        </is>
+      <c r="A1411" t="n">
+        <v>99146</v>
       </c>
       <c r="B1411" t="inlineStr">
         <is>
@@ -56574,10 +56554,8 @@
       </c>
     </row>
     <row r="1412">
-      <c r="A1412" t="inlineStr">
-        <is>
-          <t>65560</t>
-        </is>
+      <c r="A1412" t="n">
+        <v>65560</v>
       </c>
       <c r="B1412" t="inlineStr">
         <is>
@@ -56617,10 +56595,8 @@
       </c>
     </row>
     <row r="1413">
-      <c r="A1413" t="inlineStr">
-        <is>
-          <t>65557</t>
-        </is>
+      <c r="A1413" t="n">
+        <v>65557</v>
       </c>
       <c r="B1413" t="inlineStr">
         <is>
@@ -56660,10 +56636,8 @@
       </c>
     </row>
     <row r="1414">
-      <c r="A1414" t="inlineStr">
-        <is>
-          <t>65559</t>
-        </is>
+      <c r="A1414" t="n">
+        <v>65559</v>
       </c>
       <c r="B1414" t="inlineStr">
         <is>
@@ -56703,10 +56677,8 @@
       </c>
     </row>
     <row r="1415">
-      <c r="A1415" t="inlineStr">
-        <is>
-          <t>71502</t>
-        </is>
+      <c r="A1415" t="n">
+        <v>71502</v>
       </c>
       <c r="B1415" t="inlineStr">
         <is>
@@ -56746,10 +56718,8 @@
       </c>
     </row>
     <row r="1416">
-      <c r="A1416" t="inlineStr">
-        <is>
-          <t>89943</t>
-        </is>
+      <c r="A1416" t="n">
+        <v>89943</v>
       </c>
       <c r="B1416" t="inlineStr">
         <is>
@@ -56789,10 +56759,8 @@
       </c>
     </row>
     <row r="1417">
-      <c r="A1417" t="inlineStr">
-        <is>
-          <t>86880</t>
-        </is>
+      <c r="A1417" t="n">
+        <v>86880</v>
       </c>
       <c r="B1417" t="inlineStr">
         <is>
@@ -56832,10 +56800,8 @@
       </c>
     </row>
     <row r="1418">
-      <c r="A1418" t="inlineStr">
-        <is>
-          <t>65537</t>
-        </is>
+      <c r="A1418" t="n">
+        <v>65537</v>
       </c>
       <c r="B1418" t="inlineStr">
         <is>
@@ -56875,10 +56841,8 @@
       </c>
     </row>
     <row r="1419">
-      <c r="A1419" t="inlineStr">
-        <is>
-          <t>65536</t>
-        </is>
+      <c r="A1419" t="n">
+        <v>65536</v>
       </c>
       <c r="B1419" t="inlineStr">
         <is>
@@ -56918,10 +56882,8 @@
       </c>
     </row>
     <row r="1420">
-      <c r="A1420" t="inlineStr">
-        <is>
-          <t>65535</t>
-        </is>
+      <c r="A1420" t="n">
+        <v>65535</v>
       </c>
       <c r="B1420" t="inlineStr">
         <is>
@@ -56957,10 +56919,8 @@
       </c>
     </row>
     <row r="1421">
-      <c r="A1421" t="inlineStr">
-        <is>
-          <t>75425</t>
-        </is>
+      <c r="A1421" t="n">
+        <v>75425</v>
       </c>
       <c r="B1421" t="inlineStr">
         <is>
@@ -56997,6 +56957,4890 @@
       </c>
       <c r="I1421" t="n">
         <v>177.9</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="n">
+        <v>77015</v>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169873456637, 'Longitude': -123.091178619746}</t>
+        </is>
+      </c>
+      <c r="E1422" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:39:25</t>
+        </is>
+      </c>
+      <c r="F1422" t="inlineStr">
+        <is>
+          <t>2025-08-21T09:32:03.353Z</t>
+        </is>
+      </c>
+      <c r="G1422" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H1422" t="inlineStr">
+        <is>
+          <t>2025-08-21T09:31:33.362Z</t>
+        </is>
+      </c>
+      <c r="I1422" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="n">
+        <v>65511</v>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E1423" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:39:25</t>
+        </is>
+      </c>
+      <c r="F1423" t="inlineStr">
+        <is>
+          <t>2025-08-21T09:26:06.146Z</t>
+        </is>
+      </c>
+      <c r="G1423" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1423" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:54:19.348Z</t>
+        </is>
+      </c>
+      <c r="I1423" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="n">
+        <v>86650</v>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169856952787, 'Longitude': -123.123961687088}</t>
+        </is>
+      </c>
+      <c r="E1424" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:39:25</t>
+        </is>
+      </c>
+      <c r="F1424" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:16:08.792Z</t>
+        </is>
+      </c>
+      <c r="G1424" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H1424" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:05:27.032Z</t>
+        </is>
+      </c>
+      <c r="I1424" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="n">
+        <v>77218</v>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.173339635958, 'Longitude': -123.124954104424}</t>
+        </is>
+      </c>
+      <c r="E1425" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:39:25</t>
+        </is>
+      </c>
+      <c r="F1425" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:04:39.182Z</t>
+        </is>
+      </c>
+      <c r="G1425" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H1425" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:04:48.775Z</t>
+        </is>
+      </c>
+      <c r="I1425" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="n">
+        <v>77228</v>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1843249, 'Longitude': -123.1236078}</t>
+        </is>
+      </c>
+      <c r="E1426" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:39:25</t>
+        </is>
+      </c>
+      <c r="F1426" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:36:44.162Z</t>
+        </is>
+      </c>
+      <c r="G1426" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1426" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:29:09.481Z</t>
+        </is>
+      </c>
+      <c r="I1426" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="n">
+        <v>83384</v>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192001, 'Longitude': -123.124004}</t>
+        </is>
+      </c>
+      <c r="E1427" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:39:25</t>
+        </is>
+      </c>
+      <c r="F1427" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:58:54.806Z</t>
+        </is>
+      </c>
+      <c r="G1427" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H1427" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:12:26.110Z</t>
+        </is>
+      </c>
+      <c r="I1427" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="n">
+        <v>77202</v>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.162989071149, 'Longitude': -123.134229183197}</t>
+        </is>
+      </c>
+      <c r="E1428" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:39:25</t>
+        </is>
+      </c>
+      <c r="F1428" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:28:12.749Z</t>
+        </is>
+      </c>
+      <c r="G1428" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H1428" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:47:01.715Z</t>
+        </is>
+      </c>
+      <c r="I1428" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="n">
+        <v>77243</v>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.179182137142, 'Longitude': -123.137152791023}</t>
+        </is>
+      </c>
+      <c r="E1429" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:39:25</t>
+        </is>
+      </c>
+      <c r="F1429" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:55:29.336Z</t>
+        </is>
+      </c>
+      <c r="G1429" t="n">
+        <v>146.9</v>
+      </c>
+      <c r="H1429" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:55:29.368Z</t>
+        </is>
+      </c>
+      <c r="I1429" t="n">
+        <v>171.9</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="n">
+        <v>83387</v>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>710 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21081995506, 'Longitude': -123.090755939484}</t>
+        </is>
+      </c>
+      <c r="E1430" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:39:25</t>
+        </is>
+      </c>
+      <c r="F1430" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:36.070Z</t>
+        </is>
+      </c>
+      <c r="G1430" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1430" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:36.117Z</t>
+        </is>
+      </c>
+      <c r="I1430" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="n">
+        <v>65551</v>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>688 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210798928329, 'Longitude': -123.09152841568}</t>
+        </is>
+      </c>
+      <c r="E1431" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:39:25</t>
+        </is>
+      </c>
+      <c r="F1431" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:41.118Z</t>
+        </is>
+      </c>
+      <c r="G1431" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1431" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:41.149Z</t>
+        </is>
+      </c>
+      <c r="I1431" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="n">
+        <v>77235</v>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.18409178594, 'Longitude': -123.136823830688}</t>
+        </is>
+      </c>
+      <c r="E1432" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:39:25</t>
+        </is>
+      </c>
+      <c r="F1432" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:30:53.814Z</t>
+        </is>
+      </c>
+      <c r="G1432" t="n">
+        <v>151.9</v>
+      </c>
+      <c r="H1432" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:57:43.427Z</t>
+        </is>
+      </c>
+      <c r="I1432" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="n">
+        <v>82925</v>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>350 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210245, 'Longitude': -123.099328}</t>
+        </is>
+      </c>
+      <c r="E1433" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:39:25</t>
+        </is>
+      </c>
+      <c r="F1433" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:30.559Z</t>
+        </is>
+      </c>
+      <c r="G1433" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1433" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:30.605Z</t>
+        </is>
+      </c>
+      <c r="I1433" t="n">
+        <v>171.9</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="n">
+        <v>109205</v>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.133556536531, 'Longitude': -123.092424273491}</t>
+        </is>
+      </c>
+      <c r="E1434" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:39:25</t>
+        </is>
+      </c>
+      <c r="F1434" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:43:32.889Z</t>
+        </is>
+      </c>
+      <c r="G1434" t="n">
+        <v>150.9</v>
+      </c>
+      <c r="H1434" t="inlineStr">
+        <is>
+          <t>2025-08-21T09:25:44.022Z</t>
+        </is>
+      </c>
+      <c r="I1434" t="n">
+        <v>175.9</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="n">
+        <v>65540</v>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>196 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2106867, 'Longitude': -123.1027436}</t>
+        </is>
+      </c>
+      <c r="E1435" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:39:25</t>
+        </is>
+      </c>
+      <c r="F1435" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:17:29.583Z</t>
+        </is>
+      </c>
+      <c r="G1435" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1435" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:17:29.630Z</t>
+        </is>
+      </c>
+      <c r="I1435" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="n">
+        <v>65512</v>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1328393, 'Longitude': -123.0926312}</t>
+        </is>
+      </c>
+      <c r="E1436" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:39:25</t>
+        </is>
+      </c>
+      <c r="F1436" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:53:20.325Z</t>
+        </is>
+      </c>
+      <c r="G1436" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H1436" t="inlineStr">
+        <is>
+          <t>2025-08-21T09:25:57.460Z</t>
+        </is>
+      </c>
+      <c r="I1436" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="n">
+        <v>77205</v>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1558882, 'Longitude': -123.1369625}</t>
+        </is>
+      </c>
+      <c r="E1437" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:39:25</t>
+        </is>
+      </c>
+      <c r="F1437" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:35:57.949Z</t>
+        </is>
+      </c>
+      <c r="G1437" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1437" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:09:47.598Z</t>
+        </is>
+      </c>
+      <c r="I1437" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E1438" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:39:25</t>
+        </is>
+      </c>
+      <c r="F1438" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:37.582Z</t>
+        </is>
+      </c>
+      <c r="G1438" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1438" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:37.661Z</t>
+        </is>
+      </c>
+      <c r="I1438" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E1439" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:39:25</t>
+        </is>
+      </c>
+      <c r="F1439" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:56.964Z</t>
+        </is>
+      </c>
+      <c r="G1439" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1439" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:57.027Z</t>
+        </is>
+      </c>
+      <c r="I1439" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="n">
+        <v>65556</v>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20806537721, 'Longitude': -123.123285770416}</t>
+        </is>
+      </c>
+      <c r="E1440" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:39:25</t>
+        </is>
+      </c>
+      <c r="F1440" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:46.593Z</t>
+        </is>
+      </c>
+      <c r="G1440" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1440" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:46.640Z</t>
+        </is>
+      </c>
+      <c r="I1440" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="n">
+        <v>86937</v>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>8655 Boundary Rd</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20476, 'Longitude': -123.02398}</t>
+        </is>
+      </c>
+      <c r="E1441" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:39:25</t>
+        </is>
+      </c>
+      <c r="F1441" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:06:44.117Z</t>
+        </is>
+      </c>
+      <c r="G1441" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1441" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:06:44.227Z</t>
+        </is>
+      </c>
+      <c r="I1441" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="n">
+        <v>65515</v>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>4011 Francis Rd</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.14867500071, 'Longitude': -123.180856704712}</t>
+        </is>
+      </c>
+      <c r="E1442" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:41:48</t>
+        </is>
+      </c>
+      <c r="F1442" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:06:22.229Z</t>
+        </is>
+      </c>
+      <c r="G1442" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="H1442" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:49:17.229Z</t>
+        </is>
+      </c>
+      <c r="I1442" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="n">
+        <v>77205</v>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1558882, 'Longitude': -123.1369625}</t>
+        </is>
+      </c>
+      <c r="E1443" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:41:48</t>
+        </is>
+      </c>
+      <c r="F1443" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:35:57.949Z</t>
+        </is>
+      </c>
+      <c r="G1443" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1443" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:09:47.598Z</t>
+        </is>
+      </c>
+      <c r="I1443" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="n">
+        <v>77223</v>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>7991 No 1 Rd</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.155888686563, 'Longitude': -123.181414604187}</t>
+        </is>
+      </c>
+      <c r="E1444" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:41:48</t>
+        </is>
+      </c>
+      <c r="F1444" t="inlineStr"/>
+      <c r="G1444" t="inlineStr"/>
+      <c r="H1444" t="inlineStr"/>
+      <c r="I1444" t="inlineStr"/>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="n">
+        <v>65514</v>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>7980 Williams Rd</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.140582914547, 'Longitude': -123.137168884277}</t>
+        </is>
+      </c>
+      <c r="E1445" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:41:48</t>
+        </is>
+      </c>
+      <c r="F1445" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:40:55.460Z</t>
+        </is>
+      </c>
+      <c r="G1445" t="n">
+        <v>150.9</v>
+      </c>
+      <c r="H1445" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:04:20.233Z</t>
+        </is>
+      </c>
+      <c r="I1445" t="n">
+        <v>175.9</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="n">
+        <v>77232</v>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900 Westminster Hwy </t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1698419, 'Longitude': -123.159282}</t>
+        </is>
+      </c>
+      <c r="E1446" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:41:48</t>
+        </is>
+      </c>
+      <c r="F1446" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:35:40.338Z</t>
+        </is>
+      </c>
+      <c r="G1446" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1446" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:52:26.878Z</t>
+        </is>
+      </c>
+      <c r="I1446" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="n">
+        <v>77202</v>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.162989071149, 'Longitude': -123.134229183197}</t>
+        </is>
+      </c>
+      <c r="E1447" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:41:48</t>
+        </is>
+      </c>
+      <c r="F1447" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:28:12.749Z</t>
+        </is>
+      </c>
+      <c r="G1447" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H1447" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:47:01.715Z</t>
+        </is>
+      </c>
+      <c r="I1447" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="n">
+        <v>86650</v>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169856952787, 'Longitude': -123.123961687088}</t>
+        </is>
+      </c>
+      <c r="E1448" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:41:48</t>
+        </is>
+      </c>
+      <c r="F1448" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:16:08.792Z</t>
+        </is>
+      </c>
+      <c r="G1448" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H1448" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:05:27.032Z</t>
+        </is>
+      </c>
+      <c r="I1448" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="n">
+        <v>77218</v>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.173339635958, 'Longitude': -123.124954104424}</t>
+        </is>
+      </c>
+      <c r="E1449" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:41:48</t>
+        </is>
+      </c>
+      <c r="F1449" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:04:39.182Z</t>
+        </is>
+      </c>
+      <c r="G1449" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H1449" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:04:48.775Z</t>
+        </is>
+      </c>
+      <c r="I1449" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="n">
+        <v>77243</v>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.179182137142, 'Longitude': -123.137152791023}</t>
+        </is>
+      </c>
+      <c r="E1450" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:41:48</t>
+        </is>
+      </c>
+      <c r="F1450" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:55:29.336Z</t>
+        </is>
+      </c>
+      <c r="G1450" t="n">
+        <v>146.9</v>
+      </c>
+      <c r="H1450" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:55:29.368Z</t>
+        </is>
+      </c>
+      <c r="I1450" t="n">
+        <v>171.9</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="n">
+        <v>77235</v>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.18409178594, 'Longitude': -123.136823830688}</t>
+        </is>
+      </c>
+      <c r="E1451" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:41:48</t>
+        </is>
+      </c>
+      <c r="F1451" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:30:53.814Z</t>
+        </is>
+      </c>
+      <c r="G1451" t="n">
+        <v>151.9</v>
+      </c>
+      <c r="H1451" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:57:43.427Z</t>
+        </is>
+      </c>
+      <c r="I1451" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="n">
+        <v>77228</v>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1843249, 'Longitude': -123.1236078}</t>
+        </is>
+      </c>
+      <c r="E1452" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:41:48</t>
+        </is>
+      </c>
+      <c r="F1452" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:36:44.162Z</t>
+        </is>
+      </c>
+      <c r="G1452" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1452" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:29:09.481Z</t>
+        </is>
+      </c>
+      <c r="I1452" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="n">
+        <v>69163</v>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>5111 Grant McConachie Way</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192919, 'Longitude': -123.166797}</t>
+        </is>
+      </c>
+      <c r="E1453" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:41:48</t>
+        </is>
+      </c>
+      <c r="F1453" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:52:59.459Z</t>
+        </is>
+      </c>
+      <c r="G1453" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="H1453" t="inlineStr">
+        <is>
+          <t>2025-08-20T10:13:47.773Z</t>
+        </is>
+      </c>
+      <c r="I1453" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="n">
+        <v>109205</v>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.133556536531, 'Longitude': -123.092424273491}</t>
+        </is>
+      </c>
+      <c r="E1454" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:41:48</t>
+        </is>
+      </c>
+      <c r="F1454" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:43:32.889Z</t>
+        </is>
+      </c>
+      <c r="G1454" t="n">
+        <v>150.9</v>
+      </c>
+      <c r="H1454" t="inlineStr">
+        <is>
+          <t>2025-08-21T09:25:44.022Z</t>
+        </is>
+      </c>
+      <c r="I1454" t="n">
+        <v>175.9</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="n">
+        <v>65512</v>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1328393, 'Longitude': -123.0926312}</t>
+        </is>
+      </c>
+      <c r="E1455" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:41:48</t>
+        </is>
+      </c>
+      <c r="F1455" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:53:20.325Z</t>
+        </is>
+      </c>
+      <c r="G1455" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H1455" t="inlineStr">
+        <is>
+          <t>2025-08-21T09:25:57.460Z</t>
+        </is>
+      </c>
+      <c r="I1455" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="n">
+        <v>83384</v>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1456" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192001, 'Longitude': -123.124004}</t>
+        </is>
+      </c>
+      <c r="E1456" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:41:48</t>
+        </is>
+      </c>
+      <c r="F1456" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:58:54.806Z</t>
+        </is>
+      </c>
+      <c r="G1456" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H1456" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:12:26.110Z</t>
+        </is>
+      </c>
+      <c r="I1456" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="n">
+        <v>77015</v>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169873456637, 'Longitude': -123.091178619746}</t>
+        </is>
+      </c>
+      <c r="E1457" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:41:48</t>
+        </is>
+      </c>
+      <c r="F1457" t="inlineStr">
+        <is>
+          <t>2025-08-21T09:32:03.353Z</t>
+        </is>
+      </c>
+      <c r="G1457" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H1457" t="inlineStr">
+        <is>
+          <t>2025-08-21T09:31:33.362Z</t>
+        </is>
+      </c>
+      <c r="I1457" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="n">
+        <v>107728</v>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>8884 Granville St</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2054215, 'Longitude': -123.1401677}</t>
+        </is>
+      </c>
+      <c r="E1458" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:41:48</t>
+        </is>
+      </c>
+      <c r="F1458" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:13.367Z</t>
+        </is>
+      </c>
+      <c r="G1458" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1458" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:13.470Z</t>
+        </is>
+      </c>
+      <c r="I1458" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="n">
+        <v>65572</v>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E1459" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:41:48</t>
+        </is>
+      </c>
+      <c r="F1459" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:18:36.192Z</t>
+        </is>
+      </c>
+      <c r="G1459" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1459" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:31:11.263Z</t>
+        </is>
+      </c>
+      <c r="I1459" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="n">
+        <v>65511</v>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1460" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E1460" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:41:48</t>
+        </is>
+      </c>
+      <c r="F1460" t="inlineStr">
+        <is>
+          <t>2025-08-21T09:26:06.146Z</t>
+        </is>
+      </c>
+      <c r="G1460" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1460" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:54:19.348Z</t>
+        </is>
+      </c>
+      <c r="I1460" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="n">
+        <v>65556</v>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1461" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20806537721, 'Longitude': -123.123285770416}</t>
+        </is>
+      </c>
+      <c r="E1461" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:41:48</t>
+        </is>
+      </c>
+      <c r="F1461" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:46.593Z</t>
+        </is>
+      </c>
+      <c r="G1461" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1461" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:46.640Z</t>
+        </is>
+      </c>
+      <c r="I1461" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="n">
+        <v>32378</v>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>1613 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3288556, 'Longitude': -123.1592779}</t>
+        </is>
+      </c>
+      <c r="E1462" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:44:06</t>
+        </is>
+      </c>
+      <c r="F1462" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:23:48.032Z</t>
+        </is>
+      </c>
+      <c r="G1462" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1462" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:23:48.047Z</t>
+        </is>
+      </c>
+      <c r="I1462" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="n">
+        <v>98624</v>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>1503 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.328484, 'Longitude': -123.15694}</t>
+        </is>
+      </c>
+      <c r="E1463" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:44:06</t>
+        </is>
+      </c>
+      <c r="F1463" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:15:01.270Z</t>
+        </is>
+      </c>
+      <c r="G1463" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1463" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:24:13.558Z</t>
+        </is>
+      </c>
+      <c r="I1463" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="n">
+        <v>98626</v>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>1490 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.328176303121, 'Longitude': -123.1565746665}</t>
+        </is>
+      </c>
+      <c r="E1464" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:44:06</t>
+        </is>
+      </c>
+      <c r="F1464" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:14:31.488Z</t>
+        </is>
+      </c>
+      <c r="G1464" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1464" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:57:16.589Z</t>
+        </is>
+      </c>
+      <c r="I1464" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="n">
+        <v>65575</v>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>1305 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.327918987512, 'Longitude': -123.151953220367}</t>
+        </is>
+      </c>
+      <c r="E1465" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:44:06</t>
+        </is>
+      </c>
+      <c r="F1465" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:13:52.915Z</t>
+        </is>
+      </c>
+      <c r="G1465" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1465" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:58:23.220Z</t>
+        </is>
+      </c>
+      <c r="I1465" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="n">
+        <v>65505</v>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>1731 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.325583506404, 'Longitude': -123.121590614319}</t>
+        </is>
+      </c>
+      <c r="E1466" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:44:06</t>
+        </is>
+      </c>
+      <c r="F1466" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:56:52.357Z</t>
+        </is>
+      </c>
+      <c r="G1466" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1466" t="inlineStr"/>
+      <c r="I1466" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="n">
+        <v>65503</v>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>1980 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.324534601594, 'Longitude': -123.121654987335}</t>
+        </is>
+      </c>
+      <c r="E1467" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:44:06</t>
+        </is>
+      </c>
+      <c r="F1467" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:56:55.183Z</t>
+        </is>
+      </c>
+      <c r="G1467" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1467" t="inlineStr"/>
+      <c r="I1467" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="n">
+        <v>75407</v>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>2698 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3343054, 'Longitude': -123.1157865}</t>
+        </is>
+      </c>
+      <c r="E1468" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:44:06</t>
+        </is>
+      </c>
+      <c r="F1468" t="inlineStr">
+        <is>
+          <t>2025-08-20T17:57:49.298Z</t>
+        </is>
+      </c>
+      <c r="G1468" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1468" t="inlineStr"/>
+      <c r="I1468" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="n">
+        <v>75406</v>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>1198 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.323975176559, 'Longitude': -123.107525110245}</t>
+        </is>
+      </c>
+      <c r="E1469" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:44:06</t>
+        </is>
+      </c>
+      <c r="F1469" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:12:38.776Z</t>
+        </is>
+      </c>
+      <c r="G1469" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1469" t="inlineStr"/>
+      <c r="I1469" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="n">
+        <v>75409</v>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>3150 Edgemont Blvd</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.338128, 'Longitude': -123.1021338}</t>
+        </is>
+      </c>
+      <c r="E1470" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:44:06</t>
+        </is>
+      </c>
+      <c r="F1470" t="inlineStr"/>
+      <c r="G1470" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1470" t="inlineStr"/>
+      <c r="I1470" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="n">
+        <v>98622</v>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>3690 Westmount Rd</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3459143, 'Longitude': -123.2177286}</t>
+        </is>
+      </c>
+      <c r="E1471" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:44:06</t>
+        </is>
+      </c>
+      <c r="F1471" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:08:16.327Z</t>
+        </is>
+      </c>
+      <c r="G1471" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1471" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:08:16.374Z</t>
+        </is>
+      </c>
+      <c r="I1471" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="n">
+        <v>18803</v>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>2501 Westview Dr</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.332617583893, 'Longitude': -123.088846206665}</t>
+        </is>
+      </c>
+      <c r="E1472" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:44:06</t>
+        </is>
+      </c>
+      <c r="F1472" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:02:33.190Z</t>
+        </is>
+      </c>
+      <c r="G1472" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1472" t="inlineStr"/>
+      <c r="I1472" t="inlineStr"/>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="n">
+        <v>18804</v>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>660 3rd St  W</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319671, 'Longitude': -123.0902808}</t>
+        </is>
+      </c>
+      <c r="E1473" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:44:06</t>
+        </is>
+      </c>
+      <c r="F1473" t="inlineStr">
+        <is>
+          <t>2025-08-21T09:25:09.433Z</t>
+        </is>
+      </c>
+      <c r="G1473" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1473" t="inlineStr">
+        <is>
+          <t>2025-08-19T17:13:18.796Z</t>
+        </is>
+      </c>
+      <c r="I1473" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="n">
+        <v>32349</v>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>106 W Queens St</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.336724992343, 'Longitude': -123.072506189346}</t>
+        </is>
+      </c>
+      <c r="E1474" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:44:06</t>
+        </is>
+      </c>
+      <c r="F1474" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:36:38.345Z</t>
+        </is>
+      </c>
+      <c r="G1474" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1474" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:31:29.513Z</t>
+        </is>
+      </c>
+      <c r="I1474" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="n">
+        <v>18509</v>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>2305 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3306729, 'Longitude': -123.0728536}</t>
+        </is>
+      </c>
+      <c r="E1475" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:44:06</t>
+        </is>
+      </c>
+      <c r="F1475" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:46:45.103Z</t>
+        </is>
+      </c>
+      <c r="G1475" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1475" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:46:45.134Z</t>
+        </is>
+      </c>
+      <c r="I1475" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="n">
+        <v>22117</v>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>1245 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319695364751, 'Longitude': -123.07279586792}</t>
+        </is>
+      </c>
+      <c r="E1476" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:44:06</t>
+        </is>
+      </c>
+      <c r="F1476" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:11:12.019Z</t>
+        </is>
+      </c>
+      <c r="G1476" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1476" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:29:40.955Z</t>
+        </is>
+      </c>
+      <c r="I1476" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E1477" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:44:06</t>
+        </is>
+      </c>
+      <c r="F1477" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:53:46.947Z</t>
+        </is>
+      </c>
+      <c r="G1477" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1477" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:44:27.069Z</t>
+        </is>
+      </c>
+      <c r="I1477" t="n">
+        <v>199.9</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E1478" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:44:06</t>
+        </is>
+      </c>
+      <c r="F1478" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:39:08.177Z</t>
+        </is>
+      </c>
+      <c r="G1478" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1478" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:11.555Z</t>
+        </is>
+      </c>
+      <c r="I1478" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E1479" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:44:06</t>
+        </is>
+      </c>
+      <c r="F1479" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:39:05.578Z</t>
+        </is>
+      </c>
+      <c r="G1479" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1479" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:22.999Z</t>
+        </is>
+      </c>
+      <c r="I1479" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E1480" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:44:06</t>
+        </is>
+      </c>
+      <c r="F1480" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:39:55.743Z</t>
+        </is>
+      </c>
+      <c r="G1480" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1480" t="inlineStr"/>
+      <c r="I1480" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E1481" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:44:06</t>
+        </is>
+      </c>
+      <c r="F1481" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:59:52.538Z</t>
+        </is>
+      </c>
+      <c r="G1481" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1481" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:16:34.188Z</t>
+        </is>
+      </c>
+      <c r="I1481" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="n">
+        <v>18509</v>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>2305 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D1482" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3306729, 'Longitude': -123.0728536}</t>
+        </is>
+      </c>
+      <c r="E1482" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:46:32</t>
+        </is>
+      </c>
+      <c r="F1482" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:46:45.103Z</t>
+        </is>
+      </c>
+      <c r="G1482" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1482" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:46:45.134Z</t>
+        </is>
+      </c>
+      <c r="I1482" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="n">
+        <v>22117</v>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>1245 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319695364751, 'Longitude': -123.07279586792}</t>
+        </is>
+      </c>
+      <c r="E1483" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:46:32</t>
+        </is>
+      </c>
+      <c r="F1483" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:11:12.019Z</t>
+        </is>
+      </c>
+      <c r="G1483" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1483" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:29:40.955Z</t>
+        </is>
+      </c>
+      <c r="I1483" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="n">
+        <v>32349</v>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>106 W Queens St</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.336724992343, 'Longitude': -123.072506189346}</t>
+        </is>
+      </c>
+      <c r="E1484" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:46:32</t>
+        </is>
+      </c>
+      <c r="F1484" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:36:38.345Z</t>
+        </is>
+      </c>
+      <c r="G1484" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1484" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:31:29.513Z</t>
+        </is>
+      </c>
+      <c r="I1484" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="n">
+        <v>18803</v>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>2501 Westview Dr</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.332617583893, 'Longitude': -123.088846206665}</t>
+        </is>
+      </c>
+      <c r="E1485" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:46:32</t>
+        </is>
+      </c>
+      <c r="F1485" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:02:33.190Z</t>
+        </is>
+      </c>
+      <c r="G1485" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1485" t="inlineStr"/>
+      <c r="I1485" t="inlineStr"/>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="n">
+        <v>18804</v>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>660 3rd St  W</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319671, 'Longitude': -123.0902808}</t>
+        </is>
+      </c>
+      <c r="E1486" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:46:32</t>
+        </is>
+      </c>
+      <c r="F1486" t="inlineStr">
+        <is>
+          <t>2025-08-21T09:25:09.433Z</t>
+        </is>
+      </c>
+      <c r="G1486" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1486" t="inlineStr">
+        <is>
+          <t>2025-08-19T17:13:18.796Z</t>
+        </is>
+      </c>
+      <c r="I1486" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="n">
+        <v>75409</v>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>3150 Edgemont Blvd</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.338128, 'Longitude': -123.1021338}</t>
+        </is>
+      </c>
+      <c r="E1487" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:46:32</t>
+        </is>
+      </c>
+      <c r="F1487" t="inlineStr"/>
+      <c r="G1487" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1487" t="inlineStr"/>
+      <c r="I1487" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="n">
+        <v>75406</v>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>1198 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.323975176559, 'Longitude': -123.107525110245}</t>
+        </is>
+      </c>
+      <c r="E1488" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:46:32</t>
+        </is>
+      </c>
+      <c r="F1488" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:12:38.776Z</t>
+        </is>
+      </c>
+      <c r="G1488" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1488" t="inlineStr"/>
+      <c r="I1488" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="n">
+        <v>18512</v>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>2747 Mountain Hwy</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.333694, 'Longitude': -123.038315}</t>
+        </is>
+      </c>
+      <c r="E1489" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:46:32</t>
+        </is>
+      </c>
+      <c r="F1489" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:51.574Z</t>
+        </is>
+      </c>
+      <c r="G1489" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1489" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:51.669Z</t>
+        </is>
+      </c>
+      <c r="I1489" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="n">
+        <v>9706</v>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>2979 Mountain Hwy</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3356515, 'Longitude': -123.038272}</t>
+        </is>
+      </c>
+      <c r="E1490" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:46:32</t>
+        </is>
+      </c>
+      <c r="F1490" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:27.273Z</t>
+        </is>
+      </c>
+      <c r="G1490" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1490" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:24.292Z</t>
+        </is>
+      </c>
+      <c r="I1490" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="n">
+        <v>32289</v>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>1270 Lynn Valley Rd</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.337231840266, 'Longitude': -123.038763999939}</t>
+        </is>
+      </c>
+      <c r="E1491" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:46:32</t>
+        </is>
+      </c>
+      <c r="F1491" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:20:04.635Z</t>
+        </is>
+      </c>
+      <c r="G1491" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1491" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:20:21.066Z</t>
+        </is>
+      </c>
+      <c r="I1491" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="n">
+        <v>75407</v>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>2698 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3343054, 'Longitude': -123.1157865}</t>
+        </is>
+      </c>
+      <c r="E1492" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:46:32</t>
+        </is>
+      </c>
+      <c r="F1492" t="inlineStr">
+        <is>
+          <t>2025-08-20T17:57:49.298Z</t>
+        </is>
+      </c>
+      <c r="G1492" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1492" t="inlineStr"/>
+      <c r="I1492" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="n">
+        <v>65505</v>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>1731 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.325583506404, 'Longitude': -123.121590614319}</t>
+        </is>
+      </c>
+      <c r="E1493" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:46:32</t>
+        </is>
+      </c>
+      <c r="F1493" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:56:52.357Z</t>
+        </is>
+      </c>
+      <c r="G1493" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1493" t="inlineStr"/>
+      <c r="I1493" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="n">
+        <v>65503</v>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>1980 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1494" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.324534601594, 'Longitude': -123.121654987335}</t>
+        </is>
+      </c>
+      <c r="E1494" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:46:32</t>
+        </is>
+      </c>
+      <c r="F1494" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:56:55.183Z</t>
+        </is>
+      </c>
+      <c r="G1494" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1494" t="inlineStr"/>
+      <c r="I1494" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="n">
+        <v>18510</v>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>1490 Main St</t>
+        </is>
+      </c>
+      <c r="D1495" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3057944, 'Longitude': -123.0328688}</t>
+        </is>
+      </c>
+      <c r="E1495" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:46:32</t>
+        </is>
+      </c>
+      <c r="F1495" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:46:56.130Z</t>
+        </is>
+      </c>
+      <c r="G1495" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1495" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:46:56.146Z</t>
+        </is>
+      </c>
+      <c r="I1495" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="n">
+        <v>69296</v>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185 Mountain Hwy </t>
+        </is>
+      </c>
+      <c r="D1496" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.305048881232, 'Longitude': -123.0324447155}</t>
+        </is>
+      </c>
+      <c r="E1496" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:46:32</t>
+        </is>
+      </c>
+      <c r="F1496" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:47:21.070Z</t>
+        </is>
+      </c>
+      <c r="G1496" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1496" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:47:21.149Z</t>
+        </is>
+      </c>
+      <c r="I1496" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="n">
+        <v>65506</v>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>333 Seymour Blvd</t>
+        </is>
+      </c>
+      <c r="D1497" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.311498347051, 'Longitude': -123.022198677063}</t>
+        </is>
+      </c>
+      <c r="E1497" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:46:32</t>
+        </is>
+      </c>
+      <c r="F1497" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:55:45.837Z</t>
+        </is>
+      </c>
+      <c r="G1497" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1497" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:55:45.868Z</t>
+        </is>
+      </c>
+      <c r="I1497" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="n">
+        <v>98513</v>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>1955 Powell St</t>
+        </is>
+      </c>
+      <c r="D1498" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.28504, 'Longitude': -123.0643977}</t>
+        </is>
+      </c>
+      <c r="E1498" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:46:32</t>
+        </is>
+      </c>
+      <c r="F1498" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:02:42.373Z</t>
+        </is>
+      </c>
+      <c r="G1498" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1498" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:59:12.373Z</t>
+        </is>
+      </c>
+      <c r="I1498" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="n">
+        <v>75410</v>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>2177 Dollarton Hwy</t>
+        </is>
+      </c>
+      <c r="D1499" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.305160809746, 'Longitude': -123.014302253723}</t>
+        </is>
+      </c>
+      <c r="E1499" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:46:32</t>
+        </is>
+      </c>
+      <c r="F1499" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:09:28.635Z</t>
+        </is>
+      </c>
+      <c r="G1499" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1499" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:09:28.667Z</t>
+        </is>
+      </c>
+      <c r="I1499" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="n">
+        <v>65546</v>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>1212 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2809987, 'Longitude': -123.0786929}</t>
+        </is>
+      </c>
+      <c r="E1500" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:46:32</t>
+        </is>
+      </c>
+      <c r="F1500" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:16:07.492Z</t>
+        </is>
+      </c>
+      <c r="G1500" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1500" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:35:00.625Z</t>
+        </is>
+      </c>
+      <c r="I1500" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="n">
+        <v>98515</v>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>1896 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.281018940561, 'Longitude': -123.065712153912}</t>
+        </is>
+      </c>
+      <c r="E1501" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:46:32</t>
+        </is>
+      </c>
+      <c r="F1501" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:16:25.413Z</t>
+        </is>
+      </c>
+      <c r="G1501" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1501" t="inlineStr">
+        <is>
+          <t>2025-08-20T07:10:51.610Z</t>
+        </is>
+      </c>
+      <c r="I1501" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="n">
+        <v>65464</v>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>6751 Lougheed Hwy</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2598029, 'Longitude': -122.9640097}</t>
+        </is>
+      </c>
+      <c r="E1502" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:49:04</t>
+        </is>
+      </c>
+      <c r="F1502" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:49:56.063Z</t>
+        </is>
+      </c>
+      <c r="G1502" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1502" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:49:02.294Z</t>
+        </is>
+      </c>
+      <c r="I1502" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="n">
+        <v>100210</v>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>7089 Lougheed Hwy</t>
+        </is>
+      </c>
+      <c r="D1503" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259055582449, 'Longitude': -122.956455763229}</t>
+        </is>
+      </c>
+      <c r="E1503" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:49:04</t>
+        </is>
+      </c>
+      <c r="F1503" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:50:13.512Z</t>
+        </is>
+      </c>
+      <c r="G1503" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1503" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:49:43.230Z</t>
+        </is>
+      </c>
+      <c r="I1503" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="n">
+        <v>98628</v>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>6568 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D1504" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.280205, 'Longitude': -122.96824}</t>
+        </is>
+      </c>
+      <c r="E1504" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:49:04</t>
+        </is>
+      </c>
+      <c r="F1504" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:09:51.399Z</t>
+        </is>
+      </c>
+      <c r="G1504" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1504" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:03:59.509Z</t>
+        </is>
+      </c>
+      <c r="I1504" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="n">
+        <v>65465</v>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>7009 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D1505" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.280651, 'Longitude': -122.9578017}</t>
+        </is>
+      </c>
+      <c r="E1505" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:49:04</t>
+        </is>
+      </c>
+      <c r="F1505" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:44:36.309Z</t>
+        </is>
+      </c>
+      <c r="G1505" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1505" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:44:36.357Z</t>
+        </is>
+      </c>
+      <c r="I1505" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="n">
+        <v>117793</v>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>6511 Hastings St</t>
+        </is>
+      </c>
+      <c r="D1506" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.280589202387, 'Longitude': -122.969627380371}</t>
+        </is>
+      </c>
+      <c r="E1506" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:49:04</t>
+        </is>
+      </c>
+      <c r="F1506" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:04:08.264Z</t>
+        </is>
+      </c>
+      <c r="G1506" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1506" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:04:08.295Z</t>
+        </is>
+      </c>
+      <c r="I1506" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="n">
+        <v>65476</v>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>Husky</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>5720 Hastings St</t>
+        </is>
+      </c>
+      <c r="D1507" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.280138464632, 'Longitude': -122.980592250824}</t>
+        </is>
+      </c>
+      <c r="E1507" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:49:04</t>
+        </is>
+      </c>
+      <c r="F1507" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:09:18.873Z</t>
+        </is>
+      </c>
+      <c r="G1507" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1507" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:05:16.925Z</t>
+        </is>
+      </c>
+      <c r="I1507" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="n">
+        <v>212356</v>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>CENTEX</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>3855 Douglas Rd</t>
+        </is>
+      </c>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249718360686, 'Longitude': -122.981165650914}</t>
+        </is>
+      </c>
+      <c r="E1508" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:49:04</t>
+        </is>
+      </c>
+      <c r="F1508" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:29:32.947Z</t>
+        </is>
+      </c>
+      <c r="G1508" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1508" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:30:32.371Z</t>
+        </is>
+      </c>
+      <c r="I1508" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="n">
+        <v>919</v>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>4512 Lougheed Hwy</t>
+        </is>
+      </c>
+      <c r="D1509" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.266012306544, 'Longitude': -123.002243041992}</t>
+        </is>
+      </c>
+      <c r="E1509" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:49:04</t>
+        </is>
+      </c>
+      <c r="F1509" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:01:44.476Z</t>
+        </is>
+      </c>
+      <c r="G1509" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1509" t="inlineStr">
+        <is>
+          <t>2025-08-20T21:59:41.327Z</t>
+        </is>
+      </c>
+      <c r="I1509" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="n">
+        <v>164809</v>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>1969 Willingdon Ave</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.266593392816, 'Longitude': -123.003401756287}</t>
+        </is>
+      </c>
+      <c r="E1510" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:49:04</t>
+        </is>
+      </c>
+      <c r="F1510" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:31:01.089Z</t>
+        </is>
+      </c>
+      <c r="G1510" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1510" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:31:01.167Z</t>
+        </is>
+      </c>
+      <c r="I1510" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="n">
+        <v>65471</v>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>5059 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.239569143746, 'Longitude': -122.96440243721}</t>
+        </is>
+      </c>
+      <c r="E1511" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:49:04</t>
+        </is>
+      </c>
+      <c r="F1511" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:19:34.223Z</t>
+        </is>
+      </c>
+      <c r="G1511" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1511" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:32:11.629Z</t>
+        </is>
+      </c>
+      <c r="I1511" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="n">
+        <v>1669</v>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>975 Willingdon Ave</t>
+        </is>
+      </c>
+      <c r="D1512" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2758486, 'Longitude': -123.0035135}</t>
+        </is>
+      </c>
+      <c r="E1512" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:49:04</t>
+        </is>
+      </c>
+      <c r="F1512" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:28:51.214Z</t>
+        </is>
+      </c>
+      <c r="G1512" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1512" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:28:51.246Z</t>
+        </is>
+      </c>
+      <c r="I1512" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="n">
+        <v>65479</v>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>4505 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1513" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.255159438214, 'Longitude': -123.003401756287}</t>
+        </is>
+      </c>
+      <c r="E1513" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:49:04</t>
+        </is>
+      </c>
+      <c r="F1513" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:10:51.331Z</t>
+        </is>
+      </c>
+      <c r="G1513" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1513" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:10:51.378Z</t>
+        </is>
+      </c>
+      <c r="I1513" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="n">
+        <v>69963</v>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>4487 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1514" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.255044, 'Longitude': -123.0046907}</t>
+        </is>
+      </c>
+      <c r="E1514" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:49:04</t>
+        </is>
+      </c>
+      <c r="F1514" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:32:44.949Z</t>
+        </is>
+      </c>
+      <c r="G1514" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1514" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:10:38.822Z</t>
+        </is>
+      </c>
+      <c r="I1514" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="n">
+        <v>65466</v>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>4507 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D1515" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2812235, 'Longitude': -123.0025696}</t>
+        </is>
+      </c>
+      <c r="E1515" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:49:04</t>
+        </is>
+      </c>
+      <c r="F1515" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:28:44.929Z</t>
+        </is>
+      </c>
+      <c r="G1515" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1515" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:28:44.960Z</t>
+        </is>
+      </c>
+      <c r="I1515" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="n">
+        <v>65475</v>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>3826 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1516" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2544887, 'Longitude': -123.0193605}</t>
+        </is>
+      </c>
+      <c r="E1516" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:49:04</t>
+        </is>
+      </c>
+      <c r="F1516" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:58:50.738Z</t>
+        </is>
+      </c>
+      <c r="G1516" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1516" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:58:50.785Z</t>
+        </is>
+      </c>
+      <c r="I1516" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="n">
+        <v>39293</v>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>3030 Boundary Rd</t>
+        </is>
+      </c>
+      <c r="D1517" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2567447, 'Longitude': -123.0230847}</t>
+        </is>
+      </c>
+      <c r="E1517" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:49:04</t>
+        </is>
+      </c>
+      <c r="F1517" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:33:06.790Z</t>
+        </is>
+      </c>
+      <c r="G1517" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H1517" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:57:46.557Z</t>
+        </is>
+      </c>
+      <c r="I1517" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="n">
+        <v>119589</v>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>Smart Gas</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>6869 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1518" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226505740129, 'Longitude': -122.944511175156}</t>
+        </is>
+      </c>
+      <c r="E1518" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:49:04</t>
+        </is>
+      </c>
+      <c r="F1518" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:03.684Z</t>
+        </is>
+      </c>
+      <c r="G1518" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1518" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:03.731Z</t>
+        </is>
+      </c>
+      <c r="I1518" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="n">
+        <v>124671</v>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>3505 Grandview Hwy</t>
+        </is>
+      </c>
+      <c r="D1519" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2585701, 'Longitude': -123.0281066}</t>
+        </is>
+      </c>
+      <c r="E1519" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:49:04</t>
+        </is>
+      </c>
+      <c r="F1519" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:51:07.379Z</t>
+        </is>
+      </c>
+      <c r="G1519" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1519" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:53:59.992Z</t>
+        </is>
+      </c>
+      <c r="I1519" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="n">
+        <v>65474</v>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>7274 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1520" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2244118, 'Longitude': -122.9410264}</t>
+        </is>
+      </c>
+      <c r="E1520" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:49:04</t>
+        </is>
+      </c>
+      <c r="F1520" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:41:39.387Z</t>
+        </is>
+      </c>
+      <c r="G1520" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1520" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:59.321Z</t>
+        </is>
+      </c>
+      <c r="I1520" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="n">
+        <v>5768</v>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>5009 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1521" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2264629, 'Longitude': -122.992576}</t>
+        </is>
+      </c>
+      <c r="E1521" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:49:04</t>
+        </is>
+      </c>
+      <c r="F1521" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:29:04.349Z</t>
+        </is>
+      </c>
+      <c r="G1521" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1521" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:12:00.421Z</t>
+        </is>
+      </c>
+      <c r="I1521" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>65480</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>6591 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1522" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21925095319, 'Longitude': -122.968211174011}</t>
+        </is>
+      </c>
+      <c r="E1522" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:51:38</t>
+        </is>
+      </c>
+      <c r="F1522" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:37:33.570Z</t>
+        </is>
+      </c>
+      <c r="G1522" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H1522" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:25:44.411Z</t>
+        </is>
+      </c>
+      <c r="I1522" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>65467</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>6138 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1523" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2201556, 'Longitude': -122.9743751}</t>
+        </is>
+      </c>
+      <c r="E1523" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:51:38</t>
+        </is>
+      </c>
+      <c r="F1523" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:37:31.647Z</t>
+        </is>
+      </c>
+      <c r="G1523" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1523" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:56:58.102Z</t>
+        </is>
+      </c>
+      <c r="I1523" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>119589</t>
+        </is>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>Smart Gas</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>6869 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1524" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226505740129, 'Longitude': -122.944511175156}</t>
+        </is>
+      </c>
+      <c r="E1524" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:51:38</t>
+        </is>
+      </c>
+      <c r="F1524" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:03.684Z</t>
+        </is>
+      </c>
+      <c r="G1524" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1524" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:03.731Z</t>
+        </is>
+      </c>
+      <c r="I1524" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>65474</t>
+        </is>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>7274 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1525" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2244118, 'Longitude': -122.9410264}</t>
+        </is>
+      </c>
+      <c r="E1525" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:51:38</t>
+        </is>
+      </c>
+      <c r="F1525" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:41:39.387Z</t>
+        </is>
+      </c>
+      <c r="G1525" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1525" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:59.321Z</t>
+        </is>
+      </c>
+      <c r="I1525" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>87633</t>
+        </is>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>5608 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1526" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.222913, 'Longitude': -122.982433}</t>
+        </is>
+      </c>
+      <c r="E1526" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:51:38</t>
+        </is>
+      </c>
+      <c r="F1526" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:35:44.530Z</t>
+        </is>
+      </c>
+      <c r="G1526" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H1526" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:48:12.771Z</t>
+        </is>
+      </c>
+      <c r="I1526" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>65481</t>
+        </is>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>7377 6th St</t>
+        </is>
+      </c>
+      <c r="D1527" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.225214157435, 'Longitude': -122.935831546783}</t>
+        </is>
+      </c>
+      <c r="E1527" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:51:38</t>
+        </is>
+      </c>
+      <c r="F1527" t="inlineStr">
+        <is>
+          <t>2025-08-21T09:32:01.896Z</t>
+        </is>
+      </c>
+      <c r="G1527" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H1527" t="inlineStr">
+        <is>
+          <t>2025-08-21T09:31:40.802Z</t>
+        </is>
+      </c>
+      <c r="I1527" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>65477</t>
+        </is>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>7890 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1528" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.217246706543, 'Longitude': -122.931432723999}</t>
+        </is>
+      </c>
+      <c r="E1528" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:51:38</t>
+        </is>
+      </c>
+      <c r="F1528" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:38:11.932Z</t>
+        </is>
+      </c>
+      <c r="G1528" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1528" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:38:12.010Z</t>
+        </is>
+      </c>
+      <c r="I1528" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>65468</t>
+        </is>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>7587 Royal Oak Ave</t>
+        </is>
+      </c>
+      <c r="D1529" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2151443, 'Longitude': -122.9890903}</t>
+        </is>
+      </c>
+      <c r="E1529" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:51:38</t>
+        </is>
+      </c>
+      <c r="F1529" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:38:45.754Z</t>
+        </is>
+      </c>
+      <c r="G1529" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1529" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:05:59.185Z</t>
+        </is>
+      </c>
+      <c r="I1529" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>65471</t>
+        </is>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1530" t="inlineStr">
+        <is>
+          <t>5059 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1530" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.239569143746, 'Longitude': -122.96440243721}</t>
+        </is>
+      </c>
+      <c r="E1530" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:51:38</t>
+        </is>
+      </c>
+      <c r="F1530" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:19:34.223Z</t>
+        </is>
+      </c>
+      <c r="G1530" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1530" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:32:11.629Z</t>
+        </is>
+      </c>
+      <c r="I1530" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>5768</t>
+        </is>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>5009 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1531" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2264629, 'Longitude': -122.992576}</t>
+        </is>
+      </c>
+      <c r="E1531" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:51:38</t>
+        </is>
+      </c>
+      <c r="F1531" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:29:04.349Z</t>
+        </is>
+      </c>
+      <c r="G1531" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1531" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:12:00.421Z</t>
+        </is>
+      </c>
+      <c r="I1531" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>111740</t>
+        </is>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>780 6th St</t>
+        </is>
+      </c>
+      <c r="D1532" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21557, 'Longitude': -122.92387}</t>
+        </is>
+      </c>
+      <c r="E1532" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:51:38</t>
+        </is>
+      </c>
+      <c r="F1532" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:37:54.809Z</t>
+        </is>
+      </c>
+      <c r="G1532" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1532" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:37:54.856Z</t>
+        </is>
+      </c>
+      <c r="I1532" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>65469</t>
+        </is>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>4692 Imperial St</t>
+        </is>
+      </c>
+      <c r="D1533" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2217244, 'Longitude': -122.9980797}</t>
+        </is>
+      </c>
+      <c r="E1533" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:51:38</t>
+        </is>
+      </c>
+      <c r="F1533" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:16:38.363Z</t>
+        </is>
+      </c>
+      <c r="G1533" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1533" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:58:12.777Z</t>
+        </is>
+      </c>
+      <c r="I1533" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>65499</t>
+        </is>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>736 Sixth Ave</t>
+        </is>
+      </c>
+      <c r="D1534" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21129, 'Longitude': -122.92333}</t>
+        </is>
+      </c>
+      <c r="E1534" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:51:38</t>
+        </is>
+      </c>
+      <c r="F1534" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:30.175Z</t>
+        </is>
+      </c>
+      <c r="G1534" t="n">
+        <v>164.6</v>
+      </c>
+      <c r="H1534" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:30.222Z</t>
+        </is>
+      </c>
+      <c r="I1534" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>65497</t>
+        </is>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>428 Sixth St</t>
+        </is>
+      </c>
+      <c r="D1535" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2109656, 'Longitude': -122.9179526}</t>
+        </is>
+      </c>
+      <c r="E1535" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:51:38</t>
+        </is>
+      </c>
+      <c r="F1535" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:25:12.088Z</t>
+        </is>
+      </c>
+      <c r="G1535" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1535" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:25:12.166Z</t>
+        </is>
+      </c>
+      <c r="I1535" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>32350</t>
+        </is>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1536" t="inlineStr">
+        <is>
+          <t>132 12th St</t>
+        </is>
+      </c>
+      <c r="D1536" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.201144, 'Longitude': -122.922922}</t>
+        </is>
+      </c>
+      <c r="E1536" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:51:38</t>
+        </is>
+      </c>
+      <c r="F1536" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:38:14.677Z</t>
+        </is>
+      </c>
+      <c r="G1536" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1536" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:38:14.709Z</t>
+        </is>
+      </c>
+      <c r="I1536" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>65502</t>
+        </is>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>5 W 8th Ave</t>
+        </is>
+      </c>
+      <c r="D1537" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.222332, 'Longitude': -122.91267}</t>
+        </is>
+      </c>
+      <c r="E1537" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:51:38</t>
+        </is>
+      </c>
+      <c r="F1537" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:20:57.796Z</t>
+        </is>
+      </c>
+      <c r="G1537" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1537" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:44:49.538Z</t>
+        </is>
+      </c>
+      <c r="I1537" t="n">
+        <v>199.9</v>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>65498</t>
+        </is>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1538" t="inlineStr">
+        <is>
+          <t>3 E 8th Ave</t>
+        </is>
+      </c>
+      <c r="D1538" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2228942, 'Longitude': -122.9117512}</t>
+        </is>
+      </c>
+      <c r="E1538" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:51:38</t>
+        </is>
+      </c>
+      <c r="F1538" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:20:59.978Z</t>
+        </is>
+      </c>
+      <c r="G1538" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1538" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:16:11.660Z</t>
+        </is>
+      </c>
+      <c r="I1538" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>65470</t>
+        </is>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1539" t="inlineStr">
+        <is>
+          <t>4444 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1539" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.23030428362, 'Longitude': -123.006110787392}</t>
+        </is>
+      </c>
+      <c r="E1539" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:51:38</t>
+        </is>
+      </c>
+      <c r="F1539" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:31:41.284Z</t>
+        </is>
+      </c>
+      <c r="G1539" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1539" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:30:13.104Z</t>
+        </is>
+      </c>
+      <c r="I1539" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>212356</t>
+        </is>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>CENTEX</t>
+        </is>
+      </c>
+      <c r="C1540" t="inlineStr">
+        <is>
+          <t>3855 Douglas Rd</t>
+        </is>
+      </c>
+      <c r="D1540" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249718360686, 'Longitude': -122.981165650914}</t>
+        </is>
+      </c>
+      <c r="E1540" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:51:38</t>
+        </is>
+      </c>
+      <c r="F1540" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:29:32.947Z</t>
+        </is>
+      </c>
+      <c r="G1540" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1540" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:30:32.371Z</t>
+        </is>
+      </c>
+      <c r="I1540" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>99601</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1541" t="inlineStr">
+        <is>
+          <t>4177 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1541" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.232536959292, 'Longitude': -123.011408150196}</t>
+        </is>
+      </c>
+      <c r="E1541" t="inlineStr">
+        <is>
+          <t>2025-08-21 02:51:38</t>
+        </is>
+      </c>
+      <c r="F1541" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:41:22.828Z</t>
+        </is>
+      </c>
+      <c r="G1541" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1541" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:41:22.891Z</t>
+        </is>
+      </c>
+      <c r="I1541" t="n">
+        <v>191.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/gas_prices.xlsx
+++ b/data/gas_prices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1541"/>
+  <dimension ref="A1:I1701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60984,10 +60984,8 @@
       </c>
     </row>
     <row r="1522">
-      <c r="A1522" t="inlineStr">
-        <is>
-          <t>65480</t>
-        </is>
+      <c r="A1522" t="n">
+        <v>65480</v>
       </c>
       <c r="B1522" t="inlineStr">
         <is>
@@ -61027,10 +61025,8 @@
       </c>
     </row>
     <row r="1523">
-      <c r="A1523" t="inlineStr">
-        <is>
-          <t>65467</t>
-        </is>
+      <c r="A1523" t="n">
+        <v>65467</v>
       </c>
       <c r="B1523" t="inlineStr">
         <is>
@@ -61070,10 +61066,8 @@
       </c>
     </row>
     <row r="1524">
-      <c r="A1524" t="inlineStr">
-        <is>
-          <t>119589</t>
-        </is>
+      <c r="A1524" t="n">
+        <v>119589</v>
       </c>
       <c r="B1524" t="inlineStr">
         <is>
@@ -61113,10 +61107,8 @@
       </c>
     </row>
     <row r="1525">
-      <c r="A1525" t="inlineStr">
-        <is>
-          <t>65474</t>
-        </is>
+      <c r="A1525" t="n">
+        <v>65474</v>
       </c>
       <c r="B1525" t="inlineStr">
         <is>
@@ -61156,10 +61148,8 @@
       </c>
     </row>
     <row r="1526">
-      <c r="A1526" t="inlineStr">
-        <is>
-          <t>87633</t>
-        </is>
+      <c r="A1526" t="n">
+        <v>87633</v>
       </c>
       <c r="B1526" t="inlineStr">
         <is>
@@ -61199,10 +61189,8 @@
       </c>
     </row>
     <row r="1527">
-      <c r="A1527" t="inlineStr">
-        <is>
-          <t>65481</t>
-        </is>
+      <c r="A1527" t="n">
+        <v>65481</v>
       </c>
       <c r="B1527" t="inlineStr">
         <is>
@@ -61242,10 +61230,8 @@
       </c>
     </row>
     <row r="1528">
-      <c r="A1528" t="inlineStr">
-        <is>
-          <t>65477</t>
-        </is>
+      <c r="A1528" t="n">
+        <v>65477</v>
       </c>
       <c r="B1528" t="inlineStr">
         <is>
@@ -61285,10 +61271,8 @@
       </c>
     </row>
     <row r="1529">
-      <c r="A1529" t="inlineStr">
-        <is>
-          <t>65468</t>
-        </is>
+      <c r="A1529" t="n">
+        <v>65468</v>
       </c>
       <c r="B1529" t="inlineStr">
         <is>
@@ -61328,10 +61312,8 @@
       </c>
     </row>
     <row r="1530">
-      <c r="A1530" t="inlineStr">
-        <is>
-          <t>65471</t>
-        </is>
+      <c r="A1530" t="n">
+        <v>65471</v>
       </c>
       <c r="B1530" t="inlineStr">
         <is>
@@ -61371,10 +61353,8 @@
       </c>
     </row>
     <row r="1531">
-      <c r="A1531" t="inlineStr">
-        <is>
-          <t>5768</t>
-        </is>
+      <c r="A1531" t="n">
+        <v>5768</v>
       </c>
       <c r="B1531" t="inlineStr">
         <is>
@@ -61414,10 +61394,8 @@
       </c>
     </row>
     <row r="1532">
-      <c r="A1532" t="inlineStr">
-        <is>
-          <t>111740</t>
-        </is>
+      <c r="A1532" t="n">
+        <v>111740</v>
       </c>
       <c r="B1532" t="inlineStr">
         <is>
@@ -61457,10 +61435,8 @@
       </c>
     </row>
     <row r="1533">
-      <c r="A1533" t="inlineStr">
-        <is>
-          <t>65469</t>
-        </is>
+      <c r="A1533" t="n">
+        <v>65469</v>
       </c>
       <c r="B1533" t="inlineStr">
         <is>
@@ -61500,10 +61476,8 @@
       </c>
     </row>
     <row r="1534">
-      <c r="A1534" t="inlineStr">
-        <is>
-          <t>65499</t>
-        </is>
+      <c r="A1534" t="n">
+        <v>65499</v>
       </c>
       <c r="B1534" t="inlineStr">
         <is>
@@ -61543,10 +61517,8 @@
       </c>
     </row>
     <row r="1535">
-      <c r="A1535" t="inlineStr">
-        <is>
-          <t>65497</t>
-        </is>
+      <c r="A1535" t="n">
+        <v>65497</v>
       </c>
       <c r="B1535" t="inlineStr">
         <is>
@@ -61586,10 +61558,8 @@
       </c>
     </row>
     <row r="1536">
-      <c r="A1536" t="inlineStr">
-        <is>
-          <t>32350</t>
-        </is>
+      <c r="A1536" t="n">
+        <v>32350</v>
       </c>
       <c r="B1536" t="inlineStr">
         <is>
@@ -61629,10 +61599,8 @@
       </c>
     </row>
     <row r="1537">
-      <c r="A1537" t="inlineStr">
-        <is>
-          <t>65502</t>
-        </is>
+      <c r="A1537" t="n">
+        <v>65502</v>
       </c>
       <c r="B1537" t="inlineStr">
         <is>
@@ -61672,10 +61640,8 @@
       </c>
     </row>
     <row r="1538">
-      <c r="A1538" t="inlineStr">
-        <is>
-          <t>65498</t>
-        </is>
+      <c r="A1538" t="n">
+        <v>65498</v>
       </c>
       <c r="B1538" t="inlineStr">
         <is>
@@ -61715,10 +61681,8 @@
       </c>
     </row>
     <row r="1539">
-      <c r="A1539" t="inlineStr">
-        <is>
-          <t>65470</t>
-        </is>
+      <c r="A1539" t="n">
+        <v>65470</v>
       </c>
       <c r="B1539" t="inlineStr">
         <is>
@@ -61758,10 +61722,8 @@
       </c>
     </row>
     <row r="1540">
-      <c r="A1540" t="inlineStr">
-        <is>
-          <t>212356</t>
-        </is>
+      <c r="A1540" t="n">
+        <v>212356</v>
       </c>
       <c r="B1540" t="inlineStr">
         <is>
@@ -61801,10 +61763,8 @@
       </c>
     </row>
     <row r="1541">
-      <c r="A1541" t="inlineStr">
-        <is>
-          <t>99601</t>
-        </is>
+      <c r="A1541" t="n">
+        <v>99601</v>
       </c>
       <c r="B1541" t="inlineStr">
         <is>
@@ -61840,6 +61800,6502 @@
         </is>
       </c>
       <c r="I1541" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="n">
+        <v>65542</v>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1542" t="inlineStr">
+        <is>
+          <t>3250 MacDonald St</t>
+        </is>
+      </c>
+      <c r="D1542" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2573819, 'Longitude': -123.1680407}</t>
+        </is>
+      </c>
+      <c r="E1542" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:06:12</t>
+        </is>
+      </c>
+      <c r="F1542" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:37:56.487Z</t>
+        </is>
+      </c>
+      <c r="G1542" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1542" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:37:56.532Z</t>
+        </is>
+      </c>
+      <c r="I1542" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="n">
+        <v>65533</v>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1543" t="inlineStr">
+        <is>
+          <t>4615 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D1543" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2449719, 'Longitude': -123.1540385}</t>
+        </is>
+      </c>
+      <c r="E1543" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:06:12</t>
+        </is>
+      </c>
+      <c r="F1543" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:14:33.406Z</t>
+        </is>
+      </c>
+      <c r="G1543" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1543" t="inlineStr"/>
+      <c r="I1543" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="n">
+        <v>83068</v>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1544" t="inlineStr">
+        <is>
+          <t>3205 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D1544" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.256927568207, 'Longitude': -123.153288960457}</t>
+        </is>
+      </c>
+      <c r="E1544" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:06:12</t>
+        </is>
+      </c>
+      <c r="F1544" t="inlineStr"/>
+      <c r="G1544" t="inlineStr"/>
+      <c r="H1544" t="inlineStr"/>
+      <c r="I1544" t="inlineStr"/>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="n">
+        <v>65562</v>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1545" t="inlineStr">
+        <is>
+          <t>2808 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1545" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263883932125, 'Longitude': -123.168604373932}</t>
+        </is>
+      </c>
+      <c r="E1545" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:06:12</t>
+        </is>
+      </c>
+      <c r="F1545" t="inlineStr">
+        <is>
+          <t>2025-08-21T12:34:16.278Z</t>
+        </is>
+      </c>
+      <c r="G1545" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1545" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:17:36.405Z</t>
+        </is>
+      </c>
+      <c r="I1545" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="n">
+        <v>113305</v>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1546" t="inlineStr">
+        <is>
+          <t>3596 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1546" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234385296079, 'Longitude': -123.184762001038}</t>
+        </is>
+      </c>
+      <c r="E1546" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:06:12</t>
+        </is>
+      </c>
+      <c r="F1546" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:30:03.056Z</t>
+        </is>
+      </c>
+      <c r="G1546" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1546" t="inlineStr"/>
+      <c r="I1546" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1547" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1547" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E1547" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:06:12</t>
+        </is>
+      </c>
+      <c r="F1547" t="inlineStr">
+        <is>
+          <t>2025-08-21T12:33:20.103Z</t>
+        </is>
+      </c>
+      <c r="G1547" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1547" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:16:34.188Z</t>
+        </is>
+      </c>
+      <c r="I1547" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="n">
+        <v>65554</v>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1548" t="inlineStr">
+        <is>
+          <t>1795 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1548" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264037962303, 'Longitude': -123.145408630371}</t>
+        </is>
+      </c>
+      <c r="E1548" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:06:12</t>
+        </is>
+      </c>
+      <c r="F1548" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:01:33.530Z</t>
+        </is>
+      </c>
+      <c r="G1548" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1548" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:31:16.269Z</t>
+        </is>
+      </c>
+      <c r="I1548" t="n">
+        <v>199.3</v>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="n">
+        <v>65571</v>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1549" t="inlineStr">
+        <is>
+          <t>4314 W 10th Ave</t>
+        </is>
+      </c>
+      <c r="D1549" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263533861752, 'Longitude': -123.203430175781}</t>
+        </is>
+      </c>
+      <c r="E1549" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:06:12</t>
+        </is>
+      </c>
+      <c r="F1549" t="inlineStr">
+        <is>
+          <t>2025-08-21T12:37:45.764Z</t>
+        </is>
+      </c>
+      <c r="G1549" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1549" t="inlineStr">
+        <is>
+          <t>2025-08-19T16:29:09.259Z</t>
+        </is>
+      </c>
+      <c r="I1549" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1550" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D1550" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E1550" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:06:12</t>
+        </is>
+      </c>
+      <c r="F1550" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:39:55.743Z</t>
+        </is>
+      </c>
+      <c r="G1550" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1550" t="inlineStr"/>
+      <c r="I1550" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="n">
+        <v>32376</v>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1551" t="inlineStr">
+        <is>
+          <t>1503 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1551" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234634576953, 'Longitude': -123.139971792698}</t>
+        </is>
+      </c>
+      <c r="E1551" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:06:12</t>
+        </is>
+      </c>
+      <c r="F1551" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:23:03.529Z</t>
+        </is>
+      </c>
+      <c r="G1551" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1551" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:30:08.915Z</t>
+        </is>
+      </c>
+      <c r="I1551" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="n">
+        <v>65549</v>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1552" t="inlineStr">
+        <is>
+          <t>5702 Granville St</t>
+        </is>
+      </c>
+      <c r="D1552" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234036184118, 'Longitude': -123.139244914055}</t>
+        </is>
+      </c>
+      <c r="E1552" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:06:12</t>
+        </is>
+      </c>
+      <c r="F1552" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:22:50.613Z</t>
+        </is>
+      </c>
+      <c r="G1552" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1552" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:16:56.895Z</t>
+        </is>
+      </c>
+      <c r="I1552" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1553" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E1553" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:06:12</t>
+        </is>
+      </c>
+      <c r="F1553" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:59:10.061Z</t>
+        </is>
+      </c>
+      <c r="G1553" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1553" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:22.999Z</t>
+        </is>
+      </c>
+      <c r="I1553" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1554" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E1554" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:06:12</t>
+        </is>
+      </c>
+      <c r="F1554" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:59:15.632Z</t>
+        </is>
+      </c>
+      <c r="G1554" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1554" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:11.555Z</t>
+        </is>
+      </c>
+      <c r="I1554" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="n">
+        <v>72747</v>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t>1010 W King Edward Ave</t>
+        </is>
+      </c>
+      <c r="D1555" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249188, 'Longitude': -123.127767}</t>
+        </is>
+      </c>
+      <c r="E1555" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:06:12</t>
+        </is>
+      </c>
+      <c r="F1555" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:52:26.701Z</t>
+        </is>
+      </c>
+      <c r="G1555" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1555" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:43:58.867Z</t>
+        </is>
+      </c>
+      <c r="I1555" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="n">
+        <v>32375</v>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>4110 Oak St</t>
+        </is>
+      </c>
+      <c r="D1556" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.24894071957, 'Longitude': -123.127040863037}</t>
+        </is>
+      </c>
+      <c r="E1556" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:06:12</t>
+        </is>
+      </c>
+      <c r="F1556" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:52:22.489Z</t>
+        </is>
+      </c>
+      <c r="G1556" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1556" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:13:19.073Z</t>
+        </is>
+      </c>
+      <c r="I1556" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="n">
+        <v>65564</v>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1557" t="inlineStr">
+        <is>
+          <t>5680 Oak St</t>
+        </is>
+      </c>
+      <c r="D1557" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234217162181, 'Longitude': -123.127684593201}</t>
+        </is>
+      </c>
+      <c r="E1557" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:06:12</t>
+        </is>
+      </c>
+      <c r="F1557" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:49:01.067Z</t>
+        </is>
+      </c>
+      <c r="G1557" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1557" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:37:38.272Z</t>
+        </is>
+      </c>
+      <c r="I1557" t="n">
+        <v>198.9</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="n">
+        <v>32372</v>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1558" t="inlineStr">
+        <is>
+          <t>6525 Oak St</t>
+        </is>
+      </c>
+      <c r="D1558" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226226639452, 'Longitude': -123.128687739372}</t>
+        </is>
+      </c>
+      <c r="E1558" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:06:12</t>
+        </is>
+      </c>
+      <c r="F1558" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:35:35.977Z</t>
+        </is>
+      </c>
+      <c r="G1558" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1558" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:33:23.261Z</t>
+        </is>
+      </c>
+      <c r="I1558" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1559" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1559" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E1559" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:06:12</t>
+        </is>
+      </c>
+      <c r="F1559" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:53:46.947Z</t>
+        </is>
+      </c>
+      <c r="G1559" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1559" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:44:27.069Z</t>
+        </is>
+      </c>
+      <c r="I1559" t="n">
+        <v>199.9</v>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="n">
+        <v>65566</v>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>8072 Granville St</t>
+        </is>
+      </c>
+      <c r="D1560" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.212495055855, 'Longitude': -123.14013004303}</t>
+        </is>
+      </c>
+      <c r="E1560" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:06:12</t>
+        </is>
+      </c>
+      <c r="F1560" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:15:06.805Z</t>
+        </is>
+      </c>
+      <c r="G1560" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1560" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:30:08.359Z</t>
+        </is>
+      </c>
+      <c r="I1560" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="n">
+        <v>65572</v>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D1561" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E1561" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:06:12</t>
+        </is>
+      </c>
+      <c r="F1561" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:03:02.518Z</t>
+        </is>
+      </c>
+      <c r="G1561" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1561" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:12:12.232Z</t>
+        </is>
+      </c>
+      <c r="I1561" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="n">
+        <v>65558</v>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>1390 E 33rd Ave</t>
+        </is>
+      </c>
+      <c r="D1562" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.240045470021, 'Longitude': -123.076765537262}</t>
+        </is>
+      </c>
+      <c r="E1562" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:08:39</t>
+        </is>
+      </c>
+      <c r="F1562" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:19:17.439Z</t>
+        </is>
+      </c>
+      <c r="G1562" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H1562" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:19:17.486Z</t>
+        </is>
+      </c>
+      <c r="I1562" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="n">
+        <v>83394</v>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>4064 Fraser St</t>
+        </is>
+      </c>
+      <c r="D1563" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.248864, 'Longitude': -123.09002}</t>
+        </is>
+      </c>
+      <c r="E1563" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:08:39</t>
+        </is>
+      </c>
+      <c r="F1563" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:34:57.523Z</t>
+        </is>
+      </c>
+      <c r="G1563" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1563" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:15:27.854Z</t>
+        </is>
+      </c>
+      <c r="I1563" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="n">
+        <v>65573</v>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1564" t="inlineStr">
+        <is>
+          <t>1396 E 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1564" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.232593005895, 'Longitude': -123.07728856802}</t>
+        </is>
+      </c>
+      <c r="E1564" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:08:39</t>
+        </is>
+      </c>
+      <c r="F1564" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:53:30.000Z</t>
+        </is>
+      </c>
+      <c r="G1564" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1564" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:28:44.531Z</t>
+        </is>
+      </c>
+      <c r="I1564" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="n">
+        <v>80714</v>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>Husky</t>
+        </is>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>4933 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1565" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2397388, 'Longitude': -123.065748}</t>
+        </is>
+      </c>
+      <c r="E1565" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:08:39</t>
+        </is>
+      </c>
+      <c r="F1565" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:03:32.237Z</t>
+        </is>
+      </c>
+      <c r="G1565" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1565" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:17:49.745Z</t>
+        </is>
+      </c>
+      <c r="I1565" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="n">
+        <v>65552</v>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>2001 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1566" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.245312771918, 'Longitude': -123.064910173416}</t>
+        </is>
+      </c>
+      <c r="E1566" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:08:39</t>
+        </is>
+      </c>
+      <c r="F1566" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:54:53.724Z</t>
+        </is>
+      </c>
+      <c r="G1566" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H1566" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:25:23.251Z</t>
+        </is>
+      </c>
+      <c r="I1566" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="n">
+        <v>65538</v>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1567" t="inlineStr">
+        <is>
+          <t>5252 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1567" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2372145, 'Longitude': -123.0650857}</t>
+        </is>
+      </c>
+      <c r="E1567" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:08:39</t>
+        </is>
+      </c>
+      <c r="F1567" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:04:13.990Z</t>
+        </is>
+      </c>
+      <c r="G1567" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1567" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:17:15.749Z</t>
+        </is>
+      </c>
+      <c r="I1567" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="n">
+        <v>90814</v>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1568" t="inlineStr">
+        <is>
+          <t>2277 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1568" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.242132845692, 'Longitude': -123.058204650879}</t>
+        </is>
+      </c>
+      <c r="E1568" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:08:39</t>
+        </is>
+      </c>
+      <c r="F1568" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:02:05.337Z</t>
+        </is>
+      </c>
+      <c r="G1568" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1568" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:17:33.155Z</t>
+        </is>
+      </c>
+      <c r="I1568" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="n">
+        <v>39768</v>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1569" t="inlineStr">
+        <is>
+          <t>5736 Main St</t>
+        </is>
+      </c>
+      <c r="D1569" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2325708, 'Longitude': -123.1010069}</t>
+        </is>
+      </c>
+      <c r="E1569" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:08:39</t>
+        </is>
+      </c>
+      <c r="F1569" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:53:26.149Z</t>
+        </is>
+      </c>
+      <c r="G1569" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1569" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:53:26.164Z</t>
+        </is>
+      </c>
+      <c r="I1569" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="n">
+        <v>9710</v>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1570" t="inlineStr">
+        <is>
+          <t>1295 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D1570" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259878978744, 'Longitude': -123.078074455261}</t>
+        </is>
+      </c>
+      <c r="E1570" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:08:39</t>
+        </is>
+      </c>
+      <c r="F1570" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:04:27.082Z</t>
+        </is>
+      </c>
+      <c r="G1570" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1570" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:16:42.500Z</t>
+        </is>
+      </c>
+      <c r="I1570" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="n">
+        <v>99146</v>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1571" t="inlineStr">
+        <is>
+          <t>1317 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D1571" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259758544957, 'Longitude': -123.077272474766}</t>
+        </is>
+      </c>
+      <c r="E1571" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:08:39</t>
+        </is>
+      </c>
+      <c r="F1571" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:04:11.246Z</t>
+        </is>
+      </c>
+      <c r="G1571" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1571" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:16:22.548Z</t>
+        </is>
+      </c>
+      <c r="I1571" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="n">
+        <v>65560</v>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1572" t="inlineStr">
+        <is>
+          <t>1289 E Broadway</t>
+        </is>
+      </c>
+      <c r="D1572" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.262693682723, 'Longitude': -123.078117370605}</t>
+        </is>
+      </c>
+      <c r="E1572" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:08:39</t>
+        </is>
+      </c>
+      <c r="F1572" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:04:18.779Z</t>
+        </is>
+      </c>
+      <c r="G1572" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1572" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:34:57.313Z</t>
+        </is>
+      </c>
+      <c r="I1572" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="n">
+        <v>65557</v>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>2120 Grandview Hwy S</t>
+        </is>
+      </c>
+      <c r="D1573" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2591601, 'Longitude': -123.0617495}</t>
+        </is>
+      </c>
+      <c r="E1573" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:08:39</t>
+        </is>
+      </c>
+      <c r="F1573" t="inlineStr">
+        <is>
+          <t>2025-08-21T11:42:13.938Z</t>
+        </is>
+      </c>
+      <c r="G1573" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H1573" t="inlineStr">
+        <is>
+          <t>2025-08-21T11:42:13.953Z</t>
+        </is>
+      </c>
+      <c r="I1573" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="n">
+        <v>65559</v>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1574" t="inlineStr">
+        <is>
+          <t>6502 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1574" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.224996944057, 'Longitude': -123.065521717072}</t>
+        </is>
+      </c>
+      <c r="E1574" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:08:39</t>
+        </is>
+      </c>
+      <c r="F1574" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:45:10.949Z</t>
+        </is>
+      </c>
+      <c r="G1574" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1574" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:06:56.250Z</t>
+        </is>
+      </c>
+      <c r="I1574" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="n">
+        <v>71502</v>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1575" t="inlineStr">
+        <is>
+          <t>2748 Main St</t>
+        </is>
+      </c>
+      <c r="D1575" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2604441, 'Longitude': -123.1005869}</t>
+        </is>
+      </c>
+      <c r="E1575" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:08:39</t>
+        </is>
+      </c>
+      <c r="F1575" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:02:56.887Z</t>
+        </is>
+      </c>
+      <c r="G1575" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1575" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:36:49.212Z</t>
+        </is>
+      </c>
+      <c r="I1575" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="n">
+        <v>89943</v>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>6808 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1576" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2220242, 'Longitude': -123.0654247}</t>
+        </is>
+      </c>
+      <c r="E1576" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:08:39</t>
+        </is>
+      </c>
+      <c r="F1576" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:51:23.033Z</t>
+        </is>
+      </c>
+      <c r="G1576" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1576" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:59:15.108Z</t>
+        </is>
+      </c>
+      <c r="I1576" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D1577" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E1577" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:08:39</t>
+        </is>
+      </c>
+      <c r="F1577" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:52:22.849Z</t>
+        </is>
+      </c>
+      <c r="G1577" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1577" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:57.027Z</t>
+        </is>
+      </c>
+      <c r="I1577" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="n">
+        <v>65537</v>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>2918 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1578" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.23608, 'Longitude': -123.0454858}</t>
+        </is>
+      </c>
+      <c r="E1578" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:08:39</t>
+        </is>
+      </c>
+      <c r="F1578" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:15:19.497Z</t>
+        </is>
+      </c>
+      <c r="G1578" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1578" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:24:44.587Z</t>
+        </is>
+      </c>
+      <c r="I1578" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D1579" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E1579" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:08:39</t>
+        </is>
+      </c>
+      <c r="F1579" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:03:53.246Z</t>
+        </is>
+      </c>
+      <c r="G1579" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1579" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:37.661Z</t>
+        </is>
+      </c>
+      <c r="I1579" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="n">
+        <v>65535</v>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>2605 E 49th Ave</t>
+        </is>
+      </c>
+      <c r="D1580" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2251291, 'Longitude': -123.0545048}</t>
+        </is>
+      </c>
+      <c r="E1580" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:08:39</t>
+        </is>
+      </c>
+      <c r="F1580" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:14:32.764Z</t>
+        </is>
+      </c>
+      <c r="G1580" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1580" t="inlineStr"/>
+      <c r="I1580" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="n">
+        <v>75425</v>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>1785 Main St</t>
+        </is>
+      </c>
+      <c r="D1581" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.26940640121, 'Longitude': -123.101197779179}</t>
+        </is>
+      </c>
+      <c r="E1581" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:08:39</t>
+        </is>
+      </c>
+      <c r="F1581" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:56:20.135Z</t>
+        </is>
+      </c>
+      <c r="G1581" t="n">
+        <v>147.9</v>
+      </c>
+      <c r="H1581" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:55:16.815Z</t>
+        </is>
+      </c>
+      <c r="I1581" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="n">
+        <v>77015</v>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1582" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169873456637, 'Longitude': -123.091178619746}</t>
+        </is>
+      </c>
+      <c r="E1582" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:11:05</t>
+        </is>
+      </c>
+      <c r="F1582" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:31:03.749Z</t>
+        </is>
+      </c>
+      <c r="G1582" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1582" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:31:01.829Z</t>
+        </is>
+      </c>
+      <c r="I1582" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="n">
+        <v>65511</v>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1583" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E1583" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:11:05</t>
+        </is>
+      </c>
+      <c r="F1583" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:42:18.239Z</t>
+        </is>
+      </c>
+      <c r="G1583" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1583" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:42:18.255Z</t>
+        </is>
+      </c>
+      <c r="I1583" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="n">
+        <v>86650</v>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D1584" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169856952787, 'Longitude': -123.123961687088}</t>
+        </is>
+      </c>
+      <c r="E1584" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:11:05</t>
+        </is>
+      </c>
+      <c r="F1584" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:40:48.792Z</t>
+        </is>
+      </c>
+      <c r="G1584" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1584" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:05:27.032Z</t>
+        </is>
+      </c>
+      <c r="I1584" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="n">
+        <v>77218</v>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D1585" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.173339635958, 'Longitude': -123.124954104424}</t>
+        </is>
+      </c>
+      <c r="E1585" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:11:05</t>
+        </is>
+      </c>
+      <c r="F1585" t="inlineStr">
+        <is>
+          <t>2025-08-21T11:19:50.747Z</t>
+        </is>
+      </c>
+      <c r="G1585" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1585" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:04:48.775Z</t>
+        </is>
+      </c>
+      <c r="I1585" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="n">
+        <v>77228</v>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D1586" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1843249, 'Longitude': -123.1236078}</t>
+        </is>
+      </c>
+      <c r="E1586" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:11:05</t>
+        </is>
+      </c>
+      <c r="F1586" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:30:05.724Z</t>
+        </is>
+      </c>
+      <c r="G1586" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1586" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:29:09.481Z</t>
+        </is>
+      </c>
+      <c r="I1586" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="n">
+        <v>83384</v>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1587" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192001, 'Longitude': -123.124004}</t>
+        </is>
+      </c>
+      <c r="E1587" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:11:05</t>
+        </is>
+      </c>
+      <c r="F1587" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:08:44.537Z</t>
+        </is>
+      </c>
+      <c r="G1587" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1587" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:11:11.242Z</t>
+        </is>
+      </c>
+      <c r="I1587" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="n">
+        <v>77202</v>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D1588" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.162989071149, 'Longitude': -123.134229183197}</t>
+        </is>
+      </c>
+      <c r="E1588" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:11:05</t>
+        </is>
+      </c>
+      <c r="F1588" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:39:38.885Z</t>
+        </is>
+      </c>
+      <c r="G1588" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1588" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:47:01.715Z</t>
+        </is>
+      </c>
+      <c r="I1588" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="n">
+        <v>77243</v>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D1589" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.179182137142, 'Longitude': -123.137152791023}</t>
+        </is>
+      </c>
+      <c r="E1589" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:11:05</t>
+        </is>
+      </c>
+      <c r="F1589" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:39:28.689Z</t>
+        </is>
+      </c>
+      <c r="G1589" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1589" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:55:29.368Z</t>
+        </is>
+      </c>
+      <c r="I1589" t="n">
+        <v>171.9</v>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="n">
+        <v>83387</v>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>710 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1590" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21081995506, 'Longitude': -123.090755939484}</t>
+        </is>
+      </c>
+      <c r="E1590" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:11:05</t>
+        </is>
+      </c>
+      <c r="F1590" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:00:12.464Z</t>
+        </is>
+      </c>
+      <c r="G1590" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1590" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:00:12.496Z</t>
+        </is>
+      </c>
+      <c r="I1590" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="n">
+        <v>65551</v>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1591" t="inlineStr">
+        <is>
+          <t>688 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1591" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210798928329, 'Longitude': -123.09152841568}</t>
+        </is>
+      </c>
+      <c r="E1591" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:11:05</t>
+        </is>
+      </c>
+      <c r="F1591" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:59:47.806Z</t>
+        </is>
+      </c>
+      <c r="G1591" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1591" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:59:47.832Z</t>
+        </is>
+      </c>
+      <c r="I1591" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="n">
+        <v>77235</v>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C1592" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1592" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.18409178594, 'Longitude': -123.136823830688}</t>
+        </is>
+      </c>
+      <c r="E1592" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:11:05</t>
+        </is>
+      </c>
+      <c r="F1592" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:58:49.477Z</t>
+        </is>
+      </c>
+      <c r="G1592" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1592" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:58:49.493Z</t>
+        </is>
+      </c>
+      <c r="I1592" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="n">
+        <v>82925</v>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>350 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1593" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210245, 'Longitude': -123.099328}</t>
+        </is>
+      </c>
+      <c r="E1593" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:11:05</t>
+        </is>
+      </c>
+      <c r="F1593" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:10:04.520Z</t>
+        </is>
+      </c>
+      <c r="G1593" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1593" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:59:54.798Z</t>
+        </is>
+      </c>
+      <c r="I1593" t="n">
+        <v>171.9</v>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="n">
+        <v>109205</v>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D1594" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.133556536531, 'Longitude': -123.092424273491}</t>
+        </is>
+      </c>
+      <c r="E1594" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:11:05</t>
+        </is>
+      </c>
+      <c r="F1594" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:26:36.134Z</t>
+        </is>
+      </c>
+      <c r="G1594" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1594" t="inlineStr">
+        <is>
+          <t>2025-08-21T12:22:33.803Z</t>
+        </is>
+      </c>
+      <c r="I1594" t="n">
+        <v>175.9</v>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="n">
+        <v>65540</v>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1595" t="inlineStr">
+        <is>
+          <t>196 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1595" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2106867, 'Longitude': -123.1027436}</t>
+        </is>
+      </c>
+      <c r="E1595" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:11:05</t>
+        </is>
+      </c>
+      <c r="F1595" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:09:45.288Z</t>
+        </is>
+      </c>
+      <c r="G1595" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1595" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:00:05.037Z</t>
+        </is>
+      </c>
+      <c r="I1595" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="n">
+        <v>65512</v>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1596" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1596" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1328393, 'Longitude': -123.0926312}</t>
+        </is>
+      </c>
+      <c r="E1596" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:11:05</t>
+        </is>
+      </c>
+      <c r="F1596" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:26:39.986Z</t>
+        </is>
+      </c>
+      <c r="G1596" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1596" t="inlineStr">
+        <is>
+          <t>2025-08-21T12:22:38.451Z</t>
+        </is>
+      </c>
+      <c r="I1596" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="n">
+        <v>77205</v>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1597" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1597" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1558882, 'Longitude': -123.1369625}</t>
+        </is>
+      </c>
+      <c r="E1597" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:11:05</t>
+        </is>
+      </c>
+      <c r="F1597" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:52:57.153Z</t>
+        </is>
+      </c>
+      <c r="G1597" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1597" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:09:47.598Z</t>
+        </is>
+      </c>
+      <c r="I1597" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D1598" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E1598" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:11:05</t>
+        </is>
+      </c>
+      <c r="F1598" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:03:53.246Z</t>
+        </is>
+      </c>
+      <c r="G1598" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1598" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:37.661Z</t>
+        </is>
+      </c>
+      <c r="I1598" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D1599" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E1599" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:11:05</t>
+        </is>
+      </c>
+      <c r="F1599" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:52:22.849Z</t>
+        </is>
+      </c>
+      <c r="G1599" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1599" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:57.027Z</t>
+        </is>
+      </c>
+      <c r="I1599" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="n">
+        <v>65556</v>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1600" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20806537721, 'Longitude': -123.123285770416}</t>
+        </is>
+      </c>
+      <c r="E1600" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:11:05</t>
+        </is>
+      </c>
+      <c r="F1600" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:08:32.784Z</t>
+        </is>
+      </c>
+      <c r="G1600" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1600" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:46.640Z</t>
+        </is>
+      </c>
+      <c r="I1600" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="n">
+        <v>86937</v>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>8655 Boundary Rd</t>
+        </is>
+      </c>
+      <c r="D1601" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20476, 'Longitude': -123.02398}</t>
+        </is>
+      </c>
+      <c r="E1601" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:11:05</t>
+        </is>
+      </c>
+      <c r="F1601" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:42:35.068Z</t>
+        </is>
+      </c>
+      <c r="G1601" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1601" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:06:44.227Z</t>
+        </is>
+      </c>
+      <c r="I1601" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="n">
+        <v>65515</v>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>4011 Francis Rd</t>
+        </is>
+      </c>
+      <c r="D1602" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.14867500071, 'Longitude': -123.180856704712}</t>
+        </is>
+      </c>
+      <c r="E1602" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:13:17</t>
+        </is>
+      </c>
+      <c r="F1602" t="inlineStr">
+        <is>
+          <t>2025-08-21T11:09:15.092Z</t>
+        </is>
+      </c>
+      <c r="G1602" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1602" t="inlineStr">
+        <is>
+          <t>2025-08-21T11:09:15.123Z</t>
+        </is>
+      </c>
+      <c r="I1602" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="n">
+        <v>77205</v>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1603" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1558882, 'Longitude': -123.1369625}</t>
+        </is>
+      </c>
+      <c r="E1603" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:13:17</t>
+        </is>
+      </c>
+      <c r="F1603" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:52:57.153Z</t>
+        </is>
+      </c>
+      <c r="G1603" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1603" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:09:47.598Z</t>
+        </is>
+      </c>
+      <c r="I1603" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="n">
+        <v>77223</v>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>7991 No 1 Rd</t>
+        </is>
+      </c>
+      <c r="D1604" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.155888686563, 'Longitude': -123.181414604187}</t>
+        </is>
+      </c>
+      <c r="E1604" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:13:17</t>
+        </is>
+      </c>
+      <c r="F1604" t="inlineStr"/>
+      <c r="G1604" t="inlineStr"/>
+      <c r="H1604" t="inlineStr"/>
+      <c r="I1604" t="inlineStr"/>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="n">
+        <v>65514</v>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>7980 Williams Rd</t>
+        </is>
+      </c>
+      <c r="D1605" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.140582914547, 'Longitude': -123.137168884277}</t>
+        </is>
+      </c>
+      <c r="E1605" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:13:17</t>
+        </is>
+      </c>
+      <c r="F1605" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:23:11.584Z</t>
+        </is>
+      </c>
+      <c r="G1605" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1605" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:04:20.233Z</t>
+        </is>
+      </c>
+      <c r="I1605" t="n">
+        <v>175.9</v>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="n">
+        <v>77232</v>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900 Westminster Hwy </t>
+        </is>
+      </c>
+      <c r="D1606" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1698419, 'Longitude': -123.159282}</t>
+        </is>
+      </c>
+      <c r="E1606" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:13:17</t>
+        </is>
+      </c>
+      <c r="F1606" t="inlineStr">
+        <is>
+          <t>2025-08-21T11:15:53.866Z</t>
+        </is>
+      </c>
+      <c r="G1606" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1606" t="inlineStr">
+        <is>
+          <t>2025-08-21T11:15:53.929Z</t>
+        </is>
+      </c>
+      <c r="I1606" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="n">
+        <v>77202</v>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D1607" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.162989071149, 'Longitude': -123.134229183197}</t>
+        </is>
+      </c>
+      <c r="E1607" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:13:17</t>
+        </is>
+      </c>
+      <c r="F1607" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:39:38.885Z</t>
+        </is>
+      </c>
+      <c r="G1607" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1607" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:47:01.715Z</t>
+        </is>
+      </c>
+      <c r="I1607" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="n">
+        <v>86650</v>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D1608" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169856952787, 'Longitude': -123.123961687088}</t>
+        </is>
+      </c>
+      <c r="E1608" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:13:17</t>
+        </is>
+      </c>
+      <c r="F1608" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:40:48.792Z</t>
+        </is>
+      </c>
+      <c r="G1608" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1608" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:05:27.032Z</t>
+        </is>
+      </c>
+      <c r="I1608" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="n">
+        <v>77218</v>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D1609" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.173339635958, 'Longitude': -123.124954104424}</t>
+        </is>
+      </c>
+      <c r="E1609" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:13:17</t>
+        </is>
+      </c>
+      <c r="F1609" t="inlineStr">
+        <is>
+          <t>2025-08-21T11:19:50.747Z</t>
+        </is>
+      </c>
+      <c r="G1609" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1609" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:04:48.775Z</t>
+        </is>
+      </c>
+      <c r="I1609" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="n">
+        <v>77243</v>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D1610" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.179182137142, 'Longitude': -123.137152791023}</t>
+        </is>
+      </c>
+      <c r="E1610" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:13:17</t>
+        </is>
+      </c>
+      <c r="F1610" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:39:28.689Z</t>
+        </is>
+      </c>
+      <c r="G1610" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1610" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:55:29.368Z</t>
+        </is>
+      </c>
+      <c r="I1610" t="n">
+        <v>171.9</v>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="n">
+        <v>77235</v>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1611" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.18409178594, 'Longitude': -123.136823830688}</t>
+        </is>
+      </c>
+      <c r="E1611" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:13:17</t>
+        </is>
+      </c>
+      <c r="F1611" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:58:49.477Z</t>
+        </is>
+      </c>
+      <c r="G1611" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1611" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:58:49.493Z</t>
+        </is>
+      </c>
+      <c r="I1611" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="n">
+        <v>77228</v>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1612" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D1612" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1843249, 'Longitude': -123.1236078}</t>
+        </is>
+      </c>
+      <c r="E1612" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:13:17</t>
+        </is>
+      </c>
+      <c r="F1612" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:30:05.724Z</t>
+        </is>
+      </c>
+      <c r="G1612" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1612" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:29:09.481Z</t>
+        </is>
+      </c>
+      <c r="I1612" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="n">
+        <v>69163</v>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>5111 Grant McConachie Way</t>
+        </is>
+      </c>
+      <c r="D1613" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192919, 'Longitude': -123.166797}</t>
+        </is>
+      </c>
+      <c r="E1613" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:13:17</t>
+        </is>
+      </c>
+      <c r="F1613" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:04:38.760Z</t>
+        </is>
+      </c>
+      <c r="G1613" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1613" t="inlineStr">
+        <is>
+          <t>2025-08-21T11:23:53.653Z</t>
+        </is>
+      </c>
+      <c r="I1613" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="n">
+        <v>109205</v>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1614" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D1614" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.133556536531, 'Longitude': -123.092424273491}</t>
+        </is>
+      </c>
+      <c r="E1614" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:13:17</t>
+        </is>
+      </c>
+      <c r="F1614" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:11:34.348Z</t>
+        </is>
+      </c>
+      <c r="G1614" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1614" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:11:34.394Z</t>
+        </is>
+      </c>
+      <c r="I1614" t="n">
+        <v>175.9</v>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="n">
+        <v>65512</v>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1615" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1615" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1328393, 'Longitude': -123.0926312}</t>
+        </is>
+      </c>
+      <c r="E1615" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:13:17</t>
+        </is>
+      </c>
+      <c r="F1615" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:11:43.494Z</t>
+        </is>
+      </c>
+      <c r="G1615" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1615" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:11:43.509Z</t>
+        </is>
+      </c>
+      <c r="I1615" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="n">
+        <v>83384</v>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1616" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1616" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192001, 'Longitude': -123.124004}</t>
+        </is>
+      </c>
+      <c r="E1616" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:13:17</t>
+        </is>
+      </c>
+      <c r="F1616" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:08:44.537Z</t>
+        </is>
+      </c>
+      <c r="G1616" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1616" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:11:11.242Z</t>
+        </is>
+      </c>
+      <c r="I1616" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="n">
+        <v>77015</v>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1617" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1617" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169873456637, 'Longitude': -123.091178619746}</t>
+        </is>
+      </c>
+      <c r="E1617" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:13:17</t>
+        </is>
+      </c>
+      <c r="F1617" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:31:03.749Z</t>
+        </is>
+      </c>
+      <c r="G1617" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1617" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:31:01.829Z</t>
+        </is>
+      </c>
+      <c r="I1617" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="n">
+        <v>107728</v>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1618" t="inlineStr">
+        <is>
+          <t>8884 Granville St</t>
+        </is>
+      </c>
+      <c r="D1618" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2054215, 'Longitude': -123.1401677}</t>
+        </is>
+      </c>
+      <c r="E1618" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:13:17</t>
+        </is>
+      </c>
+      <c r="F1618" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:06:48.502Z</t>
+        </is>
+      </c>
+      <c r="G1618" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1618" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:13.470Z</t>
+        </is>
+      </c>
+      <c r="I1618" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="n">
+        <v>65572</v>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1619" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D1619" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E1619" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:13:17</t>
+        </is>
+      </c>
+      <c r="F1619" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:06:58.014Z</t>
+        </is>
+      </c>
+      <c r="G1619" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1619" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:12:12.232Z</t>
+        </is>
+      </c>
+      <c r="I1619" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="n">
+        <v>65511</v>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1620" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1620" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E1620" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:13:17</t>
+        </is>
+      </c>
+      <c r="F1620" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:42:18.239Z</t>
+        </is>
+      </c>
+      <c r="G1620" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1620" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:42:18.255Z</t>
+        </is>
+      </c>
+      <c r="I1620" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="n">
+        <v>65556</v>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1621" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1621" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20806537721, 'Longitude': -123.123285770416}</t>
+        </is>
+      </c>
+      <c r="E1621" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:13:17</t>
+        </is>
+      </c>
+      <c r="F1621" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:08:32.784Z</t>
+        </is>
+      </c>
+      <c r="G1621" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1621" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:46.640Z</t>
+        </is>
+      </c>
+      <c r="I1621" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="n">
+        <v>32378</v>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1622" t="inlineStr">
+        <is>
+          <t>1613 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1622" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3288556, 'Longitude': -123.1592779}</t>
+        </is>
+      </c>
+      <c r="E1622" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:15:50</t>
+        </is>
+      </c>
+      <c r="F1622" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:23:48.032Z</t>
+        </is>
+      </c>
+      <c r="G1622" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1622" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:23:48.047Z</t>
+        </is>
+      </c>
+      <c r="I1622" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="n">
+        <v>98624</v>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1623" t="inlineStr">
+        <is>
+          <t>1503 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1623" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.328484, 'Longitude': -123.15694}</t>
+        </is>
+      </c>
+      <c r="E1623" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:15:50</t>
+        </is>
+      </c>
+      <c r="F1623" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:15:01.270Z</t>
+        </is>
+      </c>
+      <c r="G1623" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1623" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:24:13.558Z</t>
+        </is>
+      </c>
+      <c r="I1623" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="n">
+        <v>98626</v>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1624" t="inlineStr">
+        <is>
+          <t>1490 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1624" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.328176303121, 'Longitude': -123.1565746665}</t>
+        </is>
+      </c>
+      <c r="E1624" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:15:50</t>
+        </is>
+      </c>
+      <c r="F1624" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:14:31.488Z</t>
+        </is>
+      </c>
+      <c r="G1624" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1624" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:57:16.589Z</t>
+        </is>
+      </c>
+      <c r="I1624" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="n">
+        <v>65575</v>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1625" t="inlineStr">
+        <is>
+          <t>1305 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1625" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.327918987512, 'Longitude': -123.151953220367}</t>
+        </is>
+      </c>
+      <c r="E1625" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:15:50</t>
+        </is>
+      </c>
+      <c r="F1625" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:13:52.915Z</t>
+        </is>
+      </c>
+      <c r="G1625" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1625" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:58:23.220Z</t>
+        </is>
+      </c>
+      <c r="I1625" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="n">
+        <v>65505</v>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1626" t="inlineStr">
+        <is>
+          <t>1731 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D1626" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.325583506404, 'Longitude': -123.121590614319}</t>
+        </is>
+      </c>
+      <c r="E1626" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:15:50</t>
+        </is>
+      </c>
+      <c r="F1626" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:56:52.357Z</t>
+        </is>
+      </c>
+      <c r="G1626" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1626" t="inlineStr"/>
+      <c r="I1626" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="n">
+        <v>65503</v>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1627" t="inlineStr">
+        <is>
+          <t>1980 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1627" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.324534601594, 'Longitude': -123.121654987335}</t>
+        </is>
+      </c>
+      <c r="E1627" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:15:50</t>
+        </is>
+      </c>
+      <c r="F1627" t="inlineStr">
+        <is>
+          <t>2025-08-21T12:34:34.230Z</t>
+        </is>
+      </c>
+      <c r="G1627" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1627" t="inlineStr"/>
+      <c r="I1627" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="n">
+        <v>75407</v>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1628" t="inlineStr">
+        <is>
+          <t>2698 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D1628" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3343054, 'Longitude': -123.1157865}</t>
+        </is>
+      </c>
+      <c r="E1628" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:15:50</t>
+        </is>
+      </c>
+      <c r="F1628" t="inlineStr">
+        <is>
+          <t>2025-08-21T12:33:20.396Z</t>
+        </is>
+      </c>
+      <c r="G1628" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1628" t="inlineStr"/>
+      <c r="I1628" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="n">
+        <v>75406</v>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1629" t="inlineStr">
+        <is>
+          <t>1198 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1629" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.323975176559, 'Longitude': -123.107525110245}</t>
+        </is>
+      </c>
+      <c r="E1629" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:15:50</t>
+        </is>
+      </c>
+      <c r="F1629" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:12:38.776Z</t>
+        </is>
+      </c>
+      <c r="G1629" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1629" t="inlineStr"/>
+      <c r="I1629" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="n">
+        <v>75409</v>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1630" t="inlineStr">
+        <is>
+          <t>3150 Edgemont Blvd</t>
+        </is>
+      </c>
+      <c r="D1630" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.338128, 'Longitude': -123.1021338}</t>
+        </is>
+      </c>
+      <c r="E1630" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:15:50</t>
+        </is>
+      </c>
+      <c r="F1630" t="inlineStr"/>
+      <c r="G1630" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1630" t="inlineStr"/>
+      <c r="I1630" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="n">
+        <v>98622</v>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1631" t="inlineStr">
+        <is>
+          <t>3690 Westmount Rd</t>
+        </is>
+      </c>
+      <c r="D1631" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3459143, 'Longitude': -123.2177286}</t>
+        </is>
+      </c>
+      <c r="E1631" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:15:50</t>
+        </is>
+      </c>
+      <c r="F1631" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:08:16.327Z</t>
+        </is>
+      </c>
+      <c r="G1631" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1631" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:08:16.374Z</t>
+        </is>
+      </c>
+      <c r="I1631" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="n">
+        <v>18803</v>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1632" t="inlineStr">
+        <is>
+          <t>2501 Westview Dr</t>
+        </is>
+      </c>
+      <c r="D1632" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.332617583893, 'Longitude': -123.088846206665}</t>
+        </is>
+      </c>
+      <c r="E1632" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:15:50</t>
+        </is>
+      </c>
+      <c r="F1632" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:02:33.190Z</t>
+        </is>
+      </c>
+      <c r="G1632" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1632" t="inlineStr"/>
+      <c r="I1632" t="inlineStr"/>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="n">
+        <v>18804</v>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1633" t="inlineStr">
+        <is>
+          <t>660 3rd St  W</t>
+        </is>
+      </c>
+      <c r="D1633" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319671, 'Longitude': -123.0902808}</t>
+        </is>
+      </c>
+      <c r="E1633" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:15:50</t>
+        </is>
+      </c>
+      <c r="F1633" t="inlineStr">
+        <is>
+          <t>2025-08-21T09:25:09.433Z</t>
+        </is>
+      </c>
+      <c r="G1633" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1633" t="inlineStr">
+        <is>
+          <t>2025-08-19T17:13:18.796Z</t>
+        </is>
+      </c>
+      <c r="I1633" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="n">
+        <v>32349</v>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1634" t="inlineStr">
+        <is>
+          <t>106 W Queens St</t>
+        </is>
+      </c>
+      <c r="D1634" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.336724992343, 'Longitude': -123.072506189346}</t>
+        </is>
+      </c>
+      <c r="E1634" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:15:50</t>
+        </is>
+      </c>
+      <c r="F1634" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:36:38.345Z</t>
+        </is>
+      </c>
+      <c r="G1634" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1634" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:31:29.513Z</t>
+        </is>
+      </c>
+      <c r="I1634" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="n">
+        <v>18509</v>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1635" t="inlineStr">
+        <is>
+          <t>2305 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D1635" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3306729, 'Longitude': -123.0728536}</t>
+        </is>
+      </c>
+      <c r="E1635" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:15:50</t>
+        </is>
+      </c>
+      <c r="F1635" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:21:45.920Z</t>
+        </is>
+      </c>
+      <c r="G1635" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1635" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:21:46.014Z</t>
+        </is>
+      </c>
+      <c r="I1635" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="n">
+        <v>22117</v>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1636" t="inlineStr">
+        <is>
+          <t>1245 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D1636" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319695364751, 'Longitude': -123.07279586792}</t>
+        </is>
+      </c>
+      <c r="E1636" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:15:50</t>
+        </is>
+      </c>
+      <c r="F1636" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:55:32.582Z</t>
+        </is>
+      </c>
+      <c r="G1636" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1636" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:54:45.752Z</t>
+        </is>
+      </c>
+      <c r="I1636" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1637" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1637" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E1637" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:15:50</t>
+        </is>
+      </c>
+      <c r="F1637" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:53:46.947Z</t>
+        </is>
+      </c>
+      <c r="G1637" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1637" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:44:27.069Z</t>
+        </is>
+      </c>
+      <c r="I1637" t="n">
+        <v>199.9</v>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1638" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1638" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E1638" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:15:50</t>
+        </is>
+      </c>
+      <c r="F1638" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:59:15.632Z</t>
+        </is>
+      </c>
+      <c r="G1638" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1638" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:11.555Z</t>
+        </is>
+      </c>
+      <c r="I1638" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1639" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1639" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E1639" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:15:50</t>
+        </is>
+      </c>
+      <c r="F1639" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:59:10.061Z</t>
+        </is>
+      </c>
+      <c r="G1639" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1639" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:22.999Z</t>
+        </is>
+      </c>
+      <c r="I1639" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1640" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D1640" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E1640" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:15:50</t>
+        </is>
+      </c>
+      <c r="F1640" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:39:55.743Z</t>
+        </is>
+      </c>
+      <c r="G1640" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1640" t="inlineStr"/>
+      <c r="I1640" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1641" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1641" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E1641" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:15:50</t>
+        </is>
+      </c>
+      <c r="F1641" t="inlineStr">
+        <is>
+          <t>2025-08-21T12:33:20.103Z</t>
+        </is>
+      </c>
+      <c r="G1641" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1641" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:16:34.188Z</t>
+        </is>
+      </c>
+      <c r="I1641" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="n">
+        <v>18509</v>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1642" t="inlineStr">
+        <is>
+          <t>2305 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D1642" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3306729, 'Longitude': -123.0728536}</t>
+        </is>
+      </c>
+      <c r="E1642" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:18:20</t>
+        </is>
+      </c>
+      <c r="F1642" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:21:45.920Z</t>
+        </is>
+      </c>
+      <c r="G1642" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1642" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:21:46.014Z</t>
+        </is>
+      </c>
+      <c r="I1642" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="n">
+        <v>22117</v>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>1245 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D1643" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319695364751, 'Longitude': -123.07279586792}</t>
+        </is>
+      </c>
+      <c r="E1643" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:18:20</t>
+        </is>
+      </c>
+      <c r="F1643" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:55:32.582Z</t>
+        </is>
+      </c>
+      <c r="G1643" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1643" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:54:45.752Z</t>
+        </is>
+      </c>
+      <c r="I1643" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="n">
+        <v>32349</v>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1644" t="inlineStr">
+        <is>
+          <t>106 W Queens St</t>
+        </is>
+      </c>
+      <c r="D1644" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.336724992343, 'Longitude': -123.072506189346}</t>
+        </is>
+      </c>
+      <c r="E1644" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:18:20</t>
+        </is>
+      </c>
+      <c r="F1644" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:36:38.345Z</t>
+        </is>
+      </c>
+      <c r="G1644" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1644" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:31:29.513Z</t>
+        </is>
+      </c>
+      <c r="I1644" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="n">
+        <v>18803</v>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1645" t="inlineStr">
+        <is>
+          <t>2501 Westview Dr</t>
+        </is>
+      </c>
+      <c r="D1645" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.332617583893, 'Longitude': -123.088846206665}</t>
+        </is>
+      </c>
+      <c r="E1645" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:18:20</t>
+        </is>
+      </c>
+      <c r="F1645" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:02:33.190Z</t>
+        </is>
+      </c>
+      <c r="G1645" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1645" t="inlineStr"/>
+      <c r="I1645" t="inlineStr"/>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="n">
+        <v>18804</v>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1646" t="inlineStr">
+        <is>
+          <t>660 3rd St  W</t>
+        </is>
+      </c>
+      <c r="D1646" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319671, 'Longitude': -123.0902808}</t>
+        </is>
+      </c>
+      <c r="E1646" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:18:20</t>
+        </is>
+      </c>
+      <c r="F1646" t="inlineStr">
+        <is>
+          <t>2025-08-21T09:25:09.433Z</t>
+        </is>
+      </c>
+      <c r="G1646" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1646" t="inlineStr">
+        <is>
+          <t>2025-08-19T17:13:18.796Z</t>
+        </is>
+      </c>
+      <c r="I1646" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="n">
+        <v>75409</v>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1647" t="inlineStr">
+        <is>
+          <t>3150 Edgemont Blvd</t>
+        </is>
+      </c>
+      <c r="D1647" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.338128, 'Longitude': -123.1021338}</t>
+        </is>
+      </c>
+      <c r="E1647" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:18:20</t>
+        </is>
+      </c>
+      <c r="F1647" t="inlineStr"/>
+      <c r="G1647" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1647" t="inlineStr"/>
+      <c r="I1647" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="n">
+        <v>75406</v>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1648" t="inlineStr">
+        <is>
+          <t>1198 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1648" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.323975176559, 'Longitude': -123.107525110245}</t>
+        </is>
+      </c>
+      <c r="E1648" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:18:20</t>
+        </is>
+      </c>
+      <c r="F1648" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:12:38.776Z</t>
+        </is>
+      </c>
+      <c r="G1648" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1648" t="inlineStr"/>
+      <c r="I1648" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="n">
+        <v>18512</v>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1649" t="inlineStr">
+        <is>
+          <t>2747 Mountain Hwy</t>
+        </is>
+      </c>
+      <c r="D1649" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.333694, 'Longitude': -123.038315}</t>
+        </is>
+      </c>
+      <c r="E1649" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:18:20</t>
+        </is>
+      </c>
+      <c r="F1649" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:58:00.450Z</t>
+        </is>
+      </c>
+      <c r="G1649" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1649" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:58:00.492Z</t>
+        </is>
+      </c>
+      <c r="I1649" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="n">
+        <v>9706</v>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1650" t="inlineStr">
+        <is>
+          <t>2979 Mountain Hwy</t>
+        </is>
+      </c>
+      <c r="D1650" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3356515, 'Longitude': -123.038272}</t>
+        </is>
+      </c>
+      <c r="E1650" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:18:20</t>
+        </is>
+      </c>
+      <c r="F1650" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:57:54.567Z</t>
+        </is>
+      </c>
+      <c r="G1650" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1650" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:57:54.599Z</t>
+        </is>
+      </c>
+      <c r="I1650" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="n">
+        <v>32289</v>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1651" t="inlineStr">
+        <is>
+          <t>1270 Lynn Valley Rd</t>
+        </is>
+      </c>
+      <c r="D1651" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.337231840266, 'Longitude': -123.038763999939}</t>
+        </is>
+      </c>
+      <c r="E1651" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:18:20</t>
+        </is>
+      </c>
+      <c r="F1651" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:57:47.623Z</t>
+        </is>
+      </c>
+      <c r="G1651" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1651" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:57:47.660Z</t>
+        </is>
+      </c>
+      <c r="I1651" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="n">
+        <v>75407</v>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1652" t="inlineStr">
+        <is>
+          <t>2698 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D1652" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3343054, 'Longitude': -123.1157865}</t>
+        </is>
+      </c>
+      <c r="E1652" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:18:20</t>
+        </is>
+      </c>
+      <c r="F1652" t="inlineStr">
+        <is>
+          <t>2025-08-21T12:33:20.396Z</t>
+        </is>
+      </c>
+      <c r="G1652" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1652" t="inlineStr"/>
+      <c r="I1652" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="n">
+        <v>65505</v>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1653" t="inlineStr">
+        <is>
+          <t>1731 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D1653" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.325583506404, 'Longitude': -123.121590614319}</t>
+        </is>
+      </c>
+      <c r="E1653" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:18:20</t>
+        </is>
+      </c>
+      <c r="F1653" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:56:52.357Z</t>
+        </is>
+      </c>
+      <c r="G1653" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1653" t="inlineStr"/>
+      <c r="I1653" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="n">
+        <v>65503</v>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1654" t="inlineStr">
+        <is>
+          <t>1980 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1654" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.324534601594, 'Longitude': -123.121654987335}</t>
+        </is>
+      </c>
+      <c r="E1654" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:18:20</t>
+        </is>
+      </c>
+      <c r="F1654" t="inlineStr">
+        <is>
+          <t>2025-08-21T12:34:34.230Z</t>
+        </is>
+      </c>
+      <c r="G1654" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1654" t="inlineStr"/>
+      <c r="I1654" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="n">
+        <v>18510</v>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1655" t="inlineStr">
+        <is>
+          <t>1490 Main St</t>
+        </is>
+      </c>
+      <c r="D1655" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3057944, 'Longitude': -123.0328688}</t>
+        </is>
+      </c>
+      <c r="E1655" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:18:20</t>
+        </is>
+      </c>
+      <c r="F1655" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:22:15.146Z</t>
+        </is>
+      </c>
+      <c r="G1655" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1655" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:22:15.178Z</t>
+        </is>
+      </c>
+      <c r="I1655" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="n">
+        <v>69296</v>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1656" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185 Mountain Hwy </t>
+        </is>
+      </c>
+      <c r="D1656" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.305048881232, 'Longitude': -123.0324447155}</t>
+        </is>
+      </c>
+      <c r="E1656" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:18:20</t>
+        </is>
+      </c>
+      <c r="F1656" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:22:20.782Z</t>
+        </is>
+      </c>
+      <c r="G1656" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1656" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:22:20.808Z</t>
+        </is>
+      </c>
+      <c r="I1656" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="n">
+        <v>65506</v>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1657" t="inlineStr">
+        <is>
+          <t>333 Seymour Blvd</t>
+        </is>
+      </c>
+      <c r="D1657" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.311498347051, 'Longitude': -123.022198677063}</t>
+        </is>
+      </c>
+      <c r="E1657" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:18:20</t>
+        </is>
+      </c>
+      <c r="F1657" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:55:45.837Z</t>
+        </is>
+      </c>
+      <c r="G1657" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1657" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:55:45.868Z</t>
+        </is>
+      </c>
+      <c r="I1657" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="n">
+        <v>98513</v>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1658" t="inlineStr">
+        <is>
+          <t>1955 Powell St</t>
+        </is>
+      </c>
+      <c r="D1658" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.28504, 'Longitude': -123.0643977}</t>
+        </is>
+      </c>
+      <c r="E1658" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:18:20</t>
+        </is>
+      </c>
+      <c r="F1658" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:22:24.458Z</t>
+        </is>
+      </c>
+      <c r="G1658" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1658" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:59:12.373Z</t>
+        </is>
+      </c>
+      <c r="I1658" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="n">
+        <v>75410</v>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1659" t="inlineStr">
+        <is>
+          <t>2177 Dollarton Hwy</t>
+        </is>
+      </c>
+      <c r="D1659" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.305160809746, 'Longitude': -123.014302253723}</t>
+        </is>
+      </c>
+      <c r="E1659" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:18:20</t>
+        </is>
+      </c>
+      <c r="F1659" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:09:28.635Z</t>
+        </is>
+      </c>
+      <c r="G1659" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1659" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:09:28.667Z</t>
+        </is>
+      </c>
+      <c r="I1659" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="n">
+        <v>65546</v>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1660" t="inlineStr">
+        <is>
+          <t>1212 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D1660" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2809987, 'Longitude': -123.0786929}</t>
+        </is>
+      </c>
+      <c r="E1660" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:18:20</t>
+        </is>
+      </c>
+      <c r="F1660" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:16:07.492Z</t>
+        </is>
+      </c>
+      <c r="G1660" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1660" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:35:00.625Z</t>
+        </is>
+      </c>
+      <c r="I1660" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="n">
+        <v>98515</v>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1661" t="inlineStr">
+        <is>
+          <t>1896 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D1661" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.281018940561, 'Longitude': -123.065712153912}</t>
+        </is>
+      </c>
+      <c r="E1661" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:18:20</t>
+        </is>
+      </c>
+      <c r="F1661" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:16:25.413Z</t>
+        </is>
+      </c>
+      <c r="G1661" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1661" t="inlineStr">
+        <is>
+          <t>2025-08-20T07:10:51.610Z</t>
+        </is>
+      </c>
+      <c r="I1661" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="n">
+        <v>65464</v>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1662" t="inlineStr">
+        <is>
+          <t>6751 Lougheed Hwy</t>
+        </is>
+      </c>
+      <c r="D1662" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2598029, 'Longitude': -122.9640097}</t>
+        </is>
+      </c>
+      <c r="E1662" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:20:44</t>
+        </is>
+      </c>
+      <c r="F1662" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:29:41.904Z</t>
+        </is>
+      </c>
+      <c r="G1662" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1662" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:54:01.680Z</t>
+        </is>
+      </c>
+      <c r="I1662" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="n">
+        <v>100210</v>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1663" t="inlineStr">
+        <is>
+          <t>7089 Lougheed Hwy</t>
+        </is>
+      </c>
+      <c r="D1663" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259055582449, 'Longitude': -122.956455763229}</t>
+        </is>
+      </c>
+      <c r="E1663" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:20:44</t>
+        </is>
+      </c>
+      <c r="F1663" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:13:21.972Z</t>
+        </is>
+      </c>
+      <c r="G1663" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1663" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:13:37.884Z</t>
+        </is>
+      </c>
+      <c r="I1663" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="n">
+        <v>98628</v>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1664" t="inlineStr">
+        <is>
+          <t>6568 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D1664" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.280205, 'Longitude': -122.96824}</t>
+        </is>
+      </c>
+      <c r="E1664" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:20:44</t>
+        </is>
+      </c>
+      <c r="F1664" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:53:30.343Z</t>
+        </is>
+      </c>
+      <c r="G1664" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1664" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:53:30.359Z</t>
+        </is>
+      </c>
+      <c r="I1664" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="n">
+        <v>65465</v>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1665" t="inlineStr">
+        <is>
+          <t>7009 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D1665" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.280651, 'Longitude': -122.9578017}</t>
+        </is>
+      </c>
+      <c r="E1665" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:20:44</t>
+        </is>
+      </c>
+      <c r="F1665" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:53:55.127Z</t>
+        </is>
+      </c>
+      <c r="G1665" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1665" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:53:55.142Z</t>
+        </is>
+      </c>
+      <c r="I1665" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="n">
+        <v>117793</v>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1666" t="inlineStr">
+        <is>
+          <t>6511 Hastings St</t>
+        </is>
+      </c>
+      <c r="D1666" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.280589202387, 'Longitude': -122.969627380371}</t>
+        </is>
+      </c>
+      <c r="E1666" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:20:44</t>
+        </is>
+      </c>
+      <c r="F1666" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:53:34.319Z</t>
+        </is>
+      </c>
+      <c r="G1666" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1666" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:53:34.347Z</t>
+        </is>
+      </c>
+      <c r="I1666" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="n">
+        <v>65476</v>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>Husky</t>
+        </is>
+      </c>
+      <c r="C1667" t="inlineStr">
+        <is>
+          <t>5720 Hastings St</t>
+        </is>
+      </c>
+      <c r="D1667" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.280138464632, 'Longitude': -122.980592250824}</t>
+        </is>
+      </c>
+      <c r="E1667" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:20:44</t>
+        </is>
+      </c>
+      <c r="F1667" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:49:43.152Z</t>
+        </is>
+      </c>
+      <c r="G1667" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1667" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:49:43.215Z</t>
+        </is>
+      </c>
+      <c r="I1667" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="n">
+        <v>212356</v>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>CENTEX</t>
+        </is>
+      </c>
+      <c r="C1668" t="inlineStr">
+        <is>
+          <t>3855 Douglas Rd</t>
+        </is>
+      </c>
+      <c r="D1668" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249718360686, 'Longitude': -122.981165650914}</t>
+        </is>
+      </c>
+      <c r="E1668" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:20:44</t>
+        </is>
+      </c>
+      <c r="F1668" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:29:32.947Z</t>
+        </is>
+      </c>
+      <c r="G1668" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1668" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:30:32.371Z</t>
+        </is>
+      </c>
+      <c r="I1668" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="n">
+        <v>919</v>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1669" t="inlineStr">
+        <is>
+          <t>4512 Lougheed Hwy</t>
+        </is>
+      </c>
+      <c r="D1669" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.266012306544, 'Longitude': -123.002243041992}</t>
+        </is>
+      </c>
+      <c r="E1669" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:20:44</t>
+        </is>
+      </c>
+      <c r="F1669" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:05:27.358Z</t>
+        </is>
+      </c>
+      <c r="G1669" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1669" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:05:27.436Z</t>
+        </is>
+      </c>
+      <c r="I1669" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="n">
+        <v>164809</v>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1670" t="inlineStr">
+        <is>
+          <t>1969 Willingdon Ave</t>
+        </is>
+      </c>
+      <c r="D1670" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.266593392816, 'Longitude': -123.003401756287}</t>
+        </is>
+      </c>
+      <c r="E1670" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:20:44</t>
+        </is>
+      </c>
+      <c r="F1670" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:05:40.695Z</t>
+        </is>
+      </c>
+      <c r="G1670" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1670" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:05:40.726Z</t>
+        </is>
+      </c>
+      <c r="I1670" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="n">
+        <v>65471</v>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1671" t="inlineStr">
+        <is>
+          <t>5059 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1671" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.239569143746, 'Longitude': -122.96440243721}</t>
+        </is>
+      </c>
+      <c r="E1671" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:20:44</t>
+        </is>
+      </c>
+      <c r="F1671" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:19:34.223Z</t>
+        </is>
+      </c>
+      <c r="G1671" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1671" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:32:11.629Z</t>
+        </is>
+      </c>
+      <c r="I1671" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="n">
+        <v>1669</v>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1672" t="inlineStr">
+        <is>
+          <t>975 Willingdon Ave</t>
+        </is>
+      </c>
+      <c r="D1672" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2758486, 'Longitude': -123.0035135}</t>
+        </is>
+      </c>
+      <c r="E1672" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:20:44</t>
+        </is>
+      </c>
+      <c r="F1672" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:28:51.214Z</t>
+        </is>
+      </c>
+      <c r="G1672" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1672" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:16:22.396Z</t>
+        </is>
+      </c>
+      <c r="I1672" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="n">
+        <v>65479</v>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1673" t="inlineStr">
+        <is>
+          <t>4505 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1673" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.255159438214, 'Longitude': -123.003401756287}</t>
+        </is>
+      </c>
+      <c r="E1673" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:20:44</t>
+        </is>
+      </c>
+      <c r="F1673" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:10:58.312Z</t>
+        </is>
+      </c>
+      <c r="G1673" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1673" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:10:58.343Z</t>
+        </is>
+      </c>
+      <c r="I1673" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="n">
+        <v>69963</v>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>4487 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1674" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.255044, 'Longitude': -123.0046907}</t>
+        </is>
+      </c>
+      <c r="E1674" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:20:44</t>
+        </is>
+      </c>
+      <c r="F1674" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:11:20.824Z</t>
+        </is>
+      </c>
+      <c r="G1674" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1674" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:11:20.964Z</t>
+        </is>
+      </c>
+      <c r="I1674" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="n">
+        <v>65466</v>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>4507 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D1675" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2812235, 'Longitude': -123.0025696}</t>
+        </is>
+      </c>
+      <c r="E1675" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:20:44</t>
+        </is>
+      </c>
+      <c r="F1675" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:49:35.122Z</t>
+        </is>
+      </c>
+      <c r="G1675" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1675" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:49:35.152Z</t>
+        </is>
+      </c>
+      <c r="I1675" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="n">
+        <v>65475</v>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>3826 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1676" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2544887, 'Longitude': -123.0193605}</t>
+        </is>
+      </c>
+      <c r="E1676" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:20:44</t>
+        </is>
+      </c>
+      <c r="F1676" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:58:50.738Z</t>
+        </is>
+      </c>
+      <c r="G1676" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1676" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:58:50.785Z</t>
+        </is>
+      </c>
+      <c r="I1676" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="n">
+        <v>39293</v>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>3030 Boundary Rd</t>
+        </is>
+      </c>
+      <c r="D1677" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2567447, 'Longitude': -123.0230847}</t>
+        </is>
+      </c>
+      <c r="E1677" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:20:44</t>
+        </is>
+      </c>
+      <c r="F1677" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:34:17.214Z</t>
+        </is>
+      </c>
+      <c r="G1677" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1677" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:53:40.788Z</t>
+        </is>
+      </c>
+      <c r="I1677" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="n">
+        <v>119589</v>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>Smart Gas</t>
+        </is>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>6869 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1678" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226505740129, 'Longitude': -122.944511175156}</t>
+        </is>
+      </c>
+      <c r="E1678" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:20:44</t>
+        </is>
+      </c>
+      <c r="F1678" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:03.684Z</t>
+        </is>
+      </c>
+      <c r="G1678" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1678" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:03.731Z</t>
+        </is>
+      </c>
+      <c r="I1678" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="n">
+        <v>124671</v>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>3505 Grandview Hwy</t>
+        </is>
+      </c>
+      <c r="D1679" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2585701, 'Longitude': -123.0281066}</t>
+        </is>
+      </c>
+      <c r="E1679" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:20:44</t>
+        </is>
+      </c>
+      <c r="F1679" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:51:07.379Z</t>
+        </is>
+      </c>
+      <c r="G1679" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1679" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:53:59.992Z</t>
+        </is>
+      </c>
+      <c r="I1679" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="n">
+        <v>65474</v>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>7274 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1680" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2244118, 'Longitude': -122.9410264}</t>
+        </is>
+      </c>
+      <c r="E1680" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:20:44</t>
+        </is>
+      </c>
+      <c r="F1680" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:41:39.387Z</t>
+        </is>
+      </c>
+      <c r="G1680" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1680" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:59.321Z</t>
+        </is>
+      </c>
+      <c r="I1680" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="n">
+        <v>5768</v>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>5009 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1681" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2264629, 'Longitude': -122.992576}</t>
+        </is>
+      </c>
+      <c r="E1681" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:20:44</t>
+        </is>
+      </c>
+      <c r="F1681" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:09:57.338Z</t>
+        </is>
+      </c>
+      <c r="G1681" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1681" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:12:00.421Z</t>
+        </is>
+      </c>
+      <c r="I1681" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>65480</t>
+        </is>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>6591 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1682" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21925095319, 'Longitude': -122.968211174011}</t>
+        </is>
+      </c>
+      <c r="E1682" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:23:15</t>
+        </is>
+      </c>
+      <c r="F1682" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:37:33.570Z</t>
+        </is>
+      </c>
+      <c r="G1682" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H1682" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:25:44.411Z</t>
+        </is>
+      </c>
+      <c r="I1682" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>65467</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>6138 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1683" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2201556, 'Longitude': -122.9743751}</t>
+        </is>
+      </c>
+      <c r="E1683" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:23:15</t>
+        </is>
+      </c>
+      <c r="F1683" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:37:31.647Z</t>
+        </is>
+      </c>
+      <c r="G1683" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1683" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:56:58.102Z</t>
+        </is>
+      </c>
+      <c r="I1683" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>119589</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>Smart Gas</t>
+        </is>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>6869 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1684" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226505740129, 'Longitude': -122.944511175156}</t>
+        </is>
+      </c>
+      <c r="E1684" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:23:15</t>
+        </is>
+      </c>
+      <c r="F1684" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:03.684Z</t>
+        </is>
+      </c>
+      <c r="G1684" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1684" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:03.731Z</t>
+        </is>
+      </c>
+      <c r="I1684" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>65474</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>7274 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1685" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2244118, 'Longitude': -122.9410264}</t>
+        </is>
+      </c>
+      <c r="E1685" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:23:15</t>
+        </is>
+      </c>
+      <c r="F1685" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:41:39.387Z</t>
+        </is>
+      </c>
+      <c r="G1685" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1685" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:59.321Z</t>
+        </is>
+      </c>
+      <c r="I1685" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>87633</t>
+        </is>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1686" t="inlineStr">
+        <is>
+          <t>5608 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1686" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.222913, 'Longitude': -122.982433}</t>
+        </is>
+      </c>
+      <c r="E1686" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:23:15</t>
+        </is>
+      </c>
+      <c r="F1686" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:49:28.052Z</t>
+        </is>
+      </c>
+      <c r="G1686" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1686" t="inlineStr">
+        <is>
+          <t>2025-08-20T20:48:12.771Z</t>
+        </is>
+      </c>
+      <c r="I1686" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>65481</t>
+        </is>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1687" t="inlineStr">
+        <is>
+          <t>7377 6th St</t>
+        </is>
+      </c>
+      <c r="D1687" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.225214157435, 'Longitude': -122.935831546783}</t>
+        </is>
+      </c>
+      <c r="E1687" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:23:15</t>
+        </is>
+      </c>
+      <c r="F1687" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:56:59.246Z</t>
+        </is>
+      </c>
+      <c r="G1687" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1687" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:31:02.731Z</t>
+        </is>
+      </c>
+      <c r="I1687" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>65477</t>
+        </is>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1688" t="inlineStr">
+        <is>
+          <t>7890 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1688" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.217246706543, 'Longitude': -122.931432723999}</t>
+        </is>
+      </c>
+      <c r="E1688" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:23:15</t>
+        </is>
+      </c>
+      <c r="F1688" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:38:11.932Z</t>
+        </is>
+      </c>
+      <c r="G1688" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1688" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:38:12.010Z</t>
+        </is>
+      </c>
+      <c r="I1688" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>65468</t>
+        </is>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1689" t="inlineStr">
+        <is>
+          <t>7587 Royal Oak Ave</t>
+        </is>
+      </c>
+      <c r="D1689" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2151443, 'Longitude': -122.9890903}</t>
+        </is>
+      </c>
+      <c r="E1689" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:23:15</t>
+        </is>
+      </c>
+      <c r="F1689" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:38:45.754Z</t>
+        </is>
+      </c>
+      <c r="G1689" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1689" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:05:59.185Z</t>
+        </is>
+      </c>
+      <c r="I1689" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>65471</t>
+        </is>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1690" t="inlineStr">
+        <is>
+          <t>5059 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1690" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.239569143746, 'Longitude': -122.96440243721}</t>
+        </is>
+      </c>
+      <c r="E1690" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:23:15</t>
+        </is>
+      </c>
+      <c r="F1690" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:19:34.223Z</t>
+        </is>
+      </c>
+      <c r="G1690" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1690" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:32:11.629Z</t>
+        </is>
+      </c>
+      <c r="I1690" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>5768</t>
+        </is>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1691" t="inlineStr">
+        <is>
+          <t>5009 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1691" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2264629, 'Longitude': -122.992576}</t>
+        </is>
+      </c>
+      <c r="E1691" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:23:15</t>
+        </is>
+      </c>
+      <c r="F1691" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:09:57.338Z</t>
+        </is>
+      </c>
+      <c r="G1691" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1691" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:12:00.421Z</t>
+        </is>
+      </c>
+      <c r="I1691" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>111740</t>
+        </is>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1692" t="inlineStr">
+        <is>
+          <t>780 6th St</t>
+        </is>
+      </c>
+      <c r="D1692" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21557, 'Longitude': -122.92387}</t>
+        </is>
+      </c>
+      <c r="E1692" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:23:15</t>
+        </is>
+      </c>
+      <c r="F1692" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:37:54.809Z</t>
+        </is>
+      </c>
+      <c r="G1692" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1692" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:37:54.856Z</t>
+        </is>
+      </c>
+      <c r="I1692" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>65469</t>
+        </is>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1693" t="inlineStr">
+        <is>
+          <t>4692 Imperial St</t>
+        </is>
+      </c>
+      <c r="D1693" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2217244, 'Longitude': -122.9980797}</t>
+        </is>
+      </c>
+      <c r="E1693" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:23:15</t>
+        </is>
+      </c>
+      <c r="F1693" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:52:01.213Z</t>
+        </is>
+      </c>
+      <c r="G1693" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1693" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:58:12.777Z</t>
+        </is>
+      </c>
+      <c r="I1693" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>65499</t>
+        </is>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1694" t="inlineStr">
+        <is>
+          <t>736 Sixth Ave</t>
+        </is>
+      </c>
+      <c r="D1694" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21129, 'Longitude': -122.92333}</t>
+        </is>
+      </c>
+      <c r="E1694" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:23:15</t>
+        </is>
+      </c>
+      <c r="F1694" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:30.175Z</t>
+        </is>
+      </c>
+      <c r="G1694" t="n">
+        <v>164.6</v>
+      </c>
+      <c r="H1694" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:30.222Z</t>
+        </is>
+      </c>
+      <c r="I1694" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>65497</t>
+        </is>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1695" t="inlineStr">
+        <is>
+          <t>428 Sixth St</t>
+        </is>
+      </c>
+      <c r="D1695" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2109656, 'Longitude': -122.9179526}</t>
+        </is>
+      </c>
+      <c r="E1695" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:23:15</t>
+        </is>
+      </c>
+      <c r="F1695" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:14:21.966Z</t>
+        </is>
+      </c>
+      <c r="G1695" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1695" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:25:12.166Z</t>
+        </is>
+      </c>
+      <c r="I1695" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>32350</t>
+        </is>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1696" t="inlineStr">
+        <is>
+          <t>132 12th St</t>
+        </is>
+      </c>
+      <c r="D1696" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.201144, 'Longitude': -122.922922}</t>
+        </is>
+      </c>
+      <c r="E1696" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:23:15</t>
+        </is>
+      </c>
+      <c r="F1696" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:11:49.411Z</t>
+        </is>
+      </c>
+      <c r="G1696" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1696" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:38:14.709Z</t>
+        </is>
+      </c>
+      <c r="I1696" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>65502</t>
+        </is>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1697" t="inlineStr">
+        <is>
+          <t>5 W 8th Ave</t>
+        </is>
+      </c>
+      <c r="D1697" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.222332, 'Longitude': -122.91267}</t>
+        </is>
+      </c>
+      <c r="E1697" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:23:15</t>
+        </is>
+      </c>
+      <c r="F1697" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:25:24.963Z</t>
+        </is>
+      </c>
+      <c r="G1697" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1697" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:25:24.979Z</t>
+        </is>
+      </c>
+      <c r="I1697" t="n">
+        <v>199.9</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>65498</t>
+        </is>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1698" t="inlineStr">
+        <is>
+          <t>3 E 8th Ave</t>
+        </is>
+      </c>
+      <c r="D1698" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2228942, 'Longitude': -122.9117512}</t>
+        </is>
+      </c>
+      <c r="E1698" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:23:15</t>
+        </is>
+      </c>
+      <c r="F1698" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:25:19.383Z</t>
+        </is>
+      </c>
+      <c r="G1698" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1698" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:25:19.414Z</t>
+        </is>
+      </c>
+      <c r="I1698" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>65470</t>
+        </is>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1699" t="inlineStr">
+        <is>
+          <t>4444 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1699" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.23030428362, 'Longitude': -123.006110787392}</t>
+        </is>
+      </c>
+      <c r="E1699" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:23:15</t>
+        </is>
+      </c>
+      <c r="F1699" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:31:41.284Z</t>
+        </is>
+      </c>
+      <c r="G1699" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1699" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:30:13.104Z</t>
+        </is>
+      </c>
+      <c r="I1699" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>212356</t>
+        </is>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>CENTEX</t>
+        </is>
+      </c>
+      <c r="C1700" t="inlineStr">
+        <is>
+          <t>3855 Douglas Rd</t>
+        </is>
+      </c>
+      <c r="D1700" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249718360686, 'Longitude': -122.981165650914}</t>
+        </is>
+      </c>
+      <c r="E1700" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:23:15</t>
+        </is>
+      </c>
+      <c r="F1700" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:29:32.947Z</t>
+        </is>
+      </c>
+      <c r="G1700" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1700" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:30:32.371Z</t>
+        </is>
+      </c>
+      <c r="I1700" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>99601</t>
+        </is>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1701" t="inlineStr">
+        <is>
+          <t>4177 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1701" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.232536959292, 'Longitude': -123.011408150196}</t>
+        </is>
+      </c>
+      <c r="E1701" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:23:15</t>
+        </is>
+      </c>
+      <c r="F1701" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:41:22.828Z</t>
+        </is>
+      </c>
+      <c r="G1701" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1701" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:41:22.891Z</t>
+        </is>
+      </c>
+      <c r="I1701" t="n">
         <v>191.9</v>
       </c>
     </row>

--- a/data/gas_prices.xlsx
+++ b/data/gas_prices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1701"/>
+  <dimension ref="A1:I1861"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67440,10 +67440,8 @@
       </c>
     </row>
     <row r="1682">
-      <c r="A1682" t="inlineStr">
-        <is>
-          <t>65480</t>
-        </is>
+      <c r="A1682" t="n">
+        <v>65480</v>
       </c>
       <c r="B1682" t="inlineStr">
         <is>
@@ -67483,10 +67481,8 @@
       </c>
     </row>
     <row r="1683">
-      <c r="A1683" t="inlineStr">
-        <is>
-          <t>65467</t>
-        </is>
+      <c r="A1683" t="n">
+        <v>65467</v>
       </c>
       <c r="B1683" t="inlineStr">
         <is>
@@ -67526,10 +67522,8 @@
       </c>
     </row>
     <row r="1684">
-      <c r="A1684" t="inlineStr">
-        <is>
-          <t>119589</t>
-        </is>
+      <c r="A1684" t="n">
+        <v>119589</v>
       </c>
       <c r="B1684" t="inlineStr">
         <is>
@@ -67569,10 +67563,8 @@
       </c>
     </row>
     <row r="1685">
-      <c r="A1685" t="inlineStr">
-        <is>
-          <t>65474</t>
-        </is>
+      <c r="A1685" t="n">
+        <v>65474</v>
       </c>
       <c r="B1685" t="inlineStr">
         <is>
@@ -67612,10 +67604,8 @@
       </c>
     </row>
     <row r="1686">
-      <c r="A1686" t="inlineStr">
-        <is>
-          <t>87633</t>
-        </is>
+      <c r="A1686" t="n">
+        <v>87633</v>
       </c>
       <c r="B1686" t="inlineStr">
         <is>
@@ -67655,10 +67645,8 @@
       </c>
     </row>
     <row r="1687">
-      <c r="A1687" t="inlineStr">
-        <is>
-          <t>65481</t>
-        </is>
+      <c r="A1687" t="n">
+        <v>65481</v>
       </c>
       <c r="B1687" t="inlineStr">
         <is>
@@ -67698,10 +67686,8 @@
       </c>
     </row>
     <row r="1688">
-      <c r="A1688" t="inlineStr">
-        <is>
-          <t>65477</t>
-        </is>
+      <c r="A1688" t="n">
+        <v>65477</v>
       </c>
       <c r="B1688" t="inlineStr">
         <is>
@@ -67741,10 +67727,8 @@
       </c>
     </row>
     <row r="1689">
-      <c r="A1689" t="inlineStr">
-        <is>
-          <t>65468</t>
-        </is>
+      <c r="A1689" t="n">
+        <v>65468</v>
       </c>
       <c r="B1689" t="inlineStr">
         <is>
@@ -67784,10 +67768,8 @@
       </c>
     </row>
     <row r="1690">
-      <c r="A1690" t="inlineStr">
-        <is>
-          <t>65471</t>
-        </is>
+      <c r="A1690" t="n">
+        <v>65471</v>
       </c>
       <c r="B1690" t="inlineStr">
         <is>
@@ -67827,10 +67809,8 @@
       </c>
     </row>
     <row r="1691">
-      <c r="A1691" t="inlineStr">
-        <is>
-          <t>5768</t>
-        </is>
+      <c r="A1691" t="n">
+        <v>5768</v>
       </c>
       <c r="B1691" t="inlineStr">
         <is>
@@ -67870,10 +67850,8 @@
       </c>
     </row>
     <row r="1692">
-      <c r="A1692" t="inlineStr">
-        <is>
-          <t>111740</t>
-        </is>
+      <c r="A1692" t="n">
+        <v>111740</v>
       </c>
       <c r="B1692" t="inlineStr">
         <is>
@@ -67913,10 +67891,8 @@
       </c>
     </row>
     <row r="1693">
-      <c r="A1693" t="inlineStr">
-        <is>
-          <t>65469</t>
-        </is>
+      <c r="A1693" t="n">
+        <v>65469</v>
       </c>
       <c r="B1693" t="inlineStr">
         <is>
@@ -67956,10 +67932,8 @@
       </c>
     </row>
     <row r="1694">
-      <c r="A1694" t="inlineStr">
-        <is>
-          <t>65499</t>
-        </is>
+      <c r="A1694" t="n">
+        <v>65499</v>
       </c>
       <c r="B1694" t="inlineStr">
         <is>
@@ -67999,10 +67973,8 @@
       </c>
     </row>
     <row r="1695">
-      <c r="A1695" t="inlineStr">
-        <is>
-          <t>65497</t>
-        </is>
+      <c r="A1695" t="n">
+        <v>65497</v>
       </c>
       <c r="B1695" t="inlineStr">
         <is>
@@ -68042,10 +68014,8 @@
       </c>
     </row>
     <row r="1696">
-      <c r="A1696" t="inlineStr">
-        <is>
-          <t>32350</t>
-        </is>
+      <c r="A1696" t="n">
+        <v>32350</v>
       </c>
       <c r="B1696" t="inlineStr">
         <is>
@@ -68085,10 +68055,8 @@
       </c>
     </row>
     <row r="1697">
-      <c r="A1697" t="inlineStr">
-        <is>
-          <t>65502</t>
-        </is>
+      <c r="A1697" t="n">
+        <v>65502</v>
       </c>
       <c r="B1697" t="inlineStr">
         <is>
@@ -68128,10 +68096,8 @@
       </c>
     </row>
     <row r="1698">
-      <c r="A1698" t="inlineStr">
-        <is>
-          <t>65498</t>
-        </is>
+      <c r="A1698" t="n">
+        <v>65498</v>
       </c>
       <c r="B1698" t="inlineStr">
         <is>
@@ -68171,10 +68137,8 @@
       </c>
     </row>
     <row r="1699">
-      <c r="A1699" t="inlineStr">
-        <is>
-          <t>65470</t>
-        </is>
+      <c r="A1699" t="n">
+        <v>65470</v>
       </c>
       <c r="B1699" t="inlineStr">
         <is>
@@ -68214,10 +68178,8 @@
       </c>
     </row>
     <row r="1700">
-      <c r="A1700" t="inlineStr">
-        <is>
-          <t>212356</t>
-        </is>
+      <c r="A1700" t="n">
+        <v>212356</v>
       </c>
       <c r="B1700" t="inlineStr">
         <is>
@@ -68257,10 +68219,8 @@
       </c>
     </row>
     <row r="1701">
-      <c r="A1701" t="inlineStr">
-        <is>
-          <t>99601</t>
-        </is>
+      <c r="A1701" t="n">
+        <v>99601</v>
       </c>
       <c r="B1701" t="inlineStr">
         <is>
@@ -68297,6 +68257,6502 @@
       </c>
       <c r="I1701" t="n">
         <v>191.9</v>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="n">
+        <v>65542</v>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1702" t="inlineStr">
+        <is>
+          <t>3250 MacDonald St</t>
+        </is>
+      </c>
+      <c r="D1702" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2573819, 'Longitude': -123.1680407}</t>
+        </is>
+      </c>
+      <c r="E1702" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:54:14</t>
+        </is>
+      </c>
+      <c r="F1702" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:37:56.487Z</t>
+        </is>
+      </c>
+      <c r="G1702" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1702" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:37:56.532Z</t>
+        </is>
+      </c>
+      <c r="I1702" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="n">
+        <v>65533</v>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1703" t="inlineStr">
+        <is>
+          <t>4615 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D1703" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2449719, 'Longitude': -123.1540385}</t>
+        </is>
+      </c>
+      <c r="E1703" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:54:14</t>
+        </is>
+      </c>
+      <c r="F1703" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:14:33.406Z</t>
+        </is>
+      </c>
+      <c r="G1703" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1703" t="inlineStr"/>
+      <c r="I1703" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="n">
+        <v>83068</v>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1704" t="inlineStr">
+        <is>
+          <t>3205 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D1704" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.256927568207, 'Longitude': -123.153288960457}</t>
+        </is>
+      </c>
+      <c r="E1704" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:54:14</t>
+        </is>
+      </c>
+      <c r="F1704" t="inlineStr"/>
+      <c r="G1704" t="inlineStr"/>
+      <c r="H1704" t="inlineStr"/>
+      <c r="I1704" t="inlineStr"/>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="n">
+        <v>65562</v>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1705" t="inlineStr">
+        <is>
+          <t>2808 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1705" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263883932125, 'Longitude': -123.168604373932}</t>
+        </is>
+      </c>
+      <c r="E1705" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:54:14</t>
+        </is>
+      </c>
+      <c r="F1705" t="inlineStr">
+        <is>
+          <t>2025-08-21T12:34:16.278Z</t>
+        </is>
+      </c>
+      <c r="G1705" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1705" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:17:36.405Z</t>
+        </is>
+      </c>
+      <c r="I1705" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="n">
+        <v>113305</v>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1706" t="inlineStr">
+        <is>
+          <t>3596 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1706" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234385296079, 'Longitude': -123.184762001038}</t>
+        </is>
+      </c>
+      <c r="E1706" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:54:14</t>
+        </is>
+      </c>
+      <c r="F1706" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:30:03.056Z</t>
+        </is>
+      </c>
+      <c r="G1706" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1706" t="inlineStr"/>
+      <c r="I1706" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1707" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1707" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E1707" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:54:14</t>
+        </is>
+      </c>
+      <c r="F1707" t="inlineStr">
+        <is>
+          <t>2025-08-21T12:33:20.103Z</t>
+        </is>
+      </c>
+      <c r="G1707" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1707" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:16:34.188Z</t>
+        </is>
+      </c>
+      <c r="I1707" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="n">
+        <v>65554</v>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1708" t="inlineStr">
+        <is>
+          <t>1795 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1708" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264037962303, 'Longitude': -123.145408630371}</t>
+        </is>
+      </c>
+      <c r="E1708" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:54:14</t>
+        </is>
+      </c>
+      <c r="F1708" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:36:45.897Z</t>
+        </is>
+      </c>
+      <c r="G1708" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1708" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:31:16.269Z</t>
+        </is>
+      </c>
+      <c r="I1708" t="n">
+        <v>199.3</v>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="n">
+        <v>65571</v>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1709" t="inlineStr">
+        <is>
+          <t>4314 W 10th Ave</t>
+        </is>
+      </c>
+      <c r="D1709" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263533861752, 'Longitude': -123.203430175781}</t>
+        </is>
+      </c>
+      <c r="E1709" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:54:14</t>
+        </is>
+      </c>
+      <c r="F1709" t="inlineStr">
+        <is>
+          <t>2025-08-21T12:37:45.764Z</t>
+        </is>
+      </c>
+      <c r="G1709" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1709" t="inlineStr">
+        <is>
+          <t>2025-08-19T16:29:09.259Z</t>
+        </is>
+      </c>
+      <c r="I1709" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1710" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D1710" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E1710" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:54:14</t>
+        </is>
+      </c>
+      <c r="F1710" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:39:01.391Z</t>
+        </is>
+      </c>
+      <c r="G1710" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1710" t="inlineStr"/>
+      <c r="I1710" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="n">
+        <v>32376</v>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1711" t="inlineStr">
+        <is>
+          <t>1503 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1711" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234634576953, 'Longitude': -123.139971792698}</t>
+        </is>
+      </c>
+      <c r="E1711" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:54:14</t>
+        </is>
+      </c>
+      <c r="F1711" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:26:32.706Z</t>
+        </is>
+      </c>
+      <c r="G1711" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1711" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:30:08.915Z</t>
+        </is>
+      </c>
+      <c r="I1711" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="n">
+        <v>65549</v>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1712" t="inlineStr">
+        <is>
+          <t>5702 Granville St</t>
+        </is>
+      </c>
+      <c r="D1712" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234036184118, 'Longitude': -123.139244914055}</t>
+        </is>
+      </c>
+      <c r="E1712" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:54:14</t>
+        </is>
+      </c>
+      <c r="F1712" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:26:37.748Z</t>
+        </is>
+      </c>
+      <c r="G1712" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1712" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:16:56.895Z</t>
+        </is>
+      </c>
+      <c r="I1712" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1713" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1713" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E1713" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:54:14</t>
+        </is>
+      </c>
+      <c r="F1713" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:38:06.221Z</t>
+        </is>
+      </c>
+      <c r="G1713" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1713" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:22.999Z</t>
+        </is>
+      </c>
+      <c r="I1713" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1714" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1714" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E1714" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:54:14</t>
+        </is>
+      </c>
+      <c r="F1714" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:59:15.632Z</t>
+        </is>
+      </c>
+      <c r="G1714" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1714" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:11.555Z</t>
+        </is>
+      </c>
+      <c r="I1714" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="n">
+        <v>72747</v>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1715" t="inlineStr">
+        <is>
+          <t>1010 W King Edward Ave</t>
+        </is>
+      </c>
+      <c r="D1715" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249188, 'Longitude': -123.127767}</t>
+        </is>
+      </c>
+      <c r="E1715" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:54:14</t>
+        </is>
+      </c>
+      <c r="F1715" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:52:26.701Z</t>
+        </is>
+      </c>
+      <c r="G1715" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1715" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:43:58.867Z</t>
+        </is>
+      </c>
+      <c r="I1715" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="n">
+        <v>32375</v>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>4110 Oak St</t>
+        </is>
+      </c>
+      <c r="D1716" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.24894071957, 'Longitude': -123.127040863037}</t>
+        </is>
+      </c>
+      <c r="E1716" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:54:14</t>
+        </is>
+      </c>
+      <c r="F1716" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:52:22.489Z</t>
+        </is>
+      </c>
+      <c r="G1716" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1716" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:13:19.073Z</t>
+        </is>
+      </c>
+      <c r="I1716" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="n">
+        <v>65564</v>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1717" t="inlineStr">
+        <is>
+          <t>5680 Oak St</t>
+        </is>
+      </c>
+      <c r="D1717" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234217162181, 'Longitude': -123.127684593201}</t>
+        </is>
+      </c>
+      <c r="E1717" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:54:14</t>
+        </is>
+      </c>
+      <c r="F1717" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:49:01.067Z</t>
+        </is>
+      </c>
+      <c r="G1717" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1717" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:37:38.272Z</t>
+        </is>
+      </c>
+      <c r="I1717" t="n">
+        <v>198.9</v>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="n">
+        <v>32372</v>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>6525 Oak St</t>
+        </is>
+      </c>
+      <c r="D1718" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226226639452, 'Longitude': -123.128687739372}</t>
+        </is>
+      </c>
+      <c r="E1718" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:54:14</t>
+        </is>
+      </c>
+      <c r="F1718" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:35:35.977Z</t>
+        </is>
+      </c>
+      <c r="G1718" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1718" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:33:23.261Z</t>
+        </is>
+      </c>
+      <c r="I1718" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1719" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1719" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E1719" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:54:14</t>
+        </is>
+      </c>
+      <c r="F1719" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:53:46.947Z</t>
+        </is>
+      </c>
+      <c r="G1719" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1719" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:44:27.069Z</t>
+        </is>
+      </c>
+      <c r="I1719" t="n">
+        <v>199.9</v>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="n">
+        <v>65566</v>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1720" t="inlineStr">
+        <is>
+          <t>8072 Granville St</t>
+        </is>
+      </c>
+      <c r="D1720" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.212495055855, 'Longitude': -123.14013004303}</t>
+        </is>
+      </c>
+      <c r="E1720" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:54:14</t>
+        </is>
+      </c>
+      <c r="F1720" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:15:06.805Z</t>
+        </is>
+      </c>
+      <c r="G1720" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1720" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:30:08.359Z</t>
+        </is>
+      </c>
+      <c r="I1720" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="n">
+        <v>65572</v>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1721" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D1721" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E1721" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:54:14</t>
+        </is>
+      </c>
+      <c r="F1721" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:52:19.053Z</t>
+        </is>
+      </c>
+      <c r="G1721" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1721" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:12:12.232Z</t>
+        </is>
+      </c>
+      <c r="I1721" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="n">
+        <v>65558</v>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1722" t="inlineStr">
+        <is>
+          <t>1390 E 33rd Ave</t>
+        </is>
+      </c>
+      <c r="D1722" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.240045470021, 'Longitude': -123.076765537262}</t>
+        </is>
+      </c>
+      <c r="E1722" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:56:35</t>
+        </is>
+      </c>
+      <c r="F1722" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:45:45.320Z</t>
+        </is>
+      </c>
+      <c r="G1722" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1722" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:19:17.486Z</t>
+        </is>
+      </c>
+      <c r="I1722" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="n">
+        <v>83394</v>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1723" t="inlineStr">
+        <is>
+          <t>4064 Fraser St</t>
+        </is>
+      </c>
+      <c r="D1723" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.248864, 'Longitude': -123.09002}</t>
+        </is>
+      </c>
+      <c r="E1723" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:56:35</t>
+        </is>
+      </c>
+      <c r="F1723" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:34:57.523Z</t>
+        </is>
+      </c>
+      <c r="G1723" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1723" t="inlineStr">
+        <is>
+          <t>2025-08-20T16:15:27.854Z</t>
+        </is>
+      </c>
+      <c r="I1723" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="n">
+        <v>65573</v>
+      </c>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1724" t="inlineStr">
+        <is>
+          <t>1396 E 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1724" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.232593005895, 'Longitude': -123.07728856802}</t>
+        </is>
+      </c>
+      <c r="E1724" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:56:35</t>
+        </is>
+      </c>
+      <c r="F1724" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:53:30.000Z</t>
+        </is>
+      </c>
+      <c r="G1724" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1724" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:28:44.531Z</t>
+        </is>
+      </c>
+      <c r="I1724" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="n">
+        <v>80714</v>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>Husky</t>
+        </is>
+      </c>
+      <c r="C1725" t="inlineStr">
+        <is>
+          <t>4933 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1725" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2397388, 'Longitude': -123.065748}</t>
+        </is>
+      </c>
+      <c r="E1725" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:56:35</t>
+        </is>
+      </c>
+      <c r="F1725" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:03:32.237Z</t>
+        </is>
+      </c>
+      <c r="G1725" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1725" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:17:49.745Z</t>
+        </is>
+      </c>
+      <c r="I1725" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="n">
+        <v>65552</v>
+      </c>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1726" t="inlineStr">
+        <is>
+          <t>2001 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1726" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.245312771918, 'Longitude': -123.064910173416}</t>
+        </is>
+      </c>
+      <c r="E1726" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:56:35</t>
+        </is>
+      </c>
+      <c r="F1726" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:16:23.714Z</t>
+        </is>
+      </c>
+      <c r="G1726" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1726" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:25:23.251Z</t>
+        </is>
+      </c>
+      <c r="I1726" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="n">
+        <v>65538</v>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1727" t="inlineStr">
+        <is>
+          <t>5252 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1727" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2372145, 'Longitude': -123.0650857}</t>
+        </is>
+      </c>
+      <c r="E1727" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:56:35</t>
+        </is>
+      </c>
+      <c r="F1727" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:04:13.990Z</t>
+        </is>
+      </c>
+      <c r="G1727" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1727" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:17:15.749Z</t>
+        </is>
+      </c>
+      <c r="I1727" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="n">
+        <v>90814</v>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1728" t="inlineStr">
+        <is>
+          <t>2277 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1728" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.242132845692, 'Longitude': -123.058204650879}</t>
+        </is>
+      </c>
+      <c r="E1728" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:56:35</t>
+        </is>
+      </c>
+      <c r="F1728" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:41:14.665Z</t>
+        </is>
+      </c>
+      <c r="G1728" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1728" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:17:33.155Z</t>
+        </is>
+      </c>
+      <c r="I1728" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="n">
+        <v>39768</v>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1729" t="inlineStr">
+        <is>
+          <t>5736 Main St</t>
+        </is>
+      </c>
+      <c r="D1729" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2325708, 'Longitude': -123.1010069}</t>
+        </is>
+      </c>
+      <c r="E1729" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:56:35</t>
+        </is>
+      </c>
+      <c r="F1729" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:53:26.149Z</t>
+        </is>
+      </c>
+      <c r="G1729" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1729" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:53:26.164Z</t>
+        </is>
+      </c>
+      <c r="I1729" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="n">
+        <v>9710</v>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1730" t="inlineStr">
+        <is>
+          <t>1295 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D1730" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259878978744, 'Longitude': -123.078074455261}</t>
+        </is>
+      </c>
+      <c r="E1730" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:56:35</t>
+        </is>
+      </c>
+      <c r="F1730" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:12:28.933Z</t>
+        </is>
+      </c>
+      <c r="G1730" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1730" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:16:42.500Z</t>
+        </is>
+      </c>
+      <c r="I1730" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="n">
+        <v>99146</v>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1731" t="inlineStr">
+        <is>
+          <t>1317 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D1731" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259758544957, 'Longitude': -123.077272474766}</t>
+        </is>
+      </c>
+      <c r="E1731" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:56:35</t>
+        </is>
+      </c>
+      <c r="F1731" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:04:11.246Z</t>
+        </is>
+      </c>
+      <c r="G1731" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1731" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:16:22.548Z</t>
+        </is>
+      </c>
+      <c r="I1731" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="n">
+        <v>65560</v>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1732" t="inlineStr">
+        <is>
+          <t>1289 E Broadway</t>
+        </is>
+      </c>
+      <c r="D1732" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.262693682723, 'Longitude': -123.078117370605}</t>
+        </is>
+      </c>
+      <c r="E1732" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:56:35</t>
+        </is>
+      </c>
+      <c r="F1732" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:45:44.998Z</t>
+        </is>
+      </c>
+      <c r="G1732" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1732" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:38:20.263Z</t>
+        </is>
+      </c>
+      <c r="I1732" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="n">
+        <v>65557</v>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1733" t="inlineStr">
+        <is>
+          <t>2120 Grandview Hwy S</t>
+        </is>
+      </c>
+      <c r="D1733" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2591601, 'Longitude': -123.0617495}</t>
+        </is>
+      </c>
+      <c r="E1733" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:56:35</t>
+        </is>
+      </c>
+      <c r="F1733" t="inlineStr">
+        <is>
+          <t>2025-08-21T11:42:13.938Z</t>
+        </is>
+      </c>
+      <c r="G1733" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H1733" t="inlineStr">
+        <is>
+          <t>2025-08-21T11:42:13.953Z</t>
+        </is>
+      </c>
+      <c r="I1733" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="n">
+        <v>65559</v>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1734" t="inlineStr">
+        <is>
+          <t>6502 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1734" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.224996944057, 'Longitude': -123.065521717072}</t>
+        </is>
+      </c>
+      <c r="E1734" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:56:35</t>
+        </is>
+      </c>
+      <c r="F1734" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:45:10.949Z</t>
+        </is>
+      </c>
+      <c r="G1734" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1734" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:06:56.250Z</t>
+        </is>
+      </c>
+      <c r="I1734" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="n">
+        <v>71502</v>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1735" t="inlineStr">
+        <is>
+          <t>2748 Main St</t>
+        </is>
+      </c>
+      <c r="D1735" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2604441, 'Longitude': -123.1005869}</t>
+        </is>
+      </c>
+      <c r="E1735" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:56:35</t>
+        </is>
+      </c>
+      <c r="F1735" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:02:56.887Z</t>
+        </is>
+      </c>
+      <c r="G1735" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1735" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:36:49.212Z</t>
+        </is>
+      </c>
+      <c r="I1735" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="n">
+        <v>89943</v>
+      </c>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1736" t="inlineStr">
+        <is>
+          <t>6808 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1736" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2220242, 'Longitude': -123.0654247}</t>
+        </is>
+      </c>
+      <c r="E1736" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:56:35</t>
+        </is>
+      </c>
+      <c r="F1736" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:51:23.033Z</t>
+        </is>
+      </c>
+      <c r="G1736" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1736" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:59:15.108Z</t>
+        </is>
+      </c>
+      <c r="I1736" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1737" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D1737" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E1737" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:56:35</t>
+        </is>
+      </c>
+      <c r="F1737" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:13:05.720Z</t>
+        </is>
+      </c>
+      <c r="G1737" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1737" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:57.027Z</t>
+        </is>
+      </c>
+      <c r="I1737" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="n">
+        <v>65537</v>
+      </c>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1738" t="inlineStr">
+        <is>
+          <t>2918 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1738" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.23608, 'Longitude': -123.0454858}</t>
+        </is>
+      </c>
+      <c r="E1738" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:56:35</t>
+        </is>
+      </c>
+      <c r="F1738" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:15:19.497Z</t>
+        </is>
+      </c>
+      <c r="G1738" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1738" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:24:44.587Z</t>
+        </is>
+      </c>
+      <c r="I1738" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1739" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D1739" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E1739" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:56:35</t>
+        </is>
+      </c>
+      <c r="F1739" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:12:59.398Z</t>
+        </is>
+      </c>
+      <c r="G1739" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1739" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:37.661Z</t>
+        </is>
+      </c>
+      <c r="I1739" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="n">
+        <v>65535</v>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1740" t="inlineStr">
+        <is>
+          <t>2605 E 49th Ave</t>
+        </is>
+      </c>
+      <c r="D1740" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2251291, 'Longitude': -123.0545048}</t>
+        </is>
+      </c>
+      <c r="E1740" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:56:35</t>
+        </is>
+      </c>
+      <c r="F1740" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:14:32.764Z</t>
+        </is>
+      </c>
+      <c r="G1740" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1740" t="inlineStr"/>
+      <c r="I1740" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="n">
+        <v>65539</v>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1741" t="inlineStr">
+        <is>
+          <t>2902 Grandview Hwy</t>
+        </is>
+      </c>
+      <c r="D1741" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2579053, 'Longitude': -123.0438464}</t>
+        </is>
+      </c>
+      <c r="E1741" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:56:35</t>
+        </is>
+      </c>
+      <c r="F1741" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:42:20.646Z</t>
+        </is>
+      </c>
+      <c r="G1741" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1741" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:53:20.781Z</t>
+        </is>
+      </c>
+      <c r="I1741" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="n">
+        <v>77015</v>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1742" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1742" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169873456637, 'Longitude': -123.091178619746}</t>
+        </is>
+      </c>
+      <c r="E1742" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:59:15</t>
+        </is>
+      </c>
+      <c r="F1742" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:31:23.403Z</t>
+        </is>
+      </c>
+      <c r="G1742" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1742" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:31:14.839Z</t>
+        </is>
+      </c>
+      <c r="I1742" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="n">
+        <v>65511</v>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1743" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1743" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E1743" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:59:15</t>
+        </is>
+      </c>
+      <c r="F1743" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:42:18.239Z</t>
+        </is>
+      </c>
+      <c r="G1743" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1743" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:42:18.255Z</t>
+        </is>
+      </c>
+      <c r="I1743" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="n">
+        <v>86650</v>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1744" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D1744" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169856952787, 'Longitude': -123.123961687088}</t>
+        </is>
+      </c>
+      <c r="E1744" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:59:15</t>
+        </is>
+      </c>
+      <c r="F1744" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:40:48.792Z</t>
+        </is>
+      </c>
+      <c r="G1744" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1744" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:05:27.032Z</t>
+        </is>
+      </c>
+      <c r="I1744" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="n">
+        <v>77218</v>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1745" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D1745" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.173339635958, 'Longitude': -123.124954104424}</t>
+        </is>
+      </c>
+      <c r="E1745" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:59:15</t>
+        </is>
+      </c>
+      <c r="F1745" t="inlineStr">
+        <is>
+          <t>2025-08-21T11:19:50.747Z</t>
+        </is>
+      </c>
+      <c r="G1745" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1745" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:04:48.775Z</t>
+        </is>
+      </c>
+      <c r="I1745" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="n">
+        <v>77228</v>
+      </c>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1746" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D1746" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1843249, 'Longitude': -123.1236078}</t>
+        </is>
+      </c>
+      <c r="E1746" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:59:15</t>
+        </is>
+      </c>
+      <c r="F1746" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:30:05.724Z</t>
+        </is>
+      </c>
+      <c r="G1746" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1746" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:29:09.481Z</t>
+        </is>
+      </c>
+      <c r="I1746" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="n">
+        <v>83384</v>
+      </c>
+      <c r="B1747" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1747" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1747" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192001, 'Longitude': -123.124004}</t>
+        </is>
+      </c>
+      <c r="E1747" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:59:15</t>
+        </is>
+      </c>
+      <c r="F1747" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:08:44.537Z</t>
+        </is>
+      </c>
+      <c r="G1747" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1747" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:11:11.242Z</t>
+        </is>
+      </c>
+      <c r="I1747" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="n">
+        <v>77202</v>
+      </c>
+      <c r="B1748" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1748" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D1748" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.162989071149, 'Longitude': -123.134229183197}</t>
+        </is>
+      </c>
+      <c r="E1748" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:59:15</t>
+        </is>
+      </c>
+      <c r="F1748" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:39:38.885Z</t>
+        </is>
+      </c>
+      <c r="G1748" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1748" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:47:01.715Z</t>
+        </is>
+      </c>
+      <c r="I1748" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="n">
+        <v>77243</v>
+      </c>
+      <c r="B1749" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1749" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D1749" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.179182137142, 'Longitude': -123.137152791023}</t>
+        </is>
+      </c>
+      <c r="E1749" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:59:15</t>
+        </is>
+      </c>
+      <c r="F1749" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:39:28.689Z</t>
+        </is>
+      </c>
+      <c r="G1749" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1749" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:55:29.368Z</t>
+        </is>
+      </c>
+      <c r="I1749" t="n">
+        <v>171.9</v>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="n">
+        <v>83387</v>
+      </c>
+      <c r="B1750" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1750" t="inlineStr">
+        <is>
+          <t>710 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1750" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21081995506, 'Longitude': -123.090755939484}</t>
+        </is>
+      </c>
+      <c r="E1750" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:59:15</t>
+        </is>
+      </c>
+      <c r="F1750" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:12:10.416Z</t>
+        </is>
+      </c>
+      <c r="G1750" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1750" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:00:12.496Z</t>
+        </is>
+      </c>
+      <c r="I1750" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="n">
+        <v>65551</v>
+      </c>
+      <c r="B1751" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1751" t="inlineStr">
+        <is>
+          <t>688 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1751" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210798928329, 'Longitude': -123.09152841568}</t>
+        </is>
+      </c>
+      <c r="E1751" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:59:15</t>
+        </is>
+      </c>
+      <c r="F1751" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:12:07.886Z</t>
+        </is>
+      </c>
+      <c r="G1751" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1751" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:59:47.832Z</t>
+        </is>
+      </c>
+      <c r="I1751" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="n">
+        <v>77235</v>
+      </c>
+      <c r="B1752" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C1752" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1752" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.18409178594, 'Longitude': -123.136823830688}</t>
+        </is>
+      </c>
+      <c r="E1752" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:59:15</t>
+        </is>
+      </c>
+      <c r="F1752" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:58:49.477Z</t>
+        </is>
+      </c>
+      <c r="G1752" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1752" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:58:49.493Z</t>
+        </is>
+      </c>
+      <c r="I1752" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="n">
+        <v>82925</v>
+      </c>
+      <c r="B1753" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1753" t="inlineStr">
+        <is>
+          <t>350 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1753" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210245, 'Longitude': -123.099328}</t>
+        </is>
+      </c>
+      <c r="E1753" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:59:15</t>
+        </is>
+      </c>
+      <c r="F1753" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:10:04.520Z</t>
+        </is>
+      </c>
+      <c r="G1753" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1753" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:59:54.798Z</t>
+        </is>
+      </c>
+      <c r="I1753" t="n">
+        <v>171.9</v>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="n">
+        <v>109205</v>
+      </c>
+      <c r="B1754" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1754" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D1754" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.133556536531, 'Longitude': -123.092424273491}</t>
+        </is>
+      </c>
+      <c r="E1754" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:59:15</t>
+        </is>
+      </c>
+      <c r="F1754" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:11:34.348Z</t>
+        </is>
+      </c>
+      <c r="G1754" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1754" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:11:34.394Z</t>
+        </is>
+      </c>
+      <c r="I1754" t="n">
+        <v>175.9</v>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="n">
+        <v>65540</v>
+      </c>
+      <c r="B1755" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1755" t="inlineStr">
+        <is>
+          <t>196 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1755" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2106867, 'Longitude': -123.1027436}</t>
+        </is>
+      </c>
+      <c r="E1755" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:59:15</t>
+        </is>
+      </c>
+      <c r="F1755" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:09:45.288Z</t>
+        </is>
+      </c>
+      <c r="G1755" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1755" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:00:05.037Z</t>
+        </is>
+      </c>
+      <c r="I1755" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="n">
+        <v>65512</v>
+      </c>
+      <c r="B1756" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1756" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1756" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1328393, 'Longitude': -123.0926312}</t>
+        </is>
+      </c>
+      <c r="E1756" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:59:15</t>
+        </is>
+      </c>
+      <c r="F1756" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:11:43.494Z</t>
+        </is>
+      </c>
+      <c r="G1756" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1756" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:11:43.509Z</t>
+        </is>
+      </c>
+      <c r="I1756" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="n">
+        <v>77205</v>
+      </c>
+      <c r="B1757" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1757" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1757" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1558882, 'Longitude': -123.1369625}</t>
+        </is>
+      </c>
+      <c r="E1757" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:59:15</t>
+        </is>
+      </c>
+      <c r="F1757" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:52:57.153Z</t>
+        </is>
+      </c>
+      <c r="G1757" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1757" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:09:47.598Z</t>
+        </is>
+      </c>
+      <c r="I1757" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B1758" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1758" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D1758" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E1758" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:59:15</t>
+        </is>
+      </c>
+      <c r="F1758" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:12:59.398Z</t>
+        </is>
+      </c>
+      <c r="G1758" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1758" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:37.661Z</t>
+        </is>
+      </c>
+      <c r="I1758" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B1759" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1759" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D1759" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E1759" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:59:15</t>
+        </is>
+      </c>
+      <c r="F1759" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:13:05.720Z</t>
+        </is>
+      </c>
+      <c r="G1759" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1759" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:57.027Z</t>
+        </is>
+      </c>
+      <c r="I1759" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" t="n">
+        <v>65556</v>
+      </c>
+      <c r="B1760" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1760" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1760" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20806537721, 'Longitude': -123.123285770416}</t>
+        </is>
+      </c>
+      <c r="E1760" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:59:15</t>
+        </is>
+      </c>
+      <c r="F1760" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:08:32.784Z</t>
+        </is>
+      </c>
+      <c r="G1760" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1760" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:46.640Z</t>
+        </is>
+      </c>
+      <c r="I1760" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="n">
+        <v>86937</v>
+      </c>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1761" t="inlineStr">
+        <is>
+          <t>8655 Boundary Rd</t>
+        </is>
+      </c>
+      <c r="D1761" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20476, 'Longitude': -123.02398}</t>
+        </is>
+      </c>
+      <c r="E1761" t="inlineStr">
+        <is>
+          <t>2025-08-21 08:59:15</t>
+        </is>
+      </c>
+      <c r="F1761" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:29:04.761Z</t>
+        </is>
+      </c>
+      <c r="G1761" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1761" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:06:44.227Z</t>
+        </is>
+      </c>
+      <c r="I1761" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="n">
+        <v>65515</v>
+      </c>
+      <c r="B1762" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1762" t="inlineStr">
+        <is>
+          <t>4011 Francis Rd</t>
+        </is>
+      </c>
+      <c r="D1762" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.14867500071, 'Longitude': -123.180856704712}</t>
+        </is>
+      </c>
+      <c r="E1762" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:01:36</t>
+        </is>
+      </c>
+      <c r="F1762" t="inlineStr">
+        <is>
+          <t>2025-08-21T11:09:15.092Z</t>
+        </is>
+      </c>
+      <c r="G1762" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1762" t="inlineStr">
+        <is>
+          <t>2025-08-21T11:09:15.123Z</t>
+        </is>
+      </c>
+      <c r="I1762" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="n">
+        <v>77205</v>
+      </c>
+      <c r="B1763" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1763" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1763" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1558882, 'Longitude': -123.1369625}</t>
+        </is>
+      </c>
+      <c r="E1763" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:01:36</t>
+        </is>
+      </c>
+      <c r="F1763" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:52:57.153Z</t>
+        </is>
+      </c>
+      <c r="G1763" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1763" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:09:47.598Z</t>
+        </is>
+      </c>
+      <c r="I1763" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" t="n">
+        <v>77223</v>
+      </c>
+      <c r="B1764" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1764" t="inlineStr">
+        <is>
+          <t>7991 No 1 Rd</t>
+        </is>
+      </c>
+      <c r="D1764" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.155888686563, 'Longitude': -123.181414604187}</t>
+        </is>
+      </c>
+      <c r="E1764" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:01:36</t>
+        </is>
+      </c>
+      <c r="F1764" t="inlineStr"/>
+      <c r="G1764" t="inlineStr"/>
+      <c r="H1764" t="inlineStr"/>
+      <c r="I1764" t="inlineStr"/>
+    </row>
+    <row r="1765">
+      <c r="A1765" t="n">
+        <v>65514</v>
+      </c>
+      <c r="B1765" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1765" t="inlineStr">
+        <is>
+          <t>7980 Williams Rd</t>
+        </is>
+      </c>
+      <c r="D1765" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.140582914547, 'Longitude': -123.137168884277}</t>
+        </is>
+      </c>
+      <c r="E1765" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:01:36</t>
+        </is>
+      </c>
+      <c r="F1765" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:23:11.584Z</t>
+        </is>
+      </c>
+      <c r="G1765" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1765" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:04:20.233Z</t>
+        </is>
+      </c>
+      <c r="I1765" t="n">
+        <v>175.9</v>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" t="n">
+        <v>77232</v>
+      </c>
+      <c r="B1766" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1766" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900 Westminster Hwy </t>
+        </is>
+      </c>
+      <c r="D1766" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1698419, 'Longitude': -123.159282}</t>
+        </is>
+      </c>
+      <c r="E1766" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:01:36</t>
+        </is>
+      </c>
+      <c r="F1766" t="inlineStr">
+        <is>
+          <t>2025-08-21T11:15:53.866Z</t>
+        </is>
+      </c>
+      <c r="G1766" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1766" t="inlineStr">
+        <is>
+          <t>2025-08-21T11:15:53.929Z</t>
+        </is>
+      </c>
+      <c r="I1766" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="n">
+        <v>77202</v>
+      </c>
+      <c r="B1767" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1767" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D1767" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.162989071149, 'Longitude': -123.134229183197}</t>
+        </is>
+      </c>
+      <c r="E1767" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:01:36</t>
+        </is>
+      </c>
+      <c r="F1767" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:39:38.885Z</t>
+        </is>
+      </c>
+      <c r="G1767" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1767" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:47:01.715Z</t>
+        </is>
+      </c>
+      <c r="I1767" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" t="n">
+        <v>86650</v>
+      </c>
+      <c r="B1768" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1768" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D1768" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169856952787, 'Longitude': -123.123961687088}</t>
+        </is>
+      </c>
+      <c r="E1768" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:01:36</t>
+        </is>
+      </c>
+      <c r="F1768" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:40:48.792Z</t>
+        </is>
+      </c>
+      <c r="G1768" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1768" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:05:27.032Z</t>
+        </is>
+      </c>
+      <c r="I1768" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" t="n">
+        <v>77218</v>
+      </c>
+      <c r="B1769" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1769" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D1769" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.173339635958, 'Longitude': -123.124954104424}</t>
+        </is>
+      </c>
+      <c r="E1769" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:01:36</t>
+        </is>
+      </c>
+      <c r="F1769" t="inlineStr">
+        <is>
+          <t>2025-08-21T11:19:50.747Z</t>
+        </is>
+      </c>
+      <c r="G1769" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1769" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:04:48.775Z</t>
+        </is>
+      </c>
+      <c r="I1769" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" t="n">
+        <v>77243</v>
+      </c>
+      <c r="B1770" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1770" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D1770" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.179182137142, 'Longitude': -123.137152791023}</t>
+        </is>
+      </c>
+      <c r="E1770" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:01:36</t>
+        </is>
+      </c>
+      <c r="F1770" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:39:28.689Z</t>
+        </is>
+      </c>
+      <c r="G1770" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1770" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:55:29.368Z</t>
+        </is>
+      </c>
+      <c r="I1770" t="n">
+        <v>171.9</v>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="n">
+        <v>77235</v>
+      </c>
+      <c r="B1771" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C1771" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1771" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.18409178594, 'Longitude': -123.136823830688}</t>
+        </is>
+      </c>
+      <c r="E1771" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:01:36</t>
+        </is>
+      </c>
+      <c r="F1771" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:58:49.477Z</t>
+        </is>
+      </c>
+      <c r="G1771" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1771" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:58:49.493Z</t>
+        </is>
+      </c>
+      <c r="I1771" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" t="n">
+        <v>77228</v>
+      </c>
+      <c r="B1772" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1772" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D1772" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1843249, 'Longitude': -123.1236078}</t>
+        </is>
+      </c>
+      <c r="E1772" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:01:36</t>
+        </is>
+      </c>
+      <c r="F1772" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:30:05.724Z</t>
+        </is>
+      </c>
+      <c r="G1772" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1772" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:29:09.481Z</t>
+        </is>
+      </c>
+      <c r="I1772" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" t="n">
+        <v>69163</v>
+      </c>
+      <c r="B1773" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1773" t="inlineStr">
+        <is>
+          <t>5111 Grant McConachie Way</t>
+        </is>
+      </c>
+      <c r="D1773" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192919, 'Longitude': -123.166797}</t>
+        </is>
+      </c>
+      <c r="E1773" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:01:36</t>
+        </is>
+      </c>
+      <c r="F1773" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:04:38.760Z</t>
+        </is>
+      </c>
+      <c r="G1773" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1773" t="inlineStr">
+        <is>
+          <t>2025-08-21T11:23:53.653Z</t>
+        </is>
+      </c>
+      <c r="I1773" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="n">
+        <v>109205</v>
+      </c>
+      <c r="B1774" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1774" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D1774" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.133556536531, 'Longitude': -123.092424273491}</t>
+        </is>
+      </c>
+      <c r="E1774" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:01:36</t>
+        </is>
+      </c>
+      <c r="F1774" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:11:34.348Z</t>
+        </is>
+      </c>
+      <c r="G1774" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1774" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:11:34.394Z</t>
+        </is>
+      </c>
+      <c r="I1774" t="n">
+        <v>175.9</v>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="n">
+        <v>65512</v>
+      </c>
+      <c r="B1775" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1775" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1775" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1328393, 'Longitude': -123.0926312}</t>
+        </is>
+      </c>
+      <c r="E1775" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:01:36</t>
+        </is>
+      </c>
+      <c r="F1775" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:11:43.494Z</t>
+        </is>
+      </c>
+      <c r="G1775" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1775" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:11:43.509Z</t>
+        </is>
+      </c>
+      <c r="I1775" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="n">
+        <v>83384</v>
+      </c>
+      <c r="B1776" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1776" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1776" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192001, 'Longitude': -123.124004}</t>
+        </is>
+      </c>
+      <c r="E1776" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:01:36</t>
+        </is>
+      </c>
+      <c r="F1776" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:08:44.537Z</t>
+        </is>
+      </c>
+      <c r="G1776" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1776" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:11:11.242Z</t>
+        </is>
+      </c>
+      <c r="I1776" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="n">
+        <v>77015</v>
+      </c>
+      <c r="B1777" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1777" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1777" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169873456637, 'Longitude': -123.091178619746}</t>
+        </is>
+      </c>
+      <c r="E1777" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:01:36</t>
+        </is>
+      </c>
+      <c r="F1777" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:31:23.403Z</t>
+        </is>
+      </c>
+      <c r="G1777" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1777" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:31:14.839Z</t>
+        </is>
+      </c>
+      <c r="I1777" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="n">
+        <v>107728</v>
+      </c>
+      <c r="B1778" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1778" t="inlineStr">
+        <is>
+          <t>8884 Granville St</t>
+        </is>
+      </c>
+      <c r="D1778" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2054215, 'Longitude': -123.1401677}</t>
+        </is>
+      </c>
+      <c r="E1778" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:01:36</t>
+        </is>
+      </c>
+      <c r="F1778" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:06:48.502Z</t>
+        </is>
+      </c>
+      <c r="G1778" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1778" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:13.470Z</t>
+        </is>
+      </c>
+      <c r="I1778" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="n">
+        <v>65572</v>
+      </c>
+      <c r="B1779" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1779" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D1779" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E1779" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:01:36</t>
+        </is>
+      </c>
+      <c r="F1779" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:52:19.053Z</t>
+        </is>
+      </c>
+      <c r="G1779" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1779" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:12:12.232Z</t>
+        </is>
+      </c>
+      <c r="I1779" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="n">
+        <v>65511</v>
+      </c>
+      <c r="B1780" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1780" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1780" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E1780" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:01:36</t>
+        </is>
+      </c>
+      <c r="F1780" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:42:18.239Z</t>
+        </is>
+      </c>
+      <c r="G1780" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1780" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:42:18.255Z</t>
+        </is>
+      </c>
+      <c r="I1780" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="n">
+        <v>65556</v>
+      </c>
+      <c r="B1781" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1781" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1781" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20806537721, 'Longitude': -123.123285770416}</t>
+        </is>
+      </c>
+      <c r="E1781" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:01:36</t>
+        </is>
+      </c>
+      <c r="F1781" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:08:32.784Z</t>
+        </is>
+      </c>
+      <c r="G1781" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1781" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:46.640Z</t>
+        </is>
+      </c>
+      <c r="I1781" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" t="n">
+        <v>32378</v>
+      </c>
+      <c r="B1782" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1782" t="inlineStr">
+        <is>
+          <t>1613 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1782" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3288556, 'Longitude': -123.1592779}</t>
+        </is>
+      </c>
+      <c r="E1782" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:04:07</t>
+        </is>
+      </c>
+      <c r="F1782" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:23:48.032Z</t>
+        </is>
+      </c>
+      <c r="G1782" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1782" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:23:48.047Z</t>
+        </is>
+      </c>
+      <c r="I1782" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" t="n">
+        <v>98624</v>
+      </c>
+      <c r="B1783" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1783" t="inlineStr">
+        <is>
+          <t>1503 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1783" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.328484, 'Longitude': -123.15694}</t>
+        </is>
+      </c>
+      <c r="E1783" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:04:07</t>
+        </is>
+      </c>
+      <c r="F1783" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:15:01.270Z</t>
+        </is>
+      </c>
+      <c r="G1783" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1783" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:24:13.558Z</t>
+        </is>
+      </c>
+      <c r="I1783" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" t="n">
+        <v>98626</v>
+      </c>
+      <c r="B1784" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1784" t="inlineStr">
+        <is>
+          <t>1490 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1784" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.328176303121, 'Longitude': -123.1565746665}</t>
+        </is>
+      </c>
+      <c r="E1784" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:04:07</t>
+        </is>
+      </c>
+      <c r="F1784" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:14:31.488Z</t>
+        </is>
+      </c>
+      <c r="G1784" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1784" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:57:16.589Z</t>
+        </is>
+      </c>
+      <c r="I1784" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" t="n">
+        <v>65575</v>
+      </c>
+      <c r="B1785" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1785" t="inlineStr">
+        <is>
+          <t>1305 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1785" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.327918987512, 'Longitude': -123.151953220367}</t>
+        </is>
+      </c>
+      <c r="E1785" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:04:07</t>
+        </is>
+      </c>
+      <c r="F1785" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:13:52.915Z</t>
+        </is>
+      </c>
+      <c r="G1785" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1785" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:58:23.220Z</t>
+        </is>
+      </c>
+      <c r="I1785" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" t="n">
+        <v>65505</v>
+      </c>
+      <c r="B1786" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1786" t="inlineStr">
+        <is>
+          <t>1731 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D1786" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.325583506404, 'Longitude': -123.121590614319}</t>
+        </is>
+      </c>
+      <c r="E1786" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:04:07</t>
+        </is>
+      </c>
+      <c r="F1786" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:56:52.357Z</t>
+        </is>
+      </c>
+      <c r="G1786" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1786" t="inlineStr"/>
+      <c r="I1786" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" t="n">
+        <v>65503</v>
+      </c>
+      <c r="B1787" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1787" t="inlineStr">
+        <is>
+          <t>1980 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1787" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.324534601594, 'Longitude': -123.121654987335}</t>
+        </is>
+      </c>
+      <c r="E1787" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:04:07</t>
+        </is>
+      </c>
+      <c r="F1787" t="inlineStr">
+        <is>
+          <t>2025-08-21T12:34:34.230Z</t>
+        </is>
+      </c>
+      <c r="G1787" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1787" t="inlineStr"/>
+      <c r="I1787" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" t="n">
+        <v>75407</v>
+      </c>
+      <c r="B1788" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1788" t="inlineStr">
+        <is>
+          <t>2698 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D1788" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3343054, 'Longitude': -123.1157865}</t>
+        </is>
+      </c>
+      <c r="E1788" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:04:07</t>
+        </is>
+      </c>
+      <c r="F1788" t="inlineStr">
+        <is>
+          <t>2025-08-21T12:33:20.396Z</t>
+        </is>
+      </c>
+      <c r="G1788" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1788" t="inlineStr"/>
+      <c r="I1788" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" t="n">
+        <v>75406</v>
+      </c>
+      <c r="B1789" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1789" t="inlineStr">
+        <is>
+          <t>1198 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1789" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.323975176559, 'Longitude': -123.107525110245}</t>
+        </is>
+      </c>
+      <c r="E1789" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:04:07</t>
+        </is>
+      </c>
+      <c r="F1789" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:12:38.776Z</t>
+        </is>
+      </c>
+      <c r="G1789" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1789" t="inlineStr"/>
+      <c r="I1789" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" t="n">
+        <v>75409</v>
+      </c>
+      <c r="B1790" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1790" t="inlineStr">
+        <is>
+          <t>3150 Edgemont Blvd</t>
+        </is>
+      </c>
+      <c r="D1790" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.338128, 'Longitude': -123.1021338}</t>
+        </is>
+      </c>
+      <c r="E1790" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:04:07</t>
+        </is>
+      </c>
+      <c r="F1790" t="inlineStr"/>
+      <c r="G1790" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1790" t="inlineStr"/>
+      <c r="I1790" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" t="n">
+        <v>98622</v>
+      </c>
+      <c r="B1791" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1791" t="inlineStr">
+        <is>
+          <t>3690 Westmount Rd</t>
+        </is>
+      </c>
+      <c r="D1791" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3459143, 'Longitude': -123.2177286}</t>
+        </is>
+      </c>
+      <c r="E1791" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:04:07</t>
+        </is>
+      </c>
+      <c r="F1791" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:24:35.951Z</t>
+        </is>
+      </c>
+      <c r="G1791" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1791" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:08:16.374Z</t>
+        </is>
+      </c>
+      <c r="I1791" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" t="n">
+        <v>18803</v>
+      </c>
+      <c r="B1792" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1792" t="inlineStr">
+        <is>
+          <t>2501 Westview Dr</t>
+        </is>
+      </c>
+      <c r="D1792" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.332617583893, 'Longitude': -123.088846206665}</t>
+        </is>
+      </c>
+      <c r="E1792" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:04:07</t>
+        </is>
+      </c>
+      <c r="F1792" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:02:33.190Z</t>
+        </is>
+      </c>
+      <c r="G1792" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1792" t="inlineStr"/>
+      <c r="I1792" t="inlineStr"/>
+    </row>
+    <row r="1793">
+      <c r="A1793" t="n">
+        <v>18804</v>
+      </c>
+      <c r="B1793" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1793" t="inlineStr">
+        <is>
+          <t>660 3rd St  W</t>
+        </is>
+      </c>
+      <c r="D1793" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319671, 'Longitude': -123.0902808}</t>
+        </is>
+      </c>
+      <c r="E1793" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:04:07</t>
+        </is>
+      </c>
+      <c r="F1793" t="inlineStr">
+        <is>
+          <t>2025-08-21T09:25:09.433Z</t>
+        </is>
+      </c>
+      <c r="G1793" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1793" t="inlineStr">
+        <is>
+          <t>2025-08-19T17:13:18.796Z</t>
+        </is>
+      </c>
+      <c r="I1793" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" t="n">
+        <v>32349</v>
+      </c>
+      <c r="B1794" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1794" t="inlineStr">
+        <is>
+          <t>106 W Queens St</t>
+        </is>
+      </c>
+      <c r="D1794" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.336724992343, 'Longitude': -123.072506189346}</t>
+        </is>
+      </c>
+      <c r="E1794" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:04:07</t>
+        </is>
+      </c>
+      <c r="F1794" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:36:38.345Z</t>
+        </is>
+      </c>
+      <c r="G1794" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1794" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:31:29.513Z</t>
+        </is>
+      </c>
+      <c r="I1794" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" t="n">
+        <v>18509</v>
+      </c>
+      <c r="B1795" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1795" t="inlineStr">
+        <is>
+          <t>2305 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D1795" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3306729, 'Longitude': -123.0728536}</t>
+        </is>
+      </c>
+      <c r="E1795" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:04:07</t>
+        </is>
+      </c>
+      <c r="F1795" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:21:45.920Z</t>
+        </is>
+      </c>
+      <c r="G1795" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1795" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:21:46.014Z</t>
+        </is>
+      </c>
+      <c r="I1795" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" t="n">
+        <v>22117</v>
+      </c>
+      <c r="B1796" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1796" t="inlineStr">
+        <is>
+          <t>1245 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D1796" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319695364751, 'Longitude': -123.07279586792}</t>
+        </is>
+      </c>
+      <c r="E1796" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:04:07</t>
+        </is>
+      </c>
+      <c r="F1796" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:55:32.582Z</t>
+        </is>
+      </c>
+      <c r="G1796" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1796" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:54:45.752Z</t>
+        </is>
+      </c>
+      <c r="I1796" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B1797" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1797" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1797" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E1797" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:04:07</t>
+        </is>
+      </c>
+      <c r="F1797" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:53:46.947Z</t>
+        </is>
+      </c>
+      <c r="G1797" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1797" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:44:27.069Z</t>
+        </is>
+      </c>
+      <c r="I1797" t="n">
+        <v>199.9</v>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B1798" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1798" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1798" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E1798" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:04:07</t>
+        </is>
+      </c>
+      <c r="F1798" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:59:15.632Z</t>
+        </is>
+      </c>
+      <c r="G1798" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1798" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:11.555Z</t>
+        </is>
+      </c>
+      <c r="I1798" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B1799" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1799" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1799" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E1799" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:04:07</t>
+        </is>
+      </c>
+      <c r="F1799" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:38:06.221Z</t>
+        </is>
+      </c>
+      <c r="G1799" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1799" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:22.999Z</t>
+        </is>
+      </c>
+      <c r="I1799" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B1800" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1800" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D1800" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E1800" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:04:07</t>
+        </is>
+      </c>
+      <c r="F1800" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:39:01.391Z</t>
+        </is>
+      </c>
+      <c r="G1800" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1800" t="inlineStr"/>
+      <c r="I1800" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B1801" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1801" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1801" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E1801" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:04:07</t>
+        </is>
+      </c>
+      <c r="F1801" t="inlineStr">
+        <is>
+          <t>2025-08-21T12:33:20.103Z</t>
+        </is>
+      </c>
+      <c r="G1801" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1801" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:16:34.188Z</t>
+        </is>
+      </c>
+      <c r="I1801" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" t="n">
+        <v>18509</v>
+      </c>
+      <c r="B1802" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1802" t="inlineStr">
+        <is>
+          <t>2305 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D1802" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3306729, 'Longitude': -123.0728536}</t>
+        </is>
+      </c>
+      <c r="E1802" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:06:33</t>
+        </is>
+      </c>
+      <c r="F1802" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:21:45.920Z</t>
+        </is>
+      </c>
+      <c r="G1802" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1802" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:21:46.014Z</t>
+        </is>
+      </c>
+      <c r="I1802" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" t="n">
+        <v>22117</v>
+      </c>
+      <c r="B1803" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1803" t="inlineStr">
+        <is>
+          <t>1245 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D1803" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319695364751, 'Longitude': -123.07279586792}</t>
+        </is>
+      </c>
+      <c r="E1803" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:06:33</t>
+        </is>
+      </c>
+      <c r="F1803" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:55:32.582Z</t>
+        </is>
+      </c>
+      <c r="G1803" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1803" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:54:45.752Z</t>
+        </is>
+      </c>
+      <c r="I1803" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="A1804" t="n">
+        <v>32349</v>
+      </c>
+      <c r="B1804" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1804" t="inlineStr">
+        <is>
+          <t>106 W Queens St</t>
+        </is>
+      </c>
+      <c r="D1804" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.336724992343, 'Longitude': -123.072506189346}</t>
+        </is>
+      </c>
+      <c r="E1804" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:06:33</t>
+        </is>
+      </c>
+      <c r="F1804" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:36:38.345Z</t>
+        </is>
+      </c>
+      <c r="G1804" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1804" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:31:29.513Z</t>
+        </is>
+      </c>
+      <c r="I1804" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1805">
+      <c r="A1805" t="n">
+        <v>18803</v>
+      </c>
+      <c r="B1805" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1805" t="inlineStr">
+        <is>
+          <t>2501 Westview Dr</t>
+        </is>
+      </c>
+      <c r="D1805" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.332617583893, 'Longitude': -123.088846206665}</t>
+        </is>
+      </c>
+      <c r="E1805" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:06:33</t>
+        </is>
+      </c>
+      <c r="F1805" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:02:33.190Z</t>
+        </is>
+      </c>
+      <c r="G1805" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1805" t="inlineStr"/>
+      <c r="I1805" t="inlineStr"/>
+    </row>
+    <row r="1806">
+      <c r="A1806" t="n">
+        <v>18804</v>
+      </c>
+      <c r="B1806" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1806" t="inlineStr">
+        <is>
+          <t>660 3rd St  W</t>
+        </is>
+      </c>
+      <c r="D1806" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319671, 'Longitude': -123.0902808}</t>
+        </is>
+      </c>
+      <c r="E1806" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:06:33</t>
+        </is>
+      </c>
+      <c r="F1806" t="inlineStr">
+        <is>
+          <t>2025-08-21T09:25:09.433Z</t>
+        </is>
+      </c>
+      <c r="G1806" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1806" t="inlineStr">
+        <is>
+          <t>2025-08-19T17:13:18.796Z</t>
+        </is>
+      </c>
+      <c r="I1806" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="A1807" t="n">
+        <v>75409</v>
+      </c>
+      <c r="B1807" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1807" t="inlineStr">
+        <is>
+          <t>3150 Edgemont Blvd</t>
+        </is>
+      </c>
+      <c r="D1807" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.338128, 'Longitude': -123.1021338}</t>
+        </is>
+      </c>
+      <c r="E1807" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:06:33</t>
+        </is>
+      </c>
+      <c r="F1807" t="inlineStr"/>
+      <c r="G1807" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1807" t="inlineStr"/>
+      <c r="I1807" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="A1808" t="n">
+        <v>75406</v>
+      </c>
+      <c r="B1808" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1808" t="inlineStr">
+        <is>
+          <t>1198 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1808" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.323975176559, 'Longitude': -123.107525110245}</t>
+        </is>
+      </c>
+      <c r="E1808" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:06:33</t>
+        </is>
+      </c>
+      <c r="F1808" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:12:38.776Z</t>
+        </is>
+      </c>
+      <c r="G1808" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1808" t="inlineStr"/>
+      <c r="I1808" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1809">
+      <c r="A1809" t="n">
+        <v>18512</v>
+      </c>
+      <c r="B1809" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1809" t="inlineStr">
+        <is>
+          <t>2747 Mountain Hwy</t>
+        </is>
+      </c>
+      <c r="D1809" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.333694, 'Longitude': -123.038315}</t>
+        </is>
+      </c>
+      <c r="E1809" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:06:33</t>
+        </is>
+      </c>
+      <c r="F1809" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:49:57.442Z</t>
+        </is>
+      </c>
+      <c r="G1809" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1809" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:58:00.492Z</t>
+        </is>
+      </c>
+      <c r="I1809" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1810">
+      <c r="A1810" t="n">
+        <v>9706</v>
+      </c>
+      <c r="B1810" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1810" t="inlineStr">
+        <is>
+          <t>2979 Mountain Hwy</t>
+        </is>
+      </c>
+      <c r="D1810" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3356515, 'Longitude': -123.038272}</t>
+        </is>
+      </c>
+      <c r="E1810" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:06:33</t>
+        </is>
+      </c>
+      <c r="F1810" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:49:25.636Z</t>
+        </is>
+      </c>
+      <c r="G1810" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1810" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:57:54.599Z</t>
+        </is>
+      </c>
+      <c r="I1810" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1811">
+      <c r="A1811" t="n">
+        <v>32289</v>
+      </c>
+      <c r="B1811" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1811" t="inlineStr">
+        <is>
+          <t>1270 Lynn Valley Rd</t>
+        </is>
+      </c>
+      <c r="D1811" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.337231840266, 'Longitude': -123.038763999939}</t>
+        </is>
+      </c>
+      <c r="E1811" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:06:33</t>
+        </is>
+      </c>
+      <c r="F1811" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:49:29.270Z</t>
+        </is>
+      </c>
+      <c r="G1811" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1811" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:57:47.660Z</t>
+        </is>
+      </c>
+      <c r="I1811" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" t="n">
+        <v>75407</v>
+      </c>
+      <c r="B1812" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1812" t="inlineStr">
+        <is>
+          <t>2698 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D1812" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3343054, 'Longitude': -123.1157865}</t>
+        </is>
+      </c>
+      <c r="E1812" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:06:33</t>
+        </is>
+      </c>
+      <c r="F1812" t="inlineStr">
+        <is>
+          <t>2025-08-21T12:33:20.396Z</t>
+        </is>
+      </c>
+      <c r="G1812" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1812" t="inlineStr"/>
+      <c r="I1812" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" t="n">
+        <v>65505</v>
+      </c>
+      <c r="B1813" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1813" t="inlineStr">
+        <is>
+          <t>1731 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D1813" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.325583506404, 'Longitude': -123.121590614319}</t>
+        </is>
+      </c>
+      <c r="E1813" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:06:33</t>
+        </is>
+      </c>
+      <c r="F1813" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:56:52.357Z</t>
+        </is>
+      </c>
+      <c r="G1813" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="H1813" t="inlineStr"/>
+      <c r="I1813" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" t="n">
+        <v>65503</v>
+      </c>
+      <c r="B1814" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1814" t="inlineStr">
+        <is>
+          <t>1980 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1814" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.324534601594, 'Longitude': -123.121654987335}</t>
+        </is>
+      </c>
+      <c r="E1814" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:06:33</t>
+        </is>
+      </c>
+      <c r="F1814" t="inlineStr">
+        <is>
+          <t>2025-08-21T12:34:34.230Z</t>
+        </is>
+      </c>
+      <c r="G1814" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1814" t="inlineStr"/>
+      <c r="I1814" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" t="n">
+        <v>18510</v>
+      </c>
+      <c r="B1815" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1815" t="inlineStr">
+        <is>
+          <t>1490 Main St</t>
+        </is>
+      </c>
+      <c r="D1815" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3057944, 'Longitude': -123.0328688}</t>
+        </is>
+      </c>
+      <c r="E1815" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:06:33</t>
+        </is>
+      </c>
+      <c r="F1815" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:42:29.198Z</t>
+        </is>
+      </c>
+      <c r="G1815" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1815" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:22:15.178Z</t>
+        </is>
+      </c>
+      <c r="I1815" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" t="n">
+        <v>69296</v>
+      </c>
+      <c r="B1816" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1816" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185 Mountain Hwy </t>
+        </is>
+      </c>
+      <c r="D1816" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.305048881232, 'Longitude': -123.0324447155}</t>
+        </is>
+      </c>
+      <c r="E1816" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:06:33</t>
+        </is>
+      </c>
+      <c r="F1816" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:41:01.789Z</t>
+        </is>
+      </c>
+      <c r="G1816" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1816" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:22:20.808Z</t>
+        </is>
+      </c>
+      <c r="I1816" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" t="n">
+        <v>65506</v>
+      </c>
+      <c r="B1817" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1817" t="inlineStr">
+        <is>
+          <t>333 Seymour Blvd</t>
+        </is>
+      </c>
+      <c r="D1817" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.311498347051, 'Longitude': -123.022198677063}</t>
+        </is>
+      </c>
+      <c r="E1817" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:06:33</t>
+        </is>
+      </c>
+      <c r="F1817" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:55:45.837Z</t>
+        </is>
+      </c>
+      <c r="G1817" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1817" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:55:45.868Z</t>
+        </is>
+      </c>
+      <c r="I1817" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" t="n">
+        <v>98513</v>
+      </c>
+      <c r="B1818" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1818" t="inlineStr">
+        <is>
+          <t>1955 Powell St</t>
+        </is>
+      </c>
+      <c r="D1818" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.28504, 'Longitude': -123.0643977}</t>
+        </is>
+      </c>
+      <c r="E1818" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:06:33</t>
+        </is>
+      </c>
+      <c r="F1818" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:38:54.379Z</t>
+        </is>
+      </c>
+      <c r="G1818" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1818" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:59:12.373Z</t>
+        </is>
+      </c>
+      <c r="I1818" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" t="n">
+        <v>75410</v>
+      </c>
+      <c r="B1819" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1819" t="inlineStr">
+        <is>
+          <t>2177 Dollarton Hwy</t>
+        </is>
+      </c>
+      <c r="D1819" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.305160809746, 'Longitude': -123.014302253723}</t>
+        </is>
+      </c>
+      <c r="E1819" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:06:33</t>
+        </is>
+      </c>
+      <c r="F1819" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:09:28.635Z</t>
+        </is>
+      </c>
+      <c r="G1819" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1819" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:09:28.667Z</t>
+        </is>
+      </c>
+      <c r="I1819" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="A1820" t="n">
+        <v>65546</v>
+      </c>
+      <c r="B1820" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1820" t="inlineStr">
+        <is>
+          <t>1212 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D1820" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2809987, 'Longitude': -123.0786929}</t>
+        </is>
+      </c>
+      <c r="E1820" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:06:33</t>
+        </is>
+      </c>
+      <c r="F1820" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:16:07.492Z</t>
+        </is>
+      </c>
+      <c r="G1820" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1820" t="inlineStr">
+        <is>
+          <t>2025-08-20T02:35:00.625Z</t>
+        </is>
+      </c>
+      <c r="I1820" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1821">
+      <c r="A1821" t="n">
+        <v>98515</v>
+      </c>
+      <c r="B1821" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1821" t="inlineStr">
+        <is>
+          <t>1896 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D1821" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.281018940561, 'Longitude': -123.065712153912}</t>
+        </is>
+      </c>
+      <c r="E1821" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:06:33</t>
+        </is>
+      </c>
+      <c r="F1821" t="inlineStr">
+        <is>
+          <t>2025-08-21T00:16:25.413Z</t>
+        </is>
+      </c>
+      <c r="G1821" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1821" t="inlineStr">
+        <is>
+          <t>2025-08-20T07:10:51.610Z</t>
+        </is>
+      </c>
+      <c r="I1821" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" t="n">
+        <v>65464</v>
+      </c>
+      <c r="B1822" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1822" t="inlineStr">
+        <is>
+          <t>6751 Lougheed Hwy</t>
+        </is>
+      </c>
+      <c r="D1822" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2598029, 'Longitude': -122.9640097}</t>
+        </is>
+      </c>
+      <c r="E1822" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:08:51</t>
+        </is>
+      </c>
+      <c r="F1822" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:29:41.904Z</t>
+        </is>
+      </c>
+      <c r="G1822" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1822" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:54:01.680Z</t>
+        </is>
+      </c>
+      <c r="I1822" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="A1823" t="n">
+        <v>100210</v>
+      </c>
+      <c r="B1823" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1823" t="inlineStr">
+        <is>
+          <t>7089 Lougheed Hwy</t>
+        </is>
+      </c>
+      <c r="D1823" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259055582449, 'Longitude': -122.956455763229}</t>
+        </is>
+      </c>
+      <c r="E1823" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:08:51</t>
+        </is>
+      </c>
+      <c r="F1823" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:13:21.972Z</t>
+        </is>
+      </c>
+      <c r="G1823" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1823" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:13:37.884Z</t>
+        </is>
+      </c>
+      <c r="I1823" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" t="n">
+        <v>98628</v>
+      </c>
+      <c r="B1824" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1824" t="inlineStr">
+        <is>
+          <t>6568 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D1824" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.280205, 'Longitude': -122.96824}</t>
+        </is>
+      </c>
+      <c r="E1824" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:08:51</t>
+        </is>
+      </c>
+      <c r="F1824" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:53:30.343Z</t>
+        </is>
+      </c>
+      <c r="G1824" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1824" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:53:30.359Z</t>
+        </is>
+      </c>
+      <c r="I1824" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1825">
+      <c r="A1825" t="n">
+        <v>65465</v>
+      </c>
+      <c r="B1825" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1825" t="inlineStr">
+        <is>
+          <t>7009 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D1825" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.280651, 'Longitude': -122.9578017}</t>
+        </is>
+      </c>
+      <c r="E1825" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:08:51</t>
+        </is>
+      </c>
+      <c r="F1825" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:53:55.127Z</t>
+        </is>
+      </c>
+      <c r="G1825" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1825" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:53:55.142Z</t>
+        </is>
+      </c>
+      <c r="I1825" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1826">
+      <c r="A1826" t="n">
+        <v>117793</v>
+      </c>
+      <c r="B1826" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1826" t="inlineStr">
+        <is>
+          <t>6511 Hastings St</t>
+        </is>
+      </c>
+      <c r="D1826" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.280589202387, 'Longitude': -122.969627380371}</t>
+        </is>
+      </c>
+      <c r="E1826" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:08:51</t>
+        </is>
+      </c>
+      <c r="F1826" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:53:34.319Z</t>
+        </is>
+      </c>
+      <c r="G1826" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1826" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:53:34.347Z</t>
+        </is>
+      </c>
+      <c r="I1826" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="A1827" t="n">
+        <v>65476</v>
+      </c>
+      <c r="B1827" t="inlineStr">
+        <is>
+          <t>Husky</t>
+        </is>
+      </c>
+      <c r="C1827" t="inlineStr">
+        <is>
+          <t>5720 Hastings St</t>
+        </is>
+      </c>
+      <c r="D1827" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.280138464632, 'Longitude': -122.980592250824}</t>
+        </is>
+      </c>
+      <c r="E1827" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:08:51</t>
+        </is>
+      </c>
+      <c r="F1827" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:49:43.152Z</t>
+        </is>
+      </c>
+      <c r="G1827" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1827" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:49:43.215Z</t>
+        </is>
+      </c>
+      <c r="I1827" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" t="n">
+        <v>212356</v>
+      </c>
+      <c r="B1828" t="inlineStr">
+        <is>
+          <t>CENTEX</t>
+        </is>
+      </c>
+      <c r="C1828" t="inlineStr">
+        <is>
+          <t>3855 Douglas Rd</t>
+        </is>
+      </c>
+      <c r="D1828" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249718360686, 'Longitude': -122.981165650914}</t>
+        </is>
+      </c>
+      <c r="E1828" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:08:51</t>
+        </is>
+      </c>
+      <c r="F1828" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:29:32.947Z</t>
+        </is>
+      </c>
+      <c r="G1828" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1828" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:30:32.371Z</t>
+        </is>
+      </c>
+      <c r="I1828" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" t="n">
+        <v>919</v>
+      </c>
+      <c r="B1829" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1829" t="inlineStr">
+        <is>
+          <t>4512 Lougheed Hwy</t>
+        </is>
+      </c>
+      <c r="D1829" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.266012306544, 'Longitude': -123.002243041992}</t>
+        </is>
+      </c>
+      <c r="E1829" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:08:51</t>
+        </is>
+      </c>
+      <c r="F1829" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:53:22.004Z</t>
+        </is>
+      </c>
+      <c r="G1829" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1829" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:05:27.436Z</t>
+        </is>
+      </c>
+      <c r="I1829" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" t="n">
+        <v>164809</v>
+      </c>
+      <c r="B1830" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1830" t="inlineStr">
+        <is>
+          <t>1969 Willingdon Ave</t>
+        </is>
+      </c>
+      <c r="D1830" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.266593392816, 'Longitude': -123.003401756287}</t>
+        </is>
+      </c>
+      <c r="E1830" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:08:51</t>
+        </is>
+      </c>
+      <c r="F1830" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:53:17.171Z</t>
+        </is>
+      </c>
+      <c r="G1830" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1830" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:05:40.726Z</t>
+        </is>
+      </c>
+      <c r="I1830" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" t="n">
+        <v>65471</v>
+      </c>
+      <c r="B1831" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1831" t="inlineStr">
+        <is>
+          <t>5059 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1831" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.239569143746, 'Longitude': -122.96440243721}</t>
+        </is>
+      </c>
+      <c r="E1831" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:08:51</t>
+        </is>
+      </c>
+      <c r="F1831" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:19:34.223Z</t>
+        </is>
+      </c>
+      <c r="G1831" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1831" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:32:11.629Z</t>
+        </is>
+      </c>
+      <c r="I1831" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" t="n">
+        <v>1669</v>
+      </c>
+      <c r="B1832" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1832" t="inlineStr">
+        <is>
+          <t>975 Willingdon Ave</t>
+        </is>
+      </c>
+      <c r="D1832" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2758486, 'Longitude': -123.0035135}</t>
+        </is>
+      </c>
+      <c r="E1832" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:08:51</t>
+        </is>
+      </c>
+      <c r="F1832" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:51:00.842Z</t>
+        </is>
+      </c>
+      <c r="G1832" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1832" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:16:22.396Z</t>
+        </is>
+      </c>
+      <c r="I1832" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" t="n">
+        <v>65479</v>
+      </c>
+      <c r="B1833" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1833" t="inlineStr">
+        <is>
+          <t>4505 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1833" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.255159438214, 'Longitude': -123.003401756287}</t>
+        </is>
+      </c>
+      <c r="E1833" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:08:51</t>
+        </is>
+      </c>
+      <c r="F1833" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:41:04.480Z</t>
+        </is>
+      </c>
+      <c r="G1833" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1833" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:10:58.343Z</t>
+        </is>
+      </c>
+      <c r="I1833" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" t="n">
+        <v>69963</v>
+      </c>
+      <c r="B1834" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1834" t="inlineStr">
+        <is>
+          <t>4487 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1834" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.255044, 'Longitude': -123.0046907}</t>
+        </is>
+      </c>
+      <c r="E1834" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:08:51</t>
+        </is>
+      </c>
+      <c r="F1834" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:41:09.130Z</t>
+        </is>
+      </c>
+      <c r="G1834" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1834" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:11:20.964Z</t>
+        </is>
+      </c>
+      <c r="I1834" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" t="n">
+        <v>65466</v>
+      </c>
+      <c r="B1835" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1835" t="inlineStr">
+        <is>
+          <t>4507 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D1835" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2812235, 'Longitude': -123.0025696}</t>
+        </is>
+      </c>
+      <c r="E1835" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:08:51</t>
+        </is>
+      </c>
+      <c r="F1835" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:49:51.349Z</t>
+        </is>
+      </c>
+      <c r="G1835" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1835" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:49:35.152Z</t>
+        </is>
+      </c>
+      <c r="I1835" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" t="n">
+        <v>65475</v>
+      </c>
+      <c r="B1836" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1836" t="inlineStr">
+        <is>
+          <t>3826 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1836" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2544887, 'Longitude': -123.0193605}</t>
+        </is>
+      </c>
+      <c r="E1836" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:08:51</t>
+        </is>
+      </c>
+      <c r="F1836" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:58:50.738Z</t>
+        </is>
+      </c>
+      <c r="G1836" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1836" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:58:50.785Z</t>
+        </is>
+      </c>
+      <c r="I1836" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" t="n">
+        <v>39293</v>
+      </c>
+      <c r="B1837" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1837" t="inlineStr">
+        <is>
+          <t>3030 Boundary Rd</t>
+        </is>
+      </c>
+      <c r="D1837" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2567447, 'Longitude': -123.0230847}</t>
+        </is>
+      </c>
+      <c r="E1837" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:08:51</t>
+        </is>
+      </c>
+      <c r="F1837" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:34:17.214Z</t>
+        </is>
+      </c>
+      <c r="G1837" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1837" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:53:40.788Z</t>
+        </is>
+      </c>
+      <c r="I1837" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" t="n">
+        <v>119589</v>
+      </c>
+      <c r="B1838" t="inlineStr">
+        <is>
+          <t>Smart Gas</t>
+        </is>
+      </c>
+      <c r="C1838" t="inlineStr">
+        <is>
+          <t>6869 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1838" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226505740129, 'Longitude': -122.944511175156}</t>
+        </is>
+      </c>
+      <c r="E1838" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:08:51</t>
+        </is>
+      </c>
+      <c r="F1838" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:51:12.850Z</t>
+        </is>
+      </c>
+      <c r="G1838" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1838" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:03.731Z</t>
+        </is>
+      </c>
+      <c r="I1838" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" t="n">
+        <v>124671</v>
+      </c>
+      <c r="B1839" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1839" t="inlineStr">
+        <is>
+          <t>3505 Grandview Hwy</t>
+        </is>
+      </c>
+      <c r="D1839" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2585701, 'Longitude': -123.0281066}</t>
+        </is>
+      </c>
+      <c r="E1839" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:08:51</t>
+        </is>
+      </c>
+      <c r="F1839" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:41:08.724Z</t>
+        </is>
+      </c>
+      <c r="G1839" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1839" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:53:59.992Z</t>
+        </is>
+      </c>
+      <c r="I1839" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" t="n">
+        <v>65474</v>
+      </c>
+      <c r="B1840" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1840" t="inlineStr">
+        <is>
+          <t>7274 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1840" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2244118, 'Longitude': -122.9410264}</t>
+        </is>
+      </c>
+      <c r="E1840" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:08:51</t>
+        </is>
+      </c>
+      <c r="F1840" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:51:05.186Z</t>
+        </is>
+      </c>
+      <c r="G1840" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1840" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:59.321Z</t>
+        </is>
+      </c>
+      <c r="I1840" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" t="n">
+        <v>5768</v>
+      </c>
+      <c r="B1841" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1841" t="inlineStr">
+        <is>
+          <t>5009 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1841" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2264629, 'Longitude': -122.992576}</t>
+        </is>
+      </c>
+      <c r="E1841" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:08:51</t>
+        </is>
+      </c>
+      <c r="F1841" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:59:03.181Z</t>
+        </is>
+      </c>
+      <c r="G1841" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1841" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:29:07.196Z</t>
+        </is>
+      </c>
+      <c r="I1841" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" t="inlineStr">
+        <is>
+          <t>65480</t>
+        </is>
+      </c>
+      <c r="B1842" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1842" t="inlineStr">
+        <is>
+          <t>6591 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1842" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21925095319, 'Longitude': -122.968211174011}</t>
+        </is>
+      </c>
+      <c r="E1842" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:11:20</t>
+        </is>
+      </c>
+      <c r="F1842" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:30:49.888Z</t>
+        </is>
+      </c>
+      <c r="G1842" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1842" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:25:44.411Z</t>
+        </is>
+      </c>
+      <c r="I1842" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" t="inlineStr">
+        <is>
+          <t>65467</t>
+        </is>
+      </c>
+      <c r="B1843" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1843" t="inlineStr">
+        <is>
+          <t>6138 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1843" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2201556, 'Longitude': -122.9743751}</t>
+        </is>
+      </c>
+      <c r="E1843" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:11:20</t>
+        </is>
+      </c>
+      <c r="F1843" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:56:41.933Z</t>
+        </is>
+      </c>
+      <c r="G1843" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1843" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:29:38.803Z</t>
+        </is>
+      </c>
+      <c r="I1843" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" t="inlineStr">
+        <is>
+          <t>119589</t>
+        </is>
+      </c>
+      <c r="B1844" t="inlineStr">
+        <is>
+          <t>Smart Gas</t>
+        </is>
+      </c>
+      <c r="C1844" t="inlineStr">
+        <is>
+          <t>6869 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1844" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226505740129, 'Longitude': -122.944511175156}</t>
+        </is>
+      </c>
+      <c r="E1844" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:11:20</t>
+        </is>
+      </c>
+      <c r="F1844" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:51:12.850Z</t>
+        </is>
+      </c>
+      <c r="G1844" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1844" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:03.731Z</t>
+        </is>
+      </c>
+      <c r="I1844" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" t="inlineStr">
+        <is>
+          <t>65474</t>
+        </is>
+      </c>
+      <c r="B1845" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1845" t="inlineStr">
+        <is>
+          <t>7274 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1845" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2244118, 'Longitude': -122.9410264}</t>
+        </is>
+      </c>
+      <c r="E1845" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:11:20</t>
+        </is>
+      </c>
+      <c r="F1845" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:51:05.186Z</t>
+        </is>
+      </c>
+      <c r="G1845" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1845" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:59.321Z</t>
+        </is>
+      </c>
+      <c r="I1845" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" t="inlineStr">
+        <is>
+          <t>87633</t>
+        </is>
+      </c>
+      <c r="B1846" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1846" t="inlineStr">
+        <is>
+          <t>5608 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1846" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.222913, 'Longitude': -122.982433}</t>
+        </is>
+      </c>
+      <c r="E1846" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:11:20</t>
+        </is>
+      </c>
+      <c r="F1846" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:57:52.459Z</t>
+        </is>
+      </c>
+      <c r="G1846" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1846" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:29:55.698Z</t>
+        </is>
+      </c>
+      <c r="I1846" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" t="inlineStr">
+        <is>
+          <t>65481</t>
+        </is>
+      </c>
+      <c r="B1847" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1847" t="inlineStr">
+        <is>
+          <t>7377 6th St</t>
+        </is>
+      </c>
+      <c r="D1847" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.225214157435, 'Longitude': -122.935831546783}</t>
+        </is>
+      </c>
+      <c r="E1847" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:11:20</t>
+        </is>
+      </c>
+      <c r="F1847" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:48:53.738Z</t>
+        </is>
+      </c>
+      <c r="G1847" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1847" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:31:12.755Z</t>
+        </is>
+      </c>
+      <c r="I1847" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" t="inlineStr">
+        <is>
+          <t>65477</t>
+        </is>
+      </c>
+      <c r="B1848" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1848" t="inlineStr">
+        <is>
+          <t>7890 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1848" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.217246706543, 'Longitude': -122.931432723999}</t>
+        </is>
+      </c>
+      <c r="E1848" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:11:20</t>
+        </is>
+      </c>
+      <c r="F1848" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:38:11.932Z</t>
+        </is>
+      </c>
+      <c r="G1848" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1848" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:38:12.010Z</t>
+        </is>
+      </c>
+      <c r="I1848" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" t="inlineStr">
+        <is>
+          <t>65468</t>
+        </is>
+      </c>
+      <c r="B1849" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1849" t="inlineStr">
+        <is>
+          <t>7587 Royal Oak Ave</t>
+        </is>
+      </c>
+      <c r="D1849" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2151443, 'Longitude': -122.9890903}</t>
+        </is>
+      </c>
+      <c r="E1849" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:11:20</t>
+        </is>
+      </c>
+      <c r="F1849" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:29:20.130Z</t>
+        </is>
+      </c>
+      <c r="G1849" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1849" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:29:20.166Z</t>
+        </is>
+      </c>
+      <c r="I1849" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" t="inlineStr">
+        <is>
+          <t>65471</t>
+        </is>
+      </c>
+      <c r="B1850" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1850" t="inlineStr">
+        <is>
+          <t>5059 Canada Way</t>
+        </is>
+      </c>
+      <c r="D1850" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.239569143746, 'Longitude': -122.96440243721}</t>
+        </is>
+      </c>
+      <c r="E1850" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:11:20</t>
+        </is>
+      </c>
+      <c r="F1850" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:19:34.223Z</t>
+        </is>
+      </c>
+      <c r="G1850" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1850" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:32:11.629Z</t>
+        </is>
+      </c>
+      <c r="I1850" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" t="inlineStr">
+        <is>
+          <t>5768</t>
+        </is>
+      </c>
+      <c r="B1851" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1851" t="inlineStr">
+        <is>
+          <t>5009 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1851" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2264629, 'Longitude': -122.992576}</t>
+        </is>
+      </c>
+      <c r="E1851" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:11:20</t>
+        </is>
+      </c>
+      <c r="F1851" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:59:03.181Z</t>
+        </is>
+      </c>
+      <c r="G1851" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1851" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:29:07.196Z</t>
+        </is>
+      </c>
+      <c r="I1851" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" t="inlineStr">
+        <is>
+          <t>111740</t>
+        </is>
+      </c>
+      <c r="B1852" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1852" t="inlineStr">
+        <is>
+          <t>780 6th St</t>
+        </is>
+      </c>
+      <c r="D1852" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21557, 'Longitude': -122.92387}</t>
+        </is>
+      </c>
+      <c r="E1852" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:11:20</t>
+        </is>
+      </c>
+      <c r="F1852" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:37:54.809Z</t>
+        </is>
+      </c>
+      <c r="G1852" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1852" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:37:54.856Z</t>
+        </is>
+      </c>
+      <c r="I1852" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" t="inlineStr">
+        <is>
+          <t>65469</t>
+        </is>
+      </c>
+      <c r="B1853" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1853" t="inlineStr">
+        <is>
+          <t>4692 Imperial St</t>
+        </is>
+      </c>
+      <c r="D1853" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2217244, 'Longitude': -122.9980797}</t>
+        </is>
+      </c>
+      <c r="E1853" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:11:20</t>
+        </is>
+      </c>
+      <c r="F1853" t="inlineStr">
+        <is>
+          <t>2025-08-21T16:01:19.770Z</t>
+        </is>
+      </c>
+      <c r="G1853" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1853" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:58:12.777Z</t>
+        </is>
+      </c>
+      <c r="I1853" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" t="inlineStr">
+        <is>
+          <t>65499</t>
+        </is>
+      </c>
+      <c r="B1854" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1854" t="inlineStr">
+        <is>
+          <t>736 Sixth Ave</t>
+        </is>
+      </c>
+      <c r="D1854" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21129, 'Longitude': -122.92333}</t>
+        </is>
+      </c>
+      <c r="E1854" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:11:20</t>
+        </is>
+      </c>
+      <c r="F1854" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:30.175Z</t>
+        </is>
+      </c>
+      <c r="G1854" t="n">
+        <v>164.6</v>
+      </c>
+      <c r="H1854" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:30.222Z</t>
+        </is>
+      </c>
+      <c r="I1854" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" t="inlineStr">
+        <is>
+          <t>65497</t>
+        </is>
+      </c>
+      <c r="B1855" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1855" t="inlineStr">
+        <is>
+          <t>428 Sixth St</t>
+        </is>
+      </c>
+      <c r="D1855" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2109656, 'Longitude': -122.9179526}</t>
+        </is>
+      </c>
+      <c r="E1855" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:11:20</t>
+        </is>
+      </c>
+      <c r="F1855" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:14:21.966Z</t>
+        </is>
+      </c>
+      <c r="G1855" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1855" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:25:12.166Z</t>
+        </is>
+      </c>
+      <c r="I1855" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" t="inlineStr">
+        <is>
+          <t>32350</t>
+        </is>
+      </c>
+      <c r="B1856" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1856" t="inlineStr">
+        <is>
+          <t>132 12th St</t>
+        </is>
+      </c>
+      <c r="D1856" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.201144, 'Longitude': -122.922922}</t>
+        </is>
+      </c>
+      <c r="E1856" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:11:20</t>
+        </is>
+      </c>
+      <c r="F1856" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:25:33.775Z</t>
+        </is>
+      </c>
+      <c r="G1856" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1856" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:38:14.709Z</t>
+        </is>
+      </c>
+      <c r="I1856" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" t="inlineStr">
+        <is>
+          <t>65502</t>
+        </is>
+      </c>
+      <c r="B1857" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1857" t="inlineStr">
+        <is>
+          <t>5 W 8th Ave</t>
+        </is>
+      </c>
+      <c r="D1857" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.222332, 'Longitude': -122.91267}</t>
+        </is>
+      </c>
+      <c r="E1857" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:11:20</t>
+        </is>
+      </c>
+      <c r="F1857" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:25:24.963Z</t>
+        </is>
+      </c>
+      <c r="G1857" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1857" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:25:24.979Z</t>
+        </is>
+      </c>
+      <c r="I1857" t="n">
+        <v>199.9</v>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" t="inlineStr">
+        <is>
+          <t>65498</t>
+        </is>
+      </c>
+      <c r="B1858" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1858" t="inlineStr">
+        <is>
+          <t>3 E 8th Ave</t>
+        </is>
+      </c>
+      <c r="D1858" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2228942, 'Longitude': -122.9117512}</t>
+        </is>
+      </c>
+      <c r="E1858" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:11:20</t>
+        </is>
+      </c>
+      <c r="F1858" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:25:19.383Z</t>
+        </is>
+      </c>
+      <c r="G1858" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1858" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:25:19.414Z</t>
+        </is>
+      </c>
+      <c r="I1858" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" t="inlineStr">
+        <is>
+          <t>65470</t>
+        </is>
+      </c>
+      <c r="B1859" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1859" t="inlineStr">
+        <is>
+          <t>4444 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1859" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.23030428362, 'Longitude': -123.006110787392}</t>
+        </is>
+      </c>
+      <c r="E1859" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:11:20</t>
+        </is>
+      </c>
+      <c r="F1859" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:26:39.163Z</t>
+        </is>
+      </c>
+      <c r="G1859" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1859" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:30:13.104Z</t>
+        </is>
+      </c>
+      <c r="I1859" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" t="inlineStr">
+        <is>
+          <t>212356</t>
+        </is>
+      </c>
+      <c r="B1860" t="inlineStr">
+        <is>
+          <t>CENTEX</t>
+        </is>
+      </c>
+      <c r="C1860" t="inlineStr">
+        <is>
+          <t>3855 Douglas Rd</t>
+        </is>
+      </c>
+      <c r="D1860" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249718360686, 'Longitude': -122.981165650914}</t>
+        </is>
+      </c>
+      <c r="E1860" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:11:20</t>
+        </is>
+      </c>
+      <c r="F1860" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:29:32.947Z</t>
+        </is>
+      </c>
+      <c r="G1860" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1860" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:30:32.371Z</t>
+        </is>
+      </c>
+      <c r="I1860" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" t="inlineStr">
+        <is>
+          <t>87636</t>
+        </is>
+      </c>
+      <c r="B1861" t="inlineStr">
+        <is>
+          <t>CENTEX</t>
+        </is>
+      </c>
+      <c r="C1861" t="inlineStr">
+        <is>
+          <t>1101 Ewen Ave</t>
+        </is>
+      </c>
+      <c r="D1861" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.185333, 'Longitude': -122.949622}</t>
+        </is>
+      </c>
+      <c r="E1861" t="inlineStr">
+        <is>
+          <t>2025-08-21 09:11:20</t>
+        </is>
+      </c>
+      <c r="F1861" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:41:02.053Z</t>
+        </is>
+      </c>
+      <c r="G1861" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1861" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:41:02.116Z</t>
+        </is>
+      </c>
+      <c r="I1861" t="n">
+        <v>183.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/gas_prices.xlsx
+++ b/data/gas_prices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1861"/>
+  <dimension ref="A1:I2001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73896,10 +73896,8 @@
       </c>
     </row>
     <row r="1842">
-      <c r="A1842" t="inlineStr">
-        <is>
-          <t>65480</t>
-        </is>
+      <c r="A1842" t="n">
+        <v>65480</v>
       </c>
       <c r="B1842" t="inlineStr">
         <is>
@@ -73939,10 +73937,8 @@
       </c>
     </row>
     <row r="1843">
-      <c r="A1843" t="inlineStr">
-        <is>
-          <t>65467</t>
-        </is>
+      <c r="A1843" t="n">
+        <v>65467</v>
       </c>
       <c r="B1843" t="inlineStr">
         <is>
@@ -73982,10 +73978,8 @@
       </c>
     </row>
     <row r="1844">
-      <c r="A1844" t="inlineStr">
-        <is>
-          <t>119589</t>
-        </is>
+      <c r="A1844" t="n">
+        <v>119589</v>
       </c>
       <c r="B1844" t="inlineStr">
         <is>
@@ -74025,10 +74019,8 @@
       </c>
     </row>
     <row r="1845">
-      <c r="A1845" t="inlineStr">
-        <is>
-          <t>65474</t>
-        </is>
+      <c r="A1845" t="n">
+        <v>65474</v>
       </c>
       <c r="B1845" t="inlineStr">
         <is>
@@ -74068,10 +74060,8 @@
       </c>
     </row>
     <row r="1846">
-      <c r="A1846" t="inlineStr">
-        <is>
-          <t>87633</t>
-        </is>
+      <c r="A1846" t="n">
+        <v>87633</v>
       </c>
       <c r="B1846" t="inlineStr">
         <is>
@@ -74111,10 +74101,8 @@
       </c>
     </row>
     <row r="1847">
-      <c r="A1847" t="inlineStr">
-        <is>
-          <t>65481</t>
-        </is>
+      <c r="A1847" t="n">
+        <v>65481</v>
       </c>
       <c r="B1847" t="inlineStr">
         <is>
@@ -74154,10 +74142,8 @@
       </c>
     </row>
     <row r="1848">
-      <c r="A1848" t="inlineStr">
-        <is>
-          <t>65477</t>
-        </is>
+      <c r="A1848" t="n">
+        <v>65477</v>
       </c>
       <c r="B1848" t="inlineStr">
         <is>
@@ -74197,10 +74183,8 @@
       </c>
     </row>
     <row r="1849">
-      <c r="A1849" t="inlineStr">
-        <is>
-          <t>65468</t>
-        </is>
+      <c r="A1849" t="n">
+        <v>65468</v>
       </c>
       <c r="B1849" t="inlineStr">
         <is>
@@ -74240,10 +74224,8 @@
       </c>
     </row>
     <row r="1850">
-      <c r="A1850" t="inlineStr">
-        <is>
-          <t>65471</t>
-        </is>
+      <c r="A1850" t="n">
+        <v>65471</v>
       </c>
       <c r="B1850" t="inlineStr">
         <is>
@@ -74283,10 +74265,8 @@
       </c>
     </row>
     <row r="1851">
-      <c r="A1851" t="inlineStr">
-        <is>
-          <t>5768</t>
-        </is>
+      <c r="A1851" t="n">
+        <v>5768</v>
       </c>
       <c r="B1851" t="inlineStr">
         <is>
@@ -74326,10 +74306,8 @@
       </c>
     </row>
     <row r="1852">
-      <c r="A1852" t="inlineStr">
-        <is>
-          <t>111740</t>
-        </is>
+      <c r="A1852" t="n">
+        <v>111740</v>
       </c>
       <c r="B1852" t="inlineStr">
         <is>
@@ -74369,10 +74347,8 @@
       </c>
     </row>
     <row r="1853">
-      <c r="A1853" t="inlineStr">
-        <is>
-          <t>65469</t>
-        </is>
+      <c r="A1853" t="n">
+        <v>65469</v>
       </c>
       <c r="B1853" t="inlineStr">
         <is>
@@ -74412,10 +74388,8 @@
       </c>
     </row>
     <row r="1854">
-      <c r="A1854" t="inlineStr">
-        <is>
-          <t>65499</t>
-        </is>
+      <c r="A1854" t="n">
+        <v>65499</v>
       </c>
       <c r="B1854" t="inlineStr">
         <is>
@@ -74455,10 +74429,8 @@
       </c>
     </row>
     <row r="1855">
-      <c r="A1855" t="inlineStr">
-        <is>
-          <t>65497</t>
-        </is>
+      <c r="A1855" t="n">
+        <v>65497</v>
       </c>
       <c r="B1855" t="inlineStr">
         <is>
@@ -74498,10 +74470,8 @@
       </c>
     </row>
     <row r="1856">
-      <c r="A1856" t="inlineStr">
-        <is>
-          <t>32350</t>
-        </is>
+      <c r="A1856" t="n">
+        <v>32350</v>
       </c>
       <c r="B1856" t="inlineStr">
         <is>
@@ -74541,10 +74511,8 @@
       </c>
     </row>
     <row r="1857">
-      <c r="A1857" t="inlineStr">
-        <is>
-          <t>65502</t>
-        </is>
+      <c r="A1857" t="n">
+        <v>65502</v>
       </c>
       <c r="B1857" t="inlineStr">
         <is>
@@ -74584,10 +74552,8 @@
       </c>
     </row>
     <row r="1858">
-      <c r="A1858" t="inlineStr">
-        <is>
-          <t>65498</t>
-        </is>
+      <c r="A1858" t="n">
+        <v>65498</v>
       </c>
       <c r="B1858" t="inlineStr">
         <is>
@@ -74627,10 +74593,8 @@
       </c>
     </row>
     <row r="1859">
-      <c r="A1859" t="inlineStr">
-        <is>
-          <t>65470</t>
-        </is>
+      <c r="A1859" t="n">
+        <v>65470</v>
       </c>
       <c r="B1859" t="inlineStr">
         <is>
@@ -74670,10 +74634,8 @@
       </c>
     </row>
     <row r="1860">
-      <c r="A1860" t="inlineStr">
-        <is>
-          <t>212356</t>
-        </is>
+      <c r="A1860" t="n">
+        <v>212356</v>
       </c>
       <c r="B1860" t="inlineStr">
         <is>
@@ -74713,10 +74675,8 @@
       </c>
     </row>
     <row r="1861">
-      <c r="A1861" t="inlineStr">
-        <is>
-          <t>87636</t>
-        </is>
+      <c r="A1861" t="n">
+        <v>87636</v>
       </c>
       <c r="B1861" t="inlineStr">
         <is>
@@ -74754,6 +74714,5594 @@
       <c r="I1861" t="n">
         <v>183.9</v>
       </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" t="n">
+        <v>65542</v>
+      </c>
+      <c r="B1862" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1862" t="inlineStr">
+        <is>
+          <t>3250 MacDonald St</t>
+        </is>
+      </c>
+      <c r="D1862" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2573819, 'Longitude': -123.1680407}</t>
+        </is>
+      </c>
+      <c r="E1862" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:13:55</t>
+        </is>
+      </c>
+      <c r="F1862" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:58:17.247Z</t>
+        </is>
+      </c>
+      <c r="G1862" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1862" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:37:56.532Z</t>
+        </is>
+      </c>
+      <c r="I1862" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" t="n">
+        <v>65533</v>
+      </c>
+      <c r="B1863" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1863" t="inlineStr">
+        <is>
+          <t>4615 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D1863" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2449719, 'Longitude': -123.1540385}</t>
+        </is>
+      </c>
+      <c r="E1863" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:13:55</t>
+        </is>
+      </c>
+      <c r="F1863" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:41:38.634Z</t>
+        </is>
+      </c>
+      <c r="G1863" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1863" t="inlineStr"/>
+      <c r="I1863" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" t="n">
+        <v>83068</v>
+      </c>
+      <c r="B1864" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1864" t="inlineStr">
+        <is>
+          <t>3205 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D1864" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.256927568207, 'Longitude': -123.153288960457}</t>
+        </is>
+      </c>
+      <c r="E1864" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:13:55</t>
+        </is>
+      </c>
+      <c r="F1864" t="inlineStr"/>
+      <c r="G1864" t="inlineStr"/>
+      <c r="H1864" t="inlineStr"/>
+      <c r="I1864" t="inlineStr"/>
+    </row>
+    <row r="1865">
+      <c r="A1865" t="n">
+        <v>65562</v>
+      </c>
+      <c r="B1865" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1865" t="inlineStr">
+        <is>
+          <t>2808 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1865" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263883932125, 'Longitude': -123.168604373932}</t>
+        </is>
+      </c>
+      <c r="E1865" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:13:55</t>
+        </is>
+      </c>
+      <c r="F1865" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:22:12.073Z</t>
+        </is>
+      </c>
+      <c r="G1865" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1865" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:22:12.089Z</t>
+        </is>
+      </c>
+      <c r="I1865" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" t="n">
+        <v>113305</v>
+      </c>
+      <c r="B1866" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1866" t="inlineStr">
+        <is>
+          <t>3596 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1866" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234385296079, 'Longitude': -123.184762001038}</t>
+        </is>
+      </c>
+      <c r="E1866" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:13:55</t>
+        </is>
+      </c>
+      <c r="F1866" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:30:03.056Z</t>
+        </is>
+      </c>
+      <c r="G1866" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1866" t="inlineStr"/>
+      <c r="I1866" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B1867" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1867" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1867" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E1867" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:13:55</t>
+        </is>
+      </c>
+      <c r="F1867" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:49:25.128Z</t>
+        </is>
+      </c>
+      <c r="G1867" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1867" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:49:25.143Z</t>
+        </is>
+      </c>
+      <c r="I1867" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" t="n">
+        <v>65554</v>
+      </c>
+      <c r="B1868" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1868" t="inlineStr">
+        <is>
+          <t>1795 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1868" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264037962303, 'Longitude': -123.145408630371}</t>
+        </is>
+      </c>
+      <c r="E1868" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:13:55</t>
+        </is>
+      </c>
+      <c r="F1868" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:52:38.101Z</t>
+        </is>
+      </c>
+      <c r="G1868" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1868" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:52:38.117Z</t>
+        </is>
+      </c>
+      <c r="I1868" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" t="n">
+        <v>65571</v>
+      </c>
+      <c r="B1869" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1869" t="inlineStr">
+        <is>
+          <t>4314 W 10th Ave</t>
+        </is>
+      </c>
+      <c r="D1869" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263533861752, 'Longitude': -123.203430175781}</t>
+        </is>
+      </c>
+      <c r="E1869" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:13:55</t>
+        </is>
+      </c>
+      <c r="F1869" t="inlineStr">
+        <is>
+          <t>2025-08-21T16:18:21.640Z</t>
+        </is>
+      </c>
+      <c r="G1869" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1869" t="inlineStr">
+        <is>
+          <t>2025-08-21T17:52:15.464Z</t>
+        </is>
+      </c>
+      <c r="I1869" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B1870" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1870" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D1870" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E1870" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:13:55</t>
+        </is>
+      </c>
+      <c r="F1870" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:30:17.051Z</t>
+        </is>
+      </c>
+      <c r="G1870" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1870" t="inlineStr"/>
+      <c r="I1870" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" t="n">
+        <v>32376</v>
+      </c>
+      <c r="B1871" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1871" t="inlineStr">
+        <is>
+          <t>1503 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1871" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234634576953, 'Longitude': -123.139971792698}</t>
+        </is>
+      </c>
+      <c r="E1871" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:13:55</t>
+        </is>
+      </c>
+      <c r="F1871" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:26:32.706Z</t>
+        </is>
+      </c>
+      <c r="G1871" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1871" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:30:08.915Z</t>
+        </is>
+      </c>
+      <c r="I1871" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" t="n">
+        <v>65549</v>
+      </c>
+      <c r="B1872" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1872" t="inlineStr">
+        <is>
+          <t>5702 Granville St</t>
+        </is>
+      </c>
+      <c r="D1872" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234036184118, 'Longitude': -123.139244914055}</t>
+        </is>
+      </c>
+      <c r="E1872" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:13:55</t>
+        </is>
+      </c>
+      <c r="F1872" t="inlineStr">
+        <is>
+          <t>2025-08-21T17:29:54.239Z</t>
+        </is>
+      </c>
+      <c r="G1872" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1872" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:16:56.895Z</t>
+        </is>
+      </c>
+      <c r="I1872" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B1873" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1873" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1873" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E1873" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:13:55</t>
+        </is>
+      </c>
+      <c r="F1873" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:46:17.762Z</t>
+        </is>
+      </c>
+      <c r="G1873" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1873" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:46:17.794Z</t>
+        </is>
+      </c>
+      <c r="I1873" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B1874" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1874" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1874" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E1874" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:13:55</t>
+        </is>
+      </c>
+      <c r="F1874" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:28:51.238Z</t>
+        </is>
+      </c>
+      <c r="G1874" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1874" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:11.555Z</t>
+        </is>
+      </c>
+      <c r="I1874" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" t="n">
+        <v>72747</v>
+      </c>
+      <c r="B1875" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1875" t="inlineStr">
+        <is>
+          <t>1010 W King Edward Ave</t>
+        </is>
+      </c>
+      <c r="D1875" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249188, 'Longitude': -123.127767}</t>
+        </is>
+      </c>
+      <c r="E1875" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:13:55</t>
+        </is>
+      </c>
+      <c r="F1875" t="inlineStr">
+        <is>
+          <t>2025-08-21T16:28:10.010Z</t>
+        </is>
+      </c>
+      <c r="G1875" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1875" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:43:58.867Z</t>
+        </is>
+      </c>
+      <c r="I1875" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" t="n">
+        <v>32375</v>
+      </c>
+      <c r="B1876" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1876" t="inlineStr">
+        <is>
+          <t>4110 Oak St</t>
+        </is>
+      </c>
+      <c r="D1876" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.24894071957, 'Longitude': -123.127040863037}</t>
+        </is>
+      </c>
+      <c r="E1876" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:13:55</t>
+        </is>
+      </c>
+      <c r="F1876" t="inlineStr">
+        <is>
+          <t>2025-08-21T17:25:22.684Z</t>
+        </is>
+      </c>
+      <c r="G1876" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1876" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:13:19.073Z</t>
+        </is>
+      </c>
+      <c r="I1876" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" t="n">
+        <v>65564</v>
+      </c>
+      <c r="B1877" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1877" t="inlineStr">
+        <is>
+          <t>5680 Oak St</t>
+        </is>
+      </c>
+      <c r="D1877" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234217162181, 'Longitude': -123.127684593201}</t>
+        </is>
+      </c>
+      <c r="E1877" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:13:55</t>
+        </is>
+      </c>
+      <c r="F1877" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:32:34.338Z</t>
+        </is>
+      </c>
+      <c r="G1877" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1877" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:37:38.272Z</t>
+        </is>
+      </c>
+      <c r="I1877" t="n">
+        <v>198.9</v>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" t="n">
+        <v>32372</v>
+      </c>
+      <c r="B1878" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1878" t="inlineStr">
+        <is>
+          <t>6525 Oak St</t>
+        </is>
+      </c>
+      <c r="D1878" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226226639452, 'Longitude': -123.128687739372}</t>
+        </is>
+      </c>
+      <c r="E1878" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:13:55</t>
+        </is>
+      </c>
+      <c r="F1878" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:34:29.486Z</t>
+        </is>
+      </c>
+      <c r="G1878" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1878" t="inlineStr">
+        <is>
+          <t>2025-08-21T16:26:51.618Z</t>
+        </is>
+      </c>
+      <c r="I1878" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B1879" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1879" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1879" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E1879" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:13:55</t>
+        </is>
+      </c>
+      <c r="F1879" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:30:02.585Z</t>
+        </is>
+      </c>
+      <c r="G1879" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1879" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:49:01.374Z</t>
+        </is>
+      </c>
+      <c r="I1879" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" t="n">
+        <v>65566</v>
+      </c>
+      <c r="B1880" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1880" t="inlineStr">
+        <is>
+          <t>8072 Granville St</t>
+        </is>
+      </c>
+      <c r="D1880" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.212495055855, 'Longitude': -123.14013004303}</t>
+        </is>
+      </c>
+      <c r="E1880" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:13:55</t>
+        </is>
+      </c>
+      <c r="F1880" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:15:06.805Z</t>
+        </is>
+      </c>
+      <c r="G1880" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1880" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:30:08.359Z</t>
+        </is>
+      </c>
+      <c r="I1880" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" t="n">
+        <v>65572</v>
+      </c>
+      <c r="B1881" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1881" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D1881" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E1881" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:13:55</t>
+        </is>
+      </c>
+      <c r="F1881" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:03:43.733Z</t>
+        </is>
+      </c>
+      <c r="G1881" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1881" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:19:00.915Z</t>
+        </is>
+      </c>
+      <c r="I1881" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" t="n">
+        <v>65558</v>
+      </c>
+      <c r="B1882" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1882" t="inlineStr">
+        <is>
+          <t>1390 E 33rd Ave</t>
+        </is>
+      </c>
+      <c r="D1882" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.240045470021, 'Longitude': -123.076765537262}</t>
+        </is>
+      </c>
+      <c r="E1882" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:16:26</t>
+        </is>
+      </c>
+      <c r="F1882" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:56:45.639Z</t>
+        </is>
+      </c>
+      <c r="G1882" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1882" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:56:45.655Z</t>
+        </is>
+      </c>
+      <c r="I1882" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" t="n">
+        <v>83394</v>
+      </c>
+      <c r="B1883" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1883" t="inlineStr">
+        <is>
+          <t>4064 Fraser St</t>
+        </is>
+      </c>
+      <c r="D1883" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.248864, 'Longitude': -123.09002}</t>
+        </is>
+      </c>
+      <c r="E1883" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:16:26</t>
+        </is>
+      </c>
+      <c r="F1883" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:22:39.047Z</t>
+        </is>
+      </c>
+      <c r="G1883" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1883" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:02:55.309Z</t>
+        </is>
+      </c>
+      <c r="I1883" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" t="n">
+        <v>65573</v>
+      </c>
+      <c r="B1884" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1884" t="inlineStr">
+        <is>
+          <t>1396 E 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1884" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.232593005895, 'Longitude': -123.07728856802}</t>
+        </is>
+      </c>
+      <c r="E1884" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:16:26</t>
+        </is>
+      </c>
+      <c r="F1884" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:53:30.000Z</t>
+        </is>
+      </c>
+      <c r="G1884" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1884" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:28:44.531Z</t>
+        </is>
+      </c>
+      <c r="I1884" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" t="n">
+        <v>80714</v>
+      </c>
+      <c r="B1885" t="inlineStr">
+        <is>
+          <t>Husky</t>
+        </is>
+      </c>
+      <c r="C1885" t="inlineStr">
+        <is>
+          <t>4933 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1885" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2397388, 'Longitude': -123.065748}</t>
+        </is>
+      </c>
+      <c r="E1885" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:16:26</t>
+        </is>
+      </c>
+      <c r="F1885" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:57:06.101Z</t>
+        </is>
+      </c>
+      <c r="G1885" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1885" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:57:06.133Z</t>
+        </is>
+      </c>
+      <c r="I1885" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" t="n">
+        <v>65552</v>
+      </c>
+      <c r="B1886" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1886" t="inlineStr">
+        <is>
+          <t>2001 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1886" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.245312771918, 'Longitude': -123.064910173416}</t>
+        </is>
+      </c>
+      <c r="E1886" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:16:26</t>
+        </is>
+      </c>
+      <c r="F1886" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:57:58.305Z</t>
+        </is>
+      </c>
+      <c r="G1886" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1886" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:25:23.251Z</t>
+        </is>
+      </c>
+      <c r="I1886" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" t="n">
+        <v>65538</v>
+      </c>
+      <c r="B1887" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1887" t="inlineStr">
+        <is>
+          <t>5252 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1887" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2372145, 'Longitude': -123.0650857}</t>
+        </is>
+      </c>
+      <c r="E1887" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:16:26</t>
+        </is>
+      </c>
+      <c r="F1887" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:04:02.554Z</t>
+        </is>
+      </c>
+      <c r="G1887" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1887" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:57:23.171Z</t>
+        </is>
+      </c>
+      <c r="I1887" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" t="n">
+        <v>90814</v>
+      </c>
+      <c r="B1888" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1888" t="inlineStr">
+        <is>
+          <t>2277 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1888" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.242132845692, 'Longitude': -123.058204650879}</t>
+        </is>
+      </c>
+      <c r="E1888" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:16:26</t>
+        </is>
+      </c>
+      <c r="F1888" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:04:23.064Z</t>
+        </is>
+      </c>
+      <c r="G1888" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1888" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:17:33.155Z</t>
+        </is>
+      </c>
+      <c r="I1888" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" t="n">
+        <v>39768</v>
+      </c>
+      <c r="B1889" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1889" t="inlineStr">
+        <is>
+          <t>5736 Main St</t>
+        </is>
+      </c>
+      <c r="D1889" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2325708, 'Longitude': -123.1010069}</t>
+        </is>
+      </c>
+      <c r="E1889" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:16:26</t>
+        </is>
+      </c>
+      <c r="F1889" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:10:07.548Z</t>
+        </is>
+      </c>
+      <c r="G1889" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1889" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:10:07.579Z</t>
+        </is>
+      </c>
+      <c r="I1889" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" t="n">
+        <v>9710</v>
+      </c>
+      <c r="B1890" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1890" t="inlineStr">
+        <is>
+          <t>1295 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D1890" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259878978744, 'Longitude': -123.078074455261}</t>
+        </is>
+      </c>
+      <c r="E1890" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:16:26</t>
+        </is>
+      </c>
+      <c r="F1890" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:14:39.759Z</t>
+        </is>
+      </c>
+      <c r="G1890" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1890" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:14:39.821Z</t>
+        </is>
+      </c>
+      <c r="I1890" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" t="n">
+        <v>99146</v>
+      </c>
+      <c r="B1891" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1891" t="inlineStr">
+        <is>
+          <t>1317 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D1891" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259758544957, 'Longitude': -123.077272474766}</t>
+        </is>
+      </c>
+      <c r="E1891" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:16:26</t>
+        </is>
+      </c>
+      <c r="F1891" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:11:49.042Z</t>
+        </is>
+      </c>
+      <c r="G1891" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1891" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:30:02.550Z</t>
+        </is>
+      </c>
+      <c r="I1891" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" t="n">
+        <v>65560</v>
+      </c>
+      <c r="B1892" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1892" t="inlineStr">
+        <is>
+          <t>1289 E Broadway</t>
+        </is>
+      </c>
+      <c r="D1892" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.262693682723, 'Longitude': -123.078117370605}</t>
+        </is>
+      </c>
+      <c r="E1892" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:16:26</t>
+        </is>
+      </c>
+      <c r="F1892" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:20:40.307Z</t>
+        </is>
+      </c>
+      <c r="G1892" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1892" t="inlineStr">
+        <is>
+          <t>2025-08-21T17:24:36.720Z</t>
+        </is>
+      </c>
+      <c r="I1892" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" t="n">
+        <v>65557</v>
+      </c>
+      <c r="B1893" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1893" t="inlineStr">
+        <is>
+          <t>2120 Grandview Hwy S</t>
+        </is>
+      </c>
+      <c r="D1893" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2591601, 'Longitude': -123.0617495}</t>
+        </is>
+      </c>
+      <c r="E1893" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:16:26</t>
+        </is>
+      </c>
+      <c r="F1893" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:52:41.250Z</t>
+        </is>
+      </c>
+      <c r="G1893" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1893" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:02:17.162Z</t>
+        </is>
+      </c>
+      <c r="I1893" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" t="n">
+        <v>71502</v>
+      </c>
+      <c r="B1894" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1894" t="inlineStr">
+        <is>
+          <t>2748 Main St</t>
+        </is>
+      </c>
+      <c r="D1894" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2604441, 'Longitude': -123.1005869}</t>
+        </is>
+      </c>
+      <c r="E1894" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:16:26</t>
+        </is>
+      </c>
+      <c r="F1894" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:11:46.990Z</t>
+        </is>
+      </c>
+      <c r="G1894" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H1894" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:11:47.005Z</t>
+        </is>
+      </c>
+      <c r="I1894" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" t="n">
+        <v>65559</v>
+      </c>
+      <c r="B1895" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1895" t="inlineStr">
+        <is>
+          <t>6502 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1895" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.224996944057, 'Longitude': -123.065521717072}</t>
+        </is>
+      </c>
+      <c r="E1895" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:16:26</t>
+        </is>
+      </c>
+      <c r="F1895" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:59:55.177Z</t>
+        </is>
+      </c>
+      <c r="G1895" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1895" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:06:56.250Z</t>
+        </is>
+      </c>
+      <c r="I1895" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" t="n">
+        <v>89943</v>
+      </c>
+      <c r="B1896" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1896" t="inlineStr">
+        <is>
+          <t>6808 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D1896" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2220242, 'Longitude': -123.0654247}</t>
+        </is>
+      </c>
+      <c r="E1896" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:16:26</t>
+        </is>
+      </c>
+      <c r="F1896" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:00:25.982Z</t>
+        </is>
+      </c>
+      <c r="G1896" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1896" t="inlineStr"/>
+      <c r="I1896" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B1897" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1897" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D1897" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E1897" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:16:26</t>
+        </is>
+      </c>
+      <c r="F1897" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:13:05.720Z</t>
+        </is>
+      </c>
+      <c r="G1897" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1897" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:57.027Z</t>
+        </is>
+      </c>
+      <c r="I1897" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" t="n">
+        <v>65537</v>
+      </c>
+      <c r="B1898" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1898" t="inlineStr">
+        <is>
+          <t>2918 Kingsway</t>
+        </is>
+      </c>
+      <c r="D1898" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.23608, 'Longitude': -123.0454858}</t>
+        </is>
+      </c>
+      <c r="E1898" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:16:26</t>
+        </is>
+      </c>
+      <c r="F1898" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:01:00.269Z</t>
+        </is>
+      </c>
+      <c r="G1898" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1898" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:24:44.587Z</t>
+        </is>
+      </c>
+      <c r="I1898" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B1899" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1899" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D1899" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E1899" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:16:26</t>
+        </is>
+      </c>
+      <c r="F1899" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:12:59.398Z</t>
+        </is>
+      </c>
+      <c r="G1899" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1899" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:37.661Z</t>
+        </is>
+      </c>
+      <c r="I1899" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" t="n">
+        <v>65535</v>
+      </c>
+      <c r="B1900" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1900" t="inlineStr">
+        <is>
+          <t>2605 E 49th Ave</t>
+        </is>
+      </c>
+      <c r="D1900" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2251291, 'Longitude': -123.0545048}</t>
+        </is>
+      </c>
+      <c r="E1900" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:16:26</t>
+        </is>
+      </c>
+      <c r="F1900" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:41:16.899Z</t>
+        </is>
+      </c>
+      <c r="G1900" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1900" t="inlineStr"/>
+      <c r="I1900" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" t="n">
+        <v>65539</v>
+      </c>
+      <c r="B1901" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1901" t="inlineStr">
+        <is>
+          <t>2902 Grandview Hwy</t>
+        </is>
+      </c>
+      <c r="D1901" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2579053, 'Longitude': -123.0438464}</t>
+        </is>
+      </c>
+      <c r="E1901" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:16:26</t>
+        </is>
+      </c>
+      <c r="F1901" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:14:39.186Z</t>
+        </is>
+      </c>
+      <c r="G1901" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H1901" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:56:25.496Z</t>
+        </is>
+      </c>
+      <c r="I1901" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" t="n">
+        <v>77015</v>
+      </c>
+      <c r="B1902" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1902" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1902" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169873456637, 'Longitude': -123.091178619746}</t>
+        </is>
+      </c>
+      <c r="E1902" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:18:52</t>
+        </is>
+      </c>
+      <c r="F1902" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:39:04.543Z</t>
+        </is>
+      </c>
+      <c r="G1902" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H1902" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:34:48.896Z</t>
+        </is>
+      </c>
+      <c r="I1902" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" t="n">
+        <v>65511</v>
+      </c>
+      <c r="B1903" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1903" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1903" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E1903" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:18:52</t>
+        </is>
+      </c>
+      <c r="F1903" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:03:07.680Z</t>
+        </is>
+      </c>
+      <c r="G1903" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1903" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:03:07.711Z</t>
+        </is>
+      </c>
+      <c r="I1903" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" t="n">
+        <v>86650</v>
+      </c>
+      <c r="B1904" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1904" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D1904" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169856952787, 'Longitude': -123.123961687088}</t>
+        </is>
+      </c>
+      <c r="E1904" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:18:52</t>
+        </is>
+      </c>
+      <c r="F1904" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:53:06.383Z</t>
+        </is>
+      </c>
+      <c r="G1904" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H1904" t="inlineStr">
+        <is>
+          <t>2025-08-21T16:28:22.342Z</t>
+        </is>
+      </c>
+      <c r="I1904" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" t="n">
+        <v>77218</v>
+      </c>
+      <c r="B1905" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1905" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D1905" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.173339635958, 'Longitude': -123.124954104424}</t>
+        </is>
+      </c>
+      <c r="E1905" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:18:52</t>
+        </is>
+      </c>
+      <c r="F1905" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:52:22.190Z</t>
+        </is>
+      </c>
+      <c r="G1905" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1905" t="inlineStr">
+        <is>
+          <t>2025-08-21T16:28:36.257Z</t>
+        </is>
+      </c>
+      <c r="I1905" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" t="n">
+        <v>77228</v>
+      </c>
+      <c r="B1906" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1906" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D1906" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1843249, 'Longitude': -123.1236078}</t>
+        </is>
+      </c>
+      <c r="E1906" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:18:52</t>
+        </is>
+      </c>
+      <c r="F1906" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:30:05.724Z</t>
+        </is>
+      </c>
+      <c r="G1906" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1906" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:29:09.481Z</t>
+        </is>
+      </c>
+      <c r="I1906" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" t="n">
+        <v>83384</v>
+      </c>
+      <c r="B1907" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1907" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1907" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192001, 'Longitude': -123.124004}</t>
+        </is>
+      </c>
+      <c r="E1907" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:18:52</t>
+        </is>
+      </c>
+      <c r="F1907" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:08:11.662Z</t>
+        </is>
+      </c>
+      <c r="G1907" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1907" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:11:11.242Z</t>
+        </is>
+      </c>
+      <c r="I1907" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" t="n">
+        <v>77202</v>
+      </c>
+      <c r="B1908" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1908" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D1908" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.162989071149, 'Longitude': -123.134229183197}</t>
+        </is>
+      </c>
+      <c r="E1908" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:18:52</t>
+        </is>
+      </c>
+      <c r="F1908" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:29:41.643Z</t>
+        </is>
+      </c>
+      <c r="G1908" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H1908" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:15:58.336Z</t>
+        </is>
+      </c>
+      <c r="I1908" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" t="n">
+        <v>77243</v>
+      </c>
+      <c r="B1909" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1909" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D1909" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.179182137142, 'Longitude': -123.137152791023}</t>
+        </is>
+      </c>
+      <c r="E1909" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:18:52</t>
+        </is>
+      </c>
+      <c r="F1909" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:17:32.569Z</t>
+        </is>
+      </c>
+      <c r="G1909" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1909" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:17:32.600Z</t>
+        </is>
+      </c>
+      <c r="I1909" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" t="n">
+        <v>83387</v>
+      </c>
+      <c r="B1910" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1910" t="inlineStr">
+        <is>
+          <t>710 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1910" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21081995506, 'Longitude': -123.090755939484}</t>
+        </is>
+      </c>
+      <c r="E1910" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:18:52</t>
+        </is>
+      </c>
+      <c r="F1910" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:44:10.544Z</t>
+        </is>
+      </c>
+      <c r="G1910" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1910" t="inlineStr">
+        <is>
+          <t>2025-08-21T16:49:06.781Z</t>
+        </is>
+      </c>
+      <c r="I1910" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" t="n">
+        <v>65551</v>
+      </c>
+      <c r="B1911" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1911" t="inlineStr">
+        <is>
+          <t>688 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1911" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210798928329, 'Longitude': -123.09152841568}</t>
+        </is>
+      </c>
+      <c r="E1911" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:18:52</t>
+        </is>
+      </c>
+      <c r="F1911" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:43:57.939Z</t>
+        </is>
+      </c>
+      <c r="G1911" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1911" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:32:56.143Z</t>
+        </is>
+      </c>
+      <c r="I1911" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" t="n">
+        <v>77235</v>
+      </c>
+      <c r="B1912" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C1912" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1912" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.18409178594, 'Longitude': -123.136823830688}</t>
+        </is>
+      </c>
+      <c r="E1912" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:18:52</t>
+        </is>
+      </c>
+      <c r="F1912" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:14:54.846Z</t>
+        </is>
+      </c>
+      <c r="G1912" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H1912" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:14:54.862Z</t>
+        </is>
+      </c>
+      <c r="I1912" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" t="n">
+        <v>82925</v>
+      </c>
+      <c r="B1913" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1913" t="inlineStr">
+        <is>
+          <t>350 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1913" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210245, 'Longitude': -123.099328}</t>
+        </is>
+      </c>
+      <c r="E1913" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:18:52</t>
+        </is>
+      </c>
+      <c r="F1913" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:42:56.247Z</t>
+        </is>
+      </c>
+      <c r="G1913" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1913" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:12:02.176Z</t>
+        </is>
+      </c>
+      <c r="I1913" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" t="n">
+        <v>109205</v>
+      </c>
+      <c r="B1914" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1914" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D1914" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.133556536531, 'Longitude': -123.092424273491}</t>
+        </is>
+      </c>
+      <c r="E1914" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:18:52</t>
+        </is>
+      </c>
+      <c r="F1914" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:17:08.800Z</t>
+        </is>
+      </c>
+      <c r="G1914" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1914" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:13:46.528Z</t>
+        </is>
+      </c>
+      <c r="I1914" t="n">
+        <v>175.9</v>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" t="n">
+        <v>65540</v>
+      </c>
+      <c r="B1915" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1915" t="inlineStr">
+        <is>
+          <t>196 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1915" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2106867, 'Longitude': -123.1027436}</t>
+        </is>
+      </c>
+      <c r="E1915" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:18:52</t>
+        </is>
+      </c>
+      <c r="F1915" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:09:45.288Z</t>
+        </is>
+      </c>
+      <c r="G1915" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1915" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:00:05.037Z</t>
+        </is>
+      </c>
+      <c r="I1915" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" t="n">
+        <v>65512</v>
+      </c>
+      <c r="B1916" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1916" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1916" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1328393, 'Longitude': -123.0926312}</t>
+        </is>
+      </c>
+      <c r="E1916" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:18:52</t>
+        </is>
+      </c>
+      <c r="F1916" t="inlineStr">
+        <is>
+          <t>2025-08-21T17:06:38.760Z</t>
+        </is>
+      </c>
+      <c r="G1916" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1916" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:13:50.028Z</t>
+        </is>
+      </c>
+      <c r="I1916" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" t="n">
+        <v>77205</v>
+      </c>
+      <c r="B1917" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1917" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1917" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1558882, 'Longitude': -123.1369625}</t>
+        </is>
+      </c>
+      <c r="E1917" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:18:52</t>
+        </is>
+      </c>
+      <c r="F1917" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:18:23.765Z</t>
+        </is>
+      </c>
+      <c r="G1917" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1917" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:09:47.598Z</t>
+        </is>
+      </c>
+      <c r="I1917" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B1918" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1918" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D1918" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E1918" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:18:52</t>
+        </is>
+      </c>
+      <c r="F1918" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:12:59.398Z</t>
+        </is>
+      </c>
+      <c r="G1918" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1918" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:37.661Z</t>
+        </is>
+      </c>
+      <c r="I1918" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B1919" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1919" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D1919" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E1919" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:18:52</t>
+        </is>
+      </c>
+      <c r="F1919" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:13:05.720Z</t>
+        </is>
+      </c>
+      <c r="G1919" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1919" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:57.027Z</t>
+        </is>
+      </c>
+      <c r="I1919" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" t="n">
+        <v>65556</v>
+      </c>
+      <c r="B1920" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1920" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1920" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20806537721, 'Longitude': -123.123285770416}</t>
+        </is>
+      </c>
+      <c r="E1920" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:18:52</t>
+        </is>
+      </c>
+      <c r="F1920" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:38:29.501Z</t>
+        </is>
+      </c>
+      <c r="G1920" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1920" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:46.640Z</t>
+        </is>
+      </c>
+      <c r="I1920" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" t="n">
+        <v>86937</v>
+      </c>
+      <c r="B1921" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1921" t="inlineStr">
+        <is>
+          <t>8655 Boundary Rd</t>
+        </is>
+      </c>
+      <c r="D1921" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20476, 'Longitude': -123.02398}</t>
+        </is>
+      </c>
+      <c r="E1921" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:18:52</t>
+        </is>
+      </c>
+      <c r="F1921" t="inlineStr">
+        <is>
+          <t>2025-08-21T17:35:59.576Z</t>
+        </is>
+      </c>
+      <c r="G1921" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1921" t="inlineStr">
+        <is>
+          <t>2025-08-21T08:06:44.227Z</t>
+        </is>
+      </c>
+      <c r="I1921" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" t="n">
+        <v>65515</v>
+      </c>
+      <c r="B1922" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1922" t="inlineStr">
+        <is>
+          <t>4011 Francis Rd</t>
+        </is>
+      </c>
+      <c r="D1922" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.14867500071, 'Longitude': -123.180856704712}</t>
+        </is>
+      </c>
+      <c r="E1922" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:21:15</t>
+        </is>
+      </c>
+      <c r="F1922" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:51:10.772Z</t>
+        </is>
+      </c>
+      <c r="G1922" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1922" t="inlineStr">
+        <is>
+          <t>2025-08-21T11:09:15.123Z</t>
+        </is>
+      </c>
+      <c r="I1922" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" t="n">
+        <v>77205</v>
+      </c>
+      <c r="B1923" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1923" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1923" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1558882, 'Longitude': -123.1369625}</t>
+        </is>
+      </c>
+      <c r="E1923" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:21:15</t>
+        </is>
+      </c>
+      <c r="F1923" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:18:23.765Z</t>
+        </is>
+      </c>
+      <c r="G1923" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H1923" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:09:47.598Z</t>
+        </is>
+      </c>
+      <c r="I1923" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" t="n">
+        <v>77223</v>
+      </c>
+      <c r="B1924" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1924" t="inlineStr">
+        <is>
+          <t>7991 No 1 Rd</t>
+        </is>
+      </c>
+      <c r="D1924" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.155888686563, 'Longitude': -123.181414604187}</t>
+        </is>
+      </c>
+      <c r="E1924" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:21:15</t>
+        </is>
+      </c>
+      <c r="F1924" t="inlineStr"/>
+      <c r="G1924" t="inlineStr"/>
+      <c r="H1924" t="inlineStr"/>
+      <c r="I1924" t="inlineStr"/>
+    </row>
+    <row r="1925">
+      <c r="A1925" t="n">
+        <v>65514</v>
+      </c>
+      <c r="B1925" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1925" t="inlineStr">
+        <is>
+          <t>7980 Williams Rd</t>
+        </is>
+      </c>
+      <c r="D1925" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.140582914547, 'Longitude': -123.137168884277}</t>
+        </is>
+      </c>
+      <c r="E1925" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:21:15</t>
+        </is>
+      </c>
+      <c r="F1925" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:37:13.412Z</t>
+        </is>
+      </c>
+      <c r="G1925" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1925" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:37:13.513Z</t>
+        </is>
+      </c>
+      <c r="I1925" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" t="n">
+        <v>77232</v>
+      </c>
+      <c r="B1926" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1926" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900 Westminster Hwy </t>
+        </is>
+      </c>
+      <c r="D1926" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1698419, 'Longitude': -123.159282}</t>
+        </is>
+      </c>
+      <c r="E1926" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:21:15</t>
+        </is>
+      </c>
+      <c r="F1926" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:43:00.365Z</t>
+        </is>
+      </c>
+      <c r="G1926" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H1926" t="inlineStr">
+        <is>
+          <t>2025-08-21T11:15:53.929Z</t>
+        </is>
+      </c>
+      <c r="I1926" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="n">
+        <v>77202</v>
+      </c>
+      <c r="B1927" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1927" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D1927" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.162989071149, 'Longitude': -123.134229183197}</t>
+        </is>
+      </c>
+      <c r="E1927" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:21:15</t>
+        </is>
+      </c>
+      <c r="F1927" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:29:41.643Z</t>
+        </is>
+      </c>
+      <c r="G1927" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H1927" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:15:58.336Z</t>
+        </is>
+      </c>
+      <c r="I1927" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" t="n">
+        <v>86650</v>
+      </c>
+      <c r="B1928" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1928" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D1928" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169856952787, 'Longitude': -123.123961687088}</t>
+        </is>
+      </c>
+      <c r="E1928" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:21:15</t>
+        </is>
+      </c>
+      <c r="F1928" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:53:06.383Z</t>
+        </is>
+      </c>
+      <c r="G1928" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H1928" t="inlineStr">
+        <is>
+          <t>2025-08-21T16:28:22.342Z</t>
+        </is>
+      </c>
+      <c r="I1928" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="n">
+        <v>77218</v>
+      </c>
+      <c r="B1929" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1929" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D1929" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.173339635958, 'Longitude': -123.124954104424}</t>
+        </is>
+      </c>
+      <c r="E1929" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:21:15</t>
+        </is>
+      </c>
+      <c r="F1929" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:52:22.190Z</t>
+        </is>
+      </c>
+      <c r="G1929" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1929" t="inlineStr">
+        <is>
+          <t>2025-08-21T16:28:36.257Z</t>
+        </is>
+      </c>
+      <c r="I1929" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" t="n">
+        <v>77243</v>
+      </c>
+      <c r="B1930" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1930" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D1930" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.179182137142, 'Longitude': -123.137152791023}</t>
+        </is>
+      </c>
+      <c r="E1930" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:21:15</t>
+        </is>
+      </c>
+      <c r="F1930" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:17:32.569Z</t>
+        </is>
+      </c>
+      <c r="G1930" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1930" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:17:32.600Z</t>
+        </is>
+      </c>
+      <c r="I1930" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" t="n">
+        <v>77235</v>
+      </c>
+      <c r="B1931" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C1931" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D1931" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.18409178594, 'Longitude': -123.136823830688}</t>
+        </is>
+      </c>
+      <c r="E1931" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:21:15</t>
+        </is>
+      </c>
+      <c r="F1931" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:14:54.846Z</t>
+        </is>
+      </c>
+      <c r="G1931" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H1931" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:14:54.862Z</t>
+        </is>
+      </c>
+      <c r="I1931" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="n">
+        <v>77228</v>
+      </c>
+      <c r="B1932" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1932" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D1932" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1843249, 'Longitude': -123.1236078}</t>
+        </is>
+      </c>
+      <c r="E1932" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:21:15</t>
+        </is>
+      </c>
+      <c r="F1932" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:30:05.724Z</t>
+        </is>
+      </c>
+      <c r="G1932" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1932" t="inlineStr">
+        <is>
+          <t>2025-08-21T01:29:09.481Z</t>
+        </is>
+      </c>
+      <c r="I1932" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" t="n">
+        <v>69163</v>
+      </c>
+      <c r="B1933" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1933" t="inlineStr">
+        <is>
+          <t>5111 Grant McConachie Way</t>
+        </is>
+      </c>
+      <c r="D1933" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192919, 'Longitude': -123.166797}</t>
+        </is>
+      </c>
+      <c r="E1933" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:21:15</t>
+        </is>
+      </c>
+      <c r="F1933" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:04:38.760Z</t>
+        </is>
+      </c>
+      <c r="G1933" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1933" t="inlineStr">
+        <is>
+          <t>2025-08-21T11:23:53.653Z</t>
+        </is>
+      </c>
+      <c r="I1933" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="n">
+        <v>109205</v>
+      </c>
+      <c r="B1934" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1934" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D1934" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.133556536531, 'Longitude': -123.092424273491}</t>
+        </is>
+      </c>
+      <c r="E1934" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:21:15</t>
+        </is>
+      </c>
+      <c r="F1934" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:17:08.800Z</t>
+        </is>
+      </c>
+      <c r="G1934" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1934" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:13:46.528Z</t>
+        </is>
+      </c>
+      <c r="I1934" t="n">
+        <v>175.9</v>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="n">
+        <v>65512</v>
+      </c>
+      <c r="B1935" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1935" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1935" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1328393, 'Longitude': -123.0926312}</t>
+        </is>
+      </c>
+      <c r="E1935" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:21:15</t>
+        </is>
+      </c>
+      <c r="F1935" t="inlineStr">
+        <is>
+          <t>2025-08-21T17:06:38.760Z</t>
+        </is>
+      </c>
+      <c r="G1935" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1935" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:13:50.028Z</t>
+        </is>
+      </c>
+      <c r="I1935" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="n">
+        <v>83384</v>
+      </c>
+      <c r="B1936" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1936" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1936" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192001, 'Longitude': -123.124004}</t>
+        </is>
+      </c>
+      <c r="E1936" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:21:15</t>
+        </is>
+      </c>
+      <c r="F1936" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:08:11.662Z</t>
+        </is>
+      </c>
+      <c r="G1936" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1936" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:11:11.242Z</t>
+        </is>
+      </c>
+      <c r="I1936" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="n">
+        <v>77015</v>
+      </c>
+      <c r="B1937" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C1937" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D1937" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169873456637, 'Longitude': -123.091178619746}</t>
+        </is>
+      </c>
+      <c r="E1937" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:21:15</t>
+        </is>
+      </c>
+      <c r="F1937" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:39:04.543Z</t>
+        </is>
+      </c>
+      <c r="G1937" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H1937" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:34:48.896Z</t>
+        </is>
+      </c>
+      <c r="I1937" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="n">
+        <v>107728</v>
+      </c>
+      <c r="B1938" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1938" t="inlineStr">
+        <is>
+          <t>8884 Granville St</t>
+        </is>
+      </c>
+      <c r="D1938" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2054215, 'Longitude': -123.1401677}</t>
+        </is>
+      </c>
+      <c r="E1938" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:21:15</t>
+        </is>
+      </c>
+      <c r="F1938" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:05:01.607Z</t>
+        </is>
+      </c>
+      <c r="G1938" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1938" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:03:15.411Z</t>
+        </is>
+      </c>
+      <c r="I1938" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" t="n">
+        <v>65572</v>
+      </c>
+      <c r="B1939" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1939" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D1939" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E1939" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:21:15</t>
+        </is>
+      </c>
+      <c r="F1939" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:03:43.733Z</t>
+        </is>
+      </c>
+      <c r="G1939" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1939" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:19:00.915Z</t>
+        </is>
+      </c>
+      <c r="I1939" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" t="n">
+        <v>65511</v>
+      </c>
+      <c r="B1940" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1940" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D1940" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E1940" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:21:15</t>
+        </is>
+      </c>
+      <c r="F1940" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:03:07.680Z</t>
+        </is>
+      </c>
+      <c r="G1940" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1940" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:03:07.711Z</t>
+        </is>
+      </c>
+      <c r="I1940" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="n">
+        <v>65556</v>
+      </c>
+      <c r="B1941" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1941" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1941" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20806537721, 'Longitude': -123.123285770416}</t>
+        </is>
+      </c>
+      <c r="E1941" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:21:15</t>
+        </is>
+      </c>
+      <c r="F1941" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:38:29.501Z</t>
+        </is>
+      </c>
+      <c r="G1941" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1941" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:15:46.640Z</t>
+        </is>
+      </c>
+      <c r="I1941" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="n">
+        <v>32378</v>
+      </c>
+      <c r="B1942" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1942" t="inlineStr">
+        <is>
+          <t>1613 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1942" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3288556, 'Longitude': -123.1592779}</t>
+        </is>
+      </c>
+      <c r="E1942" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:23:44</t>
+        </is>
+      </c>
+      <c r="F1942" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:23:48.032Z</t>
+        </is>
+      </c>
+      <c r="G1942" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1942" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:23:48.047Z</t>
+        </is>
+      </c>
+      <c r="I1942" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" t="n">
+        <v>98624</v>
+      </c>
+      <c r="B1943" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1943" t="inlineStr">
+        <is>
+          <t>1503 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1943" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.328484, 'Longitude': -123.15694}</t>
+        </is>
+      </c>
+      <c r="E1943" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:23:44</t>
+        </is>
+      </c>
+      <c r="F1943" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:15:01.270Z</t>
+        </is>
+      </c>
+      <c r="G1943" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1943" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:24:13.558Z</t>
+        </is>
+      </c>
+      <c r="I1943" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" t="n">
+        <v>98626</v>
+      </c>
+      <c r="B1944" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1944" t="inlineStr">
+        <is>
+          <t>1490 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1944" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.328176303121, 'Longitude': -123.1565746665}</t>
+        </is>
+      </c>
+      <c r="E1944" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:23:44</t>
+        </is>
+      </c>
+      <c r="F1944" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:14:31.488Z</t>
+        </is>
+      </c>
+      <c r="G1944" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1944" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:57:16.589Z</t>
+        </is>
+      </c>
+      <c r="I1944" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="n">
+        <v>65575</v>
+      </c>
+      <c r="B1945" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1945" t="inlineStr">
+        <is>
+          <t>1305 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1945" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.327918987512, 'Longitude': -123.151953220367}</t>
+        </is>
+      </c>
+      <c r="E1945" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:23:44</t>
+        </is>
+      </c>
+      <c r="F1945" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:13:52.915Z</t>
+        </is>
+      </c>
+      <c r="G1945" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1945" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:58:23.220Z</t>
+        </is>
+      </c>
+      <c r="I1945" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" t="n">
+        <v>65505</v>
+      </c>
+      <c r="B1946" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1946" t="inlineStr">
+        <is>
+          <t>1731 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D1946" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.325583506404, 'Longitude': -123.121590614319}</t>
+        </is>
+      </c>
+      <c r="E1946" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:23:44</t>
+        </is>
+      </c>
+      <c r="F1946" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:30:00.962Z</t>
+        </is>
+      </c>
+      <c r="G1946" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1946" t="inlineStr"/>
+      <c r="I1946" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" t="n">
+        <v>65503</v>
+      </c>
+      <c r="B1947" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1947" t="inlineStr">
+        <is>
+          <t>1980 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1947" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.324534601594, 'Longitude': -123.121654987335}</t>
+        </is>
+      </c>
+      <c r="E1947" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:23:44</t>
+        </is>
+      </c>
+      <c r="F1947" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:29:51.307Z</t>
+        </is>
+      </c>
+      <c r="G1947" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1947" t="inlineStr"/>
+      <c r="I1947" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" t="n">
+        <v>75407</v>
+      </c>
+      <c r="B1948" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1948" t="inlineStr">
+        <is>
+          <t>2698 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D1948" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3343054, 'Longitude': -123.1157865}</t>
+        </is>
+      </c>
+      <c r="E1948" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:23:44</t>
+        </is>
+      </c>
+      <c r="F1948" t="inlineStr">
+        <is>
+          <t>2025-08-21T12:33:20.396Z</t>
+        </is>
+      </c>
+      <c r="G1948" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1948" t="inlineStr"/>
+      <c r="I1948" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" t="n">
+        <v>75406</v>
+      </c>
+      <c r="B1949" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1949" t="inlineStr">
+        <is>
+          <t>1198 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1949" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.323975176559, 'Longitude': -123.107525110245}</t>
+        </is>
+      </c>
+      <c r="E1949" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:23:44</t>
+        </is>
+      </c>
+      <c r="F1949" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:12:38.776Z</t>
+        </is>
+      </c>
+      <c r="G1949" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1949" t="inlineStr"/>
+      <c r="I1949" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" t="n">
+        <v>75409</v>
+      </c>
+      <c r="B1950" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1950" t="inlineStr">
+        <is>
+          <t>3150 Edgemont Blvd</t>
+        </is>
+      </c>
+      <c r="D1950" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.338128, 'Longitude': -123.1021338}</t>
+        </is>
+      </c>
+      <c r="E1950" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:23:44</t>
+        </is>
+      </c>
+      <c r="F1950" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:36:44.148Z</t>
+        </is>
+      </c>
+      <c r="G1950" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1950" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:36:44.179Z</t>
+        </is>
+      </c>
+      <c r="I1950" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" t="n">
+        <v>98622</v>
+      </c>
+      <c r="B1951" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1951" t="inlineStr">
+        <is>
+          <t>3690 Westmount Rd</t>
+        </is>
+      </c>
+      <c r="D1951" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3459143, 'Longitude': -123.2177286}</t>
+        </is>
+      </c>
+      <c r="E1951" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:23:44</t>
+        </is>
+      </c>
+      <c r="F1951" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:24:35.951Z</t>
+        </is>
+      </c>
+      <c r="G1951" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1951" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:08:16.374Z</t>
+        </is>
+      </c>
+      <c r="I1951" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="n">
+        <v>18803</v>
+      </c>
+      <c r="B1952" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1952" t="inlineStr">
+        <is>
+          <t>2501 Westview Dr</t>
+        </is>
+      </c>
+      <c r="D1952" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.332617583893, 'Longitude': -123.088846206665}</t>
+        </is>
+      </c>
+      <c r="E1952" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:23:44</t>
+        </is>
+      </c>
+      <c r="F1952" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:42:47.743Z</t>
+        </is>
+      </c>
+      <c r="G1952" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1952" t="inlineStr"/>
+      <c r="I1952" t="inlineStr"/>
+    </row>
+    <row r="1953">
+      <c r="A1953" t="n">
+        <v>18804</v>
+      </c>
+      <c r="B1953" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1953" t="inlineStr">
+        <is>
+          <t>660 3rd St  W</t>
+        </is>
+      </c>
+      <c r="D1953" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319671, 'Longitude': -123.0902808}</t>
+        </is>
+      </c>
+      <c r="E1953" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:23:44</t>
+        </is>
+      </c>
+      <c r="F1953" t="inlineStr">
+        <is>
+          <t>2025-08-21T09:25:09.433Z</t>
+        </is>
+      </c>
+      <c r="G1953" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1953" t="inlineStr">
+        <is>
+          <t>2025-08-19T17:13:18.796Z</t>
+        </is>
+      </c>
+      <c r="I1953" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" t="n">
+        <v>32349</v>
+      </c>
+      <c r="B1954" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1954" t="inlineStr">
+        <is>
+          <t>106 W Queens St</t>
+        </is>
+      </c>
+      <c r="D1954" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.336724992343, 'Longitude': -123.072506189346}</t>
+        </is>
+      </c>
+      <c r="E1954" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:23:44</t>
+        </is>
+      </c>
+      <c r="F1954" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:36:38.345Z</t>
+        </is>
+      </c>
+      <c r="G1954" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1954" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:31:29.513Z</t>
+        </is>
+      </c>
+      <c r="I1954" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="n">
+        <v>18509</v>
+      </c>
+      <c r="B1955" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1955" t="inlineStr">
+        <is>
+          <t>2305 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D1955" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3306729, 'Longitude': -123.0728536}</t>
+        </is>
+      </c>
+      <c r="E1955" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:23:44</t>
+        </is>
+      </c>
+      <c r="F1955" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:21:45.920Z</t>
+        </is>
+      </c>
+      <c r="G1955" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1955" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:21:46.014Z</t>
+        </is>
+      </c>
+      <c r="I1955" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" t="n">
+        <v>22117</v>
+      </c>
+      <c r="B1956" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1956" t="inlineStr">
+        <is>
+          <t>1245 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D1956" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319695364751, 'Longitude': -123.07279586792}</t>
+        </is>
+      </c>
+      <c r="E1956" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:23:44</t>
+        </is>
+      </c>
+      <c r="F1956" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:01:11.574Z</t>
+        </is>
+      </c>
+      <c r="G1956" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1956" t="inlineStr">
+        <is>
+          <t>2025-08-21T17:38:20.236Z</t>
+        </is>
+      </c>
+      <c r="I1956" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B1957" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1957" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1957" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E1957" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:23:44</t>
+        </is>
+      </c>
+      <c r="F1957" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:30:02.585Z</t>
+        </is>
+      </c>
+      <c r="G1957" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1957" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:49:01.374Z</t>
+        </is>
+      </c>
+      <c r="I1957" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B1958" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1958" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1958" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E1958" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:23:44</t>
+        </is>
+      </c>
+      <c r="F1958" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:28:51.238Z</t>
+        </is>
+      </c>
+      <c r="G1958" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1958" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:11.555Z</t>
+        </is>
+      </c>
+      <c r="I1958" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B1959" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1959" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1959" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E1959" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:23:44</t>
+        </is>
+      </c>
+      <c r="F1959" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:46:17.762Z</t>
+        </is>
+      </c>
+      <c r="G1959" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1959" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:46:17.794Z</t>
+        </is>
+      </c>
+      <c r="I1959" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B1960" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1960" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D1960" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E1960" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:23:44</t>
+        </is>
+      </c>
+      <c r="F1960" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:30:17.051Z</t>
+        </is>
+      </c>
+      <c r="G1960" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1960" t="inlineStr"/>
+      <c r="I1960" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B1961" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1961" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1961" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E1961" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:23:44</t>
+        </is>
+      </c>
+      <c r="F1961" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:49:25.128Z</t>
+        </is>
+      </c>
+      <c r="G1961" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1961" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:49:25.143Z</t>
+        </is>
+      </c>
+      <c r="I1961" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" t="n">
+        <v>65542</v>
+      </c>
+      <c r="B1962" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1962" t="inlineStr">
+        <is>
+          <t>3250 MacDonald St</t>
+        </is>
+      </c>
+      <c r="D1962" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2573819, 'Longitude': -123.1680407}</t>
+        </is>
+      </c>
+      <c r="E1962" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:25:50</t>
+        </is>
+      </c>
+      <c r="F1962" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:18:11.422Z</t>
+        </is>
+      </c>
+      <c r="G1962" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1962" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:37:56.532Z</t>
+        </is>
+      </c>
+      <c r="I1962" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="n">
+        <v>65533</v>
+      </c>
+      <c r="B1963" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1963" t="inlineStr">
+        <is>
+          <t>4615 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D1963" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2449719, 'Longitude': -123.1540385}</t>
+        </is>
+      </c>
+      <c r="E1963" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:25:50</t>
+        </is>
+      </c>
+      <c r="F1963" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:41:38.634Z</t>
+        </is>
+      </c>
+      <c r="G1963" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1963" t="inlineStr"/>
+      <c r="I1963" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" t="n">
+        <v>83068</v>
+      </c>
+      <c r="B1964" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1964" t="inlineStr">
+        <is>
+          <t>3205 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D1964" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.256927568207, 'Longitude': -123.153288960457}</t>
+        </is>
+      </c>
+      <c r="E1964" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:25:50</t>
+        </is>
+      </c>
+      <c r="F1964" t="inlineStr"/>
+      <c r="G1964" t="inlineStr"/>
+      <c r="H1964" t="inlineStr"/>
+      <c r="I1964" t="inlineStr"/>
+    </row>
+    <row r="1965">
+      <c r="A1965" t="n">
+        <v>65562</v>
+      </c>
+      <c r="B1965" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1965" t="inlineStr">
+        <is>
+          <t>2808 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1965" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263883932125, 'Longitude': -123.168604373932}</t>
+        </is>
+      </c>
+      <c r="E1965" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:25:50</t>
+        </is>
+      </c>
+      <c r="F1965" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:18:31.521Z</t>
+        </is>
+      </c>
+      <c r="G1965" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1965" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:22:12.089Z</t>
+        </is>
+      </c>
+      <c r="I1965" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" t="n">
+        <v>113305</v>
+      </c>
+      <c r="B1966" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1966" t="inlineStr">
+        <is>
+          <t>3596 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1966" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234385296079, 'Longitude': -123.184762001038}</t>
+        </is>
+      </c>
+      <c r="E1966" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:25:50</t>
+        </is>
+      </c>
+      <c r="F1966" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:30:03.056Z</t>
+        </is>
+      </c>
+      <c r="G1966" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1966" t="inlineStr"/>
+      <c r="I1966" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B1967" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1967" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1967" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E1967" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:25:50</t>
+        </is>
+      </c>
+      <c r="F1967" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:49:25.128Z</t>
+        </is>
+      </c>
+      <c r="G1967" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1967" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:49:25.143Z</t>
+        </is>
+      </c>
+      <c r="I1967" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" t="n">
+        <v>65554</v>
+      </c>
+      <c r="B1968" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1968" t="inlineStr">
+        <is>
+          <t>1795 W Broadway</t>
+        </is>
+      </c>
+      <c r="D1968" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264037962303, 'Longitude': -123.145408630371}</t>
+        </is>
+      </c>
+      <c r="E1968" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:25:50</t>
+        </is>
+      </c>
+      <c r="F1968" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:52:38.101Z</t>
+        </is>
+      </c>
+      <c r="G1968" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1968" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:52:38.117Z</t>
+        </is>
+      </c>
+      <c r="I1968" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" t="n">
+        <v>65571</v>
+      </c>
+      <c r="B1969" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1969" t="inlineStr">
+        <is>
+          <t>4314 W 10th Ave</t>
+        </is>
+      </c>
+      <c r="D1969" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263533861752, 'Longitude': -123.203430175781}</t>
+        </is>
+      </c>
+      <c r="E1969" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:25:50</t>
+        </is>
+      </c>
+      <c r="F1969" t="inlineStr">
+        <is>
+          <t>2025-08-21T16:18:21.640Z</t>
+        </is>
+      </c>
+      <c r="G1969" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1969" t="inlineStr">
+        <is>
+          <t>2025-08-21T17:52:15.464Z</t>
+        </is>
+      </c>
+      <c r="I1969" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B1970" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1970" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D1970" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E1970" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:25:50</t>
+        </is>
+      </c>
+      <c r="F1970" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:30:17.051Z</t>
+        </is>
+      </c>
+      <c r="G1970" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1970" t="inlineStr"/>
+      <c r="I1970" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" t="n">
+        <v>32376</v>
+      </c>
+      <c r="B1971" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1971" t="inlineStr">
+        <is>
+          <t>1503 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D1971" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234634576953, 'Longitude': -123.139971792698}</t>
+        </is>
+      </c>
+      <c r="E1971" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:25:50</t>
+        </is>
+      </c>
+      <c r="F1971" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:26:32.706Z</t>
+        </is>
+      </c>
+      <c r="G1971" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1971" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:30:08.915Z</t>
+        </is>
+      </c>
+      <c r="I1971" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" t="n">
+        <v>65549</v>
+      </c>
+      <c r="B1972" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1972" t="inlineStr">
+        <is>
+          <t>5702 Granville St</t>
+        </is>
+      </c>
+      <c r="D1972" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234036184118, 'Longitude': -123.139244914055}</t>
+        </is>
+      </c>
+      <c r="E1972" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:25:50</t>
+        </is>
+      </c>
+      <c r="F1972" t="inlineStr">
+        <is>
+          <t>2025-08-21T17:29:54.239Z</t>
+        </is>
+      </c>
+      <c r="G1972" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1972" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:16:56.895Z</t>
+        </is>
+      </c>
+      <c r="I1972" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B1973" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1973" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1973" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E1973" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:25:50</t>
+        </is>
+      </c>
+      <c r="F1973" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:46:17.762Z</t>
+        </is>
+      </c>
+      <c r="G1973" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1973" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:46:17.794Z</t>
+        </is>
+      </c>
+      <c r="I1973" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B1974" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1974" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1974" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E1974" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:25:50</t>
+        </is>
+      </c>
+      <c r="F1974" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:28:51.238Z</t>
+        </is>
+      </c>
+      <c r="G1974" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1974" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:11.555Z</t>
+        </is>
+      </c>
+      <c r="I1974" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" t="n">
+        <v>72747</v>
+      </c>
+      <c r="B1975" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1975" t="inlineStr">
+        <is>
+          <t>1010 W King Edward Ave</t>
+        </is>
+      </c>
+      <c r="D1975" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249188, 'Longitude': -123.127767}</t>
+        </is>
+      </c>
+      <c r="E1975" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:25:50</t>
+        </is>
+      </c>
+      <c r="F1975" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:19:35.724Z</t>
+        </is>
+      </c>
+      <c r="G1975" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1975" t="inlineStr">
+        <is>
+          <t>2025-08-20T04:43:58.867Z</t>
+        </is>
+      </c>
+      <c r="I1975" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" t="n">
+        <v>32375</v>
+      </c>
+      <c r="B1976" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1976" t="inlineStr">
+        <is>
+          <t>4110 Oak St</t>
+        </is>
+      </c>
+      <c r="D1976" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.24894071957, 'Longitude': -123.127040863037}</t>
+        </is>
+      </c>
+      <c r="E1976" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:25:50</t>
+        </is>
+      </c>
+      <c r="F1976" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:18:48.556Z</t>
+        </is>
+      </c>
+      <c r="G1976" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1976" t="inlineStr"/>
+      <c r="I1976" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" t="n">
+        <v>65564</v>
+      </c>
+      <c r="B1977" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1977" t="inlineStr">
+        <is>
+          <t>5680 Oak St</t>
+        </is>
+      </c>
+      <c r="D1977" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234217162181, 'Longitude': -123.127684593201}</t>
+        </is>
+      </c>
+      <c r="E1977" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:25:50</t>
+        </is>
+      </c>
+      <c r="F1977" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:32:34.338Z</t>
+        </is>
+      </c>
+      <c r="G1977" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1977" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:37:38.272Z</t>
+        </is>
+      </c>
+      <c r="I1977" t="n">
+        <v>198.9</v>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" t="n">
+        <v>32372</v>
+      </c>
+      <c r="B1978" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1978" t="inlineStr">
+        <is>
+          <t>6525 Oak St</t>
+        </is>
+      </c>
+      <c r="D1978" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226226639452, 'Longitude': -123.128687739372}</t>
+        </is>
+      </c>
+      <c r="E1978" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:25:50</t>
+        </is>
+      </c>
+      <c r="F1978" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:34:29.486Z</t>
+        </is>
+      </c>
+      <c r="G1978" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1978" t="inlineStr">
+        <is>
+          <t>2025-08-21T16:26:51.618Z</t>
+        </is>
+      </c>
+      <c r="I1978" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B1979" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1979" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D1979" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E1979" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:25:50</t>
+        </is>
+      </c>
+      <c r="F1979" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:30:02.585Z</t>
+        </is>
+      </c>
+      <c r="G1979" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H1979" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:49:01.374Z</t>
+        </is>
+      </c>
+      <c r="I1979" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" t="n">
+        <v>65566</v>
+      </c>
+      <c r="B1980" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1980" t="inlineStr">
+        <is>
+          <t>8072 Granville St</t>
+        </is>
+      </c>
+      <c r="D1980" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.212495055855, 'Longitude': -123.14013004303}</t>
+        </is>
+      </c>
+      <c r="E1980" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:25:50</t>
+        </is>
+      </c>
+      <c r="F1980" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:15:06.805Z</t>
+        </is>
+      </c>
+      <c r="G1980" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1980" t="inlineStr">
+        <is>
+          <t>2025-08-19T19:30:08.359Z</t>
+        </is>
+      </c>
+      <c r="I1980" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" t="n">
+        <v>65572</v>
+      </c>
+      <c r="B1981" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1981" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D1981" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1981" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:25:50</t>
+        </is>
+      </c>
+      <c r="F1981" t="inlineStr"/>
+      <c r="G1981" t="inlineStr"/>
+      <c r="H1981" t="inlineStr"/>
+      <c r="I1981" t="inlineStr"/>
+    </row>
+    <row r="1982">
+      <c r="A1982" t="inlineStr">
+        <is>
+          <t>18509</t>
+        </is>
+      </c>
+      <c r="B1982" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1982" t="inlineStr">
+        <is>
+          <t>2305 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D1982" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3306729, 'Longitude': -123.0728536}</t>
+        </is>
+      </c>
+      <c r="E1982" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:26:11</t>
+        </is>
+      </c>
+      <c r="F1982" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:21:45.920Z</t>
+        </is>
+      </c>
+      <c r="G1982" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1982" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:21:46.014Z</t>
+        </is>
+      </c>
+      <c r="I1982" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="inlineStr">
+        <is>
+          <t>22117</t>
+        </is>
+      </c>
+      <c r="B1983" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1983" t="inlineStr">
+        <is>
+          <t>1245 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D1983" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319695364751, 'Longitude': -123.07279586792}</t>
+        </is>
+      </c>
+      <c r="E1983" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:26:11</t>
+        </is>
+      </c>
+      <c r="F1983" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:23:22.463Z</t>
+        </is>
+      </c>
+      <c r="G1983" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1983" t="inlineStr">
+        <is>
+          <t>2025-08-21T17:38:20.236Z</t>
+        </is>
+      </c>
+      <c r="I1983" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" t="inlineStr">
+        <is>
+          <t>32349</t>
+        </is>
+      </c>
+      <c r="B1984" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1984" t="inlineStr">
+        <is>
+          <t>106 W Queens St</t>
+        </is>
+      </c>
+      <c r="D1984" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.336724992343, 'Longitude': -123.072506189346}</t>
+        </is>
+      </c>
+      <c r="E1984" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:26:11</t>
+        </is>
+      </c>
+      <c r="F1984" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:36:38.345Z</t>
+        </is>
+      </c>
+      <c r="G1984" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H1984" t="inlineStr">
+        <is>
+          <t>2025-08-21T02:31:29.513Z</t>
+        </is>
+      </c>
+      <c r="I1984" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="inlineStr">
+        <is>
+          <t>18803</t>
+        </is>
+      </c>
+      <c r="B1985" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1985" t="inlineStr">
+        <is>
+          <t>2501 Westview Dr</t>
+        </is>
+      </c>
+      <c r="D1985" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.332617583893, 'Longitude': -123.088846206665}</t>
+        </is>
+      </c>
+      <c r="E1985" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:26:11</t>
+        </is>
+      </c>
+      <c r="F1985" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:42:47.743Z</t>
+        </is>
+      </c>
+      <c r="G1985" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1985" t="inlineStr"/>
+      <c r="I1985" t="inlineStr"/>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="inlineStr">
+        <is>
+          <t>18804</t>
+        </is>
+      </c>
+      <c r="B1986" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1986" t="inlineStr">
+        <is>
+          <t>660 3rd St  W</t>
+        </is>
+      </c>
+      <c r="D1986" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319671, 'Longitude': -123.0902808}</t>
+        </is>
+      </c>
+      <c r="E1986" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:26:11</t>
+        </is>
+      </c>
+      <c r="F1986" t="inlineStr">
+        <is>
+          <t>2025-08-21T09:25:09.433Z</t>
+        </is>
+      </c>
+      <c r="G1986" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H1986" t="inlineStr">
+        <is>
+          <t>2025-08-19T17:13:18.796Z</t>
+        </is>
+      </c>
+      <c r="I1986" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" t="inlineStr">
+        <is>
+          <t>75409</t>
+        </is>
+      </c>
+      <c r="B1987" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1987" t="inlineStr">
+        <is>
+          <t>3150 Edgemont Blvd</t>
+        </is>
+      </c>
+      <c r="D1987" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.338128, 'Longitude': -123.1021338}</t>
+        </is>
+      </c>
+      <c r="E1987" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:26:11</t>
+        </is>
+      </c>
+      <c r="F1987" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:36:44.148Z</t>
+        </is>
+      </c>
+      <c r="G1987" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1987" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:36:44.179Z</t>
+        </is>
+      </c>
+      <c r="I1987" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" t="inlineStr">
+        <is>
+          <t>75406</t>
+        </is>
+      </c>
+      <c r="B1988" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1988" t="inlineStr">
+        <is>
+          <t>1198 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1988" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.323975176559, 'Longitude': -123.107525110245}</t>
+        </is>
+      </c>
+      <c r="E1988" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:26:11</t>
+        </is>
+      </c>
+      <c r="F1988" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:12:38.776Z</t>
+        </is>
+      </c>
+      <c r="G1988" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H1988" t="inlineStr"/>
+      <c r="I1988" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" t="inlineStr">
+        <is>
+          <t>18512</t>
+        </is>
+      </c>
+      <c r="B1989" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1989" t="inlineStr">
+        <is>
+          <t>2747 Mountain Hwy</t>
+        </is>
+      </c>
+      <c r="D1989" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.333694, 'Longitude': -123.038315}</t>
+        </is>
+      </c>
+      <c r="E1989" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:26:11</t>
+        </is>
+      </c>
+      <c r="F1989" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:32:03.796Z</t>
+        </is>
+      </c>
+      <c r="G1989" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1989" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:31:56.006Z</t>
+        </is>
+      </c>
+      <c r="I1989" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="inlineStr">
+        <is>
+          <t>9706</t>
+        </is>
+      </c>
+      <c r="B1990" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1990" t="inlineStr">
+        <is>
+          <t>2979 Mountain Hwy</t>
+        </is>
+      </c>
+      <c r="D1990" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3356515, 'Longitude': -123.038272}</t>
+        </is>
+      </c>
+      <c r="E1990" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:26:11</t>
+        </is>
+      </c>
+      <c r="F1990" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:31:40.698Z</t>
+        </is>
+      </c>
+      <c r="G1990" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1990" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:35:28.452Z</t>
+        </is>
+      </c>
+      <c r="I1990" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="inlineStr">
+        <is>
+          <t>32289</t>
+        </is>
+      </c>
+      <c r="B1991" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1991" t="inlineStr">
+        <is>
+          <t>1270 Lynn Valley Rd</t>
+        </is>
+      </c>
+      <c r="D1991" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.337231840266, 'Longitude': -123.038763999939}</t>
+        </is>
+      </c>
+      <c r="E1991" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:26:11</t>
+        </is>
+      </c>
+      <c r="F1991" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:31:45.238Z</t>
+        </is>
+      </c>
+      <c r="G1991" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1991" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:31:45.254Z</t>
+        </is>
+      </c>
+      <c r="I1991" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" t="inlineStr">
+        <is>
+          <t>75407</t>
+        </is>
+      </c>
+      <c r="B1992" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1992" t="inlineStr">
+        <is>
+          <t>2698 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D1992" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3343054, 'Longitude': -123.1157865}</t>
+        </is>
+      </c>
+      <c r="E1992" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:26:11</t>
+        </is>
+      </c>
+      <c r="F1992" t="inlineStr">
+        <is>
+          <t>2025-08-21T12:33:20.396Z</t>
+        </is>
+      </c>
+      <c r="G1992" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1992" t="inlineStr"/>
+      <c r="I1992" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="inlineStr">
+        <is>
+          <t>65505</t>
+        </is>
+      </c>
+      <c r="B1993" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C1993" t="inlineStr">
+        <is>
+          <t>1731 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D1993" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.325583506404, 'Longitude': -123.121590614319}</t>
+        </is>
+      </c>
+      <c r="E1993" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:26:11</t>
+        </is>
+      </c>
+      <c r="F1993" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:30:00.962Z</t>
+        </is>
+      </c>
+      <c r="G1993" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1993" t="inlineStr"/>
+      <c r="I1993" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" t="inlineStr">
+        <is>
+          <t>65503</t>
+        </is>
+      </c>
+      <c r="B1994" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1994" t="inlineStr">
+        <is>
+          <t>1980 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D1994" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.324534601594, 'Longitude': -123.121654987335}</t>
+        </is>
+      </c>
+      <c r="E1994" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:26:11</t>
+        </is>
+      </c>
+      <c r="F1994" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:29:51.307Z</t>
+        </is>
+      </c>
+      <c r="G1994" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H1994" t="inlineStr"/>
+      <c r="I1994" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="inlineStr">
+        <is>
+          <t>18510</t>
+        </is>
+      </c>
+      <c r="B1995" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1995" t="inlineStr">
+        <is>
+          <t>1490 Main St</t>
+        </is>
+      </c>
+      <c r="D1995" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3057944, 'Longitude': -123.0328688}</t>
+        </is>
+      </c>
+      <c r="E1995" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:26:11</t>
+        </is>
+      </c>
+      <c r="F1995" t="inlineStr">
+        <is>
+          <t>2025-08-21T17:47:17.619Z</t>
+        </is>
+      </c>
+      <c r="G1995" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1995" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:22:15.178Z</t>
+        </is>
+      </c>
+      <c r="I1995" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
+        <is>
+          <t>69296</t>
+        </is>
+      </c>
+      <c r="B1996" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C1996" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185 Mountain Hwy </t>
+        </is>
+      </c>
+      <c r="D1996" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.305048881232, 'Longitude': -123.0324447155}</t>
+        </is>
+      </c>
+      <c r="E1996" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:26:11</t>
+        </is>
+      </c>
+      <c r="F1996" t="inlineStr">
+        <is>
+          <t>2025-08-21T17:47:05.234Z</t>
+        </is>
+      </c>
+      <c r="G1996" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H1996" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:22:20.808Z</t>
+        </is>
+      </c>
+      <c r="I1996" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
+        <is>
+          <t>65506</t>
+        </is>
+      </c>
+      <c r="B1997" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C1997" t="inlineStr">
+        <is>
+          <t>333 Seymour Blvd</t>
+        </is>
+      </c>
+      <c r="D1997" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1997" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:26:11</t>
+        </is>
+      </c>
+      <c r="F1997" t="inlineStr"/>
+      <c r="G1997" t="inlineStr"/>
+      <c r="H1997" t="inlineStr"/>
+      <c r="I1997" t="inlineStr"/>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
+        <is>
+          <t>98513</t>
+        </is>
+      </c>
+      <c r="B1998" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C1998" t="inlineStr">
+        <is>
+          <t>1955 Powell St</t>
+        </is>
+      </c>
+      <c r="D1998" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1998" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:26:11</t>
+        </is>
+      </c>
+      <c r="F1998" t="inlineStr"/>
+      <c r="G1998" t="inlineStr"/>
+      <c r="H1998" t="inlineStr"/>
+      <c r="I1998" t="inlineStr"/>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
+        <is>
+          <t>75410</t>
+        </is>
+      </c>
+      <c r="B1999" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C1999" t="inlineStr">
+        <is>
+          <t>2177 Dollarton Hwy</t>
+        </is>
+      </c>
+      <c r="D1999" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E1999" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:26:11</t>
+        </is>
+      </c>
+      <c r="F1999" t="inlineStr"/>
+      <c r="G1999" t="inlineStr"/>
+      <c r="H1999" t="inlineStr"/>
+      <c r="I1999" t="inlineStr"/>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
+        <is>
+          <t>65546</t>
+        </is>
+      </c>
+      <c r="B2000" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2000" t="inlineStr">
+        <is>
+          <t>1212 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D2000" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2000" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:26:11</t>
+        </is>
+      </c>
+      <c r="F2000" t="inlineStr"/>
+      <c r="G2000" t="inlineStr"/>
+      <c r="H2000" t="inlineStr"/>
+      <c r="I2000" t="inlineStr"/>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
+        <is>
+          <t>98515</t>
+        </is>
+      </c>
+      <c r="B2001" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2001" t="inlineStr">
+        <is>
+          <t>1896 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D2001" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2001" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:26:11</t>
+        </is>
+      </c>
+      <c r="F2001" t="inlineStr"/>
+      <c r="G2001" t="inlineStr"/>
+      <c r="H2001" t="inlineStr"/>
+      <c r="I2001" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/gas_prices.xlsx
+++ b/data/gas_prices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2001"/>
+  <dimension ref="A1:I2041"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79526,10 +79526,8 @@
       <c r="I1981" t="inlineStr"/>
     </row>
     <row r="1982">
-      <c r="A1982" t="inlineStr">
-        <is>
-          <t>18509</t>
-        </is>
+      <c r="A1982" t="n">
+        <v>18509</v>
       </c>
       <c r="B1982" t="inlineStr">
         <is>
@@ -79569,10 +79567,8 @@
       </c>
     </row>
     <row r="1983">
-      <c r="A1983" t="inlineStr">
-        <is>
-          <t>22117</t>
-        </is>
+      <c r="A1983" t="n">
+        <v>22117</v>
       </c>
       <c r="B1983" t="inlineStr">
         <is>
@@ -79612,10 +79608,8 @@
       </c>
     </row>
     <row r="1984">
-      <c r="A1984" t="inlineStr">
-        <is>
-          <t>32349</t>
-        </is>
+      <c r="A1984" t="n">
+        <v>32349</v>
       </c>
       <c r="B1984" t="inlineStr">
         <is>
@@ -79655,10 +79649,8 @@
       </c>
     </row>
     <row r="1985">
-      <c r="A1985" t="inlineStr">
-        <is>
-          <t>18803</t>
-        </is>
+      <c r="A1985" t="n">
+        <v>18803</v>
       </c>
       <c r="B1985" t="inlineStr">
         <is>
@@ -79692,10 +79684,8 @@
       <c r="I1985" t="inlineStr"/>
     </row>
     <row r="1986">
-      <c r="A1986" t="inlineStr">
-        <is>
-          <t>18804</t>
-        </is>
+      <c r="A1986" t="n">
+        <v>18804</v>
       </c>
       <c r="B1986" t="inlineStr">
         <is>
@@ -79735,10 +79725,8 @@
       </c>
     </row>
     <row r="1987">
-      <c r="A1987" t="inlineStr">
-        <is>
-          <t>75409</t>
-        </is>
+      <c r="A1987" t="n">
+        <v>75409</v>
       </c>
       <c r="B1987" t="inlineStr">
         <is>
@@ -79778,10 +79766,8 @@
       </c>
     </row>
     <row r="1988">
-      <c r="A1988" t="inlineStr">
-        <is>
-          <t>75406</t>
-        </is>
+      <c r="A1988" t="n">
+        <v>75406</v>
       </c>
       <c r="B1988" t="inlineStr">
         <is>
@@ -79817,10 +79803,8 @@
       </c>
     </row>
     <row r="1989">
-      <c r="A1989" t="inlineStr">
-        <is>
-          <t>18512</t>
-        </is>
+      <c r="A1989" t="n">
+        <v>18512</v>
       </c>
       <c r="B1989" t="inlineStr">
         <is>
@@ -79860,10 +79844,8 @@
       </c>
     </row>
     <row r="1990">
-      <c r="A1990" t="inlineStr">
-        <is>
-          <t>9706</t>
-        </is>
+      <c r="A1990" t="n">
+        <v>9706</v>
       </c>
       <c r="B1990" t="inlineStr">
         <is>
@@ -79903,10 +79885,8 @@
       </c>
     </row>
     <row r="1991">
-      <c r="A1991" t="inlineStr">
-        <is>
-          <t>32289</t>
-        </is>
+      <c r="A1991" t="n">
+        <v>32289</v>
       </c>
       <c r="B1991" t="inlineStr">
         <is>
@@ -79946,10 +79926,8 @@
       </c>
     </row>
     <row r="1992">
-      <c r="A1992" t="inlineStr">
-        <is>
-          <t>75407</t>
-        </is>
+      <c r="A1992" t="n">
+        <v>75407</v>
       </c>
       <c r="B1992" t="inlineStr">
         <is>
@@ -79985,10 +79963,8 @@
       </c>
     </row>
     <row r="1993">
-      <c r="A1993" t="inlineStr">
-        <is>
-          <t>65505</t>
-        </is>
+      <c r="A1993" t="n">
+        <v>65505</v>
       </c>
       <c r="B1993" t="inlineStr">
         <is>
@@ -80024,10 +80000,8 @@
       </c>
     </row>
     <row r="1994">
-      <c r="A1994" t="inlineStr">
-        <is>
-          <t>65503</t>
-        </is>
+      <c r="A1994" t="n">
+        <v>65503</v>
       </c>
       <c r="B1994" t="inlineStr">
         <is>
@@ -80063,10 +80037,8 @@
       </c>
     </row>
     <row r="1995">
-      <c r="A1995" t="inlineStr">
-        <is>
-          <t>18510</t>
-        </is>
+      <c r="A1995" t="n">
+        <v>18510</v>
       </c>
       <c r="B1995" t="inlineStr">
         <is>
@@ -80106,10 +80078,8 @@
       </c>
     </row>
     <row r="1996">
-      <c r="A1996" t="inlineStr">
-        <is>
-          <t>69296</t>
-        </is>
+      <c r="A1996" t="n">
+        <v>69296</v>
       </c>
       <c r="B1996" t="inlineStr">
         <is>
@@ -80149,10 +80119,8 @@
       </c>
     </row>
     <row r="1997">
-      <c r="A1997" t="inlineStr">
-        <is>
-          <t>65506</t>
-        </is>
+      <c r="A1997" t="n">
+        <v>65506</v>
       </c>
       <c r="B1997" t="inlineStr">
         <is>
@@ -80180,10 +80148,8 @@
       <c r="I1997" t="inlineStr"/>
     </row>
     <row r="1998">
-      <c r="A1998" t="inlineStr">
-        <is>
-          <t>98513</t>
-        </is>
+      <c r="A1998" t="n">
+        <v>98513</v>
       </c>
       <c r="B1998" t="inlineStr">
         <is>
@@ -80211,10 +80177,8 @@
       <c r="I1998" t="inlineStr"/>
     </row>
     <row r="1999">
-      <c r="A1999" t="inlineStr">
-        <is>
-          <t>75410</t>
-        </is>
+      <c r="A1999" t="n">
+        <v>75410</v>
       </c>
       <c r="B1999" t="inlineStr">
         <is>
@@ -80242,10 +80206,8 @@
       <c r="I1999" t="inlineStr"/>
     </row>
     <row r="2000">
-      <c r="A2000" t="inlineStr">
-        <is>
-          <t>65546</t>
-        </is>
+      <c r="A2000" t="n">
+        <v>65546</v>
       </c>
       <c r="B2000" t="inlineStr">
         <is>
@@ -80273,10 +80235,8 @@
       <c r="I2000" t="inlineStr"/>
     </row>
     <row r="2001">
-      <c r="A2001" t="inlineStr">
-        <is>
-          <t>98515</t>
-        </is>
+      <c r="A2001" t="n">
+        <v>98515</v>
       </c>
       <c r="B2001" t="inlineStr">
         <is>
@@ -80303,6 +80263,1382 @@
       <c r="H2001" t="inlineStr"/>
       <c r="I2001" t="inlineStr"/>
     </row>
+    <row r="2002">
+      <c r="A2002" t="n">
+        <v>65558</v>
+      </c>
+      <c r="B2002" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2002" t="inlineStr">
+        <is>
+          <t>1390 E 33rd Ave</t>
+        </is>
+      </c>
+      <c r="D2002" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.240045470021, 'Longitude': -123.076765537262}</t>
+        </is>
+      </c>
+      <c r="E2002" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:28:12</t>
+        </is>
+      </c>
+      <c r="F2002" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:56:45.639Z</t>
+        </is>
+      </c>
+      <c r="G2002" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H2002" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:56:45.655Z</t>
+        </is>
+      </c>
+      <c r="I2002" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="n">
+        <v>83394</v>
+      </c>
+      <c r="B2003" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2003" t="inlineStr">
+        <is>
+          <t>4064 Fraser St</t>
+        </is>
+      </c>
+      <c r="D2003" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.248864, 'Longitude': -123.09002}</t>
+        </is>
+      </c>
+      <c r="E2003" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:28:12</t>
+        </is>
+      </c>
+      <c r="F2003" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:22:39.047Z</t>
+        </is>
+      </c>
+      <c r="G2003" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H2003" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:02:55.309Z</t>
+        </is>
+      </c>
+      <c r="I2003" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="n">
+        <v>65573</v>
+      </c>
+      <c r="B2004" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2004" t="inlineStr">
+        <is>
+          <t>1396 E 41st Ave</t>
+        </is>
+      </c>
+      <c r="D2004" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.232593005895, 'Longitude': -123.07728856802}</t>
+        </is>
+      </c>
+      <c r="E2004" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:28:12</t>
+        </is>
+      </c>
+      <c r="F2004" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:53:30.000Z</t>
+        </is>
+      </c>
+      <c r="G2004" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2004" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:28:44.531Z</t>
+        </is>
+      </c>
+      <c r="I2004" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="n">
+        <v>80714</v>
+      </c>
+      <c r="B2005" t="inlineStr">
+        <is>
+          <t>Husky</t>
+        </is>
+      </c>
+      <c r="C2005" t="inlineStr">
+        <is>
+          <t>4933 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D2005" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2005" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:28:12</t>
+        </is>
+      </c>
+      <c r="F2005" t="inlineStr"/>
+      <c r="G2005" t="inlineStr"/>
+      <c r="H2005" t="inlineStr"/>
+      <c r="I2005" t="inlineStr"/>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="n">
+        <v>65552</v>
+      </c>
+      <c r="B2006" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2006" t="inlineStr">
+        <is>
+          <t>2001 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2006" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2006" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:28:12</t>
+        </is>
+      </c>
+      <c r="F2006" t="inlineStr"/>
+      <c r="G2006" t="inlineStr"/>
+      <c r="H2006" t="inlineStr"/>
+      <c r="I2006" t="inlineStr"/>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="n">
+        <v>65538</v>
+      </c>
+      <c r="B2007" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2007" t="inlineStr">
+        <is>
+          <t>5252 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D2007" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2007" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:28:12</t>
+        </is>
+      </c>
+      <c r="F2007" t="inlineStr"/>
+      <c r="G2007" t="inlineStr"/>
+      <c r="H2007" t="inlineStr"/>
+      <c r="I2007" t="inlineStr"/>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="n">
+        <v>90814</v>
+      </c>
+      <c r="B2008" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2008" t="inlineStr">
+        <is>
+          <t>2277 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2008" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2008" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:28:12</t>
+        </is>
+      </c>
+      <c r="F2008" t="inlineStr"/>
+      <c r="G2008" t="inlineStr"/>
+      <c r="H2008" t="inlineStr"/>
+      <c r="I2008" t="inlineStr"/>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="n">
+        <v>39768</v>
+      </c>
+      <c r="B2009" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2009" t="inlineStr">
+        <is>
+          <t>5736 Main St</t>
+        </is>
+      </c>
+      <c r="D2009" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2009" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:28:12</t>
+        </is>
+      </c>
+      <c r="F2009" t="inlineStr"/>
+      <c r="G2009" t="inlineStr"/>
+      <c r="H2009" t="inlineStr"/>
+      <c r="I2009" t="inlineStr"/>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="n">
+        <v>9710</v>
+      </c>
+      <c r="B2010" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2010" t="inlineStr">
+        <is>
+          <t>1295 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D2010" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259878978744, 'Longitude': -123.078074455261}</t>
+        </is>
+      </c>
+      <c r="E2010" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:28:12</t>
+        </is>
+      </c>
+      <c r="F2010" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:14:39.759Z</t>
+        </is>
+      </c>
+      <c r="G2010" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2010" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:14:39.821Z</t>
+        </is>
+      </c>
+      <c r="I2010" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="n">
+        <v>99146</v>
+      </c>
+      <c r="B2011" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C2011" t="inlineStr">
+        <is>
+          <t>1317 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D2011" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259758544957, 'Longitude': -123.077272474766}</t>
+        </is>
+      </c>
+      <c r="E2011" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:28:12</t>
+        </is>
+      </c>
+      <c r="F2011" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:11:49.042Z</t>
+        </is>
+      </c>
+      <c r="G2011" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H2011" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:30:02.550Z</t>
+        </is>
+      </c>
+      <c r="I2011" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="n">
+        <v>65560</v>
+      </c>
+      <c r="B2012" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2012" t="inlineStr">
+        <is>
+          <t>1289 E Broadway</t>
+        </is>
+      </c>
+      <c r="D2012" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2012" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:28:12</t>
+        </is>
+      </c>
+      <c r="F2012" t="inlineStr"/>
+      <c r="G2012" t="inlineStr"/>
+      <c r="H2012" t="inlineStr"/>
+      <c r="I2012" t="inlineStr"/>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="n">
+        <v>65557</v>
+      </c>
+      <c r="B2013" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2013" t="inlineStr">
+        <is>
+          <t>2120 Grandview Hwy S</t>
+        </is>
+      </c>
+      <c r="D2013" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2013" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:28:12</t>
+        </is>
+      </c>
+      <c r="F2013" t="inlineStr"/>
+      <c r="G2013" t="inlineStr"/>
+      <c r="H2013" t="inlineStr"/>
+      <c r="I2013" t="inlineStr"/>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="n">
+        <v>71502</v>
+      </c>
+      <c r="B2014" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2014" t="inlineStr">
+        <is>
+          <t>2748 Main St</t>
+        </is>
+      </c>
+      <c r="D2014" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2014" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:28:12</t>
+        </is>
+      </c>
+      <c r="F2014" t="inlineStr"/>
+      <c r="G2014" t="inlineStr"/>
+      <c r="H2014" t="inlineStr"/>
+      <c r="I2014" t="inlineStr"/>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="n">
+        <v>65559</v>
+      </c>
+      <c r="B2015" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2015" t="inlineStr">
+        <is>
+          <t>6502 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D2015" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2015" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:28:12</t>
+        </is>
+      </c>
+      <c r="F2015" t="inlineStr"/>
+      <c r="G2015" t="inlineStr"/>
+      <c r="H2015" t="inlineStr"/>
+      <c r="I2015" t="inlineStr"/>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="n">
+        <v>89943</v>
+      </c>
+      <c r="B2016" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2016" t="inlineStr">
+        <is>
+          <t>6808 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D2016" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2220242, 'Longitude': -123.0654247}</t>
+        </is>
+      </c>
+      <c r="E2016" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:28:12</t>
+        </is>
+      </c>
+      <c r="F2016" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:00:25.982Z</t>
+        </is>
+      </c>
+      <c r="G2016" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2016" t="inlineStr"/>
+      <c r="I2016" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B2017" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2017" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D2017" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E2017" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:28:12</t>
+        </is>
+      </c>
+      <c r="F2017" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:13:05.720Z</t>
+        </is>
+      </c>
+      <c r="G2017" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H2017" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:57.027Z</t>
+        </is>
+      </c>
+      <c r="I2017" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="n">
+        <v>65537</v>
+      </c>
+      <c r="B2018" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2018" t="inlineStr">
+        <is>
+          <t>2918 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2018" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.23608, 'Longitude': -123.0454858}</t>
+        </is>
+      </c>
+      <c r="E2018" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:28:12</t>
+        </is>
+      </c>
+      <c r="F2018" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:01:00.269Z</t>
+        </is>
+      </c>
+      <c r="G2018" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H2018" t="inlineStr">
+        <is>
+          <t>2025-08-20T18:24:44.587Z</t>
+        </is>
+      </c>
+      <c r="I2018" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B2019" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2019" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D2019" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2019" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:28:12</t>
+        </is>
+      </c>
+      <c r="F2019" t="inlineStr"/>
+      <c r="G2019" t="inlineStr"/>
+      <c r="H2019" t="inlineStr"/>
+      <c r="I2019" t="inlineStr"/>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="n">
+        <v>65535</v>
+      </c>
+      <c r="B2020" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2020" t="inlineStr">
+        <is>
+          <t>2605 E 49th Ave</t>
+        </is>
+      </c>
+      <c r="D2020" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2020" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:28:12</t>
+        </is>
+      </c>
+      <c r="F2020" t="inlineStr"/>
+      <c r="G2020" t="inlineStr"/>
+      <c r="H2020" t="inlineStr"/>
+      <c r="I2020" t="inlineStr"/>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="n">
+        <v>65539</v>
+      </c>
+      <c r="B2021" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2021" t="inlineStr">
+        <is>
+          <t>2902 Grandview Hwy</t>
+        </is>
+      </c>
+      <c r="D2021" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2021" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:28:12</t>
+        </is>
+      </c>
+      <c r="F2021" t="inlineStr"/>
+      <c r="G2021" t="inlineStr"/>
+      <c r="H2021" t="inlineStr"/>
+      <c r="I2021" t="inlineStr"/>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
+        <is>
+          <t>32378</t>
+        </is>
+      </c>
+      <c r="B2022" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2022" t="inlineStr">
+        <is>
+          <t>1613 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2022" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2022" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:30:58</t>
+        </is>
+      </c>
+      <c r="F2022" t="inlineStr"/>
+      <c r="G2022" t="inlineStr"/>
+      <c r="H2022" t="inlineStr"/>
+      <c r="I2022" t="inlineStr"/>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
+        <is>
+          <t>98624</t>
+        </is>
+      </c>
+      <c r="B2023" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2023" t="inlineStr">
+        <is>
+          <t>1503 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2023" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2023" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:30:58</t>
+        </is>
+      </c>
+      <c r="F2023" t="inlineStr"/>
+      <c r="G2023" t="inlineStr"/>
+      <c r="H2023" t="inlineStr"/>
+      <c r="I2023" t="inlineStr"/>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
+        <is>
+          <t>98626</t>
+        </is>
+      </c>
+      <c r="B2024" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2024" t="inlineStr">
+        <is>
+          <t>1490 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2024" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2024" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:30:58</t>
+        </is>
+      </c>
+      <c r="F2024" t="inlineStr"/>
+      <c r="G2024" t="inlineStr"/>
+      <c r="H2024" t="inlineStr"/>
+      <c r="I2024" t="inlineStr"/>
+    </row>
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
+        <is>
+          <t>65575</t>
+        </is>
+      </c>
+      <c r="B2025" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2025" t="inlineStr">
+        <is>
+          <t>1305 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2025" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.327918987512, 'Longitude': -123.151953220367}</t>
+        </is>
+      </c>
+      <c r="E2025" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:30:58</t>
+        </is>
+      </c>
+      <c r="F2025" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:13:52.915Z</t>
+        </is>
+      </c>
+      <c r="G2025" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2025" t="inlineStr">
+        <is>
+          <t>2025-08-20T00:58:23.220Z</t>
+        </is>
+      </c>
+      <c r="I2025" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
+        <is>
+          <t>65505</t>
+        </is>
+      </c>
+      <c r="B2026" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2026" t="inlineStr">
+        <is>
+          <t>1731 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D2026" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2026" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:30:58</t>
+        </is>
+      </c>
+      <c r="F2026" t="inlineStr"/>
+      <c r="G2026" t="inlineStr"/>
+      <c r="H2026" t="inlineStr"/>
+      <c r="I2026" t="inlineStr"/>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
+        <is>
+          <t>65503</t>
+        </is>
+      </c>
+      <c r="B2027" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2027" t="inlineStr">
+        <is>
+          <t>1980 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2027" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2027" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:30:58</t>
+        </is>
+      </c>
+      <c r="F2027" t="inlineStr"/>
+      <c r="G2027" t="inlineStr"/>
+      <c r="H2027" t="inlineStr"/>
+      <c r="I2027" t="inlineStr"/>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
+        <is>
+          <t>75407</t>
+        </is>
+      </c>
+      <c r="B2028" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2028" t="inlineStr">
+        <is>
+          <t>2698 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D2028" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3343054, 'Longitude': -123.1157865}</t>
+        </is>
+      </c>
+      <c r="E2028" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:30:58</t>
+        </is>
+      </c>
+      <c r="F2028" t="inlineStr">
+        <is>
+          <t>2025-08-21T12:33:20.396Z</t>
+        </is>
+      </c>
+      <c r="G2028" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2028" t="inlineStr"/>
+      <c r="I2028" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
+        <is>
+          <t>75406</t>
+        </is>
+      </c>
+      <c r="B2029" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2029" t="inlineStr">
+        <is>
+          <t>1198 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2029" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.323975176559, 'Longitude': -123.107525110245}</t>
+        </is>
+      </c>
+      <c r="E2029" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:30:58</t>
+        </is>
+      </c>
+      <c r="F2029" t="inlineStr">
+        <is>
+          <t>2025-08-21T04:12:38.776Z</t>
+        </is>
+      </c>
+      <c r="G2029" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H2029" t="inlineStr"/>
+      <c r="I2029" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
+        <is>
+          <t>75409</t>
+        </is>
+      </c>
+      <c r="B2030" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2030" t="inlineStr">
+        <is>
+          <t>3150 Edgemont Blvd</t>
+        </is>
+      </c>
+      <c r="D2030" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2030" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:30:58</t>
+        </is>
+      </c>
+      <c r="F2030" t="inlineStr"/>
+      <c r="G2030" t="inlineStr"/>
+      <c r="H2030" t="inlineStr"/>
+      <c r="I2030" t="inlineStr"/>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
+        <is>
+          <t>98622</t>
+        </is>
+      </c>
+      <c r="B2031" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2031" t="inlineStr">
+        <is>
+          <t>3690 Westmount Rd</t>
+        </is>
+      </c>
+      <c r="D2031" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2031" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:30:58</t>
+        </is>
+      </c>
+      <c r="F2031" t="inlineStr"/>
+      <c r="G2031" t="inlineStr"/>
+      <c r="H2031" t="inlineStr"/>
+      <c r="I2031" t="inlineStr"/>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
+        <is>
+          <t>18803</t>
+        </is>
+      </c>
+      <c r="B2032" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2032" t="inlineStr">
+        <is>
+          <t>2501 Westview Dr</t>
+        </is>
+      </c>
+      <c r="D2032" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2032" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:30:58</t>
+        </is>
+      </c>
+      <c r="F2032" t="inlineStr"/>
+      <c r="G2032" t="inlineStr"/>
+      <c r="H2032" t="inlineStr"/>
+      <c r="I2032" t="inlineStr"/>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
+        <is>
+          <t>18804</t>
+        </is>
+      </c>
+      <c r="B2033" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2033" t="inlineStr">
+        <is>
+          <t>660 3rd St  W</t>
+        </is>
+      </c>
+      <c r="D2033" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319671, 'Longitude': -123.0902808}</t>
+        </is>
+      </c>
+      <c r="E2033" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:30:58</t>
+        </is>
+      </c>
+      <c r="F2033" t="inlineStr">
+        <is>
+          <t>2025-08-21T09:25:09.433Z</t>
+        </is>
+      </c>
+      <c r="G2033" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H2033" t="inlineStr">
+        <is>
+          <t>2025-08-19T17:13:18.796Z</t>
+        </is>
+      </c>
+      <c r="I2033" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
+        <is>
+          <t>32349</t>
+        </is>
+      </c>
+      <c r="B2034" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2034" t="inlineStr">
+        <is>
+          <t>106 W Queens St</t>
+        </is>
+      </c>
+      <c r="D2034" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2034" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:30:58</t>
+        </is>
+      </c>
+      <c r="F2034" t="inlineStr"/>
+      <c r="G2034" t="inlineStr"/>
+      <c r="H2034" t="inlineStr"/>
+      <c r="I2034" t="inlineStr"/>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
+        <is>
+          <t>18509</t>
+        </is>
+      </c>
+      <c r="B2035" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2035" t="inlineStr">
+        <is>
+          <t>2305 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D2035" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2035" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:30:58</t>
+        </is>
+      </c>
+      <c r="F2035" t="inlineStr"/>
+      <c r="G2035" t="inlineStr"/>
+      <c r="H2035" t="inlineStr"/>
+      <c r="I2035" t="inlineStr"/>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
+        <is>
+          <t>22117</t>
+        </is>
+      </c>
+      <c r="B2036" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2036" t="inlineStr">
+        <is>
+          <t>1245 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D2036" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2036" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:30:58</t>
+        </is>
+      </c>
+      <c r="F2036" t="inlineStr"/>
+      <c r="G2036" t="inlineStr"/>
+      <c r="H2036" t="inlineStr"/>
+      <c r="I2036" t="inlineStr"/>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
+        <is>
+          <t>9707</t>
+        </is>
+      </c>
+      <c r="B2037" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2037" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D2037" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E2037" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:30:58</t>
+        </is>
+      </c>
+      <c r="F2037" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:30:02.585Z</t>
+        </is>
+      </c>
+      <c r="G2037" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2037" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:49:01.374Z</t>
+        </is>
+      </c>
+      <c r="I2037" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
+        <is>
+          <t>65563</t>
+        </is>
+      </c>
+      <c r="B2038" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2038" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D2038" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E2038" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:30:58</t>
+        </is>
+      </c>
+      <c r="F2038" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:28:51.238Z</t>
+        </is>
+      </c>
+      <c r="G2038" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H2038" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:11.555Z</t>
+        </is>
+      </c>
+      <c r="I2038" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
+        <is>
+          <t>65543</t>
+        </is>
+      </c>
+      <c r="B2039" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2039" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D2039" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2039" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:30:58</t>
+        </is>
+      </c>
+      <c r="F2039" t="inlineStr"/>
+      <c r="G2039" t="inlineStr"/>
+      <c r="H2039" t="inlineStr"/>
+      <c r="I2039" t="inlineStr"/>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
+        <is>
+          <t>65565</t>
+        </is>
+      </c>
+      <c r="B2040" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2040" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D2040" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E2040" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:30:58</t>
+        </is>
+      </c>
+      <c r="F2040" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:30:17.051Z</t>
+        </is>
+      </c>
+      <c r="G2040" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="H2040" t="inlineStr"/>
+      <c r="I2040" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
+        <is>
+          <t>65570</t>
+        </is>
+      </c>
+      <c r="B2041" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2041" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D2041" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E2041" t="inlineStr">
+        <is>
+          <t>2025-08-21 14:30:58</t>
+        </is>
+      </c>
+      <c r="F2041" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:49:25.128Z</t>
+        </is>
+      </c>
+      <c r="G2041" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2041" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:49:25.143Z</t>
+        </is>
+      </c>
+      <c r="I2041" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gas_prices.xlsx
+++ b/data/gas_prices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2041"/>
+  <dimension ref="A1:I2221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80936,10 +80936,8 @@
       <c r="I2021" t="inlineStr"/>
     </row>
     <row r="2022">
-      <c r="A2022" t="inlineStr">
-        <is>
-          <t>32378</t>
-        </is>
+      <c r="A2022" t="n">
+        <v>32378</v>
       </c>
       <c r="B2022" t="inlineStr">
         <is>
@@ -80967,10 +80965,8 @@
       <c r="I2022" t="inlineStr"/>
     </row>
     <row r="2023">
-      <c r="A2023" t="inlineStr">
-        <is>
-          <t>98624</t>
-        </is>
+      <c r="A2023" t="n">
+        <v>98624</v>
       </c>
       <c r="B2023" t="inlineStr">
         <is>
@@ -80998,10 +80994,8 @@
       <c r="I2023" t="inlineStr"/>
     </row>
     <row r="2024">
-      <c r="A2024" t="inlineStr">
-        <is>
-          <t>98626</t>
-        </is>
+      <c r="A2024" t="n">
+        <v>98626</v>
       </c>
       <c r="B2024" t="inlineStr">
         <is>
@@ -81029,10 +81023,8 @@
       <c r="I2024" t="inlineStr"/>
     </row>
     <row r="2025">
-      <c r="A2025" t="inlineStr">
-        <is>
-          <t>65575</t>
-        </is>
+      <c r="A2025" t="n">
+        <v>65575</v>
       </c>
       <c r="B2025" t="inlineStr">
         <is>
@@ -81072,10 +81064,8 @@
       </c>
     </row>
     <row r="2026">
-      <c r="A2026" t="inlineStr">
-        <is>
-          <t>65505</t>
-        </is>
+      <c r="A2026" t="n">
+        <v>65505</v>
       </c>
       <c r="B2026" t="inlineStr">
         <is>
@@ -81103,10 +81093,8 @@
       <c r="I2026" t="inlineStr"/>
     </row>
     <row r="2027">
-      <c r="A2027" t="inlineStr">
-        <is>
-          <t>65503</t>
-        </is>
+      <c r="A2027" t="n">
+        <v>65503</v>
       </c>
       <c r="B2027" t="inlineStr">
         <is>
@@ -81134,10 +81122,8 @@
       <c r="I2027" t="inlineStr"/>
     </row>
     <row r="2028">
-      <c r="A2028" t="inlineStr">
-        <is>
-          <t>75407</t>
-        </is>
+      <c r="A2028" t="n">
+        <v>75407</v>
       </c>
       <c r="B2028" t="inlineStr">
         <is>
@@ -81173,10 +81159,8 @@
       </c>
     </row>
     <row r="2029">
-      <c r="A2029" t="inlineStr">
-        <is>
-          <t>75406</t>
-        </is>
+      <c r="A2029" t="n">
+        <v>75406</v>
       </c>
       <c r="B2029" t="inlineStr">
         <is>
@@ -81212,10 +81196,8 @@
       </c>
     </row>
     <row r="2030">
-      <c r="A2030" t="inlineStr">
-        <is>
-          <t>75409</t>
-        </is>
+      <c r="A2030" t="n">
+        <v>75409</v>
       </c>
       <c r="B2030" t="inlineStr">
         <is>
@@ -81243,10 +81225,8 @@
       <c r="I2030" t="inlineStr"/>
     </row>
     <row r="2031">
-      <c r="A2031" t="inlineStr">
-        <is>
-          <t>98622</t>
-        </is>
+      <c r="A2031" t="n">
+        <v>98622</v>
       </c>
       <c r="B2031" t="inlineStr">
         <is>
@@ -81274,10 +81254,8 @@
       <c r="I2031" t="inlineStr"/>
     </row>
     <row r="2032">
-      <c r="A2032" t="inlineStr">
-        <is>
-          <t>18803</t>
-        </is>
+      <c r="A2032" t="n">
+        <v>18803</v>
       </c>
       <c r="B2032" t="inlineStr">
         <is>
@@ -81305,10 +81283,8 @@
       <c r="I2032" t="inlineStr"/>
     </row>
     <row r="2033">
-      <c r="A2033" t="inlineStr">
-        <is>
-          <t>18804</t>
-        </is>
+      <c r="A2033" t="n">
+        <v>18804</v>
       </c>
       <c r="B2033" t="inlineStr">
         <is>
@@ -81348,10 +81324,8 @@
       </c>
     </row>
     <row r="2034">
-      <c r="A2034" t="inlineStr">
-        <is>
-          <t>32349</t>
-        </is>
+      <c r="A2034" t="n">
+        <v>32349</v>
       </c>
       <c r="B2034" t="inlineStr">
         <is>
@@ -81379,10 +81353,8 @@
       <c r="I2034" t="inlineStr"/>
     </row>
     <row r="2035">
-      <c r="A2035" t="inlineStr">
-        <is>
-          <t>18509</t>
-        </is>
+      <c r="A2035" t="n">
+        <v>18509</v>
       </c>
       <c r="B2035" t="inlineStr">
         <is>
@@ -81410,10 +81382,8 @@
       <c r="I2035" t="inlineStr"/>
     </row>
     <row r="2036">
-      <c r="A2036" t="inlineStr">
-        <is>
-          <t>22117</t>
-        </is>
+      <c r="A2036" t="n">
+        <v>22117</v>
       </c>
       <c r="B2036" t="inlineStr">
         <is>
@@ -81441,10 +81411,8 @@
       <c r="I2036" t="inlineStr"/>
     </row>
     <row r="2037">
-      <c r="A2037" t="inlineStr">
-        <is>
-          <t>9707</t>
-        </is>
+      <c r="A2037" t="n">
+        <v>9707</v>
       </c>
       <c r="B2037" t="inlineStr">
         <is>
@@ -81484,10 +81452,8 @@
       </c>
     </row>
     <row r="2038">
-      <c r="A2038" t="inlineStr">
-        <is>
-          <t>65563</t>
-        </is>
+      <c r="A2038" t="n">
+        <v>65563</v>
       </c>
       <c r="B2038" t="inlineStr">
         <is>
@@ -81527,10 +81493,8 @@
       </c>
     </row>
     <row r="2039">
-      <c r="A2039" t="inlineStr">
-        <is>
-          <t>65543</t>
-        </is>
+      <c r="A2039" t="n">
+        <v>65543</v>
       </c>
       <c r="B2039" t="inlineStr">
         <is>
@@ -81558,10 +81522,8 @@
       <c r="I2039" t="inlineStr"/>
     </row>
     <row r="2040">
-      <c r="A2040" t="inlineStr">
-        <is>
-          <t>65565</t>
-        </is>
+      <c r="A2040" t="n">
+        <v>65565</v>
       </c>
       <c r="B2040" t="inlineStr">
         <is>
@@ -81597,10 +81559,8 @@
       </c>
     </row>
     <row r="2041">
-      <c r="A2041" t="inlineStr">
-        <is>
-          <t>65570</t>
-        </is>
+      <c r="A2041" t="n">
+        <v>65570</v>
       </c>
       <c r="B2041" t="inlineStr">
         <is>
@@ -81638,6 +81598,6418 @@
       <c r="I2041" t="n">
         <v>195.9</v>
       </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="n">
+        <v>65542</v>
+      </c>
+      <c r="B2042" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2042" t="inlineStr">
+        <is>
+          <t>3250 MacDonald St</t>
+        </is>
+      </c>
+      <c r="D2042" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2573819, 'Longitude': -123.1680407}</t>
+        </is>
+      </c>
+      <c r="E2042" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:29:53</t>
+        </is>
+      </c>
+      <c r="F2042" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:03:56.105Z</t>
+        </is>
+      </c>
+      <c r="G2042" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2042" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:37:56.532Z</t>
+        </is>
+      </c>
+      <c r="I2042" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="n">
+        <v>65533</v>
+      </c>
+      <c r="B2043" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2043" t="inlineStr">
+        <is>
+          <t>4615 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D2043" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2449719, 'Longitude': -123.1540385}</t>
+        </is>
+      </c>
+      <c r="E2043" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:29:53</t>
+        </is>
+      </c>
+      <c r="F2043" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:15:46.313Z</t>
+        </is>
+      </c>
+      <c r="G2043" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2043" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:15:46.360Z</t>
+        </is>
+      </c>
+      <c r="I2043" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="n">
+        <v>83068</v>
+      </c>
+      <c r="B2044" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2044" t="inlineStr">
+        <is>
+          <t>3205 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D2044" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.256927568207, 'Longitude': -123.153288960457}</t>
+        </is>
+      </c>
+      <c r="E2044" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:29:53</t>
+        </is>
+      </c>
+      <c r="F2044" t="inlineStr"/>
+      <c r="G2044" t="inlineStr"/>
+      <c r="H2044" t="inlineStr"/>
+      <c r="I2044" t="inlineStr"/>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="n">
+        <v>65562</v>
+      </c>
+      <c r="B2045" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2045" t="inlineStr">
+        <is>
+          <t>2808 W Broadway</t>
+        </is>
+      </c>
+      <c r="D2045" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263883932125, 'Longitude': -123.168604373932}</t>
+        </is>
+      </c>
+      <c r="E2045" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:29:53</t>
+        </is>
+      </c>
+      <c r="F2045" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:13:30.527Z</t>
+        </is>
+      </c>
+      <c r="G2045" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2045" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:22:12.089Z</t>
+        </is>
+      </c>
+      <c r="I2045" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="n">
+        <v>113305</v>
+      </c>
+      <c r="B2046" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2046" t="inlineStr">
+        <is>
+          <t>3596 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D2046" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234385296079, 'Longitude': -123.184762001038}</t>
+        </is>
+      </c>
+      <c r="E2046" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:29:53</t>
+        </is>
+      </c>
+      <c r="F2046" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:24:22.395Z</t>
+        </is>
+      </c>
+      <c r="G2046" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2046" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:45:28.860Z</t>
+        </is>
+      </c>
+      <c r="I2046" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B2047" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2047" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D2047" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E2047" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:29:53</t>
+        </is>
+      </c>
+      <c r="F2047" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:03:50.343Z</t>
+        </is>
+      </c>
+      <c r="G2047" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H2047" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:51:32.975Z</t>
+        </is>
+      </c>
+      <c r="I2047" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="n">
+        <v>65554</v>
+      </c>
+      <c r="B2048" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2048" t="inlineStr">
+        <is>
+          <t>1795 W Broadway</t>
+        </is>
+      </c>
+      <c r="D2048" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264037962303, 'Longitude': -123.145408630371}</t>
+        </is>
+      </c>
+      <c r="E2048" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:29:53</t>
+        </is>
+      </c>
+      <c r="F2048" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:18:17.016Z</t>
+        </is>
+      </c>
+      <c r="G2048" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2048" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:52:38.117Z</t>
+        </is>
+      </c>
+      <c r="I2048" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" t="n">
+        <v>65571</v>
+      </c>
+      <c r="B2049" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2049" t="inlineStr">
+        <is>
+          <t>4314 W 10th Ave</t>
+        </is>
+      </c>
+      <c r="D2049" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263533861752, 'Longitude': -123.203430175781}</t>
+        </is>
+      </c>
+      <c r="E2049" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:29:53</t>
+        </is>
+      </c>
+      <c r="F2049" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:28:25.070Z</t>
+        </is>
+      </c>
+      <c r="G2049" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2049" t="inlineStr">
+        <is>
+          <t>2025-08-21T17:52:15.464Z</t>
+        </is>
+      </c>
+      <c r="I2049" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B2050" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2050" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D2050" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E2050" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:29:53</t>
+        </is>
+      </c>
+      <c r="F2050" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:23:16.373Z</t>
+        </is>
+      </c>
+      <c r="G2050" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2050" t="inlineStr"/>
+      <c r="I2050" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" t="n">
+        <v>32376</v>
+      </c>
+      <c r="B2051" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2051" t="inlineStr">
+        <is>
+          <t>1503 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D2051" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234634576953, 'Longitude': -123.139971792698}</t>
+        </is>
+      </c>
+      <c r="E2051" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:29:53</t>
+        </is>
+      </c>
+      <c r="F2051" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:03:52.722Z</t>
+        </is>
+      </c>
+      <c r="G2051" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2051" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:24:56.809Z</t>
+        </is>
+      </c>
+      <c r="I2051" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" t="n">
+        <v>65549</v>
+      </c>
+      <c r="B2052" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2052" t="inlineStr">
+        <is>
+          <t>5702 Granville St</t>
+        </is>
+      </c>
+      <c r="D2052" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234036184118, 'Longitude': -123.139244914055}</t>
+        </is>
+      </c>
+      <c r="E2052" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:29:53</t>
+        </is>
+      </c>
+      <c r="F2052" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:47:29.946Z</t>
+        </is>
+      </c>
+      <c r="G2052" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2052" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:05:40.501Z</t>
+        </is>
+      </c>
+      <c r="I2052" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B2053" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2053" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D2053" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E2053" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:29:53</t>
+        </is>
+      </c>
+      <c r="F2053" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:46:17.762Z</t>
+        </is>
+      </c>
+      <c r="G2053" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2053" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:46:17.794Z</t>
+        </is>
+      </c>
+      <c r="I2053" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B2054" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2054" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D2054" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E2054" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:29:53</t>
+        </is>
+      </c>
+      <c r="F2054" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:28:51.238Z</t>
+        </is>
+      </c>
+      <c r="G2054" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H2054" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:11.555Z</t>
+        </is>
+      </c>
+      <c r="I2054" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="n">
+        <v>72747</v>
+      </c>
+      <c r="B2055" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2055" t="inlineStr">
+        <is>
+          <t>1010 W King Edward Ave</t>
+        </is>
+      </c>
+      <c r="D2055" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249188, 'Longitude': -123.127767}</t>
+        </is>
+      </c>
+      <c r="E2055" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:29:53</t>
+        </is>
+      </c>
+      <c r="F2055" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:13:46.907Z</t>
+        </is>
+      </c>
+      <c r="G2055" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2055" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:51:18.062Z</t>
+        </is>
+      </c>
+      <c r="I2055" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="n">
+        <v>32375</v>
+      </c>
+      <c r="B2056" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2056" t="inlineStr">
+        <is>
+          <t>4110 Oak St</t>
+        </is>
+      </c>
+      <c r="D2056" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.24894071957, 'Longitude': -123.127040863037}</t>
+        </is>
+      </c>
+      <c r="E2056" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:29:53</t>
+        </is>
+      </c>
+      <c r="F2056" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:14:35.071Z</t>
+        </is>
+      </c>
+      <c r="G2056" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2056" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:17:09.064Z</t>
+        </is>
+      </c>
+      <c r="I2056" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="n">
+        <v>65564</v>
+      </c>
+      <c r="B2057" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2057" t="inlineStr">
+        <is>
+          <t>5680 Oak St</t>
+        </is>
+      </c>
+      <c r="D2057" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234217162181, 'Longitude': -123.127684593201}</t>
+        </is>
+      </c>
+      <c r="E2057" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:29:53</t>
+        </is>
+      </c>
+      <c r="F2057" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:36:26.920Z</t>
+        </is>
+      </c>
+      <c r="G2057" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2057" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:48:09.828Z</t>
+        </is>
+      </c>
+      <c r="I2057" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" t="n">
+        <v>32372</v>
+      </c>
+      <c r="B2058" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2058" t="inlineStr">
+        <is>
+          <t>6525 Oak St</t>
+        </is>
+      </c>
+      <c r="D2058" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226226639452, 'Longitude': -123.128687739372}</t>
+        </is>
+      </c>
+      <c r="E2058" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:29:53</t>
+        </is>
+      </c>
+      <c r="F2058" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:25:08.864Z</t>
+        </is>
+      </c>
+      <c r="G2058" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2058" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:46:43.341Z</t>
+        </is>
+      </c>
+      <c r="I2058" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B2059" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2059" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D2059" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E2059" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:29:53</t>
+        </is>
+      </c>
+      <c r="F2059" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:49:20.616Z</t>
+        </is>
+      </c>
+      <c r="G2059" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2059" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:49:01.374Z</t>
+        </is>
+      </c>
+      <c r="I2059" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="n">
+        <v>65566</v>
+      </c>
+      <c r="B2060" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2060" t="inlineStr">
+        <is>
+          <t>8072 Granville St</t>
+        </is>
+      </c>
+      <c r="D2060" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.212495055855, 'Longitude': -123.14013004303}</t>
+        </is>
+      </c>
+      <c r="E2060" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:29:53</t>
+        </is>
+      </c>
+      <c r="F2060" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:15:48.444Z</t>
+        </is>
+      </c>
+      <c r="G2060" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2060" t="inlineStr"/>
+      <c r="I2060" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" t="n">
+        <v>65572</v>
+      </c>
+      <c r="B2061" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2061" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D2061" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E2061" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:29:53</t>
+        </is>
+      </c>
+      <c r="F2061" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:15:25.202Z</t>
+        </is>
+      </c>
+      <c r="G2061" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2061" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:50:22.600Z</t>
+        </is>
+      </c>
+      <c r="I2061" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="n">
+        <v>65558</v>
+      </c>
+      <c r="B2062" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2062" t="inlineStr">
+        <is>
+          <t>1390 E 33rd Ave</t>
+        </is>
+      </c>
+      <c r="D2062" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.240045470021, 'Longitude': -123.076765537262}</t>
+        </is>
+      </c>
+      <c r="E2062" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:32:45</t>
+        </is>
+      </c>
+      <c r="F2062" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:29:40.826Z</t>
+        </is>
+      </c>
+      <c r="G2062" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="H2062" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:25:03.687Z</t>
+        </is>
+      </c>
+      <c r="I2062" t="n">
+        <v>178.9</v>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="n">
+        <v>83394</v>
+      </c>
+      <c r="B2063" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2063" t="inlineStr">
+        <is>
+          <t>4064 Fraser St</t>
+        </is>
+      </c>
+      <c r="D2063" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.248864, 'Longitude': -123.09002}</t>
+        </is>
+      </c>
+      <c r="E2063" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:32:45</t>
+        </is>
+      </c>
+      <c r="F2063" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:40:06.733Z</t>
+        </is>
+      </c>
+      <c r="G2063" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2063" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:08:24.169Z</t>
+        </is>
+      </c>
+      <c r="I2063" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="n">
+        <v>65573</v>
+      </c>
+      <c r="B2064" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2064" t="inlineStr">
+        <is>
+          <t>1396 E 41st Ave</t>
+        </is>
+      </c>
+      <c r="D2064" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.232593005895, 'Longitude': -123.07728856802}</t>
+        </is>
+      </c>
+      <c r="E2064" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:32:45</t>
+        </is>
+      </c>
+      <c r="F2064" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:27:10.581Z</t>
+        </is>
+      </c>
+      <c r="G2064" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2064" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:57:31.376Z</t>
+        </is>
+      </c>
+      <c r="I2064" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="n">
+        <v>80714</v>
+      </c>
+      <c r="B2065" t="inlineStr">
+        <is>
+          <t>Husky</t>
+        </is>
+      </c>
+      <c r="C2065" t="inlineStr">
+        <is>
+          <t>4933 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D2065" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2397388, 'Longitude': -123.065748}</t>
+        </is>
+      </c>
+      <c r="E2065" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:32:45</t>
+        </is>
+      </c>
+      <c r="F2065" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:07:24.794Z</t>
+        </is>
+      </c>
+      <c r="G2065" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2065" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:47:42.715Z</t>
+        </is>
+      </c>
+      <c r="I2065" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="n">
+        <v>65552</v>
+      </c>
+      <c r="B2066" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2066" t="inlineStr">
+        <is>
+          <t>2001 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2066" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.245312771918, 'Longitude': -123.064910173416}</t>
+        </is>
+      </c>
+      <c r="E2066" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:32:45</t>
+        </is>
+      </c>
+      <c r="F2066" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:07:43.095Z</t>
+        </is>
+      </c>
+      <c r="G2066" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H2066" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:59:26.854Z</t>
+        </is>
+      </c>
+      <c r="I2066" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="n">
+        <v>65538</v>
+      </c>
+      <c r="B2067" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2067" t="inlineStr">
+        <is>
+          <t>5252 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D2067" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2372145, 'Longitude': -123.0650857}</t>
+        </is>
+      </c>
+      <c r="E2067" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:32:45</t>
+        </is>
+      </c>
+      <c r="F2067" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:47:51.264Z</t>
+        </is>
+      </c>
+      <c r="G2067" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2067" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:47:51.295Z</t>
+        </is>
+      </c>
+      <c r="I2067" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="n">
+        <v>90814</v>
+      </c>
+      <c r="B2068" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2068" t="inlineStr">
+        <is>
+          <t>2277 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2068" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.242132845692, 'Longitude': -123.058204650879}</t>
+        </is>
+      </c>
+      <c r="E2068" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:32:45</t>
+        </is>
+      </c>
+      <c r="F2068" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:58:58.737Z</t>
+        </is>
+      </c>
+      <c r="G2068" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2068" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:58:58.753Z</t>
+        </is>
+      </c>
+      <c r="I2068" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="n">
+        <v>39768</v>
+      </c>
+      <c r="B2069" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2069" t="inlineStr">
+        <is>
+          <t>5736 Main St</t>
+        </is>
+      </c>
+      <c r="D2069" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2325708, 'Longitude': -123.1010069}</t>
+        </is>
+      </c>
+      <c r="E2069" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:32:45</t>
+        </is>
+      </c>
+      <c r="F2069" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:00:42.103Z</t>
+        </is>
+      </c>
+      <c r="G2069" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2069" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:10:07.579Z</t>
+        </is>
+      </c>
+      <c r="I2069" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="n">
+        <v>9710</v>
+      </c>
+      <c r="B2070" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2070" t="inlineStr">
+        <is>
+          <t>1295 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D2070" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259878978744, 'Longitude': -123.078074455261}</t>
+        </is>
+      </c>
+      <c r="E2070" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:32:45</t>
+        </is>
+      </c>
+      <c r="F2070" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:29:41.384Z</t>
+        </is>
+      </c>
+      <c r="G2070" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H2070" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:29:41.417Z</t>
+        </is>
+      </c>
+      <c r="I2070" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="n">
+        <v>99146</v>
+      </c>
+      <c r="B2071" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C2071" t="inlineStr">
+        <is>
+          <t>1317 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D2071" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259758544957, 'Longitude': -123.077272474766}</t>
+        </is>
+      </c>
+      <c r="E2071" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:32:45</t>
+        </is>
+      </c>
+      <c r="F2071" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:29:55.779Z</t>
+        </is>
+      </c>
+      <c r="G2071" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="H2071" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:29:55.810Z</t>
+        </is>
+      </c>
+      <c r="I2071" t="n">
+        <v>178.9</v>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="n">
+        <v>65560</v>
+      </c>
+      <c r="B2072" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2072" t="inlineStr">
+        <is>
+          <t>1289 E Broadway</t>
+        </is>
+      </c>
+      <c r="D2072" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.262693682723, 'Longitude': -123.078117370605}</t>
+        </is>
+      </c>
+      <c r="E2072" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:32:45</t>
+        </is>
+      </c>
+      <c r="F2072" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:29:11.224Z</t>
+        </is>
+      </c>
+      <c r="G2072" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="H2072" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:29:11.256Z</t>
+        </is>
+      </c>
+      <c r="I2072" t="n">
+        <v>178.9</v>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="n">
+        <v>65557</v>
+      </c>
+      <c r="B2073" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2073" t="inlineStr">
+        <is>
+          <t>2120 Grandview Hwy S</t>
+        </is>
+      </c>
+      <c r="D2073" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2591601, 'Longitude': -123.0617495}</t>
+        </is>
+      </c>
+      <c r="E2073" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:32:45</t>
+        </is>
+      </c>
+      <c r="F2073" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:43:55.680Z</t>
+        </is>
+      </c>
+      <c r="G2073" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2073" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:21:26.056Z</t>
+        </is>
+      </c>
+      <c r="I2073" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="n">
+        <v>71502</v>
+      </c>
+      <c r="B2074" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2074" t="inlineStr">
+        <is>
+          <t>2748 Main St</t>
+        </is>
+      </c>
+      <c r="D2074" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2604441, 'Longitude': -123.1005869}</t>
+        </is>
+      </c>
+      <c r="E2074" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:32:45</t>
+        </is>
+      </c>
+      <c r="F2074" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:07:09.854Z</t>
+        </is>
+      </c>
+      <c r="G2074" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2074" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:07:09.939Z</t>
+        </is>
+      </c>
+      <c r="I2074" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="n">
+        <v>65559</v>
+      </c>
+      <c r="B2075" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2075" t="inlineStr">
+        <is>
+          <t>6502 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D2075" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.224996944057, 'Longitude': -123.065521717072}</t>
+        </is>
+      </c>
+      <c r="E2075" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:32:45</t>
+        </is>
+      </c>
+      <c r="F2075" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:59:55.177Z</t>
+        </is>
+      </c>
+      <c r="G2075" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2075" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:06:56.250Z</t>
+        </is>
+      </c>
+      <c r="I2075" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="n">
+        <v>89943</v>
+      </c>
+      <c r="B2076" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2076" t="inlineStr">
+        <is>
+          <t>6808 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D2076" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2220242, 'Longitude': -123.0654247}</t>
+        </is>
+      </c>
+      <c r="E2076" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:32:45</t>
+        </is>
+      </c>
+      <c r="F2076" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:43:44.299Z</t>
+        </is>
+      </c>
+      <c r="G2076" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2076" t="inlineStr"/>
+      <c r="I2076" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B2077" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2077" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D2077" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E2077" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:32:45</t>
+        </is>
+      </c>
+      <c r="F2077" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:15:34.212Z</t>
+        </is>
+      </c>
+      <c r="G2077" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2077" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:57.027Z</t>
+        </is>
+      </c>
+      <c r="I2077" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="n">
+        <v>65537</v>
+      </c>
+      <c r="B2078" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2078" t="inlineStr">
+        <is>
+          <t>2918 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2078" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.23608, 'Longitude': -123.0454858}</t>
+        </is>
+      </c>
+      <c r="E2078" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:32:45</t>
+        </is>
+      </c>
+      <c r="F2078" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:56:15.831Z</t>
+        </is>
+      </c>
+      <c r="G2078" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2078" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:56:15.847Z</t>
+        </is>
+      </c>
+      <c r="I2078" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B2079" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2079" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D2079" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E2079" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:32:45</t>
+        </is>
+      </c>
+      <c r="F2079" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:04:16.272Z</t>
+        </is>
+      </c>
+      <c r="G2079" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2079" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:37.661Z</t>
+        </is>
+      </c>
+      <c r="I2079" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="n">
+        <v>65535</v>
+      </c>
+      <c r="B2080" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2080" t="inlineStr">
+        <is>
+          <t>2605 E 49th Ave</t>
+        </is>
+      </c>
+      <c r="D2080" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2080" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:32:45</t>
+        </is>
+      </c>
+      <c r="F2080" t="inlineStr"/>
+      <c r="G2080" t="inlineStr"/>
+      <c r="H2080" t="inlineStr"/>
+      <c r="I2080" t="inlineStr"/>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="n">
+        <v>65539</v>
+      </c>
+      <c r="B2081" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2081" t="inlineStr">
+        <is>
+          <t>2902 Grandview Hwy</t>
+        </is>
+      </c>
+      <c r="D2081" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2081" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:32:45</t>
+        </is>
+      </c>
+      <c r="F2081" t="inlineStr"/>
+      <c r="G2081" t="inlineStr"/>
+      <c r="H2081" t="inlineStr"/>
+      <c r="I2081" t="inlineStr"/>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="n">
+        <v>65542</v>
+      </c>
+      <c r="B2082" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2082" t="inlineStr">
+        <is>
+          <t>3250 MacDonald St</t>
+        </is>
+      </c>
+      <c r="D2082" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2573819, 'Longitude': -123.1680407}</t>
+        </is>
+      </c>
+      <c r="E2082" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:33:30</t>
+        </is>
+      </c>
+      <c r="F2082" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:03:56.105Z</t>
+        </is>
+      </c>
+      <c r="G2082" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2082" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:37:56.532Z</t>
+        </is>
+      </c>
+      <c r="I2082" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="n">
+        <v>65533</v>
+      </c>
+      <c r="B2083" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2083" t="inlineStr">
+        <is>
+          <t>4615 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D2083" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2449719, 'Longitude': -123.1540385}</t>
+        </is>
+      </c>
+      <c r="E2083" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:33:30</t>
+        </is>
+      </c>
+      <c r="F2083" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:15:46.313Z</t>
+        </is>
+      </c>
+      <c r="G2083" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2083" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:15:46.360Z</t>
+        </is>
+      </c>
+      <c r="I2083" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="n">
+        <v>83068</v>
+      </c>
+      <c r="B2084" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2084" t="inlineStr">
+        <is>
+          <t>3205 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D2084" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.256927568207, 'Longitude': -123.153288960457}</t>
+        </is>
+      </c>
+      <c r="E2084" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:33:30</t>
+        </is>
+      </c>
+      <c r="F2084" t="inlineStr"/>
+      <c r="G2084" t="inlineStr"/>
+      <c r="H2084" t="inlineStr"/>
+      <c r="I2084" t="inlineStr"/>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="n">
+        <v>65562</v>
+      </c>
+      <c r="B2085" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2085" t="inlineStr">
+        <is>
+          <t>2808 W Broadway</t>
+        </is>
+      </c>
+      <c r="D2085" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263883932125, 'Longitude': -123.168604373932}</t>
+        </is>
+      </c>
+      <c r="E2085" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:33:30</t>
+        </is>
+      </c>
+      <c r="F2085" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:13:30.527Z</t>
+        </is>
+      </c>
+      <c r="G2085" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2085" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:22:12.089Z</t>
+        </is>
+      </c>
+      <c r="I2085" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="n">
+        <v>113305</v>
+      </c>
+      <c r="B2086" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2086" t="inlineStr">
+        <is>
+          <t>3596 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D2086" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234385296079, 'Longitude': -123.184762001038}</t>
+        </is>
+      </c>
+      <c r="E2086" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:33:30</t>
+        </is>
+      </c>
+      <c r="F2086" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:24:22.395Z</t>
+        </is>
+      </c>
+      <c r="G2086" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2086" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:45:28.860Z</t>
+        </is>
+      </c>
+      <c r="I2086" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B2087" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2087" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D2087" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E2087" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:33:30</t>
+        </is>
+      </c>
+      <c r="F2087" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:03:50.343Z</t>
+        </is>
+      </c>
+      <c r="G2087" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H2087" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:51:32.975Z</t>
+        </is>
+      </c>
+      <c r="I2087" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="n">
+        <v>65554</v>
+      </c>
+      <c r="B2088" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2088" t="inlineStr">
+        <is>
+          <t>1795 W Broadway</t>
+        </is>
+      </c>
+      <c r="D2088" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264037962303, 'Longitude': -123.145408630371}</t>
+        </is>
+      </c>
+      <c r="E2088" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:33:30</t>
+        </is>
+      </c>
+      <c r="F2088" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:18:17.016Z</t>
+        </is>
+      </c>
+      <c r="G2088" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2088" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:52:38.117Z</t>
+        </is>
+      </c>
+      <c r="I2088" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="n">
+        <v>65571</v>
+      </c>
+      <c r="B2089" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2089" t="inlineStr">
+        <is>
+          <t>4314 W 10th Ave</t>
+        </is>
+      </c>
+      <c r="D2089" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263533861752, 'Longitude': -123.203430175781}</t>
+        </is>
+      </c>
+      <c r="E2089" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:33:30</t>
+        </is>
+      </c>
+      <c r="F2089" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:28:25.070Z</t>
+        </is>
+      </c>
+      <c r="G2089" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2089" t="inlineStr">
+        <is>
+          <t>2025-08-21T17:52:15.464Z</t>
+        </is>
+      </c>
+      <c r="I2089" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B2090" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2090" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D2090" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E2090" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:33:30</t>
+        </is>
+      </c>
+      <c r="F2090" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:23:16.373Z</t>
+        </is>
+      </c>
+      <c r="G2090" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2090" t="inlineStr"/>
+      <c r="I2090" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="n">
+        <v>32376</v>
+      </c>
+      <c r="B2091" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2091" t="inlineStr">
+        <is>
+          <t>1503 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D2091" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234634576953, 'Longitude': -123.139971792698}</t>
+        </is>
+      </c>
+      <c r="E2091" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:33:30</t>
+        </is>
+      </c>
+      <c r="F2091" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:03:52.722Z</t>
+        </is>
+      </c>
+      <c r="G2091" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2091" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:24:56.809Z</t>
+        </is>
+      </c>
+      <c r="I2091" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="n">
+        <v>65549</v>
+      </c>
+      <c r="B2092" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2092" t="inlineStr">
+        <is>
+          <t>5702 Granville St</t>
+        </is>
+      </c>
+      <c r="D2092" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234036184118, 'Longitude': -123.139244914055}</t>
+        </is>
+      </c>
+      <c r="E2092" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:33:30</t>
+        </is>
+      </c>
+      <c r="F2092" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:47:29.946Z</t>
+        </is>
+      </c>
+      <c r="G2092" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2092" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:05:40.501Z</t>
+        </is>
+      </c>
+      <c r="I2092" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B2093" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2093" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D2093" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E2093" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:33:30</t>
+        </is>
+      </c>
+      <c r="F2093" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:46:17.762Z</t>
+        </is>
+      </c>
+      <c r="G2093" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2093" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:46:17.794Z</t>
+        </is>
+      </c>
+      <c r="I2093" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B2094" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2094" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D2094" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E2094" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:33:30</t>
+        </is>
+      </c>
+      <c r="F2094" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:28:51.238Z</t>
+        </is>
+      </c>
+      <c r="G2094" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H2094" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:11.555Z</t>
+        </is>
+      </c>
+      <c r="I2094" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="n">
+        <v>72747</v>
+      </c>
+      <c r="B2095" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2095" t="inlineStr">
+        <is>
+          <t>1010 W King Edward Ave</t>
+        </is>
+      </c>
+      <c r="D2095" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2095" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:33:30</t>
+        </is>
+      </c>
+      <c r="F2095" t="inlineStr"/>
+      <c r="G2095" t="inlineStr"/>
+      <c r="H2095" t="inlineStr"/>
+      <c r="I2095" t="inlineStr"/>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="n">
+        <v>32375</v>
+      </c>
+      <c r="B2096" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2096" t="inlineStr">
+        <is>
+          <t>4110 Oak St</t>
+        </is>
+      </c>
+      <c r="D2096" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2096" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:33:30</t>
+        </is>
+      </c>
+      <c r="F2096" t="inlineStr"/>
+      <c r="G2096" t="inlineStr"/>
+      <c r="H2096" t="inlineStr"/>
+      <c r="I2096" t="inlineStr"/>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="n">
+        <v>65564</v>
+      </c>
+      <c r="B2097" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2097" t="inlineStr">
+        <is>
+          <t>5680 Oak St</t>
+        </is>
+      </c>
+      <c r="D2097" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234217162181, 'Longitude': -123.127684593201}</t>
+        </is>
+      </c>
+      <c r="E2097" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:33:30</t>
+        </is>
+      </c>
+      <c r="F2097" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:29:33.603Z</t>
+        </is>
+      </c>
+      <c r="G2097" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2097" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:48:09.828Z</t>
+        </is>
+      </c>
+      <c r="I2097" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="n">
+        <v>32372</v>
+      </c>
+      <c r="B2098" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2098" t="inlineStr">
+        <is>
+          <t>6525 Oak St</t>
+        </is>
+      </c>
+      <c r="D2098" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226226639452, 'Longitude': -123.128687739372}</t>
+        </is>
+      </c>
+      <c r="E2098" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:33:30</t>
+        </is>
+      </c>
+      <c r="F2098" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:25:08.864Z</t>
+        </is>
+      </c>
+      <c r="G2098" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2098" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:46:43.341Z</t>
+        </is>
+      </c>
+      <c r="I2098" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B2099" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2099" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D2099" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2099" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:33:30</t>
+        </is>
+      </c>
+      <c r="F2099" t="inlineStr"/>
+      <c r="G2099" t="inlineStr"/>
+      <c r="H2099" t="inlineStr"/>
+      <c r="I2099" t="inlineStr"/>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="n">
+        <v>65566</v>
+      </c>
+      <c r="B2100" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2100" t="inlineStr">
+        <is>
+          <t>8072 Granville St</t>
+        </is>
+      </c>
+      <c r="D2100" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2100" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:33:30</t>
+        </is>
+      </c>
+      <c r="F2100" t="inlineStr"/>
+      <c r="G2100" t="inlineStr"/>
+      <c r="H2100" t="inlineStr"/>
+      <c r="I2100" t="inlineStr"/>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="n">
+        <v>65572</v>
+      </c>
+      <c r="B2101" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2101" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D2101" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E2101" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:33:30</t>
+        </is>
+      </c>
+      <c r="F2101" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:15:25.202Z</t>
+        </is>
+      </c>
+      <c r="G2101" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2101" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:50:22.600Z</t>
+        </is>
+      </c>
+      <c r="I2101" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="n">
+        <v>65542</v>
+      </c>
+      <c r="B2102" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2102" t="inlineStr">
+        <is>
+          <t>3250 MacDonald St</t>
+        </is>
+      </c>
+      <c r="D2102" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2573819, 'Longitude': -123.1680407}</t>
+        </is>
+      </c>
+      <c r="E2102" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:34:37</t>
+        </is>
+      </c>
+      <c r="F2102" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:03:56.105Z</t>
+        </is>
+      </c>
+      <c r="G2102" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2102" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:37:56.532Z</t>
+        </is>
+      </c>
+      <c r="I2102" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="n">
+        <v>65533</v>
+      </c>
+      <c r="B2103" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2103" t="inlineStr">
+        <is>
+          <t>4615 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D2103" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2449719, 'Longitude': -123.1540385}</t>
+        </is>
+      </c>
+      <c r="E2103" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:34:37</t>
+        </is>
+      </c>
+      <c r="F2103" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:15:46.313Z</t>
+        </is>
+      </c>
+      <c r="G2103" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2103" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:15:46.360Z</t>
+        </is>
+      </c>
+      <c r="I2103" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="n">
+        <v>83068</v>
+      </c>
+      <c r="B2104" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2104" t="inlineStr">
+        <is>
+          <t>3205 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D2104" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.256927568207, 'Longitude': -123.153288960457}</t>
+        </is>
+      </c>
+      <c r="E2104" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:34:37</t>
+        </is>
+      </c>
+      <c r="F2104" t="inlineStr"/>
+      <c r="G2104" t="inlineStr"/>
+      <c r="H2104" t="inlineStr"/>
+      <c r="I2104" t="inlineStr"/>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="n">
+        <v>65562</v>
+      </c>
+      <c r="B2105" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2105" t="inlineStr">
+        <is>
+          <t>2808 W Broadway</t>
+        </is>
+      </c>
+      <c r="D2105" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2105" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:34:37</t>
+        </is>
+      </c>
+      <c r="F2105" t="inlineStr"/>
+      <c r="G2105" t="inlineStr"/>
+      <c r="H2105" t="inlineStr"/>
+      <c r="I2105" t="inlineStr"/>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="n">
+        <v>113305</v>
+      </c>
+      <c r="B2106" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2106" t="inlineStr">
+        <is>
+          <t>3596 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D2106" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2106" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:34:37</t>
+        </is>
+      </c>
+      <c r="F2106" t="inlineStr"/>
+      <c r="G2106" t="inlineStr"/>
+      <c r="H2106" t="inlineStr"/>
+      <c r="I2106" t="inlineStr"/>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B2107" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2107" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D2107" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2107" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:34:37</t>
+        </is>
+      </c>
+      <c r="F2107" t="inlineStr"/>
+      <c r="G2107" t="inlineStr"/>
+      <c r="H2107" t="inlineStr"/>
+      <c r="I2107" t="inlineStr"/>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="n">
+        <v>65554</v>
+      </c>
+      <c r="B2108" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2108" t="inlineStr">
+        <is>
+          <t>1795 W Broadway</t>
+        </is>
+      </c>
+      <c r="D2108" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264037962303, 'Longitude': -123.145408630371}</t>
+        </is>
+      </c>
+      <c r="E2108" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:34:37</t>
+        </is>
+      </c>
+      <c r="F2108" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:18:17.016Z</t>
+        </is>
+      </c>
+      <c r="G2108" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2108" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:52:38.117Z</t>
+        </is>
+      </c>
+      <c r="I2108" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="n">
+        <v>65571</v>
+      </c>
+      <c r="B2109" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2109" t="inlineStr">
+        <is>
+          <t>4314 W 10th Ave</t>
+        </is>
+      </c>
+      <c r="D2109" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2109" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:34:37</t>
+        </is>
+      </c>
+      <c r="F2109" t="inlineStr"/>
+      <c r="G2109" t="inlineStr"/>
+      <c r="H2109" t="inlineStr"/>
+      <c r="I2109" t="inlineStr"/>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B2110" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2110" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D2110" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2110" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:34:37</t>
+        </is>
+      </c>
+      <c r="F2110" t="inlineStr"/>
+      <c r="G2110" t="inlineStr"/>
+      <c r="H2110" t="inlineStr"/>
+      <c r="I2110" t="inlineStr"/>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="n">
+        <v>32376</v>
+      </c>
+      <c r="B2111" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2111" t="inlineStr">
+        <is>
+          <t>1503 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D2111" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2111" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:34:37</t>
+        </is>
+      </c>
+      <c r="F2111" t="inlineStr"/>
+      <c r="G2111" t="inlineStr"/>
+      <c r="H2111" t="inlineStr"/>
+      <c r="I2111" t="inlineStr"/>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="n">
+        <v>65549</v>
+      </c>
+      <c r="B2112" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2112" t="inlineStr">
+        <is>
+          <t>5702 Granville St</t>
+        </is>
+      </c>
+      <c r="D2112" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2112" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:34:37</t>
+        </is>
+      </c>
+      <c r="F2112" t="inlineStr"/>
+      <c r="G2112" t="inlineStr"/>
+      <c r="H2112" t="inlineStr"/>
+      <c r="I2112" t="inlineStr"/>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B2113" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2113" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D2113" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2113" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:34:37</t>
+        </is>
+      </c>
+      <c r="F2113" t="inlineStr"/>
+      <c r="G2113" t="inlineStr"/>
+      <c r="H2113" t="inlineStr"/>
+      <c r="I2113" t="inlineStr"/>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B2114" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2114" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D2114" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2114" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:34:37</t>
+        </is>
+      </c>
+      <c r="F2114" t="inlineStr"/>
+      <c r="G2114" t="inlineStr"/>
+      <c r="H2114" t="inlineStr"/>
+      <c r="I2114" t="inlineStr"/>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="n">
+        <v>72747</v>
+      </c>
+      <c r="B2115" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2115" t="inlineStr">
+        <is>
+          <t>1010 W King Edward Ave</t>
+        </is>
+      </c>
+      <c r="D2115" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2115" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:34:37</t>
+        </is>
+      </c>
+      <c r="F2115" t="inlineStr"/>
+      <c r="G2115" t="inlineStr"/>
+      <c r="H2115" t="inlineStr"/>
+      <c r="I2115" t="inlineStr"/>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="n">
+        <v>32375</v>
+      </c>
+      <c r="B2116" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2116" t="inlineStr">
+        <is>
+          <t>4110 Oak St</t>
+        </is>
+      </c>
+      <c r="D2116" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.24894071957, 'Longitude': -123.127040863037}</t>
+        </is>
+      </c>
+      <c r="E2116" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:34:37</t>
+        </is>
+      </c>
+      <c r="F2116" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:14:35.071Z</t>
+        </is>
+      </c>
+      <c r="G2116" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2116" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:17:09.064Z</t>
+        </is>
+      </c>
+      <c r="I2116" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="n">
+        <v>65564</v>
+      </c>
+      <c r="B2117" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2117" t="inlineStr">
+        <is>
+          <t>5680 Oak St</t>
+        </is>
+      </c>
+      <c r="D2117" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2117" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:34:37</t>
+        </is>
+      </c>
+      <c r="F2117" t="inlineStr"/>
+      <c r="G2117" t="inlineStr"/>
+      <c r="H2117" t="inlineStr"/>
+      <c r="I2117" t="inlineStr"/>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="n">
+        <v>32372</v>
+      </c>
+      <c r="B2118" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2118" t="inlineStr">
+        <is>
+          <t>6525 Oak St</t>
+        </is>
+      </c>
+      <c r="D2118" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2118" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:34:37</t>
+        </is>
+      </c>
+      <c r="F2118" t="inlineStr"/>
+      <c r="G2118" t="inlineStr"/>
+      <c r="H2118" t="inlineStr"/>
+      <c r="I2118" t="inlineStr"/>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B2119" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2119" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D2119" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E2119" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:34:37</t>
+        </is>
+      </c>
+      <c r="F2119" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:49:20.616Z</t>
+        </is>
+      </c>
+      <c r="G2119" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2119" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:49:01.374Z</t>
+        </is>
+      </c>
+      <c r="I2119" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="n">
+        <v>65566</v>
+      </c>
+      <c r="B2120" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2120" t="inlineStr">
+        <is>
+          <t>8072 Granville St</t>
+        </is>
+      </c>
+      <c r="D2120" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2120" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:34:37</t>
+        </is>
+      </c>
+      <c r="F2120" t="inlineStr"/>
+      <c r="G2120" t="inlineStr"/>
+      <c r="H2120" t="inlineStr"/>
+      <c r="I2120" t="inlineStr"/>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="n">
+        <v>65572</v>
+      </c>
+      <c r="B2121" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2121" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D2121" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2121" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:34:37</t>
+        </is>
+      </c>
+      <c r="F2121" t="inlineStr"/>
+      <c r="G2121" t="inlineStr"/>
+      <c r="H2121" t="inlineStr"/>
+      <c r="I2121" t="inlineStr"/>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="n">
+        <v>32378</v>
+      </c>
+      <c r="B2122" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2122" t="inlineStr">
+        <is>
+          <t>1613 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2122" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2122" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:35:52</t>
+        </is>
+      </c>
+      <c r="F2122" t="inlineStr"/>
+      <c r="G2122" t="inlineStr"/>
+      <c r="H2122" t="inlineStr"/>
+      <c r="I2122" t="inlineStr"/>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="n">
+        <v>98624</v>
+      </c>
+      <c r="B2123" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2123" t="inlineStr">
+        <is>
+          <t>1503 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2123" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2123" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:35:52</t>
+        </is>
+      </c>
+      <c r="F2123" t="inlineStr"/>
+      <c r="G2123" t="inlineStr"/>
+      <c r="H2123" t="inlineStr"/>
+      <c r="I2123" t="inlineStr"/>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="n">
+        <v>98626</v>
+      </c>
+      <c r="B2124" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2124" t="inlineStr">
+        <is>
+          <t>1490 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2124" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2124" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:35:52</t>
+        </is>
+      </c>
+      <c r="F2124" t="inlineStr"/>
+      <c r="G2124" t="inlineStr"/>
+      <c r="H2124" t="inlineStr"/>
+      <c r="I2124" t="inlineStr"/>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="n">
+        <v>65575</v>
+      </c>
+      <c r="B2125" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2125" t="inlineStr">
+        <is>
+          <t>1305 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2125" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2125" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:35:52</t>
+        </is>
+      </c>
+      <c r="F2125" t="inlineStr"/>
+      <c r="G2125" t="inlineStr"/>
+      <c r="H2125" t="inlineStr"/>
+      <c r="I2125" t="inlineStr"/>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="n">
+        <v>65505</v>
+      </c>
+      <c r="B2126" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2126" t="inlineStr">
+        <is>
+          <t>1731 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D2126" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2126" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:35:52</t>
+        </is>
+      </c>
+      <c r="F2126" t="inlineStr"/>
+      <c r="G2126" t="inlineStr"/>
+      <c r="H2126" t="inlineStr"/>
+      <c r="I2126" t="inlineStr"/>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="n">
+        <v>65503</v>
+      </c>
+      <c r="B2127" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2127" t="inlineStr">
+        <is>
+          <t>1980 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2127" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2127" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:35:52</t>
+        </is>
+      </c>
+      <c r="F2127" t="inlineStr"/>
+      <c r="G2127" t="inlineStr"/>
+      <c r="H2127" t="inlineStr"/>
+      <c r="I2127" t="inlineStr"/>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="n">
+        <v>75407</v>
+      </c>
+      <c r="B2128" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2128" t="inlineStr">
+        <is>
+          <t>2698 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D2128" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2128" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:35:52</t>
+        </is>
+      </c>
+      <c r="F2128" t="inlineStr"/>
+      <c r="G2128" t="inlineStr"/>
+      <c r="H2128" t="inlineStr"/>
+      <c r="I2128" t="inlineStr"/>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="n">
+        <v>75406</v>
+      </c>
+      <c r="B2129" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2129" t="inlineStr">
+        <is>
+          <t>1198 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2129" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2129" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:35:52</t>
+        </is>
+      </c>
+      <c r="F2129" t="inlineStr"/>
+      <c r="G2129" t="inlineStr"/>
+      <c r="H2129" t="inlineStr"/>
+      <c r="I2129" t="inlineStr"/>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="n">
+        <v>75409</v>
+      </c>
+      <c r="B2130" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2130" t="inlineStr">
+        <is>
+          <t>3150 Edgemont Blvd</t>
+        </is>
+      </c>
+      <c r="D2130" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2130" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:35:52</t>
+        </is>
+      </c>
+      <c r="F2130" t="inlineStr"/>
+      <c r="G2130" t="inlineStr"/>
+      <c r="H2130" t="inlineStr"/>
+      <c r="I2130" t="inlineStr"/>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="n">
+        <v>98622</v>
+      </c>
+      <c r="B2131" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2131" t="inlineStr">
+        <is>
+          <t>3690 Westmount Rd</t>
+        </is>
+      </c>
+      <c r="D2131" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2131" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:35:52</t>
+        </is>
+      </c>
+      <c r="F2131" t="inlineStr"/>
+      <c r="G2131" t="inlineStr"/>
+      <c r="H2131" t="inlineStr"/>
+      <c r="I2131" t="inlineStr"/>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="n">
+        <v>18803</v>
+      </c>
+      <c r="B2132" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2132" t="inlineStr">
+        <is>
+          <t>2501 Westview Dr</t>
+        </is>
+      </c>
+      <c r="D2132" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2132" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:35:52</t>
+        </is>
+      </c>
+      <c r="F2132" t="inlineStr"/>
+      <c r="G2132" t="inlineStr"/>
+      <c r="H2132" t="inlineStr"/>
+      <c r="I2132" t="inlineStr"/>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="n">
+        <v>18804</v>
+      </c>
+      <c r="B2133" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2133" t="inlineStr">
+        <is>
+          <t>660 3rd St  W</t>
+        </is>
+      </c>
+      <c r="D2133" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2133" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:35:52</t>
+        </is>
+      </c>
+      <c r="F2133" t="inlineStr"/>
+      <c r="G2133" t="inlineStr"/>
+      <c r="H2133" t="inlineStr"/>
+      <c r="I2133" t="inlineStr"/>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="n">
+        <v>32349</v>
+      </c>
+      <c r="B2134" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2134" t="inlineStr">
+        <is>
+          <t>106 W Queens St</t>
+        </is>
+      </c>
+      <c r="D2134" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.336724992343, 'Longitude': -123.072506189346}</t>
+        </is>
+      </c>
+      <c r="E2134" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:35:52</t>
+        </is>
+      </c>
+      <c r="F2134" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:47:52.962Z</t>
+        </is>
+      </c>
+      <c r="G2134" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2134" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:04:13.955Z</t>
+        </is>
+      </c>
+      <c r="I2134" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="n">
+        <v>18509</v>
+      </c>
+      <c r="B2135" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2135" t="inlineStr">
+        <is>
+          <t>2305 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D2135" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3306729, 'Longitude': -123.0728536}</t>
+        </is>
+      </c>
+      <c r="E2135" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:35:52</t>
+        </is>
+      </c>
+      <c r="F2135" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:36:28.622Z</t>
+        </is>
+      </c>
+      <c r="G2135" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2135" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:21:46.014Z</t>
+        </is>
+      </c>
+      <c r="I2135" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="n">
+        <v>22117</v>
+      </c>
+      <c r="B2136" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2136" t="inlineStr">
+        <is>
+          <t>1245 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D2136" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2136" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:35:52</t>
+        </is>
+      </c>
+      <c r="F2136" t="inlineStr"/>
+      <c r="G2136" t="inlineStr"/>
+      <c r="H2136" t="inlineStr"/>
+      <c r="I2136" t="inlineStr"/>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B2137" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2137" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D2137" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E2137" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:35:52</t>
+        </is>
+      </c>
+      <c r="F2137" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:49:20.616Z</t>
+        </is>
+      </c>
+      <c r="G2137" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2137" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:49:01.374Z</t>
+        </is>
+      </c>
+      <c r="I2137" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B2138" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2138" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D2138" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2138" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:35:52</t>
+        </is>
+      </c>
+      <c r="F2138" t="inlineStr"/>
+      <c r="G2138" t="inlineStr"/>
+      <c r="H2138" t="inlineStr"/>
+      <c r="I2138" t="inlineStr"/>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B2139" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2139" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D2139" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E2139" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:35:52</t>
+        </is>
+      </c>
+      <c r="F2139" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:46:17.762Z</t>
+        </is>
+      </c>
+      <c r="G2139" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2139" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:46:17.794Z</t>
+        </is>
+      </c>
+      <c r="I2139" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B2140" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2140" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D2140" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2140" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:35:52</t>
+        </is>
+      </c>
+      <c r="F2140" t="inlineStr"/>
+      <c r="G2140" t="inlineStr"/>
+      <c r="H2140" t="inlineStr"/>
+      <c r="I2140" t="inlineStr"/>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B2141" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2141" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D2141" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2141" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:35:52</t>
+        </is>
+      </c>
+      <c r="F2141" t="inlineStr"/>
+      <c r="G2141" t="inlineStr"/>
+      <c r="H2141" t="inlineStr"/>
+      <c r="I2141" t="inlineStr"/>
+    </row>
+    <row r="2142">
+      <c r="A2142" t="n">
+        <v>65558</v>
+      </c>
+      <c r="B2142" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2142" t="inlineStr">
+        <is>
+          <t>1390 E 33rd Ave</t>
+        </is>
+      </c>
+      <c r="D2142" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2142" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:37:32</t>
+        </is>
+      </c>
+      <c r="F2142" t="inlineStr"/>
+      <c r="G2142" t="inlineStr"/>
+      <c r="H2142" t="inlineStr"/>
+      <c r="I2142" t="inlineStr"/>
+    </row>
+    <row r="2143">
+      <c r="A2143" t="n">
+        <v>83394</v>
+      </c>
+      <c r="B2143" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2143" t="inlineStr">
+        <is>
+          <t>4064 Fraser St</t>
+        </is>
+      </c>
+      <c r="D2143" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2143" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:37:32</t>
+        </is>
+      </c>
+      <c r="F2143" t="inlineStr"/>
+      <c r="G2143" t="inlineStr"/>
+      <c r="H2143" t="inlineStr"/>
+      <c r="I2143" t="inlineStr"/>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="n">
+        <v>65573</v>
+      </c>
+      <c r="B2144" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2144" t="inlineStr">
+        <is>
+          <t>1396 E 41st Ave</t>
+        </is>
+      </c>
+      <c r="D2144" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2144" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:37:32</t>
+        </is>
+      </c>
+      <c r="F2144" t="inlineStr"/>
+      <c r="G2144" t="inlineStr"/>
+      <c r="H2144" t="inlineStr"/>
+      <c r="I2144" t="inlineStr"/>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="n">
+        <v>80714</v>
+      </c>
+      <c r="B2145" t="inlineStr">
+        <is>
+          <t>Husky</t>
+        </is>
+      </c>
+      <c r="C2145" t="inlineStr">
+        <is>
+          <t>4933 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D2145" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2145" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:37:32</t>
+        </is>
+      </c>
+      <c r="F2145" t="inlineStr"/>
+      <c r="G2145" t="inlineStr"/>
+      <c r="H2145" t="inlineStr"/>
+      <c r="I2145" t="inlineStr"/>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="n">
+        <v>65552</v>
+      </c>
+      <c r="B2146" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2146" t="inlineStr">
+        <is>
+          <t>2001 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2146" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2146" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:37:32</t>
+        </is>
+      </c>
+      <c r="F2146" t="inlineStr"/>
+      <c r="G2146" t="inlineStr"/>
+      <c r="H2146" t="inlineStr"/>
+      <c r="I2146" t="inlineStr"/>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="n">
+        <v>65538</v>
+      </c>
+      <c r="B2147" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2147" t="inlineStr">
+        <is>
+          <t>5252 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D2147" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2372145, 'Longitude': -123.0650857}</t>
+        </is>
+      </c>
+      <c r="E2147" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:37:32</t>
+        </is>
+      </c>
+      <c r="F2147" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:47:51.264Z</t>
+        </is>
+      </c>
+      <c r="G2147" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2147" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:47:51.295Z</t>
+        </is>
+      </c>
+      <c r="I2147" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="n">
+        <v>90814</v>
+      </c>
+      <c r="B2148" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2148" t="inlineStr">
+        <is>
+          <t>2277 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2148" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2148" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:37:32</t>
+        </is>
+      </c>
+      <c r="F2148" t="inlineStr"/>
+      <c r="G2148" t="inlineStr"/>
+      <c r="H2148" t="inlineStr"/>
+      <c r="I2148" t="inlineStr"/>
+    </row>
+    <row r="2149">
+      <c r="A2149" t="n">
+        <v>39768</v>
+      </c>
+      <c r="B2149" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2149" t="inlineStr">
+        <is>
+          <t>5736 Main St</t>
+        </is>
+      </c>
+      <c r="D2149" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2149" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:37:32</t>
+        </is>
+      </c>
+      <c r="F2149" t="inlineStr"/>
+      <c r="G2149" t="inlineStr"/>
+      <c r="H2149" t="inlineStr"/>
+      <c r="I2149" t="inlineStr"/>
+    </row>
+    <row r="2150">
+      <c r="A2150" t="n">
+        <v>9710</v>
+      </c>
+      <c r="B2150" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2150" t="inlineStr">
+        <is>
+          <t>1295 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D2150" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2150" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:37:32</t>
+        </is>
+      </c>
+      <c r="F2150" t="inlineStr"/>
+      <c r="G2150" t="inlineStr"/>
+      <c r="H2150" t="inlineStr"/>
+      <c r="I2150" t="inlineStr"/>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="n">
+        <v>99146</v>
+      </c>
+      <c r="B2151" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C2151" t="inlineStr">
+        <is>
+          <t>1317 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D2151" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259758544957, 'Longitude': -123.077272474766}</t>
+        </is>
+      </c>
+      <c r="E2151" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:37:32</t>
+        </is>
+      </c>
+      <c r="F2151" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:29:55.779Z</t>
+        </is>
+      </c>
+      <c r="G2151" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="H2151" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:29:55.810Z</t>
+        </is>
+      </c>
+      <c r="I2151" t="n">
+        <v>178.9</v>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" t="n">
+        <v>65560</v>
+      </c>
+      <c r="B2152" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2152" t="inlineStr">
+        <is>
+          <t>1289 E Broadway</t>
+        </is>
+      </c>
+      <c r="D2152" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.262693682723, 'Longitude': -123.078117370605}</t>
+        </is>
+      </c>
+      <c r="E2152" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:37:32</t>
+        </is>
+      </c>
+      <c r="F2152" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:29:11.224Z</t>
+        </is>
+      </c>
+      <c r="G2152" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="H2152" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:29:11.256Z</t>
+        </is>
+      </c>
+      <c r="I2152" t="n">
+        <v>178.9</v>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="n">
+        <v>65557</v>
+      </c>
+      <c r="B2153" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2153" t="inlineStr">
+        <is>
+          <t>2120 Grandview Hwy S</t>
+        </is>
+      </c>
+      <c r="D2153" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2153" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:37:32</t>
+        </is>
+      </c>
+      <c r="F2153" t="inlineStr"/>
+      <c r="G2153" t="inlineStr"/>
+      <c r="H2153" t="inlineStr"/>
+      <c r="I2153" t="inlineStr"/>
+    </row>
+    <row r="2154">
+      <c r="A2154" t="n">
+        <v>71502</v>
+      </c>
+      <c r="B2154" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2154" t="inlineStr">
+        <is>
+          <t>2748 Main St</t>
+        </is>
+      </c>
+      <c r="D2154" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2154" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:37:32</t>
+        </is>
+      </c>
+      <c r="F2154" t="inlineStr"/>
+      <c r="G2154" t="inlineStr"/>
+      <c r="H2154" t="inlineStr"/>
+      <c r="I2154" t="inlineStr"/>
+    </row>
+    <row r="2155">
+      <c r="A2155" t="n">
+        <v>65559</v>
+      </c>
+      <c r="B2155" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2155" t="inlineStr">
+        <is>
+          <t>6502 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D2155" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2155" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:37:32</t>
+        </is>
+      </c>
+      <c r="F2155" t="inlineStr"/>
+      <c r="G2155" t="inlineStr"/>
+      <c r="H2155" t="inlineStr"/>
+      <c r="I2155" t="inlineStr"/>
+    </row>
+    <row r="2156">
+      <c r="A2156" t="n">
+        <v>89943</v>
+      </c>
+      <c r="B2156" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2156" t="inlineStr">
+        <is>
+          <t>6808 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D2156" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2220242, 'Longitude': -123.0654247}</t>
+        </is>
+      </c>
+      <c r="E2156" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:37:32</t>
+        </is>
+      </c>
+      <c r="F2156" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:43:44.299Z</t>
+        </is>
+      </c>
+      <c r="G2156" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2156" t="inlineStr"/>
+      <c r="I2156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B2157" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2157" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D2157" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E2157" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:37:32</t>
+        </is>
+      </c>
+      <c r="F2157" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:15:34.212Z</t>
+        </is>
+      </c>
+      <c r="G2157" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2157" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:57.027Z</t>
+        </is>
+      </c>
+      <c r="I2157" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" t="n">
+        <v>65537</v>
+      </c>
+      <c r="B2158" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2158" t="inlineStr">
+        <is>
+          <t>2918 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2158" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.23608, 'Longitude': -123.0454858}</t>
+        </is>
+      </c>
+      <c r="E2158" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:37:32</t>
+        </is>
+      </c>
+      <c r="F2158" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:56:15.831Z</t>
+        </is>
+      </c>
+      <c r="G2158" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2158" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:56:15.847Z</t>
+        </is>
+      </c>
+      <c r="I2158" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B2159" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2159" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D2159" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2159" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:37:32</t>
+        </is>
+      </c>
+      <c r="F2159" t="inlineStr"/>
+      <c r="G2159" t="inlineStr"/>
+      <c r="H2159" t="inlineStr"/>
+      <c r="I2159" t="inlineStr"/>
+    </row>
+    <row r="2160">
+      <c r="A2160" t="n">
+        <v>65535</v>
+      </c>
+      <c r="B2160" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2160" t="inlineStr">
+        <is>
+          <t>2605 E 49th Ave</t>
+        </is>
+      </c>
+      <c r="D2160" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2251291, 'Longitude': -123.0545048}</t>
+        </is>
+      </c>
+      <c r="E2160" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:37:32</t>
+        </is>
+      </c>
+      <c r="F2160" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:44:29.896Z</t>
+        </is>
+      </c>
+      <c r="G2160" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2160" t="inlineStr"/>
+      <c r="I2160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" t="n">
+        <v>65539</v>
+      </c>
+      <c r="B2161" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2161" t="inlineStr">
+        <is>
+          <t>2902 Grandview Hwy</t>
+        </is>
+      </c>
+      <c r="D2161" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2161" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:37:32</t>
+        </is>
+      </c>
+      <c r="F2161" t="inlineStr"/>
+      <c r="G2161" t="inlineStr"/>
+      <c r="H2161" t="inlineStr"/>
+      <c r="I2161" t="inlineStr"/>
+    </row>
+    <row r="2162">
+      <c r="A2162" t="n">
+        <v>65464</v>
+      </c>
+      <c r="B2162" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2162" t="inlineStr">
+        <is>
+          <t>6751 Lougheed Hwy</t>
+        </is>
+      </c>
+      <c r="D2162" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2162" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:38:56</t>
+        </is>
+      </c>
+      <c r="F2162" t="inlineStr"/>
+      <c r="G2162" t="inlineStr"/>
+      <c r="H2162" t="inlineStr"/>
+      <c r="I2162" t="inlineStr"/>
+    </row>
+    <row r="2163">
+      <c r="A2163" t="n">
+        <v>100210</v>
+      </c>
+      <c r="B2163" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2163" t="inlineStr">
+        <is>
+          <t>7089 Lougheed Hwy</t>
+        </is>
+      </c>
+      <c r="D2163" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2163" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:38:56</t>
+        </is>
+      </c>
+      <c r="F2163" t="inlineStr"/>
+      <c r="G2163" t="inlineStr"/>
+      <c r="H2163" t="inlineStr"/>
+      <c r="I2163" t="inlineStr"/>
+    </row>
+    <row r="2164">
+      <c r="A2164" t="n">
+        <v>98628</v>
+      </c>
+      <c r="B2164" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2164" t="inlineStr">
+        <is>
+          <t>6568 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D2164" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.280205, 'Longitude': -122.96824}</t>
+        </is>
+      </c>
+      <c r="E2164" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:38:56</t>
+        </is>
+      </c>
+      <c r="F2164" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:56:07.146Z</t>
+        </is>
+      </c>
+      <c r="G2164" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2164" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:56:07.178Z</t>
+        </is>
+      </c>
+      <c r="I2164" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" t="n">
+        <v>65465</v>
+      </c>
+      <c r="B2165" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2165" t="inlineStr">
+        <is>
+          <t>7009 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D2165" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2165" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:38:56</t>
+        </is>
+      </c>
+      <c r="F2165" t="inlineStr"/>
+      <c r="G2165" t="inlineStr"/>
+      <c r="H2165" t="inlineStr"/>
+      <c r="I2165" t="inlineStr"/>
+    </row>
+    <row r="2166">
+      <c r="A2166" t="n">
+        <v>117793</v>
+      </c>
+      <c r="B2166" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2166" t="inlineStr">
+        <is>
+          <t>6511 Hastings St</t>
+        </is>
+      </c>
+      <c r="D2166" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2166" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:38:56</t>
+        </is>
+      </c>
+      <c r="F2166" t="inlineStr"/>
+      <c r="G2166" t="inlineStr"/>
+      <c r="H2166" t="inlineStr"/>
+      <c r="I2166" t="inlineStr"/>
+    </row>
+    <row r="2167">
+      <c r="A2167" t="n">
+        <v>65476</v>
+      </c>
+      <c r="B2167" t="inlineStr">
+        <is>
+          <t>Husky</t>
+        </is>
+      </c>
+      <c r="C2167" t="inlineStr">
+        <is>
+          <t>5720 Hastings St</t>
+        </is>
+      </c>
+      <c r="D2167" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.280138464632, 'Longitude': -122.980592250824}</t>
+        </is>
+      </c>
+      <c r="E2167" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:38:56</t>
+        </is>
+      </c>
+      <c r="F2167" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:57:48.287Z</t>
+        </is>
+      </c>
+      <c r="G2167" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="H2167" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:57:48.327Z</t>
+        </is>
+      </c>
+      <c r="I2167" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" t="n">
+        <v>212356</v>
+      </c>
+      <c r="B2168" t="inlineStr">
+        <is>
+          <t>CENTEX</t>
+        </is>
+      </c>
+      <c r="C2168" t="inlineStr">
+        <is>
+          <t>3855 Douglas Rd</t>
+        </is>
+      </c>
+      <c r="D2168" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2168" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:38:56</t>
+        </is>
+      </c>
+      <c r="F2168" t="inlineStr"/>
+      <c r="G2168" t="inlineStr"/>
+      <c r="H2168" t="inlineStr"/>
+      <c r="I2168" t="inlineStr"/>
+    </row>
+    <row r="2169">
+      <c r="A2169" t="n">
+        <v>919</v>
+      </c>
+      <c r="B2169" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2169" t="inlineStr">
+        <is>
+          <t>4512 Lougheed Hwy</t>
+        </is>
+      </c>
+      <c r="D2169" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.266012306544, 'Longitude': -123.002243041992}</t>
+        </is>
+      </c>
+      <c r="E2169" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:38:56</t>
+        </is>
+      </c>
+      <c r="F2169" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:23:26.310Z</t>
+        </is>
+      </c>
+      <c r="G2169" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2169" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:53:09.376Z</t>
+        </is>
+      </c>
+      <c r="I2169" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" t="n">
+        <v>164809</v>
+      </c>
+      <c r="B2170" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2170" t="inlineStr">
+        <is>
+          <t>1969 Willingdon Ave</t>
+        </is>
+      </c>
+      <c r="D2170" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2170" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:38:56</t>
+        </is>
+      </c>
+      <c r="F2170" t="inlineStr"/>
+      <c r="G2170" t="inlineStr"/>
+      <c r="H2170" t="inlineStr"/>
+      <c r="I2170" t="inlineStr"/>
+    </row>
+    <row r="2171">
+      <c r="A2171" t="n">
+        <v>65471</v>
+      </c>
+      <c r="B2171" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2171" t="inlineStr">
+        <is>
+          <t>5059 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2171" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2171" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:38:56</t>
+        </is>
+      </c>
+      <c r="F2171" t="inlineStr"/>
+      <c r="G2171" t="inlineStr"/>
+      <c r="H2171" t="inlineStr"/>
+      <c r="I2171" t="inlineStr"/>
+    </row>
+    <row r="2172">
+      <c r="A2172" t="n">
+        <v>1669</v>
+      </c>
+      <c r="B2172" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2172" t="inlineStr">
+        <is>
+          <t>975 Willingdon Ave</t>
+        </is>
+      </c>
+      <c r="D2172" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2172" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:38:56</t>
+        </is>
+      </c>
+      <c r="F2172" t="inlineStr"/>
+      <c r="G2172" t="inlineStr"/>
+      <c r="H2172" t="inlineStr"/>
+      <c r="I2172" t="inlineStr"/>
+    </row>
+    <row r="2173">
+      <c r="A2173" t="n">
+        <v>65479</v>
+      </c>
+      <c r="B2173" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2173" t="inlineStr">
+        <is>
+          <t>4505 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2173" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.255159438214, 'Longitude': -123.003401756287}</t>
+        </is>
+      </c>
+      <c r="E2173" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:38:56</t>
+        </is>
+      </c>
+      <c r="F2173" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:02:43.535Z</t>
+        </is>
+      </c>
+      <c r="G2173" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H2173" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:56:09.110Z</t>
+        </is>
+      </c>
+      <c r="I2173" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" t="n">
+        <v>69963</v>
+      </c>
+      <c r="B2174" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2174" t="inlineStr">
+        <is>
+          <t>4487 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2174" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.255044, 'Longitude': -123.0046907}</t>
+        </is>
+      </c>
+      <c r="E2174" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:38:56</t>
+        </is>
+      </c>
+      <c r="F2174" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:55:50.848Z</t>
+        </is>
+      </c>
+      <c r="G2174" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H2174" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:56:01.154Z</t>
+        </is>
+      </c>
+      <c r="I2174" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" t="n">
+        <v>65466</v>
+      </c>
+      <c r="B2175" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2175" t="inlineStr">
+        <is>
+          <t>4507 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D2175" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2175" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:38:56</t>
+        </is>
+      </c>
+      <c r="F2175" t="inlineStr"/>
+      <c r="G2175" t="inlineStr"/>
+      <c r="H2175" t="inlineStr"/>
+      <c r="I2175" t="inlineStr"/>
+    </row>
+    <row r="2176">
+      <c r="A2176" t="n">
+        <v>65475</v>
+      </c>
+      <c r="B2176" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2176" t="inlineStr">
+        <is>
+          <t>3826 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2176" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2176" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:38:56</t>
+        </is>
+      </c>
+      <c r="F2176" t="inlineStr"/>
+      <c r="G2176" t="inlineStr"/>
+      <c r="H2176" t="inlineStr"/>
+      <c r="I2176" t="inlineStr"/>
+    </row>
+    <row r="2177">
+      <c r="A2177" t="n">
+        <v>39293</v>
+      </c>
+      <c r="B2177" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2177" t="inlineStr">
+        <is>
+          <t>3030 Boundary Rd</t>
+        </is>
+      </c>
+      <c r="D2177" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2567447, 'Longitude': -123.0230847}</t>
+        </is>
+      </c>
+      <c r="E2177" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:38:56</t>
+        </is>
+      </c>
+      <c r="F2177" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:43.292Z</t>
+        </is>
+      </c>
+      <c r="G2177" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2177" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:43.307Z</t>
+        </is>
+      </c>
+      <c r="I2177" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" t="n">
+        <v>119589</v>
+      </c>
+      <c r="B2178" t="inlineStr">
+        <is>
+          <t>Smart Gas</t>
+        </is>
+      </c>
+      <c r="C2178" t="inlineStr">
+        <is>
+          <t>6869 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2178" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226505740129, 'Longitude': -122.944511175156}</t>
+        </is>
+      </c>
+      <c r="E2178" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:38:56</t>
+        </is>
+      </c>
+      <c r="F2178" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:09:26.720Z</t>
+        </is>
+      </c>
+      <c r="G2178" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2178" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:03.731Z</t>
+        </is>
+      </c>
+      <c r="I2178" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" t="n">
+        <v>124671</v>
+      </c>
+      <c r="B2179" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2179" t="inlineStr">
+        <is>
+          <t>3505 Grandview Hwy</t>
+        </is>
+      </c>
+      <c r="D2179" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2179" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:38:56</t>
+        </is>
+      </c>
+      <c r="F2179" t="inlineStr"/>
+      <c r="G2179" t="inlineStr"/>
+      <c r="H2179" t="inlineStr"/>
+      <c r="I2179" t="inlineStr"/>
+    </row>
+    <row r="2180">
+      <c r="A2180" t="n">
+        <v>5768</v>
+      </c>
+      <c r="B2180" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2180" t="inlineStr">
+        <is>
+          <t>5009 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2180" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2180" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:38:56</t>
+        </is>
+      </c>
+      <c r="F2180" t="inlineStr"/>
+      <c r="G2180" t="inlineStr"/>
+      <c r="H2180" t="inlineStr"/>
+      <c r="I2180" t="inlineStr"/>
+    </row>
+    <row r="2181">
+      <c r="A2181" t="n">
+        <v>65474</v>
+      </c>
+      <c r="B2181" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2181" t="inlineStr">
+        <is>
+          <t>7274 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2181" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2244118, 'Longitude': -122.9410264}</t>
+        </is>
+      </c>
+      <c r="E2181" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:38:56</t>
+        </is>
+      </c>
+      <c r="F2181" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:51:05.186Z</t>
+        </is>
+      </c>
+      <c r="G2181" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2181" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:59.321Z</t>
+        </is>
+      </c>
+      <c r="I2181" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" t="n">
+        <v>65464</v>
+      </c>
+      <c r="B2182" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2182" t="inlineStr">
+        <is>
+          <t>6751 Lougheed Hwy</t>
+        </is>
+      </c>
+      <c r="D2182" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2182" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:07</t>
+        </is>
+      </c>
+      <c r="F2182" t="inlineStr"/>
+      <c r="G2182" t="inlineStr"/>
+      <c r="H2182" t="inlineStr"/>
+      <c r="I2182" t="inlineStr"/>
+    </row>
+    <row r="2183">
+      <c r="A2183" t="n">
+        <v>100210</v>
+      </c>
+      <c r="B2183" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2183" t="inlineStr">
+        <is>
+          <t>7089 Lougheed Hwy</t>
+        </is>
+      </c>
+      <c r="D2183" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259055582449, 'Longitude': -122.956455763229}</t>
+        </is>
+      </c>
+      <c r="E2183" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:07</t>
+        </is>
+      </c>
+      <c r="F2183" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:58:56.196Z</t>
+        </is>
+      </c>
+      <c r="G2183" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H2183" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:13:37.884Z</t>
+        </is>
+      </c>
+      <c r="I2183" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="2184">
+      <c r="A2184" t="n">
+        <v>98628</v>
+      </c>
+      <c r="B2184" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2184" t="inlineStr">
+        <is>
+          <t>6568 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D2184" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.280205, 'Longitude': -122.96824}</t>
+        </is>
+      </c>
+      <c r="E2184" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:07</t>
+        </is>
+      </c>
+      <c r="F2184" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:56:07.146Z</t>
+        </is>
+      </c>
+      <c r="G2184" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2184" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:56:07.178Z</t>
+        </is>
+      </c>
+      <c r="I2184" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="2185">
+      <c r="A2185" t="n">
+        <v>65465</v>
+      </c>
+      <c r="B2185" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2185" t="inlineStr">
+        <is>
+          <t>7009 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D2185" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2185" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:07</t>
+        </is>
+      </c>
+      <c r="F2185" t="inlineStr"/>
+      <c r="G2185" t="inlineStr"/>
+      <c r="H2185" t="inlineStr"/>
+      <c r="I2185" t="inlineStr"/>
+    </row>
+    <row r="2186">
+      <c r="A2186" t="n">
+        <v>117793</v>
+      </c>
+      <c r="B2186" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2186" t="inlineStr">
+        <is>
+          <t>6511 Hastings St</t>
+        </is>
+      </c>
+      <c r="D2186" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2186" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:07</t>
+        </is>
+      </c>
+      <c r="F2186" t="inlineStr"/>
+      <c r="G2186" t="inlineStr"/>
+      <c r="H2186" t="inlineStr"/>
+      <c r="I2186" t="inlineStr"/>
+    </row>
+    <row r="2187">
+      <c r="A2187" t="n">
+        <v>65476</v>
+      </c>
+      <c r="B2187" t="inlineStr">
+        <is>
+          <t>Husky</t>
+        </is>
+      </c>
+      <c r="C2187" t="inlineStr">
+        <is>
+          <t>5720 Hastings St</t>
+        </is>
+      </c>
+      <c r="D2187" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.280138464632, 'Longitude': -122.980592250824}</t>
+        </is>
+      </c>
+      <c r="E2187" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:07</t>
+        </is>
+      </c>
+      <c r="F2187" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:57:48.287Z</t>
+        </is>
+      </c>
+      <c r="G2187" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="H2187" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:57:48.327Z</t>
+        </is>
+      </c>
+      <c r="I2187" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="2188">
+      <c r="A2188" t="n">
+        <v>212356</v>
+      </c>
+      <c r="B2188" t="inlineStr">
+        <is>
+          <t>CENTEX</t>
+        </is>
+      </c>
+      <c r="C2188" t="inlineStr">
+        <is>
+          <t>3855 Douglas Rd</t>
+        </is>
+      </c>
+      <c r="D2188" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249718360686, 'Longitude': -122.981165650914}</t>
+        </is>
+      </c>
+      <c r="E2188" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:07</t>
+        </is>
+      </c>
+      <c r="F2188" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:49:43.061Z</t>
+        </is>
+      </c>
+      <c r="G2188" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2188" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:02:08.577Z</t>
+        </is>
+      </c>
+      <c r="I2188" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="2189">
+      <c r="A2189" t="n">
+        <v>919</v>
+      </c>
+      <c r="B2189" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2189" t="inlineStr">
+        <is>
+          <t>4512 Lougheed Hwy</t>
+        </is>
+      </c>
+      <c r="D2189" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.266012306544, 'Longitude': -123.002243041992}</t>
+        </is>
+      </c>
+      <c r="E2189" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:07</t>
+        </is>
+      </c>
+      <c r="F2189" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:23:26.310Z</t>
+        </is>
+      </c>
+      <c r="G2189" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2189" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:53:09.376Z</t>
+        </is>
+      </c>
+      <c r="I2189" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="2190">
+      <c r="A2190" t="n">
+        <v>164809</v>
+      </c>
+      <c r="B2190" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2190" t="inlineStr">
+        <is>
+          <t>1969 Willingdon Ave</t>
+        </is>
+      </c>
+      <c r="D2190" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.266593392816, 'Longitude': -123.003401756287}</t>
+        </is>
+      </c>
+      <c r="E2190" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:07</t>
+        </is>
+      </c>
+      <c r="F2190" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:36:02.839Z</t>
+        </is>
+      </c>
+      <c r="G2190" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H2190" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:53:04.028Z</t>
+        </is>
+      </c>
+      <c r="I2190" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="2191">
+      <c r="A2191" t="n">
+        <v>65471</v>
+      </c>
+      <c r="B2191" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2191" t="inlineStr">
+        <is>
+          <t>5059 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2191" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.239569143746, 'Longitude': -122.96440243721}</t>
+        </is>
+      </c>
+      <c r="E2191" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:07</t>
+        </is>
+      </c>
+      <c r="F2191" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:03:48.358Z</t>
+        </is>
+      </c>
+      <c r="G2191" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2191" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:03:48.389Z</t>
+        </is>
+      </c>
+      <c r="I2191" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="2192">
+      <c r="A2192" t="n">
+        <v>1669</v>
+      </c>
+      <c r="B2192" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2192" t="inlineStr">
+        <is>
+          <t>975 Willingdon Ave</t>
+        </is>
+      </c>
+      <c r="D2192" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2758486, 'Longitude': -123.0035135}</t>
+        </is>
+      </c>
+      <c r="E2192" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:07</t>
+        </is>
+      </c>
+      <c r="F2192" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:54:39.233Z</t>
+        </is>
+      </c>
+      <c r="G2192" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H2192" t="inlineStr">
+        <is>
+          <t>2025-08-21T17:38:43.806Z</t>
+        </is>
+      </c>
+      <c r="I2192" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="2193">
+      <c r="A2193" t="n">
+        <v>65479</v>
+      </c>
+      <c r="B2193" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2193" t="inlineStr">
+        <is>
+          <t>4505 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2193" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.255159438214, 'Longitude': -123.003401756287}</t>
+        </is>
+      </c>
+      <c r="E2193" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:07</t>
+        </is>
+      </c>
+      <c r="F2193" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:02:43.535Z</t>
+        </is>
+      </c>
+      <c r="G2193" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H2193" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:56:09.110Z</t>
+        </is>
+      </c>
+      <c r="I2193" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="2194">
+      <c r="A2194" t="n">
+        <v>69963</v>
+      </c>
+      <c r="B2194" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2194" t="inlineStr">
+        <is>
+          <t>4487 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2194" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2194" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:07</t>
+        </is>
+      </c>
+      <c r="F2194" t="inlineStr"/>
+      <c r="G2194" t="inlineStr"/>
+      <c r="H2194" t="inlineStr"/>
+      <c r="I2194" t="inlineStr"/>
+    </row>
+    <row r="2195">
+      <c r="A2195" t="n">
+        <v>65466</v>
+      </c>
+      <c r="B2195" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2195" t="inlineStr">
+        <is>
+          <t>4507 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D2195" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2195" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:07</t>
+        </is>
+      </c>
+      <c r="F2195" t="inlineStr"/>
+      <c r="G2195" t="inlineStr"/>
+      <c r="H2195" t="inlineStr"/>
+      <c r="I2195" t="inlineStr"/>
+    </row>
+    <row r="2196">
+      <c r="A2196" t="n">
+        <v>65475</v>
+      </c>
+      <c r="B2196" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2196" t="inlineStr">
+        <is>
+          <t>3826 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2196" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2196" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:07</t>
+        </is>
+      </c>
+      <c r="F2196" t="inlineStr"/>
+      <c r="G2196" t="inlineStr"/>
+      <c r="H2196" t="inlineStr"/>
+      <c r="I2196" t="inlineStr"/>
+    </row>
+    <row r="2197">
+      <c r="A2197" t="n">
+        <v>39293</v>
+      </c>
+      <c r="B2197" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2197" t="inlineStr">
+        <is>
+          <t>3030 Boundary Rd</t>
+        </is>
+      </c>
+      <c r="D2197" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2567447, 'Longitude': -123.0230847}</t>
+        </is>
+      </c>
+      <c r="E2197" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:07</t>
+        </is>
+      </c>
+      <c r="F2197" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:38:36.619Z</t>
+        </is>
+      </c>
+      <c r="G2197" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2197" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:38:36.650Z</t>
+        </is>
+      </c>
+      <c r="I2197" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="2198">
+      <c r="A2198" t="n">
+        <v>119589</v>
+      </c>
+      <c r="B2198" t="inlineStr">
+        <is>
+          <t>Smart Gas</t>
+        </is>
+      </c>
+      <c r="C2198" t="inlineStr">
+        <is>
+          <t>6869 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2198" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226505740129, 'Longitude': -122.944511175156}</t>
+        </is>
+      </c>
+      <c r="E2198" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:07</t>
+        </is>
+      </c>
+      <c r="F2198" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:09:26.720Z</t>
+        </is>
+      </c>
+      <c r="G2198" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2198" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:03.731Z</t>
+        </is>
+      </c>
+      <c r="I2198" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="2199">
+      <c r="A2199" t="n">
+        <v>124671</v>
+      </c>
+      <c r="B2199" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2199" t="inlineStr">
+        <is>
+          <t>3505 Grandview Hwy</t>
+        </is>
+      </c>
+      <c r="D2199" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2585701, 'Longitude': -123.0281066}</t>
+        </is>
+      </c>
+      <c r="E2199" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:07</t>
+        </is>
+      </c>
+      <c r="F2199" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:36:20.854Z</t>
+        </is>
+      </c>
+      <c r="G2199" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2199" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:36:20.885Z</t>
+        </is>
+      </c>
+      <c r="I2199" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="2200">
+      <c r="A2200" t="n">
+        <v>65474</v>
+      </c>
+      <c r="B2200" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2200" t="inlineStr">
+        <is>
+          <t>7274 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2200" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2200" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:07</t>
+        </is>
+      </c>
+      <c r="F2200" t="inlineStr"/>
+      <c r="G2200" t="inlineStr"/>
+      <c r="H2200" t="inlineStr"/>
+      <c r="I2200" t="inlineStr"/>
+    </row>
+    <row r="2201">
+      <c r="A2201" t="n">
+        <v>5768</v>
+      </c>
+      <c r="B2201" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2201" t="inlineStr">
+        <is>
+          <t>5009 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2201" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2201" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:07</t>
+        </is>
+      </c>
+      <c r="F2201" t="inlineStr"/>
+      <c r="G2201" t="inlineStr"/>
+      <c r="H2201" t="inlineStr"/>
+      <c r="I2201" t="inlineStr"/>
+    </row>
+    <row r="2202">
+      <c r="A2202" t="inlineStr">
+        <is>
+          <t>65480</t>
+        </is>
+      </c>
+      <c r="B2202" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C2202" t="inlineStr">
+        <is>
+          <t>6591 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2202" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21925095319, 'Longitude': -122.968211174011}</t>
+        </is>
+      </c>
+      <c r="E2202" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:43</t>
+        </is>
+      </c>
+      <c r="F2202" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:39:17.805Z</t>
+        </is>
+      </c>
+      <c r="G2202" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H2202" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:25:44.411Z</t>
+        </is>
+      </c>
+      <c r="I2202" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="A2203" t="inlineStr">
+        <is>
+          <t>65467</t>
+        </is>
+      </c>
+      <c r="B2203" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2203" t="inlineStr">
+        <is>
+          <t>6138 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2203" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2203" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:43</t>
+        </is>
+      </c>
+      <c r="F2203" t="inlineStr"/>
+      <c r="G2203" t="inlineStr"/>
+      <c r="H2203" t="inlineStr"/>
+      <c r="I2203" t="inlineStr"/>
+    </row>
+    <row r="2204">
+      <c r="A2204" t="inlineStr">
+        <is>
+          <t>119589</t>
+        </is>
+      </c>
+      <c r="B2204" t="inlineStr">
+        <is>
+          <t>Smart Gas</t>
+        </is>
+      </c>
+      <c r="C2204" t="inlineStr">
+        <is>
+          <t>6869 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2204" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226505740129, 'Longitude': -122.944511175156}</t>
+        </is>
+      </c>
+      <c r="E2204" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:43</t>
+        </is>
+      </c>
+      <c r="F2204" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:09:26.720Z</t>
+        </is>
+      </c>
+      <c r="G2204" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2204" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:03.731Z</t>
+        </is>
+      </c>
+      <c r="I2204" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" t="inlineStr">
+        <is>
+          <t>65474</t>
+        </is>
+      </c>
+      <c r="B2205" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2205" t="inlineStr">
+        <is>
+          <t>7274 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2205" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2244118, 'Longitude': -122.9410264}</t>
+        </is>
+      </c>
+      <c r="E2205" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:43</t>
+        </is>
+      </c>
+      <c r="F2205" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:51:05.186Z</t>
+        </is>
+      </c>
+      <c r="G2205" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2205" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:59.321Z</t>
+        </is>
+      </c>
+      <c r="I2205" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="2206">
+      <c r="A2206" t="inlineStr">
+        <is>
+          <t>87633</t>
+        </is>
+      </c>
+      <c r="B2206" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C2206" t="inlineStr">
+        <is>
+          <t>5608 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2206" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.222913, 'Longitude': -122.982433}</t>
+        </is>
+      </c>
+      <c r="E2206" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:43</t>
+        </is>
+      </c>
+      <c r="F2206" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:24:38.616Z</t>
+        </is>
+      </c>
+      <c r="G2206" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H2206" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:29:55.698Z</t>
+        </is>
+      </c>
+      <c r="I2206" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" t="inlineStr">
+        <is>
+          <t>65481</t>
+        </is>
+      </c>
+      <c r="B2207" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C2207" t="inlineStr">
+        <is>
+          <t>7377 6th St</t>
+        </is>
+      </c>
+      <c r="D2207" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.225214157435, 'Longitude': -122.935831546783}</t>
+        </is>
+      </c>
+      <c r="E2207" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:43</t>
+        </is>
+      </c>
+      <c r="F2207" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:11:43.763Z</t>
+        </is>
+      </c>
+      <c r="G2207" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H2207" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:11:43.810Z</t>
+        </is>
+      </c>
+      <c r="I2207" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" t="inlineStr">
+        <is>
+          <t>65477</t>
+        </is>
+      </c>
+      <c r="B2208" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2208" t="inlineStr">
+        <is>
+          <t>7890 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2208" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2208" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:43</t>
+        </is>
+      </c>
+      <c r="F2208" t="inlineStr"/>
+      <c r="G2208" t="inlineStr"/>
+      <c r="H2208" t="inlineStr"/>
+      <c r="I2208" t="inlineStr"/>
+    </row>
+    <row r="2209">
+      <c r="A2209" t="inlineStr">
+        <is>
+          <t>65468</t>
+        </is>
+      </c>
+      <c r="B2209" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2209" t="inlineStr">
+        <is>
+          <t>7587 Royal Oak Ave</t>
+        </is>
+      </c>
+      <c r="D2209" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2151443, 'Longitude': -122.9890903}</t>
+        </is>
+      </c>
+      <c r="E2209" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:43</t>
+        </is>
+      </c>
+      <c r="F2209" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:59.619Z</t>
+        </is>
+      </c>
+      <c r="G2209" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2209" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:29:20.166Z</t>
+        </is>
+      </c>
+      <c r="I2209" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="2210">
+      <c r="A2210" t="inlineStr">
+        <is>
+          <t>65471</t>
+        </is>
+      </c>
+      <c r="B2210" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2210" t="inlineStr">
+        <is>
+          <t>5059 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2210" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.239569143746, 'Longitude': -122.96440243721}</t>
+        </is>
+      </c>
+      <c r="E2210" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:43</t>
+        </is>
+      </c>
+      <c r="F2210" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:03:48.358Z</t>
+        </is>
+      </c>
+      <c r="G2210" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2210" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:03:48.389Z</t>
+        </is>
+      </c>
+      <c r="I2210" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="2211">
+      <c r="A2211" t="inlineStr">
+        <is>
+          <t>5768</t>
+        </is>
+      </c>
+      <c r="B2211" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2211" t="inlineStr">
+        <is>
+          <t>5009 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2211" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2211" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:43</t>
+        </is>
+      </c>
+      <c r="F2211" t="inlineStr"/>
+      <c r="G2211" t="inlineStr"/>
+      <c r="H2211" t="inlineStr"/>
+      <c r="I2211" t="inlineStr"/>
+    </row>
+    <row r="2212">
+      <c r="A2212" t="inlineStr">
+        <is>
+          <t>111740</t>
+        </is>
+      </c>
+      <c r="B2212" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2212" t="inlineStr">
+        <is>
+          <t>780 6th St</t>
+        </is>
+      </c>
+      <c r="D2212" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2212" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:43</t>
+        </is>
+      </c>
+      <c r="F2212" t="inlineStr"/>
+      <c r="G2212" t="inlineStr"/>
+      <c r="H2212" t="inlineStr"/>
+      <c r="I2212" t="inlineStr"/>
+    </row>
+    <row r="2213">
+      <c r="A2213" t="inlineStr">
+        <is>
+          <t>65469</t>
+        </is>
+      </c>
+      <c r="B2213" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2213" t="inlineStr">
+        <is>
+          <t>4692 Imperial St</t>
+        </is>
+      </c>
+      <c r="D2213" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2217244, 'Longitude': -122.9980797}</t>
+        </is>
+      </c>
+      <c r="E2213" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:43</t>
+        </is>
+      </c>
+      <c r="F2213" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:04:25.698Z</t>
+        </is>
+      </c>
+      <c r="G2213" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2213" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:58:12.777Z</t>
+        </is>
+      </c>
+      <c r="I2213" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="2214">
+      <c r="A2214" t="inlineStr">
+        <is>
+          <t>65499</t>
+        </is>
+      </c>
+      <c r="B2214" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2214" t="inlineStr">
+        <is>
+          <t>736 Sixth Ave</t>
+        </is>
+      </c>
+      <c r="D2214" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2214" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:43</t>
+        </is>
+      </c>
+      <c r="F2214" t="inlineStr"/>
+      <c r="G2214" t="inlineStr"/>
+      <c r="H2214" t="inlineStr"/>
+      <c r="I2214" t="inlineStr"/>
+    </row>
+    <row r="2215">
+      <c r="A2215" t="inlineStr">
+        <is>
+          <t>65497</t>
+        </is>
+      </c>
+      <c r="B2215" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2215" t="inlineStr">
+        <is>
+          <t>428 Sixth St</t>
+        </is>
+      </c>
+      <c r="D2215" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2109656, 'Longitude': -122.9179526}</t>
+        </is>
+      </c>
+      <c r="E2215" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:43</t>
+        </is>
+      </c>
+      <c r="F2215" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:24.583Z</t>
+        </is>
+      </c>
+      <c r="G2215" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2215" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:24.614Z</t>
+        </is>
+      </c>
+      <c r="I2215" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="2216">
+      <c r="A2216" t="inlineStr">
+        <is>
+          <t>32350</t>
+        </is>
+      </c>
+      <c r="B2216" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2216" t="inlineStr">
+        <is>
+          <t>132 12th St</t>
+        </is>
+      </c>
+      <c r="D2216" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2216" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:43</t>
+        </is>
+      </c>
+      <c r="F2216" t="inlineStr"/>
+      <c r="G2216" t="inlineStr"/>
+      <c r="H2216" t="inlineStr"/>
+      <c r="I2216" t="inlineStr"/>
+    </row>
+    <row r="2217">
+      <c r="A2217" t="inlineStr">
+        <is>
+          <t>65502</t>
+        </is>
+      </c>
+      <c r="B2217" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2217" t="inlineStr">
+        <is>
+          <t>5 W 8th Ave</t>
+        </is>
+      </c>
+      <c r="D2217" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2217" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:43</t>
+        </is>
+      </c>
+      <c r="F2217" t="inlineStr"/>
+      <c r="G2217" t="inlineStr"/>
+      <c r="H2217" t="inlineStr"/>
+      <c r="I2217" t="inlineStr"/>
+    </row>
+    <row r="2218">
+      <c r="A2218" t="inlineStr">
+        <is>
+          <t>65498</t>
+        </is>
+      </c>
+      <c r="B2218" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2218" t="inlineStr">
+        <is>
+          <t>3 E 8th Ave</t>
+        </is>
+      </c>
+      <c r="D2218" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2228942, 'Longitude': -122.9117512}</t>
+        </is>
+      </c>
+      <c r="E2218" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:43</t>
+        </is>
+      </c>
+      <c r="F2218" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:29:02.534Z</t>
+        </is>
+      </c>
+      <c r="G2218" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H2218" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:29:02.565Z</t>
+        </is>
+      </c>
+      <c r="I2218" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" t="inlineStr">
+        <is>
+          <t>65470</t>
+        </is>
+      </c>
+      <c r="B2219" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2219" t="inlineStr">
+        <is>
+          <t>4444 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2219" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2219" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:43</t>
+        </is>
+      </c>
+      <c r="F2219" t="inlineStr"/>
+      <c r="G2219" t="inlineStr"/>
+      <c r="H2219" t="inlineStr"/>
+      <c r="I2219" t="inlineStr"/>
+    </row>
+    <row r="2220">
+      <c r="A2220" t="inlineStr">
+        <is>
+          <t>212356</t>
+        </is>
+      </c>
+      <c r="B2220" t="inlineStr">
+        <is>
+          <t>CENTEX</t>
+        </is>
+      </c>
+      <c r="C2220" t="inlineStr">
+        <is>
+          <t>3855 Douglas Rd</t>
+        </is>
+      </c>
+      <c r="D2220" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2220" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:43</t>
+        </is>
+      </c>
+      <c r="F2220" t="inlineStr"/>
+      <c r="G2220" t="inlineStr"/>
+      <c r="H2220" t="inlineStr"/>
+      <c r="I2220" t="inlineStr"/>
+    </row>
+    <row r="2221">
+      <c r="A2221" t="inlineStr">
+        <is>
+          <t>87636</t>
+        </is>
+      </c>
+      <c r="B2221" t="inlineStr">
+        <is>
+          <t>CENTEX</t>
+        </is>
+      </c>
+      <c r="C2221" t="inlineStr">
+        <is>
+          <t>1101 Ewen Ave</t>
+        </is>
+      </c>
+      <c r="D2221" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2221" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:41:43</t>
+        </is>
+      </c>
+      <c r="F2221" t="inlineStr"/>
+      <c r="G2221" t="inlineStr"/>
+      <c r="H2221" t="inlineStr"/>
+      <c r="I2221" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/gas_prices.xlsx
+++ b/data/gas_prices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2221"/>
+  <dimension ref="A1:I2241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87272,10 +87272,8 @@
       <c r="I2201" t="inlineStr"/>
     </row>
     <row r="2202">
-      <c r="A2202" t="inlineStr">
-        <is>
-          <t>65480</t>
-        </is>
+      <c r="A2202" t="n">
+        <v>65480</v>
       </c>
       <c r="B2202" t="inlineStr">
         <is>
@@ -87315,10 +87313,8 @@
       </c>
     </row>
     <row r="2203">
-      <c r="A2203" t="inlineStr">
-        <is>
-          <t>65467</t>
-        </is>
+      <c r="A2203" t="n">
+        <v>65467</v>
       </c>
       <c r="B2203" t="inlineStr">
         <is>
@@ -87346,10 +87342,8 @@
       <c r="I2203" t="inlineStr"/>
     </row>
     <row r="2204">
-      <c r="A2204" t="inlineStr">
-        <is>
-          <t>119589</t>
-        </is>
+      <c r="A2204" t="n">
+        <v>119589</v>
       </c>
       <c r="B2204" t="inlineStr">
         <is>
@@ -87389,10 +87383,8 @@
       </c>
     </row>
     <row r="2205">
-      <c r="A2205" t="inlineStr">
-        <is>
-          <t>65474</t>
-        </is>
+      <c r="A2205" t="n">
+        <v>65474</v>
       </c>
       <c r="B2205" t="inlineStr">
         <is>
@@ -87432,10 +87424,8 @@
       </c>
     </row>
     <row r="2206">
-      <c r="A2206" t="inlineStr">
-        <is>
-          <t>87633</t>
-        </is>
+      <c r="A2206" t="n">
+        <v>87633</v>
       </c>
       <c r="B2206" t="inlineStr">
         <is>
@@ -87475,10 +87465,8 @@
       </c>
     </row>
     <row r="2207">
-      <c r="A2207" t="inlineStr">
-        <is>
-          <t>65481</t>
-        </is>
+      <c r="A2207" t="n">
+        <v>65481</v>
       </c>
       <c r="B2207" t="inlineStr">
         <is>
@@ -87518,10 +87506,8 @@
       </c>
     </row>
     <row r="2208">
-      <c r="A2208" t="inlineStr">
-        <is>
-          <t>65477</t>
-        </is>
+      <c r="A2208" t="n">
+        <v>65477</v>
       </c>
       <c r="B2208" t="inlineStr">
         <is>
@@ -87549,10 +87535,8 @@
       <c r="I2208" t="inlineStr"/>
     </row>
     <row r="2209">
-      <c r="A2209" t="inlineStr">
-        <is>
-          <t>65468</t>
-        </is>
+      <c r="A2209" t="n">
+        <v>65468</v>
       </c>
       <c r="B2209" t="inlineStr">
         <is>
@@ -87592,10 +87576,8 @@
       </c>
     </row>
     <row r="2210">
-      <c r="A2210" t="inlineStr">
-        <is>
-          <t>65471</t>
-        </is>
+      <c r="A2210" t="n">
+        <v>65471</v>
       </c>
       <c r="B2210" t="inlineStr">
         <is>
@@ -87635,10 +87617,8 @@
       </c>
     </row>
     <row r="2211">
-      <c r="A2211" t="inlineStr">
-        <is>
-          <t>5768</t>
-        </is>
+      <c r="A2211" t="n">
+        <v>5768</v>
       </c>
       <c r="B2211" t="inlineStr">
         <is>
@@ -87666,10 +87646,8 @@
       <c r="I2211" t="inlineStr"/>
     </row>
     <row r="2212">
-      <c r="A2212" t="inlineStr">
-        <is>
-          <t>111740</t>
-        </is>
+      <c r="A2212" t="n">
+        <v>111740</v>
       </c>
       <c r="B2212" t="inlineStr">
         <is>
@@ -87697,10 +87675,8 @@
       <c r="I2212" t="inlineStr"/>
     </row>
     <row r="2213">
-      <c r="A2213" t="inlineStr">
-        <is>
-          <t>65469</t>
-        </is>
+      <c r="A2213" t="n">
+        <v>65469</v>
       </c>
       <c r="B2213" t="inlineStr">
         <is>
@@ -87740,10 +87716,8 @@
       </c>
     </row>
     <row r="2214">
-      <c r="A2214" t="inlineStr">
-        <is>
-          <t>65499</t>
-        </is>
+      <c r="A2214" t="n">
+        <v>65499</v>
       </c>
       <c r="B2214" t="inlineStr">
         <is>
@@ -87771,10 +87745,8 @@
       <c r="I2214" t="inlineStr"/>
     </row>
     <row r="2215">
-      <c r="A2215" t="inlineStr">
-        <is>
-          <t>65497</t>
-        </is>
+      <c r="A2215" t="n">
+        <v>65497</v>
       </c>
       <c r="B2215" t="inlineStr">
         <is>
@@ -87814,10 +87786,8 @@
       </c>
     </row>
     <row r="2216">
-      <c r="A2216" t="inlineStr">
-        <is>
-          <t>32350</t>
-        </is>
+      <c r="A2216" t="n">
+        <v>32350</v>
       </c>
       <c r="B2216" t="inlineStr">
         <is>
@@ -87845,10 +87815,8 @@
       <c r="I2216" t="inlineStr"/>
     </row>
     <row r="2217">
-      <c r="A2217" t="inlineStr">
-        <is>
-          <t>65502</t>
-        </is>
+      <c r="A2217" t="n">
+        <v>65502</v>
       </c>
       <c r="B2217" t="inlineStr">
         <is>
@@ -87876,10 +87844,8 @@
       <c r="I2217" t="inlineStr"/>
     </row>
     <row r="2218">
-      <c r="A2218" t="inlineStr">
-        <is>
-          <t>65498</t>
-        </is>
+      <c r="A2218" t="n">
+        <v>65498</v>
       </c>
       <c r="B2218" t="inlineStr">
         <is>
@@ -87919,10 +87885,8 @@
       </c>
     </row>
     <row r="2219">
-      <c r="A2219" t="inlineStr">
-        <is>
-          <t>65470</t>
-        </is>
+      <c r="A2219" t="n">
+        <v>65470</v>
       </c>
       <c r="B2219" t="inlineStr">
         <is>
@@ -87950,10 +87914,8 @@
       <c r="I2219" t="inlineStr"/>
     </row>
     <row r="2220">
-      <c r="A2220" t="inlineStr">
-        <is>
-          <t>212356</t>
-        </is>
+      <c r="A2220" t="n">
+        <v>212356</v>
       </c>
       <c r="B2220" t="inlineStr">
         <is>
@@ -87981,10 +87943,8 @@
       <c r="I2220" t="inlineStr"/>
     </row>
     <row r="2221">
-      <c r="A2221" t="inlineStr">
-        <is>
-          <t>87636</t>
-        </is>
+      <c r="A2221" t="n">
+        <v>87636</v>
       </c>
       <c r="B2221" t="inlineStr">
         <is>
@@ -88011,6 +87971,782 @@
       <c r="H2221" t="inlineStr"/>
       <c r="I2221" t="inlineStr"/>
     </row>
+    <row r="2222">
+      <c r="A2222" t="inlineStr">
+        <is>
+          <t>65480</t>
+        </is>
+      </c>
+      <c r="B2222" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C2222" t="inlineStr">
+        <is>
+          <t>6591 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2222" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21925095319, 'Longitude': -122.968211174011}</t>
+        </is>
+      </c>
+      <c r="E2222" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:44:00</t>
+        </is>
+      </c>
+      <c r="F2222" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:39:17.805Z</t>
+        </is>
+      </c>
+      <c r="G2222" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H2222" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:25:44.411Z</t>
+        </is>
+      </c>
+      <c r="I2222" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="2223">
+      <c r="A2223" t="inlineStr">
+        <is>
+          <t>65467</t>
+        </is>
+      </c>
+      <c r="B2223" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2223" t="inlineStr">
+        <is>
+          <t>6138 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2223" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2223" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:44:00</t>
+        </is>
+      </c>
+      <c r="F2223" t="inlineStr"/>
+      <c r="G2223" t="inlineStr"/>
+      <c r="H2223" t="inlineStr"/>
+      <c r="I2223" t="inlineStr"/>
+    </row>
+    <row r="2224">
+      <c r="A2224" t="inlineStr">
+        <is>
+          <t>119589</t>
+        </is>
+      </c>
+      <c r="B2224" t="inlineStr">
+        <is>
+          <t>Smart Gas</t>
+        </is>
+      </c>
+      <c r="C2224" t="inlineStr">
+        <is>
+          <t>6869 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2224" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2224" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:44:00</t>
+        </is>
+      </c>
+      <c r="F2224" t="inlineStr"/>
+      <c r="G2224" t="inlineStr"/>
+      <c r="H2224" t="inlineStr"/>
+      <c r="I2224" t="inlineStr"/>
+    </row>
+    <row r="2225">
+      <c r="A2225" t="inlineStr">
+        <is>
+          <t>65474</t>
+        </is>
+      </c>
+      <c r="B2225" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2225" t="inlineStr">
+        <is>
+          <t>7274 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2225" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2225" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:44:00</t>
+        </is>
+      </c>
+      <c r="F2225" t="inlineStr"/>
+      <c r="G2225" t="inlineStr"/>
+      <c r="H2225" t="inlineStr"/>
+      <c r="I2225" t="inlineStr"/>
+    </row>
+    <row r="2226">
+      <c r="A2226" t="inlineStr">
+        <is>
+          <t>87633</t>
+        </is>
+      </c>
+      <c r="B2226" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C2226" t="inlineStr">
+        <is>
+          <t>5608 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2226" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2226" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:44:00</t>
+        </is>
+      </c>
+      <c r="F2226" t="inlineStr"/>
+      <c r="G2226" t="inlineStr"/>
+      <c r="H2226" t="inlineStr"/>
+      <c r="I2226" t="inlineStr"/>
+    </row>
+    <row r="2227">
+      <c r="A2227" t="inlineStr">
+        <is>
+          <t>65481</t>
+        </is>
+      </c>
+      <c r="B2227" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C2227" t="inlineStr">
+        <is>
+          <t>7377 6th St</t>
+        </is>
+      </c>
+      <c r="D2227" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.225214157435, 'Longitude': -122.935831546783}</t>
+        </is>
+      </c>
+      <c r="E2227" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:44:00</t>
+        </is>
+      </c>
+      <c r="F2227" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:11:43.763Z</t>
+        </is>
+      </c>
+      <c r="G2227" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H2227" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:11:43.810Z</t>
+        </is>
+      </c>
+      <c r="I2227" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="2228">
+      <c r="A2228" t="inlineStr">
+        <is>
+          <t>65477</t>
+        </is>
+      </c>
+      <c r="B2228" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2228" t="inlineStr">
+        <is>
+          <t>7890 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2228" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2228" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:44:00</t>
+        </is>
+      </c>
+      <c r="F2228" t="inlineStr"/>
+      <c r="G2228" t="inlineStr"/>
+      <c r="H2228" t="inlineStr"/>
+      <c r="I2228" t="inlineStr"/>
+    </row>
+    <row r="2229">
+      <c r="A2229" t="inlineStr">
+        <is>
+          <t>65468</t>
+        </is>
+      </c>
+      <c r="B2229" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2229" t="inlineStr">
+        <is>
+          <t>7587 Royal Oak Ave</t>
+        </is>
+      </c>
+      <c r="D2229" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2229" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:44:00</t>
+        </is>
+      </c>
+      <c r="F2229" t="inlineStr"/>
+      <c r="G2229" t="inlineStr"/>
+      <c r="H2229" t="inlineStr"/>
+      <c r="I2229" t="inlineStr"/>
+    </row>
+    <row r="2230">
+      <c r="A2230" t="inlineStr">
+        <is>
+          <t>65471</t>
+        </is>
+      </c>
+      <c r="B2230" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2230" t="inlineStr">
+        <is>
+          <t>5059 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2230" t="inlineStr">
+        <is>
+          <t>{'Latitude': None, 'Longitude': None}</t>
+        </is>
+      </c>
+      <c r="E2230" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:44:00</t>
+        </is>
+      </c>
+      <c r="F2230" t="inlineStr"/>
+      <c r="G2230" t="inlineStr"/>
+      <c r="H2230" t="inlineStr"/>
+      <c r="I2230" t="inlineStr"/>
+    </row>
+    <row r="2231">
+      <c r="A2231" t="inlineStr">
+        <is>
+          <t>5768</t>
+        </is>
+      </c>
+      <c r="B2231" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2231" t="inlineStr">
+        <is>
+          <t>5009 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2231" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2264629, 'Longitude': -122.992576}</t>
+        </is>
+      </c>
+      <c r="E2231" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:44:00</t>
+        </is>
+      </c>
+      <c r="F2231" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:41:13.695Z</t>
+        </is>
+      </c>
+      <c r="G2231" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2231" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:29:07.196Z</t>
+        </is>
+      </c>
+      <c r="I2231" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="2232">
+      <c r="A2232" t="inlineStr">
+        <is>
+          <t>111740</t>
+        </is>
+      </c>
+      <c r="B2232" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2232" t="inlineStr">
+        <is>
+          <t>780 6th St</t>
+        </is>
+      </c>
+      <c r="D2232" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21557, 'Longitude': -122.92387}</t>
+        </is>
+      </c>
+      <c r="E2232" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:44:00</t>
+        </is>
+      </c>
+      <c r="F2232" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:09:24.586Z</t>
+        </is>
+      </c>
+      <c r="G2232" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H2232" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:09:24.679Z</t>
+        </is>
+      </c>
+      <c r="I2232" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="2233">
+      <c r="A2233" t="inlineStr">
+        <is>
+          <t>65469</t>
+        </is>
+      </c>
+      <c r="B2233" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2233" t="inlineStr">
+        <is>
+          <t>4692 Imperial St</t>
+        </is>
+      </c>
+      <c r="D2233" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2217244, 'Longitude': -122.9980797}</t>
+        </is>
+      </c>
+      <c r="E2233" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:44:00</t>
+        </is>
+      </c>
+      <c r="F2233" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:04:25.698Z</t>
+        </is>
+      </c>
+      <c r="G2233" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2233" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:58:12.777Z</t>
+        </is>
+      </c>
+      <c r="I2233" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="2234">
+      <c r="A2234" t="inlineStr">
+        <is>
+          <t>65499</t>
+        </is>
+      </c>
+      <c r="B2234" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2234" t="inlineStr">
+        <is>
+          <t>736 Sixth Ave</t>
+        </is>
+      </c>
+      <c r="D2234" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21129, 'Longitude': -122.92333}</t>
+        </is>
+      </c>
+      <c r="E2234" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:44:00</t>
+        </is>
+      </c>
+      <c r="F2234" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:19.310Z</t>
+        </is>
+      </c>
+      <c r="G2234" t="n">
+        <v>164.6</v>
+      </c>
+      <c r="H2234" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:19.329Z</t>
+        </is>
+      </c>
+      <c r="I2234" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="2235">
+      <c r="A2235" t="inlineStr">
+        <is>
+          <t>65497</t>
+        </is>
+      </c>
+      <c r="B2235" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2235" t="inlineStr">
+        <is>
+          <t>428 Sixth St</t>
+        </is>
+      </c>
+      <c r="D2235" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2109656, 'Longitude': -122.9179526}</t>
+        </is>
+      </c>
+      <c r="E2235" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:44:00</t>
+        </is>
+      </c>
+      <c r="F2235" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:24.583Z</t>
+        </is>
+      </c>
+      <c r="G2235" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2235" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:24.614Z</t>
+        </is>
+      </c>
+      <c r="I2235" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="2236">
+      <c r="A2236" t="inlineStr">
+        <is>
+          <t>32350</t>
+        </is>
+      </c>
+      <c r="B2236" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2236" t="inlineStr">
+        <is>
+          <t>132 12th St</t>
+        </is>
+      </c>
+      <c r="D2236" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.201144, 'Longitude': -122.922922}</t>
+        </is>
+      </c>
+      <c r="E2236" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:44:00</t>
+        </is>
+      </c>
+      <c r="F2236" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:39:32.127Z</t>
+        </is>
+      </c>
+      <c r="G2236" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2236" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:54:43.702Z</t>
+        </is>
+      </c>
+      <c r="I2236" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="A2237" t="inlineStr">
+        <is>
+          <t>65502</t>
+        </is>
+      </c>
+      <c r="B2237" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2237" t="inlineStr">
+        <is>
+          <t>5 W 8th Ave</t>
+        </is>
+      </c>
+      <c r="D2237" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.222332, 'Longitude': -122.91267}</t>
+        </is>
+      </c>
+      <c r="E2237" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:44:00</t>
+        </is>
+      </c>
+      <c r="F2237" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:28:55.366Z</t>
+        </is>
+      </c>
+      <c r="G2237" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H2237" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:28:55.397Z</t>
+        </is>
+      </c>
+      <c r="I2237" t="n">
+        <v>199.9</v>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="A2238" t="inlineStr">
+        <is>
+          <t>65498</t>
+        </is>
+      </c>
+      <c r="B2238" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2238" t="inlineStr">
+        <is>
+          <t>3 E 8th Ave</t>
+        </is>
+      </c>
+      <c r="D2238" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2228942, 'Longitude': -122.9117512}</t>
+        </is>
+      </c>
+      <c r="E2238" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:44:00</t>
+        </is>
+      </c>
+      <c r="F2238" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:29:02.534Z</t>
+        </is>
+      </c>
+      <c r="G2238" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H2238" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:29:02.565Z</t>
+        </is>
+      </c>
+      <c r="I2238" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="2239">
+      <c r="A2239" t="inlineStr">
+        <is>
+          <t>65470</t>
+        </is>
+      </c>
+      <c r="B2239" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2239" t="inlineStr">
+        <is>
+          <t>4444 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2239" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.23030428362, 'Longitude': -123.006110787392}</t>
+        </is>
+      </c>
+      <c r="E2239" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:44:00</t>
+        </is>
+      </c>
+      <c r="F2239" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:23:17.106Z</t>
+        </is>
+      </c>
+      <c r="G2239" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2239" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:23:17.129Z</t>
+        </is>
+      </c>
+      <c r="I2239" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="2240">
+      <c r="A2240" t="inlineStr">
+        <is>
+          <t>212356</t>
+        </is>
+      </c>
+      <c r="B2240" t="inlineStr">
+        <is>
+          <t>CENTEX</t>
+        </is>
+      </c>
+      <c r="C2240" t="inlineStr">
+        <is>
+          <t>3855 Douglas Rd</t>
+        </is>
+      </c>
+      <c r="D2240" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249718360686, 'Longitude': -122.981165650914}</t>
+        </is>
+      </c>
+      <c r="E2240" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:44:00</t>
+        </is>
+      </c>
+      <c r="F2240" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:49:43.061Z</t>
+        </is>
+      </c>
+      <c r="G2240" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2240" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:02:08.577Z</t>
+        </is>
+      </c>
+      <c r="I2240" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="2241">
+      <c r="A2241" t="inlineStr">
+        <is>
+          <t>87636</t>
+        </is>
+      </c>
+      <c r="B2241" t="inlineStr">
+        <is>
+          <t>CENTEX</t>
+        </is>
+      </c>
+      <c r="C2241" t="inlineStr">
+        <is>
+          <t>1101 Ewen Ave</t>
+        </is>
+      </c>
+      <c r="D2241" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.185333, 'Longitude': -122.949622}</t>
+        </is>
+      </c>
+      <c r="E2241" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:44:00</t>
+        </is>
+      </c>
+      <c r="F2241" t="inlineStr">
+        <is>
+          <t>2025-08-21T17:41:46.201Z</t>
+        </is>
+      </c>
+      <c r="G2241" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="H2241" t="inlineStr">
+        <is>
+          <t>2025-08-21T17:41:46.232Z</t>
+        </is>
+      </c>
+      <c r="I2241" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gas_prices.xlsx
+++ b/data/gas_prices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2241"/>
+  <dimension ref="A1:I2381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87972,10 +87972,8 @@
       <c r="I2221" t="inlineStr"/>
     </row>
     <row r="2222">
-      <c r="A2222" t="inlineStr">
-        <is>
-          <t>65480</t>
-        </is>
+      <c r="A2222" t="n">
+        <v>65480</v>
       </c>
       <c r="B2222" t="inlineStr">
         <is>
@@ -88015,10 +88013,8 @@
       </c>
     </row>
     <row r="2223">
-      <c r="A2223" t="inlineStr">
-        <is>
-          <t>65467</t>
-        </is>
+      <c r="A2223" t="n">
+        <v>65467</v>
       </c>
       <c r="B2223" t="inlineStr">
         <is>
@@ -88046,10 +88042,8 @@
       <c r="I2223" t="inlineStr"/>
     </row>
     <row r="2224">
-      <c r="A2224" t="inlineStr">
-        <is>
-          <t>119589</t>
-        </is>
+      <c r="A2224" t="n">
+        <v>119589</v>
       </c>
       <c r="B2224" t="inlineStr">
         <is>
@@ -88077,10 +88071,8 @@
       <c r="I2224" t="inlineStr"/>
     </row>
     <row r="2225">
-      <c r="A2225" t="inlineStr">
-        <is>
-          <t>65474</t>
-        </is>
+      <c r="A2225" t="n">
+        <v>65474</v>
       </c>
       <c r="B2225" t="inlineStr">
         <is>
@@ -88108,10 +88100,8 @@
       <c r="I2225" t="inlineStr"/>
     </row>
     <row r="2226">
-      <c r="A2226" t="inlineStr">
-        <is>
-          <t>87633</t>
-        </is>
+      <c r="A2226" t="n">
+        <v>87633</v>
       </c>
       <c r="B2226" t="inlineStr">
         <is>
@@ -88139,10 +88129,8 @@
       <c r="I2226" t="inlineStr"/>
     </row>
     <row r="2227">
-      <c r="A2227" t="inlineStr">
-        <is>
-          <t>65481</t>
-        </is>
+      <c r="A2227" t="n">
+        <v>65481</v>
       </c>
       <c r="B2227" t="inlineStr">
         <is>
@@ -88182,10 +88170,8 @@
       </c>
     </row>
     <row r="2228">
-      <c r="A2228" t="inlineStr">
-        <is>
-          <t>65477</t>
-        </is>
+      <c r="A2228" t="n">
+        <v>65477</v>
       </c>
       <c r="B2228" t="inlineStr">
         <is>
@@ -88213,10 +88199,8 @@
       <c r="I2228" t="inlineStr"/>
     </row>
     <row r="2229">
-      <c r="A2229" t="inlineStr">
-        <is>
-          <t>65468</t>
-        </is>
+      <c r="A2229" t="n">
+        <v>65468</v>
       </c>
       <c r="B2229" t="inlineStr">
         <is>
@@ -88244,10 +88228,8 @@
       <c r="I2229" t="inlineStr"/>
     </row>
     <row r="2230">
-      <c r="A2230" t="inlineStr">
-        <is>
-          <t>65471</t>
-        </is>
+      <c r="A2230" t="n">
+        <v>65471</v>
       </c>
       <c r="B2230" t="inlineStr">
         <is>
@@ -88275,10 +88257,8 @@
       <c r="I2230" t="inlineStr"/>
     </row>
     <row r="2231">
-      <c r="A2231" t="inlineStr">
-        <is>
-          <t>5768</t>
-        </is>
+      <c r="A2231" t="n">
+        <v>5768</v>
       </c>
       <c r="B2231" t="inlineStr">
         <is>
@@ -88318,10 +88298,8 @@
       </c>
     </row>
     <row r="2232">
-      <c r="A2232" t="inlineStr">
-        <is>
-          <t>111740</t>
-        </is>
+      <c r="A2232" t="n">
+        <v>111740</v>
       </c>
       <c r="B2232" t="inlineStr">
         <is>
@@ -88361,10 +88339,8 @@
       </c>
     </row>
     <row r="2233">
-      <c r="A2233" t="inlineStr">
-        <is>
-          <t>65469</t>
-        </is>
+      <c r="A2233" t="n">
+        <v>65469</v>
       </c>
       <c r="B2233" t="inlineStr">
         <is>
@@ -88404,10 +88380,8 @@
       </c>
     </row>
     <row r="2234">
-      <c r="A2234" t="inlineStr">
-        <is>
-          <t>65499</t>
-        </is>
+      <c r="A2234" t="n">
+        <v>65499</v>
       </c>
       <c r="B2234" t="inlineStr">
         <is>
@@ -88447,10 +88421,8 @@
       </c>
     </row>
     <row r="2235">
-      <c r="A2235" t="inlineStr">
-        <is>
-          <t>65497</t>
-        </is>
+      <c r="A2235" t="n">
+        <v>65497</v>
       </c>
       <c r="B2235" t="inlineStr">
         <is>
@@ -88490,10 +88462,8 @@
       </c>
     </row>
     <row r="2236">
-      <c r="A2236" t="inlineStr">
-        <is>
-          <t>32350</t>
-        </is>
+      <c r="A2236" t="n">
+        <v>32350</v>
       </c>
       <c r="B2236" t="inlineStr">
         <is>
@@ -88533,10 +88503,8 @@
       </c>
     </row>
     <row r="2237">
-      <c r="A2237" t="inlineStr">
-        <is>
-          <t>65502</t>
-        </is>
+      <c r="A2237" t="n">
+        <v>65502</v>
       </c>
       <c r="B2237" t="inlineStr">
         <is>
@@ -88576,10 +88544,8 @@
       </c>
     </row>
     <row r="2238">
-      <c r="A2238" t="inlineStr">
-        <is>
-          <t>65498</t>
-        </is>
+      <c r="A2238" t="n">
+        <v>65498</v>
       </c>
       <c r="B2238" t="inlineStr">
         <is>
@@ -88619,10 +88585,8 @@
       </c>
     </row>
     <row r="2239">
-      <c r="A2239" t="inlineStr">
-        <is>
-          <t>65470</t>
-        </is>
+      <c r="A2239" t="n">
+        <v>65470</v>
       </c>
       <c r="B2239" t="inlineStr">
         <is>
@@ -88662,10 +88626,8 @@
       </c>
     </row>
     <row r="2240">
-      <c r="A2240" t="inlineStr">
-        <is>
-          <t>212356</t>
-        </is>
+      <c r="A2240" t="n">
+        <v>212356</v>
       </c>
       <c r="B2240" t="inlineStr">
         <is>
@@ -88705,10 +88667,8 @@
       </c>
     </row>
     <row r="2241">
-      <c r="A2241" t="inlineStr">
-        <is>
-          <t>87636</t>
-        </is>
+      <c r="A2241" t="n">
+        <v>87636</v>
       </c>
       <c r="B2241" t="inlineStr">
         <is>
@@ -88745,6 +88705,5698 @@
       </c>
       <c r="I2241" t="n">
         <v>183.9</v>
+      </c>
+    </row>
+    <row r="2242">
+      <c r="A2242" t="n">
+        <v>65542</v>
+      </c>
+      <c r="B2242" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2242" t="inlineStr">
+        <is>
+          <t>3250 MacDonald St</t>
+        </is>
+      </c>
+      <c r="D2242" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2573819, 'Longitude': -123.1680407}</t>
+        </is>
+      </c>
+      <c r="E2242" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:48:52</t>
+        </is>
+      </c>
+      <c r="F2242" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:03:56.105Z</t>
+        </is>
+      </c>
+      <c r="G2242" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2242" t="inlineStr">
+        <is>
+          <t>2025-08-21T05:37:56.532Z</t>
+        </is>
+      </c>
+      <c r="I2242" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="2243">
+      <c r="A2243" t="n">
+        <v>65533</v>
+      </c>
+      <c r="B2243" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2243" t="inlineStr">
+        <is>
+          <t>4615 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D2243" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2449719, 'Longitude': -123.1540385}</t>
+        </is>
+      </c>
+      <c r="E2243" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:48:52</t>
+        </is>
+      </c>
+      <c r="F2243" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:15:46.313Z</t>
+        </is>
+      </c>
+      <c r="G2243" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2243" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:15:46.360Z</t>
+        </is>
+      </c>
+      <c r="I2243" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="2244">
+      <c r="A2244" t="n">
+        <v>83068</v>
+      </c>
+      <c r="B2244" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2244" t="inlineStr">
+        <is>
+          <t>3205 Arbutus St</t>
+        </is>
+      </c>
+      <c r="D2244" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.256927568207, 'Longitude': -123.153288960457}</t>
+        </is>
+      </c>
+      <c r="E2244" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:48:52</t>
+        </is>
+      </c>
+      <c r="F2244" t="inlineStr"/>
+      <c r="G2244" t="inlineStr"/>
+      <c r="H2244" t="inlineStr"/>
+      <c r="I2244" t="inlineStr"/>
+    </row>
+    <row r="2245">
+      <c r="A2245" t="n">
+        <v>65562</v>
+      </c>
+      <c r="B2245" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2245" t="inlineStr">
+        <is>
+          <t>2808 W Broadway</t>
+        </is>
+      </c>
+      <c r="D2245" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263883932125, 'Longitude': -123.168604373932}</t>
+        </is>
+      </c>
+      <c r="E2245" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:48:52</t>
+        </is>
+      </c>
+      <c r="F2245" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:13:30.527Z</t>
+        </is>
+      </c>
+      <c r="G2245" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2245" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:22:12.089Z</t>
+        </is>
+      </c>
+      <c r="I2245" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="2246">
+      <c r="A2246" t="n">
+        <v>113305</v>
+      </c>
+      <c r="B2246" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2246" t="inlineStr">
+        <is>
+          <t>3596 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D2246" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234385296079, 'Longitude': -123.184762001038}</t>
+        </is>
+      </c>
+      <c r="E2246" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:48:52</t>
+        </is>
+      </c>
+      <c r="F2246" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:24:22.395Z</t>
+        </is>
+      </c>
+      <c r="G2246" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2246" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:45:28.860Z</t>
+        </is>
+      </c>
+      <c r="I2246" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="2247">
+      <c r="A2247" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B2247" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2247" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D2247" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E2247" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:48:52</t>
+        </is>
+      </c>
+      <c r="F2247" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:03:50.343Z</t>
+        </is>
+      </c>
+      <c r="G2247" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H2247" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:51:32.975Z</t>
+        </is>
+      </c>
+      <c r="I2247" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="2248">
+      <c r="A2248" t="n">
+        <v>65554</v>
+      </c>
+      <c r="B2248" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2248" t="inlineStr">
+        <is>
+          <t>1795 W Broadway</t>
+        </is>
+      </c>
+      <c r="D2248" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264037962303, 'Longitude': -123.145408630371}</t>
+        </is>
+      </c>
+      <c r="E2248" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:48:52</t>
+        </is>
+      </c>
+      <c r="F2248" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:18:17.016Z</t>
+        </is>
+      </c>
+      <c r="G2248" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2248" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:52:38.117Z</t>
+        </is>
+      </c>
+      <c r="I2248" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="2249">
+      <c r="A2249" t="n">
+        <v>65571</v>
+      </c>
+      <c r="B2249" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2249" t="inlineStr">
+        <is>
+          <t>4314 W 10th Ave</t>
+        </is>
+      </c>
+      <c r="D2249" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.263533861752, 'Longitude': -123.203430175781}</t>
+        </is>
+      </c>
+      <c r="E2249" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:48:52</t>
+        </is>
+      </c>
+      <c r="F2249" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:28:25.070Z</t>
+        </is>
+      </c>
+      <c r="G2249" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2249" t="inlineStr">
+        <is>
+          <t>2025-08-21T17:52:15.464Z</t>
+        </is>
+      </c>
+      <c r="I2249" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="2250">
+      <c r="A2250" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B2250" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2250" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D2250" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E2250" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:48:52</t>
+        </is>
+      </c>
+      <c r="F2250" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:23:16.373Z</t>
+        </is>
+      </c>
+      <c r="G2250" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2250" t="inlineStr"/>
+      <c r="I2250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2251">
+      <c r="A2251" t="n">
+        <v>32376</v>
+      </c>
+      <c r="B2251" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2251" t="inlineStr">
+        <is>
+          <t>1503 W 41st Ave</t>
+        </is>
+      </c>
+      <c r="D2251" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234634576953, 'Longitude': -123.139971792698}</t>
+        </is>
+      </c>
+      <c r="E2251" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:48:52</t>
+        </is>
+      </c>
+      <c r="F2251" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:03:52.722Z</t>
+        </is>
+      </c>
+      <c r="G2251" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2251" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:24:56.809Z</t>
+        </is>
+      </c>
+      <c r="I2251" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="A2252" t="n">
+        <v>65549</v>
+      </c>
+      <c r="B2252" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2252" t="inlineStr">
+        <is>
+          <t>5702 Granville St</t>
+        </is>
+      </c>
+      <c r="D2252" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234036184118, 'Longitude': -123.139244914055}</t>
+        </is>
+      </c>
+      <c r="E2252" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:48:52</t>
+        </is>
+      </c>
+      <c r="F2252" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:47:29.946Z</t>
+        </is>
+      </c>
+      <c r="G2252" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2252" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:05:40.501Z</t>
+        </is>
+      </c>
+      <c r="I2252" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="A2253" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B2253" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2253" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D2253" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E2253" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:48:52</t>
+        </is>
+      </c>
+      <c r="F2253" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:46:17.762Z</t>
+        </is>
+      </c>
+      <c r="G2253" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2253" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:46:17.794Z</t>
+        </is>
+      </c>
+      <c r="I2253" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="2254">
+      <c r="A2254" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B2254" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2254" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D2254" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E2254" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:48:52</t>
+        </is>
+      </c>
+      <c r="F2254" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:28:51.238Z</t>
+        </is>
+      </c>
+      <c r="G2254" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H2254" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:11.555Z</t>
+        </is>
+      </c>
+      <c r="I2254" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="2255">
+      <c r="A2255" t="n">
+        <v>72747</v>
+      </c>
+      <c r="B2255" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2255" t="inlineStr">
+        <is>
+          <t>1010 W King Edward Ave</t>
+        </is>
+      </c>
+      <c r="D2255" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249188, 'Longitude': -123.127767}</t>
+        </is>
+      </c>
+      <c r="E2255" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:48:52</t>
+        </is>
+      </c>
+      <c r="F2255" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:13:46.907Z</t>
+        </is>
+      </c>
+      <c r="G2255" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2255" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:51:18.062Z</t>
+        </is>
+      </c>
+      <c r="I2255" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="2256">
+      <c r="A2256" t="n">
+        <v>32375</v>
+      </c>
+      <c r="B2256" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2256" t="inlineStr">
+        <is>
+          <t>4110 Oak St</t>
+        </is>
+      </c>
+      <c r="D2256" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.24894071957, 'Longitude': -123.127040863037}</t>
+        </is>
+      </c>
+      <c r="E2256" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:48:52</t>
+        </is>
+      </c>
+      <c r="F2256" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:14:35.071Z</t>
+        </is>
+      </c>
+      <c r="G2256" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2256" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:17:09.064Z</t>
+        </is>
+      </c>
+      <c r="I2256" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="2257">
+      <c r="A2257" t="n">
+        <v>65564</v>
+      </c>
+      <c r="B2257" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2257" t="inlineStr">
+        <is>
+          <t>5680 Oak St</t>
+        </is>
+      </c>
+      <c r="D2257" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.234217162181, 'Longitude': -123.127684593201}</t>
+        </is>
+      </c>
+      <c r="E2257" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:48:52</t>
+        </is>
+      </c>
+      <c r="F2257" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:29:33.603Z</t>
+        </is>
+      </c>
+      <c r="G2257" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2257" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:48:09.828Z</t>
+        </is>
+      </c>
+      <c r="I2257" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="2258">
+      <c r="A2258" t="n">
+        <v>32372</v>
+      </c>
+      <c r="B2258" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2258" t="inlineStr">
+        <is>
+          <t>6525 Oak St</t>
+        </is>
+      </c>
+      <c r="D2258" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226226639452, 'Longitude': -123.128687739372}</t>
+        </is>
+      </c>
+      <c r="E2258" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:48:52</t>
+        </is>
+      </c>
+      <c r="F2258" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:25:08.864Z</t>
+        </is>
+      </c>
+      <c r="G2258" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2258" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:46:43.341Z</t>
+        </is>
+      </c>
+      <c r="I2258" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="2259">
+      <c r="A2259" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B2259" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2259" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D2259" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E2259" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:48:52</t>
+        </is>
+      </c>
+      <c r="F2259" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:49:20.616Z</t>
+        </is>
+      </c>
+      <c r="G2259" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2259" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:49:01.374Z</t>
+        </is>
+      </c>
+      <c r="I2259" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="2260">
+      <c r="A2260" t="n">
+        <v>65566</v>
+      </c>
+      <c r="B2260" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2260" t="inlineStr">
+        <is>
+          <t>8072 Granville St</t>
+        </is>
+      </c>
+      <c r="D2260" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.212495055855, 'Longitude': -123.14013004303}</t>
+        </is>
+      </c>
+      <c r="E2260" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:48:52</t>
+        </is>
+      </c>
+      <c r="F2260" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:15:48.444Z</t>
+        </is>
+      </c>
+      <c r="G2260" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2260" t="inlineStr"/>
+      <c r="I2260" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2261">
+      <c r="A2261" t="n">
+        <v>65572</v>
+      </c>
+      <c r="B2261" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2261" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D2261" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E2261" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:48:52</t>
+        </is>
+      </c>
+      <c r="F2261" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:15:25.202Z</t>
+        </is>
+      </c>
+      <c r="G2261" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2261" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:50:22.600Z</t>
+        </is>
+      </c>
+      <c r="I2261" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="2262">
+      <c r="A2262" t="n">
+        <v>65558</v>
+      </c>
+      <c r="B2262" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2262" t="inlineStr">
+        <is>
+          <t>1390 E 33rd Ave</t>
+        </is>
+      </c>
+      <c r="D2262" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.240045470021, 'Longitude': -123.076765537262}</t>
+        </is>
+      </c>
+      <c r="E2262" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:51:47</t>
+        </is>
+      </c>
+      <c r="F2262" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:41:41.334Z</t>
+        </is>
+      </c>
+      <c r="G2262" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="H2262" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:41:41.365Z</t>
+        </is>
+      </c>
+      <c r="I2262" t="n">
+        <v>178.9</v>
+      </c>
+    </row>
+    <row r="2263">
+      <c r="A2263" t="n">
+        <v>83394</v>
+      </c>
+      <c r="B2263" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2263" t="inlineStr">
+        <is>
+          <t>4064 Fraser St</t>
+        </is>
+      </c>
+      <c r="D2263" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.248864, 'Longitude': -123.09002}</t>
+        </is>
+      </c>
+      <c r="E2263" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:51:47</t>
+        </is>
+      </c>
+      <c r="F2263" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:40:06.733Z</t>
+        </is>
+      </c>
+      <c r="G2263" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2263" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:08:24.169Z</t>
+        </is>
+      </c>
+      <c r="I2263" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="2264">
+      <c r="A2264" t="n">
+        <v>65573</v>
+      </c>
+      <c r="B2264" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2264" t="inlineStr">
+        <is>
+          <t>1396 E 41st Ave</t>
+        </is>
+      </c>
+      <c r="D2264" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.232593005895, 'Longitude': -123.07728856802}</t>
+        </is>
+      </c>
+      <c r="E2264" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:51:47</t>
+        </is>
+      </c>
+      <c r="F2264" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:47:11.149Z</t>
+        </is>
+      </c>
+      <c r="G2264" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2264" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:57:31.376Z</t>
+        </is>
+      </c>
+      <c r="I2264" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="2265">
+      <c r="A2265" t="n">
+        <v>80714</v>
+      </c>
+      <c r="B2265" t="inlineStr">
+        <is>
+          <t>Husky</t>
+        </is>
+      </c>
+      <c r="C2265" t="inlineStr">
+        <is>
+          <t>4933 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D2265" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2397388, 'Longitude': -123.065748}</t>
+        </is>
+      </c>
+      <c r="E2265" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:51:47</t>
+        </is>
+      </c>
+      <c r="F2265" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:07:24.794Z</t>
+        </is>
+      </c>
+      <c r="G2265" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2265" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:47:42.715Z</t>
+        </is>
+      </c>
+      <c r="I2265" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="2266">
+      <c r="A2266" t="n">
+        <v>65552</v>
+      </c>
+      <c r="B2266" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2266" t="inlineStr">
+        <is>
+          <t>2001 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2266" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.245312771918, 'Longitude': -123.064910173416}</t>
+        </is>
+      </c>
+      <c r="E2266" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:51:47</t>
+        </is>
+      </c>
+      <c r="F2266" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:07:43.095Z</t>
+        </is>
+      </c>
+      <c r="G2266" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="H2266" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:59:26.854Z</t>
+        </is>
+      </c>
+      <c r="I2266" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="A2267" t="n">
+        <v>65538</v>
+      </c>
+      <c r="B2267" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2267" t="inlineStr">
+        <is>
+          <t>5252 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D2267" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2372145, 'Longitude': -123.0650857}</t>
+        </is>
+      </c>
+      <c r="E2267" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:51:47</t>
+        </is>
+      </c>
+      <c r="F2267" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:47:51.264Z</t>
+        </is>
+      </c>
+      <c r="G2267" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2267" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:47:51.295Z</t>
+        </is>
+      </c>
+      <c r="I2267" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="2268">
+      <c r="A2268" t="n">
+        <v>90814</v>
+      </c>
+      <c r="B2268" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2268" t="inlineStr">
+        <is>
+          <t>2277 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2268" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.242132845692, 'Longitude': -123.058204650879}</t>
+        </is>
+      </c>
+      <c r="E2268" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:51:47</t>
+        </is>
+      </c>
+      <c r="F2268" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:58:58.737Z</t>
+        </is>
+      </c>
+      <c r="G2268" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2268" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:58:58.753Z</t>
+        </is>
+      </c>
+      <c r="I2268" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="2269">
+      <c r="A2269" t="n">
+        <v>39768</v>
+      </c>
+      <c r="B2269" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2269" t="inlineStr">
+        <is>
+          <t>5736 Main St</t>
+        </is>
+      </c>
+      <c r="D2269" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2325708, 'Longitude': -123.1010069}</t>
+        </is>
+      </c>
+      <c r="E2269" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:51:47</t>
+        </is>
+      </c>
+      <c r="F2269" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:00:42.103Z</t>
+        </is>
+      </c>
+      <c r="G2269" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2269" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:10:07.579Z</t>
+        </is>
+      </c>
+      <c r="I2269" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="2270">
+      <c r="A2270" t="n">
+        <v>9710</v>
+      </c>
+      <c r="B2270" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2270" t="inlineStr">
+        <is>
+          <t>1295 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D2270" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259878978744, 'Longitude': -123.078074455261}</t>
+        </is>
+      </c>
+      <c r="E2270" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:51:47</t>
+        </is>
+      </c>
+      <c r="F2270" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:29:41.384Z</t>
+        </is>
+      </c>
+      <c r="G2270" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H2270" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:29:41.417Z</t>
+        </is>
+      </c>
+      <c r="I2270" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="2271">
+      <c r="A2271" t="n">
+        <v>99146</v>
+      </c>
+      <c r="B2271" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C2271" t="inlineStr">
+        <is>
+          <t>1317 E 12th Ave</t>
+        </is>
+      </c>
+      <c r="D2271" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.259758544957, 'Longitude': -123.077272474766}</t>
+        </is>
+      </c>
+      <c r="E2271" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:51:47</t>
+        </is>
+      </c>
+      <c r="F2271" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:49:23.212Z</t>
+        </is>
+      </c>
+      <c r="G2271" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="H2271" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:49:23.228Z</t>
+        </is>
+      </c>
+      <c r="I2271" t="n">
+        <v>178.9</v>
+      </c>
+    </row>
+    <row r="2272">
+      <c r="A2272" t="n">
+        <v>65560</v>
+      </c>
+      <c r="B2272" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2272" t="inlineStr">
+        <is>
+          <t>1289 E Broadway</t>
+        </is>
+      </c>
+      <c r="D2272" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.262693682723, 'Longitude': -123.078117370605}</t>
+        </is>
+      </c>
+      <c r="E2272" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:51:47</t>
+        </is>
+      </c>
+      <c r="F2272" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:39:45.101Z</t>
+        </is>
+      </c>
+      <c r="G2272" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="H2272" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:29:11.256Z</t>
+        </is>
+      </c>
+      <c r="I2272" t="n">
+        <v>178.9</v>
+      </c>
+    </row>
+    <row r="2273">
+      <c r="A2273" t="n">
+        <v>65557</v>
+      </c>
+      <c r="B2273" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2273" t="inlineStr">
+        <is>
+          <t>2120 Grandview Hwy S</t>
+        </is>
+      </c>
+      <c r="D2273" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2591601, 'Longitude': -123.0617495}</t>
+        </is>
+      </c>
+      <c r="E2273" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:51:47</t>
+        </is>
+      </c>
+      <c r="F2273" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:32.320Z</t>
+        </is>
+      </c>
+      <c r="G2273" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2273" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:32.351Z</t>
+        </is>
+      </c>
+      <c r="I2273" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="2274">
+      <c r="A2274" t="n">
+        <v>71502</v>
+      </c>
+      <c r="B2274" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2274" t="inlineStr">
+        <is>
+          <t>2748 Main St</t>
+        </is>
+      </c>
+      <c r="D2274" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2604441, 'Longitude': -123.1005869}</t>
+        </is>
+      </c>
+      <c r="E2274" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:51:47</t>
+        </is>
+      </c>
+      <c r="F2274" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:07:09.854Z</t>
+        </is>
+      </c>
+      <c r="G2274" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2274" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:07:09.939Z</t>
+        </is>
+      </c>
+      <c r="I2274" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="2275">
+      <c r="A2275" t="n">
+        <v>65559</v>
+      </c>
+      <c r="B2275" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2275" t="inlineStr">
+        <is>
+          <t>6502 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D2275" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.224996944057, 'Longitude': -123.065521717072}</t>
+        </is>
+      </c>
+      <c r="E2275" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:51:47</t>
+        </is>
+      </c>
+      <c r="F2275" t="inlineStr">
+        <is>
+          <t>2025-08-21T20:59:55.177Z</t>
+        </is>
+      </c>
+      <c r="G2275" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2275" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:06:56.250Z</t>
+        </is>
+      </c>
+      <c r="I2275" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="2276">
+      <c r="A2276" t="n">
+        <v>89943</v>
+      </c>
+      <c r="B2276" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2276" t="inlineStr">
+        <is>
+          <t>6808 Victoria Dr</t>
+        </is>
+      </c>
+      <c r="D2276" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2220242, 'Longitude': -123.0654247}</t>
+        </is>
+      </c>
+      <c r="E2276" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:51:47</t>
+        </is>
+      </c>
+      <c r="F2276" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:43:44.299Z</t>
+        </is>
+      </c>
+      <c r="G2276" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2276" t="inlineStr"/>
+      <c r="I2276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B2277" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2277" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D2277" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E2277" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:51:47</t>
+        </is>
+      </c>
+      <c r="F2277" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:50:45.909Z</t>
+        </is>
+      </c>
+      <c r="G2277" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2277" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:57.027Z</t>
+        </is>
+      </c>
+      <c r="I2277" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="A2278" t="n">
+        <v>65537</v>
+      </c>
+      <c r="B2278" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2278" t="inlineStr">
+        <is>
+          <t>2918 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2278" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.23608, 'Longitude': -123.0454858}</t>
+        </is>
+      </c>
+      <c r="E2278" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:51:47</t>
+        </is>
+      </c>
+      <c r="F2278" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:56:15.831Z</t>
+        </is>
+      </c>
+      <c r="G2278" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2278" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:56:15.847Z</t>
+        </is>
+      </c>
+      <c r="I2278" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B2279" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2279" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D2279" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E2279" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:51:47</t>
+        </is>
+      </c>
+      <c r="F2279" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:50:29.133Z</t>
+        </is>
+      </c>
+      <c r="G2279" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2279" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:37.661Z</t>
+        </is>
+      </c>
+      <c r="I2279" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" t="n">
+        <v>65535</v>
+      </c>
+      <c r="B2280" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2280" t="inlineStr">
+        <is>
+          <t>2605 E 49th Ave</t>
+        </is>
+      </c>
+      <c r="D2280" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2251291, 'Longitude': -123.0545048}</t>
+        </is>
+      </c>
+      <c r="E2280" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:51:47</t>
+        </is>
+      </c>
+      <c r="F2280" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:44:29.896Z</t>
+        </is>
+      </c>
+      <c r="G2280" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2280" t="inlineStr"/>
+      <c r="I2280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" t="n">
+        <v>65539</v>
+      </c>
+      <c r="B2281" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2281" t="inlineStr">
+        <is>
+          <t>2902 Grandview Hwy</t>
+        </is>
+      </c>
+      <c r="D2281" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2579053, 'Longitude': -123.0438464}</t>
+        </is>
+      </c>
+      <c r="E2281" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:51:47</t>
+        </is>
+      </c>
+      <c r="F2281" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:34:23.583Z</t>
+        </is>
+      </c>
+      <c r="G2281" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2281" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:34:23.614Z</t>
+        </is>
+      </c>
+      <c r="I2281" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" t="n">
+        <v>77015</v>
+      </c>
+      <c r="B2282" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C2282" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D2282" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169873456637, 'Longitude': -123.091178619746}</t>
+        </is>
+      </c>
+      <c r="E2282" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:54:42</t>
+        </is>
+      </c>
+      <c r="F2282" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:51:08.322Z</t>
+        </is>
+      </c>
+      <c r="G2282" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="H2282" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:30:39.668Z</t>
+        </is>
+      </c>
+      <c r="I2282" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" t="n">
+        <v>65511</v>
+      </c>
+      <c r="B2283" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2283" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D2283" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E2283" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:54:42</t>
+        </is>
+      </c>
+      <c r="F2283" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:03:07.680Z</t>
+        </is>
+      </c>
+      <c r="G2283" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2283" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:06:39.475Z</t>
+        </is>
+      </c>
+      <c r="I2283" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" t="n">
+        <v>86650</v>
+      </c>
+      <c r="B2284" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2284" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D2284" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169856952787, 'Longitude': -123.123961687088}</t>
+        </is>
+      </c>
+      <c r="E2284" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:54:42</t>
+        </is>
+      </c>
+      <c r="F2284" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:52:50.545Z</t>
+        </is>
+      </c>
+      <c r="G2284" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H2284" t="inlineStr">
+        <is>
+          <t>2025-08-21T16:28:22.342Z</t>
+        </is>
+      </c>
+      <c r="I2284" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" t="n">
+        <v>77218</v>
+      </c>
+      <c r="B2285" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2285" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D2285" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.173339635958, 'Longitude': -123.124954104424}</t>
+        </is>
+      </c>
+      <c r="E2285" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:54:42</t>
+        </is>
+      </c>
+      <c r="F2285" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:30:10.839Z</t>
+        </is>
+      </c>
+      <c r="G2285" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H2285" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:24:59.489Z</t>
+        </is>
+      </c>
+      <c r="I2285" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" t="n">
+        <v>77228</v>
+      </c>
+      <c r="B2286" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2286" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D2286" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1843249, 'Longitude': -123.1236078}</t>
+        </is>
+      </c>
+      <c r="E2286" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:54:42</t>
+        </is>
+      </c>
+      <c r="F2286" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:06:09.195Z</t>
+        </is>
+      </c>
+      <c r="G2286" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H2286" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:34:11.536Z</t>
+        </is>
+      </c>
+      <c r="I2286" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" t="n">
+        <v>83384</v>
+      </c>
+      <c r="B2287" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2287" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D2287" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192001, 'Longitude': -123.124004}</t>
+        </is>
+      </c>
+      <c r="E2287" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:54:42</t>
+        </is>
+      </c>
+      <c r="F2287" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:45:08.232Z</t>
+        </is>
+      </c>
+      <c r="G2287" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="H2287" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:11:11.242Z</t>
+        </is>
+      </c>
+      <c r="I2287" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" t="n">
+        <v>77202</v>
+      </c>
+      <c r="B2288" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2288" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D2288" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.162989071149, 'Longitude': -123.134229183197}</t>
+        </is>
+      </c>
+      <c r="E2288" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:54:42</t>
+        </is>
+      </c>
+      <c r="F2288" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:09:03.542Z</t>
+        </is>
+      </c>
+      <c r="G2288" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H2288" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:38.856Z</t>
+        </is>
+      </c>
+      <c r="I2288" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" t="n">
+        <v>77243</v>
+      </c>
+      <c r="B2289" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C2289" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D2289" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.179182137142, 'Longitude': -123.137152791023}</t>
+        </is>
+      </c>
+      <c r="E2289" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:54:42</t>
+        </is>
+      </c>
+      <c r="F2289" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:34:36.670Z</t>
+        </is>
+      </c>
+      <c r="G2289" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="H2289" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:18:11.516Z</t>
+        </is>
+      </c>
+      <c r="I2289" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" t="n">
+        <v>83387</v>
+      </c>
+      <c r="B2290" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2290" t="inlineStr">
+        <is>
+          <t>710 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2290" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21081995506, 'Longitude': -123.090755939484}</t>
+        </is>
+      </c>
+      <c r="E2290" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:54:42</t>
+        </is>
+      </c>
+      <c r="F2290" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:52:22.022Z</t>
+        </is>
+      </c>
+      <c r="G2290" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="H2290" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:42:56.969Z</t>
+        </is>
+      </c>
+      <c r="I2290" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" t="n">
+        <v>65551</v>
+      </c>
+      <c r="B2291" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2291" t="inlineStr">
+        <is>
+          <t>688 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2291" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210798928329, 'Longitude': -123.09152841568}</t>
+        </is>
+      </c>
+      <c r="E2291" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:54:42</t>
+        </is>
+      </c>
+      <c r="F2291" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:52:27.993Z</t>
+        </is>
+      </c>
+      <c r="G2291" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="H2291" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:28:11.063Z</t>
+        </is>
+      </c>
+      <c r="I2291" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" t="n">
+        <v>77235</v>
+      </c>
+      <c r="B2292" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C2292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D2292" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.18409178594, 'Longitude': -123.136823830688}</t>
+        </is>
+      </c>
+      <c r="E2292" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:54:42</t>
+        </is>
+      </c>
+      <c r="F2292" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:42:15.614Z</t>
+        </is>
+      </c>
+      <c r="G2292" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="H2292" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:49:33.815Z</t>
+        </is>
+      </c>
+      <c r="I2292" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" t="n">
+        <v>82925</v>
+      </c>
+      <c r="B2293" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C2293" t="inlineStr">
+        <is>
+          <t>350 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2293" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.210245, 'Longitude': -123.099328}</t>
+        </is>
+      </c>
+      <c r="E2293" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:54:42</t>
+        </is>
+      </c>
+      <c r="F2293" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:48:49.927Z</t>
+        </is>
+      </c>
+      <c r="G2293" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="H2293" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:48:49.959Z</t>
+        </is>
+      </c>
+      <c r="I2293" t="n">
+        <v>178.9</v>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" t="n">
+        <v>109205</v>
+      </c>
+      <c r="B2294" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2294" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D2294" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.133556536531, 'Longitude': -123.092424273491}</t>
+        </is>
+      </c>
+      <c r="E2294" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:54:42</t>
+        </is>
+      </c>
+      <c r="F2294" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:28:34.945Z</t>
+        </is>
+      </c>
+      <c r="G2294" t="n">
+        <v>151.9</v>
+      </c>
+      <c r="H2294" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:26:13.953Z</t>
+        </is>
+      </c>
+      <c r="I2294" t="n">
+        <v>176.9</v>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" t="n">
+        <v>65540</v>
+      </c>
+      <c r="B2295" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2295" t="inlineStr">
+        <is>
+          <t>196 SE Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2295" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2106867, 'Longitude': -123.1027436}</t>
+        </is>
+      </c>
+      <c r="E2295" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:54:42</t>
+        </is>
+      </c>
+      <c r="F2295" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:52:47.285Z</t>
+        </is>
+      </c>
+      <c r="G2295" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H2295" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:31:31.066Z</t>
+        </is>
+      </c>
+      <c r="I2295" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" t="n">
+        <v>65512</v>
+      </c>
+      <c r="B2296" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2296" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D2296" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1328393, 'Longitude': -123.0926312}</t>
+        </is>
+      </c>
+      <c r="E2296" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:54:42</t>
+        </is>
+      </c>
+      <c r="F2296" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:28:32.580Z</t>
+        </is>
+      </c>
+      <c r="G2296" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2296" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:48:05.943Z</t>
+        </is>
+      </c>
+      <c r="I2296" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" t="n">
+        <v>77205</v>
+      </c>
+      <c r="B2297" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D2297" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1558882, 'Longitude': -123.1369625}</t>
+        </is>
+      </c>
+      <c r="E2297" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:54:42</t>
+        </is>
+      </c>
+      <c r="F2297" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:53:37.289Z</t>
+        </is>
+      </c>
+      <c r="G2297" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2297" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:09:47.598Z</t>
+        </is>
+      </c>
+      <c r="I2297" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" t="n">
+        <v>65536</v>
+      </c>
+      <c r="B2298" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2298" t="inlineStr">
+        <is>
+          <t>7309 Knight St</t>
+        </is>
+      </c>
+      <c r="D2298" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2177761, 'Longitude': -123.0775405}</t>
+        </is>
+      </c>
+      <c r="E2298" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:54:42</t>
+        </is>
+      </c>
+      <c r="F2298" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:50:29.133Z</t>
+        </is>
+      </c>
+      <c r="G2298" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2298" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:37.661Z</t>
+        </is>
+      </c>
+      <c r="I2298" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" t="n">
+        <v>86880</v>
+      </c>
+      <c r="B2299" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2299" t="inlineStr">
+        <is>
+          <t>7282 Knight St</t>
+        </is>
+      </c>
+      <c r="D2299" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.218250007984, 'Longitude': -123.076816499233}</t>
+        </is>
+      </c>
+      <c r="E2299" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:54:42</t>
+        </is>
+      </c>
+      <c r="F2299" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:50:45.909Z</t>
+        </is>
+      </c>
+      <c r="G2299" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2299" t="inlineStr">
+        <is>
+          <t>2025-08-21T07:19:57.027Z</t>
+        </is>
+      </c>
+      <c r="I2299" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" t="n">
+        <v>65556</v>
+      </c>
+      <c r="B2300" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2300" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2300" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20806537721, 'Longitude': -123.123285770416}</t>
+        </is>
+      </c>
+      <c r="E2300" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:54:42</t>
+        </is>
+      </c>
+      <c r="F2300" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:03:38.237Z</t>
+        </is>
+      </c>
+      <c r="G2300" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2300" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:46:59.765Z</t>
+        </is>
+      </c>
+      <c r="I2300" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" t="n">
+        <v>86937</v>
+      </c>
+      <c r="B2301" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2301" t="inlineStr">
+        <is>
+          <t>8655 Boundary Rd</t>
+        </is>
+      </c>
+      <c r="D2301" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20476, 'Longitude': -123.02398}</t>
+        </is>
+      </c>
+      <c r="E2301" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:54:42</t>
+        </is>
+      </c>
+      <c r="F2301" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:46:39.336Z</t>
+        </is>
+      </c>
+      <c r="G2301" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2301" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:50:23.986Z</t>
+        </is>
+      </c>
+      <c r="I2301" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" t="n">
+        <v>65515</v>
+      </c>
+      <c r="B2302" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2302" t="inlineStr">
+        <is>
+          <t>4011 Francis Rd</t>
+        </is>
+      </c>
+      <c r="D2302" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.14867500071, 'Longitude': -123.180856704712}</t>
+        </is>
+      </c>
+      <c r="E2302" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:57:15</t>
+        </is>
+      </c>
+      <c r="F2302" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:25:29.633Z</t>
+        </is>
+      </c>
+      <c r="G2302" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H2302" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:26:10.208Z</t>
+        </is>
+      </c>
+      <c r="I2302" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" t="n">
+        <v>77205</v>
+      </c>
+      <c r="B2303" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7951 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D2303" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1558882, 'Longitude': -123.1369625}</t>
+        </is>
+      </c>
+      <c r="E2303" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:57:15</t>
+        </is>
+      </c>
+      <c r="F2303" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:53:37.289Z</t>
+        </is>
+      </c>
+      <c r="G2303" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2303" t="inlineStr">
+        <is>
+          <t>2025-08-21T03:09:47.598Z</t>
+        </is>
+      </c>
+      <c r="I2303" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="2304">
+      <c r="A2304" t="n">
+        <v>77223</v>
+      </c>
+      <c r="B2304" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2304" t="inlineStr">
+        <is>
+          <t>7991 No 1 Rd</t>
+        </is>
+      </c>
+      <c r="D2304" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.155888686563, 'Longitude': -123.181414604187}</t>
+        </is>
+      </c>
+      <c r="E2304" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:57:15</t>
+        </is>
+      </c>
+      <c r="F2304" t="inlineStr"/>
+      <c r="G2304" t="inlineStr"/>
+      <c r="H2304" t="inlineStr"/>
+      <c r="I2304" t="inlineStr"/>
+    </row>
+    <row r="2305">
+      <c r="A2305" t="n">
+        <v>65514</v>
+      </c>
+      <c r="B2305" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2305" t="inlineStr">
+        <is>
+          <t>7980 Williams Rd</t>
+        </is>
+      </c>
+      <c r="D2305" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.140582914547, 'Longitude': -123.137168884277}</t>
+        </is>
+      </c>
+      <c r="E2305" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:57:15</t>
+        </is>
+      </c>
+      <c r="F2305" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:14:48.590Z</t>
+        </is>
+      </c>
+      <c r="G2305" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="H2305" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:37:13.513Z</t>
+        </is>
+      </c>
+      <c r="I2305" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="A2306" t="n">
+        <v>77232</v>
+      </c>
+      <c r="B2306" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900 Westminster Hwy </t>
+        </is>
+      </c>
+      <c r="D2306" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1698419, 'Longitude': -123.159282}</t>
+        </is>
+      </c>
+      <c r="E2306" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:57:15</t>
+        </is>
+      </c>
+      <c r="F2306" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:25:11.773Z</t>
+        </is>
+      </c>
+      <c r="G2306" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2306" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:25:11.805Z</t>
+        </is>
+      </c>
+      <c r="I2306" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" t="n">
+        <v>77202</v>
+      </c>
+      <c r="B2307" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2307" t="inlineStr">
+        <is>
+          <t>8151 Granville Ave</t>
+        </is>
+      </c>
+      <c r="D2307" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.162989071149, 'Longitude': -123.134229183197}</t>
+        </is>
+      </c>
+      <c r="E2307" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:57:15</t>
+        </is>
+      </c>
+      <c r="F2307" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:09:03.542Z</t>
+        </is>
+      </c>
+      <c r="G2307" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="H2307" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:38.856Z</t>
+        </is>
+      </c>
+      <c r="I2307" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" t="n">
+        <v>86650</v>
+      </c>
+      <c r="B2308" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2308" t="inlineStr">
+        <is>
+          <t>9100 Westminster Hwy</t>
+        </is>
+      </c>
+      <c r="D2308" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169856952787, 'Longitude': -123.123961687088}</t>
+        </is>
+      </c>
+      <c r="E2308" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:57:15</t>
+        </is>
+      </c>
+      <c r="F2308" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:53:39.660Z</t>
+        </is>
+      </c>
+      <c r="G2308" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H2308" t="inlineStr">
+        <is>
+          <t>2025-08-21T16:28:22.342Z</t>
+        </is>
+      </c>
+      <c r="I2308" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" t="n">
+        <v>77218</v>
+      </c>
+      <c r="B2309" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2309" t="inlineStr">
+        <is>
+          <t>5511 Garden City Rd</t>
+        </is>
+      </c>
+      <c r="D2309" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.173339635958, 'Longitude': -123.124954104424}</t>
+        </is>
+      </c>
+      <c r="E2309" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:57:15</t>
+        </is>
+      </c>
+      <c r="F2309" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:53:49.418Z</t>
+        </is>
+      </c>
+      <c r="G2309" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H2309" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:24:59.489Z</t>
+        </is>
+      </c>
+      <c r="I2309" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" t="n">
+        <v>77243</v>
+      </c>
+      <c r="B2310" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C2310" t="inlineStr">
+        <is>
+          <t>4651 No  3 Rd</t>
+        </is>
+      </c>
+      <c r="D2310" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.179182137142, 'Longitude': -123.137152791023}</t>
+        </is>
+      </c>
+      <c r="E2310" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:57:15</t>
+        </is>
+      </c>
+      <c r="F2310" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:34:36.670Z</t>
+        </is>
+      </c>
+      <c r="G2310" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="H2310" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:18:11.516Z</t>
+        </is>
+      </c>
+      <c r="I2310" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" t="n">
+        <v>77235</v>
+      </c>
+      <c r="B2311" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C2311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4071 No 3 Rd </t>
+        </is>
+      </c>
+      <c r="D2311" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.18409178594, 'Longitude': -123.136823830688}</t>
+        </is>
+      </c>
+      <c r="E2311" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:57:15</t>
+        </is>
+      </c>
+      <c r="F2311" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:42:15.614Z</t>
+        </is>
+      </c>
+      <c r="G2311" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="H2311" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:49:33.815Z</t>
+        </is>
+      </c>
+      <c r="I2311" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="A2312" t="n">
+        <v>77228</v>
+      </c>
+      <c r="B2312" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2312" t="inlineStr">
+        <is>
+          <t>9100 Cambie Rd</t>
+        </is>
+      </c>
+      <c r="D2312" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1843249, 'Longitude': -123.1236078}</t>
+        </is>
+      </c>
+      <c r="E2312" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:57:15</t>
+        </is>
+      </c>
+      <c r="F2312" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:06:09.195Z</t>
+        </is>
+      </c>
+      <c r="G2312" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H2312" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:34:11.536Z</t>
+        </is>
+      </c>
+      <c r="I2312" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="2313">
+      <c r="A2313" t="n">
+        <v>69163</v>
+      </c>
+      <c r="B2313" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2313" t="inlineStr">
+        <is>
+          <t>5111 Grant McConachie Way</t>
+        </is>
+      </c>
+      <c r="D2313" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192919, 'Longitude': -123.166797}</t>
+        </is>
+      </c>
+      <c r="E2313" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:57:15</t>
+        </is>
+      </c>
+      <c r="F2313" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:14:03.433Z</t>
+        </is>
+      </c>
+      <c r="G2313" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H2313" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:14:03.449Z</t>
+        </is>
+      </c>
+      <c r="I2313" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="2314">
+      <c r="A2314" t="n">
+        <v>109205</v>
+      </c>
+      <c r="B2314" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2314" t="inlineStr">
+        <is>
+          <t>11991 Steveston Hwy</t>
+        </is>
+      </c>
+      <c r="D2314" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.133556536531, 'Longitude': -123.092424273491}</t>
+        </is>
+      </c>
+      <c r="E2314" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:57:15</t>
+        </is>
+      </c>
+      <c r="F2314" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:28:34.945Z</t>
+        </is>
+      </c>
+      <c r="G2314" t="n">
+        <v>151.9</v>
+      </c>
+      <c r="H2314" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:26:13.953Z</t>
+        </is>
+      </c>
+      <c r="I2314" t="n">
+        <v>176.9</v>
+      </c>
+    </row>
+    <row r="2315">
+      <c r="A2315" t="n">
+        <v>65512</v>
+      </c>
+      <c r="B2315" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2315" t="inlineStr">
+        <is>
+          <t>11131 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D2315" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1328393, 'Longitude': -123.0926312}</t>
+        </is>
+      </c>
+      <c r="E2315" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:57:15</t>
+        </is>
+      </c>
+      <c r="F2315" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:28:32.580Z</t>
+        </is>
+      </c>
+      <c r="G2315" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2315" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:48:05.943Z</t>
+        </is>
+      </c>
+      <c r="I2315" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="2316">
+      <c r="A2316" t="n">
+        <v>83384</v>
+      </c>
+      <c r="B2316" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2316" t="inlineStr">
+        <is>
+          <t>9060 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D2316" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.192001, 'Longitude': -123.124004}</t>
+        </is>
+      </c>
+      <c r="E2316" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:57:15</t>
+        </is>
+      </c>
+      <c r="F2316" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:45:08.232Z</t>
+        </is>
+      </c>
+      <c r="G2316" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="H2316" t="inlineStr">
+        <is>
+          <t>2025-08-21T13:11:11.242Z</t>
+        </is>
+      </c>
+      <c r="I2316" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="2317">
+      <c r="A2317" t="n">
+        <v>77015</v>
+      </c>
+      <c r="B2317" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C2317" t="inlineStr">
+        <is>
+          <t>6000 No 5 Rd</t>
+        </is>
+      </c>
+      <c r="D2317" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.169873456637, 'Longitude': -123.091178619746}</t>
+        </is>
+      </c>
+      <c r="E2317" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:57:15</t>
+        </is>
+      </c>
+      <c r="F2317" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:51:08.322Z</t>
+        </is>
+      </c>
+      <c r="G2317" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="H2317" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:30:39.668Z</t>
+        </is>
+      </c>
+      <c r="I2317" t="n">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="2318">
+      <c r="A2318" t="n">
+        <v>107728</v>
+      </c>
+      <c r="B2318" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2318" t="inlineStr">
+        <is>
+          <t>8884 Granville St</t>
+        </is>
+      </c>
+      <c r="D2318" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2054215, 'Longitude': -123.1401677}</t>
+        </is>
+      </c>
+      <c r="E2318" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:57:15</t>
+        </is>
+      </c>
+      <c r="F2318" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:27:50.787Z</t>
+        </is>
+      </c>
+      <c r="G2318" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2318" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:50:11.686Z</t>
+        </is>
+      </c>
+      <c r="I2318" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="2319">
+      <c r="A2319" t="n">
+        <v>65572</v>
+      </c>
+      <c r="B2319" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2319" t="inlineStr">
+        <is>
+          <t>8686 Granville St</t>
+        </is>
+      </c>
+      <c r="D2319" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.207280329467, 'Longitude': -123.140280246735}</t>
+        </is>
+      </c>
+      <c r="E2319" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:57:15</t>
+        </is>
+      </c>
+      <c r="F2319" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:15:25.202Z</t>
+        </is>
+      </c>
+      <c r="G2319" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2319" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:50:22.600Z</t>
+        </is>
+      </c>
+      <c r="I2319" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="2320">
+      <c r="A2320" t="n">
+        <v>65511</v>
+      </c>
+      <c r="B2320" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2320" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12011 Bridgeport Rd</t>
+        </is>
+      </c>
+      <c r="D2320" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.1923857, 'Longitude': -123.0911072}</t>
+        </is>
+      </c>
+      <c r="E2320" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:57:15</t>
+        </is>
+      </c>
+      <c r="F2320" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:03:07.680Z</t>
+        </is>
+      </c>
+      <c r="G2320" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2320" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:06:39.475Z</t>
+        </is>
+      </c>
+      <c r="I2320" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="2321">
+      <c r="A2321" t="n">
+        <v>65556</v>
+      </c>
+      <c r="B2321" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2321" t="inlineStr">
+        <is>
+          <t>709 SW Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2321" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.20806537721, 'Longitude': -123.123285770416}</t>
+        </is>
+      </c>
+      <c r="E2321" t="inlineStr">
+        <is>
+          <t>2025-08-21 20:57:15</t>
+        </is>
+      </c>
+      <c r="F2321" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:03:38.237Z</t>
+        </is>
+      </c>
+      <c r="G2321" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="H2321" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:46:59.765Z</t>
+        </is>
+      </c>
+      <c r="I2321" t="n">
+        <v>179.9</v>
+      </c>
+    </row>
+    <row r="2322">
+      <c r="A2322" t="n">
+        <v>32378</v>
+      </c>
+      <c r="B2322" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2322" t="inlineStr">
+        <is>
+          <t>1613 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2322" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3288556, 'Longitude': -123.1592779}</t>
+        </is>
+      </c>
+      <c r="E2322" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:00:02</t>
+        </is>
+      </c>
+      <c r="F2322" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:23:48.032Z</t>
+        </is>
+      </c>
+      <c r="G2322" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2322" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:23:48.047Z</t>
+        </is>
+      </c>
+      <c r="I2322" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="2323">
+      <c r="A2323" t="n">
+        <v>98624</v>
+      </c>
+      <c r="B2323" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2323" t="inlineStr">
+        <is>
+          <t>1503 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2323" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.328484, 'Longitude': -123.15694}</t>
+        </is>
+      </c>
+      <c r="E2323" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:00:02</t>
+        </is>
+      </c>
+      <c r="F2323" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:35:39.741Z</t>
+        </is>
+      </c>
+      <c r="G2323" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2323" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:31:37.975Z</t>
+        </is>
+      </c>
+      <c r="I2323" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="2324">
+      <c r="A2324" t="n">
+        <v>98626</v>
+      </c>
+      <c r="B2324" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2324" t="inlineStr">
+        <is>
+          <t>1490 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2324" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.328176303121, 'Longitude': -123.1565746665}</t>
+        </is>
+      </c>
+      <c r="E2324" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:00:02</t>
+        </is>
+      </c>
+      <c r="F2324" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:49:48.536Z</t>
+        </is>
+      </c>
+      <c r="G2324" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2324" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:52:54.859Z</t>
+        </is>
+      </c>
+      <c r="I2324" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="2325">
+      <c r="A2325" t="n">
+        <v>65575</v>
+      </c>
+      <c r="B2325" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2325" t="inlineStr">
+        <is>
+          <t>1305 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2325" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.327918987512, 'Longitude': -123.151953220367}</t>
+        </is>
+      </c>
+      <c r="E2325" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:00:02</t>
+        </is>
+      </c>
+      <c r="F2325" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:36:41.431Z</t>
+        </is>
+      </c>
+      <c r="G2325" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2325" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:53:04.130Z</t>
+        </is>
+      </c>
+      <c r="I2325" t="n">
+        <v>197.9</v>
+      </c>
+    </row>
+    <row r="2326">
+      <c r="A2326" t="n">
+        <v>65505</v>
+      </c>
+      <c r="B2326" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2326" t="inlineStr">
+        <is>
+          <t>1731 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D2326" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.325583506404, 'Longitude': -123.121590614319}</t>
+        </is>
+      </c>
+      <c r="E2326" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:00:02</t>
+        </is>
+      </c>
+      <c r="F2326" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:20.984Z</t>
+        </is>
+      </c>
+      <c r="G2326" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2326" t="inlineStr"/>
+      <c r="I2326" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2327">
+      <c r="A2327" t="n">
+        <v>65503</v>
+      </c>
+      <c r="B2327" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2327" t="inlineStr">
+        <is>
+          <t>1980 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2327" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.324534601594, 'Longitude': -123.121654987335}</t>
+        </is>
+      </c>
+      <c r="E2327" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:00:02</t>
+        </is>
+      </c>
+      <c r="F2327" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:03.926Z</t>
+        </is>
+      </c>
+      <c r="G2327" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2327" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:33:50.835Z</t>
+        </is>
+      </c>
+      <c r="I2327" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="2328">
+      <c r="A2328" t="n">
+        <v>75407</v>
+      </c>
+      <c r="B2328" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2328" t="inlineStr">
+        <is>
+          <t>2698 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D2328" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3343054, 'Longitude': -123.1157865}</t>
+        </is>
+      </c>
+      <c r="E2328" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:00:02</t>
+        </is>
+      </c>
+      <c r="F2328" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:34:17.217Z</t>
+        </is>
+      </c>
+      <c r="G2328" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2328" t="inlineStr"/>
+      <c r="I2328" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2329">
+      <c r="A2329" t="n">
+        <v>75406</v>
+      </c>
+      <c r="B2329" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2329" t="inlineStr">
+        <is>
+          <t>1198 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2329" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.323975176559, 'Longitude': -123.107525110245}</t>
+        </is>
+      </c>
+      <c r="E2329" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:00:02</t>
+        </is>
+      </c>
+      <c r="F2329" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:02:12.531Z</t>
+        </is>
+      </c>
+      <c r="G2329" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2329" t="inlineStr"/>
+      <c r="I2329" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2330">
+      <c r="A2330" t="n">
+        <v>75409</v>
+      </c>
+      <c r="B2330" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2330" t="inlineStr">
+        <is>
+          <t>3150 Edgemont Blvd</t>
+        </is>
+      </c>
+      <c r="D2330" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.338128, 'Longitude': -123.1021338}</t>
+        </is>
+      </c>
+      <c r="E2330" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:00:02</t>
+        </is>
+      </c>
+      <c r="F2330" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:36:44.148Z</t>
+        </is>
+      </c>
+      <c r="G2330" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2330" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:36:44.179Z</t>
+        </is>
+      </c>
+      <c r="I2330" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="2331">
+      <c r="A2331" t="n">
+        <v>98622</v>
+      </c>
+      <c r="B2331" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2331" t="inlineStr">
+        <is>
+          <t>3690 Westmount Rd</t>
+        </is>
+      </c>
+      <c r="D2331" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3459143, 'Longitude': -123.2177286}</t>
+        </is>
+      </c>
+      <c r="E2331" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:00:02</t>
+        </is>
+      </c>
+      <c r="F2331" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:24:35.951Z</t>
+        </is>
+      </c>
+      <c r="G2331" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2331" t="inlineStr">
+        <is>
+          <t>2025-08-19T22:08:16.374Z</t>
+        </is>
+      </c>
+      <c r="I2331" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="2332">
+      <c r="A2332" t="n">
+        <v>18803</v>
+      </c>
+      <c r="B2332" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2332" t="inlineStr">
+        <is>
+          <t>2501 Westview Dr</t>
+        </is>
+      </c>
+      <c r="D2332" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.332617583893, 'Longitude': -123.088846206665}</t>
+        </is>
+      </c>
+      <c r="E2332" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:00:02</t>
+        </is>
+      </c>
+      <c r="F2332" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:42:47.743Z</t>
+        </is>
+      </c>
+      <c r="G2332" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2332" t="inlineStr"/>
+      <c r="I2332" t="inlineStr"/>
+    </row>
+    <row r="2333">
+      <c r="A2333" t="n">
+        <v>18804</v>
+      </c>
+      <c r="B2333" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2333" t="inlineStr">
+        <is>
+          <t>660 3rd St  W</t>
+        </is>
+      </c>
+      <c r="D2333" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319671, 'Longitude': -123.0902808}</t>
+        </is>
+      </c>
+      <c r="E2333" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:00:02</t>
+        </is>
+      </c>
+      <c r="F2333" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:16:49.201Z</t>
+        </is>
+      </c>
+      <c r="G2333" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2333" t="inlineStr"/>
+      <c r="I2333" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2334">
+      <c r="A2334" t="n">
+        <v>32349</v>
+      </c>
+      <c r="B2334" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2334" t="inlineStr">
+        <is>
+          <t>106 W Queens St</t>
+        </is>
+      </c>
+      <c r="D2334" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.336724992343, 'Longitude': -123.072506189346}</t>
+        </is>
+      </c>
+      <c r="E2334" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:00:02</t>
+        </is>
+      </c>
+      <c r="F2334" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:47:52.962Z</t>
+        </is>
+      </c>
+      <c r="G2334" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2334" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:04:13.955Z</t>
+        </is>
+      </c>
+      <c r="I2334" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="2335">
+      <c r="A2335" t="n">
+        <v>18509</v>
+      </c>
+      <c r="B2335" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2335" t="inlineStr">
+        <is>
+          <t>2305 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D2335" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3306729, 'Longitude': -123.0728536}</t>
+        </is>
+      </c>
+      <c r="E2335" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:00:02</t>
+        </is>
+      </c>
+      <c r="F2335" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:36:28.622Z</t>
+        </is>
+      </c>
+      <c r="G2335" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2335" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:21:46.014Z</t>
+        </is>
+      </c>
+      <c r="I2335" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="2336">
+      <c r="A2336" t="n">
+        <v>22117</v>
+      </c>
+      <c r="B2336" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2336" t="inlineStr">
+        <is>
+          <t>1245 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D2336" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319695364751, 'Longitude': -123.07279586792}</t>
+        </is>
+      </c>
+      <c r="E2336" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:00:02</t>
+        </is>
+      </c>
+      <c r="F2336" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:38:20.818Z</t>
+        </is>
+      </c>
+      <c r="G2336" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2336" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:38:20.872Z</t>
+        </is>
+      </c>
+      <c r="I2336" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="2337">
+      <c r="A2337" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B2337" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2337" t="inlineStr">
+        <is>
+          <t>1205 Burrard St</t>
+        </is>
+      </c>
+      <c r="D2337" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.279145231489, 'Longitude': -123.12982365489}</t>
+        </is>
+      </c>
+      <c r="E2337" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:00:02</t>
+        </is>
+      </c>
+      <c r="F2337" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:49:20.616Z</t>
+        </is>
+      </c>
+      <c r="G2337" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2337" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:49:01.374Z</t>
+        </is>
+      </c>
+      <c r="I2337" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="2338">
+      <c r="A2338" t="n">
+        <v>65563</v>
+      </c>
+      <c r="B2338" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2338" t="inlineStr">
+        <is>
+          <t>1743 Burrard St</t>
+        </is>
+      </c>
+      <c r="D2338" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.270429790667, 'Longitude': -123.145886063576}</t>
+        </is>
+      </c>
+      <c r="E2338" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:00:02</t>
+        </is>
+      </c>
+      <c r="F2338" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:28:51.238Z</t>
+        </is>
+      </c>
+      <c r="G2338" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H2338" t="inlineStr">
+        <is>
+          <t>2025-08-20T23:25:11.555Z</t>
+        </is>
+      </c>
+      <c r="I2338" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="2339">
+      <c r="A2339" t="n">
+        <v>65543</v>
+      </c>
+      <c r="B2339" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2339" t="inlineStr">
+        <is>
+          <t>1900 Burrard St</t>
+        </is>
+      </c>
+      <c r="D2339" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2685375, 'Longitude': -123.1453067}</t>
+        </is>
+      </c>
+      <c r="E2339" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:00:02</t>
+        </is>
+      </c>
+      <c r="F2339" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:46:17.762Z</t>
+        </is>
+      </c>
+      <c r="G2339" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2339" t="inlineStr">
+        <is>
+          <t>2025-08-21T19:46:17.794Z</t>
+        </is>
+      </c>
+      <c r="I2339" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="2340">
+      <c r="A2340" t="n">
+        <v>65565</v>
+      </c>
+      <c r="B2340" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2340" t="inlineStr">
+        <is>
+          <t>1896 W 4th Ave</t>
+        </is>
+      </c>
+      <c r="D2340" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.267881559667, 'Longitude': -123.14772605896}</t>
+        </is>
+      </c>
+      <c r="E2340" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:00:02</t>
+        </is>
+      </c>
+      <c r="F2340" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:23:16.373Z</t>
+        </is>
+      </c>
+      <c r="G2340" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2340" t="inlineStr"/>
+      <c r="I2340" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2341">
+      <c r="A2341" t="n">
+        <v>65570</v>
+      </c>
+      <c r="B2341" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2341" t="inlineStr">
+        <is>
+          <t>2103 W Broadway</t>
+        </is>
+      </c>
+      <c r="D2341" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.264135981257, 'Longitude': -123.153326511383}</t>
+        </is>
+      </c>
+      <c r="E2341" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:00:02</t>
+        </is>
+      </c>
+      <c r="F2341" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:03:50.343Z</t>
+        </is>
+      </c>
+      <c r="G2341" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H2341" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:51:32.975Z</t>
+        </is>
+      </c>
+      <c r="I2341" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="2342">
+      <c r="A2342" t="n">
+        <v>18509</v>
+      </c>
+      <c r="B2342" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2342" t="inlineStr">
+        <is>
+          <t>2305 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D2342" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3306729, 'Longitude': -123.0728536}</t>
+        </is>
+      </c>
+      <c r="E2342" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:02:49</t>
+        </is>
+      </c>
+      <c r="F2342" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:36:28.622Z</t>
+        </is>
+      </c>
+      <c r="G2342" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2342" t="inlineStr">
+        <is>
+          <t>2025-08-21T14:21:46.014Z</t>
+        </is>
+      </c>
+      <c r="I2342" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="2343">
+      <c r="A2343" t="n">
+        <v>22117</v>
+      </c>
+      <c r="B2343" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2343" t="inlineStr">
+        <is>
+          <t>1245 Lonsdale Ave</t>
+        </is>
+      </c>
+      <c r="D2343" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319695364751, 'Longitude': -123.07279586792}</t>
+        </is>
+      </c>
+      <c r="E2343" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:02:49</t>
+        </is>
+      </c>
+      <c r="F2343" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:38:20.818Z</t>
+        </is>
+      </c>
+      <c r="G2343" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2343" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:38:20.872Z</t>
+        </is>
+      </c>
+      <c r="I2343" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="2344">
+      <c r="A2344" t="n">
+        <v>32349</v>
+      </c>
+      <c r="B2344" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2344" t="inlineStr">
+        <is>
+          <t>106 W Queens St</t>
+        </is>
+      </c>
+      <c r="D2344" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.336724992343, 'Longitude': -123.072506189346}</t>
+        </is>
+      </c>
+      <c r="E2344" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:02:49</t>
+        </is>
+      </c>
+      <c r="F2344" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:47:52.962Z</t>
+        </is>
+      </c>
+      <c r="G2344" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2344" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:04:13.955Z</t>
+        </is>
+      </c>
+      <c r="I2344" t="n">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="2345">
+      <c r="A2345" t="n">
+        <v>18803</v>
+      </c>
+      <c r="B2345" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2345" t="inlineStr">
+        <is>
+          <t>2501 Westview Dr</t>
+        </is>
+      </c>
+      <c r="D2345" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.332617583893, 'Longitude': -123.088846206665}</t>
+        </is>
+      </c>
+      <c r="E2345" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:02:49</t>
+        </is>
+      </c>
+      <c r="F2345" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:42:47.743Z</t>
+        </is>
+      </c>
+      <c r="G2345" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2345" t="inlineStr"/>
+      <c r="I2345" t="inlineStr"/>
+    </row>
+    <row r="2346">
+      <c r="A2346" t="n">
+        <v>18804</v>
+      </c>
+      <c r="B2346" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2346" t="inlineStr">
+        <is>
+          <t>660 3rd St  W</t>
+        </is>
+      </c>
+      <c r="D2346" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.319671, 'Longitude': -123.0902808}</t>
+        </is>
+      </c>
+      <c r="E2346" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:02:49</t>
+        </is>
+      </c>
+      <c r="F2346" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:16:49.201Z</t>
+        </is>
+      </c>
+      <c r="G2346" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2346" t="inlineStr"/>
+      <c r="I2346" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2347">
+      <c r="A2347" t="n">
+        <v>75409</v>
+      </c>
+      <c r="B2347" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2347" t="inlineStr">
+        <is>
+          <t>3150 Edgemont Blvd</t>
+        </is>
+      </c>
+      <c r="D2347" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.338128, 'Longitude': -123.1021338}</t>
+        </is>
+      </c>
+      <c r="E2347" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:02:49</t>
+        </is>
+      </c>
+      <c r="F2347" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:36:44.148Z</t>
+        </is>
+      </c>
+      <c r="G2347" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2347" t="inlineStr">
+        <is>
+          <t>2025-08-21T18:36:44.179Z</t>
+        </is>
+      </c>
+      <c r="I2347" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="2348">
+      <c r="A2348" t="n">
+        <v>75406</v>
+      </c>
+      <c r="B2348" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2348" t="inlineStr">
+        <is>
+          <t>1198 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2348" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.323975176559, 'Longitude': -123.107525110245}</t>
+        </is>
+      </c>
+      <c r="E2348" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:02:49</t>
+        </is>
+      </c>
+      <c r="F2348" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:02:12.531Z</t>
+        </is>
+      </c>
+      <c r="G2348" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2348" t="inlineStr"/>
+      <c r="I2348" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2349">
+      <c r="A2349" t="n">
+        <v>18512</v>
+      </c>
+      <c r="B2349" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2349" t="inlineStr">
+        <is>
+          <t>2747 Mountain Hwy</t>
+        </is>
+      </c>
+      <c r="D2349" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.333694, 'Longitude': -123.038315}</t>
+        </is>
+      </c>
+      <c r="E2349" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:02:49</t>
+        </is>
+      </c>
+      <c r="F2349" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:54:07.553Z</t>
+        </is>
+      </c>
+      <c r="G2349" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2349" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:54:07.584Z</t>
+        </is>
+      </c>
+      <c r="I2349" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="2350">
+      <c r="A2350" t="n">
+        <v>9706</v>
+      </c>
+      <c r="B2350" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2350" t="inlineStr">
+        <is>
+          <t>2979 Mountain Hwy</t>
+        </is>
+      </c>
+      <c r="D2350" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3356515, 'Longitude': -123.038272}</t>
+        </is>
+      </c>
+      <c r="E2350" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:02:49</t>
+        </is>
+      </c>
+      <c r="F2350" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:54:33.680Z</t>
+        </is>
+      </c>
+      <c r="G2350" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2350" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:54:33.711Z</t>
+        </is>
+      </c>
+      <c r="I2350" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="2351">
+      <c r="A2351" t="n">
+        <v>32289</v>
+      </c>
+      <c r="B2351" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2351" t="inlineStr">
+        <is>
+          <t>1270 Lynn Valley Rd</t>
+        </is>
+      </c>
+      <c r="D2351" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.337231840266, 'Longitude': -123.038763999939}</t>
+        </is>
+      </c>
+      <c r="E2351" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:02:49</t>
+        </is>
+      </c>
+      <c r="F2351" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:39.253Z</t>
+        </is>
+      </c>
+      <c r="G2351" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2351" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:39.297Z</t>
+        </is>
+      </c>
+      <c r="I2351" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="2352">
+      <c r="A2352" t="n">
+        <v>75407</v>
+      </c>
+      <c r="B2352" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2352" t="inlineStr">
+        <is>
+          <t>2698 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D2352" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3343054, 'Longitude': -123.1157865}</t>
+        </is>
+      </c>
+      <c r="E2352" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:02:49</t>
+        </is>
+      </c>
+      <c r="F2352" t="inlineStr">
+        <is>
+          <t>2025-08-21T21:34:17.217Z</t>
+        </is>
+      </c>
+      <c r="G2352" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2352" t="inlineStr"/>
+      <c r="I2352" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2353">
+      <c r="A2353" t="n">
+        <v>65505</v>
+      </c>
+      <c r="B2353" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2353" t="inlineStr">
+        <is>
+          <t>1731 Capilano Rd</t>
+        </is>
+      </c>
+      <c r="D2353" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.325583506404, 'Longitude': -123.121590614319}</t>
+        </is>
+      </c>
+      <c r="E2353" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:02:49</t>
+        </is>
+      </c>
+      <c r="F2353" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:20.984Z</t>
+        </is>
+      </c>
+      <c r="G2353" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2353" t="inlineStr"/>
+      <c r="I2353" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2354">
+      <c r="A2354" t="n">
+        <v>65503</v>
+      </c>
+      <c r="B2354" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2354" t="inlineStr">
+        <is>
+          <t>1980 Marine Dr</t>
+        </is>
+      </c>
+      <c r="D2354" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.324534601594, 'Longitude': -123.121654987335}</t>
+        </is>
+      </c>
+      <c r="E2354" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:02:49</t>
+        </is>
+      </c>
+      <c r="F2354" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:03.926Z</t>
+        </is>
+      </c>
+      <c r="G2354" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2354" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:33:50.835Z</t>
+        </is>
+      </c>
+      <c r="I2354" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="2355">
+      <c r="A2355" t="n">
+        <v>18510</v>
+      </c>
+      <c r="B2355" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2355" t="inlineStr">
+        <is>
+          <t>1490 Main St</t>
+        </is>
+      </c>
+      <c r="D2355" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.3057944, 'Longitude': -123.0328688}</t>
+        </is>
+      </c>
+      <c r="E2355" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:02:49</t>
+        </is>
+      </c>
+      <c r="F2355" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:48:58.430Z</t>
+        </is>
+      </c>
+      <c r="G2355" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2355" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:52:25.183Z</t>
+        </is>
+      </c>
+      <c r="I2355" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="2356">
+      <c r="A2356" t="n">
+        <v>69296</v>
+      </c>
+      <c r="B2356" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185 Mountain Hwy </t>
+        </is>
+      </c>
+      <c r="D2356" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.305048881232, 'Longitude': -123.0324447155}</t>
+        </is>
+      </c>
+      <c r="E2356" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:02:49</t>
+        </is>
+      </c>
+      <c r="F2356" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:49:08.129Z</t>
+        </is>
+      </c>
+      <c r="G2356" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2356" t="inlineStr">
+        <is>
+          <t>2025-08-22T01:52:45.908Z</t>
+        </is>
+      </c>
+      <c r="I2356" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="2357">
+      <c r="A2357" t="n">
+        <v>65506</v>
+      </c>
+      <c r="B2357" t="inlineStr">
+        <is>
+          <t>Mobil</t>
+        </is>
+      </c>
+      <c r="C2357" t="inlineStr">
+        <is>
+          <t>333 Seymour Blvd</t>
+        </is>
+      </c>
+      <c r="D2357" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.311498347051, 'Longitude': -123.022198677063}</t>
+        </is>
+      </c>
+      <c r="E2357" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:02:49</t>
+        </is>
+      </c>
+      <c r="F2357" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:02:17.275Z</t>
+        </is>
+      </c>
+      <c r="G2357" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2357" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:02:17.291Z</t>
+        </is>
+      </c>
+      <c r="I2357" t="n">
+        <v>186.9</v>
+      </c>
+    </row>
+    <row r="2358">
+      <c r="A2358" t="n">
+        <v>98513</v>
+      </c>
+      <c r="B2358" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2358" t="inlineStr">
+        <is>
+          <t>1955 Powell St</t>
+        </is>
+      </c>
+      <c r="D2358" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.28504, 'Longitude': -123.0643977}</t>
+        </is>
+      </c>
+      <c r="E2358" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:02:49</t>
+        </is>
+      </c>
+      <c r="F2358" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:25:30.530Z</t>
+        </is>
+      </c>
+      <c r="G2358" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2358" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:07:30.259Z</t>
+        </is>
+      </c>
+      <c r="I2358" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="2359">
+      <c r="A2359" t="n">
+        <v>75410</v>
+      </c>
+      <c r="B2359" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2359" t="inlineStr">
+        <is>
+          <t>2177 Dollarton Hwy</t>
+        </is>
+      </c>
+      <c r="D2359" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.305160809746, 'Longitude': -123.014302253723}</t>
+        </is>
+      </c>
+      <c r="E2359" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:02:49</t>
+        </is>
+      </c>
+      <c r="F2359" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:04:14.448Z</t>
+        </is>
+      </c>
+      <c r="G2359" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2359" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:40:56.005Z</t>
+        </is>
+      </c>
+      <c r="I2359" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="2360">
+      <c r="A2360" t="n">
+        <v>65546</v>
+      </c>
+      <c r="B2360" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2360" t="inlineStr">
+        <is>
+          <t>1212 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D2360" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2809987, 'Longitude': -123.0786929}</t>
+        </is>
+      </c>
+      <c r="E2360" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:02:49</t>
+        </is>
+      </c>
+      <c r="F2360" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:25:34.430Z</t>
+        </is>
+      </c>
+      <c r="G2360" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2360" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:09:51.728Z</t>
+        </is>
+      </c>
+      <c r="I2360" t="n">
+        <v>190.9</v>
+      </c>
+    </row>
+    <row r="2361">
+      <c r="A2361" t="n">
+        <v>98515</v>
+      </c>
+      <c r="B2361" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2361" t="inlineStr">
+        <is>
+          <t>1896 E Hastings St</t>
+        </is>
+      </c>
+      <c r="D2361" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.281018940561, 'Longitude': -123.065712153912}</t>
+        </is>
+      </c>
+      <c r="E2361" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:02:49</t>
+        </is>
+      </c>
+      <c r="F2361" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:35:03.001Z</t>
+        </is>
+      </c>
+      <c r="G2361" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="H2361" t="inlineStr">
+        <is>
+          <t>2025-08-20T07:10:51.610Z</t>
+        </is>
+      </c>
+      <c r="I2361" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="2362">
+      <c r="A2362" t="inlineStr">
+        <is>
+          <t>65480</t>
+        </is>
+      </c>
+      <c r="B2362" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C2362" t="inlineStr">
+        <is>
+          <t>6591 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2362" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21925095319, 'Longitude': -122.968211174011}</t>
+        </is>
+      </c>
+      <c r="E2362" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:05:52</t>
+        </is>
+      </c>
+      <c r="F2362" t="inlineStr">
+        <is>
+          <t>2025-08-22T04:02:44.999Z</t>
+        </is>
+      </c>
+      <c r="G2362" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H2362" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:25:44.411Z</t>
+        </is>
+      </c>
+      <c r="I2362" t="n">
+        <v>180.9</v>
+      </c>
+    </row>
+    <row r="2363">
+      <c r="A2363" t="inlineStr">
+        <is>
+          <t>65467</t>
+        </is>
+      </c>
+      <c r="B2363" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2363" t="inlineStr">
+        <is>
+          <t>6138 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2363" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2201556, 'Longitude': -122.9743751}</t>
+        </is>
+      </c>
+      <c r="E2363" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:05:52</t>
+        </is>
+      </c>
+      <c r="F2363" t="inlineStr">
+        <is>
+          <t>2025-08-22T04:00:11.705Z</t>
+        </is>
+      </c>
+      <c r="G2363" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2363" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:10:44.178Z</t>
+        </is>
+      </c>
+      <c r="I2363" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="2364">
+      <c r="A2364" t="inlineStr">
+        <is>
+          <t>119589</t>
+        </is>
+      </c>
+      <c r="B2364" t="inlineStr">
+        <is>
+          <t>Smart Gas</t>
+        </is>
+      </c>
+      <c r="C2364" t="inlineStr">
+        <is>
+          <t>6869 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2364" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.226505740129, 'Longitude': -122.944511175156}</t>
+        </is>
+      </c>
+      <c r="E2364" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:05:52</t>
+        </is>
+      </c>
+      <c r="F2364" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:09:26.720Z</t>
+        </is>
+      </c>
+      <c r="G2364" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2364" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:03.731Z</t>
+        </is>
+      </c>
+      <c r="I2364" t="n">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="2365">
+      <c r="A2365" t="inlineStr">
+        <is>
+          <t>65474</t>
+        </is>
+      </c>
+      <c r="B2365" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2365" t="inlineStr">
+        <is>
+          <t>7274 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2365" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2244118, 'Longitude': -122.9410264}</t>
+        </is>
+      </c>
+      <c r="E2365" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:05:52</t>
+        </is>
+      </c>
+      <c r="F2365" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:51:05.186Z</t>
+        </is>
+      </c>
+      <c r="G2365" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2365" t="inlineStr">
+        <is>
+          <t>2025-08-21T06:24:59.321Z</t>
+        </is>
+      </c>
+      <c r="I2365" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="2366">
+      <c r="A2366" t="inlineStr">
+        <is>
+          <t>87633</t>
+        </is>
+      </c>
+      <c r="B2366" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C2366" t="inlineStr">
+        <is>
+          <t>5608 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2366" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.222913, 'Longitude': -122.982433}</t>
+        </is>
+      </c>
+      <c r="E2366" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:05:52</t>
+        </is>
+      </c>
+      <c r="F2366" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:58:48.040Z</t>
+        </is>
+      </c>
+      <c r="G2366" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H2366" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:29:55.698Z</t>
+        </is>
+      </c>
+      <c r="I2366" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="2367">
+      <c r="A2367" t="inlineStr">
+        <is>
+          <t>65481</t>
+        </is>
+      </c>
+      <c r="B2367" t="inlineStr">
+        <is>
+          <t>Super Save Gas</t>
+        </is>
+      </c>
+      <c r="C2367" t="inlineStr">
+        <is>
+          <t>7377 6th St</t>
+        </is>
+      </c>
+      <c r="D2367" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.225214157435, 'Longitude': -122.935831546783}</t>
+        </is>
+      </c>
+      <c r="E2367" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:05:52</t>
+        </is>
+      </c>
+      <c r="F2367" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:52:54.529Z</t>
+        </is>
+      </c>
+      <c r="G2367" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H2367" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:52:54.544Z</t>
+        </is>
+      </c>
+      <c r="I2367" t="n">
+        <v>182.9</v>
+      </c>
+    </row>
+    <row r="2368">
+      <c r="A2368" t="inlineStr">
+        <is>
+          <t>65477</t>
+        </is>
+      </c>
+      <c r="B2368" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2368" t="inlineStr">
+        <is>
+          <t>7890 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2368" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.217246706543, 'Longitude': -122.931432723999}</t>
+        </is>
+      </c>
+      <c r="E2368" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:05:52</t>
+        </is>
+      </c>
+      <c r="F2368" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:09:15.340Z</t>
+        </is>
+      </c>
+      <c r="G2368" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2368" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:09:15.373Z</t>
+        </is>
+      </c>
+      <c r="I2368" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="2369">
+      <c r="A2369" t="inlineStr">
+        <is>
+          <t>65468</t>
+        </is>
+      </c>
+      <c r="B2369" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2369" t="inlineStr">
+        <is>
+          <t>7587 Royal Oak Ave</t>
+        </is>
+      </c>
+      <c r="D2369" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2151443, 'Longitude': -122.9890903}</t>
+        </is>
+      </c>
+      <c r="E2369" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:05:52</t>
+        </is>
+      </c>
+      <c r="F2369" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:59.619Z</t>
+        </is>
+      </c>
+      <c r="G2369" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2369" t="inlineStr">
+        <is>
+          <t>2025-08-21T15:29:20.166Z</t>
+        </is>
+      </c>
+      <c r="I2369" t="n">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="2370">
+      <c r="A2370" t="inlineStr">
+        <is>
+          <t>65471</t>
+        </is>
+      </c>
+      <c r="B2370" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2370" t="inlineStr">
+        <is>
+          <t>5059 Canada Way</t>
+        </is>
+      </c>
+      <c r="D2370" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.239569143746, 'Longitude': -122.96440243721}</t>
+        </is>
+      </c>
+      <c r="E2370" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:05:52</t>
+        </is>
+      </c>
+      <c r="F2370" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:03:48.358Z</t>
+        </is>
+      </c>
+      <c r="G2370" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="H2370" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:03:48.389Z</t>
+        </is>
+      </c>
+      <c r="I2370" t="n">
+        <v>194.9</v>
+      </c>
+    </row>
+    <row r="2371">
+      <c r="A2371" t="inlineStr">
+        <is>
+          <t>5768</t>
+        </is>
+      </c>
+      <c r="B2371" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2371" t="inlineStr">
+        <is>
+          <t>5009 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2371" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2264629, 'Longitude': -122.992576}</t>
+        </is>
+      </c>
+      <c r="E2371" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:05:52</t>
+        </is>
+      </c>
+      <c r="F2371" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:58:00.233Z</t>
+        </is>
+      </c>
+      <c r="G2371" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2371" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:44:31.280Z</t>
+        </is>
+      </c>
+      <c r="I2371" t="n">
+        <v>185.9</v>
+      </c>
+    </row>
+    <row r="2372">
+      <c r="A2372" t="inlineStr">
+        <is>
+          <t>111740</t>
+        </is>
+      </c>
+      <c r="B2372" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2372" t="inlineStr">
+        <is>
+          <t>780 6th St</t>
+        </is>
+      </c>
+      <c r="D2372" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21557, 'Longitude': -122.92387}</t>
+        </is>
+      </c>
+      <c r="E2372" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:05:52</t>
+        </is>
+      </c>
+      <c r="F2372" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:09:24.586Z</t>
+        </is>
+      </c>
+      <c r="G2372" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="H2372" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:09:24.679Z</t>
+        </is>
+      </c>
+      <c r="I2372" t="n">
+        <v>192.9</v>
+      </c>
+    </row>
+    <row r="2373">
+      <c r="A2373" t="inlineStr">
+        <is>
+          <t>65469</t>
+        </is>
+      </c>
+      <c r="B2373" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2373" t="inlineStr">
+        <is>
+          <t>4692 Imperial St</t>
+        </is>
+      </c>
+      <c r="D2373" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2217244, 'Longitude': -122.9980797}</t>
+        </is>
+      </c>
+      <c r="E2373" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:05:52</t>
+        </is>
+      </c>
+      <c r="F2373" t="inlineStr">
+        <is>
+          <t>2025-08-22T02:04:25.698Z</t>
+        </is>
+      </c>
+      <c r="G2373" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2373" t="inlineStr">
+        <is>
+          <t>2025-08-20T22:58:12.777Z</t>
+        </is>
+      </c>
+      <c r="I2373" t="n">
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="2374">
+      <c r="A2374" t="inlineStr">
+        <is>
+          <t>65499</t>
+        </is>
+      </c>
+      <c r="B2374" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2374" t="inlineStr">
+        <is>
+          <t>736 Sixth Ave</t>
+        </is>
+      </c>
+      <c r="D2374" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.21129, 'Longitude': -122.92333}</t>
+        </is>
+      </c>
+      <c r="E2374" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:05:52</t>
+        </is>
+      </c>
+      <c r="F2374" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:19.310Z</t>
+        </is>
+      </c>
+      <c r="G2374" t="n">
+        <v>164.6</v>
+      </c>
+      <c r="H2374" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:19.329Z</t>
+        </is>
+      </c>
+      <c r="I2374" t="n">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="2375">
+      <c r="A2375" t="inlineStr">
+        <is>
+          <t>65497</t>
+        </is>
+      </c>
+      <c r="B2375" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2375" t="inlineStr">
+        <is>
+          <t>428 Sixth St</t>
+        </is>
+      </c>
+      <c r="D2375" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2109656, 'Longitude': -122.9179526}</t>
+        </is>
+      </c>
+      <c r="E2375" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:05:52</t>
+        </is>
+      </c>
+      <c r="F2375" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:24.583Z</t>
+        </is>
+      </c>
+      <c r="G2375" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="H2375" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:32:24.614Z</t>
+        </is>
+      </c>
+      <c r="I2375" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="2376">
+      <c r="A2376" t="inlineStr">
+        <is>
+          <t>32350</t>
+        </is>
+      </c>
+      <c r="B2376" t="inlineStr">
+        <is>
+          <t>Petro-Canada</t>
+        </is>
+      </c>
+      <c r="C2376" t="inlineStr">
+        <is>
+          <t>132 12th St</t>
+        </is>
+      </c>
+      <c r="D2376" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.201144, 'Longitude': -122.922922}</t>
+        </is>
+      </c>
+      <c r="E2376" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:05:52</t>
+        </is>
+      </c>
+      <c r="F2376" t="inlineStr">
+        <is>
+          <t>2025-08-21T23:39:32.127Z</t>
+        </is>
+      </c>
+      <c r="G2376" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="H2376" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:54:43.702Z</t>
+        </is>
+      </c>
+      <c r="I2376" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="2377">
+      <c r="A2377" t="inlineStr">
+        <is>
+          <t>65502</t>
+        </is>
+      </c>
+      <c r="B2377" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2377" t="inlineStr">
+        <is>
+          <t>5 W 8th Ave</t>
+        </is>
+      </c>
+      <c r="D2377" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.222332, 'Longitude': -122.91267}</t>
+        </is>
+      </c>
+      <c r="E2377" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:05:52</t>
+        </is>
+      </c>
+      <c r="F2377" t="inlineStr">
+        <is>
+          <t>2025-08-22T04:02:23.919Z</t>
+        </is>
+      </c>
+      <c r="G2377" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H2377" t="inlineStr">
+        <is>
+          <t>2025-08-22T04:02:23.951Z</t>
+        </is>
+      </c>
+      <c r="I2377" t="n">
+        <v>199.9</v>
+      </c>
+    </row>
+    <row r="2378">
+      <c r="A2378" t="inlineStr">
+        <is>
+          <t>65498</t>
+        </is>
+      </c>
+      <c r="B2378" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C2378" t="inlineStr">
+        <is>
+          <t>3 E 8th Ave</t>
+        </is>
+      </c>
+      <c r="D2378" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.2228942, 'Longitude': -122.9117512}</t>
+        </is>
+      </c>
+      <c r="E2378" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:05:52</t>
+        </is>
+      </c>
+      <c r="F2378" t="inlineStr">
+        <is>
+          <t>2025-08-22T04:02:37.229Z</t>
+        </is>
+      </c>
+      <c r="G2378" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="H2378" t="inlineStr">
+        <is>
+          <t>2025-08-22T04:02:37.276Z</t>
+        </is>
+      </c>
+      <c r="I2378" t="n">
+        <v>196.9</v>
+      </c>
+    </row>
+    <row r="2379">
+      <c r="A2379" t="inlineStr">
+        <is>
+          <t>65470</t>
+        </is>
+      </c>
+      <c r="B2379" t="inlineStr">
+        <is>
+          <t>Esso</t>
+        </is>
+      </c>
+      <c r="C2379" t="inlineStr">
+        <is>
+          <t>4444 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2379" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.23030428362, 'Longitude': -123.006110787392}</t>
+        </is>
+      </c>
+      <c r="E2379" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:05:52</t>
+        </is>
+      </c>
+      <c r="F2379" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:54:27.533Z</t>
+        </is>
+      </c>
+      <c r="G2379" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2379" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:23:17.129Z</t>
+        </is>
+      </c>
+      <c r="I2379" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="2380">
+      <c r="A2380" t="inlineStr">
+        <is>
+          <t>212356</t>
+        </is>
+      </c>
+      <c r="B2380" t="inlineStr">
+        <is>
+          <t>CENTEX</t>
+        </is>
+      </c>
+      <c r="C2380" t="inlineStr">
+        <is>
+          <t>3855 Douglas Rd</t>
+        </is>
+      </c>
+      <c r="D2380" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.249718360686, 'Longitude': -122.981165650914}</t>
+        </is>
+      </c>
+      <c r="E2380" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:05:52</t>
+        </is>
+      </c>
+      <c r="F2380" t="inlineStr">
+        <is>
+          <t>2025-08-22T00:49:43.061Z</t>
+        </is>
+      </c>
+      <c r="G2380" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="H2380" t="inlineStr">
+        <is>
+          <t>2025-08-21T22:02:08.577Z</t>
+        </is>
+      </c>
+      <c r="I2380" t="n">
+        <v>195.9</v>
+      </c>
+    </row>
+    <row r="2381">
+      <c r="A2381" t="inlineStr">
+        <is>
+          <t>99601</t>
+        </is>
+      </c>
+      <c r="B2381" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C2381" t="inlineStr">
+        <is>
+          <t>4177 Kingsway</t>
+        </is>
+      </c>
+      <c r="D2381" t="inlineStr">
+        <is>
+          <t>{'Latitude': 49.232536959292, 'Longitude': -123.011408150196}</t>
+        </is>
+      </c>
+      <c r="E2381" t="inlineStr">
+        <is>
+          <t>2025-08-21 21:05:52</t>
+        </is>
+      </c>
+      <c r="F2381" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:53:02.163Z</t>
+        </is>
+      </c>
+      <c r="G2381" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="H2381" t="inlineStr">
+        <is>
+          <t>2025-08-22T03:12:46.730Z</t>
+        </is>
+      </c>
+      <c r="I2381" t="n">
+        <v>192.9</v>
       </c>
     </row>
   </sheetData>
